--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D03D30-0E17-4F8E-96BC-842CE50F02DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{440E365E-38EF-4AAF-B041-E2C0A636220D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -822,7 +822,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -874,6 +874,8 @@
     <xf numFmtId="3" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1159,12 +1161,14 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="9.140625" style="1"/>
-    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="95.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="9.140625" style="1"/>
+    <col min="10" max="10" width="9.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
     <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -1242,7 +1246,7 @@
       <c r="E3" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="23">
+      <c r="F3" s="29">
         <v>9</v>
       </c>
       <c r="G3" s="23">
@@ -1252,7 +1256,7 @@
         <v>35</v>
       </c>
       <c r="I3" s="23">
-        <f>G3-H3</f>
+        <f t="shared" ref="I3:I8" si="0">G3-H3</f>
         <v>860</v>
       </c>
       <c r="J3" s="22" t="s">
@@ -1286,7 +1290,7 @@
       <c r="E4" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="29" t="s">
         <v>42</v>
       </c>
       <c r="G4" s="23">
@@ -1296,7 +1300,7 @@
         <v>30</v>
       </c>
       <c r="I4" s="23">
-        <f>G4-H4</f>
+        <f t="shared" si="0"/>
         <v>890</v>
       </c>
       <c r="J4" s="22" t="s">
@@ -1330,7 +1334,7 @@
       <c r="E5" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="29">
         <v>12</v>
       </c>
       <c r="G5" s="23">
@@ -1340,7 +1344,7 @@
         <v>30</v>
       </c>
       <c r="I5" s="23">
-        <f>G5-H5</f>
+        <f t="shared" si="0"/>
         <v>860</v>
       </c>
       <c r="J5" s="22" t="s">
@@ -1374,7 +1378,7 @@
       <c r="E6" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="29">
         <v>12</v>
       </c>
       <c r="G6" s="23">
@@ -1384,7 +1388,7 @@
         <v>30</v>
       </c>
       <c r="I6" s="23">
-        <f>G6-H6</f>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
       <c r="J6" s="22" t="s">
@@ -1418,7 +1422,7 @@
       <c r="E7" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="29">
         <v>8</v>
       </c>
       <c r="G7" s="23">
@@ -1428,7 +1432,7 @@
         <v>30</v>
       </c>
       <c r="I7" s="23">
-        <f>G7-H7</f>
+        <f t="shared" si="0"/>
         <v>470</v>
       </c>
       <c r="J7" s="22" t="s">
@@ -1462,7 +1466,7 @@
       <c r="E8" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="29">
         <v>8</v>
       </c>
       <c r="G8" s="23">
@@ -1472,7 +1476,7 @@
         <v>30</v>
       </c>
       <c r="I8" s="23">
-        <f>G8-H8</f>
+        <f t="shared" si="0"/>
         <v>860</v>
       </c>
       <c r="J8" s="22" t="s">
@@ -1506,7 +1510,7 @@
       <c r="E9" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="29">
         <v>12</v>
       </c>
       <c r="G9" s="23">
@@ -1554,7 +1558,7 @@
       <c r="E10" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="29" t="s">
         <v>62</v>
       </c>
       <c r="G10" s="23">
@@ -1564,7 +1568,7 @@
         <v>25</v>
       </c>
       <c r="I10" s="23">
-        <f>G10-H10</f>
+        <f t="shared" ref="I10:I15" si="1">G10-H10</f>
         <v>760</v>
       </c>
       <c r="J10" s="22" t="s">
@@ -1598,7 +1602,7 @@
       <c r="E11" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="29" t="s">
         <v>42</v>
       </c>
       <c r="G11" s="23">
@@ -1608,7 +1612,7 @@
         <v>30</v>
       </c>
       <c r="I11" s="23">
-        <f>G11-H11</f>
+        <f t="shared" si="1"/>
         <v>690</v>
       </c>
       <c r="J11" s="22" t="s">
@@ -1642,7 +1646,7 @@
       <c r="E12" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="29">
         <v>8</v>
       </c>
       <c r="G12" s="23">
@@ -1652,7 +1656,7 @@
         <v>30</v>
       </c>
       <c r="I12" s="23">
-        <f>G12-H12</f>
+        <f t="shared" si="1"/>
         <v>750</v>
       </c>
       <c r="J12" s="22" t="s">
@@ -1686,7 +1690,7 @@
       <c r="E13" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="29" t="s">
         <v>42</v>
       </c>
       <c r="G13" s="23">
@@ -1696,7 +1700,7 @@
         <v>30</v>
       </c>
       <c r="I13" s="23">
-        <f>G13-H13</f>
+        <f t="shared" si="1"/>
         <v>640</v>
       </c>
       <c r="J13" s="22" t="s">
@@ -1730,7 +1734,7 @@
       <c r="E14" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="29">
         <v>6</v>
       </c>
       <c r="G14" s="23">
@@ -1740,7 +1744,7 @@
         <v>25</v>
       </c>
       <c r="I14" s="23">
-        <f>G14-H14</f>
+        <f t="shared" si="1"/>
         <v>1420</v>
       </c>
       <c r="J14" s="22" t="s">
@@ -1774,7 +1778,7 @@
       <c r="E15" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="29">
         <v>9</v>
       </c>
       <c r="G15" s="23">
@@ -1784,7 +1788,7 @@
         <v>30</v>
       </c>
       <c r="I15" s="23">
-        <f>G15-H15</f>
+        <f t="shared" si="1"/>
         <v>750</v>
       </c>
       <c r="J15" s="22" t="s">
@@ -1818,7 +1822,7 @@
       <c r="E16" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="29" t="s">
         <v>42</v>
       </c>
       <c r="G16" s="23">
@@ -1866,7 +1870,7 @@
       <c r="E17" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="29">
         <v>12</v>
       </c>
       <c r="G17" s="23">
@@ -1910,7 +1914,7 @@
       <c r="E18" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="29">
         <v>2</v>
       </c>
       <c r="G18" s="23">
@@ -1954,7 +1958,7 @@
       <c r="E19" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="29">
         <v>12</v>
       </c>
       <c r="G19" s="23">
@@ -1984,7 +1988,7 @@
         <v>1</v>
       </c>
       <c r="R19" s="24">
-        <f t="shared" ref="R19:R20" si="0">H19</f>
+        <f t="shared" ref="R19:R20" si="2">H19</f>
         <v>30</v>
       </c>
     </row>
@@ -2002,7 +2006,7 @@
       <c r="E20" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="29" t="s">
         <v>93</v>
       </c>
       <c r="G20" s="23">
@@ -2032,7 +2036,7 @@
         <v>1</v>
       </c>
       <c r="R20" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
     </row>
@@ -2050,7 +2054,7 @@
       <c r="E21" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="29" t="s">
         <v>97</v>
       </c>
       <c r="G21" s="23">
@@ -2094,7 +2098,7 @@
       <c r="E22" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="29" t="s">
         <v>101</v>
       </c>
       <c r="G22" s="23">
@@ -2138,7 +2142,7 @@
       <c r="E23" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="F23" s="22" t="s">
+      <c r="F23" s="29" t="s">
         <v>93</v>
       </c>
       <c r="G23" s="23">
@@ -2182,7 +2186,7 @@
       <c r="E24" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="F24" s="22" t="s">
+      <c r="F24" s="29" t="s">
         <v>93</v>
       </c>
       <c r="G24" s="23">
@@ -2230,7 +2234,7 @@
       <c r="E25" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F25" s="22" t="s">
+      <c r="F25" s="29" t="s">
         <v>111</v>
       </c>
       <c r="G25" s="23">
@@ -2274,7 +2278,7 @@
       <c r="E26" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="F26" s="22" t="s">
+      <c r="F26" s="29" t="s">
         <v>93</v>
       </c>
       <c r="G26" s="23">
@@ -2322,7 +2326,7 @@
       <c r="E27" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="F27" s="22" t="s">
+      <c r="F27" s="29" t="s">
         <v>93</v>
       </c>
       <c r="G27" s="23">
@@ -2366,7 +2370,7 @@
       <c r="E28" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="F28" s="22" t="s">
+      <c r="F28" s="29" t="s">
         <v>93</v>
       </c>
       <c r="G28" s="23">
@@ -2414,7 +2418,7 @@
       <c r="E29" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="F29" s="22" t="s">
+      <c r="F29" s="29" t="s">
         <v>93</v>
       </c>
       <c r="G29" s="23">
@@ -2458,7 +2462,7 @@
       <c r="E30" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="F30" s="22" t="s">
+      <c r="F30" s="29" t="s">
         <v>97</v>
       </c>
       <c r="G30" s="23">
@@ -2502,7 +2506,7 @@
       <c r="E31" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="F31" s="22" t="s">
+      <c r="F31" s="29" t="s">
         <v>101</v>
       </c>
       <c r="G31" s="23">
@@ -2546,7 +2550,7 @@
       <c r="E32" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="F32" s="22" t="s">
+      <c r="F32" s="29" t="s">
         <v>101</v>
       </c>
       <c r="G32" s="23">
@@ -2590,7 +2594,7 @@
       <c r="E33" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="F33" s="23">
+      <c r="F33" s="29">
         <v>2</v>
       </c>
       <c r="G33" s="23">
@@ -2638,7 +2642,7 @@
       <c r="E34" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="F34" s="22" t="s">
+      <c r="F34" s="29" t="s">
         <v>101</v>
       </c>
       <c r="G34" s="23">
@@ -2648,7 +2652,7 @@
         <v>20</v>
       </c>
       <c r="I34" s="23">
-        <f>G34-H34</f>
+        <f t="shared" ref="I34:I41" si="3">G34-H34</f>
         <v>570</v>
       </c>
       <c r="J34" s="22" t="s">
@@ -2682,7 +2686,7 @@
       <c r="E35" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="F35" s="26">
+      <c r="F35" s="30">
         <v>2</v>
       </c>
       <c r="G35" s="26">
@@ -2692,7 +2696,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="26">
-        <f>G35-H35</f>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="J35" s="25" t="s">
@@ -2728,7 +2732,7 @@
       <c r="E36" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="F36" s="22" t="s">
+      <c r="F36" s="29" t="s">
         <v>97</v>
       </c>
       <c r="G36" s="23">
@@ -2738,7 +2742,7 @@
         <v>35</v>
       </c>
       <c r="I36" s="23">
-        <f>G36-H36</f>
+        <f t="shared" si="3"/>
         <v>1130</v>
       </c>
       <c r="J36" s="22" t="s">
@@ -2772,7 +2776,7 @@
       <c r="E37" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="F37" s="22" t="s">
+      <c r="F37" s="29" t="s">
         <v>93</v>
       </c>
       <c r="G37" s="23">
@@ -2782,7 +2786,7 @@
         <v>35</v>
       </c>
       <c r="I37" s="23">
-        <f>G37-H37</f>
+        <f t="shared" si="3"/>
         <v>2950</v>
       </c>
       <c r="J37" s="22" t="s">
@@ -2816,7 +2820,7 @@
       <c r="E38" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="F38" s="22" t="s">
+      <c r="F38" s="29" t="s">
         <v>150</v>
       </c>
       <c r="G38" s="23">
@@ -2826,7 +2830,7 @@
         <v>35</v>
       </c>
       <c r="I38" s="23">
-        <f>G38-H38</f>
+        <f t="shared" si="3"/>
         <v>1110</v>
       </c>
       <c r="J38" s="22" t="s">
@@ -2860,7 +2864,7 @@
       <c r="E39" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="F39" s="22" t="s">
+      <c r="F39" s="29" t="s">
         <v>155</v>
       </c>
       <c r="G39" s="23">
@@ -2870,7 +2874,7 @@
         <v>35</v>
       </c>
       <c r="I39" s="23">
-        <f>G39-H39</f>
+        <f t="shared" si="3"/>
         <v>640</v>
       </c>
       <c r="J39" s="22" t="s">
@@ -2904,7 +2908,7 @@
       <c r="E40" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="F40" s="23">
+      <c r="F40" s="29">
         <v>5</v>
       </c>
       <c r="G40" s="23">
@@ -2914,7 +2918,7 @@
         <v>25</v>
       </c>
       <c r="I40" s="23">
-        <f>G40-H40</f>
+        <f t="shared" si="3"/>
         <v>760</v>
       </c>
       <c r="J40" s="22" t="s">
@@ -2948,7 +2952,7 @@
       <c r="E41" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="F41" s="23">
+      <c r="F41" s="29">
         <v>1</v>
       </c>
       <c r="G41" s="23">
@@ -2958,7 +2962,7 @@
         <v>25</v>
       </c>
       <c r="I41" s="23">
-        <f>G41-H41</f>
+        <f t="shared" si="3"/>
         <v>700</v>
       </c>
       <c r="J41" s="22" t="s">
@@ -2992,7 +2996,7 @@
       <c r="E42" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="F42" s="23">
+      <c r="F42" s="29">
         <v>5</v>
       </c>
       <c r="G42" s="23">
@@ -3040,7 +3044,7 @@
       <c r="E43" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="F43" s="23">
+      <c r="F43" s="29">
         <v>3</v>
       </c>
       <c r="G43" s="23">
@@ -3084,7 +3088,7 @@
       <c r="E44" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="F44" s="23">
+      <c r="F44" s="29">
         <v>3</v>
       </c>
       <c r="G44" s="23">
@@ -3128,7 +3132,7 @@
       <c r="E45" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="F45" s="23">
+      <c r="F45" s="29">
         <v>7</v>
       </c>
       <c r="G45" s="23">
@@ -3172,7 +3176,7 @@
       <c r="E46" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="F46" s="22" t="s">
+      <c r="F46" s="29" t="s">
         <v>111</v>
       </c>
       <c r="G46" s="23">
@@ -3220,7 +3224,7 @@
       <c r="E47" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="F47" s="23">
+      <c r="F47" s="29">
         <v>7</v>
       </c>
       <c r="G47" s="23">
@@ -3264,7 +3268,7 @@
       <c r="E48" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="F48" s="23">
+      <c r="F48" s="29">
         <v>1</v>
       </c>
       <c r="G48" s="23">
@@ -3314,7 +3318,7 @@
       <c r="E49" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="F49" s="23">
+      <c r="F49" s="29">
         <v>7</v>
       </c>
       <c r="G49" s="23">
@@ -3358,7 +3362,7 @@
       <c r="E50" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="F50" s="23">
+      <c r="F50" s="29">
         <v>7</v>
       </c>
       <c r="G50" s="23">
@@ -3402,7 +3406,7 @@
       <c r="E51" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="F51" s="23">
+      <c r="F51" s="29">
         <v>7</v>
       </c>
       <c r="G51" s="23">
@@ -3446,7 +3450,7 @@
       <c r="E52" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="F52" s="23">
+      <c r="F52" s="29">
         <v>8</v>
       </c>
       <c r="G52" s="23">
@@ -3476,7 +3480,7 @@
         <v>1</v>
       </c>
       <c r="R52" s="24">
-        <f t="shared" ref="R52:R53" si="1">H52</f>
+        <f t="shared" ref="R52:R53" si="4">H52</f>
         <v>25</v>
       </c>
     </row>
@@ -3494,7 +3498,7 @@
       <c r="E53" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="F53" s="23">
+      <c r="F53" s="29">
         <v>3</v>
       </c>
       <c r="G53" s="23">
@@ -3524,7 +3528,7 @@
         <v>1</v>
       </c>
       <c r="R53" s="24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
     </row>
@@ -3542,7 +3546,7 @@
       <c r="E54" s="22" t="s">
         <v>201</v>
       </c>
-      <c r="F54" s="23">
+      <c r="F54" s="29">
         <v>4</v>
       </c>
       <c r="G54" s="23">
@@ -3586,7 +3590,7 @@
       <c r="E55" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="F55" s="23">
+      <c r="F55" s="29">
         <v>4</v>
       </c>
       <c r="G55" s="23">
@@ -3630,7 +3634,7 @@
       <c r="E56" s="22" t="s">
         <v>206</v>
       </c>
-      <c r="F56" s="23">
+      <c r="F56" s="29">
         <v>5</v>
       </c>
       <c r="G56" s="23">
@@ -3666,51 +3670,51 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G58" s="1">
-        <f>SUBTOTAL(9,G3:G57)</f>
+        <f t="shared" ref="G58:R58" si="5">SUBTOTAL(9,G3:G57)</f>
         <v>37475</v>
       </c>
       <c r="H58" s="1">
-        <f>SUBTOTAL(9,H3:H57)</f>
+        <f t="shared" si="5"/>
         <v>1520</v>
       </c>
       <c r="I58" s="1">
-        <f>SUBTOTAL(9,I3:I57)</f>
+        <f t="shared" si="5"/>
         <v>35955</v>
       </c>
       <c r="J58" s="1">
-        <f>SUBTOTAL(9,J3:J57)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K58" s="1">
-        <f>SUBTOTAL(9,K3:K57)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L58" s="1">
-        <f>SUBTOTAL(9,L3:L57)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M58" s="1">
-        <f>SUBTOTAL(9,M3:M57)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N58" s="1">
-        <f>SUBTOTAL(9,N3:N57)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O58" s="1">
-        <f>SUBTOTAL(9,O3:O57)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P58" s="1">
-        <f>SUBTOTAL(9,P3:P57)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q58" s="1">
-        <f>SUBTOTAL(9,Q3:Q57)</f>
+        <f t="shared" si="5"/>
         <v>54</v>
       </c>
       <c r="R58" s="1">
-        <f>SUBTOTAL(9,R3:R57)</f>
+        <f t="shared" si="5"/>
         <v>395</v>
       </c>
     </row>
@@ -4940,51 +4944,51 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G58" s="1">
-        <f>SUBTOTAL(9,G3:G57)</f>
+        <f t="shared" ref="G58:R58" si="0">SUBTOTAL(9,G3:G57)</f>
         <v>0</v>
       </c>
       <c r="H58" s="1">
-        <f>SUBTOTAL(9,H3:H57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I58" s="1">
-        <f>SUBTOTAL(9,I3:I57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J58" s="1">
-        <f>SUBTOTAL(9,J3:J57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K58" s="1">
-        <f>SUBTOTAL(9,K3:K57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L58" s="1">
-        <f>SUBTOTAL(9,L3:L57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M58" s="1">
-        <f>SUBTOTAL(9,M3:M57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N58" s="1">
-        <f>SUBTOTAL(9,N3:N57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O58" s="1">
-        <f>SUBTOTAL(9,O3:O57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P58" s="1">
-        <f>SUBTOTAL(9,P3:P57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q58" s="1">
-        <f>SUBTOTAL(9,Q3:Q57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R58" s="1">
-        <f>SUBTOTAL(9,R3:R57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>

--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,17 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{440E365E-38EF-4AAF-B041-E2C0A636220D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32148833-C6B8-40C6-9E96-9336EC4E3AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-5" sheetId="3" r:id="rId1"/>
-    <sheet name="2-5" sheetId="4" r:id="rId2"/>
+    <sheet name="4-5" sheetId="4" r:id="rId2"/>
+    <sheet name="5-5" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-5'!$A$2:$P$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'4-5'!$A$2:$P$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'5-5'!$A$2:$P$56</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="269">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -121,15 +123,6 @@
     <t>ĐỊA CHỈ</t>
   </si>
   <si>
-    <t>THU 7</t>
-  </si>
-  <si>
-    <t>NGAY 2-5</t>
-  </si>
-  <si>
-    <t>T7.2.5.2026</t>
-  </si>
-  <si>
     <t>THU 6</t>
   </si>
   <si>
@@ -662,6 +655,201 @@
   </si>
   <si>
     <t>135 hải thượng lãn ông P10</t>
+  </si>
+  <si>
+    <t>NGAY 4-5</t>
+  </si>
+  <si>
+    <t>THU 2</t>
+  </si>
+  <si>
+    <t>T2.4.5.2026</t>
+  </si>
+  <si>
+    <t>Hồ Thị Mỹ Hạnh</t>
+  </si>
+  <si>
+    <t>HD018199</t>
+  </si>
+  <si>
+    <t>S3.02 vinhomes garden park long bình</t>
+  </si>
+  <si>
+    <t>04-05-2026</t>
+  </si>
+  <si>
+    <t>Dạ Thảo (Hàng của Thanh đi Malaysia)</t>
+  </si>
+  <si>
+    <t>HD018104</t>
+  </si>
+  <si>
+    <t>66 đường số 17 phường 10</t>
+  </si>
+  <si>
+    <t>AT 04-05</t>
+  </si>
+  <si>
+    <t>hương</t>
+  </si>
+  <si>
+    <t>HD018201</t>
+  </si>
+  <si>
+    <t>97 đường 24A -bình trị đông b</t>
+  </si>
+  <si>
+    <t>Ngọc - fb Nguyễn Mười Ut</t>
+  </si>
+  <si>
+    <t>HD018123</t>
+  </si>
+  <si>
+    <t>45/8 đường số 8 phường bình hưng hòa A</t>
+  </si>
+  <si>
+    <t>Hạnh Huỳnh</t>
+  </si>
+  <si>
+    <t>HD018243</t>
+  </si>
+  <si>
+    <t>42A, đường Mã Lò, phường Bình Trị Đông A</t>
+  </si>
+  <si>
+    <t>Bé Bờm</t>
+  </si>
+  <si>
+    <t>HD018225</t>
+  </si>
+  <si>
+    <t>167/10 Đào Sư Tích, Phước Kiển</t>
+  </si>
+  <si>
+    <t>Quế Trân Nguyễn</t>
+  </si>
+  <si>
+    <t>HD018214</t>
+  </si>
+  <si>
+    <t>145 Nguyễn Cửu Đàm - Tân Sơn Nhì</t>
+  </si>
+  <si>
+    <t>Bé My</t>
+  </si>
+  <si>
+    <t>HD017792</t>
+  </si>
+  <si>
+    <t>304/45 đường số 8 bình hưng hoà a</t>
+  </si>
+  <si>
+    <t>chip chip</t>
+  </si>
+  <si>
+    <t>HD018274</t>
+  </si>
+  <si>
+    <t>71/16 thới an 16</t>
+  </si>
+  <si>
+    <t>My Nguyễn</t>
+  </si>
+  <si>
+    <t>HD018234</t>
+  </si>
+  <si>
+    <t>256/33 liên khu 4 - 5 - Bình Hưng Hòa B</t>
+  </si>
+  <si>
+    <t>Hoàng Trinh</t>
+  </si>
+  <si>
+    <t>HD018238</t>
+  </si>
+  <si>
+    <t>71/1/33.Nguyễn van Thuong p Thạnh mỹ tây</t>
+  </si>
+  <si>
+    <t>chi hương fb Kim Tien Phan</t>
+  </si>
+  <si>
+    <t>HD018239</t>
+  </si>
+  <si>
+    <t>328 đường số 8 thông tây hội</t>
+  </si>
+  <si>
+    <t>Kim Anh</t>
+  </si>
+  <si>
+    <t>HD018216</t>
+  </si>
+  <si>
+    <t>124/83/1 xô viết nghệ tĩnh p21</t>
+  </si>
+  <si>
+    <t>TRANG TRẦN 2</t>
+  </si>
+  <si>
+    <t>1122/23/7 quang trung phường 8</t>
+  </si>
+  <si>
+    <t>Qn Nguyễn</t>
+  </si>
+  <si>
+    <t>189/46a Bạch Đằng, phường Hạnh Thông</t>
+  </si>
+  <si>
+    <t>NIKI VIJANDRE + Air Shipment + Mien Tran</t>
+  </si>
+  <si>
+    <t>14 Lam Thi Ho, Tan Chanh Hiep Ward</t>
+  </si>
+  <si>
+    <t>Ngọc Thủy</t>
+  </si>
+  <si>
+    <t>41 Mạc Đĩnh Chi, đakao, P1</t>
+  </si>
+  <si>
+    <t>Mã Thục Phối</t>
+  </si>
+  <si>
+    <t>HD016561</t>
+  </si>
+  <si>
+    <t>156 hàn hải nguyên f8</t>
+  </si>
+  <si>
+    <t>Ngọc Tuyền</t>
+  </si>
+  <si>
+    <t>HD018193</t>
+  </si>
+  <si>
+    <t>Saigon Royal OT2</t>
+  </si>
+  <si>
+    <t>Người nhận chuột</t>
+  </si>
+  <si>
+    <t>HD018256</t>
+  </si>
+  <si>
+    <t>số 229A Đường bùi thị xuân phường 1</t>
+  </si>
+  <si>
+    <t>đơn trả 5.5</t>
+  </si>
+  <si>
+    <t>THU 3</t>
+  </si>
+  <si>
+    <t>NGAY 5-5</t>
+  </si>
+  <si>
+    <t>T3.5.5.2026</t>
   </si>
 </sst>
 </file>
@@ -1175,10 +1363,10 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -1234,17 +1422,17 @@
     </row>
     <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D3" s="22"/>
       <c r="E3" s="22" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F3" s="29">
         <v>9</v>
@@ -1260,13 +1448,13 @@
         <v>860</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K3" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="22"/>
@@ -1279,19 +1467,19 @@
     <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C4" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="29" t="s">
         <v>39</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="29" t="s">
-        <v>42</v>
       </c>
       <c r="G4" s="23">
         <v>920</v>
@@ -1304,13 +1492,13 @@
         <v>890</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K4" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L4" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
@@ -1323,16 +1511,16 @@
     <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="22"/>
       <c r="B5" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F5" s="29">
         <v>12</v>
@@ -1348,13 +1536,13 @@
         <v>860</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K5" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L5" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M5" s="22"/>
       <c r="N5" s="22"/>
@@ -1367,16 +1555,16 @@
     <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="22"/>
       <c r="B6" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F6" s="29">
         <v>12</v>
@@ -1392,13 +1580,13 @@
         <v>350</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K6" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L6" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="22"/>
@@ -1411,16 +1599,16 @@
     <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="22"/>
       <c r="B7" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F7" s="29">
         <v>8</v>
@@ -1436,13 +1624,13 @@
         <v>470</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M7" s="22"/>
       <c r="N7" s="22"/>
@@ -1455,16 +1643,16 @@
     <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="22"/>
       <c r="B8" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F8" s="29">
         <v>8</v>
@@ -1480,13 +1668,13 @@
         <v>860</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K8" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M8" s="22"/>
       <c r="N8" s="22"/>
@@ -1499,16 +1687,16 @@
     <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="22"/>
       <c r="B9" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F9" s="29">
         <v>12</v>
@@ -1524,13 +1712,13 @@
         <v>-30</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -1547,19 +1735,19 @@
     <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22"/>
       <c r="B10" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C10" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="29" t="s">
         <v>59</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="29" t="s">
-        <v>62</v>
       </c>
       <c r="G10" s="23">
         <v>785</v>
@@ -1572,13 +1760,13 @@
         <v>760</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K10" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -1591,19 +1779,19 @@
     <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="22"/>
       <c r="B11" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G11" s="23">
         <v>720</v>
@@ -1616,13 +1804,13 @@
         <v>690</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K11" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
@@ -1635,16 +1823,16 @@
     <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="22"/>
       <c r="B12" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F12" s="29">
         <v>8</v>
@@ -1660,13 +1848,13 @@
         <v>750</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K12" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
@@ -1679,19 +1867,19 @@
     <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="22"/>
       <c r="B13" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F13" s="29" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G13" s="23">
         <v>670</v>
@@ -1704,13 +1892,13 @@
         <v>640</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K13" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M13" s="22"/>
       <c r="N13" s="22"/>
@@ -1723,16 +1911,16 @@
     <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="22"/>
       <c r="B14" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F14" s="29">
         <v>6</v>
@@ -1748,13 +1936,13 @@
         <v>1420</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K14" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M14" s="22"/>
       <c r="N14" s="22"/>
@@ -1767,16 +1955,16 @@
     <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="22"/>
       <c r="B15" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F15" s="29">
         <v>9</v>
@@ -1792,13 +1980,13 @@
         <v>750</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K15" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M15" s="22"/>
       <c r="N15" s="22"/>
@@ -1811,19 +1999,19 @@
     <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="22"/>
       <c r="B16" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G16" s="23">
         <v>0</v>
@@ -1836,13 +2024,13 @@
         <v>-30</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K16" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M16" s="22"/>
       <c r="N16" s="22"/>
@@ -1859,16 +2047,16 @@
     <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="22"/>
       <c r="B17" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F17" s="29">
         <v>12</v>
@@ -1884,13 +2072,13 @@
         <v>660</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K17" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M17" s="22"/>
       <c r="N17" s="22"/>
@@ -1903,16 +2091,16 @@
     <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="22"/>
       <c r="B18" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F18" s="29">
         <v>2</v>
@@ -1928,13 +2116,13 @@
         <v>790</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K18" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M18" s="22"/>
       <c r="N18" s="22"/>
@@ -1947,16 +2135,16 @@
     <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="22"/>
       <c r="B19" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F19" s="29">
         <v>12</v>
@@ -1972,13 +2160,13 @@
         <v>-30</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K19" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M19" s="22"/>
       <c r="N19" s="22"/>
@@ -1995,19 +2183,19 @@
     <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="22"/>
       <c r="B20" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C20" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" s="29" t="s">
         <v>90</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="F20" s="29" t="s">
-        <v>93</v>
       </c>
       <c r="G20" s="23">
         <v>0</v>
@@ -2020,13 +2208,13 @@
         <v>-40</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K20" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
@@ -2043,19 +2231,19 @@
     <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="22"/>
       <c r="B21" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C21" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F21" s="29" t="s">
         <v>94</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="F21" s="29" t="s">
-        <v>97</v>
       </c>
       <c r="G21" s="23">
         <v>690</v>
@@ -2068,13 +2256,13 @@
         <v>660</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K21" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M21" s="22"/>
       <c r="N21" s="22"/>
@@ -2087,19 +2275,19 @@
     <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="22"/>
       <c r="B22" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C22" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="F22" s="29" t="s">
         <v>98</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="F22" s="29" t="s">
-        <v>101</v>
       </c>
       <c r="G22" s="23">
         <v>660</v>
@@ -2112,13 +2300,13 @@
         <v>640</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K22" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M22" s="22"/>
       <c r="N22" s="22"/>
@@ -2131,19 +2319,19 @@
     <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="22"/>
       <c r="B23" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F23" s="29" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G23" s="23">
         <v>375</v>
@@ -2156,13 +2344,13 @@
         <v>350</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K23" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M23" s="22"/>
       <c r="N23" s="22"/>
@@ -2175,19 +2363,19 @@
     <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="22"/>
       <c r="B24" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F24" s="29" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G24" s="23">
         <v>0</v>
@@ -2200,13 +2388,13 @@
         <v>-25</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K24" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M24" s="22"/>
       <c r="N24" s="22"/>
@@ -2223,19 +2411,19 @@
     <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="22"/>
       <c r="B25" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C25" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="F25" s="29" t="s">
         <v>108</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="F25" s="29" t="s">
-        <v>111</v>
       </c>
       <c r="G25" s="23">
         <v>725</v>
@@ -2248,13 +2436,13 @@
         <v>700</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K25" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M25" s="22"/>
       <c r="N25" s="22"/>
@@ -2267,19 +2455,19 @@
     <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="22"/>
       <c r="B26" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F26" s="29" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G26" s="23">
         <v>0</v>
@@ -2292,13 +2480,13 @@
         <v>-25</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K26" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L26" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M26" s="22"/>
       <c r="N26" s="22"/>
@@ -2315,19 +2503,19 @@
     <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="22"/>
       <c r="B27" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F27" s="29" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G27" s="23">
         <v>1765</v>
@@ -2340,13 +2528,13 @@
         <v>1740</v>
       </c>
       <c r="J27" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K27" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M27" s="22"/>
       <c r="N27" s="22"/>
@@ -2359,19 +2547,19 @@
     <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="22"/>
       <c r="B28" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F28" s="29" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G28" s="23">
         <v>0</v>
@@ -2384,13 +2572,13 @@
         <v>-25</v>
       </c>
       <c r="J28" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K28" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L28" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
@@ -2407,19 +2595,19 @@
     <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="22"/>
       <c r="B29" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F29" s="29" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G29" s="23">
         <v>765</v>
@@ -2432,13 +2620,13 @@
         <v>740</v>
       </c>
       <c r="J29" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K29" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L29" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M29" s="22"/>
       <c r="N29" s="22"/>
@@ -2451,19 +2639,19 @@
     <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="22"/>
       <c r="B30" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F30" s="29" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G30" s="23">
         <v>820</v>
@@ -2476,13 +2664,13 @@
         <v>790</v>
       </c>
       <c r="J30" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K30" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L30" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M30" s="22"/>
       <c r="N30" s="22"/>
@@ -2495,19 +2683,19 @@
     <row r="31" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="22"/>
       <c r="B31" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F31" s="29" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G31" s="23">
         <v>740</v>
@@ -2520,13 +2708,13 @@
         <v>720</v>
       </c>
       <c r="J31" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K31" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L31" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M31" s="22"/>
       <c r="N31" s="22"/>
@@ -2539,19 +2727,19 @@
     <row r="32" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="22"/>
       <c r="B32" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F32" s="29" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G32" s="23">
         <v>770</v>
@@ -2564,13 +2752,13 @@
         <v>750</v>
       </c>
       <c r="J32" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K32" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L32" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M32" s="22"/>
       <c r="N32" s="22"/>
@@ -2583,16 +2771,16 @@
     <row r="33" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="22"/>
       <c r="B33" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F33" s="29">
         <v>2</v>
@@ -2608,13 +2796,13 @@
         <v>-30</v>
       </c>
       <c r="J33" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K33" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L33" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M33" s="22"/>
       <c r="N33" s="22"/>
@@ -2631,19 +2819,19 @@
     <row r="34" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="22"/>
       <c r="B34" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F34" s="29" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G34" s="23">
         <v>590</v>
@@ -2656,13 +2844,13 @@
         <v>570</v>
       </c>
       <c r="J34" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K34" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L34" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M34" s="22"/>
       <c r="N34" s="22"/>
@@ -2675,16 +2863,16 @@
     <row r="35" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="25"/>
       <c r="B35" s="25" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E35" s="25" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F35" s="30">
         <v>2</v>
@@ -2700,16 +2888,16 @@
         <v>80</v>
       </c>
       <c r="J35" s="25" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K35" s="25" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L35" s="25" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M35" s="25" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="N35" s="25"/>
       <c r="O35" s="25"/>
@@ -2720,20 +2908,20 @@
     </row>
     <row r="36" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D36" s="22"/>
       <c r="E36" s="22" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G36" s="23">
         <v>1165</v>
@@ -2746,13 +2934,13 @@
         <v>1130</v>
       </c>
       <c r="J36" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K36" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L36" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M36" s="22"/>
       <c r="N36" s="22"/>
@@ -2764,20 +2952,20 @@
     </row>
     <row r="37" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D37" s="22"/>
       <c r="E37" s="22" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G37" s="23">
         <v>2985</v>
@@ -2790,13 +2978,13 @@
         <v>2950</v>
       </c>
       <c r="J37" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K37" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L37" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M37" s="22"/>
       <c r="N37" s="22"/>
@@ -2809,19 +2997,19 @@
     <row r="38" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="22"/>
       <c r="B38" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C38" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="D38" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F38" s="29" t="s">
         <v>147</v>
-      </c>
-      <c r="D38" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="E38" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="F38" s="29" t="s">
-        <v>150</v>
       </c>
       <c r="G38" s="23">
         <v>1145</v>
@@ -2834,13 +3022,13 @@
         <v>1110</v>
       </c>
       <c r="J38" s="22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K38" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L38" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M38" s="22"/>
       <c r="N38" s="22"/>
@@ -2853,19 +3041,19 @@
     <row r="39" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="22"/>
       <c r="B39" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C39" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="D39" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="F39" s="29" t="s">
         <v>152</v>
-      </c>
-      <c r="D39" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="F39" s="29" t="s">
-        <v>155</v>
       </c>
       <c r="G39" s="23">
         <v>675</v>
@@ -2878,13 +3066,13 @@
         <v>640</v>
       </c>
       <c r="J39" s="22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K39" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L39" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M39" s="22"/>
       <c r="N39" s="22"/>
@@ -2897,16 +3085,16 @@
     <row r="40" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22"/>
       <c r="B40" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F40" s="29">
         <v>5</v>
@@ -2922,13 +3110,13 @@
         <v>760</v>
       </c>
       <c r="J40" s="22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K40" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L40" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M40" s="22"/>
       <c r="N40" s="22"/>
@@ -2941,16 +3129,16 @@
     <row r="41" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="22"/>
       <c r="B41" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D41" s="22" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F41" s="29">
         <v>1</v>
@@ -2966,13 +3154,13 @@
         <v>700</v>
       </c>
       <c r="J41" s="22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K41" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L41" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M41" s="22"/>
       <c r="N41" s="22"/>
@@ -2985,16 +3173,16 @@
     <row r="42" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22"/>
       <c r="B42" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F42" s="29">
         <v>5</v>
@@ -3010,13 +3198,13 @@
         <v>-25</v>
       </c>
       <c r="J42" s="22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K42" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L42" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M42" s="22"/>
       <c r="N42" s="22"/>
@@ -3033,16 +3221,16 @@
     <row r="43" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="22"/>
       <c r="B43" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F43" s="29">
         <v>3</v>
@@ -3058,13 +3246,13 @@
         <v>1560</v>
       </c>
       <c r="J43" s="22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K43" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L43" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M43" s="22"/>
       <c r="N43" s="22"/>
@@ -3077,16 +3265,16 @@
     <row r="44" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="22"/>
       <c r="B44" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F44" s="29">
         <v>3</v>
@@ -3102,13 +3290,13 @@
         <v>790</v>
       </c>
       <c r="J44" s="22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K44" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L44" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M44" s="22"/>
       <c r="N44" s="22"/>
@@ -3121,16 +3309,16 @@
     <row r="45" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="22"/>
       <c r="B45" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D45" s="22" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F45" s="29">
         <v>7</v>
@@ -3146,13 +3334,13 @@
         <v>660</v>
       </c>
       <c r="J45" s="22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K45" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L45" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M45" s="22"/>
       <c r="N45" s="22"/>
@@ -3165,19 +3353,19 @@
     <row r="46" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="22"/>
       <c r="B46" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D46" s="22" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G46" s="23">
         <v>0</v>
@@ -3190,13 +3378,13 @@
         <v>-25</v>
       </c>
       <c r="J46" s="22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K46" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L46" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M46" s="22"/>
       <c r="N46" s="22"/>
@@ -3210,63 +3398,65 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="22"/>
-      <c r="B47" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C47" s="22" t="s">
-        <v>177</v>
-      </c>
-      <c r="D47" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="E47" s="22" t="s">
-        <v>179</v>
-      </c>
-      <c r="F47" s="29">
+    <row r="47" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="25"/>
+      <c r="B47" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="D47" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="E47" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="F47" s="30">
         <v>7</v>
       </c>
-      <c r="G47" s="23">
-        <v>720</v>
-      </c>
-      <c r="H47" s="23">
-        <v>30</v>
-      </c>
-      <c r="I47" s="23">
+      <c r="G47" s="26">
+        <v>60</v>
+      </c>
+      <c r="H47" s="26">
+        <v>30</v>
+      </c>
+      <c r="I47" s="26">
         <f>G47-H47</f>
-        <v>690</v>
-      </c>
-      <c r="J47" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="K47" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="L47" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="M47" s="22"/>
-      <c r="N47" s="22"/>
-      <c r="O47" s="22"/>
-      <c r="P47" s="22"/>
-      <c r="Q47" s="22">
+        <v>30</v>
+      </c>
+      <c r="J47" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="K47" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L47" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="M47" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N47" s="25"/>
+      <c r="O47" s="25"/>
+      <c r="P47" s="25"/>
+      <c r="Q47" s="25">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="22"/>
       <c r="B48" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E48" s="22" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F48" s="29">
         <v>1</v>
@@ -3282,16 +3472,16 @@
         <v>2010</v>
       </c>
       <c r="J48" s="22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K48" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L48" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M48" s="28" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="N48" s="22"/>
       <c r="O48" s="22"/>
@@ -3307,16 +3497,16 @@
     <row r="49" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="22"/>
       <c r="B49" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E49" s="22" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F49" s="29">
         <v>7</v>
@@ -3332,13 +3522,13 @@
         <v>1770</v>
       </c>
       <c r="J49" s="22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K49" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L49" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M49" s="22"/>
       <c r="N49" s="22"/>
@@ -3351,16 +3541,16 @@
     <row r="50" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="22"/>
       <c r="B50" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E50" s="22" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F50" s="29">
         <v>7</v>
@@ -3376,13 +3566,13 @@
         <v>740</v>
       </c>
       <c r="J50" s="22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K50" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L50" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M50" s="22"/>
       <c r="N50" s="22"/>
@@ -3395,16 +3585,16 @@
     <row r="51" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="22"/>
       <c r="B51" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D51" s="22" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F51" s="29">
         <v>7</v>
@@ -3420,13 +3610,13 @@
         <v>740</v>
       </c>
       <c r="J51" s="22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K51" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L51" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M51" s="22"/>
       <c r="N51" s="22"/>
@@ -3439,16 +3629,16 @@
     <row r="52" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="22"/>
       <c r="B52" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D52" s="22" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F52" s="29">
         <v>8</v>
@@ -3464,13 +3654,13 @@
         <v>-25</v>
       </c>
       <c r="J52" s="22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K52" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L52" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M52" s="22"/>
       <c r="N52" s="22"/>
@@ -3487,16 +3677,16 @@
     <row r="53" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="22"/>
       <c r="B53" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D53" s="22" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F53" s="29">
         <v>3</v>
@@ -3512,13 +3702,13 @@
         <v>-25</v>
       </c>
       <c r="J53" s="22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K53" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L53" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M53" s="22"/>
       <c r="N53" s="22"/>
@@ -3535,16 +3725,16 @@
     <row r="54" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="22"/>
       <c r="B54" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D54" s="22" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F54" s="29">
         <v>4</v>
@@ -3560,13 +3750,13 @@
         <v>790</v>
       </c>
       <c r="J54" s="22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K54" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L54" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M54" s="22"/>
       <c r="N54" s="22"/>
@@ -3579,16 +3769,16 @@
     <row r="55" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="22"/>
       <c r="B55" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D55" s="22" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E55" s="22" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F55" s="29">
         <v>4</v>
@@ -3604,13 +3794,13 @@
         <v>790</v>
       </c>
       <c r="J55" s="22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K55" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L55" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M55" s="22"/>
       <c r="N55" s="22"/>
@@ -3622,17 +3812,17 @@
     </row>
     <row r="56" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="22" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D56" s="22"/>
       <c r="E56" s="22" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F56" s="29">
         <v>5</v>
@@ -3648,13 +3838,13 @@
         <v>-30</v>
       </c>
       <c r="J56" s="22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K56" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L56" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M56" s="22"/>
       <c r="N56" s="22"/>
@@ -3671,7 +3861,7 @@
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G58" s="1">
         <f t="shared" ref="G58:R58" si="5">SUBTOTAL(9,G3:G57)</f>
-        <v>37475</v>
+        <v>36815</v>
       </c>
       <c r="H58" s="1">
         <f t="shared" si="5"/>
@@ -3679,7 +3869,7 @@
       </c>
       <c r="I58" s="1">
         <f t="shared" si="5"/>
-        <v>35955</v>
+        <v>35295</v>
       </c>
       <c r="J58" s="1">
         <f t="shared" si="5"/>
@@ -3720,7 +3910,7 @@
     </row>
     <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H62" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>15</v>
@@ -3735,7 +3925,7 @@
       </c>
       <c r="I63" s="8">
         <f>SUM(I57:I61)</f>
-        <v>35955</v>
+        <v>35295</v>
       </c>
       <c r="J63" s="8">
         <f>Q58</f>
@@ -3802,7 +3992,7 @@
       </c>
       <c r="I70" s="16">
         <f>SUM(I63:I69)</f>
-        <v>36350</v>
+        <v>35690</v>
       </c>
       <c r="J70" s="16">
         <f>SUM(J63:J67)</f>
@@ -3822,6 +4012,1129 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC23166D-647F-4247-A049-709567A97092}">
+  <dimension ref="A1:R36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="F3" s="23">
+        <v>9</v>
+      </c>
+      <c r="G3" s="23">
+        <v>60</v>
+      </c>
+      <c r="H3" s="23">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f>G3-H3</f>
+        <v>30</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M3" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="F4" s="23">
+        <v>6</v>
+      </c>
+      <c r="G4" s="23">
+        <v>0</v>
+      </c>
+      <c r="H4" s="23">
+        <v>25</v>
+      </c>
+      <c r="I4" s="23">
+        <f>-H4</f>
+        <v>-25</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="23">
+        <v>0</v>
+      </c>
+      <c r="H5" s="23">
+        <v>30</v>
+      </c>
+      <c r="I5" s="23">
+        <f>-H5</f>
+        <v>-30</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M5" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="23">
+        <v>0</v>
+      </c>
+      <c r="H6" s="23">
+        <v>30</v>
+      </c>
+      <c r="I6" s="23">
+        <f>-H6</f>
+        <v>-30</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="23">
+        <v>820</v>
+      </c>
+      <c r="H7" s="23">
+        <v>30</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" ref="I7:I12" si="0">G7-H7</f>
+        <v>790</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="G8" s="23">
+        <v>35</v>
+      </c>
+      <c r="H8" s="23">
+        <v>35</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M8" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="23">
+        <v>985</v>
+      </c>
+      <c r="H9" s="23">
+        <v>25</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>232</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="23">
+        <v>1430</v>
+      </c>
+      <c r="H10" s="23">
+        <v>30</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="F11" s="23">
+        <v>12</v>
+      </c>
+      <c r="G11" s="23">
+        <v>890</v>
+      </c>
+      <c r="H11" s="23">
+        <v>30</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="23">
+        <v>770</v>
+      </c>
+      <c r="H12" s="23">
+        <v>30</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G13" s="23">
+        <v>0</v>
+      </c>
+      <c r="H13" s="23">
+        <v>20</v>
+      </c>
+      <c r="I13" s="23">
+        <f>-H13</f>
+        <v>-20</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="23">
+        <v>905</v>
+      </c>
+      <c r="H14" s="23">
+        <v>25</v>
+      </c>
+      <c r="I14" s="23">
+        <f>G14-H14</f>
+        <v>880</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="23">
+        <v>0</v>
+      </c>
+      <c r="H15" s="23">
+        <v>20</v>
+      </c>
+      <c r="I15" s="23">
+        <f>-H15</f>
+        <v>-20</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="23">
+        <v>0</v>
+      </c>
+      <c r="H16" s="23">
+        <v>40</v>
+      </c>
+      <c r="I16" s="23">
+        <f>-H16</f>
+        <v>-40</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="23">
+        <v>1720</v>
+      </c>
+      <c r="H17" s="23">
+        <v>30</v>
+      </c>
+      <c r="I17" s="23">
+        <f>G17-H17</f>
+        <v>1690</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="F18" s="23">
+        <v>12</v>
+      </c>
+      <c r="G18" s="23">
+        <v>50</v>
+      </c>
+      <c r="H18" s="23">
+        <v>50</v>
+      </c>
+      <c r="I18" s="23">
+        <f>G18-H18</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="F19" s="23">
+        <v>1</v>
+      </c>
+      <c r="G19" s="23">
+        <v>0</v>
+      </c>
+      <c r="H19" s="23">
+        <v>25</v>
+      </c>
+      <c r="I19" s="23">
+        <f>-H19</f>
+        <v>-25</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M19" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="F20" s="23">
+        <v>11</v>
+      </c>
+      <c r="G20" s="23">
+        <v>615</v>
+      </c>
+      <c r="H20" s="23">
+        <v>25</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" ref="I20:I22" si="1">G20-H20</f>
+        <v>590</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="F21" s="23">
+        <v>4</v>
+      </c>
+      <c r="G21" s="23">
+        <v>815</v>
+      </c>
+      <c r="H21" s="23">
+        <v>25</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="1"/>
+        <v>790</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G22" s="23">
+        <v>765</v>
+      </c>
+      <c r="H22" s="23">
+        <v>25</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="1"/>
+        <v>740</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G24" s="1">
+        <f>SUBTOTAL(9,G3:G23)</f>
+        <v>9860</v>
+      </c>
+      <c r="H24" s="1">
+        <f>SUBTOTAL(9,H3:H23)</f>
+        <v>580</v>
+      </c>
+      <c r="I24" s="1">
+        <f>SUBTOTAL(9,I3:I23)</f>
+        <v>9280</v>
+      </c>
+      <c r="J24" s="1">
+        <f>SUBTOTAL(9,J3:J23)</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <f>SUBTOTAL(9,K3:K23)</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
+        <f>SUBTOTAL(9,L3:L23)</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="1">
+        <f>SUBTOTAL(9,M3:M23)</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="1">
+        <f>SUBTOTAL(9,N3:N23)</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="1">
+        <f>SUBTOTAL(9,O3:O23)</f>
+        <v>0</v>
+      </c>
+      <c r="P24" s="1">
+        <f>SUBTOTAL(9,P3:P23)</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="1">
+        <f>SUBTOTAL(9,Q3:Q23)</f>
+        <v>20</v>
+      </c>
+      <c r="R24" s="1">
+        <f>SUBTOTAL(9,R3:R23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I25" s="1">
+        <v>-3055</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H28" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="8">
+        <f>SUM(I23:I27)</f>
+        <v>6225</v>
+      </c>
+      <c r="J29" s="8">
+        <f>Q24</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H30" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="10">
+        <f>R24</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="11"/>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H31" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" s="10">
+        <f>S23</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="11"/>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H32" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I32" s="10">
+        <f>T23</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="11"/>
+    </row>
+    <row r="33" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H33" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" s="10">
+        <f>U23</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="11"/>
+    </row>
+    <row r="34" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H34" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+    </row>
+    <row r="35" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H35" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+    </row>
+    <row r="36" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H36" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="16">
+        <f>SUM(I29:I35)</f>
+        <v>6225</v>
+      </c>
+      <c r="J36" s="16">
+        <f>SUM(J29:J33)</f>
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P22" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P22">
+      <sortCondition ref="J2:J22"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03AB5974-9CA3-40AA-9389-A33FB2F60527}">
   <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3838,10 +5151,10 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>266</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -4994,7 +6307,7 @@
     </row>
     <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H62" s="4" t="s">
-        <v>28</v>
+        <v>268</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>15</v>

--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32148833-C6B8-40C6-9E96-9336EC4E3AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666B0499-C917-413B-9DEF-ADFFAE18DBD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,11 +16,13 @@
     <sheet name="1-5" sheetId="3" r:id="rId1"/>
     <sheet name="4-5" sheetId="4" r:id="rId2"/>
     <sheet name="5-5" sheetId="5" r:id="rId3"/>
+    <sheet name="6-5" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-5'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'4-5'!$A$2:$P$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'5-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'5-5'!$A$2:$P$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'6-5'!$A$2:$P$56</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="422">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -850,6 +852,465 @@
   </si>
   <si>
     <t>T3.5.5.2026</t>
+  </si>
+  <si>
+    <t>T4.6.5.2026</t>
+  </si>
+  <si>
+    <t>THU 4</t>
+  </si>
+  <si>
+    <t>NGAY 6-5</t>
+  </si>
+  <si>
+    <t>Lan Anh Nguyễn</t>
+  </si>
+  <si>
+    <t>HD018539</t>
+  </si>
+  <si>
+    <t>70 đường số 1 KDC nam long</t>
+  </si>
+  <si>
+    <t>AT 05-05</t>
+  </si>
+  <si>
+    <t>05-05-2026</t>
+  </si>
+  <si>
+    <t>Giáng Hương</t>
+  </si>
+  <si>
+    <t>HD018400</t>
+  </si>
+  <si>
+    <t>111 đường số 10 phường 13</t>
+  </si>
+  <si>
+    <t>Hiểu My</t>
+  </si>
+  <si>
+    <t>HD018563</t>
+  </si>
+  <si>
+    <t>Toà 2, chung cư river panorama, 20 lê thị chợ, phường phú thuận</t>
+  </si>
+  <si>
+    <t>Nhung Bùi</t>
+  </si>
+  <si>
+    <t>H0018373</t>
+  </si>
+  <si>
+    <t>409/108/32/14c huynh thị hai, tân chánh hiệp</t>
+  </si>
+  <si>
+    <t>C. Phương fb Nuory Le</t>
+  </si>
+  <si>
+    <t>HD018435</t>
+  </si>
+  <si>
+    <t>A28/1Dw3 quốc lộ 50 ấp 1 xã bình hưng</t>
+  </si>
+  <si>
+    <t>ny nhỏ</t>
+  </si>
+  <si>
+    <t>HD018341</t>
+  </si>
+  <si>
+    <t>49 le quang kim p8</t>
+  </si>
+  <si>
+    <t>Hoàng Bảo Trân</t>
+  </si>
+  <si>
+    <t>HD018387</t>
+  </si>
+  <si>
+    <t>2/11 đường thiên phước, p9</t>
+  </si>
+  <si>
+    <t>Lê Thị Minh Phượng</t>
+  </si>
+  <si>
+    <t>HD018553</t>
+  </si>
+  <si>
+    <t>155/14 đs 11 bình hưng hoà</t>
+  </si>
+  <si>
+    <t>Tuyết Nhi</t>
+  </si>
+  <si>
+    <t>HD018231</t>
+  </si>
+  <si>
+    <t>100/17 liên khu 1-6 bình trị đông</t>
+  </si>
+  <si>
+    <t>hàng của Đào Ngọc Bích</t>
+  </si>
+  <si>
+    <t>HD018540</t>
+  </si>
+  <si>
+    <t>007 Lộ B chung cư Tây Thạnh, phường Tân Thạnh</t>
+  </si>
+  <si>
+    <t>Việt Anh - fb Hồ Thị Uyên</t>
+  </si>
+  <si>
+    <t>HD018388</t>
+  </si>
+  <si>
+    <t>350/27 Lê Văn Quới, Bình Hưng Hòa A</t>
+  </si>
+  <si>
+    <t>cô dung fb Nini Thach</t>
+  </si>
+  <si>
+    <t>HD018521</t>
+  </si>
+  <si>
+    <t>137/74a âu dương lân - p2</t>
+  </si>
+  <si>
+    <t>Mi Ni</t>
+  </si>
+  <si>
+    <t>HD018437</t>
+  </si>
+  <si>
+    <t>536/32/23 âu cơ</t>
+  </si>
+  <si>
+    <t>HD018486</t>
+  </si>
+  <si>
+    <t>Châu Châu</t>
+  </si>
+  <si>
+    <t>HD018490</t>
+  </si>
+  <si>
+    <t>E3/8 ấp 56 xã vĩnh lộc</t>
+  </si>
+  <si>
+    <t>Thanh Xuân</t>
+  </si>
+  <si>
+    <t>HD018565</t>
+  </si>
+  <si>
+    <t>17/4B Liên khu 5-6 bình hưng hòa b</t>
+  </si>
+  <si>
+    <t>Hồng My</t>
+  </si>
+  <si>
+    <t>HD018549</t>
+  </si>
+  <si>
+    <t>192 Phạm Đức Sơn, Phường 16 (Chung Cư Heaven Riverview - Mỹ Phúc) Block B</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hải</t>
+  </si>
+  <si>
+    <t>17 Đường Số 13 Bình Hưng Hoà</t>
+  </si>
+  <si>
+    <t>My Luu</t>
+  </si>
+  <si>
+    <t>HD018546</t>
+  </si>
+  <si>
+    <t>Toà T1, chung cư Vista Verde, số 8 Nguyễn Thanh Sơn, phường Cát Lái</t>
+  </si>
+  <si>
+    <t>gộp, đổi hàng</t>
+  </si>
+  <si>
+    <t>HD018552</t>
+  </si>
+  <si>
+    <t>Thảo</t>
+  </si>
+  <si>
+    <t>HD018440</t>
+  </si>
+  <si>
+    <t>280a12 Lương Đình Của. An Phú</t>
+  </si>
+  <si>
+    <t>Nguyen Diem My</t>
+  </si>
+  <si>
+    <t>HD018321</t>
+  </si>
+  <si>
+    <t>212 lê quang định phường 14</t>
+  </si>
+  <si>
+    <t>Love May</t>
+  </si>
+  <si>
+    <t>HD018311</t>
+  </si>
+  <si>
+    <t>T4 Masteri Đường Số 10, Thảo Điền</t>
+  </si>
+  <si>
+    <t>Đinh Thị Kim Lan</t>
+  </si>
+  <si>
+    <t>HD018306</t>
+  </si>
+  <si>
+    <t>Ngân hàng Tpbank 303 (39/6) Trường Chinh P Tân Thới Nhất</t>
+  </si>
+  <si>
+    <t>Thu Ba DS</t>
+  </si>
+  <si>
+    <t>HD018302</t>
+  </si>
+  <si>
+    <t>395 Bùi Đình Tuý, p14</t>
+  </si>
+  <si>
+    <t>Ivy Dao</t>
+  </si>
+  <si>
+    <t>HD018318</t>
+  </si>
+  <si>
+    <t>238/3 trường chinh, đông hưng thuận</t>
+  </si>
+  <si>
+    <t>Mỹ Ngọc</t>
+  </si>
+  <si>
+    <t>HD018275</t>
+  </si>
+  <si>
+    <t>242 nguyễn oanh, phường gò vấp</t>
+  </si>
+  <si>
+    <t>Ly Clara Selena</t>
+  </si>
+  <si>
+    <t>403 tân sơn p12</t>
+  </si>
+  <si>
+    <t>LISA</t>
+  </si>
+  <si>
+    <t>685 tân sơn phường 12</t>
+  </si>
+  <si>
+    <t>THU TRƯƠNG</t>
+  </si>
+  <si>
+    <t>159/43/5 Đường Bạch Đằng, phường Tân Sơn Hòa</t>
+  </si>
+  <si>
+    <t>Nhung SaLin</t>
+  </si>
+  <si>
+    <t>HD018386</t>
+  </si>
+  <si>
+    <t>19a Trần Quang diệu p13</t>
+  </si>
+  <si>
+    <t>gộp</t>
+  </si>
+  <si>
+    <t>HD018538</t>
+  </si>
+  <si>
+    <t>Trâm Trang</t>
+  </si>
+  <si>
+    <t>HD018328</t>
+  </si>
+  <si>
+    <t>346 bến vân đồn p1</t>
+  </si>
+  <si>
+    <t>Nhi</t>
+  </si>
+  <si>
+    <t>HD018213</t>
+  </si>
+  <si>
+    <t>27 nguyễn hữu thọ (sunrise city toà X1) phường Tân Hưng</t>
+  </si>
+  <si>
+    <t>Trần Thục Oanh</t>
+  </si>
+  <si>
+    <t>HD018532</t>
+  </si>
+  <si>
+    <t>118 đường 3/2, p12</t>
+  </si>
+  <si>
+    <t>Trần Ngọc Thúy</t>
+  </si>
+  <si>
+    <t>HD018516</t>
+  </si>
+  <si>
+    <t>saigon mia block b cổng sau</t>
+  </si>
+  <si>
+    <t>Ngọc Vinh</t>
+  </si>
+  <si>
+    <t>HD018285</t>
+  </si>
+  <si>
+    <t>17-19 Trường Sơn P4</t>
+  </si>
+  <si>
+    <t>Miu miu quỳnh</t>
+  </si>
+  <si>
+    <t>HD018466</t>
+  </si>
+  <si>
+    <t>109 Bến Vân Đồn P9</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Bảo Loan</t>
+  </si>
+  <si>
+    <t>HD018401</t>
+  </si>
+  <si>
+    <t>tòa b2 chung cư lavida plus số 1181 nguyễn văn linh tân phong</t>
+  </si>
+  <si>
+    <t>Vy Vy</t>
+  </si>
+  <si>
+    <t>HD018348</t>
+  </si>
+  <si>
+    <t>Block B chung cư Sunrise RiverSide, Nguyễn Hữu Thọ, Phước Kiển</t>
+  </si>
+  <si>
+    <t>Ngà Ngọc</t>
+  </si>
+  <si>
+    <t>HD018269</t>
+  </si>
+  <si>
+    <t>85 phan xích long p2</t>
+  </si>
+  <si>
+    <t>phu nhuan</t>
+  </si>
+  <si>
+    <t>Elena Nguyễn</t>
+  </si>
+  <si>
+    <t>HD018325</t>
+  </si>
+  <si>
+    <t>56/41 dương ba trạc, Phường 02</t>
+  </si>
+  <si>
+    <t>HD018494</t>
+  </si>
+  <si>
+    <t>chung cư the park residence, 12 nguyễn hữu thọ phước kien nha be</t>
+  </si>
+  <si>
+    <t>Hoàng Thuý Liên</t>
+  </si>
+  <si>
+    <t>HD017772</t>
+  </si>
+  <si>
+    <t>290 an dương vương phường chợ quán</t>
+  </si>
+  <si>
+    <t>yenchau</t>
+  </si>
+  <si>
+    <t>HD018526</t>
+  </si>
+  <si>
+    <t>Chung cu Horita, lo C, Đường D4, P. Tân Hưng</t>
+  </si>
+  <si>
+    <t>Thư Ánh Võ</t>
+  </si>
+  <si>
+    <t>HD018343</t>
+  </si>
+  <si>
+    <t>5 lê thánh tôn bến nghé</t>
+  </si>
+  <si>
+    <t>Ly Sokny- 012776599</t>
+  </si>
+  <si>
+    <t>HD018248</t>
+  </si>
+  <si>
+    <t>359 phạm ngũ lão</t>
+  </si>
+  <si>
+    <t>shipper ứng tiền cho nhà xe</t>
+  </si>
+  <si>
+    <t>Tuyết</t>
+  </si>
+  <si>
+    <t>HD018429</t>
+  </si>
+  <si>
+    <t>30/18 đường số 6 KP18 Phường Vĩnh Hội</t>
+  </si>
+  <si>
+    <t>Hồng Miên</t>
+  </si>
+  <si>
+    <t>HD018250</t>
+  </si>
+  <si>
+    <t>123 đường số 11 tân kiểng tân quy</t>
+  </si>
+  <si>
+    <t>HD018376</t>
+  </si>
+  <si>
+    <t>Loan Thỏ</t>
+  </si>
+  <si>
+    <t>HD018544</t>
+  </si>
+  <si>
+    <t>81/6 Hồ thị kỷ, phường 1</t>
+  </si>
+  <si>
+    <t>FANG FANG</t>
+  </si>
+  <si>
+    <t>A75/6B/2 Bạch Đằng, Phường 2</t>
+  </si>
+  <si>
+    <t>DARAVIN</t>
+  </si>
+  <si>
+    <t>301 Phạm Ngũ Lão, Phường Phạm Ngũ Lão</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1471,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1064,6 +1525,7 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4975,51 +5437,51 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G24" s="1">
-        <f>SUBTOTAL(9,G3:G23)</f>
+        <f t="shared" ref="G24:R24" si="2">SUBTOTAL(9,G3:G23)</f>
         <v>9860</v>
       </c>
       <c r="H24" s="1">
-        <f>SUBTOTAL(9,H3:H23)</f>
+        <f t="shared" si="2"/>
         <v>580</v>
       </c>
       <c r="I24" s="1">
-        <f>SUBTOTAL(9,I3:I23)</f>
+        <f t="shared" si="2"/>
         <v>9280</v>
       </c>
       <c r="J24" s="1">
-        <f>SUBTOTAL(9,J3:J23)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K24" s="1">
-        <f>SUBTOTAL(9,K3:K23)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L24" s="1">
-        <f>SUBTOTAL(9,L3:L23)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M24" s="1">
-        <f>SUBTOTAL(9,M3:M23)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N24" s="1">
-        <f>SUBTOTAL(9,N3:N23)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O24" s="1">
-        <f>SUBTOTAL(9,O3:O23)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P24" s="1">
-        <f>SUBTOTAL(9,P3:P23)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q24" s="1">
-        <f>SUBTOTAL(9,Q3:Q23)</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="R24" s="1">
-        <f>SUBTOTAL(9,R3:R23)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -5135,6 +5597,2641 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03AB5974-9CA3-40AA-9389-A33FB2F60527}">
+  <dimension ref="A1:R69"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="25"/>
+      <c r="B3" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>272</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>274</v>
+      </c>
+      <c r="F3" s="26">
+        <v>7</v>
+      </c>
+      <c r="G3" s="26">
+        <v>30</v>
+      </c>
+      <c r="H3" s="26">
+        <v>30</v>
+      </c>
+      <c r="I3" s="26">
+        <f t="shared" ref="I3:I55" si="0">G3-H3</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="25" t="s">
+        <v>276</v>
+      </c>
+      <c r="M3" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>277</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>278</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="F4" s="23">
+        <v>6</v>
+      </c>
+      <c r="G4" s="23">
+        <v>915</v>
+      </c>
+      <c r="H4" s="23">
+        <v>25</v>
+      </c>
+      <c r="I4" s="18">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="F5" s="23">
+        <v>7</v>
+      </c>
+      <c r="G5" s="23">
+        <v>850</v>
+      </c>
+      <c r="H5" s="23">
+        <v>30</v>
+      </c>
+      <c r="I5" s="18">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="F6" s="23">
+        <v>12</v>
+      </c>
+      <c r="G6" s="23">
+        <v>670</v>
+      </c>
+      <c r="H6" s="23">
+        <v>30</v>
+      </c>
+      <c r="I6" s="18">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G7" s="23">
+        <v>1515</v>
+      </c>
+      <c r="H7" s="23">
+        <v>35</v>
+      </c>
+      <c r="I7" s="18">
+        <f t="shared" si="0"/>
+        <v>1480</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>291</v>
+      </c>
+      <c r="F8" s="23">
+        <v>8</v>
+      </c>
+      <c r="G8" s="23">
+        <v>690</v>
+      </c>
+      <c r="H8" s="23">
+        <v>30</v>
+      </c>
+      <c r="I8" s="18">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G9" s="23">
+        <v>1345</v>
+      </c>
+      <c r="H9" s="23">
+        <v>25</v>
+      </c>
+      <c r="I9" s="18">
+        <f t="shared" si="0"/>
+        <v>1320</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="23">
+        <v>850</v>
+      </c>
+      <c r="H10" s="23">
+        <v>30</v>
+      </c>
+      <c r="I10" s="18">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="23">
+        <v>830</v>
+      </c>
+      <c r="H11" s="23">
+        <v>30</v>
+      </c>
+      <c r="I11" s="18">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>303</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="23">
+        <v>0</v>
+      </c>
+      <c r="H12" s="23">
+        <v>25</v>
+      </c>
+      <c r="I12" s="18">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+      <c r="R12" s="24">
+        <f>H12</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="23">
+        <v>780</v>
+      </c>
+      <c r="H13" s="23">
+        <v>30</v>
+      </c>
+      <c r="I13" s="18">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="F14" s="23">
+        <v>8</v>
+      </c>
+      <c r="G14" s="23">
+        <v>740</v>
+      </c>
+      <c r="H14" s="23">
+        <v>30</v>
+      </c>
+      <c r="I14" s="18">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>312</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G15" s="23">
+        <v>755</v>
+      </c>
+      <c r="H15" s="23">
+        <v>25</v>
+      </c>
+      <c r="I15" s="18">
+        <f t="shared" si="0"/>
+        <v>730</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="23">
+        <v>12</v>
+      </c>
+      <c r="G16" s="23">
+        <v>770</v>
+      </c>
+      <c r="H16" s="23">
+        <v>30</v>
+      </c>
+      <c r="I16" s="18">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>316</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G17" s="23">
+        <v>735</v>
+      </c>
+      <c r="H17" s="23">
+        <v>35</v>
+      </c>
+      <c r="I17" s="18">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>318</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" s="23">
+        <v>0</v>
+      </c>
+      <c r="H18" s="23">
+        <v>30</v>
+      </c>
+      <c r="I18" s="18">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+      <c r="R18" s="24">
+        <f>H18</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>320</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>322</v>
+      </c>
+      <c r="F19" s="23">
+        <v>8</v>
+      </c>
+      <c r="G19" s="23">
+        <v>690</v>
+      </c>
+      <c r="H19" s="23">
+        <v>30</v>
+      </c>
+      <c r="I19" s="18">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>323</v>
+      </c>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22" t="s">
+        <v>324</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="23">
+        <v>0</v>
+      </c>
+      <c r="H20" s="23">
+        <v>35</v>
+      </c>
+      <c r="I20" s="18">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+      <c r="R20" s="24">
+        <f>H20</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="25"/>
+      <c r="B21" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>327</v>
+      </c>
+      <c r="F21" s="26">
+        <v>2</v>
+      </c>
+      <c r="G21" s="26">
+        <v>120</v>
+      </c>
+      <c r="H21" s="26">
+        <v>60</v>
+      </c>
+      <c r="I21" s="26">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="J21" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="25" t="s">
+        <v>276</v>
+      </c>
+      <c r="M21" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="N21" s="25"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="25"/>
+      <c r="B22" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>329</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>327</v>
+      </c>
+      <c r="F22" s="26">
+        <v>2</v>
+      </c>
+      <c r="G22" s="26">
+        <v>0</v>
+      </c>
+      <c r="H22" s="26">
+        <v>0</v>
+      </c>
+      <c r="I22" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="25" t="s">
+        <v>276</v>
+      </c>
+      <c r="M22" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="N22" s="25"/>
+      <c r="O22" s="25"/>
+      <c r="P22" s="25"/>
+      <c r="Q22" s="25">
+        <v>1</v>
+      </c>
+      <c r="R22" s="31">
+        <f>H22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>330</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>331</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>332</v>
+      </c>
+      <c r="F23" s="23">
+        <v>2</v>
+      </c>
+      <c r="G23" s="23">
+        <v>1150</v>
+      </c>
+      <c r="H23" s="23">
+        <v>30</v>
+      </c>
+      <c r="I23" s="18">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>333</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" s="23">
+        <v>820</v>
+      </c>
+      <c r="H24" s="23">
+        <v>20</v>
+      </c>
+      <c r="I24" s="18">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>336</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="F25" s="23">
+        <v>2</v>
+      </c>
+      <c r="G25" s="23">
+        <v>2120</v>
+      </c>
+      <c r="H25" s="23">
+        <v>35</v>
+      </c>
+      <c r="I25" s="18">
+        <f t="shared" si="0"/>
+        <v>2085</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M25" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+      <c r="R25" s="24">
+        <f>H25</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>339</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>341</v>
+      </c>
+      <c r="F26" s="23">
+        <v>12</v>
+      </c>
+      <c r="G26" s="23">
+        <v>0</v>
+      </c>
+      <c r="H26" s="23">
+        <v>30</v>
+      </c>
+      <c r="I26" s="18">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+      <c r="R26" s="24">
+        <f>H26</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="25"/>
+      <c r="B27" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>342</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>343</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>344</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="G27" s="26">
+        <v>0</v>
+      </c>
+      <c r="H27" s="26">
+        <v>20</v>
+      </c>
+      <c r="I27" s="26">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J27" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="K27" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="25" t="s">
+        <v>276</v>
+      </c>
+      <c r="M27" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N27" s="25"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="25">
+        <v>1</v>
+      </c>
+      <c r="R27" s="31">
+        <f>H27</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>345</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>347</v>
+      </c>
+      <c r="F28" s="23">
+        <v>12</v>
+      </c>
+      <c r="G28" s="23">
+        <v>0</v>
+      </c>
+      <c r="H28" s="23">
+        <v>30</v>
+      </c>
+      <c r="I28" s="18">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22">
+        <v>1</v>
+      </c>
+      <c r="R28" s="24">
+        <f>H28</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G29" s="23">
+        <v>1165</v>
+      </c>
+      <c r="H29" s="23">
+        <v>25</v>
+      </c>
+      <c r="I29" s="18">
+        <f t="shared" si="0"/>
+        <v>1140</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>351</v>
+      </c>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G30" s="23">
+        <v>30</v>
+      </c>
+      <c r="H30" s="23">
+        <v>30</v>
+      </c>
+      <c r="I30" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G31" s="23">
+        <v>30</v>
+      </c>
+      <c r="H31" s="23">
+        <v>30</v>
+      </c>
+      <c r="I31" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K31" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="F32" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G32" s="23">
+        <v>40</v>
+      </c>
+      <c r="H32" s="23">
+        <v>40</v>
+      </c>
+      <c r="I32" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K32" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L32" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>358</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>359</v>
+      </c>
+      <c r="F33" s="23">
+        <v>3</v>
+      </c>
+      <c r="G33" s="23">
+        <v>775</v>
+      </c>
+      <c r="H33" s="23">
+        <v>25</v>
+      </c>
+      <c r="I33" s="18">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J33" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K33" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M33" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>359</v>
+      </c>
+      <c r="F34" s="23">
+        <v>3</v>
+      </c>
+      <c r="G34" s="23">
+        <v>790</v>
+      </c>
+      <c r="H34" s="23">
+        <v>0</v>
+      </c>
+      <c r="I34" s="18">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J34" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K34" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M34" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>362</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>363</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>364</v>
+      </c>
+      <c r="F35" s="23">
+        <v>4</v>
+      </c>
+      <c r="G35" s="23">
+        <v>535</v>
+      </c>
+      <c r="H35" s="23">
+        <v>25</v>
+      </c>
+      <c r="I35" s="18">
+        <f t="shared" si="0"/>
+        <v>510</v>
+      </c>
+      <c r="J35" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K35" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M35" s="22"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>365</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="F36" s="23">
+        <v>7</v>
+      </c>
+      <c r="G36" s="23">
+        <v>820</v>
+      </c>
+      <c r="H36" s="23">
+        <v>30</v>
+      </c>
+      <c r="I36" s="18">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J36" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K36" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="22"/>
+      <c r="B37" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>368</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>369</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>370</v>
+      </c>
+      <c r="F37" s="23">
+        <v>10</v>
+      </c>
+      <c r="G37" s="23">
+        <v>2620</v>
+      </c>
+      <c r="H37" s="23">
+        <v>30</v>
+      </c>
+      <c r="I37" s="18">
+        <f t="shared" si="0"/>
+        <v>2590</v>
+      </c>
+      <c r="J37" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K37" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L37" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M37" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="22"/>
+      <c r="Q37" s="22">
+        <v>1</v>
+      </c>
+      <c r="R37" s="24">
+        <f>H37</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="22"/>
+      <c r="B38" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="D38" s="22" t="s">
+        <v>372</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>373</v>
+      </c>
+      <c r="F38" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G38" s="23">
+        <v>705</v>
+      </c>
+      <c r="H38" s="23">
+        <v>35</v>
+      </c>
+      <c r="I38" s="18">
+        <f t="shared" si="0"/>
+        <v>670</v>
+      </c>
+      <c r="J38" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K38" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M38" s="22"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="22"/>
+      <c r="P38" s="22"/>
+      <c r="Q38" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="22"/>
+      <c r="B39" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="22" t="s">
+        <v>374</v>
+      </c>
+      <c r="D39" s="22" t="s">
+        <v>375</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>376</v>
+      </c>
+      <c r="F39" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G39" s="23">
+        <v>2860</v>
+      </c>
+      <c r="H39" s="23">
+        <v>30</v>
+      </c>
+      <c r="I39" s="18">
+        <f t="shared" si="0"/>
+        <v>2830</v>
+      </c>
+      <c r="J39" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K39" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L39" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M39" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N39" s="22"/>
+      <c r="O39" s="22"/>
+      <c r="P39" s="22"/>
+      <c r="Q39" s="22">
+        <v>1</v>
+      </c>
+      <c r="R39" s="24">
+        <f>H39</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="22"/>
+      <c r="B40" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>377</v>
+      </c>
+      <c r="D40" s="22" t="s">
+        <v>378</v>
+      </c>
+      <c r="E40" s="22" t="s">
+        <v>379</v>
+      </c>
+      <c r="F40" s="23">
+        <v>4</v>
+      </c>
+      <c r="G40" s="23">
+        <v>1165</v>
+      </c>
+      <c r="H40" s="23">
+        <v>25</v>
+      </c>
+      <c r="I40" s="18">
+        <f t="shared" si="0"/>
+        <v>1140</v>
+      </c>
+      <c r="J40" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K40" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L40" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M40" s="22"/>
+      <c r="N40" s="22"/>
+      <c r="O40" s="22"/>
+      <c r="P40" s="22"/>
+      <c r="Q40" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="22"/>
+      <c r="B41" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" s="22" t="s">
+        <v>380</v>
+      </c>
+      <c r="D41" s="22" t="s">
+        <v>381</v>
+      </c>
+      <c r="E41" s="22" t="s">
+        <v>382</v>
+      </c>
+      <c r="F41" s="23">
+        <v>7</v>
+      </c>
+      <c r="G41" s="23">
+        <v>1350</v>
+      </c>
+      <c r="H41" s="23">
+        <v>30</v>
+      </c>
+      <c r="I41" s="18">
+        <f t="shared" si="0"/>
+        <v>1320</v>
+      </c>
+      <c r="J41" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K41" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L41" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M41" s="22"/>
+      <c r="N41" s="22"/>
+      <c r="O41" s="22"/>
+      <c r="P41" s="22"/>
+      <c r="Q41" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="22"/>
+      <c r="B42" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" s="22" t="s">
+        <v>383</v>
+      </c>
+      <c r="D42" s="22" t="s">
+        <v>384</v>
+      </c>
+      <c r="E42" s="22" t="s">
+        <v>385</v>
+      </c>
+      <c r="F42" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="G42" s="23">
+        <v>675</v>
+      </c>
+      <c r="H42" s="23">
+        <v>35</v>
+      </c>
+      <c r="I42" s="18">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="J42" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K42" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L42" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M42" s="22"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="22"/>
+      <c r="P42" s="22"/>
+      <c r="Q42" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="22"/>
+      <c r="B43" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" s="22" t="s">
+        <v>386</v>
+      </c>
+      <c r="D43" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="E43" s="22" t="s">
+        <v>388</v>
+      </c>
+      <c r="F43" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="G43" s="23">
+        <v>660</v>
+      </c>
+      <c r="H43" s="23">
+        <v>20</v>
+      </c>
+      <c r="I43" s="18">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="J43" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K43" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L43" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M43" s="22"/>
+      <c r="N43" s="22"/>
+      <c r="O43" s="22"/>
+      <c r="P43" s="22"/>
+      <c r="Q43" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="22"/>
+      <c r="B44" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="D44" s="22" t="s">
+        <v>391</v>
+      </c>
+      <c r="E44" s="22" t="s">
+        <v>392</v>
+      </c>
+      <c r="F44" s="23">
+        <v>8</v>
+      </c>
+      <c r="G44" s="23">
+        <v>1430</v>
+      </c>
+      <c r="H44" s="23">
+        <v>30</v>
+      </c>
+      <c r="I44" s="18">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="J44" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K44" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L44" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M44" s="22"/>
+      <c r="N44" s="22"/>
+      <c r="O44" s="22"/>
+      <c r="P44" s="22"/>
+      <c r="Q44" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="22"/>
+      <c r="B45" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="D45" s="22" t="s">
+        <v>393</v>
+      </c>
+      <c r="E45" s="22" t="s">
+        <v>394</v>
+      </c>
+      <c r="F45" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="G45" s="23">
+        <v>855</v>
+      </c>
+      <c r="H45" s="23">
+        <v>35</v>
+      </c>
+      <c r="I45" s="18">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J45" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K45" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L45" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M45" s="22"/>
+      <c r="N45" s="22"/>
+      <c r="O45" s="22"/>
+      <c r="P45" s="22"/>
+      <c r="Q45" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="22"/>
+      <c r="B46" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" s="22" t="s">
+        <v>395</v>
+      </c>
+      <c r="D46" s="22" t="s">
+        <v>396</v>
+      </c>
+      <c r="E46" s="22" t="s">
+        <v>397</v>
+      </c>
+      <c r="F46" s="23">
+        <v>5</v>
+      </c>
+      <c r="G46" s="23">
+        <v>2120</v>
+      </c>
+      <c r="H46" s="23">
+        <v>30</v>
+      </c>
+      <c r="I46" s="18">
+        <f t="shared" si="0"/>
+        <v>2090</v>
+      </c>
+      <c r="J46" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K46" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L46" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M46" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N46" s="22"/>
+      <c r="O46" s="22"/>
+      <c r="P46" s="22"/>
+      <c r="Q46" s="22">
+        <v>1</v>
+      </c>
+      <c r="R46" s="24">
+        <f>H46</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="22"/>
+      <c r="B47" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47" s="22" t="s">
+        <v>398</v>
+      </c>
+      <c r="D47" s="22" t="s">
+        <v>399</v>
+      </c>
+      <c r="E47" s="22" t="s">
+        <v>400</v>
+      </c>
+      <c r="F47" s="23">
+        <v>7</v>
+      </c>
+      <c r="G47" s="23">
+        <v>0</v>
+      </c>
+      <c r="H47" s="23">
+        <v>30</v>
+      </c>
+      <c r="I47" s="18">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J47" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K47" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L47" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M47" s="22"/>
+      <c r="N47" s="22"/>
+      <c r="O47" s="22"/>
+      <c r="P47" s="22"/>
+      <c r="Q47" s="22">
+        <v>1</v>
+      </c>
+      <c r="R47" s="24">
+        <f>H47</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="22"/>
+      <c r="B48" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>401</v>
+      </c>
+      <c r="D48" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="E48" s="22" t="s">
+        <v>403</v>
+      </c>
+      <c r="F48" s="23">
+        <v>1</v>
+      </c>
+      <c r="G48" s="23">
+        <v>535</v>
+      </c>
+      <c r="H48" s="23">
+        <v>25</v>
+      </c>
+      <c r="I48" s="18">
+        <f t="shared" si="0"/>
+        <v>510</v>
+      </c>
+      <c r="J48" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K48" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L48" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M48" s="22"/>
+      <c r="N48" s="22"/>
+      <c r="O48" s="22"/>
+      <c r="P48" s="22"/>
+      <c r="Q48" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="22"/>
+      <c r="B49" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>404</v>
+      </c>
+      <c r="D49" s="22" t="s">
+        <v>405</v>
+      </c>
+      <c r="E49" s="22" t="s">
+        <v>406</v>
+      </c>
+      <c r="F49" s="23">
+        <v>1</v>
+      </c>
+      <c r="G49" s="23">
+        <v>-180</v>
+      </c>
+      <c r="H49" s="23">
+        <v>25</v>
+      </c>
+      <c r="I49" s="18">
+        <f t="shared" si="0"/>
+        <v>-205</v>
+      </c>
+      <c r="J49" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K49" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L49" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M49" s="28" t="s">
+        <v>407</v>
+      </c>
+      <c r="N49" s="22"/>
+      <c r="O49" s="22"/>
+      <c r="P49" s="22"/>
+      <c r="Q49" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="22"/>
+      <c r="B50" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>408</v>
+      </c>
+      <c r="D50" s="22" t="s">
+        <v>409</v>
+      </c>
+      <c r="E50" s="22" t="s">
+        <v>410</v>
+      </c>
+      <c r="F50" s="23">
+        <v>4</v>
+      </c>
+      <c r="G50" s="23">
+        <v>1355</v>
+      </c>
+      <c r="H50" s="23">
+        <v>25</v>
+      </c>
+      <c r="I50" s="18">
+        <f t="shared" si="0"/>
+        <v>1330</v>
+      </c>
+      <c r="J50" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K50" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L50" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M50" s="22"/>
+      <c r="N50" s="22"/>
+      <c r="O50" s="22"/>
+      <c r="P50" s="22"/>
+      <c r="Q50" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="22"/>
+      <c r="B51" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>411</v>
+      </c>
+      <c r="D51" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="E51" s="22" t="s">
+        <v>413</v>
+      </c>
+      <c r="F51" s="23">
+        <v>7</v>
+      </c>
+      <c r="G51" s="23">
+        <v>1890</v>
+      </c>
+      <c r="H51" s="23">
+        <v>30</v>
+      </c>
+      <c r="I51" s="18">
+        <f t="shared" si="0"/>
+        <v>1860</v>
+      </c>
+      <c r="J51" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K51" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L51" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M51" s="22"/>
+      <c r="N51" s="22"/>
+      <c r="O51" s="22"/>
+      <c r="P51" s="22"/>
+      <c r="Q51" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="25"/>
+      <c r="B52" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="D52" s="25" t="s">
+        <v>414</v>
+      </c>
+      <c r="E52" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="F52" s="26">
+        <v>7</v>
+      </c>
+      <c r="G52" s="26">
+        <v>30</v>
+      </c>
+      <c r="H52" s="26">
+        <v>30</v>
+      </c>
+      <c r="I52" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="K52" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L52" s="25" t="s">
+        <v>276</v>
+      </c>
+      <c r="M52" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N52" s="25"/>
+      <c r="O52" s="25"/>
+      <c r="P52" s="25"/>
+      <c r="Q52" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="22"/>
+      <c r="B53" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="22" t="s">
+        <v>415</v>
+      </c>
+      <c r="D53" s="22" t="s">
+        <v>416</v>
+      </c>
+      <c r="E53" s="22" t="s">
+        <v>417</v>
+      </c>
+      <c r="F53" s="23">
+        <v>10</v>
+      </c>
+      <c r="G53" s="23">
+        <v>25</v>
+      </c>
+      <c r="H53" s="23">
+        <v>25</v>
+      </c>
+      <c r="I53" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K53" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L53" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M53" s="22"/>
+      <c r="N53" s="22"/>
+      <c r="O53" s="22"/>
+      <c r="P53" s="22"/>
+      <c r="Q53" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B54" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" s="22" t="s">
+        <v>418</v>
+      </c>
+      <c r="D54" s="22"/>
+      <c r="E54" s="22" t="s">
+        <v>419</v>
+      </c>
+      <c r="F54" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G54" s="23">
+        <v>750</v>
+      </c>
+      <c r="H54" s="23">
+        <v>30</v>
+      </c>
+      <c r="I54" s="18">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J54" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K54" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L54" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M54" s="22"/>
+      <c r="N54" s="22"/>
+      <c r="O54" s="22"/>
+      <c r="P54" s="22"/>
+      <c r="Q54" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B55" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22" t="s">
+        <v>421</v>
+      </c>
+      <c r="F55" s="23">
+        <v>1</v>
+      </c>
+      <c r="G55" s="23">
+        <v>0</v>
+      </c>
+      <c r="H55" s="23">
+        <v>30</v>
+      </c>
+      <c r="I55" s="18">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J55" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K55" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L55" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="M55" s="22"/>
+      <c r="N55" s="22"/>
+      <c r="O55" s="22"/>
+      <c r="P55" s="22"/>
+      <c r="Q55" s="22">
+        <v>1</v>
+      </c>
+      <c r="R55" s="24">
+        <f>H55</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G57" s="1">
+        <f>SUBTOTAL(9,G3:G56)</f>
+        <v>39405</v>
+      </c>
+      <c r="H57" s="1">
+        <f>SUBTOTAL(9,H3:H56)</f>
+        <v>1515</v>
+      </c>
+      <c r="I57" s="1">
+        <f>SUBTOTAL(9,I3:I56)</f>
+        <v>37890</v>
+      </c>
+      <c r="J57" s="1">
+        <f>SUBTOTAL(9,J3:J56)</f>
+        <v>0</v>
+      </c>
+      <c r="K57" s="1">
+        <f>SUBTOTAL(9,K3:K56)</f>
+        <v>0</v>
+      </c>
+      <c r="L57" s="1">
+        <f>SUBTOTAL(9,L3:L56)</f>
+        <v>0</v>
+      </c>
+      <c r="M57" s="1">
+        <f>SUBTOTAL(9,M3:M56)</f>
+        <v>0</v>
+      </c>
+      <c r="N57" s="1">
+        <f>SUBTOTAL(9,N3:N56)</f>
+        <v>0</v>
+      </c>
+      <c r="O57" s="1">
+        <f>SUBTOTAL(9,O3:O56)</f>
+        <v>0</v>
+      </c>
+      <c r="P57" s="1">
+        <f>SUBTOTAL(9,P3:P56)</f>
+        <v>0</v>
+      </c>
+      <c r="Q57" s="1">
+        <f>SUBTOTAL(9,Q3:Q56)</f>
+        <v>53</v>
+      </c>
+      <c r="R57" s="1">
+        <f>SUBTOTAL(9,R3:R56)</f>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H61" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H62" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I62" s="8">
+        <f>SUM(I56:I60)</f>
+        <v>37890</v>
+      </c>
+      <c r="J62" s="8">
+        <f>Q57</f>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H63" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I63" s="10">
+        <f>R57</f>
+        <v>355</v>
+      </c>
+      <c r="J63" s="11"/>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H64" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I64" s="10">
+        <f>S56</f>
+        <v>0</v>
+      </c>
+      <c r="J64" s="11"/>
+    </row>
+    <row r="65" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H65" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I65" s="10">
+        <f>T56</f>
+        <v>0</v>
+      </c>
+      <c r="J65" s="11"/>
+    </row>
+    <row r="66" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H66" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I66" s="10">
+        <f>U56</f>
+        <v>0</v>
+      </c>
+      <c r="J66" s="11"/>
+    </row>
+    <row r="67" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H67" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I67" s="13"/>
+      <c r="J67" s="13"/>
+    </row>
+    <row r="68" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H68" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+    </row>
+    <row r="69" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H69" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I69" s="16">
+        <f>SUM(I62:I68)</f>
+        <v>38245</v>
+      </c>
+      <c r="J69" s="16">
+        <f>SUM(J62:J66)</f>
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P55" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P55">
+      <sortCondition ref="J2:J55"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE07F0EA-33EE-4115-8B9A-CA76170BD361}">
   <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5151,10 +8248,10 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -6307,7 +9404,7 @@
     </row>
     <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H62" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>15</v>

--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666B0499-C917-413B-9DEF-ADFFAE18DBD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E6E4FB-56E8-4479-99D5-3277C5727F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-5" sheetId="3" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="423">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -1311,6 +1311,9 @@
   </si>
   <si>
     <t>301 Phạm Ngũ Lão, Phường Phạm Ngũ Lão</t>
+  </si>
+  <si>
+    <t>đơn lấy hàng về cho shop</t>
   </si>
 </sst>
 </file>
@@ -4478,7 +4481,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -8080,52 +8083,60 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G57" s="1">
-        <f>SUBTOTAL(9,G3:G56)</f>
+        <f t="shared" ref="G57:R57" si="1">SUBTOTAL(9,G3:G56)</f>
         <v>39405</v>
       </c>
       <c r="H57" s="1">
-        <f>SUBTOTAL(9,H3:H56)</f>
+        <f t="shared" si="1"/>
         <v>1515</v>
       </c>
       <c r="I57" s="1">
-        <f>SUBTOTAL(9,I3:I56)</f>
+        <f t="shared" si="1"/>
         <v>37890</v>
       </c>
       <c r="J57" s="1">
-        <f>SUBTOTAL(9,J3:J56)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K57" s="1">
-        <f>SUBTOTAL(9,K3:K56)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L57" s="1">
-        <f>SUBTOTAL(9,L3:L56)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M57" s="1">
-        <f>SUBTOTAL(9,M3:M56)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N57" s="1">
-        <f>SUBTOTAL(9,N3:N56)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O57" s="1">
-        <f>SUBTOTAL(9,O3:O56)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P57" s="1">
-        <f>SUBTOTAL(9,P3:P56)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q57" s="1">
-        <f>SUBTOTAL(9,Q3:Q56)</f>
+        <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="R57" s="1">
-        <f>SUBTOTAL(9,R3:R56)</f>
+        <f t="shared" si="1"/>
         <v>355</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I58" s="1">
+        <v>-30</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="61" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8145,7 +8156,7 @@
       </c>
       <c r="I62" s="8">
         <f>SUM(I56:I60)</f>
-        <v>37890</v>
+        <v>37860</v>
       </c>
       <c r="J62" s="8">
         <f>Q57</f>
@@ -8212,7 +8223,7 @@
       </c>
       <c r="I69" s="16">
         <f>SUM(I62:I68)</f>
-        <v>38245</v>
+        <v>38215</v>
       </c>
       <c r="J69" s="16">
         <f>SUM(J62:J66)</f>

--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,21 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E6E4FB-56E8-4479-99D5-3277C5727F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4652AD-69EF-4ADB-9839-8DB322F41C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-5" sheetId="3" r:id="rId1"/>
     <sheet name="4-5" sheetId="4" r:id="rId2"/>
     <sheet name="5-5" sheetId="5" r:id="rId3"/>
     <sheet name="6-5" sheetId="6" r:id="rId4"/>
+    <sheet name="7-5" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-5'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'4-5'!$A$2:$P$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'5-5'!$A$2:$P$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'6-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'6-5'!$A$2:$P$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'7-5'!$A$2:$P$56</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="521">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -1314,13 +1316,307 @@
   </si>
   <si>
     <t>đơn lấy hàng về cho shop</t>
+  </si>
+  <si>
+    <t>Cc cardinal tower B Phường Tân Phú</t>
+  </si>
+  <si>
+    <t>THU 5</t>
+  </si>
+  <si>
+    <t>NGAY 7-5</t>
+  </si>
+  <si>
+    <t>T4.7.5.2026</t>
+  </si>
+  <si>
+    <t>C Phước - fb Yến Nguyễn</t>
+  </si>
+  <si>
+    <t>HD018741</t>
+  </si>
+  <si>
+    <t>Block C 685 Âu Cơ, Chung Cư Oriental Plaza</t>
+  </si>
+  <si>
+    <t>AT 06-05</t>
+  </si>
+  <si>
+    <t>06-05-2026</t>
+  </si>
+  <si>
+    <t>Chi Kim</t>
+  </si>
+  <si>
+    <t>HD018829</t>
+  </si>
+  <si>
+    <t>68A trung mỹ tây 3, phường trung mỹ tây</t>
+  </si>
+  <si>
+    <t>Tăng Ánh Hồng</t>
+  </si>
+  <si>
+    <t>HD018739</t>
+  </si>
+  <si>
+    <t>41a phú định p16</t>
+  </si>
+  <si>
+    <t>Trúc Ly</t>
+  </si>
+  <si>
+    <t>HD018824</t>
+  </si>
+  <si>
+    <t>280 Bình Trị Đông, Phường Bình Trị Đông</t>
+  </si>
+  <si>
+    <t>Jasploy9989 (inst slideincloset)</t>
+  </si>
+  <si>
+    <t>HD018695</t>
+  </si>
+  <si>
+    <t>275/14B1 Đặng Nguyên Cẩn, Phường Phú Lâm (phường 14 cũ)</t>
+  </si>
+  <si>
+    <t>Tên dinh - fb NG Eric 0đ</t>
+  </si>
+  <si>
+    <t>HD018721</t>
+  </si>
+  <si>
+    <t>215 tên lửa, bình trị đông b</t>
+  </si>
+  <si>
+    <t>Phương Như Tiết</t>
+  </si>
+  <si>
+    <t>HD018610</t>
+  </si>
+  <si>
+    <t>8 đường 19 phường Bình Trị Đông B</t>
+  </si>
+  <si>
+    <t>Gia Linh</t>
+  </si>
+  <si>
+    <t>HD018601</t>
+  </si>
+  <si>
+    <t>100 đinh văn ước ấp5 xã hưng long</t>
+  </si>
+  <si>
+    <t>Nam Diep Hung Tue</t>
+  </si>
+  <si>
+    <t>HD018802</t>
+  </si>
+  <si>
+    <t>Chung cư Sơn Kỳ 2 số 37 đường DC 13 p Tây Thạnh</t>
+  </si>
+  <si>
+    <t>Lý Ngọc Khuyên ( 1805) fb Jessy Dang</t>
+  </si>
+  <si>
+    <t>HD018774</t>
+  </si>
+  <si>
+    <t>Toà nhà Bảy Hiền : 9 Phạm Phu Thử, nay phường Bảy Hiền (phuong 11 cũ)</t>
+  </si>
+  <si>
+    <t>Huỳnh Thị Thúy Kiều</t>
+  </si>
+  <si>
+    <t>HD018671</t>
+  </si>
+  <si>
+    <t>Chung cư zentower 34/1 ql1 phường thới an</t>
+  </si>
+  <si>
+    <t>Trân Hoàng Kỳ Châu</t>
+  </si>
+  <si>
+    <t>HD018517</t>
+  </si>
+  <si>
+    <t>Công ty TNHH GỐM sứ Kim Trúc, khu công nghiệp Tân Bình, đường số 3 lô 4, phường Tây Thạnh</t>
+  </si>
+  <si>
+    <t>TEQUILA THAO VY</t>
+  </si>
+  <si>
+    <t>426 nơ trang long</t>
+  </si>
+  <si>
+    <t>Phạm Vui</t>
+  </si>
+  <si>
+    <t>HD018823</t>
+  </si>
+  <si>
+    <t>508/16 trường chinh p13</t>
+  </si>
+  <si>
+    <t>Tâm Như</t>
+  </si>
+  <si>
+    <t>HD018669</t>
+  </si>
+  <si>
+    <t>33 Võ Văn Ngân, P.Linh Chiểu</t>
+  </si>
+  <si>
+    <t>Fb: Vân Nhung</t>
+  </si>
+  <si>
+    <t>HD018780</t>
+  </si>
+  <si>
+    <t>Cty Thế Long Express 27/5 quách văn tuấn, F12</t>
+  </si>
+  <si>
+    <t>thaoquyen tran</t>
+  </si>
+  <si>
+    <t>HD018784</t>
+  </si>
+  <si>
+    <t>21/41 bình lợi p13</t>
+  </si>
+  <si>
+    <t>Hoàng Nhung</t>
+  </si>
+  <si>
+    <t>HD018652</t>
+  </si>
+  <si>
+    <t>Chung cư Sai Gon Avenue - Đường số 11, khu phố 4, phường Tam Bình</t>
+  </si>
+  <si>
+    <t>Hoàng Thúy Triều</t>
+  </si>
+  <si>
+    <t>HD018807</t>
+  </si>
+  <si>
+    <t>477 19 nguyễn văn công p3</t>
+  </si>
+  <si>
+    <t>Charii ( inst chari_importshop )-BN2441</t>
+  </si>
+  <si>
+    <t>HD018456</t>
+  </si>
+  <si>
+    <t>163 Trương Thị Hoa, phường Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>BN182 miki chouchou Fb</t>
+  </si>
+  <si>
+    <t>HD018603</t>
+  </si>
+  <si>
+    <t>163 Đường Trương Thị Hoa, phường Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>KIM LIÊN</t>
+  </si>
+  <si>
+    <t>25/17/11 CỬU LONG PHƯỜNG 2</t>
+  </si>
+  <si>
+    <t>Su Anh</t>
+  </si>
+  <si>
+    <t>22/40 Yên Thế, P2</t>
+  </si>
+  <si>
+    <t>TOM AG</t>
+  </si>
+  <si>
+    <t>12 HỒ VĂN HUÊ PHƯỜNG 9</t>
+  </si>
+  <si>
+    <t>Tường Vi</t>
+  </si>
+  <si>
+    <t>HD018651</t>
+  </si>
+  <si>
+    <t>325 phan xích long</t>
+  </si>
+  <si>
+    <t>Lê Thảo</t>
+  </si>
+  <si>
+    <t>HD017759</t>
+  </si>
+  <si>
+    <t>3 Đặng Dung, P Tân Định</t>
+  </si>
+  <si>
+    <t>Ánh Tuyết</t>
+  </si>
+  <si>
+    <t>HD018620</t>
+  </si>
+  <si>
+    <t>23 lộc hưng p6</t>
+  </si>
+  <si>
+    <t>Michelle Nguyen (Tu Anh)</t>
+  </si>
+  <si>
+    <t>HD018799</t>
+  </si>
+  <si>
+    <t>19 Yên Thế p.2</t>
+  </si>
+  <si>
+    <t>Thiên Trang</t>
+  </si>
+  <si>
+    <t>HD018668</t>
+  </si>
+  <si>
+    <t>221 trần bình trọng p2</t>
+  </si>
+  <si>
+    <t>Phượng Nhi</t>
+  </si>
+  <si>
+    <t>HD018622</t>
+  </si>
+  <si>
+    <t>35 đặng thị nhu phường Nguyễn thái bình</t>
+  </si>
+  <si>
+    <t>Quỳnh Hương</t>
+  </si>
+  <si>
+    <t>HD018593</t>
+  </si>
+  <si>
+    <t>Saigon Royal Residence, Nguyễn Trường Tộ, phường 13</t>
+  </si>
+  <si>
+    <t>Macie Nguyen</t>
+  </si>
+  <si>
+    <t>HD018621</t>
+  </si>
+  <si>
+    <t>91 Phạm Văn Hai, f3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1388,6 +1684,14 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1474,7 +1778,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1529,6 +1833,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5600,7 +5906,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03AB5974-9CA3-40AA-9389-A33FB2F60527}">
-  <dimension ref="A1:R69"/>
+  <dimension ref="A1:R72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
@@ -8183,7 +8489,7 @@
       </c>
       <c r="J64" s="11"/>
     </row>
-    <row r="65" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H65" s="9" t="s">
         <v>20</v>
       </c>
@@ -8193,7 +8499,7 @@
       </c>
       <c r="J65" s="11"/>
     </row>
-    <row r="66" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H66" s="9" t="s">
         <v>21</v>
       </c>
@@ -8203,21 +8509,21 @@
       </c>
       <c r="J66" s="11"/>
     </row>
-    <row r="67" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H67" s="12" t="s">
         <v>22</v>
       </c>
       <c r="I67" s="13"/>
       <c r="J67" s="13"/>
     </row>
-    <row r="68" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H68" s="14" t="s">
         <v>23</v>
       </c>
       <c r="I68" s="13"/>
       <c r="J68" s="13"/>
     </row>
-    <row r="69" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H69" s="15" t="s">
         <v>24</v>
       </c>
@@ -8229,6 +8535,40 @@
         <f>SUM(J62:J66)</f>
         <v>53</v>
       </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B72" s="33"/>
+      <c r="C72" s="33"/>
+      <c r="D72" s="33" t="s">
+        <v>423</v>
+      </c>
+      <c r="E72" s="33">
+        <v>7</v>
+      </c>
+      <c r="F72" s="33">
+        <v>30</v>
+      </c>
+      <c r="G72" s="33">
+        <v>0</v>
+      </c>
+      <c r="H72" s="33">
+        <f>F72-G72</f>
+        <v>30</v>
+      </c>
+      <c r="I72" s="33"/>
+      <c r="J72" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="K72" s="32"/>
+      <c r="L72" s="32"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:P55" xr:uid="{00000000-0009-0000-0000-000006000000}">
@@ -8243,6 +8583,1701 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE07F0EA-33EE-4115-8B9A-CA76170BD361}">
+  <dimension ref="A1:R48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>427</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>428</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="23">
+        <v>0</v>
+      </c>
+      <c r="H3" s="23">
+        <v>25</v>
+      </c>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
+        <v>-25</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>430</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+      <c r="R3" s="24">
+        <f>H3</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>432</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>433</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>434</v>
+      </c>
+      <c r="F4" s="23">
+        <v>12</v>
+      </c>
+      <c r="G4" s="23">
+        <v>400</v>
+      </c>
+      <c r="H4" s="23">
+        <v>30</v>
+      </c>
+      <c r="I4" s="23">
+        <f t="shared" si="0"/>
+        <v>370</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>430</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>435</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>436</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>437</v>
+      </c>
+      <c r="F5" s="23">
+        <v>8</v>
+      </c>
+      <c r="G5" s="23">
+        <v>1060</v>
+      </c>
+      <c r="H5" s="23">
+        <v>30</v>
+      </c>
+      <c r="I5" s="23">
+        <f t="shared" si="0"/>
+        <v>1030</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>430</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>438</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>439</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>440</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="23">
+        <v>820</v>
+      </c>
+      <c r="H6" s="23">
+        <v>30</v>
+      </c>
+      <c r="I6" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>430</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>441</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>442</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>443</v>
+      </c>
+      <c r="F7" s="23">
+        <v>6</v>
+      </c>
+      <c r="G7" s="23">
+        <v>0</v>
+      </c>
+      <c r="H7" s="23">
+        <v>25</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>430</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+      <c r="R7" s="24">
+        <f>H7</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>444</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>445</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>446</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="23">
+        <v>890</v>
+      </c>
+      <c r="H8" s="23">
+        <v>30</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>430</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>447</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>448</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>449</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="23">
+        <v>850</v>
+      </c>
+      <c r="H9" s="23">
+        <v>30</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>430</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>450</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>451</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>452</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G10" s="23">
+        <v>855</v>
+      </c>
+      <c r="H10" s="23">
+        <v>35</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>430</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>453</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>454</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>455</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="23">
+        <v>1175</v>
+      </c>
+      <c r="H11" s="23">
+        <v>25</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>1150</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>430</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>456</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>457</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>458</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G12" s="23">
+        <v>715</v>
+      </c>
+      <c r="H12" s="23">
+        <v>25</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>430</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>459</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>460</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>461</v>
+      </c>
+      <c r="F13" s="23">
+        <v>12</v>
+      </c>
+      <c r="G13" s="23">
+        <v>1150</v>
+      </c>
+      <c r="H13" s="23">
+        <v>30</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>430</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>462</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>463</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>464</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="23">
+        <v>0</v>
+      </c>
+      <c r="H14" s="23">
+        <v>25</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>430</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+      <c r="R14" s="24">
+        <f>H14</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25" t="s">
+        <v>466</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="26">
+        <v>0</v>
+      </c>
+      <c r="H15" s="26">
+        <v>25</v>
+      </c>
+      <c r="I15" s="26">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J15" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="25" t="s">
+        <v>431</v>
+      </c>
+      <c r="M15" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25">
+        <v>1</v>
+      </c>
+      <c r="R15" s="31">
+        <f>H15</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>467</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>468</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>469</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G16" s="23">
+        <v>985</v>
+      </c>
+      <c r="H16" s="23">
+        <v>25</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>470</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>471</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>472</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="23">
+        <v>560</v>
+      </c>
+      <c r="H17" s="23">
+        <v>30</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
+        <v>530</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>473</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>475</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G18" s="23">
+        <v>815</v>
+      </c>
+      <c r="H18" s="23">
+        <v>25</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>476</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>477</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>478</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="23">
+        <v>1140</v>
+      </c>
+      <c r="H19" s="23">
+        <v>20</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>480</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>481</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" s="23">
+        <v>410</v>
+      </c>
+      <c r="H20" s="23">
+        <v>30</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>380</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>482</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>483</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>484</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="23">
+        <v>0</v>
+      </c>
+      <c r="H21" s="23">
+        <v>25</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+      <c r="R21" s="24">
+        <f>H21</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>485</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>486</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>487</v>
+      </c>
+      <c r="F22" s="23">
+        <v>12</v>
+      </c>
+      <c r="G22" s="23">
+        <v>0</v>
+      </c>
+      <c r="H22" s="23">
+        <v>30</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+      <c r="R22" s="24">
+        <f t="shared" ref="R22:R25" si="1">H22</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>488</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>490</v>
+      </c>
+      <c r="F23" s="23">
+        <v>12</v>
+      </c>
+      <c r="G23" s="23">
+        <v>0</v>
+      </c>
+      <c r="H23" s="23">
+        <v>30</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+      <c r="R23" s="24">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>491</v>
+      </c>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22" t="s">
+        <v>492</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="23">
+        <v>0</v>
+      </c>
+      <c r="H24" s="23">
+        <v>30</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22">
+        <v>1</v>
+      </c>
+      <c r="R24" s="24">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22" t="s">
+        <v>494</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G25" s="23">
+        <v>0</v>
+      </c>
+      <c r="H25" s="23">
+        <v>30</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+      <c r="R25" s="24">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>495</v>
+      </c>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22" t="s">
+        <v>496</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="G26" s="23">
+        <v>25</v>
+      </c>
+      <c r="H26" s="23">
+        <v>25</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>497</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>498</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>499</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="G27" s="23">
+        <v>4860</v>
+      </c>
+      <c r="H27" s="23">
+        <v>30</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="0"/>
+        <v>4830</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M27" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22">
+        <v>1</v>
+      </c>
+      <c r="R27" s="24">
+        <f>H27</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>500</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>501</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>502</v>
+      </c>
+      <c r="F28" s="23">
+        <v>1</v>
+      </c>
+      <c r="G28" s="23">
+        <v>0</v>
+      </c>
+      <c r="H28" s="23">
+        <v>25</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22">
+        <v>1</v>
+      </c>
+      <c r="R28" s="24">
+        <f>H28</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>503</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>504</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G29" s="23">
+        <v>795</v>
+      </c>
+      <c r="H29" s="23">
+        <v>25</v>
+      </c>
+      <c r="I29" s="23">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>506</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>507</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>508</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G30" s="23">
+        <v>0</v>
+      </c>
+      <c r="H30" s="23">
+        <v>25</v>
+      </c>
+      <c r="I30" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22">
+        <v>1</v>
+      </c>
+      <c r="R30" s="24">
+        <f>H30</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="25"/>
+      <c r="B31" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>509</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>510</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>511</v>
+      </c>
+      <c r="F31" s="26">
+        <v>5</v>
+      </c>
+      <c r="G31" s="26">
+        <v>25</v>
+      </c>
+      <c r="H31" s="26">
+        <v>25</v>
+      </c>
+      <c r="I31" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="K31" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" s="25" t="s">
+        <v>431</v>
+      </c>
+      <c r="M31" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N31" s="25"/>
+      <c r="O31" s="25"/>
+      <c r="P31" s="25"/>
+      <c r="Q31" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>512</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>513</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>514</v>
+      </c>
+      <c r="F32" s="23">
+        <v>1</v>
+      </c>
+      <c r="G32" s="23">
+        <v>1475</v>
+      </c>
+      <c r="H32" s="23">
+        <v>25</v>
+      </c>
+      <c r="I32" s="23">
+        <f t="shared" si="0"/>
+        <v>1450</v>
+      </c>
+      <c r="J32" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K32" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L32" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>515</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>516</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>517</v>
+      </c>
+      <c r="F33" s="23">
+        <v>4</v>
+      </c>
+      <c r="G33" s="23">
+        <v>825</v>
+      </c>
+      <c r="H33" s="23">
+        <v>25</v>
+      </c>
+      <c r="I33" s="23">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="J33" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K33" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M33" s="22"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>518</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>519</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>520</v>
+      </c>
+      <c r="F34" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G34" s="23">
+        <v>3370</v>
+      </c>
+      <c r="H34" s="23">
+        <v>30</v>
+      </c>
+      <c r="I34" s="23">
+        <f t="shared" si="0"/>
+        <v>3340</v>
+      </c>
+      <c r="J34" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K34" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="M34" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22">
+        <v>1</v>
+      </c>
+      <c r="R34" s="24">
+        <f>H34</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G36" s="1">
+        <f>SUBTOTAL(9,G3:G35)</f>
+        <v>23200</v>
+      </c>
+      <c r="H36" s="1">
+        <f>SUBTOTAL(9,H3:H35)</f>
+        <v>875</v>
+      </c>
+      <c r="I36" s="1">
+        <f>SUBTOTAL(9,I3:I35)</f>
+        <v>22325</v>
+      </c>
+      <c r="J36" s="1">
+        <f>SUBTOTAL(9,J3:J35)</f>
+        <v>0</v>
+      </c>
+      <c r="K36" s="1">
+        <f>SUBTOTAL(9,K3:K35)</f>
+        <v>0</v>
+      </c>
+      <c r="L36" s="1">
+        <f>SUBTOTAL(9,L3:L35)</f>
+        <v>0</v>
+      </c>
+      <c r="M36" s="1">
+        <f>SUBTOTAL(9,M3:M35)</f>
+        <v>0</v>
+      </c>
+      <c r="N36" s="1">
+        <f>SUBTOTAL(9,N3:N35)</f>
+        <v>0</v>
+      </c>
+      <c r="O36" s="1">
+        <f>SUBTOTAL(9,O3:O35)</f>
+        <v>0</v>
+      </c>
+      <c r="P36" s="1">
+        <f>SUBTOTAL(9,P3:P35)</f>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="1">
+        <f>SUBTOTAL(9,Q3:Q35)</f>
+        <v>32</v>
+      </c>
+      <c r="R36" s="1">
+        <f>SUBTOTAL(9,R3:R35)</f>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H40" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H41" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="8">
+        <f>SUM(I35:I39)</f>
+        <v>22325</v>
+      </c>
+      <c r="J41" s="8">
+        <f>Q36</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H42" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="10">
+        <f>R36</f>
+        <v>355</v>
+      </c>
+      <c r="J42" s="11"/>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H43" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" s="10">
+        <f>S35</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="11"/>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H44" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" s="10">
+        <f>T35</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="11"/>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H45" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I45" s="10">
+        <f>U35</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="11"/>
+    </row>
+    <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H46" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
+    </row>
+    <row r="47" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H47" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
+    </row>
+    <row r="48" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H48" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I48" s="16">
+        <f>SUM(I41:I47)</f>
+        <v>22680</v>
+      </c>
+      <c r="J48" s="16">
+        <f>SUM(J41:J45)</f>
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P34" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P34">
+      <sortCondition ref="J2:J34"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B35704C-EE25-4E64-8D81-EF9F283336A2}">
   <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8259,10 +10294,10 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>270</v>
+        <v>424</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>271</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -9415,7 +11450,7 @@
     </row>
     <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H62" s="4" t="s">
-        <v>269</v>
+        <v>426</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>15</v>

--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4652AD-69EF-4ADB-9839-8DB322F41C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E91AFB4-9804-497A-9A37-53303E1C3BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-5" sheetId="3" r:id="rId1"/>
@@ -18,13 +18,15 @@
     <sheet name="5-5" sheetId="5" r:id="rId3"/>
     <sheet name="6-5" sheetId="6" r:id="rId4"/>
     <sheet name="7-5" sheetId="7" r:id="rId5"/>
+    <sheet name="8-5" sheetId="8" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-5'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'4-5'!$A$2:$P$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'5-5'!$A$2:$P$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'6-5'!$A$2:$P$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'7-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'7-5'!$A$2:$P$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'8-5'!$A$2:$P$56</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="618">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -1327,9 +1329,6 @@
     <t>NGAY 7-5</t>
   </si>
   <si>
-    <t>T4.7.5.2026</t>
-  </si>
-  <si>
     <t>C Phước - fb Yến Nguyễn</t>
   </si>
   <si>
@@ -1610,6 +1609,300 @@
   </si>
   <si>
     <t>91 Phạm Văn Hai, f3</t>
+  </si>
+  <si>
+    <t>NGAY 8-5</t>
+  </si>
+  <si>
+    <t>T6.8.5.2026</t>
+  </si>
+  <si>
+    <t>T5.7.5.2026</t>
+  </si>
+  <si>
+    <t>Thuỳ Duyên - fb Elyna Tran</t>
+  </si>
+  <si>
+    <t>HD019033</t>
+  </si>
+  <si>
+    <t>Vinhome Grandpark Be3, Nguyễn Xiển, Long Bình</t>
+  </si>
+  <si>
+    <t>07-05-2026</t>
+  </si>
+  <si>
+    <t>Phương Phạm</t>
+  </si>
+  <si>
+    <t>HD018958</t>
+  </si>
+  <si>
+    <t>Bs16A vinhome grand park long bình</t>
+  </si>
+  <si>
+    <t>Tuyến fb Có Đuôi Gà</t>
+  </si>
+  <si>
+    <t>HD019062</t>
+  </si>
+  <si>
+    <t>7/88, Ik 5-6, bình Hưng hoà B</t>
+  </si>
+  <si>
+    <t>AT 07-05</t>
+  </si>
+  <si>
+    <t>Lê Thị Minh Phượng.</t>
+  </si>
+  <si>
+    <t>HD019071</t>
+  </si>
+  <si>
+    <t>155/14 ds 11 bình hưng hoà</t>
+  </si>
+  <si>
+    <t>My Nhung Ly</t>
+  </si>
+  <si>
+    <t>HD019061</t>
+  </si>
+  <si>
+    <t>số 13 đường số 9, P13</t>
+  </si>
+  <si>
+    <t>Chị Phương</t>
+  </si>
+  <si>
+    <t>HD019053</t>
+  </si>
+  <si>
+    <t>984/62 hà huy giáp</t>
+  </si>
+  <si>
+    <t>Nguyễn Kim Dung</t>
+  </si>
+  <si>
+    <t>HD019069</t>
+  </si>
+  <si>
+    <t>40/20 trần văn quang p10</t>
+  </si>
+  <si>
+    <t>Thu Phương</t>
+  </si>
+  <si>
+    <t>HD018907</t>
+  </si>
+  <si>
+    <t>96a đg 79 phường tân quy</t>
+  </si>
+  <si>
+    <t>Uyên Phương ( Trân)</t>
+  </si>
+  <si>
+    <t>HD018834</t>
+  </si>
+  <si>
+    <t>31 Nguyễn Văn Linh, phường Tân Thuận Tây</t>
+  </si>
+  <si>
+    <t>Trần Phương Quỳnh</t>
+  </si>
+  <si>
+    <t>HD018973</t>
+  </si>
+  <si>
+    <t>53 nguyễn thị minh khai, p sài gòn tòa nhà avalon</t>
+  </si>
+  <si>
+    <t>VN ( Allie Biiny)</t>
+  </si>
+  <si>
+    <t>HD018858</t>
+  </si>
+  <si>
+    <t>Phương 1 Street/Buildding Name: \450/28Gdương bá trạc(061771181)</t>
+  </si>
+  <si>
+    <t>Kim Hằng</t>
+  </si>
+  <si>
+    <t>HD018939</t>
+  </si>
+  <si>
+    <t>PARK VIEW APARTMENT R4-10-11, Hưng Gia 1,Đ. Số 2, Tân Phong</t>
+  </si>
+  <si>
+    <t>HD018855</t>
+  </si>
+  <si>
+    <t>chung cư the park residence. 12 nguyễn hữu thọ phước kien</t>
+  </si>
+  <si>
+    <t>Ngọc Hân Nghiêm</t>
+  </si>
+  <si>
+    <t>HD018899</t>
+  </si>
+  <si>
+    <t>124 đường số 9 KDC Bình Hưng, Bình Hưng</t>
+  </si>
+  <si>
+    <t>HD018512</t>
+  </si>
+  <si>
+    <t>Thỏ Selina</t>
+  </si>
+  <si>
+    <t>HD019055</t>
+  </si>
+  <si>
+    <t>Tháp S2 - The sun avenue 28 Mai Chí Thọ, P bình trưng</t>
+  </si>
+  <si>
+    <t>ái quyên mai malaysia</t>
+  </si>
+  <si>
+    <t>HD018836</t>
+  </si>
+  <si>
+    <t>22 Tân Thới Nhất 1B, p. Tân Thới Nhất</t>
+  </si>
+  <si>
+    <t>Trang Lê</t>
+  </si>
+  <si>
+    <t>HD019057</t>
+  </si>
+  <si>
+    <t>8A Sông Thương P2</t>
+  </si>
+  <si>
+    <t>Phạm Thị Bảo Trân</t>
+  </si>
+  <si>
+    <t>HD018909</t>
+  </si>
+  <si>
+    <t>Block B Chung Cư Urban Green, Đường Số 6, Hiệp Bình</t>
+  </si>
+  <si>
+    <t>Thụy Uyên Vũ</t>
+  </si>
+  <si>
+    <t>HD018911</t>
+  </si>
+  <si>
+    <t>Chung cư the manor 2</t>
+  </si>
+  <si>
+    <t>Phương Thúy</t>
+  </si>
+  <si>
+    <t>HD018990</t>
+  </si>
+  <si>
+    <t>33 đường số 5 cát lái</t>
+  </si>
+  <si>
+    <t>HD019025</t>
+  </si>
+  <si>
+    <t>Nguyễn Trang</t>
+  </si>
+  <si>
+    <t>HD018885</t>
+  </si>
+  <si>
+    <t>Chung cư freshca lock b Phường Bình Chiểu</t>
+  </si>
+  <si>
+    <t>Diễm Quỳnh</t>
+  </si>
+  <si>
+    <t>HD019054</t>
+  </si>
+  <si>
+    <t>Masteri thảo điền tháp t3 Thao dien</t>
+  </si>
+  <si>
+    <t>ELLY NGUYỄN - THẮM NGUYÊN</t>
+  </si>
+  <si>
+    <t>HD019058</t>
+  </si>
+  <si>
+    <t>120/3/11 Đăng Thùy Trâm, P13 ( CTY GIA HUY EXPRESS )</t>
+  </si>
+  <si>
+    <t>Lê Thị Quỳnh Yến</t>
+  </si>
+  <si>
+    <t>HD019032</t>
+  </si>
+  <si>
+    <t>82 bạch vân</t>
+  </si>
+  <si>
+    <t>Phương Thảo</t>
+  </si>
+  <si>
+    <t>HD018831</t>
+  </si>
+  <si>
+    <t>504 Nguyễn Tất Thành, phường 18 chung cư Riva Park</t>
+  </si>
+  <si>
+    <t>Huyền</t>
+  </si>
+  <si>
+    <t>HD018987</t>
+  </si>
+  <si>
+    <t>218/10 nam kì khởi nghĩa</t>
+  </si>
+  <si>
+    <t>huyền nguyễn</t>
+  </si>
+  <si>
+    <t>HD016429</t>
+  </si>
+  <si>
+    <t>Trần HUỆ</t>
+  </si>
+  <si>
+    <t>HD018874</t>
+  </si>
+  <si>
+    <t>391 ngô gia tự p2</t>
+  </si>
+  <si>
+    <t>CUS TWO EIGHT EIGHT TWO NINE</t>
+  </si>
+  <si>
+    <t>HD018877</t>
+  </si>
+  <si>
+    <t>270B LÝ THƯỜNG KIỆT KP1 P6</t>
+  </si>
+  <si>
+    <t>hải my fb Bé Hân</t>
+  </si>
+  <si>
+    <t>HD018959</t>
+  </si>
+  <si>
+    <t>31 an bình P6</t>
+  </si>
+  <si>
+    <t>Thanh Thanh Trương</t>
+  </si>
+  <si>
+    <t>HD019041</t>
+  </si>
+  <si>
+    <t>518/24 võ văn kiệt</t>
   </si>
 </sst>
 </file>
@@ -8662,13 +8955,13 @@
         <v>30</v>
       </c>
       <c r="C3" s="22" t="s">
+        <v>426</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>427</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="E3" s="22" t="s">
         <v>428</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>429</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>59</v>
@@ -8684,13 +8977,13 @@
         <v>-25</v>
       </c>
       <c r="J3" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
         <v>430</v>
-      </c>
-      <c r="K3" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="22" t="s">
-        <v>431</v>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="22"/>
@@ -8710,13 +9003,13 @@
         <v>30</v>
       </c>
       <c r="C4" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="D4" s="22" t="s">
         <v>432</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="E4" s="22" t="s">
         <v>433</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>434</v>
       </c>
       <c r="F4" s="23">
         <v>12</v>
@@ -8732,13 +9025,13 @@
         <v>370</v>
       </c>
       <c r="J4" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
         <v>430</v>
-      </c>
-      <c r="K4" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="22" t="s">
-        <v>431</v>
       </c>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
@@ -8754,13 +9047,13 @@
         <v>30</v>
       </c>
       <c r="C5" s="22" t="s">
+        <v>434</v>
+      </c>
+      <c r="D5" s="22" t="s">
         <v>435</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="E5" s="22" t="s">
         <v>436</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>437</v>
       </c>
       <c r="F5" s="23">
         <v>8</v>
@@ -8776,13 +9069,13 @@
         <v>1030</v>
       </c>
       <c r="J5" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
         <v>430</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>431</v>
       </c>
       <c r="M5" s="22"/>
       <c r="N5" s="22"/>
@@ -8798,13 +9091,13 @@
         <v>30</v>
       </c>
       <c r="C6" s="22" t="s">
+        <v>437</v>
+      </c>
+      <c r="D6" s="22" t="s">
         <v>438</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="E6" s="22" t="s">
         <v>439</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>440</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>39</v>
@@ -8820,13 +9113,13 @@
         <v>790</v>
       </c>
       <c r="J6" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
         <v>430</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>431</v>
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="22"/>
@@ -8842,13 +9135,13 @@
         <v>30</v>
       </c>
       <c r="C7" s="22" t="s">
+        <v>440</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>441</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="E7" s="22" t="s">
         <v>442</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>443</v>
       </c>
       <c r="F7" s="23">
         <v>6</v>
@@ -8864,13 +9157,13 @@
         <v>-25</v>
       </c>
       <c r="J7" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
         <v>430</v>
-      </c>
-      <c r="K7" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="22" t="s">
-        <v>431</v>
       </c>
       <c r="M7" s="22"/>
       <c r="N7" s="22"/>
@@ -8890,13 +9183,13 @@
         <v>30</v>
       </c>
       <c r="C8" s="22" t="s">
+        <v>443</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>444</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="E8" s="22" t="s">
         <v>445</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>446</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>39</v>
@@ -8912,13 +9205,13 @@
         <v>860</v>
       </c>
       <c r="J8" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
         <v>430</v>
-      </c>
-      <c r="K8" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>431</v>
       </c>
       <c r="M8" s="22"/>
       <c r="N8" s="22"/>
@@ -8934,13 +9227,13 @@
         <v>30</v>
       </c>
       <c r="C9" s="22" t="s">
+        <v>446</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>447</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="E9" s="22" t="s">
         <v>448</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>449</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>39</v>
@@ -8956,13 +9249,13 @@
         <v>820</v>
       </c>
       <c r="J9" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
         <v>430</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="22" t="s">
-        <v>431</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -8978,13 +9271,13 @@
         <v>30</v>
       </c>
       <c r="C10" s="22" t="s">
+        <v>449</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>450</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="E10" s="22" t="s">
         <v>451</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>452</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>152</v>
@@ -9000,13 +9293,13 @@
         <v>820</v>
       </c>
       <c r="J10" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
         <v>430</v>
-      </c>
-      <c r="K10" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10" s="22" t="s">
-        <v>431</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -9022,13 +9315,13 @@
         <v>30</v>
       </c>
       <c r="C11" s="22" t="s">
+        <v>452</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>453</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="E11" s="22" t="s">
         <v>454</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>455</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>59</v>
@@ -9044,13 +9337,13 @@
         <v>1150</v>
       </c>
       <c r="J11" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
         <v>430</v>
-      </c>
-      <c r="K11" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L11" s="22" t="s">
-        <v>431</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
@@ -9066,13 +9359,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="22" t="s">
+        <v>455</v>
+      </c>
+      <c r="D12" s="22" t="s">
         <v>456</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="E12" s="22" t="s">
         <v>457</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>458</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>108</v>
@@ -9088,13 +9381,13 @@
         <v>690</v>
       </c>
       <c r="J12" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
         <v>430</v>
-      </c>
-      <c r="K12" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L12" s="22" t="s">
-        <v>431</v>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
@@ -9110,13 +9403,13 @@
         <v>30</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>458</v>
+      </c>
+      <c r="D13" s="22" t="s">
         <v>459</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="E13" s="22" t="s">
         <v>460</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>461</v>
       </c>
       <c r="F13" s="23">
         <v>12</v>
@@ -9132,13 +9425,13 @@
         <v>1120</v>
       </c>
       <c r="J13" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
         <v>430</v>
-      </c>
-      <c r="K13" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L13" s="22" t="s">
-        <v>431</v>
       </c>
       <c r="M13" s="22"/>
       <c r="N13" s="22"/>
@@ -9154,13 +9447,13 @@
         <v>30</v>
       </c>
       <c r="C14" s="22" t="s">
+        <v>461</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>462</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="E14" s="22" t="s">
         <v>463</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>464</v>
       </c>
       <c r="F14" s="22" t="s">
         <v>59</v>
@@ -9176,13 +9469,13 @@
         <v>-25</v>
       </c>
       <c r="J14" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
         <v>430</v>
-      </c>
-      <c r="K14" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L14" s="22" t="s">
-        <v>431</v>
       </c>
       <c r="M14" s="22"/>
       <c r="N14" s="22"/>
@@ -9204,11 +9497,11 @@
         <v>30</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D15" s="25"/>
       <c r="E15" s="25" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F15" s="25" t="s">
         <v>98</v>
@@ -9230,7 +9523,7 @@
         <v>34</v>
       </c>
       <c r="L15" s="25" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M15" s="25" t="s">
         <v>139</v>
@@ -9252,13 +9545,13 @@
         <v>30</v>
       </c>
       <c r="C16" s="22" t="s">
+        <v>466</v>
+      </c>
+      <c r="D16" s="22" t="s">
         <v>467</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="E16" s="22" t="s">
         <v>468</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>469</v>
       </c>
       <c r="F16" s="22" t="s">
         <v>108</v>
@@ -9280,7 +9573,7 @@
         <v>34</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M16" s="22"/>
       <c r="N16" s="22"/>
@@ -9296,13 +9589,13 @@
         <v>30</v>
       </c>
       <c r="C17" s="22" t="s">
+        <v>469</v>
+      </c>
+      <c r="D17" s="22" t="s">
         <v>470</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="E17" s="22" t="s">
         <v>471</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>472</v>
       </c>
       <c r="F17" s="22" t="s">
         <v>94</v>
@@ -9324,7 +9617,7 @@
         <v>34</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M17" s="22"/>
       <c r="N17" s="22"/>
@@ -9340,13 +9633,13 @@
         <v>30</v>
       </c>
       <c r="C18" s="22" t="s">
+        <v>472</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>473</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="E18" s="22" t="s">
         <v>474</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>475</v>
       </c>
       <c r="F18" s="22" t="s">
         <v>108</v>
@@ -9368,7 +9661,7 @@
         <v>34</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M18" s="22"/>
       <c r="N18" s="22"/>
@@ -9384,13 +9677,13 @@
         <v>30</v>
       </c>
       <c r="C19" s="22" t="s">
+        <v>475</v>
+      </c>
+      <c r="D19" s="22" t="s">
         <v>476</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="E19" s="22" t="s">
         <v>477</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>478</v>
       </c>
       <c r="F19" s="22" t="s">
         <v>98</v>
@@ -9412,7 +9705,7 @@
         <v>34</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M19" s="22"/>
       <c r="N19" s="22"/>
@@ -9428,13 +9721,13 @@
         <v>30</v>
       </c>
       <c r="C20" s="22" t="s">
+        <v>478</v>
+      </c>
+      <c r="D20" s="22" t="s">
         <v>479</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="E20" s="22" t="s">
         <v>480</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>481</v>
       </c>
       <c r="F20" s="22" t="s">
         <v>94</v>
@@ -9456,7 +9749,7 @@
         <v>34</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
@@ -9472,13 +9765,13 @@
         <v>30</v>
       </c>
       <c r="C21" s="22" t="s">
+        <v>481</v>
+      </c>
+      <c r="D21" s="22" t="s">
         <v>482</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="E21" s="22" t="s">
         <v>483</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>484</v>
       </c>
       <c r="F21" s="22" t="s">
         <v>90</v>
@@ -9500,7 +9793,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M21" s="22"/>
       <c r="N21" s="22"/>
@@ -9520,13 +9813,13 @@
         <v>30</v>
       </c>
       <c r="C22" s="22" t="s">
+        <v>484</v>
+      </c>
+      <c r="D22" s="22" t="s">
         <v>485</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="E22" s="22" t="s">
         <v>486</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>487</v>
       </c>
       <c r="F22" s="23">
         <v>12</v>
@@ -9548,7 +9841,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M22" s="22"/>
       <c r="N22" s="22"/>
@@ -9568,13 +9861,13 @@
         <v>30</v>
       </c>
       <c r="C23" s="22" t="s">
+        <v>487</v>
+      </c>
+      <c r="D23" s="22" t="s">
         <v>488</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="E23" s="22" t="s">
         <v>489</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>490</v>
       </c>
       <c r="F23" s="23">
         <v>12</v>
@@ -9596,7 +9889,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M23" s="22"/>
       <c r="N23" s="22"/>
@@ -9618,11 +9911,11 @@
         <v>30</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D24" s="22"/>
       <c r="E24" s="22" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F24" s="22" t="s">
         <v>108</v>
@@ -9644,7 +9937,7 @@
         <v>34</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M24" s="22"/>
       <c r="N24" s="22"/>
@@ -9666,11 +9959,11 @@
         <v>30</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D25" s="22"/>
       <c r="E25" s="22" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F25" s="22" t="s">
         <v>108</v>
@@ -9692,7 +9985,7 @@
         <v>34</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M25" s="22"/>
       <c r="N25" s="22"/>
@@ -9714,11 +10007,11 @@
         <v>30</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="22" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F26" s="22" t="s">
         <v>389</v>
@@ -9740,7 +10033,7 @@
         <v>34</v>
       </c>
       <c r="L26" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M26" s="22"/>
       <c r="N26" s="22"/>
@@ -9756,13 +10049,13 @@
         <v>30</v>
       </c>
       <c r="C27" s="22" t="s">
+        <v>496</v>
+      </c>
+      <c r="D27" s="22" t="s">
         <v>497</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="E27" s="22" t="s">
         <v>498</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>499</v>
       </c>
       <c r="F27" s="22" t="s">
         <v>389</v>
@@ -9784,7 +10077,7 @@
         <v>34</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M27" s="28" t="s">
         <v>180</v>
@@ -9806,13 +10099,13 @@
         <v>30</v>
       </c>
       <c r="C28" s="22" t="s">
+        <v>499</v>
+      </c>
+      <c r="D28" s="22" t="s">
         <v>500</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="E28" s="22" t="s">
         <v>501</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>502</v>
       </c>
       <c r="F28" s="23">
         <v>1</v>
@@ -9834,7 +10127,7 @@
         <v>34</v>
       </c>
       <c r="L28" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
@@ -9854,13 +10147,13 @@
         <v>30</v>
       </c>
       <c r="C29" s="22" t="s">
+        <v>502</v>
+      </c>
+      <c r="D29" s="22" t="s">
         <v>503</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="E29" s="22" t="s">
         <v>504</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>505</v>
       </c>
       <c r="F29" s="22" t="s">
         <v>108</v>
@@ -9882,7 +10175,7 @@
         <v>34</v>
       </c>
       <c r="L29" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M29" s="22"/>
       <c r="N29" s="22"/>
@@ -9898,13 +10191,13 @@
         <v>30</v>
       </c>
       <c r="C30" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="D30" s="22" t="s">
         <v>506</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="E30" s="22" t="s">
         <v>507</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>508</v>
       </c>
       <c r="F30" s="22" t="s">
         <v>108</v>
@@ -9926,7 +10219,7 @@
         <v>34</v>
       </c>
       <c r="L30" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M30" s="22"/>
       <c r="N30" s="22"/>
@@ -9946,13 +10239,13 @@
         <v>30</v>
       </c>
       <c r="C31" s="25" t="s">
+        <v>508</v>
+      </c>
+      <c r="D31" s="25" t="s">
         <v>509</v>
       </c>
-      <c r="D31" s="25" t="s">
+      <c r="E31" s="25" t="s">
         <v>510</v>
-      </c>
-      <c r="E31" s="25" t="s">
-        <v>511</v>
       </c>
       <c r="F31" s="26">
         <v>5</v>
@@ -9974,7 +10267,7 @@
         <v>34</v>
       </c>
       <c r="L31" s="25" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M31" s="25" t="s">
         <v>139</v>
@@ -9992,13 +10285,13 @@
         <v>30</v>
       </c>
       <c r="C32" s="22" t="s">
+        <v>511</v>
+      </c>
+      <c r="D32" s="22" t="s">
         <v>512</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="E32" s="22" t="s">
         <v>513</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>514</v>
       </c>
       <c r="F32" s="23">
         <v>1</v>
@@ -10020,7 +10313,7 @@
         <v>34</v>
       </c>
       <c r="L32" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M32" s="22"/>
       <c r="N32" s="22"/>
@@ -10036,13 +10329,13 @@
         <v>30</v>
       </c>
       <c r="C33" s="22" t="s">
+        <v>514</v>
+      </c>
+      <c r="D33" s="22" t="s">
         <v>515</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="E33" s="22" t="s">
         <v>516</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>517</v>
       </c>
       <c r="F33" s="23">
         <v>4</v>
@@ -10064,7 +10357,7 @@
         <v>34</v>
       </c>
       <c r="L33" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M33" s="22"/>
       <c r="N33" s="22"/>
@@ -10080,13 +10373,13 @@
         <v>30</v>
       </c>
       <c r="C34" s="22" t="s">
+        <v>517</v>
+      </c>
+      <c r="D34" s="22" t="s">
         <v>518</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="E34" s="22" t="s">
         <v>519</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>520</v>
       </c>
       <c r="F34" s="22" t="s">
         <v>108</v>
@@ -10108,7 +10401,7 @@
         <v>34</v>
       </c>
       <c r="L34" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M34" s="28" t="s">
         <v>180</v>
@@ -10126,51 +10419,51 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G36" s="1">
-        <f>SUBTOTAL(9,G3:G35)</f>
+        <f t="shared" ref="G36:R36" si="2">SUBTOTAL(9,G3:G35)</f>
         <v>23200</v>
       </c>
       <c r="H36" s="1">
-        <f>SUBTOTAL(9,H3:H35)</f>
+        <f t="shared" si="2"/>
         <v>875</v>
       </c>
       <c r="I36" s="1">
-        <f>SUBTOTAL(9,I3:I35)</f>
+        <f t="shared" si="2"/>
         <v>22325</v>
       </c>
       <c r="J36" s="1">
-        <f>SUBTOTAL(9,J3:J35)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K36" s="1">
-        <f>SUBTOTAL(9,K3:K35)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L36" s="1">
-        <f>SUBTOTAL(9,L3:L35)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M36" s="1">
-        <f>SUBTOTAL(9,M3:M35)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N36" s="1">
-        <f>SUBTOTAL(9,N3:N35)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O36" s="1">
-        <f>SUBTOTAL(9,O3:O35)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P36" s="1">
-        <f>SUBTOTAL(9,P3:P35)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q36" s="1">
-        <f>SUBTOTAL(9,Q3:Q35)</f>
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
       <c r="R36" s="1">
-        <f>SUBTOTAL(9,R3:R35)</f>
+        <f t="shared" si="2"/>
         <v>355</v>
       </c>
     </row>
@@ -10278,6 +10571,1793 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B35704C-EE25-4E64-8D81-EF9F283336A2}">
+  <dimension ref="A1:R50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>523</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>524</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>525</v>
+      </c>
+      <c r="F3" s="23">
+        <v>9</v>
+      </c>
+      <c r="G3" s="23">
+        <v>850</v>
+      </c>
+      <c r="H3" s="23">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I16" si="0">G3-H3</f>
+        <v>820</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>527</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>528</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>529</v>
+      </c>
+      <c r="F4" s="23">
+        <v>9</v>
+      </c>
+      <c r="G4" s="23">
+        <v>750</v>
+      </c>
+      <c r="H4" s="23">
+        <v>30</v>
+      </c>
+      <c r="I4" s="23">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>530</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>531</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>532</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="23">
+        <v>0</v>
+      </c>
+      <c r="H5" s="23">
+        <v>30</v>
+      </c>
+      <c r="I5" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>533</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+      <c r="R5" s="24">
+        <f>H5</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>534</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>535</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>536</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="23">
+        <v>900</v>
+      </c>
+      <c r="H6" s="23">
+        <v>30</v>
+      </c>
+      <c r="I6" s="23">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>533</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>537</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>538</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>539</v>
+      </c>
+      <c r="F7" s="23">
+        <v>6</v>
+      </c>
+      <c r="G7" s="23">
+        <v>775</v>
+      </c>
+      <c r="H7" s="23">
+        <v>25</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>533</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>540</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>541</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>542</v>
+      </c>
+      <c r="F8" s="23">
+        <v>12</v>
+      </c>
+      <c r="G8" s="23">
+        <v>400</v>
+      </c>
+      <c r="H8" s="23">
+        <v>30</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>370</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>533</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>543</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>544</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>545</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0</v>
+      </c>
+      <c r="H9" s="23">
+        <v>25</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>533</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+      <c r="R9" s="24">
+        <f>H9</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>546</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>547</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>548</v>
+      </c>
+      <c r="F10" s="23">
+        <v>7</v>
+      </c>
+      <c r="G10" s="23">
+        <v>850</v>
+      </c>
+      <c r="H10" s="23">
+        <v>30</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>533</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>549</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>550</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>551</v>
+      </c>
+      <c r="F11" s="23">
+        <v>7</v>
+      </c>
+      <c r="G11" s="23">
+        <v>480</v>
+      </c>
+      <c r="H11" s="23">
+        <v>30</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>450</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>533</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>552</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>553</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>554</v>
+      </c>
+      <c r="F12" s="23">
+        <v>1</v>
+      </c>
+      <c r="G12" s="23">
+        <v>1135</v>
+      </c>
+      <c r="H12" s="23">
+        <v>25</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>1110</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>533</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>555</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>556</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>557</v>
+      </c>
+      <c r="F13" s="23">
+        <v>8</v>
+      </c>
+      <c r="G13" s="23">
+        <v>0</v>
+      </c>
+      <c r="H13" s="23">
+        <v>30</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>533</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+      <c r="R13" s="24">
+        <f>H13</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>558</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>559</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>560</v>
+      </c>
+      <c r="F14" s="23">
+        <v>7</v>
+      </c>
+      <c r="G14" s="23">
+        <v>670</v>
+      </c>
+      <c r="H14" s="23">
+        <v>30</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>533</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="25"/>
+      <c r="B15" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>561</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>562</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="G15" s="26">
+        <v>95</v>
+      </c>
+      <c r="H15" s="26">
+        <v>35</v>
+      </c>
+      <c r="I15" s="26">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="J15" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="K15" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="25" t="s">
+        <v>526</v>
+      </c>
+      <c r="M15" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>564</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>565</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G16" s="23">
+        <v>0</v>
+      </c>
+      <c r="H16" s="23">
+        <v>35</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>533</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M16" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+      <c r="R16" s="24">
+        <f t="shared" ref="R16:R17" si="1">H16</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>565</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G17" s="23">
+        <v>0</v>
+      </c>
+      <c r="H17" s="23">
+        <v>0</v>
+      </c>
+      <c r="I17" s="23">
+        <f>H17</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>533</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M17" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+      <c r="R17" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>567</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>569</v>
+      </c>
+      <c r="F18" s="23">
+        <v>2</v>
+      </c>
+      <c r="G18" s="23">
+        <v>850</v>
+      </c>
+      <c r="H18" s="23">
+        <v>30</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" ref="I18:I36" si="2">G18-H18</f>
+        <v>820</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>570</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>571</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>572</v>
+      </c>
+      <c r="F19" s="23">
+        <v>12</v>
+      </c>
+      <c r="G19" s="23">
+        <v>0</v>
+      </c>
+      <c r="H19" s="23">
+        <v>30</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="2"/>
+        <v>-30</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+      <c r="R19" s="24">
+        <f>H19</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>573</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>574</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>575</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G20" s="23">
+        <v>2200</v>
+      </c>
+      <c r="H20" s="23">
+        <v>30</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="2"/>
+        <v>2170</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M20" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+      <c r="R20" s="24">
+        <f>H20</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>576</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>577</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>578</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" s="23">
+        <v>670</v>
+      </c>
+      <c r="H21" s="23">
+        <v>30</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="2"/>
+        <v>640</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>579</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>580</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>581</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" s="23">
+        <v>0</v>
+      </c>
+      <c r="H22" s="23">
+        <v>20</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="2"/>
+        <v>-20</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+      <c r="R22" s="24">
+        <f>H22</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>582</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>583</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>584</v>
+      </c>
+      <c r="F23" s="23">
+        <v>2</v>
+      </c>
+      <c r="G23" s="23">
+        <v>690</v>
+      </c>
+      <c r="H23" s="23">
+        <v>30</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="2"/>
+        <v>660</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25"/>
+      <c r="B24" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>585</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="F24" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="G24" s="26">
+        <v>30</v>
+      </c>
+      <c r="H24" s="26">
+        <v>30</v>
+      </c>
+      <c r="I24" s="26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="25" t="s">
+        <v>526</v>
+      </c>
+      <c r="M24" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N24" s="25"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>586</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>587</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>588</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G25" s="23">
+        <v>780</v>
+      </c>
+      <c r="H25" s="23">
+        <v>30</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="2"/>
+        <v>750</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>589</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>590</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>591</v>
+      </c>
+      <c r="F26" s="23">
+        <v>2</v>
+      </c>
+      <c r="G26" s="23">
+        <v>850</v>
+      </c>
+      <c r="H26" s="23">
+        <v>30</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="2"/>
+        <v>820</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>592</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>593</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>594</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G27" s="23">
+        <v>0</v>
+      </c>
+      <c r="H27" s="23">
+        <v>20</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="2"/>
+        <v>-20</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22">
+        <v>1</v>
+      </c>
+      <c r="R27" s="24">
+        <f>H27</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="23">
+        <v>30</v>
+      </c>
+      <c r="H28" s="23">
+        <v>30</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>595</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>596</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>597</v>
+      </c>
+      <c r="F29" s="23">
+        <v>5</v>
+      </c>
+      <c r="G29" s="23">
+        <v>1175</v>
+      </c>
+      <c r="H29" s="23">
+        <v>25</v>
+      </c>
+      <c r="I29" s="23">
+        <f t="shared" si="2"/>
+        <v>1150</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>598</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>599</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>600</v>
+      </c>
+      <c r="F30" s="23">
+        <v>4</v>
+      </c>
+      <c r="G30" s="23">
+        <v>765</v>
+      </c>
+      <c r="H30" s="23">
+        <v>25</v>
+      </c>
+      <c r="I30" s="23">
+        <f t="shared" si="2"/>
+        <v>740</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>601</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>602</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>603</v>
+      </c>
+      <c r="F31" s="23">
+        <v>3</v>
+      </c>
+      <c r="G31" s="23">
+        <v>0</v>
+      </c>
+      <c r="H31" s="23">
+        <v>25</v>
+      </c>
+      <c r="I31" s="23">
+        <f t="shared" si="2"/>
+        <v>-25</v>
+      </c>
+      <c r="J31" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K31" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22">
+        <v>1</v>
+      </c>
+      <c r="R31" s="24">
+        <f>H31</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>604</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>605</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="F32" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G32" s="23">
+        <v>685</v>
+      </c>
+      <c r="H32" s="23">
+        <v>25</v>
+      </c>
+      <c r="I32" s="23">
+        <f t="shared" si="2"/>
+        <v>660</v>
+      </c>
+      <c r="J32" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K32" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L32" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>606</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>607</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>608</v>
+      </c>
+      <c r="F33" s="23">
+        <v>10</v>
+      </c>
+      <c r="G33" s="23">
+        <v>865</v>
+      </c>
+      <c r="H33" s="23">
+        <v>25</v>
+      </c>
+      <c r="I33" s="23">
+        <f t="shared" si="2"/>
+        <v>840</v>
+      </c>
+      <c r="J33" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K33" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M33" s="22"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>609</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>610</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>611</v>
+      </c>
+      <c r="F34" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G34" s="23">
+        <v>0</v>
+      </c>
+      <c r="H34" s="23">
+        <v>25</v>
+      </c>
+      <c r="I34" s="23">
+        <f t="shared" si="2"/>
+        <v>-25</v>
+      </c>
+      <c r="J34" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K34" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22">
+        <v>1</v>
+      </c>
+      <c r="R34" s="24">
+        <f t="shared" ref="R34:R35" si="3">H34</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>612</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>613</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>614</v>
+      </c>
+      <c r="F35" s="23">
+        <v>5</v>
+      </c>
+      <c r="G35" s="23">
+        <v>0</v>
+      </c>
+      <c r="H35" s="23">
+        <v>25</v>
+      </c>
+      <c r="I35" s="23">
+        <f t="shared" si="2"/>
+        <v>-25</v>
+      </c>
+      <c r="J35" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K35" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M35" s="22"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22">
+        <v>1</v>
+      </c>
+      <c r="R35" s="24">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>615</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>616</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>617</v>
+      </c>
+      <c r="F36" s="23">
+        <v>1</v>
+      </c>
+      <c r="G36" s="23">
+        <v>2050</v>
+      </c>
+      <c r="H36" s="23">
+        <v>30</v>
+      </c>
+      <c r="I36" s="23">
+        <f t="shared" si="2"/>
+        <v>2020</v>
+      </c>
+      <c r="J36" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K36" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="M36" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="22">
+        <v>1</v>
+      </c>
+      <c r="R36" s="24">
+        <f>H36</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G38" s="1">
+        <f>SUBTOTAL(9,G3:G37)</f>
+        <v>18545</v>
+      </c>
+      <c r="H38" s="1">
+        <f>SUBTOTAL(9,H3:H37)</f>
+        <v>930</v>
+      </c>
+      <c r="I38" s="1">
+        <f>SUBTOTAL(9,I3:I37)</f>
+        <v>17615</v>
+      </c>
+      <c r="J38" s="1">
+        <f>SUBTOTAL(9,J3:J37)</f>
+        <v>0</v>
+      </c>
+      <c r="K38" s="1">
+        <f>SUBTOTAL(9,K3:K37)</f>
+        <v>0</v>
+      </c>
+      <c r="L38" s="1">
+        <f>SUBTOTAL(9,L3:L37)</f>
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
+        <f>SUBTOTAL(9,M3:M37)</f>
+        <v>0</v>
+      </c>
+      <c r="N38" s="1">
+        <f>SUBTOTAL(9,N3:N37)</f>
+        <v>0</v>
+      </c>
+      <c r="O38" s="1">
+        <f>SUBTOTAL(9,O3:O37)</f>
+        <v>0</v>
+      </c>
+      <c r="P38" s="1">
+        <f>SUBTOTAL(9,P3:P37)</f>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="1">
+        <f>SUBTOTAL(9,Q3:Q37)</f>
+        <v>34</v>
+      </c>
+      <c r="R38" s="1">
+        <f>SUBTOTAL(9,R3:R37)</f>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H42" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H43" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" s="8">
+        <f>SUM(I37:I41)</f>
+        <v>17615</v>
+      </c>
+      <c r="J43" s="8">
+        <f>Q38</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H44" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44" s="10">
+        <f>R38</f>
+        <v>325</v>
+      </c>
+      <c r="J44" s="11"/>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H45" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" s="10">
+        <f>S37</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="11"/>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H46" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I46" s="10">
+        <f>T37</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="11"/>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H47" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I47" s="10">
+        <f>U37</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="11"/>
+    </row>
+    <row r="48" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H48" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13"/>
+    </row>
+    <row r="49" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H49" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I49" s="13"/>
+      <c r="J49" s="13"/>
+    </row>
+    <row r="50" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H50" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I50" s="16">
+        <f>SUM(I43:I49)</f>
+        <v>17940</v>
+      </c>
+      <c r="J50" s="16">
+        <f>SUM(J43:J47)</f>
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P36" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P36">
+      <sortCondition ref="J2:J36"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B54A00B3-0891-4E25-BC1A-2BDA276BB257}">
   <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10294,10 +12374,10 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>424</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>425</v>
+        <v>520</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -11450,7 +13530,7 @@
     </row>
     <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H62" s="4" t="s">
-        <v>426</v>
+        <v>521</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>15</v>

--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E91AFB4-9804-497A-9A37-53303E1C3BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE0C0A2-39A0-47B1-ACA2-E9F7AFF6E7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-5" sheetId="3" r:id="rId1"/>
@@ -19,14 +19,18 @@
     <sheet name="6-5" sheetId="6" r:id="rId4"/>
     <sheet name="7-5" sheetId="7" r:id="rId5"/>
     <sheet name="8-5" sheetId="8" r:id="rId6"/>
+    <sheet name="9-5" sheetId="9" r:id="rId7"/>
+    <sheet name="11-5" sheetId="10" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'11-5'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-5'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'4-5'!$A$2:$P$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'5-5'!$A$2:$P$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'6-5'!$A$2:$P$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'7-5'!$A$2:$P$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'8-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'8-5'!$A$2:$P$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'9-5'!$A$2:$P$56</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="722">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -1903,13 +1907,325 @@
   </si>
   <si>
     <t>518/24 võ văn kiệt</t>
+  </si>
+  <si>
+    <t>Cindy Nguyễn</t>
+  </si>
+  <si>
+    <t>HD017482</t>
+  </si>
+  <si>
+    <t>12/7 đường P - Khu phố Mỹ Tú 2 - P. Tân Hưng</t>
+  </si>
+  <si>
+    <t>29-04-2026</t>
+  </si>
+  <si>
+    <t>đơn cũ ck</t>
+  </si>
+  <si>
+    <t>luu tra</t>
+  </si>
+  <si>
+    <t>kh ck shop 1980k</t>
+  </si>
+  <si>
+    <t>VNTH Dịch vụ vận chuyển - NoyNa Thailand Service</t>
+  </si>
+  <si>
+    <t>275/14B1 Đặng Nguyên Cẩn, Phường Phú Lâm</t>
+  </si>
+  <si>
+    <t>AT 08-05</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hải (Bow)</t>
+  </si>
+  <si>
+    <t>17 Đường Số 13 Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Thịnh Nguyễn fb Loan Nguyen</t>
+  </si>
+  <si>
+    <t>HD019175</t>
+  </si>
+  <si>
+    <t>20/15 đường số 8 hẻm 20 phường Long Phước</t>
+  </si>
+  <si>
+    <t>Nhật Nguyên</t>
+  </si>
+  <si>
+    <t>HD019225</t>
+  </si>
+  <si>
+    <t>Nhà Trọ Mai Anh, Ấp 3, Phước kiển (cuối đường b7)</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Kim Ngân</t>
+  </si>
+  <si>
+    <t>HD019275</t>
+  </si>
+  <si>
+    <t>Hẻm 218, An dương vương, phường 16</t>
+  </si>
+  <si>
+    <t>Mi Mi</t>
+  </si>
+  <si>
+    <t>HD018473</t>
+  </si>
+  <si>
+    <t>2 đường 3643 phạm thế hiển p7</t>
+  </si>
+  <si>
+    <t>Tuyến fb Cỏ Đuôi Già</t>
+  </si>
+  <si>
+    <t>HD019271</t>
+  </si>
+  <si>
+    <t>Mai Nguyen</t>
+  </si>
+  <si>
+    <t>HD019299</t>
+  </si>
+  <si>
+    <t>272/21D lê văn quới, phường bình trị đông</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Trà My</t>
+  </si>
+  <si>
+    <t>HD019248</t>
+  </si>
+  <si>
+    <t>325/9 bùi minh trực phường 6</t>
+  </si>
+  <si>
+    <t>Thuy An Dao</t>
+  </si>
+  <si>
+    <t>HD019092</t>
+  </si>
+  <si>
+    <t>Sảnh B2 chung cư Emerald phường Sơn Kỳ</t>
+  </si>
+  <si>
+    <t>HD019293</t>
+  </si>
+  <si>
+    <t>Ngọc Diệp</t>
+  </si>
+  <si>
+    <t>HD019226</t>
+  </si>
+  <si>
+    <t>Ngọc diệp ak neo chung cư akari 77 đại lộ võ văn kiệt p an lạc</t>
+  </si>
+  <si>
+    <t>Trương Kim Hồng</t>
+  </si>
+  <si>
+    <t>HD019237</t>
+  </si>
+  <si>
+    <t>114/15/14 Phạm Văn Chiêu, P.Thông Tây Hội</t>
+  </si>
+  <si>
+    <t>Tần Châu Yến Vy</t>
+  </si>
+  <si>
+    <t>HD019113</t>
+  </si>
+  <si>
+    <t>2B Mai Chí Thọ, Enpi, Toà "lạ thường Thủ Thiêm</t>
+  </si>
+  <si>
+    <t>HD019096</t>
+  </si>
+  <si>
+    <t>W3337</t>
+  </si>
+  <si>
+    <t>HD019276</t>
+  </si>
+  <si>
+    <t>375 tân thới hiệp</t>
+  </si>
+  <si>
+    <t>Thảo Nguyên Thị Nguyễn</t>
+  </si>
+  <si>
+    <t>HD019222</t>
+  </si>
+  <si>
+    <t>40/18 ấp bắc</t>
+  </si>
+  <si>
+    <t>Minh Nguyệt + Lin Xiao</t>
+  </si>
+  <si>
+    <t>HD019184</t>
+  </si>
+  <si>
+    <t>C16 - Lô C1, đg DD5, Phường Đông Hưng Thuận (Sau chợ An Sương)</t>
+  </si>
+  <si>
+    <t>Hà Chi</t>
+  </si>
+  <si>
+    <t>HD014556</t>
+  </si>
+  <si>
+    <t>1400 Đồng Văn Cống, phường Thạnh Mỹ Lợi</t>
+  </si>
+  <si>
+    <t>Mỷ Ý</t>
+  </si>
+  <si>
+    <t>HD019154</t>
+  </si>
+  <si>
+    <t>137 Hoàng Hoa Thám</t>
+  </si>
+  <si>
+    <t>Hoàng Lê Dung</t>
+  </si>
+  <si>
+    <t>HD019266</t>
+  </si>
+  <si>
+    <t>27/24/30 điện biên phủ, F. gia định</t>
+  </si>
+  <si>
+    <t>Trúc Anh</t>
+  </si>
+  <si>
+    <t>HD018871</t>
+  </si>
+  <si>
+    <t>99 trần não phường an khánh</t>
+  </si>
+  <si>
+    <t>Thuý Đào</t>
+  </si>
+  <si>
+    <t>HD019309</t>
+  </si>
+  <si>
+    <t>53/34/49 bình lợi, p13</t>
+  </si>
+  <si>
+    <t>HD019277</t>
+  </si>
+  <si>
+    <t>Phương liên (jun đặng)</t>
+  </si>
+  <si>
+    <t>HD019311</t>
+  </si>
+  <si>
+    <t>241 đông Hưng Thuận 2 phường Tân Hưng</t>
+  </si>
+  <si>
+    <t>Trân Helen</t>
+  </si>
+  <si>
+    <t>HD019219</t>
+  </si>
+  <si>
+    <t>36/15 Yên Thế, Phường Tân Sơn Hoà, Phường Tân Bình</t>
+  </si>
+  <si>
+    <t>HD019156</t>
+  </si>
+  <si>
+    <t>Trần Hạ Mây</t>
+  </si>
+  <si>
+    <t>HD019227</t>
+  </si>
+  <si>
+    <t>Hòm thư A1.11-14, toà Aqua 1, Vinhomes golden river, số 2 Tôn Đức Thắng, phường Bến Nghé</t>
+  </si>
+  <si>
+    <t>Cô Kiều</t>
+  </si>
+  <si>
+    <t>HD019279</t>
+  </si>
+  <si>
+    <t>59/7 điện biên phủ p10</t>
+  </si>
+  <si>
+    <t>Nguyễn Ái My</t>
+  </si>
+  <si>
+    <t>HD019244</t>
+  </si>
+  <si>
+    <t>702/45/31 điện biên phủ phường 13</t>
+  </si>
+  <si>
+    <t>Kim - fb July Phan</t>
+  </si>
+  <si>
+    <t>HD019137</t>
+  </si>
+  <si>
+    <t>86 Lê Thị Riêng p. Bến Thành</t>
+  </si>
+  <si>
+    <t>Trần Thảo Ngân</t>
+  </si>
+  <si>
+    <t>HD019270</t>
+  </si>
+  <si>
+    <t>Ngân 27-19 block G chung cư eco green, đường nguyễn văn linh, phường tân thuận tây</t>
+  </si>
+  <si>
+    <t>borameyyy 015738168</t>
+  </si>
+  <si>
+    <t>HD019089</t>
+  </si>
+  <si>
+    <t>363-365-367 363 Đi Hung Vương, Phường 9</t>
+  </si>
+  <si>
+    <t>Trần Chi</t>
+  </si>
+  <si>
+    <t>HD019216</t>
+  </si>
+  <si>
+    <t>260 Nguyễn Tiểu La P8</t>
+  </si>
+  <si>
+    <t>THU 7</t>
+  </si>
+  <si>
+    <t>NGAY 9-5</t>
+  </si>
+  <si>
+    <t>T7.9.5.2026</t>
+  </si>
+  <si>
+    <t>NGAY 11-5</t>
+  </si>
+  <si>
+    <t>T2.11.5.2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1986,8 +2302,22 @@
       <charset val="163"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2042,8 +2372,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA9694"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2066,12 +2408,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2128,6 +2507,29 @@
     <xf numFmtId="3" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10571,7 +10973,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B35704C-EE25-4E64-8D81-EF9F283336A2}">
-  <dimension ref="A1:R50"/>
+  <dimension ref="A1:R51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
@@ -12206,51 +12608,51 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G38" s="1">
-        <f>SUBTOTAL(9,G3:G37)</f>
+        <f t="shared" ref="G38:R38" si="4">SUBTOTAL(9,G3:G37)</f>
         <v>18545</v>
       </c>
       <c r="H38" s="1">
-        <f>SUBTOTAL(9,H3:H37)</f>
+        <f t="shared" si="4"/>
         <v>930</v>
       </c>
       <c r="I38" s="1">
-        <f>SUBTOTAL(9,I3:I37)</f>
+        <f t="shared" si="4"/>
         <v>17615</v>
       </c>
       <c r="J38" s="1">
-        <f>SUBTOTAL(9,J3:J37)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K38" s="1">
-        <f>SUBTOTAL(9,K3:K37)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L38" s="1">
-        <f>SUBTOTAL(9,L3:L37)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M38" s="1">
-        <f>SUBTOTAL(9,M3:M37)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N38" s="1">
-        <f>SUBTOTAL(9,N3:N37)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O38" s="1">
-        <f>SUBTOTAL(9,O3:O37)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P38" s="1">
-        <f>SUBTOTAL(9,P3:P37)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q38" s="1">
-        <f>SUBTOTAL(9,Q3:Q37)</f>
+        <f t="shared" si="4"/>
         <v>34</v>
       </c>
       <c r="R38" s="1">
-        <f>SUBTOTAL(9,R3:R37)</f>
+        <f t="shared" si="4"/>
         <v>325</v>
       </c>
     </row>
@@ -12344,6 +12746,11 @@
         <f>SUM(J43:J47)</f>
         <v>34</v>
       </c>
+    </row>
+    <row r="51" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H51" s="34"/>
+      <c r="I51" s="35"/>
+      <c r="J51" s="35"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:P36" xr:uid="{00000000-0009-0000-0000-000006000000}">
@@ -12358,6 +12765,1901 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B54A00B3-0891-4E25-BC1A-2BDA276BB257}">
+  <dimension ref="A1:R55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>625</v>
+      </c>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40" t="s">
+        <v>626</v>
+      </c>
+      <c r="F3" s="42">
+        <v>6</v>
+      </c>
+      <c r="G3" s="42">
+        <v>0</v>
+      </c>
+      <c r="H3" s="42">
+        <v>30</v>
+      </c>
+      <c r="I3" s="42">
+        <v>-30</v>
+      </c>
+      <c r="J3" s="40" t="s">
+        <v>627</v>
+      </c>
+      <c r="K3" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="40">
+        <v>46239</v>
+      </c>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40">
+        <v>1</v>
+      </c>
+      <c r="R3" s="43">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="45" t="s">
+        <v>628</v>
+      </c>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45" t="s">
+        <v>629</v>
+      </c>
+      <c r="F4" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="46">
+        <v>0</v>
+      </c>
+      <c r="H4" s="46">
+        <v>35</v>
+      </c>
+      <c r="I4" s="46">
+        <v>-35</v>
+      </c>
+      <c r="J4" s="45" t="s">
+        <v>627</v>
+      </c>
+      <c r="K4" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M4" s="45"/>
+      <c r="N4" s="45"/>
+      <c r="O4" s="45"/>
+      <c r="P4" s="45"/>
+      <c r="Q4" s="45">
+        <v>1</v>
+      </c>
+      <c r="R4" s="43">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="44"/>
+      <c r="B5" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>630</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>631</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>632</v>
+      </c>
+      <c r="F5" s="46">
+        <v>9</v>
+      </c>
+      <c r="G5" s="46">
+        <v>2630</v>
+      </c>
+      <c r="H5" s="46">
+        <v>30</v>
+      </c>
+      <c r="I5" s="46">
+        <v>2600</v>
+      </c>
+      <c r="J5" s="45" t="s">
+        <v>627</v>
+      </c>
+      <c r="K5" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M5" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
+      <c r="P5" s="45"/>
+      <c r="Q5" s="45">
+        <v>1</v>
+      </c>
+      <c r="R5" s="43">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="44"/>
+      <c r="B6" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>633</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>634</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>635</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="G6" s="46">
+        <v>905</v>
+      </c>
+      <c r="H6" s="46">
+        <v>35</v>
+      </c>
+      <c r="I6" s="46">
+        <v>870</v>
+      </c>
+      <c r="J6" s="45" t="s">
+        <v>627</v>
+      </c>
+      <c r="K6" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
+      <c r="P6" s="45"/>
+      <c r="Q6" s="45">
+        <v>1</v>
+      </c>
+      <c r="R6" s="41"/>
+    </row>
+    <row r="7" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="44"/>
+      <c r="B7" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>636</v>
+      </c>
+      <c r="D7" s="45" t="s">
+        <v>637</v>
+      </c>
+      <c r="E7" s="45" t="s">
+        <v>638</v>
+      </c>
+      <c r="F7" s="46">
+        <v>8</v>
+      </c>
+      <c r="G7" s="46">
+        <v>0</v>
+      </c>
+      <c r="H7" s="46">
+        <v>30</v>
+      </c>
+      <c r="I7" s="46">
+        <v>-30</v>
+      </c>
+      <c r="J7" s="45" t="s">
+        <v>627</v>
+      </c>
+      <c r="K7" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M7" s="45"/>
+      <c r="N7" s="45"/>
+      <c r="O7" s="45"/>
+      <c r="P7" s="45"/>
+      <c r="Q7" s="45">
+        <v>1</v>
+      </c>
+      <c r="R7" s="43">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="44"/>
+      <c r="B8" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>639</v>
+      </c>
+      <c r="D8" s="45" t="s">
+        <v>640</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>641</v>
+      </c>
+      <c r="F8" s="46">
+        <v>8</v>
+      </c>
+      <c r="G8" s="46">
+        <v>470</v>
+      </c>
+      <c r="H8" s="46">
+        <v>30</v>
+      </c>
+      <c r="I8" s="46">
+        <v>440</v>
+      </c>
+      <c r="J8" s="45" t="s">
+        <v>627</v>
+      </c>
+      <c r="K8" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M8" s="45"/>
+      <c r="N8" s="45"/>
+      <c r="O8" s="45"/>
+      <c r="P8" s="45"/>
+      <c r="Q8" s="45">
+        <v>1</v>
+      </c>
+      <c r="R8" s="41"/>
+    </row>
+    <row r="9" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="44"/>
+      <c r="B9" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>642</v>
+      </c>
+      <c r="D9" s="45" t="s">
+        <v>643</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>532</v>
+      </c>
+      <c r="F9" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="46">
+        <v>0</v>
+      </c>
+      <c r="H9" s="46">
+        <v>30</v>
+      </c>
+      <c r="I9" s="46">
+        <v>-30</v>
+      </c>
+      <c r="J9" s="45" t="s">
+        <v>627</v>
+      </c>
+      <c r="K9" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M9" s="45"/>
+      <c r="N9" s="45"/>
+      <c r="O9" s="45"/>
+      <c r="P9" s="45"/>
+      <c r="Q9" s="45">
+        <v>1</v>
+      </c>
+      <c r="R9" s="43">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="44"/>
+      <c r="B10" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>644</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>645</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>646</v>
+      </c>
+      <c r="F10" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="46">
+        <v>980</v>
+      </c>
+      <c r="H10" s="46">
+        <v>30</v>
+      </c>
+      <c r="I10" s="46">
+        <v>950</v>
+      </c>
+      <c r="J10" s="45" t="s">
+        <v>627</v>
+      </c>
+      <c r="K10" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M10" s="45"/>
+      <c r="N10" s="45"/>
+      <c r="O10" s="45"/>
+      <c r="P10" s="45"/>
+      <c r="Q10" s="45">
+        <v>1</v>
+      </c>
+      <c r="R10" s="41"/>
+    </row>
+    <row r="11" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="44"/>
+      <c r="B11" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>647</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>648</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>649</v>
+      </c>
+      <c r="F11" s="46">
+        <v>8</v>
+      </c>
+      <c r="G11" s="46">
+        <v>950</v>
+      </c>
+      <c r="H11" s="46">
+        <v>30</v>
+      </c>
+      <c r="I11" s="46">
+        <v>920</v>
+      </c>
+      <c r="J11" s="45" t="s">
+        <v>627</v>
+      </c>
+      <c r="K11" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M11" s="45"/>
+      <c r="N11" s="45"/>
+      <c r="O11" s="45"/>
+      <c r="P11" s="45"/>
+      <c r="Q11" s="45">
+        <v>1</v>
+      </c>
+      <c r="R11" s="41"/>
+    </row>
+    <row r="12" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="44"/>
+      <c r="B12" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>650</v>
+      </c>
+      <c r="D12" s="45" t="s">
+        <v>651</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>652</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="46">
+        <v>895</v>
+      </c>
+      <c r="H12" s="46">
+        <v>25</v>
+      </c>
+      <c r="I12" s="46">
+        <v>870</v>
+      </c>
+      <c r="J12" s="45" t="s">
+        <v>627</v>
+      </c>
+      <c r="K12" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M12" s="45"/>
+      <c r="N12" s="45"/>
+      <c r="O12" s="45"/>
+      <c r="P12" s="45"/>
+      <c r="Q12" s="45">
+        <v>1</v>
+      </c>
+      <c r="R12" s="41"/>
+    </row>
+    <row r="13" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="48"/>
+      <c r="B13" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="49" t="s">
+        <v>653</v>
+      </c>
+      <c r="E13" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="50">
+        <v>8</v>
+      </c>
+      <c r="G13" s="50">
+        <v>0</v>
+      </c>
+      <c r="H13" s="50">
+        <v>30</v>
+      </c>
+      <c r="I13" s="50">
+        <v>-30</v>
+      </c>
+      <c r="J13" s="49" t="s">
+        <v>627</v>
+      </c>
+      <c r="K13" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="49">
+        <v>46239</v>
+      </c>
+      <c r="M13" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="N13" s="49"/>
+      <c r="O13" s="49"/>
+      <c r="P13" s="49"/>
+      <c r="Q13" s="49">
+        <v>1</v>
+      </c>
+      <c r="R13" s="51">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="44"/>
+      <c r="B14" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>654</v>
+      </c>
+      <c r="D14" s="45" t="s">
+        <v>655</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>656</v>
+      </c>
+      <c r="F14" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="46">
+        <v>670</v>
+      </c>
+      <c r="H14" s="46">
+        <v>30</v>
+      </c>
+      <c r="I14" s="46">
+        <v>640</v>
+      </c>
+      <c r="J14" s="45" t="s">
+        <v>627</v>
+      </c>
+      <c r="K14" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M14" s="45"/>
+      <c r="N14" s="45"/>
+      <c r="O14" s="45"/>
+      <c r="P14" s="45"/>
+      <c r="Q14" s="45">
+        <v>1</v>
+      </c>
+      <c r="R14" s="41"/>
+    </row>
+    <row r="15" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="45" t="s">
+        <v>353</v>
+      </c>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45" t="s">
+        <v>354</v>
+      </c>
+      <c r="F15" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="46">
+        <v>30</v>
+      </c>
+      <c r="H15" s="46">
+        <v>30</v>
+      </c>
+      <c r="I15" s="46">
+        <v>0</v>
+      </c>
+      <c r="J15" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M15" s="45"/>
+      <c r="N15" s="45"/>
+      <c r="O15" s="45"/>
+      <c r="P15" s="45"/>
+      <c r="Q15" s="45">
+        <v>1</v>
+      </c>
+      <c r="R15" s="41"/>
+    </row>
+    <row r="16" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="44"/>
+      <c r="B16" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>657</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>658</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>659</v>
+      </c>
+      <c r="F16" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="46">
+        <v>565</v>
+      </c>
+      <c r="H16" s="46">
+        <v>25</v>
+      </c>
+      <c r="I16" s="46">
+        <v>540</v>
+      </c>
+      <c r="J16" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M16" s="45"/>
+      <c r="N16" s="45"/>
+      <c r="O16" s="45"/>
+      <c r="P16" s="45"/>
+      <c r="Q16" s="45">
+        <v>1</v>
+      </c>
+      <c r="R16" s="41"/>
+    </row>
+    <row r="17" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="44"/>
+      <c r="B17" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="45" t="s">
+        <v>660</v>
+      </c>
+      <c r="D17" s="45" t="s">
+        <v>661</v>
+      </c>
+      <c r="E17" s="45" t="s">
+        <v>662</v>
+      </c>
+      <c r="F17" s="46">
+        <v>2</v>
+      </c>
+      <c r="G17" s="46">
+        <v>1670</v>
+      </c>
+      <c r="H17" s="46">
+        <v>30</v>
+      </c>
+      <c r="I17" s="46">
+        <v>1640</v>
+      </c>
+      <c r="J17" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M17" s="45"/>
+      <c r="N17" s="45"/>
+      <c r="O17" s="45"/>
+      <c r="P17" s="45"/>
+      <c r="Q17" s="45">
+        <v>1</v>
+      </c>
+      <c r="R17" s="41"/>
+    </row>
+    <row r="18" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="44"/>
+      <c r="B18" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="45" t="s">
+        <v>339</v>
+      </c>
+      <c r="D18" s="45" t="s">
+        <v>663</v>
+      </c>
+      <c r="E18" s="45" t="s">
+        <v>341</v>
+      </c>
+      <c r="F18" s="46">
+        <v>12</v>
+      </c>
+      <c r="G18" s="46">
+        <v>741</v>
+      </c>
+      <c r="H18" s="46">
+        <v>30</v>
+      </c>
+      <c r="I18" s="46">
+        <v>711</v>
+      </c>
+      <c r="J18" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M18" s="45"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="45"/>
+      <c r="P18" s="45"/>
+      <c r="Q18" s="45">
+        <v>1</v>
+      </c>
+      <c r="R18" s="41"/>
+    </row>
+    <row r="19" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="44"/>
+      <c r="B19" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="45" t="s">
+        <v>664</v>
+      </c>
+      <c r="D19" s="45" t="s">
+        <v>665</v>
+      </c>
+      <c r="E19" s="45" t="s">
+        <v>666</v>
+      </c>
+      <c r="F19" s="46">
+        <v>12</v>
+      </c>
+      <c r="G19" s="46">
+        <v>0</v>
+      </c>
+      <c r="H19" s="46">
+        <v>30</v>
+      </c>
+      <c r="I19" s="46">
+        <v>-30</v>
+      </c>
+      <c r="J19" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M19" s="45"/>
+      <c r="N19" s="45"/>
+      <c r="O19" s="45"/>
+      <c r="P19" s="45"/>
+      <c r="Q19" s="45">
+        <v>1</v>
+      </c>
+      <c r="R19" s="43">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="44"/>
+      <c r="B20" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="45" t="s">
+        <v>667</v>
+      </c>
+      <c r="D20" s="45" t="s">
+        <v>668</v>
+      </c>
+      <c r="E20" s="45" t="s">
+        <v>669</v>
+      </c>
+      <c r="F20" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="G20" s="46">
+        <v>805</v>
+      </c>
+      <c r="H20" s="46">
+        <v>25</v>
+      </c>
+      <c r="I20" s="46">
+        <v>780</v>
+      </c>
+      <c r="J20" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M20" s="45"/>
+      <c r="N20" s="45"/>
+      <c r="O20" s="45"/>
+      <c r="P20" s="45"/>
+      <c r="Q20" s="45">
+        <v>1</v>
+      </c>
+      <c r="R20" s="41"/>
+    </row>
+    <row r="21" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="44"/>
+      <c r="B21" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="45" t="s">
+        <v>670</v>
+      </c>
+      <c r="D21" s="45" t="s">
+        <v>671</v>
+      </c>
+      <c r="E21" s="45" t="s">
+        <v>672</v>
+      </c>
+      <c r="F21" s="46">
+        <v>12</v>
+      </c>
+      <c r="G21" s="46">
+        <v>0</v>
+      </c>
+      <c r="H21" s="46">
+        <v>30</v>
+      </c>
+      <c r="I21" s="46">
+        <v>-30</v>
+      </c>
+      <c r="J21" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M21" s="45"/>
+      <c r="N21" s="45"/>
+      <c r="O21" s="45"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="45">
+        <v>1</v>
+      </c>
+      <c r="R21" s="43">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="44"/>
+      <c r="B22" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="45" t="s">
+        <v>673</v>
+      </c>
+      <c r="D22" s="45" t="s">
+        <v>674</v>
+      </c>
+      <c r="E22" s="45" t="s">
+        <v>675</v>
+      </c>
+      <c r="F22" s="46">
+        <v>2</v>
+      </c>
+      <c r="G22" s="46">
+        <v>30</v>
+      </c>
+      <c r="H22" s="46">
+        <v>30</v>
+      </c>
+      <c r="I22" s="46">
+        <v>0</v>
+      </c>
+      <c r="J22" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M22" s="45"/>
+      <c r="N22" s="45"/>
+      <c r="O22" s="45"/>
+      <c r="P22" s="45"/>
+      <c r="Q22" s="45">
+        <v>1</v>
+      </c>
+      <c r="R22" s="41"/>
+    </row>
+    <row r="23" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="44"/>
+      <c r="B23" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="45" t="s">
+        <v>676</v>
+      </c>
+      <c r="D23" s="45" t="s">
+        <v>677</v>
+      </c>
+      <c r="E23" s="45" t="s">
+        <v>678</v>
+      </c>
+      <c r="F23" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="G23" s="46">
+        <v>50</v>
+      </c>
+      <c r="H23" s="46">
+        <v>50</v>
+      </c>
+      <c r="I23" s="46">
+        <v>0</v>
+      </c>
+      <c r="J23" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="45"/>
+      <c r="P23" s="45"/>
+      <c r="Q23" s="45">
+        <v>1</v>
+      </c>
+      <c r="R23" s="41"/>
+    </row>
+    <row r="24" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="44"/>
+      <c r="B24" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="45" t="s">
+        <v>679</v>
+      </c>
+      <c r="D24" s="45" t="s">
+        <v>680</v>
+      </c>
+      <c r="E24" s="45" t="s">
+        <v>681</v>
+      </c>
+      <c r="F24" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" s="46">
+        <v>710</v>
+      </c>
+      <c r="H24" s="46">
+        <v>20</v>
+      </c>
+      <c r="I24" s="46">
+        <v>690</v>
+      </c>
+      <c r="J24" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M24" s="45"/>
+      <c r="N24" s="45"/>
+      <c r="O24" s="45"/>
+      <c r="P24" s="45"/>
+      <c r="Q24" s="45">
+        <v>1</v>
+      </c>
+      <c r="R24" s="41"/>
+    </row>
+    <row r="25" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="44"/>
+      <c r="B25" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="45" t="s">
+        <v>682</v>
+      </c>
+      <c r="D25" s="45" t="s">
+        <v>683</v>
+      </c>
+      <c r="E25" s="45" t="s">
+        <v>684</v>
+      </c>
+      <c r="F25" s="46">
+        <v>2</v>
+      </c>
+      <c r="G25" s="46">
+        <v>820</v>
+      </c>
+      <c r="H25" s="46">
+        <v>30</v>
+      </c>
+      <c r="I25" s="46">
+        <v>790</v>
+      </c>
+      <c r="J25" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M25" s="45"/>
+      <c r="N25" s="45"/>
+      <c r="O25" s="45"/>
+      <c r="P25" s="45"/>
+      <c r="Q25" s="45">
+        <v>1</v>
+      </c>
+      <c r="R25" s="41"/>
+    </row>
+    <row r="26" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="44"/>
+      <c r="B26" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="45" t="s">
+        <v>685</v>
+      </c>
+      <c r="D26" s="45" t="s">
+        <v>686</v>
+      </c>
+      <c r="E26" s="45" t="s">
+        <v>687</v>
+      </c>
+      <c r="F26" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="G26" s="46">
+        <v>880</v>
+      </c>
+      <c r="H26" s="46">
+        <v>20</v>
+      </c>
+      <c r="I26" s="46">
+        <v>860</v>
+      </c>
+      <c r="J26" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="K26" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="45"/>
+      <c r="P26" s="45"/>
+      <c r="Q26" s="45">
+        <v>1</v>
+      </c>
+      <c r="R26" s="41"/>
+    </row>
+    <row r="27" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="44"/>
+      <c r="B27" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="45" t="s">
+        <v>348</v>
+      </c>
+      <c r="D27" s="45" t="s">
+        <v>688</v>
+      </c>
+      <c r="E27" s="45" t="s">
+        <v>350</v>
+      </c>
+      <c r="F27" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" s="46">
+        <v>845</v>
+      </c>
+      <c r="H27" s="46">
+        <v>25</v>
+      </c>
+      <c r="I27" s="46">
+        <v>820</v>
+      </c>
+      <c r="J27" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="K27" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M27" s="45"/>
+      <c r="N27" s="45"/>
+      <c r="O27" s="45"/>
+      <c r="P27" s="45"/>
+      <c r="Q27" s="45">
+        <v>1</v>
+      </c>
+      <c r="R27" s="41"/>
+    </row>
+    <row r="28" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="44"/>
+      <c r="B28" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="45" t="s">
+        <v>689</v>
+      </c>
+      <c r="D28" s="45" t="s">
+        <v>690</v>
+      </c>
+      <c r="E28" s="45" t="s">
+        <v>691</v>
+      </c>
+      <c r="F28" s="46">
+        <v>12</v>
+      </c>
+      <c r="G28" s="46">
+        <v>0</v>
+      </c>
+      <c r="H28" s="46">
+        <v>30</v>
+      </c>
+      <c r="I28" s="46">
+        <v>-30</v>
+      </c>
+      <c r="J28" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="K28" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M28" s="45"/>
+      <c r="N28" s="45"/>
+      <c r="O28" s="45"/>
+      <c r="P28" s="45"/>
+      <c r="Q28" s="45">
+        <v>1</v>
+      </c>
+      <c r="R28" s="43">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="45" t="s">
+        <v>420</v>
+      </c>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45" t="s">
+        <v>421</v>
+      </c>
+      <c r="F29" s="46">
+        <v>1</v>
+      </c>
+      <c r="G29" s="46">
+        <v>0</v>
+      </c>
+      <c r="H29" s="46">
+        <v>30</v>
+      </c>
+      <c r="I29" s="46">
+        <v>-30</v>
+      </c>
+      <c r="J29" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="K29" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M29" s="45"/>
+      <c r="N29" s="45"/>
+      <c r="O29" s="45"/>
+      <c r="P29" s="45"/>
+      <c r="Q29" s="45">
+        <v>1</v>
+      </c>
+      <c r="R29" s="43">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="44"/>
+      <c r="B30" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="45" t="s">
+        <v>692</v>
+      </c>
+      <c r="D30" s="45" t="s">
+        <v>693</v>
+      </c>
+      <c r="E30" s="45" t="s">
+        <v>694</v>
+      </c>
+      <c r="F30" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="G30" s="46">
+        <v>0</v>
+      </c>
+      <c r="H30" s="46">
+        <v>25</v>
+      </c>
+      <c r="I30" s="46">
+        <v>-25</v>
+      </c>
+      <c r="J30" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="K30" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M30" s="45"/>
+      <c r="N30" s="45"/>
+      <c r="O30" s="45"/>
+      <c r="P30" s="45"/>
+      <c r="Q30" s="45">
+        <v>1</v>
+      </c>
+      <c r="R30" s="43">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="44"/>
+      <c r="B31" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="45" t="s">
+        <v>196</v>
+      </c>
+      <c r="D31" s="45" t="s">
+        <v>695</v>
+      </c>
+      <c r="E31" s="45" t="s">
+        <v>198</v>
+      </c>
+      <c r="F31" s="46">
+        <v>4</v>
+      </c>
+      <c r="G31" s="46">
+        <v>885</v>
+      </c>
+      <c r="H31" s="46">
+        <v>25</v>
+      </c>
+      <c r="I31" s="46">
+        <v>860</v>
+      </c>
+      <c r="J31" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="K31" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M31" s="45"/>
+      <c r="N31" s="45"/>
+      <c r="O31" s="45"/>
+      <c r="P31" s="45"/>
+      <c r="Q31" s="45">
+        <v>1</v>
+      </c>
+      <c r="R31" s="41"/>
+    </row>
+    <row r="32" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="44"/>
+      <c r="B32" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="45" t="s">
+        <v>696</v>
+      </c>
+      <c r="D32" s="45" t="s">
+        <v>697</v>
+      </c>
+      <c r="E32" s="45" t="s">
+        <v>698</v>
+      </c>
+      <c r="F32" s="46">
+        <v>1</v>
+      </c>
+      <c r="G32" s="46">
+        <v>825</v>
+      </c>
+      <c r="H32" s="46">
+        <v>25</v>
+      </c>
+      <c r="I32" s="46">
+        <v>800</v>
+      </c>
+      <c r="J32" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="K32" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L32" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M32" s="45"/>
+      <c r="N32" s="45"/>
+      <c r="O32" s="45"/>
+      <c r="P32" s="45"/>
+      <c r="Q32" s="45">
+        <v>1</v>
+      </c>
+      <c r="R32" s="41"/>
+    </row>
+    <row r="33" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="44"/>
+      <c r="B33" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="45" t="s">
+        <v>699</v>
+      </c>
+      <c r="D33" s="45" t="s">
+        <v>700</v>
+      </c>
+      <c r="E33" s="45" t="s">
+        <v>701</v>
+      </c>
+      <c r="F33" s="46">
+        <v>10</v>
+      </c>
+      <c r="G33" s="46">
+        <v>0</v>
+      </c>
+      <c r="H33" s="46">
+        <v>25</v>
+      </c>
+      <c r="I33" s="46">
+        <v>-25</v>
+      </c>
+      <c r="J33" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="K33" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M33" s="45"/>
+      <c r="N33" s="45"/>
+      <c r="O33" s="45"/>
+      <c r="P33" s="45"/>
+      <c r="Q33" s="45">
+        <v>1</v>
+      </c>
+      <c r="R33" s="43">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="44"/>
+      <c r="B34" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="45" t="s">
+        <v>702</v>
+      </c>
+      <c r="D34" s="45" t="s">
+        <v>703</v>
+      </c>
+      <c r="E34" s="45" t="s">
+        <v>704</v>
+      </c>
+      <c r="F34" s="46">
+        <v>10</v>
+      </c>
+      <c r="G34" s="46">
+        <v>815</v>
+      </c>
+      <c r="H34" s="46">
+        <v>25</v>
+      </c>
+      <c r="I34" s="46">
+        <v>790</v>
+      </c>
+      <c r="J34" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="K34" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M34" s="45"/>
+      <c r="N34" s="45"/>
+      <c r="O34" s="45"/>
+      <c r="P34" s="45"/>
+      <c r="Q34" s="45">
+        <v>1</v>
+      </c>
+      <c r="R34" s="41"/>
+    </row>
+    <row r="35" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="48"/>
+      <c r="B35" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="49" t="s">
+        <v>705</v>
+      </c>
+      <c r="D35" s="49" t="s">
+        <v>706</v>
+      </c>
+      <c r="E35" s="49" t="s">
+        <v>707</v>
+      </c>
+      <c r="F35" s="50">
+        <v>1</v>
+      </c>
+      <c r="G35" s="50">
+        <v>25</v>
+      </c>
+      <c r="H35" s="50">
+        <v>25</v>
+      </c>
+      <c r="I35" s="50">
+        <v>0</v>
+      </c>
+      <c r="J35" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="K35" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" s="49">
+        <v>46239</v>
+      </c>
+      <c r="M35" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="N35" s="49"/>
+      <c r="O35" s="49"/>
+      <c r="P35" s="49"/>
+      <c r="Q35" s="49">
+        <v>1</v>
+      </c>
+      <c r="R35" s="52"/>
+    </row>
+    <row r="36" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="44"/>
+      <c r="B36" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="45" t="s">
+        <v>708</v>
+      </c>
+      <c r="D36" s="45" t="s">
+        <v>709</v>
+      </c>
+      <c r="E36" s="45" t="s">
+        <v>710</v>
+      </c>
+      <c r="F36" s="46">
+        <v>7</v>
+      </c>
+      <c r="G36" s="46">
+        <v>850</v>
+      </c>
+      <c r="H36" s="46">
+        <v>30</v>
+      </c>
+      <c r="I36" s="46">
+        <v>820</v>
+      </c>
+      <c r="J36" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="K36" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M36" s="45"/>
+      <c r="N36" s="45"/>
+      <c r="O36" s="45"/>
+      <c r="P36" s="45"/>
+      <c r="Q36" s="45">
+        <v>1</v>
+      </c>
+      <c r="R36" s="41"/>
+    </row>
+    <row r="37" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="44"/>
+      <c r="B37" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="45" t="s">
+        <v>711</v>
+      </c>
+      <c r="D37" s="45" t="s">
+        <v>712</v>
+      </c>
+      <c r="E37" s="45" t="s">
+        <v>713</v>
+      </c>
+      <c r="F37" s="46">
+        <v>5</v>
+      </c>
+      <c r="G37" s="46">
+        <v>0</v>
+      </c>
+      <c r="H37" s="46">
+        <v>25</v>
+      </c>
+      <c r="I37" s="46">
+        <v>-25</v>
+      </c>
+      <c r="J37" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="K37" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L37" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M37" s="45"/>
+      <c r="N37" s="45"/>
+      <c r="O37" s="45"/>
+      <c r="P37" s="45"/>
+      <c r="Q37" s="45">
+        <v>1</v>
+      </c>
+      <c r="R37" s="43">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="44"/>
+      <c r="B38" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="45" t="s">
+        <v>714</v>
+      </c>
+      <c r="D38" s="45" t="s">
+        <v>715</v>
+      </c>
+      <c r="E38" s="45" t="s">
+        <v>716</v>
+      </c>
+      <c r="F38" s="46">
+        <v>10</v>
+      </c>
+      <c r="G38" s="46">
+        <v>455</v>
+      </c>
+      <c r="H38" s="46">
+        <v>25</v>
+      </c>
+      <c r="I38" s="46">
+        <v>430</v>
+      </c>
+      <c r="J38" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="K38" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38" s="45">
+        <v>46239</v>
+      </c>
+      <c r="M38" s="45"/>
+      <c r="N38" s="45"/>
+      <c r="O38" s="45"/>
+      <c r="P38" s="45"/>
+      <c r="Q38" s="45">
+        <v>1</v>
+      </c>
+      <c r="R38" s="41"/>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G40" s="1">
+        <f t="shared" ref="G40:R40" si="0">SUBTOTAL(9,G3:G39)</f>
+        <v>18501</v>
+      </c>
+      <c r="H40" s="1">
+        <f t="shared" si="0"/>
+        <v>1030</v>
+      </c>
+      <c r="I40" s="1">
+        <f t="shared" si="0"/>
+        <v>17471</v>
+      </c>
+      <c r="J40" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L40" s="1">
+        <f t="shared" si="0"/>
+        <v>1664604</v>
+      </c>
+      <c r="M40" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N40" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O40" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P40" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q40" s="1">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="R40" s="1">
+        <f t="shared" si="0"/>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I41" s="1">
+        <v>-1980</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H44" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H45" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" s="8">
+        <f>SUM(I39:I43)</f>
+        <v>15491</v>
+      </c>
+      <c r="J45" s="8">
+        <f>Q40</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H46" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I46" s="10">
+        <f>R40</f>
+        <v>380</v>
+      </c>
+      <c r="J46" s="11"/>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H47" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" s="10">
+        <f>S39</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="11"/>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H48" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" s="10">
+        <f>T39</f>
+        <v>0</v>
+      </c>
+      <c r="J48" s="11"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H49" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I49" s="10">
+        <f>U39</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="11"/>
+    </row>
+    <row r="50" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H50" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
+    </row>
+    <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H51" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+    </row>
+    <row r="52" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H52" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I52" s="16">
+        <f>SUM(I45:I51)</f>
+        <v>15871</v>
+      </c>
+      <c r="J52" s="16">
+        <f>SUM(J45:J49)</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B55" s="36" t="s">
+        <v>618</v>
+      </c>
+      <c r="C55" s="36" t="s">
+        <v>619</v>
+      </c>
+      <c r="D55" s="36" t="s">
+        <v>620</v>
+      </c>
+      <c r="E55" s="37">
+        <v>7</v>
+      </c>
+      <c r="F55" s="37">
+        <v>1980</v>
+      </c>
+      <c r="G55" s="37">
+        <v>0</v>
+      </c>
+      <c r="H55" s="37">
+        <f>F55-G55</f>
+        <v>1980</v>
+      </c>
+      <c r="I55" s="36" t="s">
+        <v>623</v>
+      </c>
+      <c r="J55" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="K55" s="36" t="s">
+        <v>621</v>
+      </c>
+      <c r="L55" s="38" t="s">
+        <v>624</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P38" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P38">
+      <sortCondition ref="J2:J38"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52BDCE89-8A5E-4F72-A1A8-5286164E7275}">
   <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12374,10 +14676,10 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>717</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>520</v>
+        <v>718</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -13530,7 +15832,1281 @@
     </row>
     <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H62" s="4" t="s">
-        <v>521</v>
+        <v>719</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I63" s="8">
+        <f>SUM(I57:I61)</f>
+        <v>0</v>
+      </c>
+      <c r="J63" s="8">
+        <f>Q58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H64" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I64" s="10">
+        <f>R58</f>
+        <v>0</v>
+      </c>
+      <c r="J64" s="11"/>
+    </row>
+    <row r="65" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H65" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I65" s="10">
+        <f>S57</f>
+        <v>0</v>
+      </c>
+      <c r="J65" s="11"/>
+    </row>
+    <row r="66" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H66" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" s="10">
+        <f>T57</f>
+        <v>0</v>
+      </c>
+      <c r="J66" s="11"/>
+    </row>
+    <row r="67" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H67" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I67" s="10">
+        <f>U57</f>
+        <v>0</v>
+      </c>
+      <c r="J67" s="11"/>
+    </row>
+    <row r="68" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H68" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+    </row>
+    <row r="69" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H69" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
+    </row>
+    <row r="70" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H70" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I70" s="16">
+        <f>SUM(I63:I69)</f>
+        <v>0</v>
+      </c>
+      <c r="J70" s="16">
+        <f>SUM(J63:J67)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P56" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P56">
+      <sortCondition ref="J2:J56"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EA17D5-9933-4EE3-ACD1-20C1C25F3DB5}">
+  <dimension ref="A1:R70"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+    </row>
+    <row r="4" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+    </row>
+    <row r="5" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="20"/>
+    </row>
+    <row r="6" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+    </row>
+    <row r="7" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="20"/>
+    </row>
+    <row r="8" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+    </row>
+    <row r="9" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+    </row>
+    <row r="10" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="20"/>
+    </row>
+    <row r="11" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="20"/>
+    </row>
+    <row r="12" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+    </row>
+    <row r="13" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+    </row>
+    <row r="14" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+    </row>
+    <row r="15" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="20"/>
+    </row>
+    <row r="16" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="20"/>
+    </row>
+    <row r="17" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="20"/>
+    </row>
+    <row r="18" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+    </row>
+    <row r="19" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="20"/>
+    </row>
+    <row r="20" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+    </row>
+    <row r="21" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+    </row>
+    <row r="22" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+    </row>
+    <row r="23" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="20"/>
+    </row>
+    <row r="24" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+    </row>
+    <row r="25" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="20"/>
+    </row>
+    <row r="26" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+    </row>
+    <row r="27" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+    </row>
+    <row r="28" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="20"/>
+    </row>
+    <row r="29" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="20"/>
+    </row>
+    <row r="30" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+    </row>
+    <row r="31" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17"/>
+    </row>
+    <row r="32" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+    </row>
+    <row r="33" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="20"/>
+    </row>
+    <row r="34" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+    </row>
+    <row r="35" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+    </row>
+    <row r="36" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="20"/>
+    </row>
+    <row r="37" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+    </row>
+    <row r="38" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+    </row>
+    <row r="39" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="17"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="20"/>
+    </row>
+    <row r="40" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+    </row>
+    <row r="41" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+    </row>
+    <row r="42" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="17"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+    </row>
+    <row r="43" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17"/>
+      <c r="P43" s="17"/>
+      <c r="Q43" s="17"/>
+      <c r="R43" s="20"/>
+    </row>
+    <row r="44" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="17"/>
+    </row>
+    <row r="45" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="20"/>
+    </row>
+    <row r="46" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="17"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17"/>
+      <c r="P46" s="17"/>
+      <c r="Q46" s="17"/>
+      <c r="R46" s="20"/>
+    </row>
+    <row r="47" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="17"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="17"/>
+      <c r="M47" s="17"/>
+      <c r="N47" s="17"/>
+      <c r="O47" s="17"/>
+      <c r="P47" s="17"/>
+      <c r="Q47" s="17"/>
+    </row>
+    <row r="48" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="17"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
+      <c r="Q48" s="17"/>
+    </row>
+    <row r="49" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="17"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
+      <c r="L49" s="17"/>
+      <c r="M49" s="17"/>
+      <c r="N49" s="17"/>
+      <c r="O49" s="17"/>
+      <c r="P49" s="17"/>
+      <c r="Q49" s="17"/>
+      <c r="R49" s="20"/>
+    </row>
+    <row r="50" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="17"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="17"/>
+      <c r="M50" s="17"/>
+      <c r="N50" s="17"/>
+      <c r="O50" s="17"/>
+      <c r="P50" s="17"/>
+      <c r="Q50" s="17"/>
+    </row>
+    <row r="51" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="17"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="18"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="17"/>
+      <c r="M51" s="17"/>
+      <c r="N51" s="17"/>
+      <c r="O51" s="17"/>
+      <c r="P51" s="17"/>
+      <c r="Q51" s="17"/>
+    </row>
+    <row r="52" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="17"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
+      <c r="N52" s="17"/>
+      <c r="O52" s="17"/>
+      <c r="P52" s="17"/>
+      <c r="Q52" s="17"/>
+      <c r="R52" s="20"/>
+    </row>
+    <row r="53" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="17"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="17"/>
+      <c r="L53" s="17"/>
+      <c r="M53" s="17"/>
+      <c r="N53" s="17"/>
+      <c r="O53" s="17"/>
+      <c r="P53" s="17"/>
+      <c r="Q53" s="17"/>
+    </row>
+    <row r="54" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="17"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
+      <c r="O54" s="17"/>
+      <c r="P54" s="17"/>
+      <c r="Q54" s="17"/>
+    </row>
+    <row r="55" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="17"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="17"/>
+      <c r="K55" s="17"/>
+      <c r="L55" s="17"/>
+      <c r="M55" s="17"/>
+      <c r="N55" s="17"/>
+      <c r="O55" s="17"/>
+      <c r="P55" s="17"/>
+      <c r="Q55" s="17"/>
+    </row>
+    <row r="56" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="17"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="17"/>
+      <c r="M56" s="17"/>
+      <c r="N56" s="17"/>
+      <c r="O56" s="17"/>
+      <c r="P56" s="17"/>
+      <c r="Q56" s="17"/>
+      <c r="R56" s="20"/>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G58" s="1">
+        <f t="shared" ref="G58:R58" si="0">SUBTOTAL(9,G3:G57)</f>
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H62" s="4" t="s">
+        <v>721</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>15</v>

--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE0C0A2-39A0-47B1-ACA2-E9F7AFF6E7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C41E2E2-63DA-484F-9441-1533B6076FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-5" sheetId="3" r:id="rId1"/>
@@ -21,16 +21,18 @@
     <sheet name="8-5" sheetId="8" r:id="rId6"/>
     <sheet name="9-5" sheetId="9" r:id="rId7"/>
     <sheet name="11-5" sheetId="10" r:id="rId8"/>
+    <sheet name="12-5" sheetId="11" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'11-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'12-5'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-5'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'4-5'!$A$2:$P$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'5-5'!$A$2:$P$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'6-5'!$A$2:$P$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'7-5'!$A$2:$P$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'8-5'!$A$2:$P$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'9-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'9-5'!$A$2:$P$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2235" uniqueCount="803">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -2219,6 +2221,249 @@
   </si>
   <si>
     <t>T2.11.5.2026</t>
+  </si>
+  <si>
+    <t>KIỀU HOANH</t>
+  </si>
+  <si>
+    <t>277 âu dương lân p2</t>
+  </si>
+  <si>
+    <t>AT 09-05</t>
+  </si>
+  <si>
+    <t>09-05-2026</t>
+  </si>
+  <si>
+    <t>THƯƠNG</t>
+  </si>
+  <si>
+    <t>49 TX22, phường Thới An</t>
+  </si>
+  <si>
+    <t>TUYẾT NHI</t>
+  </si>
+  <si>
+    <t>170F Tân Hoà Đông f14</t>
+  </si>
+  <si>
+    <t>Nguyễn Hà</t>
+  </si>
+  <si>
+    <t>HD019502</t>
+  </si>
+  <si>
+    <t>007 Lô B chung cư Tây Thạnh phường Tân Thạnh</t>
+  </si>
+  <si>
+    <t>HD019300</t>
+  </si>
+  <si>
+    <t>Barmey Bori Ev26146</t>
+  </si>
+  <si>
+    <t>HD019327</t>
+  </si>
+  <si>
+    <t>315/18/6 Nhuyễn Thị Tú, Phường Bình Hưng Hòa B</t>
+  </si>
+  <si>
+    <t>Hạnh Trần</t>
+  </si>
+  <si>
+    <t>HD019306</t>
+  </si>
+  <si>
+    <t>Chung cư Tecco, block C, đường Nguyễn Cửu Phủ, phường Tân Tạo</t>
+  </si>
+  <si>
+    <t>Huyền Nhung</t>
+  </si>
+  <si>
+    <t>HD019331</t>
+  </si>
+  <si>
+    <t>910 Nguyễn chí thanh, p4</t>
+  </si>
+  <si>
+    <t>Thu Hà</t>
+  </si>
+  <si>
+    <t>HD019369</t>
+  </si>
+  <si>
+    <t>số 201/12 mã văn lò, p, bình trị đông a</t>
+  </si>
+  <si>
+    <t>Thuý Heri</t>
+  </si>
+  <si>
+    <t>HD019180</t>
+  </si>
+  <si>
+    <t>184/17/35 bãi sậy, phường bình tiên</t>
+  </si>
+  <si>
+    <t>Thy Mai</t>
+  </si>
+  <si>
+    <t>HD019514</t>
+  </si>
+  <si>
+    <t>2 nguyễn văn tưởng, phường tân phú</t>
+  </si>
+  <si>
+    <t>Isabella</t>
+  </si>
+  <si>
+    <t>494/1/12 Le Quang Dinh, P1</t>
+  </si>
+  <si>
+    <t>NGUYỄN MINH DUY</t>
+  </si>
+  <si>
+    <t>90/35 Trần Văn Ơn, Phường Tân Sơn Nhì</t>
+  </si>
+  <si>
+    <t>Thanh Thao</t>
+  </si>
+  <si>
+    <t>HD019454</t>
+  </si>
+  <si>
+    <t>9a8, Chung cư Phúc Yên 1, 31 Phan Huy Ích, p Tân sơn</t>
+  </si>
+  <si>
+    <t>Trang Phan</t>
+  </si>
+  <si>
+    <t>HD019513</t>
+  </si>
+  <si>
+    <t>162/25, Đường Nguyễn Văn Khối, Phường 8</t>
+  </si>
+  <si>
+    <t>Phạm Dung</t>
+  </si>
+  <si>
+    <t>HD019531</t>
+  </si>
+  <si>
+    <t>208 nguyễn hữu cảnh phường 22 chung cư vinhome toà lanmark 5</t>
+  </si>
+  <si>
+    <t>mai anh</t>
+  </si>
+  <si>
+    <t>HD019506</t>
+  </si>
+  <si>
+    <t>Gate 4 - Feliz en vista, 1 trương văn bang, thạnh mỹ lợi 42 Toà cruz - C810</t>
+  </si>
+  <si>
+    <t>Minh Uyên (Kaydis T Ha)</t>
+  </si>
+  <si>
+    <t>HD019522</t>
+  </si>
+  <si>
+    <t>154/4/7, Nguyễn Phúc Chu Phường 15</t>
+  </si>
+  <si>
+    <t>HD019413</t>
+  </si>
+  <si>
+    <t>32B đường số 8 thông tây hội</t>
+  </si>
+  <si>
+    <t>HD019503</t>
+  </si>
+  <si>
+    <t>HD018297</t>
+  </si>
+  <si>
+    <t>SU MO</t>
+  </si>
+  <si>
+    <t>487 le van sy f12</t>
+  </si>
+  <si>
+    <t>NOTE GỬI CHO SU ANH</t>
+  </si>
+  <si>
+    <t>22/40 Yên Thế, P2, Tân Bình</t>
+  </si>
+  <si>
+    <t>Ashley Khin (inst ashley__khin)</t>
+  </si>
+  <si>
+    <t>HD015540</t>
+  </si>
+  <si>
+    <t>100/2A Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>kh ck shop 975k</t>
+  </si>
+  <si>
+    <t>Kimchou Try</t>
+  </si>
+  <si>
+    <t>HD019523</t>
+  </si>
+  <si>
+    <t>301 Pham Ngu Lao Street</t>
+  </si>
+  <si>
+    <t>HD019430</t>
+  </si>
+  <si>
+    <t>702/45/31 điện biên phủ phường 10</t>
+  </si>
+  <si>
+    <t>Minh Ngọc</t>
+  </si>
+  <si>
+    <t>HD019516</t>
+  </si>
+  <si>
+    <t>Vincom đồng khởi 45 lý tự trọng căn hộ 2604</t>
+  </si>
+  <si>
+    <t>Lê Nguyễn Nhật Ánh</t>
+  </si>
+  <si>
+    <t>HD019357</t>
+  </si>
+  <si>
+    <t>orchid 1, Hà Đô Centrosa, 118 3/2, phường Hòa Hưng</t>
+  </si>
+  <si>
+    <t>Kim Mese Phan</t>
+  </si>
+  <si>
+    <t>HD019317</t>
+  </si>
+  <si>
+    <t>72 bùi hữu nghĩa p7</t>
+  </si>
+  <si>
+    <t>Hương Giang SHIP GIỜ HÀNH CHÍNH</t>
+  </si>
+  <si>
+    <t>HDO19455</t>
+  </si>
+  <si>
+    <t>92 Nguyễn Trãi, phường Bến Thành</t>
+  </si>
+  <si>
+    <t>đơn ck</t>
+  </si>
+  <si>
+    <t>NGAY 12-5</t>
+  </si>
+  <si>
+    <t>T3.12.5.2026</t>
   </si>
 </sst>
 </file>
@@ -14660,7 +14905,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52BDCE89-8A5E-4F72-A1A8-5286164E7275}">
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
@@ -14733,1198 +14978,1613 @@
       </c>
       <c r="Q2" s="3"/>
     </row>
-    <row r="3" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-    </row>
-    <row r="4" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-    </row>
-    <row r="5" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="20"/>
-    </row>
-    <row r="6" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-    </row>
-    <row r="7" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="20"/>
-    </row>
-    <row r="8" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-    </row>
-    <row r="9" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-    </row>
-    <row r="10" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="20"/>
-    </row>
-    <row r="11" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="20"/>
-    </row>
-    <row r="12" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-    </row>
-    <row r="13" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-    </row>
-    <row r="14" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-    </row>
-    <row r="15" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="20"/>
-    </row>
-    <row r="16" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="20"/>
-    </row>
-    <row r="17" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="20"/>
-    </row>
-    <row r="18" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-    </row>
-    <row r="19" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="20"/>
-    </row>
-    <row r="20" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
-    </row>
-    <row r="21" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-    </row>
-    <row r="22" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-    </row>
-    <row r="23" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="20"/>
-    </row>
-    <row r="24" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
-    </row>
-    <row r="25" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="20"/>
-    </row>
-    <row r="26" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
-    </row>
-    <row r="27" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
-    </row>
-    <row r="28" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="20"/>
-    </row>
-    <row r="29" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="20"/>
-    </row>
-    <row r="30" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
-      <c r="P30" s="17"/>
-      <c r="Q30" s="17"/>
-    </row>
-    <row r="31" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17"/>
-      <c r="O31" s="17"/>
-      <c r="P31" s="17"/>
-      <c r="Q31" s="17"/>
-    </row>
-    <row r="32" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="17"/>
-      <c r="P32" s="17"/>
-      <c r="Q32" s="17"/>
-    </row>
-    <row r="33" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
-      <c r="P33" s="17"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="20"/>
-    </row>
-    <row r="34" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="17"/>
-    </row>
-    <row r="35" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
-    </row>
-    <row r="36" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="17"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17"/>
-      <c r="P36" s="17"/>
-      <c r="Q36" s="17"/>
-      <c r="R36" s="20"/>
-    </row>
-    <row r="37" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="17"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
-    </row>
-    <row r="38" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="17"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
-      <c r="N38" s="17"/>
-      <c r="O38" s="17"/>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17"/>
-    </row>
-    <row r="39" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="17"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
-      <c r="N39" s="17"/>
-      <c r="O39" s="17"/>
-      <c r="P39" s="17"/>
-      <c r="Q39" s="17"/>
-      <c r="R39" s="20"/>
-    </row>
-    <row r="40" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
-      <c r="N40" s="17"/>
-      <c r="O40" s="17"/>
-      <c r="P40" s="17"/>
-      <c r="Q40" s="17"/>
-    </row>
-    <row r="41" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
-      <c r="N41" s="17"/>
-      <c r="O41" s="17"/>
-      <c r="P41" s="17"/>
-      <c r="Q41" s="17"/>
-    </row>
-    <row r="42" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
-      <c r="M42" s="17"/>
-      <c r="N42" s="17"/>
-      <c r="O42" s="17"/>
-      <c r="P42" s="17"/>
-      <c r="Q42" s="17"/>
-    </row>
-    <row r="43" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
-      <c r="M43" s="17"/>
-      <c r="N43" s="17"/>
-      <c r="O43" s="17"/>
-      <c r="P43" s="17"/>
-      <c r="Q43" s="17"/>
-      <c r="R43" s="20"/>
-    </row>
-    <row r="44" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-      <c r="N44" s="17"/>
-      <c r="O44" s="17"/>
-      <c r="P44" s="17"/>
-      <c r="Q44" s="17"/>
-    </row>
-    <row r="45" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17"/>
-      <c r="O45" s="17"/>
-      <c r="P45" s="17"/>
-      <c r="Q45" s="17"/>
-      <c r="R45" s="20"/>
-    </row>
-    <row r="46" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="17"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="18"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="17"/>
-      <c r="M46" s="17"/>
-      <c r="N46" s="17"/>
-      <c r="O46" s="17"/>
-      <c r="P46" s="17"/>
-      <c r="Q46" s="17"/>
-      <c r="R46" s="20"/>
-    </row>
-    <row r="47" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="17"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="18"/>
-      <c r="I47" s="18"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
-      <c r="L47" s="17"/>
-      <c r="M47" s="17"/>
-      <c r="N47" s="17"/>
-      <c r="O47" s="17"/>
-      <c r="P47" s="17"/>
-      <c r="Q47" s="17"/>
-    </row>
-    <row r="48" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="17"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="18"/>
-      <c r="I48" s="18"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="17"/>
-      <c r="M48" s="17"/>
-      <c r="N48" s="17"/>
-      <c r="O48" s="17"/>
-      <c r="P48" s="17"/>
-      <c r="Q48" s="17"/>
-    </row>
-    <row r="49" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="17"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="18"/>
-      <c r="I49" s="18"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
-      <c r="N49" s="17"/>
-      <c r="O49" s="17"/>
-      <c r="P49" s="17"/>
-      <c r="Q49" s="17"/>
-      <c r="R49" s="20"/>
-    </row>
-    <row r="50" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="17"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
-      <c r="H50" s="18"/>
-      <c r="I50" s="18"/>
-      <c r="J50" s="17"/>
-      <c r="K50" s="17"/>
-      <c r="L50" s="17"/>
-      <c r="M50" s="17"/>
-      <c r="N50" s="17"/>
-      <c r="O50" s="17"/>
-      <c r="P50" s="17"/>
-      <c r="Q50" s="17"/>
-    </row>
-    <row r="51" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="17"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="18"/>
-      <c r="I51" s="18"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="17"/>
-      <c r="M51" s="17"/>
-      <c r="N51" s="17"/>
-      <c r="O51" s="17"/>
-      <c r="P51" s="17"/>
-      <c r="Q51" s="17"/>
-    </row>
-    <row r="52" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="17"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="18"/>
-      <c r="H52" s="18"/>
-      <c r="I52" s="18"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
-      <c r="M52" s="17"/>
-      <c r="N52" s="17"/>
-      <c r="O52" s="17"/>
-      <c r="P52" s="17"/>
-      <c r="Q52" s="17"/>
-      <c r="R52" s="20"/>
-    </row>
-    <row r="53" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="17"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="18"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
-      <c r="M53" s="17"/>
-      <c r="N53" s="17"/>
-      <c r="O53" s="17"/>
-      <c r="P53" s="17"/>
-      <c r="Q53" s="17"/>
-    </row>
-    <row r="54" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="17"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
-      <c r="H54" s="18"/>
-      <c r="I54" s="18"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="17"/>
-      <c r="O54" s="17"/>
-      <c r="P54" s="17"/>
-      <c r="Q54" s="17"/>
-    </row>
-    <row r="55" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="17"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-      <c r="H55" s="18"/>
-      <c r="I55" s="18"/>
-      <c r="J55" s="17"/>
-      <c r="K55" s="17"/>
-      <c r="L55" s="17"/>
-      <c r="M55" s="17"/>
-      <c r="N55" s="17"/>
-      <c r="O55" s="17"/>
-      <c r="P55" s="17"/>
-      <c r="Q55" s="17"/>
-    </row>
-    <row r="56" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="17"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="18"/>
-      <c r="I56" s="18"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="17"/>
-      <c r="O56" s="17"/>
-      <c r="P56" s="17"/>
-      <c r="Q56" s="17"/>
-      <c r="R56" s="20"/>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="G58" s="1">
-        <f t="shared" ref="G58:R58" si="0">SUBTOTAL(9,G3:G57)</f>
-        <v>0</v>
-      </c>
-      <c r="H58" s="1">
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>722</v>
+      </c>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22" t="s">
+        <v>723</v>
+      </c>
+      <c r="F3" s="23">
+        <v>8</v>
+      </c>
+      <c r="G3" s="23">
+        <v>30</v>
+      </c>
+      <c r="H3" s="23">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I33" si="0">G3-H3</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>724</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>323</v>
+      </c>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22" t="s">
+        <v>629</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="23">
+        <v>35</v>
+      </c>
+      <c r="H4" s="23">
+        <v>35</v>
+      </c>
+      <c r="I4" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I58" s="1">
+      <c r="J4" s="22" t="s">
+        <v>724</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>726</v>
+      </c>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22" t="s">
+        <v>727</v>
+      </c>
+      <c r="F5" s="23">
+        <v>12</v>
+      </c>
+      <c r="G5" s="23">
+        <v>35</v>
+      </c>
+      <c r="H5" s="23">
+        <v>35</v>
+      </c>
+      <c r="I5" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J58" s="1">
+      <c r="J5" s="22" t="s">
+        <v>724</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>728</v>
+      </c>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22" t="s">
+        <v>729</v>
+      </c>
+      <c r="F6" s="23">
+        <v>6</v>
+      </c>
+      <c r="G6" s="23">
+        <v>650</v>
+      </c>
+      <c r="H6" s="23">
+        <v>30</v>
+      </c>
+      <c r="I6" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K58" s="1">
+        <v>620</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>724</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>730</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>731</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>732</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="23">
+        <v>0</v>
+      </c>
+      <c r="H7" s="23">
+        <v>25</v>
+      </c>
+      <c r="I7" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L58" s="1">
+        <v>-25</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>724</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+      <c r="R7" s="24">
+        <f>H7</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>733</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>562</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="G8" s="26">
+        <v>35</v>
+      </c>
+      <c r="H8" s="26">
+        <v>35</v>
+      </c>
+      <c r="I8" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M58" s="1">
+      <c r="J8" s="25" t="s">
+        <v>724</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="25" t="s">
+        <v>725</v>
+      </c>
+      <c r="M8" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>734</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>735</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>736</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0</v>
+      </c>
+      <c r="H9" s="23">
+        <v>30</v>
+      </c>
+      <c r="I9" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N58" s="1">
+        <v>-30</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>724</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+      <c r="R9" s="24">
+        <f>H9</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>737</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>738</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>739</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="23">
+        <v>400</v>
+      </c>
+      <c r="H10" s="23">
+        <v>30</v>
+      </c>
+      <c r="I10" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O58" s="1">
+        <v>370</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>724</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>740</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>741</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>742</v>
+      </c>
+      <c r="F11" s="23">
+        <v>11</v>
+      </c>
+      <c r="G11" s="23">
+        <v>665</v>
+      </c>
+      <c r="H11" s="23">
+        <v>25</v>
+      </c>
+      <c r="I11" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P58" s="1">
+        <v>640</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>724</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>743</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>744</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>745</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="23">
+        <v>820</v>
+      </c>
+      <c r="H12" s="23">
+        <v>30</v>
+      </c>
+      <c r="I12" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q58" s="1">
+        <v>790</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>724</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>746</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>747</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>748</v>
+      </c>
+      <c r="F13" s="23">
+        <v>6</v>
+      </c>
+      <c r="G13" s="23">
+        <v>0</v>
+      </c>
+      <c r="H13" s="23">
+        <v>25</v>
+      </c>
+      <c r="I13" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R58" s="1">
+        <v>-25</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>724</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+      <c r="R13" s="24">
+        <f>H13</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>749</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>750</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>751</v>
+      </c>
+      <c r="F14" s="23">
+        <v>7</v>
+      </c>
+      <c r="G14" s="23">
+        <v>770</v>
+      </c>
+      <c r="H14" s="23">
+        <v>30</v>
+      </c>
+      <c r="I14" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H62" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>724</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>752</v>
+      </c>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22" t="s">
+        <v>753</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="23">
+        <v>0</v>
+      </c>
+      <c r="H15" s="23">
+        <v>30</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22">
+        <v>1</v>
+      </c>
+      <c r="R15" s="24">
+        <f>H15</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>754</v>
+      </c>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22" t="s">
+        <v>755</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="23">
+        <v>12110</v>
+      </c>
+      <c r="H16" s="23">
+        <v>60</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>12050</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>756</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>757</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>758</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G17" s="23">
+        <v>795</v>
+      </c>
+      <c r="H17" s="23">
+        <v>25</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>759</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>760</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>761</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="23">
+        <v>1145</v>
+      </c>
+      <c r="H18" s="23">
+        <v>25</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>762</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>763</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>764</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="23">
+        <v>3640</v>
+      </c>
+      <c r="H19" s="23">
+        <v>30</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>3610</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M19" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+      <c r="R19" s="24">
+        <f>H19</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>765</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>766</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>767</v>
+      </c>
+      <c r="F20" s="23">
+        <v>2</v>
+      </c>
+      <c r="G20" s="23">
+        <v>690</v>
+      </c>
+      <c r="H20" s="23">
+        <v>30</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>768</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>769</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>770</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G21" s="23">
+        <v>2310</v>
+      </c>
+      <c r="H21" s="23">
+        <v>30</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>2280</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M21" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+      <c r="R21" s="24">
+        <f>H21</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>771</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>772</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" s="23">
+        <v>395</v>
+      </c>
+      <c r="H22" s="23">
+        <v>25</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="0"/>
+        <v>370</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25"/>
+      <c r="B23" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>685</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>773</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>687</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="G23" s="26">
+        <v>200</v>
+      </c>
+      <c r="H23" s="26">
+        <v>20</v>
+      </c>
+      <c r="I23" s="26">
+        <f t="shared" si="0"/>
+        <v>180</v>
+      </c>
+      <c r="J23" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="25" t="s">
+        <v>725</v>
+      </c>
+      <c r="M23" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25"/>
+      <c r="B24" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>774</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="F24" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="26">
+        <v>25</v>
+      </c>
+      <c r="H24" s="26">
+        <v>25</v>
+      </c>
+      <c r="I24" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="25" t="s">
+        <v>725</v>
+      </c>
+      <c r="M24" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N24" s="25"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>775</v>
+      </c>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22" t="s">
+        <v>776</v>
+      </c>
+      <c r="F25" s="23">
+        <v>3</v>
+      </c>
+      <c r="G25" s="23">
+        <v>2070</v>
+      </c>
+      <c r="H25" s="23">
+        <v>30</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="0"/>
+        <v>2040</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>777</v>
+      </c>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22" t="s">
+        <v>778</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G26" s="23">
+        <v>0</v>
+      </c>
+      <c r="H26" s="23">
+        <v>30</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+      <c r="R26" s="24">
+        <f>H26</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>779</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>780</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>781</v>
+      </c>
+      <c r="F27" s="23">
+        <v>1</v>
+      </c>
+      <c r="G27" s="23">
+        <v>0</v>
+      </c>
+      <c r="H27" s="23">
+        <v>25</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M27" s="28" t="s">
+        <v>782</v>
+      </c>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>783</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>784</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>785</v>
+      </c>
+      <c r="F28" s="23">
+        <v>1</v>
+      </c>
+      <c r="G28" s="23">
+        <v>0</v>
+      </c>
+      <c r="H28" s="23">
+        <v>25</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22">
+        <v>1</v>
+      </c>
+      <c r="R28" s="24">
+        <f>H28</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="25"/>
+      <c r="B29" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>702</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>786</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>787</v>
+      </c>
+      <c r="F29" s="26">
+        <v>10</v>
+      </c>
+      <c r="G29" s="26">
+        <v>25</v>
+      </c>
+      <c r="H29" s="26">
+        <v>25</v>
+      </c>
+      <c r="I29" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="K29" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="25" t="s">
+        <v>725</v>
+      </c>
+      <c r="M29" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N29" s="25"/>
+      <c r="O29" s="25"/>
+      <c r="P29" s="25"/>
+      <c r="Q29" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>788</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>789</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>790</v>
+      </c>
+      <c r="F30" s="23">
+        <v>1</v>
+      </c>
+      <c r="G30" s="23">
+        <v>0</v>
+      </c>
+      <c r="H30" s="23">
+        <v>25</v>
+      </c>
+      <c r="I30" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22">
+        <v>1</v>
+      </c>
+      <c r="R30" s="24">
+        <f>H30</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>791</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>792</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>793</v>
+      </c>
+      <c r="F31" s="23">
+        <v>10</v>
+      </c>
+      <c r="G31" s="23">
+        <v>815</v>
+      </c>
+      <c r="H31" s="23">
+        <v>25</v>
+      </c>
+      <c r="I31" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J31" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K31" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>794</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>795</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>796</v>
+      </c>
+      <c r="F32" s="23">
+        <v>5</v>
+      </c>
+      <c r="G32" s="23">
+        <v>775</v>
+      </c>
+      <c r="H32" s="23">
+        <v>25</v>
+      </c>
+      <c r="I32" s="23">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J32" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K32" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L32" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>797</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>798</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>799</v>
+      </c>
+      <c r="F33" s="23">
+        <v>1</v>
+      </c>
+      <c r="G33" s="23">
+        <v>0</v>
+      </c>
+      <c r="H33" s="23">
+        <v>25</v>
+      </c>
+      <c r="I33" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J33" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K33" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="M33" s="22"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22">
+        <v>1</v>
+      </c>
+      <c r="R33" s="24">
+        <f>H33</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G35" s="1">
+        <f t="shared" ref="G35:R35" si="1">SUBTOTAL(9,G3:G34)</f>
+        <v>28435</v>
+      </c>
+      <c r="H35" s="1">
+        <f t="shared" si="1"/>
+        <v>895</v>
+      </c>
+      <c r="I35" s="1">
+        <f t="shared" si="1"/>
+        <v>27540</v>
+      </c>
+      <c r="J35" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M35" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N35" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O35" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P35" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="1">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="R35" s="1">
+        <f t="shared" si="1"/>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H39" s="4" t="s">
         <v>719</v>
       </c>
-      <c r="I62" s="5" t="s">
+      <c r="I39" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J62" s="6" t="s">
+      <c r="J39" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H63" s="7" t="s">
+    <row r="40" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H40" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I63" s="8">
-        <f>SUM(I57:I61)</f>
-        <v>0</v>
-      </c>
-      <c r="J63" s="8">
-        <f>Q58</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="H64" s="9" t="s">
+      <c r="I40" s="8">
+        <f>SUM(I34:I38)</f>
+        <v>27540</v>
+      </c>
+      <c r="J40" s="8">
+        <f>Q35</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H41" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I64" s="10">
-        <f>R58</f>
-        <v>0</v>
-      </c>
-      <c r="J64" s="11"/>
-    </row>
-    <row r="65" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H65" s="9" t="s">
+      <c r="I41" s="10">
+        <f>R35</f>
+        <v>275</v>
+      </c>
+      <c r="J41" s="11"/>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H42" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I65" s="10">
-        <f>S57</f>
-        <v>0</v>
-      </c>
-      <c r="J65" s="11"/>
-    </row>
-    <row r="66" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H66" s="9" t="s">
+      <c r="I42" s="10">
+        <f>S34</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="11"/>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H43" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I66" s="10">
-        <f>T57</f>
-        <v>0</v>
-      </c>
-      <c r="J66" s="11"/>
-    </row>
-    <row r="67" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H67" s="9" t="s">
+      <c r="I43" s="10">
+        <f>T34</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="11"/>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H44" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I67" s="10">
-        <f>U57</f>
-        <v>0</v>
-      </c>
-      <c r="J67" s="11"/>
-    </row>
-    <row r="68" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H68" s="12" t="s">
+      <c r="I44" s="10">
+        <f>U34</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="11"/>
+    </row>
+    <row r="45" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H45" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
-    </row>
-    <row r="69" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H69" s="14" t="s">
+      <c r="I45" s="13"/>
+      <c r="J45" s="13"/>
+    </row>
+    <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H46" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13"/>
-    </row>
-    <row r="70" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="H70" s="15" t="s">
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
+    </row>
+    <row r="47" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H47" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I70" s="16">
-        <f>SUM(I63:I69)</f>
-        <v>0</v>
-      </c>
-      <c r="J70" s="16">
-        <f>SUM(J63:J67)</f>
-        <v>0</v>
+      <c r="I47" s="16">
+        <f>SUM(I40:I46)</f>
+        <v>27815</v>
+      </c>
+      <c r="J47" s="16">
+        <f>SUM(J40:J44)</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B50" s="36" t="s">
+        <v>779</v>
+      </c>
+      <c r="C50" s="36" t="s">
+        <v>780</v>
+      </c>
+      <c r="D50" s="36" t="s">
+        <v>781</v>
+      </c>
+      <c r="E50" s="37">
+        <v>1</v>
+      </c>
+      <c r="F50" s="37">
+        <v>975</v>
+      </c>
+      <c r="G50" s="37">
+        <v>0</v>
+      </c>
+      <c r="H50" s="37">
+        <f t="shared" ref="H50" si="2">F50-G50</f>
+        <v>975</v>
+      </c>
+      <c r="I50" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="J50" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="K50" s="36" t="s">
+        <v>725</v>
+      </c>
+      <c r="L50" s="28" t="s">
+        <v>782</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P56" xr:uid="{00000000-0009-0000-0000-000006000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P56">
-      <sortCondition ref="J2:J56"/>
+  <autoFilter ref="A2:P33" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P33">
+      <sortCondition ref="J2:J33"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17204,4 +17864,1278 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F101346F-FE09-4B80-8463-3C38A222BEE2}">
+  <dimension ref="A1:R70"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+    </row>
+    <row r="4" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+    </row>
+    <row r="5" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="20"/>
+    </row>
+    <row r="6" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+    </row>
+    <row r="7" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="20"/>
+    </row>
+    <row r="8" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+    </row>
+    <row r="9" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+    </row>
+    <row r="10" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="20"/>
+    </row>
+    <row r="11" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="20"/>
+    </row>
+    <row r="12" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+    </row>
+    <row r="13" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+    </row>
+    <row r="14" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+    </row>
+    <row r="15" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="20"/>
+    </row>
+    <row r="16" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="20"/>
+    </row>
+    <row r="17" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="20"/>
+    </row>
+    <row r="18" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+    </row>
+    <row r="19" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="20"/>
+    </row>
+    <row r="20" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+    </row>
+    <row r="21" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+    </row>
+    <row r="22" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+    </row>
+    <row r="23" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="20"/>
+    </row>
+    <row r="24" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+    </row>
+    <row r="25" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="20"/>
+    </row>
+    <row r="26" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+    </row>
+    <row r="27" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+    </row>
+    <row r="28" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="20"/>
+    </row>
+    <row r="29" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="20"/>
+    </row>
+    <row r="30" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+    </row>
+    <row r="31" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17"/>
+    </row>
+    <row r="32" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+    </row>
+    <row r="33" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="20"/>
+    </row>
+    <row r="34" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+    </row>
+    <row r="35" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+    </row>
+    <row r="36" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="20"/>
+    </row>
+    <row r="37" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+    </row>
+    <row r="38" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+    </row>
+    <row r="39" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="17"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="20"/>
+    </row>
+    <row r="40" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+    </row>
+    <row r="41" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+    </row>
+    <row r="42" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="17"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+    </row>
+    <row r="43" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17"/>
+      <c r="P43" s="17"/>
+      <c r="Q43" s="17"/>
+      <c r="R43" s="20"/>
+    </row>
+    <row r="44" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="17"/>
+    </row>
+    <row r="45" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="20"/>
+    </row>
+    <row r="46" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="17"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17"/>
+      <c r="P46" s="17"/>
+      <c r="Q46" s="17"/>
+      <c r="R46" s="20"/>
+    </row>
+    <row r="47" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="17"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="17"/>
+      <c r="M47" s="17"/>
+      <c r="N47" s="17"/>
+      <c r="O47" s="17"/>
+      <c r="P47" s="17"/>
+      <c r="Q47" s="17"/>
+    </row>
+    <row r="48" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="17"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
+      <c r="Q48" s="17"/>
+    </row>
+    <row r="49" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="17"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
+      <c r="L49" s="17"/>
+      <c r="M49" s="17"/>
+      <c r="N49" s="17"/>
+      <c r="O49" s="17"/>
+      <c r="P49" s="17"/>
+      <c r="Q49" s="17"/>
+      <c r="R49" s="20"/>
+    </row>
+    <row r="50" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="17"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="17"/>
+      <c r="M50" s="17"/>
+      <c r="N50" s="17"/>
+      <c r="O50" s="17"/>
+      <c r="P50" s="17"/>
+      <c r="Q50" s="17"/>
+    </row>
+    <row r="51" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="17"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="18"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="17"/>
+      <c r="M51" s="17"/>
+      <c r="N51" s="17"/>
+      <c r="O51" s="17"/>
+      <c r="P51" s="17"/>
+      <c r="Q51" s="17"/>
+    </row>
+    <row r="52" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="17"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
+      <c r="N52" s="17"/>
+      <c r="O52" s="17"/>
+      <c r="P52" s="17"/>
+      <c r="Q52" s="17"/>
+      <c r="R52" s="20"/>
+    </row>
+    <row r="53" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="17"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="17"/>
+      <c r="L53" s="17"/>
+      <c r="M53" s="17"/>
+      <c r="N53" s="17"/>
+      <c r="O53" s="17"/>
+      <c r="P53" s="17"/>
+      <c r="Q53" s="17"/>
+    </row>
+    <row r="54" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="17"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
+      <c r="O54" s="17"/>
+      <c r="P54" s="17"/>
+      <c r="Q54" s="17"/>
+    </row>
+    <row r="55" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="17"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="17"/>
+      <c r="K55" s="17"/>
+      <c r="L55" s="17"/>
+      <c r="M55" s="17"/>
+      <c r="N55" s="17"/>
+      <c r="O55" s="17"/>
+      <c r="P55" s="17"/>
+      <c r="Q55" s="17"/>
+    </row>
+    <row r="56" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="17"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="17"/>
+      <c r="M56" s="17"/>
+      <c r="N56" s="17"/>
+      <c r="O56" s="17"/>
+      <c r="P56" s="17"/>
+      <c r="Q56" s="17"/>
+      <c r="R56" s="20"/>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G58" s="1">
+        <f t="shared" ref="G58:R58" si="0">SUBTOTAL(9,G3:G57)</f>
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H62" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I63" s="8">
+        <f>SUM(I57:I61)</f>
+        <v>0</v>
+      </c>
+      <c r="J63" s="8">
+        <f>Q58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H64" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I64" s="10">
+        <f>R58</f>
+        <v>0</v>
+      </c>
+      <c r="J64" s="11"/>
+    </row>
+    <row r="65" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H65" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I65" s="10">
+        <f>S57</f>
+        <v>0</v>
+      </c>
+      <c r="J65" s="11"/>
+    </row>
+    <row r="66" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H66" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" s="10">
+        <f>T57</f>
+        <v>0</v>
+      </c>
+      <c r="J66" s="11"/>
+    </row>
+    <row r="67" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H67" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I67" s="10">
+        <f>U57</f>
+        <v>0</v>
+      </c>
+      <c r="J67" s="11"/>
+    </row>
+    <row r="68" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H68" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+    </row>
+    <row r="69" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H69" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
+    </row>
+    <row r="70" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H70" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I70" s="16">
+        <f>SUM(I63:I69)</f>
+        <v>0</v>
+      </c>
+      <c r="J70" s="16">
+        <f>SUM(J63:J67)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P56" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P56">
+      <sortCondition ref="J2:J56"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C41E2E2-63DA-484F-9441-1533B6076FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD43E377-304A-4721-8533-95445C7C5ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-5" sheetId="3" r:id="rId1"/>
@@ -22,10 +22,12 @@
     <sheet name="9-5" sheetId="9" r:id="rId7"/>
     <sheet name="11-5" sheetId="10" r:id="rId8"/>
     <sheet name="12-5" sheetId="11" r:id="rId9"/>
+    <sheet name="13-5" sheetId="12" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'11-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'11-5'!$A$2:$P$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'12-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'13-5'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-5'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'4-5'!$A$2:$P$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'5-5'!$A$2:$P$55</definedName>
@@ -55,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2235" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2686" uniqueCount="962">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -2464,6 +2466,483 @@
   </si>
   <si>
     <t>T3.12.5.2026</t>
+  </si>
+  <si>
+    <t>Minh Nguyệt + Lin Xiao + Hàng Air</t>
+  </si>
+  <si>
+    <t>HD019693</t>
+  </si>
+  <si>
+    <t>C16-17 lô C1, đường DD5, phường Đông Hưng Thuận (ghi chú: sau lưng chợ An Sương)</t>
+  </si>
+  <si>
+    <t>AT 11-05</t>
+  </si>
+  <si>
+    <t>11-05-2026</t>
+  </si>
+  <si>
+    <t>Thúy Kiều</t>
+  </si>
+  <si>
+    <t>HD019818</t>
+  </si>
+  <si>
+    <t>Số 6 mai văn vĩnh tân quy</t>
+  </si>
+  <si>
+    <t>HD019881</t>
+  </si>
+  <si>
+    <t>100.đinh văn ước ấp5 xã hưng long</t>
+  </si>
+  <si>
+    <t>Ruby Cẩm Tú</t>
+  </si>
+  <si>
+    <t>HD019626</t>
+  </si>
+  <si>
+    <t>61 bui diên p4</t>
+  </si>
+  <si>
+    <t>Phương Bình</t>
+  </si>
+  <si>
+    <t>HD019877</t>
+  </si>
+  <si>
+    <t>CC Ehome3, Hồ Học Lãm, An Lạc</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Ngọc Ngà</t>
+  </si>
+  <si>
+    <t>HD019744</t>
+  </si>
+  <si>
+    <t>38b đường số 12 tân quy</t>
+  </si>
+  <si>
+    <t>Minh Hải ( Ruby Eyelash - Nail )</t>
+  </si>
+  <si>
+    <t>HD019891</t>
+  </si>
+  <si>
+    <t>17 Đường Số 13 Phường Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Đỗ Đông Mi</t>
+  </si>
+  <si>
+    <t>HD019570</t>
+  </si>
+  <si>
+    <t>115 phan huy thuc ptan kieng</t>
+  </si>
+  <si>
+    <t>Nguyễn Cao Kim Anh</t>
+  </si>
+  <si>
+    <t>HD019644</t>
+  </si>
+  <si>
+    <t>264 lê văn lương phước kiểng</t>
+  </si>
+  <si>
+    <t>Trúc Uyên</t>
+  </si>
+  <si>
+    <t>HD019781</t>
+  </si>
+  <si>
+    <t>Trường Ruby Hồng Ngọc, số 4 Lê Quát, Phường Tân Thới Hoà cũ</t>
+  </si>
+  <si>
+    <t>Kaity Hg</t>
+  </si>
+  <si>
+    <t>HD019671</t>
+  </si>
+  <si>
+    <t>6B8/23/1c hương lộ 2, p bình trị đông A</t>
+  </si>
+  <si>
+    <t>Trang Cherry</t>
+  </si>
+  <si>
+    <t>HD019937</t>
+  </si>
+  <si>
+    <t>Chung cư an gia thị trấn Tân túc</t>
+  </si>
+  <si>
+    <t>Thuỳ</t>
+  </si>
+  <si>
+    <t>HD019994</t>
+  </si>
+  <si>
+    <t>24b tân sơn nhì</t>
+  </si>
+  <si>
+    <t>W24130 miki</t>
+  </si>
+  <si>
+    <t>624 Lê Thị Riêng, Thới An</t>
+  </si>
+  <si>
+    <t>Myle Pham</t>
+  </si>
+  <si>
+    <t>HD019988</t>
+  </si>
+  <si>
+    <t>88/29 đường 17, phường Tân thuận Tây</t>
+  </si>
+  <si>
+    <t>Yến Phương</t>
+  </si>
+  <si>
+    <t>HD020005</t>
+  </si>
+  <si>
+    <t>Toà nhà Namn 10 đường số 67 phường tân quy</t>
+  </si>
+  <si>
+    <t>Lê Hữu Nhân</t>
+  </si>
+  <si>
+    <t>HD019980</t>
+  </si>
+  <si>
+    <t>53/3B Mai Hắc Đế, phường Phú Định</t>
+  </si>
+  <si>
+    <t>Anh Thu</t>
+  </si>
+  <si>
+    <t>HD019992</t>
+  </si>
+  <si>
+    <t>157/59/11 Dương Bá Trạc Phường 1</t>
+  </si>
+  <si>
+    <t>Võ Trần Như Bích</t>
+  </si>
+  <si>
+    <t>HD019760</t>
+  </si>
+  <si>
+    <t>Chung cư Richstar 1, sảnh RS1 - 278A Hoà Bình, P. Hiệp Tân</t>
+  </si>
+  <si>
+    <t>Nguyễn Kim Ngân</t>
+  </si>
+  <si>
+    <t>HD019934</t>
+  </si>
+  <si>
+    <t>Lavida Plus, Nguyễn Văn Linh, Tân Phong</t>
+  </si>
+  <si>
+    <t>135 hải thượng lãn Ông P10</t>
+  </si>
+  <si>
+    <t>MIE</t>
+  </si>
+  <si>
+    <t>Phan Nhi</t>
+  </si>
+  <si>
+    <t>HD019796</t>
+  </si>
+  <si>
+    <t>107/189 quang trung, f.10</t>
+  </si>
+  <si>
+    <t>Kiên Thị Thanh Hiền</t>
+  </si>
+  <si>
+    <t>HD019616</t>
+  </si>
+  <si>
+    <t>31 đường số 30 phường cát lái</t>
+  </si>
+  <si>
+    <t>Cẩm Tú</t>
+  </si>
+  <si>
+    <t>HD019735</t>
+  </si>
+  <si>
+    <t>chung cư terrace 21 võ trường toản</t>
+  </si>
+  <si>
+    <t>HD019469</t>
+  </si>
+  <si>
+    <t>Diệu Linh</t>
+  </si>
+  <si>
+    <t>HD019905</t>
+  </si>
+  <si>
+    <t>Vinhomes central park( park 2 -P2) 720a Điện Biên Phủ, Phường 22</t>
+  </si>
+  <si>
+    <t>Mary Tran</t>
+  </si>
+  <si>
+    <t>HD019738</t>
+  </si>
+  <si>
+    <t>9/5 đường số 66 Phường thảo điền</t>
+  </si>
+  <si>
+    <t>Trang Nhung Bui</t>
+  </si>
+  <si>
+    <t>HD019787</t>
+  </si>
+  <si>
+    <t>Toà Golden House - Sunwah Pearl 90 Nguyễn Hữu Cảnh - phường 22</t>
+  </si>
+  <si>
+    <t>chi hương fb Kim Tien Pham</t>
+  </si>
+  <si>
+    <t>HD19599</t>
+  </si>
+  <si>
+    <t>Đỗ Thị Kiều Chinh</t>
+  </si>
+  <si>
+    <t>HD019899</t>
+  </si>
+  <si>
+    <t>42, đường 21,Khu dân cư bình chiểu, P tam binh (chợ đầu mối nông sản thủ đức)</t>
+  </si>
+  <si>
+    <t>Dung Nguyen</t>
+  </si>
+  <si>
+    <t>HD019705</t>
+  </si>
+  <si>
+    <t>15/32/2 võ duy ninh f22</t>
+  </si>
+  <si>
+    <t>Vân Ốc</t>
+  </si>
+  <si>
+    <t>HD019745</t>
+  </si>
+  <si>
+    <t>16 đường 6, p linh chiểu</t>
+  </si>
+  <si>
+    <t>HD019779</t>
+  </si>
+  <si>
+    <t>Gate 4 - Feliz en vista, 1 trương văn bang, thạnh mỹ lợi Toà cruz - C810</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thuỳ Trang</t>
+  </si>
+  <si>
+    <t>HD020003</t>
+  </si>
+  <si>
+    <t>41A huỳnh tịnh của p19</t>
+  </si>
+  <si>
+    <t>Hồ Ly</t>
+  </si>
+  <si>
+    <t>HD019939</t>
+  </si>
+  <si>
+    <t>cổng B Cát Lái đường Lê Phụng Hiểu, Cát Lái</t>
+  </si>
+  <si>
+    <t>HƯƠNG TRẦN</t>
+  </si>
+  <si>
+    <t>261/26c chu văn an p12</t>
+  </si>
+  <si>
+    <t>UYÊN MI</t>
+  </si>
+  <si>
+    <t>78 Trần Não, P. An Khánh</t>
+  </si>
+  <si>
+    <t>quyên quyên</t>
+  </si>
+  <si>
+    <t>HD019808</t>
+  </si>
+  <si>
+    <t>89 thành thái diên hồng</t>
+  </si>
+  <si>
+    <t>Na Na</t>
+  </si>
+  <si>
+    <t>HD019683</t>
+  </si>
+  <si>
+    <t>145/11 Nguyễn Văn trỗi</t>
+  </si>
+  <si>
+    <t>Ngô Thị Bích Loan</t>
+  </si>
+  <si>
+    <t>HD019556</t>
+  </si>
+  <si>
+    <t>167 đặng văn ngữ</t>
+  </si>
+  <si>
+    <t>Trần Chi / Yaya Tran</t>
+  </si>
+  <si>
+    <t>HD019782</t>
+  </si>
+  <si>
+    <t>36 sư vạn hạnh p9</t>
+  </si>
+  <si>
+    <t>Nhy Lê</t>
+  </si>
+  <si>
+    <t>HD019780</t>
+  </si>
+  <si>
+    <t>42 nguyễn sơn hà f5</t>
+  </si>
+  <si>
+    <t>Nguyet</t>
+  </si>
+  <si>
+    <t>HD019907</t>
+  </si>
+  <si>
+    <t>Toà nhà lux 6...Vinhomes Golden River (Bason), 2 Nguyễn Hữu Cảnh, P. Bến Nghé</t>
+  </si>
+  <si>
+    <t>Phi Phụng</t>
+  </si>
+  <si>
+    <t>HD019753</t>
+  </si>
+  <si>
+    <t>85 hồ tùng mậu bến nghé</t>
+  </si>
+  <si>
+    <t>Vi Chanel</t>
+  </si>
+  <si>
+    <t>HD019639</t>
+  </si>
+  <si>
+    <t>132 Bến Vân Đồn Chung cư Millennium toà A 22.07</t>
+  </si>
+  <si>
+    <t>Huỳnh Kim</t>
+  </si>
+  <si>
+    <t>HD019764</t>
+  </si>
+  <si>
+    <t>109 bến vân đồn, phường 9</t>
+  </si>
+  <si>
+    <t>Huynh Anh</t>
+  </si>
+  <si>
+    <t>HD019576</t>
+  </si>
+  <si>
+    <t>284 nguyễn thiện thuật</t>
+  </si>
+  <si>
+    <t>Tuyet Nhung Nguyen</t>
+  </si>
+  <si>
+    <t>HD019767</t>
+  </si>
+  <si>
+    <t>36 Lê lai phường Bảy Hiền</t>
+  </si>
+  <si>
+    <t>Chị Dương - fb Lien Phuong Bui</t>
+  </si>
+  <si>
+    <t>HD019733</t>
+  </si>
+  <si>
+    <t>14 Bạch Mã, p15 cư xá bắc hải</t>
+  </si>
+  <si>
+    <t>HD019969</t>
+  </si>
+  <si>
+    <t>Yến Nhi - fb Thanh Thanh</t>
+  </si>
+  <si>
+    <t>HD020012</t>
+  </si>
+  <si>
+    <t>38 Nguyễn Bá Tuyển, P12</t>
+  </si>
+  <si>
+    <t>Ama Bella - zalo</t>
+  </si>
+  <si>
+    <t>HD020009</t>
+  </si>
+  <si>
+    <t>363 Hùng Vương An Đông</t>
+  </si>
+  <si>
+    <t>Titi</t>
+  </si>
+  <si>
+    <t>HD019977</t>
+  </si>
+  <si>
+    <t>196/16 Đề Thám, P. Cầu Ông Lãnh</t>
+  </si>
+  <si>
+    <t>Mỹ Hương</t>
+  </si>
+  <si>
+    <t>HD020008</t>
+  </si>
+  <si>
+    <t>1A Đ. Lý Thường Kiệt, Phường 7</t>
+  </si>
+  <si>
+    <t>Diễm My</t>
+  </si>
+  <si>
+    <t>HD020004</t>
+  </si>
+  <si>
+    <t>174 ton dan p4</t>
+  </si>
+  <si>
+    <t>đơn trả 12.5</t>
+  </si>
+  <si>
+    <t>T4.13.5.2026</t>
+  </si>
+  <si>
+    <t>NGAY 13-5</t>
   </si>
 </sst>
 </file>
@@ -5721,6 +6200,1280 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3899F5A-29E8-4E78-9648-A9394903C07E}">
+  <dimension ref="A1:R70"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+    </row>
+    <row r="4" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+    </row>
+    <row r="5" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="20"/>
+    </row>
+    <row r="6" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+    </row>
+    <row r="7" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="20"/>
+    </row>
+    <row r="8" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+    </row>
+    <row r="9" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+    </row>
+    <row r="10" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="20"/>
+    </row>
+    <row r="11" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="20"/>
+    </row>
+    <row r="12" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+    </row>
+    <row r="13" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+    </row>
+    <row r="14" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+    </row>
+    <row r="15" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="20"/>
+    </row>
+    <row r="16" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="20"/>
+    </row>
+    <row r="17" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="20"/>
+    </row>
+    <row r="18" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+    </row>
+    <row r="19" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="20"/>
+    </row>
+    <row r="20" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+    </row>
+    <row r="21" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+    </row>
+    <row r="22" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+    </row>
+    <row r="23" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="20"/>
+    </row>
+    <row r="24" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+    </row>
+    <row r="25" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="20"/>
+    </row>
+    <row r="26" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+    </row>
+    <row r="27" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+    </row>
+    <row r="28" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="20"/>
+    </row>
+    <row r="29" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="20"/>
+    </row>
+    <row r="30" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+    </row>
+    <row r="31" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17"/>
+    </row>
+    <row r="32" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+    </row>
+    <row r="33" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="20"/>
+    </row>
+    <row r="34" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+    </row>
+    <row r="35" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+    </row>
+    <row r="36" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="20"/>
+    </row>
+    <row r="37" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+    </row>
+    <row r="38" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+    </row>
+    <row r="39" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="17"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="20"/>
+    </row>
+    <row r="40" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+    </row>
+    <row r="41" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+    </row>
+    <row r="42" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="17"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+    </row>
+    <row r="43" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17"/>
+      <c r="P43" s="17"/>
+      <c r="Q43" s="17"/>
+      <c r="R43" s="20"/>
+    </row>
+    <row r="44" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="17"/>
+    </row>
+    <row r="45" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="20"/>
+    </row>
+    <row r="46" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="17"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17"/>
+      <c r="P46" s="17"/>
+      <c r="Q46" s="17"/>
+      <c r="R46" s="20"/>
+    </row>
+    <row r="47" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="17"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="17"/>
+      <c r="M47" s="17"/>
+      <c r="N47" s="17"/>
+      <c r="O47" s="17"/>
+      <c r="P47" s="17"/>
+      <c r="Q47" s="17"/>
+    </row>
+    <row r="48" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="17"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
+      <c r="Q48" s="17"/>
+    </row>
+    <row r="49" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="17"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
+      <c r="L49" s="17"/>
+      <c r="M49" s="17"/>
+      <c r="N49" s="17"/>
+      <c r="O49" s="17"/>
+      <c r="P49" s="17"/>
+      <c r="Q49" s="17"/>
+      <c r="R49" s="20"/>
+    </row>
+    <row r="50" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="17"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="17"/>
+      <c r="M50" s="17"/>
+      <c r="N50" s="17"/>
+      <c r="O50" s="17"/>
+      <c r="P50" s="17"/>
+      <c r="Q50" s="17"/>
+    </row>
+    <row r="51" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="17"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="18"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="17"/>
+      <c r="M51" s="17"/>
+      <c r="N51" s="17"/>
+      <c r="O51" s="17"/>
+      <c r="P51" s="17"/>
+      <c r="Q51" s="17"/>
+    </row>
+    <row r="52" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="17"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
+      <c r="N52" s="17"/>
+      <c r="O52" s="17"/>
+      <c r="P52" s="17"/>
+      <c r="Q52" s="17"/>
+      <c r="R52" s="20"/>
+    </row>
+    <row r="53" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="17"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="17"/>
+      <c r="L53" s="17"/>
+      <c r="M53" s="17"/>
+      <c r="N53" s="17"/>
+      <c r="O53" s="17"/>
+      <c r="P53" s="17"/>
+      <c r="Q53" s="17"/>
+    </row>
+    <row r="54" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="17"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
+      <c r="O54" s="17"/>
+      <c r="P54" s="17"/>
+      <c r="Q54" s="17"/>
+    </row>
+    <row r="55" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="17"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="17"/>
+      <c r="K55" s="17"/>
+      <c r="L55" s="17"/>
+      <c r="M55" s="17"/>
+      <c r="N55" s="17"/>
+      <c r="O55" s="17"/>
+      <c r="P55" s="17"/>
+      <c r="Q55" s="17"/>
+    </row>
+    <row r="56" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="17"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="17"/>
+      <c r="M56" s="17"/>
+      <c r="N56" s="17"/>
+      <c r="O56" s="17"/>
+      <c r="P56" s="17"/>
+      <c r="Q56" s="17"/>
+      <c r="R56" s="20"/>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G58" s="1">
+        <f t="shared" ref="G58:R58" si="0">SUBTOTAL(9,G3:G57)</f>
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H62" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I63" s="8">
+        <f>SUM(I57:I61)</f>
+        <v>0</v>
+      </c>
+      <c r="J63" s="8">
+        <f>Q58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H64" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I64" s="10">
+        <f>R58</f>
+        <v>0</v>
+      </c>
+      <c r="J64" s="11"/>
+    </row>
+    <row r="65" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H65" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I65" s="10">
+        <f>S57</f>
+        <v>0</v>
+      </c>
+      <c r="J65" s="11"/>
+    </row>
+    <row r="66" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H66" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" s="10">
+        <f>T57</f>
+        <v>0</v>
+      </c>
+      <c r="J66" s="11"/>
+    </row>
+    <row r="67" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H67" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I67" s="10">
+        <f>U57</f>
+        <v>0</v>
+      </c>
+      <c r="J67" s="11"/>
+    </row>
+    <row r="68" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H68" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+    </row>
+    <row r="69" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H69" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
+    </row>
+    <row r="70" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H70" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I70" s="16">
+        <f>SUM(I63:I69)</f>
+        <v>0</v>
+      </c>
+      <c r="J70" s="16">
+        <f>SUM(J63:J67)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P56" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P56">
+      <sortCondition ref="J2:J56"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC23166D-647F-4247-A049-709567A97092}">
   <dimension ref="A1:R36"/>
@@ -16594,7 +18347,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EA17D5-9933-4EE3-ACD1-20C1C25F3DB5}">
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
@@ -16667,1198 +18420,2681 @@
       </c>
       <c r="Q2" s="3"/>
     </row>
-    <row r="3" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-    </row>
-    <row r="4" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-    </row>
-    <row r="5" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="20"/>
-    </row>
-    <row r="6" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-    </row>
-    <row r="7" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="20"/>
-    </row>
-    <row r="8" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-    </row>
-    <row r="9" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-    </row>
-    <row r="10" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="20"/>
-    </row>
-    <row r="11" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="20"/>
-    </row>
-    <row r="12" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-    </row>
-    <row r="13" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-    </row>
-    <row r="14" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-    </row>
-    <row r="15" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="20"/>
-    </row>
-    <row r="16" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="20"/>
-    </row>
-    <row r="17" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="20"/>
-    </row>
-    <row r="18" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-    </row>
-    <row r="19" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="20"/>
-    </row>
-    <row r="20" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
-    </row>
-    <row r="21" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-    </row>
-    <row r="22" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-    </row>
-    <row r="23" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="20"/>
-    </row>
-    <row r="24" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
-    </row>
-    <row r="25" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="20"/>
-    </row>
-    <row r="26" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
-    </row>
-    <row r="27" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
-    </row>
-    <row r="28" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="20"/>
-    </row>
-    <row r="29" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="20"/>
-    </row>
-    <row r="30" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
-      <c r="P30" s="17"/>
-      <c r="Q30" s="17"/>
-    </row>
-    <row r="31" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17"/>
-      <c r="O31" s="17"/>
-      <c r="P31" s="17"/>
-      <c r="Q31" s="17"/>
-    </row>
-    <row r="32" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="17"/>
-      <c r="P32" s="17"/>
-      <c r="Q32" s="17"/>
-    </row>
-    <row r="33" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
-      <c r="P33" s="17"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="20"/>
-    </row>
-    <row r="34" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="17"/>
-    </row>
-    <row r="35" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
-    </row>
-    <row r="36" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="17"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17"/>
-      <c r="P36" s="17"/>
-      <c r="Q36" s="17"/>
-      <c r="R36" s="20"/>
-    </row>
-    <row r="37" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="17"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
-    </row>
-    <row r="38" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="17"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
-      <c r="N38" s="17"/>
-      <c r="O38" s="17"/>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17"/>
-    </row>
-    <row r="39" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="17"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
-      <c r="N39" s="17"/>
-      <c r="O39" s="17"/>
-      <c r="P39" s="17"/>
-      <c r="Q39" s="17"/>
-      <c r="R39" s="20"/>
-    </row>
-    <row r="40" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
-      <c r="N40" s="17"/>
-      <c r="O40" s="17"/>
-      <c r="P40" s="17"/>
-      <c r="Q40" s="17"/>
-    </row>
-    <row r="41" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
-      <c r="N41" s="17"/>
-      <c r="O41" s="17"/>
-      <c r="P41" s="17"/>
-      <c r="Q41" s="17"/>
-    </row>
-    <row r="42" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
-      <c r="M42" s="17"/>
-      <c r="N42" s="17"/>
-      <c r="O42" s="17"/>
-      <c r="P42" s="17"/>
-      <c r="Q42" s="17"/>
-    </row>
-    <row r="43" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
-      <c r="M43" s="17"/>
-      <c r="N43" s="17"/>
-      <c r="O43" s="17"/>
-      <c r="P43" s="17"/>
-      <c r="Q43" s="17"/>
-      <c r="R43" s="20"/>
-    </row>
-    <row r="44" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-      <c r="N44" s="17"/>
-      <c r="O44" s="17"/>
-      <c r="P44" s="17"/>
-      <c r="Q44" s="17"/>
-    </row>
-    <row r="45" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17"/>
-      <c r="O45" s="17"/>
-      <c r="P45" s="17"/>
-      <c r="Q45" s="17"/>
-      <c r="R45" s="20"/>
-    </row>
-    <row r="46" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="17"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="18"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="17"/>
-      <c r="M46" s="17"/>
-      <c r="N46" s="17"/>
-      <c r="O46" s="17"/>
-      <c r="P46" s="17"/>
-      <c r="Q46" s="17"/>
-      <c r="R46" s="20"/>
-    </row>
-    <row r="47" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="17"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="18"/>
-      <c r="I47" s="18"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
-      <c r="L47" s="17"/>
-      <c r="M47" s="17"/>
-      <c r="N47" s="17"/>
-      <c r="O47" s="17"/>
-      <c r="P47" s="17"/>
-      <c r="Q47" s="17"/>
-    </row>
-    <row r="48" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="17"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="18"/>
-      <c r="I48" s="18"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="17"/>
-      <c r="M48" s="17"/>
-      <c r="N48" s="17"/>
-      <c r="O48" s="17"/>
-      <c r="P48" s="17"/>
-      <c r="Q48" s="17"/>
-    </row>
-    <row r="49" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="17"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="18"/>
-      <c r="I49" s="18"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
-      <c r="N49" s="17"/>
-      <c r="O49" s="17"/>
-      <c r="P49" s="17"/>
-      <c r="Q49" s="17"/>
-      <c r="R49" s="20"/>
-    </row>
-    <row r="50" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="17"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
-      <c r="H50" s="18"/>
-      <c r="I50" s="18"/>
-      <c r="J50" s="17"/>
-      <c r="K50" s="17"/>
-      <c r="L50" s="17"/>
-      <c r="M50" s="17"/>
-      <c r="N50" s="17"/>
-      <c r="O50" s="17"/>
-      <c r="P50" s="17"/>
-      <c r="Q50" s="17"/>
-    </row>
-    <row r="51" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="17"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="18"/>
-      <c r="I51" s="18"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="17"/>
-      <c r="M51" s="17"/>
-      <c r="N51" s="17"/>
-      <c r="O51" s="17"/>
-      <c r="P51" s="17"/>
-      <c r="Q51" s="17"/>
-    </row>
-    <row r="52" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="17"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="18"/>
-      <c r="H52" s="18"/>
-      <c r="I52" s="18"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
-      <c r="M52" s="17"/>
-      <c r="N52" s="17"/>
-      <c r="O52" s="17"/>
-      <c r="P52" s="17"/>
-      <c r="Q52" s="17"/>
-      <c r="R52" s="20"/>
-    </row>
-    <row r="53" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="17"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="18"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
-      <c r="M53" s="17"/>
-      <c r="N53" s="17"/>
-      <c r="O53" s="17"/>
-      <c r="P53" s="17"/>
-      <c r="Q53" s="17"/>
-    </row>
-    <row r="54" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="17"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
-      <c r="H54" s="18"/>
-      <c r="I54" s="18"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="17"/>
-      <c r="O54" s="17"/>
-      <c r="P54" s="17"/>
-      <c r="Q54" s="17"/>
-    </row>
-    <row r="55" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="17"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-      <c r="H55" s="18"/>
-      <c r="I55" s="18"/>
-      <c r="J55" s="17"/>
-      <c r="K55" s="17"/>
-      <c r="L55" s="17"/>
-      <c r="M55" s="17"/>
-      <c r="N55" s="17"/>
-      <c r="O55" s="17"/>
-      <c r="P55" s="17"/>
-      <c r="Q55" s="17"/>
-    </row>
-    <row r="56" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="17"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="18"/>
-      <c r="I56" s="18"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="17"/>
-      <c r="O56" s="17"/>
-      <c r="P56" s="17"/>
-      <c r="Q56" s="17"/>
-      <c r="R56" s="20"/>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="G58" s="1">
-        <f t="shared" ref="G58:R58" si="0">SUBTOTAL(9,G3:G57)</f>
-        <v>0</v>
-      </c>
-      <c r="H58" s="1">
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>803</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>804</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>805</v>
+      </c>
+      <c r="F3" s="23">
+        <v>12</v>
+      </c>
+      <c r="G3" s="23">
+        <v>0</v>
+      </c>
+      <c r="H3" s="23">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I58" si="0">G3-H3</f>
+        <v>-30</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+      <c r="R3" s="24">
+        <f>H3</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>808</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>809</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>810</v>
+      </c>
+      <c r="F4" s="23">
+        <v>7</v>
+      </c>
+      <c r="G4" s="23">
+        <v>1800</v>
+      </c>
+      <c r="H4" s="23">
+        <v>30</v>
+      </c>
+      <c r="I4" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I58" s="1">
+        <v>1770</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="25"/>
+      <c r="B5" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>449</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>811</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>812</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="G5" s="26">
+        <v>35</v>
+      </c>
+      <c r="H5" s="26">
+        <v>35</v>
+      </c>
+      <c r="I5" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J58" s="1">
+      <c r="J5" s="25" t="s">
+        <v>806</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="25" t="s">
+        <v>807</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>813</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>814</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>815</v>
+      </c>
+      <c r="F6" s="23">
+        <v>8</v>
+      </c>
+      <c r="G6" s="23">
+        <v>820</v>
+      </c>
+      <c r="H6" s="23">
+        <v>30</v>
+      </c>
+      <c r="I6" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K58" s="1">
+        <v>790</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>816</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>817</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>818</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="23">
+        <v>790</v>
+      </c>
+      <c r="H7" s="23">
+        <v>30</v>
+      </c>
+      <c r="I7" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L58" s="1">
+        <v>760</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>819</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>820</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>821</v>
+      </c>
+      <c r="F8" s="23">
+        <v>7</v>
+      </c>
+      <c r="G8" s="23">
+        <v>780</v>
+      </c>
+      <c r="H8" s="23">
+        <v>30</v>
+      </c>
+      <c r="I8" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M58" s="1">
+        <v>750</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>822</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>823</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>824</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="23">
+        <v>1090</v>
+      </c>
+      <c r="H9" s="23">
+        <v>30</v>
+      </c>
+      <c r="I9" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N58" s="1">
+        <v>1060</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>825</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>826</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>827</v>
+      </c>
+      <c r="F10" s="23">
+        <v>7</v>
+      </c>
+      <c r="G10" s="23">
+        <v>850</v>
+      </c>
+      <c r="H10" s="23">
+        <v>30</v>
+      </c>
+      <c r="I10" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O58" s="1">
+        <v>820</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>828</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>829</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>830</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="G11" s="23">
+        <v>1185</v>
+      </c>
+      <c r="H11" s="23">
+        <v>35</v>
+      </c>
+      <c r="I11" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P58" s="1">
+        <v>1150</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>831</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>832</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>833</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="23">
+        <v>975</v>
+      </c>
+      <c r="H12" s="23">
+        <v>25</v>
+      </c>
+      <c r="I12" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q58" s="1">
+        <v>950</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>834</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>835</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>836</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="23">
+        <v>0</v>
+      </c>
+      <c r="H13" s="23">
+        <v>30</v>
+      </c>
+      <c r="I13" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R58" s="1">
+        <v>-30</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+      <c r="R13" s="24">
+        <f>H13</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>837</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>838</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>839</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G14" s="23">
+        <v>905</v>
+      </c>
+      <c r="H14" s="23">
+        <v>35</v>
+      </c>
+      <c r="I14" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H62" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>840</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>841</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>842</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="23">
+        <v>0</v>
+      </c>
+      <c r="H15" s="23">
+        <v>25</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22">
+        <v>1</v>
+      </c>
+      <c r="R15" s="24">
+        <f t="shared" ref="R15:R16" si="1">H15</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>843</v>
+      </c>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22" t="s">
+        <v>844</v>
+      </c>
+      <c r="F16" s="23">
+        <v>12</v>
+      </c>
+      <c r="G16" s="23">
+        <v>0</v>
+      </c>
+      <c r="H16" s="23">
+        <v>30</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+      <c r="R16" s="24">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>845</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>846</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>847</v>
+      </c>
+      <c r="F17" s="23">
+        <v>7</v>
+      </c>
+      <c r="G17" s="23">
+        <v>820</v>
+      </c>
+      <c r="H17" s="23">
+        <v>30</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>848</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>849</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>850</v>
+      </c>
+      <c r="F18" s="23">
+        <v>7</v>
+      </c>
+      <c r="G18" s="23">
+        <v>780</v>
+      </c>
+      <c r="H18" s="23">
+        <v>30</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>851</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>852</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>853</v>
+      </c>
+      <c r="F19" s="23">
+        <v>8</v>
+      </c>
+      <c r="G19" s="23">
+        <v>890</v>
+      </c>
+      <c r="H19" s="23">
+        <v>30</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>854</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>855</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>856</v>
+      </c>
+      <c r="F20" s="23">
+        <v>8</v>
+      </c>
+      <c r="G20" s="23">
+        <v>900</v>
+      </c>
+      <c r="H20" s="23">
+        <v>30</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>857</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>858</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>859</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="23">
+        <v>845</v>
+      </c>
+      <c r="H21" s="23">
+        <v>25</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="25"/>
+      <c r="B22" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>860</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>861</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>862</v>
+      </c>
+      <c r="F22" s="26">
+        <v>7</v>
+      </c>
+      <c r="G22" s="26">
+        <v>30</v>
+      </c>
+      <c r="H22" s="26">
+        <v>30</v>
+      </c>
+      <c r="I22" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="25" t="s">
+        <v>806</v>
+      </c>
+      <c r="K22" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="25" t="s">
+        <v>807</v>
+      </c>
+      <c r="M22" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N22" s="25"/>
+      <c r="O22" s="25"/>
+      <c r="P22" s="25"/>
+      <c r="Q22" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22" t="s">
+        <v>863</v>
+      </c>
+      <c r="F23" s="23">
+        <v>5</v>
+      </c>
+      <c r="G23" s="23">
+        <v>30</v>
+      </c>
+      <c r="H23" s="23">
+        <v>30</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>864</v>
+      </c>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22" t="s">
+        <v>626</v>
+      </c>
+      <c r="F24" s="23">
+        <v>6</v>
+      </c>
+      <c r="G24" s="23">
+        <v>0</v>
+      </c>
+      <c r="H24" s="23">
+        <v>30</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22">
+        <v>1</v>
+      </c>
+      <c r="R24" s="24">
+        <f>H24</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>865</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>866</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>867</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="23">
+        <v>975</v>
+      </c>
+      <c r="H25" s="23">
+        <v>25</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>868</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>869</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>870</v>
+      </c>
+      <c r="F26" s="23">
+        <v>2</v>
+      </c>
+      <c r="G26" s="23">
+        <v>850</v>
+      </c>
+      <c r="H26" s="23">
+        <v>30</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>871</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>872</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>873</v>
+      </c>
+      <c r="F27" s="23">
+        <v>2</v>
+      </c>
+      <c r="G27" s="23">
+        <v>400</v>
+      </c>
+      <c r="H27" s="23">
+        <v>30</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="0"/>
+        <v>370</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="25"/>
+      <c r="B28" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>682</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>874</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>684</v>
+      </c>
+      <c r="F28" s="26">
+        <v>2</v>
+      </c>
+      <c r="G28" s="26">
+        <v>0</v>
+      </c>
+      <c r="H28" s="26">
+        <v>30</v>
+      </c>
+      <c r="I28" s="26">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J28" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="K28" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="25" t="s">
+        <v>807</v>
+      </c>
+      <c r="M28" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N28" s="25"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="25"/>
+      <c r="Q28" s="25">
+        <v>1</v>
+      </c>
+      <c r="R28" s="31">
+        <f>H28</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>875</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>876</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>877</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G29" s="23">
+        <v>840</v>
+      </c>
+      <c r="H29" s="23">
+        <v>20</v>
+      </c>
+      <c r="I29" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>878</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>879</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>880</v>
+      </c>
+      <c r="F30" s="23">
+        <v>2</v>
+      </c>
+      <c r="G30" s="23">
+        <v>790</v>
+      </c>
+      <c r="H30" s="23">
+        <v>30</v>
+      </c>
+      <c r="I30" s="23">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>881</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>882</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>883</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G31" s="23">
+        <v>970</v>
+      </c>
+      <c r="H31" s="23">
+        <v>20</v>
+      </c>
+      <c r="I31" s="23">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J31" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K31" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>884</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>885</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="F32" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G32" s="23">
+        <v>975</v>
+      </c>
+      <c r="H32" s="23">
+        <v>25</v>
+      </c>
+      <c r="I32" s="23">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J32" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K32" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L32" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>886</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>887</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>888</v>
+      </c>
+      <c r="F33" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G33" s="23">
+        <v>890</v>
+      </c>
+      <c r="H33" s="23">
+        <v>30</v>
+      </c>
+      <c r="I33" s="23">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J33" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K33" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M33" s="22"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>889</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>890</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>891</v>
+      </c>
+      <c r="F34" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G34" s="23">
+        <v>1300</v>
+      </c>
+      <c r="H34" s="23">
+        <v>20</v>
+      </c>
+      <c r="I34" s="23">
+        <f t="shared" si="0"/>
+        <v>1280</v>
+      </c>
+      <c r="J34" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K34" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>892</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>893</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>894</v>
+      </c>
+      <c r="F35" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G35" s="23">
+        <v>750</v>
+      </c>
+      <c r="H35" s="23">
+        <v>30</v>
+      </c>
+      <c r="I35" s="23">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J35" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K35" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M35" s="22"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>765</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>895</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>896</v>
+      </c>
+      <c r="F36" s="23">
+        <v>2</v>
+      </c>
+      <c r="G36" s="23">
+        <v>380</v>
+      </c>
+      <c r="H36" s="23">
+        <v>30</v>
+      </c>
+      <c r="I36" s="23">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J36" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K36" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="22"/>
+      <c r="B37" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>897</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>898</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>899</v>
+      </c>
+      <c r="F37" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G37" s="23">
+        <v>0</v>
+      </c>
+      <c r="H37" s="23">
+        <v>20</v>
+      </c>
+      <c r="I37" s="23">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J37" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K37" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L37" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="22"/>
+      <c r="Q37" s="22">
+        <v>1</v>
+      </c>
+      <c r="R37" s="24">
+        <f t="shared" ref="R37:R38" si="2">H37</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="22"/>
+      <c r="B38" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>900</v>
+      </c>
+      <c r="D38" s="22" t="s">
+        <v>901</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>902</v>
+      </c>
+      <c r="F38" s="23">
+        <v>2</v>
+      </c>
+      <c r="G38" s="23">
+        <v>0</v>
+      </c>
+      <c r="H38" s="23">
+        <v>30</v>
+      </c>
+      <c r="I38" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J38" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K38" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M38" s="22"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="22"/>
+      <c r="P38" s="22"/>
+      <c r="Q38" s="22">
+        <v>1</v>
+      </c>
+      <c r="R38" s="24">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="22" t="s">
+        <v>903</v>
+      </c>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22" t="s">
+        <v>904</v>
+      </c>
+      <c r="F39" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G39" s="23">
+        <v>455</v>
+      </c>
+      <c r="H39" s="23">
+        <v>25</v>
+      </c>
+      <c r="I39" s="23">
+        <f t="shared" si="0"/>
+        <v>430</v>
+      </c>
+      <c r="J39" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K39" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L39" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M39" s="22"/>
+      <c r="N39" s="22"/>
+      <c r="O39" s="22"/>
+      <c r="P39" s="22"/>
+      <c r="Q39" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>905</v>
+      </c>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22" t="s">
+        <v>906</v>
+      </c>
+      <c r="F40" s="23">
+        <v>2</v>
+      </c>
+      <c r="G40" s="23">
+        <v>1405</v>
+      </c>
+      <c r="H40" s="23">
+        <v>35</v>
+      </c>
+      <c r="I40" s="23">
+        <f t="shared" si="0"/>
+        <v>1370</v>
+      </c>
+      <c r="J40" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K40" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L40" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M40" s="22"/>
+      <c r="N40" s="22"/>
+      <c r="O40" s="22"/>
+      <c r="P40" s="22"/>
+      <c r="Q40" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="22"/>
+      <c r="B41" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" s="22" t="s">
+        <v>907</v>
+      </c>
+      <c r="D41" s="22" t="s">
+        <v>908</v>
+      </c>
+      <c r="E41" s="22" t="s">
+        <v>909</v>
+      </c>
+      <c r="F41" s="23">
+        <v>10</v>
+      </c>
+      <c r="G41" s="23">
+        <v>685</v>
+      </c>
+      <c r="H41" s="23">
+        <v>25</v>
+      </c>
+      <c r="I41" s="23">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J41" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K41" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L41" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M41" s="22"/>
+      <c r="N41" s="22"/>
+      <c r="O41" s="22"/>
+      <c r="P41" s="22"/>
+      <c r="Q41" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="25"/>
+      <c r="B42" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>910</v>
+      </c>
+      <c r="D42" s="25" t="s">
+        <v>911</v>
+      </c>
+      <c r="E42" s="25" t="s">
+        <v>912</v>
+      </c>
+      <c r="F42" s="25" t="s">
+        <v>389</v>
+      </c>
+      <c r="G42" s="26">
+        <v>0</v>
+      </c>
+      <c r="H42" s="26">
+        <v>20</v>
+      </c>
+      <c r="I42" s="26">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J42" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="K42" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L42" s="25" t="s">
+        <v>807</v>
+      </c>
+      <c r="M42" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N42" s="25"/>
+      <c r="O42" s="25"/>
+      <c r="P42" s="25"/>
+      <c r="Q42" s="25">
+        <v>1</v>
+      </c>
+      <c r="R42" s="31">
+        <f>H42</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="22"/>
+      <c r="B43" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" s="22" t="s">
+        <v>913</v>
+      </c>
+      <c r="D43" s="22" t="s">
+        <v>914</v>
+      </c>
+      <c r="E43" s="22" t="s">
+        <v>915</v>
+      </c>
+      <c r="F43" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="G43" s="23">
+        <v>1060</v>
+      </c>
+      <c r="H43" s="23">
+        <v>20</v>
+      </c>
+      <c r="I43" s="23">
+        <f t="shared" si="0"/>
+        <v>1040</v>
+      </c>
+      <c r="J43" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K43" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L43" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M43" s="22"/>
+      <c r="N43" s="22"/>
+      <c r="O43" s="22"/>
+      <c r="P43" s="22"/>
+      <c r="Q43" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="22"/>
+      <c r="B44" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44" s="22" t="s">
+        <v>916</v>
+      </c>
+      <c r="D44" s="22" t="s">
+        <v>917</v>
+      </c>
+      <c r="E44" s="22" t="s">
+        <v>918</v>
+      </c>
+      <c r="F44" s="23">
+        <v>5</v>
+      </c>
+      <c r="G44" s="23">
+        <v>0</v>
+      </c>
+      <c r="H44" s="23">
+        <v>25</v>
+      </c>
+      <c r="I44" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J44" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K44" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L44" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M44" s="22"/>
+      <c r="N44" s="22"/>
+      <c r="O44" s="22"/>
+      <c r="P44" s="22"/>
+      <c r="Q44" s="22">
+        <v>1</v>
+      </c>
+      <c r="R44" s="24">
+        <f>H44</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="22"/>
+      <c r="B45" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>919</v>
+      </c>
+      <c r="D45" s="22" t="s">
+        <v>920</v>
+      </c>
+      <c r="E45" s="22" t="s">
+        <v>921</v>
+      </c>
+      <c r="F45" s="23">
+        <v>3</v>
+      </c>
+      <c r="G45" s="23">
+        <v>845</v>
+      </c>
+      <c r="H45" s="23">
+        <v>25</v>
+      </c>
+      <c r="I45" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J45" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K45" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L45" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M45" s="22"/>
+      <c r="N45" s="22"/>
+      <c r="O45" s="22"/>
+      <c r="P45" s="22"/>
+      <c r="Q45" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="22"/>
+      <c r="B46" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" s="22" t="s">
+        <v>922</v>
+      </c>
+      <c r="D46" s="22" t="s">
+        <v>923</v>
+      </c>
+      <c r="E46" s="22" t="s">
+        <v>924</v>
+      </c>
+      <c r="F46" s="23">
+        <v>1</v>
+      </c>
+      <c r="G46" s="23">
+        <v>915</v>
+      </c>
+      <c r="H46" s="23">
+        <v>25</v>
+      </c>
+      <c r="I46" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J46" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K46" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L46" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M46" s="22"/>
+      <c r="N46" s="22"/>
+      <c r="O46" s="22"/>
+      <c r="P46" s="22"/>
+      <c r="Q46" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="22"/>
+      <c r="B47" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47" s="22" t="s">
+        <v>925</v>
+      </c>
+      <c r="D47" s="22" t="s">
+        <v>926</v>
+      </c>
+      <c r="E47" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="F47" s="23">
+        <v>1</v>
+      </c>
+      <c r="G47" s="23">
+        <v>1135</v>
+      </c>
+      <c r="H47" s="23">
+        <v>25</v>
+      </c>
+      <c r="I47" s="23">
+        <f t="shared" si="0"/>
+        <v>1110</v>
+      </c>
+      <c r="J47" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K47" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L47" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M47" s="22"/>
+      <c r="N47" s="22"/>
+      <c r="O47" s="22"/>
+      <c r="P47" s="22"/>
+      <c r="Q47" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="22"/>
+      <c r="B48" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>928</v>
+      </c>
+      <c r="D48" s="22" t="s">
+        <v>929</v>
+      </c>
+      <c r="E48" s="22" t="s">
+        <v>930</v>
+      </c>
+      <c r="F48" s="23">
+        <v>4</v>
+      </c>
+      <c r="G48" s="23">
+        <v>1065</v>
+      </c>
+      <c r="H48" s="23">
+        <v>25</v>
+      </c>
+      <c r="I48" s="23">
+        <f t="shared" si="0"/>
+        <v>1040</v>
+      </c>
+      <c r="J48" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K48" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L48" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M48" s="22"/>
+      <c r="N48" s="22"/>
+      <c r="O48" s="22"/>
+      <c r="P48" s="22"/>
+      <c r="Q48" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="22"/>
+      <c r="B49" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>931</v>
+      </c>
+      <c r="D49" s="22" t="s">
+        <v>932</v>
+      </c>
+      <c r="E49" s="22" t="s">
+        <v>933</v>
+      </c>
+      <c r="F49" s="23">
+        <v>4</v>
+      </c>
+      <c r="G49" s="23">
+        <v>465</v>
+      </c>
+      <c r="H49" s="23">
+        <v>25</v>
+      </c>
+      <c r="I49" s="23">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J49" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K49" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L49" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M49" s="22"/>
+      <c r="N49" s="22"/>
+      <c r="O49" s="22"/>
+      <c r="P49" s="22"/>
+      <c r="Q49" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="22"/>
+      <c r="B50" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>934</v>
+      </c>
+      <c r="D50" s="22" t="s">
+        <v>935</v>
+      </c>
+      <c r="E50" s="22" t="s">
+        <v>936</v>
+      </c>
+      <c r="F50" s="23">
+        <v>3</v>
+      </c>
+      <c r="G50" s="23">
+        <v>815</v>
+      </c>
+      <c r="H50" s="23">
+        <v>25</v>
+      </c>
+      <c r="I50" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J50" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K50" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L50" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M50" s="22"/>
+      <c r="N50" s="22"/>
+      <c r="O50" s="22"/>
+      <c r="P50" s="22"/>
+      <c r="Q50" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="22"/>
+      <c r="B51" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>937</v>
+      </c>
+      <c r="D51" s="22" t="s">
+        <v>938</v>
+      </c>
+      <c r="E51" s="22" t="s">
+        <v>939</v>
+      </c>
+      <c r="F51" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G51" s="23">
+        <v>845</v>
+      </c>
+      <c r="H51" s="23">
+        <v>25</v>
+      </c>
+      <c r="I51" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J51" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K51" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L51" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M51" s="22"/>
+      <c r="N51" s="22"/>
+      <c r="O51" s="22"/>
+      <c r="P51" s="22"/>
+      <c r="Q51" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="22"/>
+      <c r="B52" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="22" t="s">
+        <v>940</v>
+      </c>
+      <c r="D52" s="22" t="s">
+        <v>941</v>
+      </c>
+      <c r="E52" s="22" t="s">
+        <v>942</v>
+      </c>
+      <c r="F52" s="23">
+        <v>10</v>
+      </c>
+      <c r="G52" s="23">
+        <v>3360</v>
+      </c>
+      <c r="H52" s="23">
+        <v>35</v>
+      </c>
+      <c r="I52" s="23">
+        <f t="shared" si="0"/>
+        <v>3325</v>
+      </c>
+      <c r="J52" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K52" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L52" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M52" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N52" s="22"/>
+      <c r="O52" s="22"/>
+      <c r="P52" s="22"/>
+      <c r="Q52" s="22">
+        <v>1</v>
+      </c>
+      <c r="R52" s="24">
+        <f>H52</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="22"/>
+      <c r="B53" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="22" t="s">
+        <v>573</v>
+      </c>
+      <c r="D53" s="22" t="s">
+        <v>943</v>
+      </c>
+      <c r="E53" s="22" t="s">
+        <v>575</v>
+      </c>
+      <c r="F53" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G53" s="23">
+        <v>895</v>
+      </c>
+      <c r="H53" s="23">
+        <v>25</v>
+      </c>
+      <c r="I53" s="23">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J53" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K53" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L53" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M53" s="22"/>
+      <c r="N53" s="22"/>
+      <c r="O53" s="22"/>
+      <c r="P53" s="22"/>
+      <c r="Q53" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="22"/>
+      <c r="B54" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" s="22" t="s">
+        <v>944</v>
+      </c>
+      <c r="D54" s="22" t="s">
+        <v>945</v>
+      </c>
+      <c r="E54" s="22" t="s">
+        <v>946</v>
+      </c>
+      <c r="F54" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G54" s="23">
+        <v>795</v>
+      </c>
+      <c r="H54" s="23">
+        <v>25</v>
+      </c>
+      <c r="I54" s="23">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J54" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K54" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L54" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M54" s="22"/>
+      <c r="N54" s="22"/>
+      <c r="O54" s="22"/>
+      <c r="P54" s="22"/>
+      <c r="Q54" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="22"/>
+      <c r="B55" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" s="22" t="s">
+        <v>947</v>
+      </c>
+      <c r="D55" s="22" t="s">
+        <v>948</v>
+      </c>
+      <c r="E55" s="22" t="s">
+        <v>949</v>
+      </c>
+      <c r="F55" s="23">
+        <v>5</v>
+      </c>
+      <c r="G55" s="23">
+        <v>0</v>
+      </c>
+      <c r="H55" s="23">
+        <v>25</v>
+      </c>
+      <c r="I55" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J55" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K55" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L55" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M55" s="22"/>
+      <c r="N55" s="22"/>
+      <c r="O55" s="22"/>
+      <c r="P55" s="22"/>
+      <c r="Q55" s="22">
+        <v>1</v>
+      </c>
+      <c r="R55" s="24">
+        <f>H55</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="22"/>
+      <c r="B56" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" s="22" t="s">
+        <v>950</v>
+      </c>
+      <c r="D56" s="22" t="s">
+        <v>951</v>
+      </c>
+      <c r="E56" s="22" t="s">
+        <v>952</v>
+      </c>
+      <c r="F56" s="23">
+        <v>1</v>
+      </c>
+      <c r="G56" s="23">
+        <v>865</v>
+      </c>
+      <c r="H56" s="23">
+        <v>25</v>
+      </c>
+      <c r="I56" s="23">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J56" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K56" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L56" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M56" s="22"/>
+      <c r="N56" s="22"/>
+      <c r="O56" s="22"/>
+      <c r="P56" s="22"/>
+      <c r="Q56" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="22"/>
+      <c r="B57" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" s="22" t="s">
+        <v>953</v>
+      </c>
+      <c r="D57" s="22" t="s">
+        <v>954</v>
+      </c>
+      <c r="E57" s="22" t="s">
+        <v>955</v>
+      </c>
+      <c r="F57" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G57" s="23">
+        <v>915</v>
+      </c>
+      <c r="H57" s="23">
+        <v>25</v>
+      </c>
+      <c r="I57" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J57" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K57" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L57" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M57" s="22"/>
+      <c r="N57" s="22"/>
+      <c r="O57" s="22"/>
+      <c r="P57" s="22"/>
+      <c r="Q57" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="22"/>
+      <c r="B58" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" s="22" t="s">
+        <v>956</v>
+      </c>
+      <c r="D58" s="22" t="s">
+        <v>957</v>
+      </c>
+      <c r="E58" s="22" t="s">
+        <v>958</v>
+      </c>
+      <c r="F58" s="23">
+        <v>4</v>
+      </c>
+      <c r="G58" s="23">
+        <v>715</v>
+      </c>
+      <c r="H58" s="23">
+        <v>25</v>
+      </c>
+      <c r="I58" s="23">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J58" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K58" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L58" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="M58" s="22"/>
+      <c r="N58" s="22"/>
+      <c r="O58" s="22"/>
+      <c r="P58" s="22"/>
+      <c r="Q58" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G60" s="1">
+        <f t="shared" ref="G60:R60" si="3">SUBTOTAL(9,G3:G59)</f>
+        <v>39880</v>
+      </c>
+      <c r="H60" s="1">
+        <f t="shared" si="3"/>
+        <v>1540</v>
+      </c>
+      <c r="I60" s="1">
+        <f t="shared" si="3"/>
+        <v>38340</v>
+      </c>
+      <c r="J60" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K60" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L60" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M60" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O60" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q60" s="1">
+        <f t="shared" si="3"/>
+        <v>56</v>
+      </c>
+      <c r="R60" s="1">
+        <f t="shared" si="3"/>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I61" s="1">
+        <v>-3360</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H64" s="4" t="s">
         <v>721</v>
       </c>
-      <c r="I62" s="5" t="s">
+      <c r="I64" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J62" s="6" t="s">
+      <c r="J64" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H63" s="7" t="s">
+    <row r="65" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H65" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I63" s="8">
-        <f>SUM(I57:I61)</f>
-        <v>0</v>
-      </c>
-      <c r="J63" s="8">
-        <f>Q58</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="H64" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I64" s="10">
-        <f>R58</f>
-        <v>0</v>
-      </c>
-      <c r="J64" s="11"/>
-    </row>
-    <row r="65" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H65" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="I65" s="10">
-        <f>S57</f>
-        <v>0</v>
-      </c>
-      <c r="J65" s="11"/>
+      <c r="I65" s="8">
+        <f>SUM(I59:I63)</f>
+        <v>34980</v>
+      </c>
+      <c r="J65" s="8">
+        <f>Q60</f>
+        <v>56</v>
+      </c>
     </row>
     <row r="66" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H66" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I66" s="10">
-        <f>T57</f>
-        <v>0</v>
+        <f>R60</f>
+        <v>330</v>
       </c>
       <c r="J66" s="11"/>
     </row>
     <row r="67" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H67" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I67" s="10">
+        <f>S59</f>
+        <v>0</v>
+      </c>
+      <c r="J67" s="11"/>
+    </row>
+    <row r="68" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H68" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I68" s="10">
+        <f>T59</f>
+        <v>0</v>
+      </c>
+      <c r="J68" s="11"/>
+    </row>
+    <row r="69" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H69" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I67" s="10">
-        <f>U57</f>
-        <v>0</v>
-      </c>
-      <c r="J67" s="11"/>
-    </row>
-    <row r="68" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H68" s="12" t="s">
+      <c r="I69" s="10">
+        <f>U59</f>
+        <v>0</v>
+      </c>
+      <c r="J69" s="11"/>
+    </row>
+    <row r="70" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H70" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
-    </row>
-    <row r="69" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H69" s="14" t="s">
+      <c r="I70" s="13"/>
+      <c r="J70" s="13"/>
+    </row>
+    <row r="71" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H71" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13"/>
-    </row>
-    <row r="70" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="H70" s="15" t="s">
+      <c r="I71" s="13"/>
+      <c r="J71" s="13"/>
+    </row>
+    <row r="72" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H72" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I70" s="16">
-        <f>SUM(I63:I69)</f>
-        <v>0</v>
-      </c>
-      <c r="J70" s="16">
-        <f>SUM(J63:J67)</f>
-        <v>0</v>
+      <c r="I72" s="16">
+        <f>SUM(I65:I71)</f>
+        <v>35310</v>
+      </c>
+      <c r="J72" s="16">
+        <f>SUM(J65:J69)</f>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P56" xr:uid="{00000000-0009-0000-0000-000006000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P56">
-      <sortCondition ref="J2:J56"/>
+  <autoFilter ref="A2:P58" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P58">
+      <sortCondition ref="J2:J58"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD43E377-304A-4721-8533-95445C7C5ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA5640E-763A-4203-A173-D0426942A48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'11-5'!$A$2:$P$58</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'12-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'12-5'!$A$2:$P$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'13-5'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-5'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'4-5'!$A$2:$P$22</definedName>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2686" uniqueCount="962">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2870" uniqueCount="1030">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -2943,6 +2943,210 @@
   </si>
   <si>
     <t>NGAY 13-5</t>
+  </si>
+  <si>
+    <t>Thiên Nga</t>
+  </si>
+  <si>
+    <t>HD020151</t>
+  </si>
+  <si>
+    <t>S5.02 Vinhomes grand park, Nguyễn Xiển, Long Mỹ</t>
+  </si>
+  <si>
+    <t>12-05-2026</t>
+  </si>
+  <si>
+    <t>kim xuyến</t>
+  </si>
+  <si>
+    <t>HD019918</t>
+  </si>
+  <si>
+    <t>1002 tạ quang bửu p6</t>
+  </si>
+  <si>
+    <t>AT 12-05</t>
+  </si>
+  <si>
+    <t>Bella Tran (Lê Huy)</t>
+  </si>
+  <si>
+    <t>HD020184</t>
+  </si>
+  <si>
+    <t>67B đường T5, phường Tây Thạnh</t>
+  </si>
+  <si>
+    <t>Phạm Oanh</t>
+  </si>
+  <si>
+    <t>HD020045</t>
+  </si>
+  <si>
+    <t>Cty Eidaikake xưởng 2. đường số 8 phường tân thuận đông đường huỳnh tấn phát kcxtt</t>
+  </si>
+  <si>
+    <t>Trần Thị Kim Phương</t>
+  </si>
+  <si>
+    <t>HD020054</t>
+  </si>
+  <si>
+    <t>1870\1\98\14a tỉnh lộ 10 tân tạo bình tân</t>
+  </si>
+  <si>
+    <t>Hoàng Thị Hồng</t>
+  </si>
+  <si>
+    <t>HD020036</t>
+  </si>
+  <si>
+    <t>Eco green tòa E nguyễn văn linh tân thuận tây</t>
+  </si>
+  <si>
+    <t>Trinh Kim</t>
+  </si>
+  <si>
+    <t>HD020079</t>
+  </si>
+  <si>
+    <t>2117A/9 Phạm Thế Hiển phường 6</t>
+  </si>
+  <si>
+    <t>HD020221</t>
+  </si>
+  <si>
+    <t>90a /10/10 Âu duong lân p3</t>
+  </si>
+  <si>
+    <t>Thu Thủy</t>
+  </si>
+  <si>
+    <t>HD020187</t>
+  </si>
+  <si>
+    <t>287 Kinh Dương Vương, P An Lạc</t>
+  </si>
+  <si>
+    <t>Đoàn Ngọc</t>
+  </si>
+  <si>
+    <t>HD020082</t>
+  </si>
+  <si>
+    <t>137/2 bình long</t>
+  </si>
+  <si>
+    <t>Thế Diễm</t>
+  </si>
+  <si>
+    <t>HD020049</t>
+  </si>
+  <si>
+    <t>159 Võ Nguyên Giáp, P Thảo Điền Chung cư Masteri Thảo Điền (Tháp 3)</t>
+  </si>
+  <si>
+    <t>Trần Thị Ngọc Trâm</t>
+  </si>
+  <si>
+    <t>HD020123</t>
+  </si>
+  <si>
+    <t>5/1H đường số 11 Bình Thọ</t>
+  </si>
+  <si>
+    <t>Bella</t>
+  </si>
+  <si>
+    <t>HD020155</t>
+  </si>
+  <si>
+    <t>209/8 nguyễn duy cung, P12</t>
+  </si>
+  <si>
+    <t>Lọ Lem</t>
+  </si>
+  <si>
+    <t>HD020148</t>
+  </si>
+  <si>
+    <t>484B no trang long p13</t>
+  </si>
+  <si>
+    <t>Hải Anh</t>
+  </si>
+  <si>
+    <t>HDO1778410597940_472532</t>
+  </si>
+  <si>
+    <t>L-1506, chung cư One Verandah, số 2 Bát Nàn p. Thạnh Mỹ Lợi</t>
+  </si>
+  <si>
+    <t>Hoang Yen</t>
+  </si>
+  <si>
+    <t>HD020081</t>
+  </si>
+  <si>
+    <t>652/7A Cộng Hoà - P13</t>
+  </si>
+  <si>
+    <t>HẠNH NARIN</t>
+  </si>
+  <si>
+    <t>Nguyễn My</t>
+  </si>
+  <si>
+    <t>HD020162</t>
+  </si>
+  <si>
+    <t>Tk18/3 nguyễn cảnh chân p cầu kho</t>
+  </si>
+  <si>
+    <t>Chị Quyên fb An Nhiên</t>
+  </si>
+  <si>
+    <t>HD020066</t>
+  </si>
+  <si>
+    <t>510 Ngô Gia Tự, P.An Đông</t>
+  </si>
+  <si>
+    <t>HD020192</t>
+  </si>
+  <si>
+    <t>#301 Pham Ngu Lao Street</t>
+  </si>
+  <si>
+    <t>HD020091</t>
+  </si>
+  <si>
+    <t>594/7 điện biên phủ p10</t>
+  </si>
+  <si>
+    <t>Tram Hoang Ngoc</t>
+  </si>
+  <si>
+    <t>HD020186</t>
+  </si>
+  <si>
+    <t>105K 15 hồ thị kỷ vườn lài</t>
+  </si>
+  <si>
+    <t>Phương Anh Chu</t>
+  </si>
+  <si>
+    <t>HD020219</t>
+  </si>
+  <si>
+    <t>Chung cư Grand Riverside - 278 Bến Vân Đồn P2</t>
+  </si>
+  <si>
+    <t>Em Na</t>
+  </si>
+  <si>
+    <t>Xe Khải Nam</t>
   </si>
 </sst>
 </file>
@@ -19656,14 +19860,14 @@
         <v>2</v>
       </c>
       <c r="G30" s="23">
+        <v>820</v>
+      </c>
+      <c r="H30" s="23">
+        <v>30</v>
+      </c>
+      <c r="I30" s="23">
+        <f t="shared" si="0"/>
         <v>790</v>
-      </c>
-      <c r="H30" s="23">
-        <v>30</v>
-      </c>
-      <c r="I30" s="23">
-        <f t="shared" si="0"/>
-        <v>760</v>
       </c>
       <c r="J30" s="22" t="s">
         <v>34</v>
@@ -20945,7 +21149,7 @@
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G60" s="1">
         <f t="shared" ref="G60:R60" si="3">SUBTOTAL(9,G3:G59)</f>
-        <v>39880</v>
+        <v>39910</v>
       </c>
       <c r="H60" s="1">
         <f t="shared" si="3"/>
@@ -20953,7 +21157,7 @@
       </c>
       <c r="I60" s="1">
         <f t="shared" si="3"/>
-        <v>38340</v>
+        <v>38370</v>
       </c>
       <c r="J60" s="1">
         <f t="shared" si="3"/>
@@ -21017,7 +21221,7 @@
       </c>
       <c r="I65" s="8">
         <f>SUM(I59:I63)</f>
-        <v>34980</v>
+        <v>35010</v>
       </c>
       <c r="J65" s="8">
         <f>Q60</f>
@@ -21084,7 +21288,7 @@
       </c>
       <c r="I72" s="16">
         <f>SUM(I65:I71)</f>
-        <v>35310</v>
+        <v>35340</v>
       </c>
       <c r="J72" s="16">
         <f>SUM(J65:J69)</f>
@@ -21104,7 +21308,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F101346F-FE09-4B80-8463-3C38A222BEE2}">
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
@@ -21177,1198 +21381,1281 @@
       </c>
       <c r="Q2" s="3"/>
     </row>
-    <row r="3" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-    </row>
-    <row r="4" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-    </row>
-    <row r="5" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="20"/>
-    </row>
-    <row r="6" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-    </row>
-    <row r="7" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="20"/>
-    </row>
-    <row r="8" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-    </row>
-    <row r="9" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-    </row>
-    <row r="10" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="20"/>
-    </row>
-    <row r="11" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="20"/>
-    </row>
-    <row r="12" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-    </row>
-    <row r="13" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-    </row>
-    <row r="14" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-    </row>
-    <row r="15" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="20"/>
-    </row>
-    <row r="16" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="20"/>
-    </row>
-    <row r="17" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="20"/>
-    </row>
-    <row r="18" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-    </row>
-    <row r="19" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="20"/>
-    </row>
-    <row r="20" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
-    </row>
-    <row r="21" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-    </row>
-    <row r="22" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-    </row>
-    <row r="23" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="20"/>
-    </row>
-    <row r="24" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
-    </row>
-    <row r="25" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="20"/>
-    </row>
-    <row r="26" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
-    </row>
-    <row r="27" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
-    </row>
-    <row r="28" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="20"/>
-    </row>
-    <row r="29" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="20"/>
-    </row>
-    <row r="30" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
-      <c r="P30" s="17"/>
-      <c r="Q30" s="17"/>
-    </row>
-    <row r="31" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17"/>
-      <c r="O31" s="17"/>
-      <c r="P31" s="17"/>
-      <c r="Q31" s="17"/>
-    </row>
-    <row r="32" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="17"/>
-      <c r="P32" s="17"/>
-      <c r="Q32" s="17"/>
-    </row>
-    <row r="33" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
-      <c r="P33" s="17"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="20"/>
-    </row>
-    <row r="34" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="17"/>
-    </row>
-    <row r="35" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
-    </row>
-    <row r="36" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="17"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17"/>
-      <c r="P36" s="17"/>
-      <c r="Q36" s="17"/>
-      <c r="R36" s="20"/>
-    </row>
-    <row r="37" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="17"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
-    </row>
-    <row r="38" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="17"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
-      <c r="N38" s="17"/>
-      <c r="O38" s="17"/>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17"/>
-    </row>
-    <row r="39" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="17"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
-      <c r="N39" s="17"/>
-      <c r="O39" s="17"/>
-      <c r="P39" s="17"/>
-      <c r="Q39" s="17"/>
-      <c r="R39" s="20"/>
-    </row>
-    <row r="40" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
-      <c r="N40" s="17"/>
-      <c r="O40" s="17"/>
-      <c r="P40" s="17"/>
-      <c r="Q40" s="17"/>
-    </row>
-    <row r="41" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
-      <c r="N41" s="17"/>
-      <c r="O41" s="17"/>
-      <c r="P41" s="17"/>
-      <c r="Q41" s="17"/>
-    </row>
-    <row r="42" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
-      <c r="M42" s="17"/>
-      <c r="N42" s="17"/>
-      <c r="O42" s="17"/>
-      <c r="P42" s="17"/>
-      <c r="Q42" s="17"/>
-    </row>
-    <row r="43" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
-      <c r="M43" s="17"/>
-      <c r="N43" s="17"/>
-      <c r="O43" s="17"/>
-      <c r="P43" s="17"/>
-      <c r="Q43" s="17"/>
-      <c r="R43" s="20"/>
-    </row>
-    <row r="44" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-      <c r="N44" s="17"/>
-      <c r="O44" s="17"/>
-      <c r="P44" s="17"/>
-      <c r="Q44" s="17"/>
-    </row>
-    <row r="45" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17"/>
-      <c r="O45" s="17"/>
-      <c r="P45" s="17"/>
-      <c r="Q45" s="17"/>
-      <c r="R45" s="20"/>
-    </row>
-    <row r="46" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="17"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="18"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="17"/>
-      <c r="M46" s="17"/>
-      <c r="N46" s="17"/>
-      <c r="O46" s="17"/>
-      <c r="P46" s="17"/>
-      <c r="Q46" s="17"/>
-      <c r="R46" s="20"/>
-    </row>
-    <row r="47" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="17"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="18"/>
-      <c r="I47" s="18"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
-      <c r="L47" s="17"/>
-      <c r="M47" s="17"/>
-      <c r="N47" s="17"/>
-      <c r="O47" s="17"/>
-      <c r="P47" s="17"/>
-      <c r="Q47" s="17"/>
-    </row>
-    <row r="48" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="17"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="18"/>
-      <c r="I48" s="18"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="17"/>
-      <c r="M48" s="17"/>
-      <c r="N48" s="17"/>
-      <c r="O48" s="17"/>
-      <c r="P48" s="17"/>
-      <c r="Q48" s="17"/>
-    </row>
-    <row r="49" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="17"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="18"/>
-      <c r="I49" s="18"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
-      <c r="N49" s="17"/>
-      <c r="O49" s="17"/>
-      <c r="P49" s="17"/>
-      <c r="Q49" s="17"/>
-      <c r="R49" s="20"/>
-    </row>
-    <row r="50" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="17"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
-      <c r="H50" s="18"/>
-      <c r="I50" s="18"/>
-      <c r="J50" s="17"/>
-      <c r="K50" s="17"/>
-      <c r="L50" s="17"/>
-      <c r="M50" s="17"/>
-      <c r="N50" s="17"/>
-      <c r="O50" s="17"/>
-      <c r="P50" s="17"/>
-      <c r="Q50" s="17"/>
-    </row>
-    <row r="51" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="17"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="18"/>
-      <c r="I51" s="18"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="17"/>
-      <c r="M51" s="17"/>
-      <c r="N51" s="17"/>
-      <c r="O51" s="17"/>
-      <c r="P51" s="17"/>
-      <c r="Q51" s="17"/>
-    </row>
-    <row r="52" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="17"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="18"/>
-      <c r="H52" s="18"/>
-      <c r="I52" s="18"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
-      <c r="M52" s="17"/>
-      <c r="N52" s="17"/>
-      <c r="O52" s="17"/>
-      <c r="P52" s="17"/>
-      <c r="Q52" s="17"/>
-      <c r="R52" s="20"/>
-    </row>
-    <row r="53" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="17"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="18"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
-      <c r="M53" s="17"/>
-      <c r="N53" s="17"/>
-      <c r="O53" s="17"/>
-      <c r="P53" s="17"/>
-      <c r="Q53" s="17"/>
-    </row>
-    <row r="54" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="17"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
-      <c r="H54" s="18"/>
-      <c r="I54" s="18"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="17"/>
-      <c r="O54" s="17"/>
-      <c r="P54" s="17"/>
-      <c r="Q54" s="17"/>
-    </row>
-    <row r="55" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="17"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-      <c r="H55" s="18"/>
-      <c r="I55" s="18"/>
-      <c r="J55" s="17"/>
-      <c r="K55" s="17"/>
-      <c r="L55" s="17"/>
-      <c r="M55" s="17"/>
-      <c r="N55" s="17"/>
-      <c r="O55" s="17"/>
-      <c r="P55" s="17"/>
-      <c r="Q55" s="17"/>
-    </row>
-    <row r="56" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="17"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="18"/>
-      <c r="I56" s="18"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="17"/>
-      <c r="O56" s="17"/>
-      <c r="P56" s="17"/>
-      <c r="Q56" s="17"/>
-      <c r="R56" s="20"/>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="G58" s="1">
-        <f t="shared" ref="G58:R58" si="0">SUBTOTAL(9,G3:G57)</f>
-        <v>0</v>
-      </c>
-      <c r="H58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H62" s="4" t="s">
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>962</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>964</v>
+      </c>
+      <c r="F3" s="23">
+        <v>9</v>
+      </c>
+      <c r="G3" s="23">
+        <v>820</v>
+      </c>
+      <c r="H3" s="23">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I27" si="0">G3-H3</f>
+        <v>790</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>966</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>967</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>968</v>
+      </c>
+      <c r="F4" s="23">
+        <v>8</v>
+      </c>
+      <c r="G4" s="23">
+        <v>1020</v>
+      </c>
+      <c r="H4" s="23">
+        <v>30</v>
+      </c>
+      <c r="I4" s="23">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>969</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>970</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>971</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>972</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="23">
+        <v>0</v>
+      </c>
+      <c r="H5" s="23">
+        <v>25</v>
+      </c>
+      <c r="I5" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>969</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+      <c r="R5" s="24">
+        <f>H5</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>973</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>974</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>975</v>
+      </c>
+      <c r="F6" s="23">
+        <v>7</v>
+      </c>
+      <c r="G6" s="23">
+        <v>400</v>
+      </c>
+      <c r="H6" s="23">
+        <v>30</v>
+      </c>
+      <c r="I6" s="23">
+        <f t="shared" si="0"/>
+        <v>370</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>969</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>976</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>977</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>978</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="23">
+        <v>920</v>
+      </c>
+      <c r="H7" s="23">
+        <v>30</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>969</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>979</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>980</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>981</v>
+      </c>
+      <c r="F8" s="23">
+        <v>7</v>
+      </c>
+      <c r="G8" s="23">
+        <v>920</v>
+      </c>
+      <c r="H8" s="23">
+        <v>30</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>969</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>982</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>983</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>984</v>
+      </c>
+      <c r="F9" s="23">
+        <v>8</v>
+      </c>
+      <c r="G9" s="23">
+        <v>980</v>
+      </c>
+      <c r="H9" s="23">
+        <v>30</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>969</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>537</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>985</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>986</v>
+      </c>
+      <c r="F10" s="23">
+        <v>8</v>
+      </c>
+      <c r="G10" s="23">
+        <v>900</v>
+      </c>
+      <c r="H10" s="23">
+        <v>30</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>969</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>987</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>988</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>989</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="23">
+        <v>670</v>
+      </c>
+      <c r="H11" s="23">
+        <v>30</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>969</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>990</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>991</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>992</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="23">
+        <v>920</v>
+      </c>
+      <c r="H12" s="23">
+        <v>30</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>969</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>993</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>994</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>995</v>
+      </c>
+      <c r="F13" s="23">
+        <v>2</v>
+      </c>
+      <c r="G13" s="23">
+        <v>1760</v>
+      </c>
+      <c r="H13" s="23">
+        <v>30</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>1730</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>996</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>997</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>998</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" s="23">
+        <v>920</v>
+      </c>
+      <c r="H14" s="23">
+        <v>30</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>999</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="23">
+        <v>0</v>
+      </c>
+      <c r="H15" s="23">
+        <v>25</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22">
+        <v>1</v>
+      </c>
+      <c r="R15" s="24">
+        <f>H15</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="23">
+        <v>910</v>
+      </c>
+      <c r="H16" s="23">
+        <v>20</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F17" s="23">
+        <v>2</v>
+      </c>
+      <c r="G17" s="23">
+        <v>920</v>
+      </c>
+      <c r="H17" s="23">
+        <v>30</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G18" s="23">
+        <v>865</v>
+      </c>
+      <c r="H18" s="23">
+        <v>25</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="F19" s="23">
+        <v>12</v>
+      </c>
+      <c r="G19" s="23">
+        <v>0</v>
+      </c>
+      <c r="H19" s="23">
+        <v>40</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+      <c r="R19" s="24">
+        <f>H19</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F20" s="23">
+        <v>1</v>
+      </c>
+      <c r="G20" s="23">
+        <v>975</v>
+      </c>
+      <c r="H20" s="23">
+        <v>25</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F21" s="23">
+        <v>5</v>
+      </c>
+      <c r="G21" s="23">
+        <v>2070</v>
+      </c>
+      <c r="H21" s="23">
+        <v>25</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>2045</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M21" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+      <c r="R21" s="24">
+        <f>H21</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>783</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F22" s="23">
+        <v>1</v>
+      </c>
+      <c r="G22" s="23">
+        <v>0</v>
+      </c>
+      <c r="H22" s="23">
+        <v>25</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+      <c r="R22" s="24">
+        <f t="shared" ref="R22:R23" si="1">H22</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>699</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F23" s="23">
+        <v>10</v>
+      </c>
+      <c r="G23" s="23">
+        <v>0</v>
+      </c>
+      <c r="H23" s="23">
+        <v>25</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+      <c r="R23" s="24">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F24" s="23">
+        <v>10</v>
+      </c>
+      <c r="G24" s="23">
+        <v>1145</v>
+      </c>
+      <c r="H24" s="23">
+        <v>25</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F25" s="23">
+        <v>4</v>
+      </c>
+      <c r="G25" s="23">
+        <v>845</v>
+      </c>
+      <c r="H25" s="23">
+        <v>25</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F26" s="23">
+        <v>5</v>
+      </c>
+      <c r="G26" s="23">
+        <v>0</v>
+      </c>
+      <c r="H26" s="23">
+        <v>35</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+      <c r="R26" s="24">
+        <f>H26</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22" t="s">
+        <v>421</v>
+      </c>
+      <c r="F27" s="23">
+        <v>1</v>
+      </c>
+      <c r="G27" s="23">
+        <v>0</v>
+      </c>
+      <c r="H27" s="23">
+        <v>30</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G29" s="1">
+        <f t="shared" ref="G29:R29" si="2">SUBTOTAL(9,G3:G28)</f>
+        <v>17960</v>
+      </c>
+      <c r="H29" s="1">
+        <f t="shared" si="2"/>
+        <v>710</v>
+      </c>
+      <c r="I29" s="1">
+        <f t="shared" si="2"/>
+        <v>17250</v>
+      </c>
+      <c r="J29" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N29" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O29" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P29" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="1">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="R29" s="1">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="8:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H33" s="4" t="s">
         <v>802</v>
       </c>
-      <c r="I62" s="5" t="s">
+      <c r="I33" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J62" s="6" t="s">
+      <c r="J33" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H63" s="7" t="s">
+    <row r="34" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H34" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I63" s="8">
-        <f>SUM(I57:I61)</f>
-        <v>0</v>
-      </c>
-      <c r="J63" s="8">
-        <f>Q58</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="H64" s="9" t="s">
+      <c r="I34" s="8">
+        <f>SUM(I28:I32)</f>
+        <v>17250</v>
+      </c>
+      <c r="J34" s="8">
+        <f>Q29</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H35" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I64" s="10">
-        <f>R58</f>
-        <v>0</v>
-      </c>
-      <c r="J64" s="11"/>
-    </row>
-    <row r="65" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H65" s="9" t="s">
+      <c r="I35" s="10">
+        <f>R29</f>
+        <v>200</v>
+      </c>
+      <c r="J35" s="11"/>
+    </row>
+    <row r="36" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H36" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I65" s="10">
-        <f>S57</f>
-        <v>0</v>
-      </c>
-      <c r="J65" s="11"/>
-    </row>
-    <row r="66" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H66" s="9" t="s">
+      <c r="I36" s="10">
+        <f>S28</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="11"/>
+    </row>
+    <row r="37" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H37" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I66" s="10">
-        <f>T57</f>
-        <v>0</v>
-      </c>
-      <c r="J66" s="11"/>
-    </row>
-    <row r="67" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H67" s="9" t="s">
+      <c r="I37" s="10">
+        <f>T28</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="11"/>
+    </row>
+    <row r="38" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H38" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I67" s="10">
-        <f>U57</f>
-        <v>0</v>
-      </c>
-      <c r="J67" s="11"/>
-    </row>
-    <row r="68" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H68" s="12" t="s">
+      <c r="I38" s="10">
+        <f>U28</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="11"/>
+    </row>
+    <row r="39" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H39" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
-    </row>
-    <row r="69" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H69" s="14" t="s">
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+    </row>
+    <row r="40" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H40" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13"/>
-    </row>
-    <row r="70" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="H70" s="15" t="s">
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+    </row>
+    <row r="41" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H41" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I70" s="16">
-        <f>SUM(I63:I69)</f>
-        <v>0</v>
-      </c>
-      <c r="J70" s="16">
-        <f>SUM(J63:J67)</f>
-        <v>0</v>
+      <c r="I41" s="16">
+        <f>SUM(I34:I40)</f>
+        <v>17450</v>
+      </c>
+      <c r="J41" s="16">
+        <f>SUM(J34:J38)</f>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P56" xr:uid="{00000000-0009-0000-0000-000006000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P56">
-      <sortCondition ref="J2:J56"/>
+  <autoFilter ref="A2:P27" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P27">
+      <sortCondition ref="J2:J27"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA5640E-763A-4203-A173-D0426942A48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68516E69-2F31-4390-BB95-10FF87B91BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-5" sheetId="3" r:id="rId1"/>
@@ -23,12 +23,20 @@
     <sheet name="11-5" sheetId="10" r:id="rId8"/>
     <sheet name="12-5" sheetId="11" r:id="rId9"/>
     <sheet name="13-5" sheetId="12" r:id="rId10"/>
+    <sheet name="14-5" sheetId="13" r:id="rId11"/>
+    <sheet name="15-5" sheetId="14" r:id="rId12"/>
+    <sheet name="16-5" sheetId="15" r:id="rId13"/>
+    <sheet name="18-5" sheetId="16" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'11-5'!$A$2:$P$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'12-5'!$A$2:$P$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'13-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'13-5'!$A$2:$P$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'14-5'!$A$2:$P$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'15-5'!$A$2:$P$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'16-5'!$A$2:$P$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'18-5'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'4-5'!$A$2:$P$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'5-5'!$A$2:$P$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'6-5'!$A$2:$P$34</definedName>
@@ -57,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2870" uniqueCount="1030">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4090" uniqueCount="1411">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -3147,6 +3155,1149 @@
   </si>
   <si>
     <t>Xe Khải Nam</t>
+  </si>
+  <si>
+    <t>NGAY 14-5</t>
+  </si>
+  <si>
+    <t>T5.14.5.2026</t>
+  </si>
+  <si>
+    <t>Sun Na</t>
+  </si>
+  <si>
+    <t>HD020281</t>
+  </si>
+  <si>
+    <t>Chung cư cardinal court toà B</t>
+  </si>
+  <si>
+    <t>AT 13-05</t>
+  </si>
+  <si>
+    <t>13-05-2026</t>
+  </si>
+  <si>
+    <t>tran Bảo Châu</t>
+  </si>
+  <si>
+    <t>HD020279</t>
+  </si>
+  <si>
+    <t>654/6 lạc long quân p9</t>
+  </si>
+  <si>
+    <t>Kim Nhân</t>
+  </si>
+  <si>
+    <t>HD020448</t>
+  </si>
+  <si>
+    <t>5M1/10 An Hạ</t>
+  </si>
+  <si>
+    <t>Mie Mie</t>
+  </si>
+  <si>
+    <t>HD020255</t>
+  </si>
+  <si>
+    <t>38 đường số 3, phường Tân Phú</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Kim Thoa</t>
+  </si>
+  <si>
+    <t>HD020457</t>
+  </si>
+  <si>
+    <t>số 25a đường 22 tình hưng hòa a</t>
+  </si>
+  <si>
+    <t>gộp, shop chịu ship</t>
+  </si>
+  <si>
+    <t>Bé Ty - fb Anh Lan</t>
+  </si>
+  <si>
+    <t>HD020293</t>
+  </si>
+  <si>
+    <t>532/3/6 Kinh Dương Vương, Phường An Lạc</t>
+  </si>
+  <si>
+    <t>FB NGUYỄN THỊ TRÚC NGÂN</t>
+  </si>
+  <si>
+    <t>HD020315</t>
+  </si>
+  <si>
+    <t>Số 78 Đường Số 7, P. Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Heng Roza (EV35382)</t>
+  </si>
+  <si>
+    <t>HD019725</t>
+  </si>
+  <si>
+    <t>HD020460</t>
+  </si>
+  <si>
+    <t>Hồng Phấn</t>
+  </si>
+  <si>
+    <t>HD020494</t>
+  </si>
+  <si>
+    <t>Ship Sảnh RS4 chung cư richstar 278 hoà bình, p.phú thạnh</t>
+  </si>
+  <si>
+    <t>Đoàn Kim</t>
+  </si>
+  <si>
+    <t>HD020450</t>
+  </si>
+  <si>
+    <t>Block D, chung cư floria đường số 1, tân hưng</t>
+  </si>
+  <si>
+    <t>HD020509</t>
+  </si>
+  <si>
+    <t>số 25a đường 22 bình hưng hòa a</t>
+  </si>
+  <si>
+    <t>nguyễn minh hải</t>
+  </si>
+  <si>
+    <t>No. 17, Street No. 13, Binh Hung Hoa Ward</t>
+  </si>
+  <si>
+    <t>Roxy Nguyen</t>
+  </si>
+  <si>
+    <t>HD020452</t>
+  </si>
+  <si>
+    <t>965/14c quang Trung, P.14</t>
+  </si>
+  <si>
+    <t>Nho Nhỏ</t>
+  </si>
+  <si>
+    <t>HD020360</t>
+  </si>
+  <si>
+    <t>Số 35 đường 34 phường linh đông</t>
+  </si>
+  <si>
+    <t>Đoan Trang</t>
+  </si>
+  <si>
+    <t>HD020499</t>
+  </si>
+  <si>
+    <t>Chung cư CitiEsto, Đ. 33-CL, Cát Lái, B02-07, Phường Cát Lái</t>
+  </si>
+  <si>
+    <t>HD020451</t>
+  </si>
+  <si>
+    <t>Tâm Vũ</t>
+  </si>
+  <si>
+    <t>HD020429</t>
+  </si>
+  <si>
+    <t>100/40/56 lê văn duyệt, phường gia định (p1 cũ)</t>
+  </si>
+  <si>
+    <t>(phan pham ngô nhi)</t>
+  </si>
+  <si>
+    <t>HD020453</t>
+  </si>
+  <si>
+    <t>403 đường tân sơn - phường an hội tây</t>
+  </si>
+  <si>
+    <t>zalo tuyền hoàng</t>
+  </si>
+  <si>
+    <t>HD020393</t>
+  </si>
+  <si>
+    <t>433/11/2 Lê Đức Thọ, Phường Gò Vấp (phường 17 CŨ)</t>
+  </si>
+  <si>
+    <t>Nytha</t>
+  </si>
+  <si>
+    <t>HD020287</t>
+  </si>
+  <si>
+    <t>392/2 ung văn khiêm p25</t>
+  </si>
+  <si>
+    <t>lindsiepham</t>
+  </si>
+  <si>
+    <t>HD020177</t>
+  </si>
+  <si>
+    <t>landmark 5b vinhomes central park</t>
+  </si>
+  <si>
+    <t>401 quang trung f10</t>
+  </si>
+  <si>
+    <t>huỳnh như</t>
+  </si>
+  <si>
+    <t>HD020300</t>
+  </si>
+  <si>
+    <t>387/12 phan văn trị chợ quán</t>
+  </si>
+  <si>
+    <t>Linh Đan</t>
+  </si>
+  <si>
+    <t>HD020536</t>
+  </si>
+  <si>
+    <t>Saigon Royal; Tháp AP1, 34-35 Bến Vân Đồn, P. 12</t>
+  </si>
+  <si>
+    <t>Thanh Phương</t>
+  </si>
+  <si>
+    <t>HD020444</t>
+  </si>
+  <si>
+    <t>Tòa nhà C22 Building S6 G26, đường C22, Phường 12</t>
+  </si>
+  <si>
+    <t>suz, fb Bei Bei</t>
+  </si>
+  <si>
+    <t>HD020337</t>
+  </si>
+  <si>
+    <t>256- 258 Lý thường kiết p14 (chung cư xi grand) Lock A2</t>
+  </si>
+  <si>
+    <t>Thanh Hương-Hương Missi</t>
+  </si>
+  <si>
+    <t>HD020496</t>
+  </si>
+  <si>
+    <t>215 Nam Kì Khởi Nghĩa Phường Võ Thị Sáu</t>
+  </si>
+  <si>
+    <t>Kim Tuyến</t>
+  </si>
+  <si>
+    <t>HD012977</t>
+  </si>
+  <si>
+    <t>718/3/12 trần hưng đạo p2</t>
+  </si>
+  <si>
+    <t>HD020295</t>
+  </si>
+  <si>
+    <t>36 Lê Lai phường bảy Hiền</t>
+  </si>
+  <si>
+    <t>HD020486</t>
+  </si>
+  <si>
+    <t>Mai Mai</t>
+  </si>
+  <si>
+    <t>HD020230</t>
+  </si>
+  <si>
+    <t>21b lý van phức tân định</t>
+  </si>
+  <si>
+    <t>T6.15.5.2026</t>
+  </si>
+  <si>
+    <t>NGAY 15-5</t>
+  </si>
+  <si>
+    <t>Bé Sarah</t>
+  </si>
+  <si>
+    <t>HD020613</t>
+  </si>
+  <si>
+    <t>Vinhome grand park toà gh2</t>
+  </si>
+  <si>
+    <t>14-05-2026</t>
+  </si>
+  <si>
+    <t>LDVKH</t>
+  </si>
+  <si>
+    <t>HD020852</t>
+  </si>
+  <si>
+    <t>(LDVKH1211714)177C ( Đối diện 93C) Đường Số 1, Phường Hưng Hoà B</t>
+  </si>
+  <si>
+    <t>AT 14-05</t>
+  </si>
+  <si>
+    <t>Lê Ngọc Nhân</t>
+  </si>
+  <si>
+    <t>HD20811</t>
+  </si>
+  <si>
+    <t>192 Phạm đức Sơn, P. Phú Định</t>
+  </si>
+  <si>
+    <t>My My</t>
+  </si>
+  <si>
+    <t>HD020534</t>
+  </si>
+  <si>
+    <t>114 vỏ liêm Sơn, phường Chánh hưng</t>
+  </si>
+  <si>
+    <t>Thùy An</t>
+  </si>
+  <si>
+    <t>HD020806</t>
+  </si>
+  <si>
+    <t>57/16 Phùng Chí Kiên</t>
+  </si>
+  <si>
+    <t>MeyMey EV28641</t>
+  </si>
+  <si>
+    <t>HD020601</t>
+  </si>
+  <si>
+    <t>315/18/6 Nguyễn Thị Tú Bình Hưng Hòa B</t>
+  </si>
+  <si>
+    <t>thanh nhàn - fb Lam Ng</t>
+  </si>
+  <si>
+    <t>HD020612</t>
+  </si>
+  <si>
+    <t>156a Tân quý phường Phú thọ hòa</t>
+  </si>
+  <si>
+    <t>VTS-34309SAK</t>
+  </si>
+  <si>
+    <t>HD020558</t>
+  </si>
+  <si>
+    <t>VTS-34309SAK, 601 QL1A, An Lạc</t>
+  </si>
+  <si>
+    <t>Mỹ Linh</t>
+  </si>
+  <si>
+    <t>HD020896</t>
+  </si>
+  <si>
+    <t>117/4b/15 hồ văn long, tân tạo, gần cây xăng đức lợi phát</t>
+  </si>
+  <si>
+    <t>Hiếu Lee</t>
+  </si>
+  <si>
+    <t>HD020637</t>
+  </si>
+  <si>
+    <t>Chung cu folita him lam</t>
+  </si>
+  <si>
+    <t>Nguyên Hà</t>
+  </si>
+  <si>
+    <t>HD020597</t>
+  </si>
+  <si>
+    <t>007 lô B chung cư Tây Thạnh, phườn Tân Thạnh</t>
+  </si>
+  <si>
+    <t>Thư Thỏ</t>
+  </si>
+  <si>
+    <t>HD020632</t>
+  </si>
+  <si>
+    <t>13 phạm thế hiển phường chánh hưng</t>
+  </si>
+  <si>
+    <t>Uyen Cam Cao</t>
+  </si>
+  <si>
+    <t>HD020895</t>
+  </si>
+  <si>
+    <t>182/8 đường số 6, bình hưng hoà b</t>
+  </si>
+  <si>
+    <t>Bookzan</t>
+  </si>
+  <si>
+    <t>137 phan huy ich p15</t>
+  </si>
+  <si>
+    <t>tân sơn phường 12</t>
+  </si>
+  <si>
+    <t>Anh Thư</t>
+  </si>
+  <si>
+    <t>HD020661</t>
+  </si>
+  <si>
+    <t>số 69 trần quốc tuấn hạnh thông</t>
+  </si>
+  <si>
+    <t>HD020802</t>
+  </si>
+  <si>
+    <t>cát giang</t>
+  </si>
+  <si>
+    <t>HD020867</t>
+  </si>
+  <si>
+    <t>1 ấp bắc</t>
+  </si>
+  <si>
+    <t>Khánh</t>
+  </si>
+  <si>
+    <t>HD020813</t>
+  </si>
+  <si>
+    <t>11 tam bình khu phố 7, phường hiệp bình</t>
+  </si>
+  <si>
+    <t>Linh Anh</t>
+  </si>
+  <si>
+    <t>HD020801</t>
+  </si>
+  <si>
+    <t>208 nguyễn hữu cảnh phường 22</t>
+  </si>
+  <si>
+    <t>HD020548</t>
+  </si>
+  <si>
+    <t>Tòa landmark 2</t>
+  </si>
+  <si>
+    <t>Thảo Ngân Lê</t>
+  </si>
+  <si>
+    <t>HD020823</t>
+  </si>
+  <si>
+    <t>1264/19/8 lê đức thọ, p13</t>
+  </si>
+  <si>
+    <t>THẢO PHẠM</t>
+  </si>
+  <si>
+    <t>NHÀ XE MINH QUỐC</t>
+  </si>
+  <si>
+    <t>LYKA</t>
+  </si>
+  <si>
+    <t>Gửi qua xe Khải Nam 363 Đường Hùng vương P. 9</t>
+  </si>
+  <si>
+    <t>Kim Hân</t>
+  </si>
+  <si>
+    <t>HD020598</t>
+  </si>
+  <si>
+    <t>302 Nguyễn chí thanh p5</t>
+  </si>
+  <si>
+    <t>kim nhung châu</t>
+  </si>
+  <si>
+    <t>HD020804</t>
+  </si>
+  <si>
+    <t>phòng 14.07 chung cư riva park số 504 nguyễn tất thành phường xóm chiếu</t>
+  </si>
+  <si>
+    <t>Ngan Tran</t>
+  </si>
+  <si>
+    <t>HD020814</t>
+  </si>
+  <si>
+    <t>11/39, Nguyễn Văn Mại, Phường Tân Sơn Nhất</t>
+  </si>
+  <si>
+    <t>Cherry Nguyễn</t>
+  </si>
+  <si>
+    <t>HD020793</t>
+  </si>
+  <si>
+    <t>66 hùng vương p1</t>
+  </si>
+  <si>
+    <t>Trâm</t>
+  </si>
+  <si>
+    <t>HD020800</t>
+  </si>
+  <si>
+    <t>132 bến vân đồn p9</t>
+  </si>
+  <si>
+    <t>___det___ insta</t>
+  </si>
+  <si>
+    <t>HD020529</t>
+  </si>
+  <si>
+    <t>363 Hùng Vương,p9</t>
+  </si>
+  <si>
+    <t>HD020687</t>
+  </si>
+  <si>
+    <t>HD020757</t>
+  </si>
+  <si>
+    <t>324/11 lý thường kiệt</t>
+  </si>
+  <si>
+    <t>HD020885</t>
+  </si>
+  <si>
+    <t>Linh Huệ</t>
+  </si>
+  <si>
+    <t>HD020761</t>
+  </si>
+  <si>
+    <t>12 tôn đản</t>
+  </si>
+  <si>
+    <t>Kami - fb Đan Khanh</t>
+  </si>
+  <si>
+    <t>HD020872</t>
+  </si>
+  <si>
+    <t>Chung cư DELASOL, căn A2.09.04, số 1 Tôn Thất Thuyết, P1</t>
+  </si>
+  <si>
+    <t>Elly Nguyễn</t>
+  </si>
+  <si>
+    <t>HD020858</t>
+  </si>
+  <si>
+    <t>431/7b đường Phan Văn Trị phường 7</t>
+  </si>
+  <si>
+    <t>kh ck shop 775k</t>
+  </si>
+  <si>
+    <t>T7.16.5.2026</t>
+  </si>
+  <si>
+    <t>NGAY 16-5</t>
+  </si>
+  <si>
+    <t>THƯƠNG 1994</t>
+  </si>
+  <si>
+    <t>Tòa S501, Vinhome grand park, Long Thạnh Mỹ</t>
+  </si>
+  <si>
+    <t>15-05-2026</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoài An</t>
+  </si>
+  <si>
+    <t>HD020928</t>
+  </si>
+  <si>
+    <t>15 đặng thai mai p7</t>
+  </si>
+  <si>
+    <t>Trang Nguyên</t>
+  </si>
+  <si>
+    <t>HD021087</t>
+  </si>
+  <si>
+    <t>13c lê thánh tôn</t>
+  </si>
+  <si>
+    <t>W24130 MiKi</t>
+  </si>
+  <si>
+    <t>HD021125</t>
+  </si>
+  <si>
+    <t>64 Lê Thị Riêng</t>
+  </si>
+  <si>
+    <t>Thanh Hà Phạm</t>
+  </si>
+  <si>
+    <t>HD020997</t>
+  </si>
+  <si>
+    <t>29/15 yên thế, p2</t>
+  </si>
+  <si>
+    <t>Binh Hương</t>
+  </si>
+  <si>
+    <t>HD020878</t>
+  </si>
+  <si>
+    <t>13 đươngg 44 phường 14</t>
+  </si>
+  <si>
+    <t>Người Nhận BN2705</t>
+  </si>
+  <si>
+    <t>HD021163</t>
+  </si>
+  <si>
+    <t>Đăng + Hạnh</t>
+  </si>
+  <si>
+    <t>HD021152</t>
+  </si>
+  <si>
+    <t>403 Tân Sơn, P12</t>
+  </si>
+  <si>
+    <t>HD021002</t>
+  </si>
+  <si>
+    <t>Tòa nhà C22 Building Số G26, đường C22, Phường 12</t>
+  </si>
+  <si>
+    <t>Lê Thị Ngọc Vân</t>
+  </si>
+  <si>
+    <t>HD021150</t>
+  </si>
+  <si>
+    <t>34 phùng văn cung p7</t>
+  </si>
+  <si>
+    <t>Huyền Trang</t>
+  </si>
+  <si>
+    <t>HD021153</t>
+  </si>
+  <si>
+    <t>108 hồng hà p2</t>
+  </si>
+  <si>
+    <t>Đức nhận hộ Mimi -87780266</t>
+  </si>
+  <si>
+    <t>HD020538</t>
+  </si>
+  <si>
+    <t>39 an nhơn phương 17</t>
+  </si>
+  <si>
+    <t>Bing Bing</t>
+  </si>
+  <si>
+    <t>HD021129</t>
+  </si>
+  <si>
+    <t>Landmark 5, Vinhome central park, F22</t>
+  </si>
+  <si>
+    <t>Vu Hiếu</t>
+  </si>
+  <si>
+    <t>HD021028</t>
+  </si>
+  <si>
+    <t>Số 10 đuong 18 linh đông</t>
+  </si>
+  <si>
+    <t>ĐÔNG MIÊN malay</t>
+  </si>
+  <si>
+    <t>HD021014</t>
+  </si>
+  <si>
+    <t>22 TÂN THỚI NHẤT 1B, Phường Tân Thới Nhất</t>
+  </si>
+  <si>
+    <t>Daisy</t>
+  </si>
+  <si>
+    <t>HD021054</t>
+  </si>
+  <si>
+    <t>5A Lam Sơn, Phường Tân Sơn Hòa</t>
+  </si>
+  <si>
+    <t>Mr Thế</t>
+  </si>
+  <si>
+    <t>27/5 Quách Văn Tuấn, F12</t>
+  </si>
+  <si>
+    <t>Kiên Hoàng Khiêm</t>
+  </si>
+  <si>
+    <t>HD020881</t>
+  </si>
+  <si>
+    <t>531 Điện Biên Phủ P. Bàn Cờ</t>
+  </si>
+  <si>
+    <t>AT 15-05</t>
+  </si>
+  <si>
+    <t>Hồ Nguyễn Quỳnh Như</t>
+  </si>
+  <si>
+    <t>HD020995</t>
+  </si>
+  <si>
+    <t>Central premium lock A 0946374247</t>
+  </si>
+  <si>
+    <t>Người nhận: Vũ Hạ</t>
+  </si>
+  <si>
+    <t>HD020648</t>
+  </si>
+  <si>
+    <t>cầu thang số 2 lô F, chung cư Sơn Kỳ, đường CC5, P. Tây Thạnh</t>
+  </si>
+  <si>
+    <t>Jenny Đoàn</t>
+  </si>
+  <si>
+    <t>HD021013</t>
+  </si>
+  <si>
+    <t>lô m3 chung cư số 1 tôn thất thuyết p1</t>
+  </si>
+  <si>
+    <t>Mứt Dâu</t>
+  </si>
+  <si>
+    <t>HD018064</t>
+  </si>
+  <si>
+    <t>238/14 quốc lộ 50 phường 6</t>
+  </si>
+  <si>
+    <t>HD021101</t>
+  </si>
+  <si>
+    <t>Megan Truong</t>
+  </si>
+  <si>
+    <t>HD020862</t>
+  </si>
+  <si>
+    <t>số nhà 1527/3/1 hẻm 1545 lê văn lương, nhơn đức</t>
+  </si>
+  <si>
+    <t>HD021024</t>
+  </si>
+  <si>
+    <t>Nguyễn Thùy</t>
+  </si>
+  <si>
+    <t>HD021164</t>
+  </si>
+  <si>
+    <t>71/46 gò xoài p bình hưng hoà a</t>
+  </si>
+  <si>
+    <t>Bảo Trân</t>
+  </si>
+  <si>
+    <t>HD021085</t>
+  </si>
+  <si>
+    <t>90a đường 37 Tân Quy</t>
+  </si>
+  <si>
+    <t>Bác Thanh - fb Pé Síu</t>
+  </si>
+  <si>
+    <t>HDO21082</t>
+  </si>
+  <si>
+    <t>566/17 An Duong Vuong p11</t>
+  </si>
+  <si>
+    <t>VTS-51916TNV</t>
+  </si>
+  <si>
+    <t>HD020984</t>
+  </si>
+  <si>
+    <t>601 QL1A, An Lạc</t>
+  </si>
+  <si>
+    <t>coca ( kẹ)</t>
+  </si>
+  <si>
+    <t>HD021127</t>
+  </si>
+  <si>
+    <t>532/3/93 kinh dương vương, Phường an lạc</t>
+  </si>
+  <si>
+    <t>Phương Dung</t>
+  </si>
+  <si>
+    <t>HD020877</t>
+  </si>
+  <si>
+    <t>Sunshine sky city tòa A2</t>
+  </si>
+  <si>
+    <t>Phuong Ho</t>
+  </si>
+  <si>
+    <t>HD021147</t>
+  </si>
+  <si>
+    <t>576a dien bien phu phuong vuon lai</t>
+  </si>
+  <si>
+    <t>NGAY 18-5</t>
+  </si>
+  <si>
+    <t>T2.18.5.2026</t>
+  </si>
+  <si>
+    <t>yến trinh</t>
+  </si>
+  <si>
+    <t>HD021308</t>
+  </si>
+  <si>
+    <t>321 an dương vương, an lạc, bình tân Chung cư khang điền lộck b</t>
+  </si>
+  <si>
+    <t>AT 16-05</t>
+  </si>
+  <si>
+    <t>16-05-2026</t>
+  </si>
+  <si>
+    <t>kh ck shop 4210k</t>
+  </si>
+  <si>
+    <t>Phạm T. Thảo</t>
+  </si>
+  <si>
+    <t>HD021288</t>
+  </si>
+  <si>
+    <t>63 dương bá trạc p. rạch ông</t>
+  </si>
+  <si>
+    <t>Nhận hành giúp chị phương (ở Úc) fb Phương My</t>
+  </si>
+  <si>
+    <t>HD021421</t>
+  </si>
+  <si>
+    <t>126/5h song hành, tân hiệp</t>
+  </si>
+  <si>
+    <t>hoc mon</t>
+  </si>
+  <si>
+    <t>Trần Bảo Hân (inst tienbaohen17)</t>
+  </si>
+  <si>
+    <t>HD021310</t>
+  </si>
+  <si>
+    <t>E4/25a đường Nguyễn Hữu Trí, khu phố 12, thị trấn Tân Túc</t>
+  </si>
+  <si>
+    <t>Trần Bảo Hân (inst tranbaohan17)</t>
+  </si>
+  <si>
+    <t>HD021309</t>
+  </si>
+  <si>
+    <t>Loan Trần</t>
+  </si>
+  <si>
+    <t>HD021379</t>
+  </si>
+  <si>
+    <t>64/24C hoà bình phường hòa bình</t>
+  </si>
+  <si>
+    <t>Đỗ T. Thu Hồng</t>
+  </si>
+  <si>
+    <t>HD021466</t>
+  </si>
+  <si>
+    <t>Lock A - eco green - nguyễn văn linh</t>
+  </si>
+  <si>
+    <t>Nguyễn Lê</t>
+  </si>
+  <si>
+    <t>HD021425</t>
+  </si>
+  <si>
+    <t>287/1/5 thành công, tân thành</t>
+  </si>
+  <si>
+    <t>HD021282</t>
+  </si>
+  <si>
+    <t>287/1/5 thành công, tấn thành</t>
+  </si>
+  <si>
+    <t>Ngọc Mỹ Kim</t>
+  </si>
+  <si>
+    <t>HD021327</t>
+  </si>
+  <si>
+    <t>Chung cu topaz elite drgon 2c p4 ta quang buu</t>
+  </si>
+  <si>
+    <t>kh ck shop 1820k</t>
+  </si>
+  <si>
+    <t>Cẩm Cẩm</t>
+  </si>
+  <si>
+    <t>HD021193</t>
+  </si>
+  <si>
+    <t>150 Hoàng Trọng Mậu Tân Hưng</t>
+  </si>
+  <si>
+    <t>Sam Sam</t>
+  </si>
+  <si>
+    <t>HD021214</t>
+  </si>
+  <si>
+    <t>Sunrise city view tòa B .33 Nguyễn Hữu Thọ phường tân hưng</t>
+  </si>
+  <si>
+    <t>Ann Ann</t>
+  </si>
+  <si>
+    <t>HD021246</t>
+  </si>
+  <si>
+    <t>172 lê thị bạch cát p11</t>
+  </si>
+  <si>
+    <t>HD021369</t>
+  </si>
+  <si>
+    <t>87/10 trần quang cơ phú thạnh</t>
+  </si>
+  <si>
+    <t>Người nhận: Fb Phương Mai</t>
+  </si>
+  <si>
+    <t>HD020876</t>
+  </si>
+  <si>
+    <t>433/11/2 Lê Đức Thọ, Phường 17</t>
+  </si>
+  <si>
+    <t>HD021355</t>
+  </si>
+  <si>
+    <t>HD021442</t>
+  </si>
+  <si>
+    <t>42, đường 21,Khu dân cư bình chiểu, P tam bình (chợ đầu mối nông sản thủ đức)</t>
+  </si>
+  <si>
+    <t>chị Huyền</t>
+  </si>
+  <si>
+    <t>HĐ021386</t>
+  </si>
+  <si>
+    <t>9B nguyễn xí, phường 26</t>
+  </si>
+  <si>
+    <t>Duyên Duyên</t>
+  </si>
+  <si>
+    <t>HD021253</t>
+  </si>
+  <si>
+    <t>Đường số 9 hẻm 58/36 linh tây</t>
+  </si>
+  <si>
+    <t>Nuong Huynh</t>
+  </si>
+  <si>
+    <t>HD021213</t>
+  </si>
+  <si>
+    <t>67 mai chí thọ phường an phú</t>
+  </si>
+  <si>
+    <t>HD021227</t>
+  </si>
+  <si>
+    <t>BN9663</t>
+  </si>
+  <si>
+    <t>HD021364</t>
+  </si>
+  <si>
+    <t>Khả Di</t>
+  </si>
+  <si>
+    <t>HD021217</t>
+  </si>
+  <si>
+    <t>54A đường số 7, Linh Trung</t>
+  </si>
+  <si>
+    <t>Ánh Hoàng</t>
+  </si>
+  <si>
+    <t>HD021275</t>
+  </si>
+  <si>
+    <t>Stown Tham Lương sảnh B Phường Tân Thới Nhất</t>
+  </si>
+  <si>
+    <t>Huỳnh Phương Mỹ Duyên</t>
+  </si>
+  <si>
+    <t>HD021212</t>
+  </si>
+  <si>
+    <t>21 bis đường số 10, phường bình an</t>
+  </si>
+  <si>
+    <t>Hồng Thắm</t>
+  </si>
+  <si>
+    <t>27 đông hưng thuận 45 tân hưng thuận</t>
+  </si>
+  <si>
+    <t>tân sơn p12</t>
+  </si>
+  <si>
+    <t>VERISKA (YAYANG) - ROOM 104.</t>
+  </si>
+  <si>
+    <t>HD021409</t>
+  </si>
+  <si>
+    <t>Saigon Europe Hotel, Số 207 đường Đề Thám, phường bến Thành</t>
+  </si>
+  <si>
+    <t>HD021185</t>
+  </si>
+  <si>
+    <t>Số 207 đường Đề Thám, phường bến Thành</t>
+  </si>
+  <si>
+    <t>Hiệp fb Đặng Tổ Trinh</t>
+  </si>
+  <si>
+    <t>HD021271</t>
+  </si>
+  <si>
+    <t>Số 3 hoàng minh giám phường đức nhuận</t>
+  </si>
+  <si>
+    <t>Linh Tiêu</t>
+  </si>
+  <si>
+    <t>HD021267</t>
+  </si>
+  <si>
+    <t>97 Ký Con, p. Nguyễn Thái Bình</t>
+  </si>
+  <si>
+    <t>Thien Phu Nguyen</t>
+  </si>
+  <si>
+    <t>HD021468</t>
+  </si>
+  <si>
+    <t>Block B - Chung cư RiverGate Residence 151-155 Bến Vân Đồn, Phường Khánh Hội</t>
+  </si>
+  <si>
+    <t>Mai Sương</t>
+  </si>
+  <si>
+    <t>HD021469</t>
+  </si>
+  <si>
+    <t>55/3 trần đình xu, phường cầu kho</t>
+  </si>
+  <si>
+    <t>Heng Stella</t>
+  </si>
+  <si>
+    <t>Ngọc Phượng</t>
+  </si>
+  <si>
+    <t>HD014928</t>
+  </si>
+  <si>
+    <t>The grand midtown m5 đường số 16 p. Tân Phú</t>
+  </si>
+  <si>
+    <t>24-04-2026</t>
+  </si>
+  <si>
+    <t>kh ck shop 870k</t>
+  </si>
+  <si>
+    <t>đơn trả 18.5</t>
   </si>
 </sst>
 </file>
@@ -6406,6 +7557,7372 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3899F5A-29E8-4E78-9648-A9394903C07E}">
+  <dimension ref="A1:R49"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F3" s="23">
+        <v>7</v>
+      </c>
+      <c r="G3" s="23">
+        <v>980</v>
+      </c>
+      <c r="H3" s="23">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I35" si="0">G3-H3</f>
+        <v>950</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4" s="23">
+        <v>845</v>
+      </c>
+      <c r="H4" s="23">
+        <v>25</v>
+      </c>
+      <c r="I4" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="25"/>
+      <c r="B5" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="G5" s="26">
+        <v>35</v>
+      </c>
+      <c r="H5" s="26">
+        <v>35</v>
+      </c>
+      <c r="I5" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="25" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="25" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F6" s="23">
+        <v>7</v>
+      </c>
+      <c r="G6" s="23">
+        <v>900</v>
+      </c>
+      <c r="H6" s="23">
+        <v>30</v>
+      </c>
+      <c r="I6" s="23">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="23">
+        <v>1570</v>
+      </c>
+      <c r="H7" s="23">
+        <v>35</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
+        <v>1535</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M7" s="28" t="s">
+        <v>1049</v>
+      </c>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+      <c r="R7" s="24">
+        <f>H7</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="23">
+        <v>3930</v>
+      </c>
+      <c r="H8" s="23">
+        <v>40</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>3890</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0</v>
+      </c>
+      <c r="H9" s="23">
+        <v>30</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+      <c r="R9" s="24">
+        <f>H9</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>736</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0</v>
+      </c>
+      <c r="H10" s="23">
+        <v>30</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+      <c r="R10" s="24">
+        <f>H10</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>630</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>632</v>
+      </c>
+      <c r="F11" s="23">
+        <v>9</v>
+      </c>
+      <c r="G11" s="23">
+        <v>880</v>
+      </c>
+      <c r="H11" s="23">
+        <v>30</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="23">
+        <v>875</v>
+      </c>
+      <c r="H12" s="23">
+        <v>25</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F13" s="23">
+        <v>7</v>
+      </c>
+      <c r="G13" s="23">
+        <v>0</v>
+      </c>
+      <c r="H13" s="23">
+        <v>30</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+      <c r="R13" s="24">
+        <f>H13</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="23">
+        <v>780</v>
+      </c>
+      <c r="H14" s="23">
+        <v>0</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M14" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="23">
+        <v>50</v>
+      </c>
+      <c r="H15" s="23">
+        <v>50</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="23">
+        <v>875</v>
+      </c>
+      <c r="H16" s="23">
+        <v>25</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="23">
+        <v>0</v>
+      </c>
+      <c r="H17" s="23">
+        <v>30</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+      <c r="R17" s="24">
+        <f>H17</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F18" s="23">
+        <v>2</v>
+      </c>
+      <c r="G18" s="23">
+        <v>920</v>
+      </c>
+      <c r="H18" s="23">
+        <v>30</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="23">
+        <v>870</v>
+      </c>
+      <c r="H19" s="23">
+        <v>20</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" s="23">
+        <v>20</v>
+      </c>
+      <c r="H20" s="23">
+        <v>20</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="23">
+        <v>0</v>
+      </c>
+      <c r="H21" s="23">
+        <v>25</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+      <c r="R21" s="24">
+        <f>H21</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" s="23">
+        <v>875</v>
+      </c>
+      <c r="H22" s="23">
+        <v>25</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G23" s="23">
+        <v>0</v>
+      </c>
+      <c r="H23" s="23">
+        <v>20</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+      <c r="R23" s="24">
+        <f>H23</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" s="23">
+        <v>840</v>
+      </c>
+      <c r="H24" s="23">
+        <v>20</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="23">
+        <v>30</v>
+      </c>
+      <c r="H25" s="23">
+        <v>30</v>
+      </c>
+      <c r="I25" s="23">
+        <f>G25-H25</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26" s="23">
+        <v>3955</v>
+      </c>
+      <c r="H26" s="23">
+        <v>35</v>
+      </c>
+      <c r="I26" s="23">
+        <f>G26-H26</f>
+        <v>3920</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" s="23">
+        <v>815</v>
+      </c>
+      <c r="H27" s="23">
+        <v>25</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F28" s="23">
+        <v>4</v>
+      </c>
+      <c r="G28" s="23">
+        <v>765</v>
+      </c>
+      <c r="H28" s="23">
+        <v>25</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G29" s="23">
+        <v>25</v>
+      </c>
+      <c r="H29" s="23">
+        <v>25</v>
+      </c>
+      <c r="I29" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F30" s="23">
+        <v>10</v>
+      </c>
+      <c r="G30" s="23">
+        <v>725</v>
+      </c>
+      <c r="H30" s="23">
+        <v>25</v>
+      </c>
+      <c r="I30" s="23">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F31" s="23">
+        <v>3</v>
+      </c>
+      <c r="G31" s="23">
+        <v>765</v>
+      </c>
+      <c r="H31" s="23">
+        <v>25</v>
+      </c>
+      <c r="I31" s="23">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J31" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K31" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F32" s="23">
+        <v>5</v>
+      </c>
+      <c r="G32" s="23">
+        <v>1115</v>
+      </c>
+      <c r="H32" s="23">
+        <v>25</v>
+      </c>
+      <c r="I32" s="23">
+        <f t="shared" si="0"/>
+        <v>1090</v>
+      </c>
+      <c r="J32" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K32" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L32" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>937</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F33" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G33" s="23">
+        <v>815</v>
+      </c>
+      <c r="H33" s="23">
+        <v>25</v>
+      </c>
+      <c r="I33" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J33" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K33" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M33" s="22"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="25"/>
+      <c r="B34" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F34" s="26">
+        <v>4</v>
+      </c>
+      <c r="G34" s="26">
+        <v>45</v>
+      </c>
+      <c r="H34" s="26">
+        <v>25</v>
+      </c>
+      <c r="I34" s="26">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="J34" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="K34" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34" s="25" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M34" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N34" s="25"/>
+      <c r="O34" s="25"/>
+      <c r="P34" s="25"/>
+      <c r="Q34" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F35" s="23">
+        <v>1</v>
+      </c>
+      <c r="G35" s="23">
+        <v>765</v>
+      </c>
+      <c r="H35" s="23">
+        <v>25</v>
+      </c>
+      <c r="I35" s="23">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J35" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K35" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M35" s="22"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G37" s="1">
+        <f t="shared" ref="G37:R37" si="1">SUBTOTAL(9,G3:G36)</f>
+        <v>25065</v>
+      </c>
+      <c r="H37" s="1">
+        <f t="shared" si="1"/>
+        <v>895</v>
+      </c>
+      <c r="I37" s="1">
+        <f t="shared" si="1"/>
+        <v>24170</v>
+      </c>
+      <c r="J37" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N37" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O37" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P37" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q37" s="1">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="R37" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H41" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I42" s="8">
+        <f>SUM(I36:I40)</f>
+        <v>24170</v>
+      </c>
+      <c r="J42" s="8">
+        <f>Q37</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" s="10">
+        <f>R37</f>
+        <v>200</v>
+      </c>
+      <c r="J43" s="11"/>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H44" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44" s="10">
+        <f>S36</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="11"/>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H45" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45" s="10">
+        <f>T36</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="11"/>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H46" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I46" s="10">
+        <f>U36</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="11"/>
+    </row>
+    <row r="47" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H47" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
+    </row>
+    <row r="48" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H48" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13"/>
+    </row>
+    <row r="49" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H49" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I49" s="16">
+        <f>SUM(I42:I48)</f>
+        <v>24370</v>
+      </c>
+      <c r="J49" s="16">
+        <f>SUM(J42:J46)</f>
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P35" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P35">
+      <sortCondition ref="J2:J35"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{742339B8-44B5-456F-904E-6135F949606D}">
+  <dimension ref="A1:R56"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F3" s="23">
+        <v>9</v>
+      </c>
+      <c r="G3" s="23">
+        <v>980</v>
+      </c>
+      <c r="H3" s="23">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I39" si="0">G3-H3</f>
+        <v>950</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="23">
+        <v>0</v>
+      </c>
+      <c r="H4" s="23">
+        <v>30</v>
+      </c>
+      <c r="I4" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4" s="24">
+        <f>H4</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F5" s="23">
+        <v>7</v>
+      </c>
+      <c r="G5" s="23">
+        <v>810</v>
+      </c>
+      <c r="H5" s="23">
+        <v>30</v>
+      </c>
+      <c r="I5" s="23">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="F6" s="23">
+        <v>8</v>
+      </c>
+      <c r="G6" s="23">
+        <v>1550</v>
+      </c>
+      <c r="H6" s="23">
+        <v>30</v>
+      </c>
+      <c r="I6" s="23">
+        <f t="shared" si="0"/>
+        <v>1520</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="23">
+        <v>835</v>
+      </c>
+      <c r="H7" s="23">
+        <v>25</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
+        <v>810</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="23">
+        <v>0</v>
+      </c>
+      <c r="H8" s="23">
+        <v>30</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8" s="24">
+        <f>H8</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="23">
+        <v>805</v>
+      </c>
+      <c r="H9" s="23">
+        <v>25</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0</v>
+      </c>
+      <c r="H10" s="23">
+        <v>30</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10" s="24">
+        <f>H10</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="23">
+        <v>810</v>
+      </c>
+      <c r="H11" s="23">
+        <v>30</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F12" s="23">
+        <v>7</v>
+      </c>
+      <c r="G12" s="23">
+        <v>720</v>
+      </c>
+      <c r="H12" s="23">
+        <v>30</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>1155</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="23">
+        <v>0</v>
+      </c>
+      <c r="H13" s="23">
+        <v>25</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13" s="24">
+        <f>H13</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F14" s="23">
+        <v>8</v>
+      </c>
+      <c r="G14" s="23">
+        <v>810</v>
+      </c>
+      <c r="H14" s="23">
+        <v>30</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="23">
+        <v>750</v>
+      </c>
+      <c r="H15" s="23">
+        <v>30</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G16" s="23">
+        <v>0</v>
+      </c>
+      <c r="H16" s="23">
+        <v>40</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16" s="24">
+        <f>H16</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="23">
+        <v>30</v>
+      </c>
+      <c r="H17" s="23">
+        <v>30</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="23">
+        <v>25</v>
+      </c>
+      <c r="H18" s="23">
+        <v>25</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>803</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>805</v>
+      </c>
+      <c r="F19" s="23">
+        <v>12</v>
+      </c>
+      <c r="G19" s="23">
+        <v>0</v>
+      </c>
+      <c r="H19" s="23">
+        <v>30</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19" s="24">
+        <f>H19</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G20" s="23">
+        <v>1145</v>
+      </c>
+      <c r="H20" s="23">
+        <v>25</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" s="23">
+        <v>0</v>
+      </c>
+      <c r="H21" s="23">
+        <v>30</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21" s="24">
+        <f>H21</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" s="23">
+        <v>660</v>
+      </c>
+      <c r="H22" s="23">
+        <v>20</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G23" s="23">
+        <v>800</v>
+      </c>
+      <c r="H23" s="23">
+        <v>20</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="23">
+        <v>825</v>
+      </c>
+      <c r="H24" s="23">
+        <v>25</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G25" s="23">
+        <v>0</v>
+      </c>
+      <c r="H25" s="23">
+        <v>40</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="Q25">
+        <v>1</v>
+      </c>
+      <c r="R25" s="24">
+        <f t="shared" ref="R25:R27" si="1">H25</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F26" s="23">
+        <v>5</v>
+      </c>
+      <c r="G26" s="23">
+        <v>0</v>
+      </c>
+      <c r="H26" s="23">
+        <v>30</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="Q26">
+        <v>1</v>
+      </c>
+      <c r="R26" s="24">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>490</v>
+      </c>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22" t="s">
+        <v>491</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G27" s="23">
+        <v>0</v>
+      </c>
+      <c r="H27" s="23">
+        <v>30</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="Q27">
+        <v>1</v>
+      </c>
+      <c r="R27" s="24">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F28" s="23">
+        <v>10</v>
+      </c>
+      <c r="G28" s="23">
+        <v>805</v>
+      </c>
+      <c r="H28" s="23">
+        <v>25</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="Q28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F29" s="23">
+        <v>4</v>
+      </c>
+      <c r="G29" s="23">
+        <v>0</v>
+      </c>
+      <c r="H29" s="23">
+        <v>25</v>
+      </c>
+      <c r="I29" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="Q29">
+        <v>1</v>
+      </c>
+      <c r="R29" s="24">
+        <f>H29</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G30" s="23">
+        <v>1655</v>
+      </c>
+      <c r="H30" s="23">
+        <v>25</v>
+      </c>
+      <c r="I30" s="23">
+        <f t="shared" si="0"/>
+        <v>1630</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="Q30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F31" s="23">
+        <v>10</v>
+      </c>
+      <c r="G31" s="23">
+        <v>375</v>
+      </c>
+      <c r="H31" s="23">
+        <v>25</v>
+      </c>
+      <c r="I31" s="23">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J31" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K31" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="Q31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F32" s="23">
+        <v>4</v>
+      </c>
+      <c r="G32" s="23">
+        <v>1455</v>
+      </c>
+      <c r="H32" s="23">
+        <v>25</v>
+      </c>
+      <c r="I32" s="23">
+        <f t="shared" si="0"/>
+        <v>1430</v>
+      </c>
+      <c r="J32" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K32" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L32" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="Q32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F33" s="23">
+        <v>5</v>
+      </c>
+      <c r="G33" s="23">
+        <v>0</v>
+      </c>
+      <c r="H33" s="23">
+        <v>25</v>
+      </c>
+      <c r="I33" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J33" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K33" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M33" s="22"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+      <c r="Q33">
+        <v>1</v>
+      </c>
+      <c r="R33" s="24">
+        <f>H33</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F34" s="23">
+        <v>3</v>
+      </c>
+      <c r="G34" s="23">
+        <v>715</v>
+      </c>
+      <c r="H34" s="23">
+        <v>25</v>
+      </c>
+      <c r="I34" s="23">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J34" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K34" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="Q34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F35" s="23">
+        <v>10</v>
+      </c>
+      <c r="G35" s="23">
+        <v>895</v>
+      </c>
+      <c r="H35" s="23">
+        <v>25</v>
+      </c>
+      <c r="I35" s="23">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J35" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K35" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M35" s="22"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="Q35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="F36" s="23">
+        <v>3</v>
+      </c>
+      <c r="G36" s="23">
+        <v>0</v>
+      </c>
+      <c r="H36" s="23">
+        <v>25</v>
+      </c>
+      <c r="I36" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J36" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K36" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="Q36">
+        <v>1</v>
+      </c>
+      <c r="R36" s="24">
+        <f>H36</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="22"/>
+      <c r="B37" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F37" s="23">
+        <v>4</v>
+      </c>
+      <c r="G37" s="23">
+        <v>815</v>
+      </c>
+      <c r="H37" s="23">
+        <v>25</v>
+      </c>
+      <c r="I37" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J37" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K37" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L37" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="Q37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="22"/>
+      <c r="B38" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D38" s="22" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F38" s="23">
+        <v>4</v>
+      </c>
+      <c r="G38" s="23">
+        <v>3100</v>
+      </c>
+      <c r="H38" s="23">
+        <v>35</v>
+      </c>
+      <c r="I38" s="23">
+        <f t="shared" si="0"/>
+        <v>3065</v>
+      </c>
+      <c r="J38" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K38" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M38" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N38" s="22"/>
+      <c r="O38" s="22"/>
+      <c r="Q38">
+        <v>1</v>
+      </c>
+      <c r="R38" s="24">
+        <f>H38</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="22"/>
+      <c r="B39" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="22" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D39" s="22" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>1217</v>
+      </c>
+      <c r="F39" s="23">
+        <v>5</v>
+      </c>
+      <c r="G39" s="23">
+        <v>0</v>
+      </c>
+      <c r="H39" s="23">
+        <v>25</v>
+      </c>
+      <c r="I39" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J39" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K39" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L39" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M39" s="28" t="s">
+        <v>1218</v>
+      </c>
+      <c r="N39" s="22"/>
+      <c r="O39" s="22"/>
+      <c r="Q39">
+        <v>1</v>
+      </c>
+      <c r="R39" s="24">
+        <f>H39</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G41" s="1">
+        <f t="shared" ref="G41:R41" si="2">SUBTOTAL(9,G3:G40)</f>
+        <v>21370</v>
+      </c>
+      <c r="H41" s="1">
+        <f t="shared" si="2"/>
+        <v>1030</v>
+      </c>
+      <c r="I41" s="1">
+        <f t="shared" si="2"/>
+        <v>20340</v>
+      </c>
+      <c r="J41" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L41" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N41" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O41" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P41" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q41" s="1">
+        <f t="shared" si="2"/>
+        <v>37</v>
+      </c>
+      <c r="R41" s="1">
+        <f t="shared" si="2"/>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H45" s="4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H46" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="8">
+        <f>SUM(I40:I44)</f>
+        <v>20340</v>
+      </c>
+      <c r="J46" s="8">
+        <f>Q41</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H47" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I47" s="10">
+        <f>R41</f>
+        <v>450</v>
+      </c>
+      <c r="J47" s="11"/>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H48" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I48" s="10">
+        <f>S40</f>
+        <v>0</v>
+      </c>
+      <c r="J48" s="11"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H49" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" s="10">
+        <f>T40</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="11"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H50" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I50" s="10">
+        <f>U40</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="11"/>
+    </row>
+    <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H51" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+    </row>
+    <row r="52" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H52" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
+    </row>
+    <row r="53" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H53" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I53" s="16">
+        <f>SUM(I46:I52)</f>
+        <v>20790</v>
+      </c>
+      <c r="J53" s="16">
+        <f>SUM(J46:J50)</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B56" s="36" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C56" s="36" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D56" s="36" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E56" s="37">
+        <v>5</v>
+      </c>
+      <c r="F56" s="37">
+        <v>775</v>
+      </c>
+      <c r="G56" s="37">
+        <v>0</v>
+      </c>
+      <c r="H56" s="37">
+        <f t="shared" ref="H56" si="3">F56-G56</f>
+        <v>775</v>
+      </c>
+      <c r="I56" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="J56" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="K56" s="36" t="s">
+        <v>1124</v>
+      </c>
+      <c r="L56" s="28" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P39" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P39">
+      <sortCondition ref="J2:J39"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1B4C39C-4E26-4B64-9E99-33EB9C7E67B7}">
+  <dimension ref="A1:R48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F3" s="23">
+        <v>9</v>
+      </c>
+      <c r="G3" s="23">
+        <v>35</v>
+      </c>
+      <c r="H3" s="23">
+        <v>35</v>
+      </c>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>1225</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>1226</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="G4" s="23">
+        <v>0</v>
+      </c>
+      <c r="H4" s="23">
+        <v>20</v>
+      </c>
+      <c r="I4" s="23">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+      <c r="R4" s="24">
+        <f>H4</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>1229</v>
+      </c>
+      <c r="F5" s="23">
+        <v>1</v>
+      </c>
+      <c r="G5" s="23">
+        <v>845</v>
+      </c>
+      <c r="H5" s="23">
+        <v>25</v>
+      </c>
+      <c r="I5" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>1231</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F6" s="23">
+        <v>12</v>
+      </c>
+      <c r="G6" s="23">
+        <v>0</v>
+      </c>
+      <c r="H6" s="23">
+        <v>40</v>
+      </c>
+      <c r="I6" s="23">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+      <c r="R6" s="24">
+        <f>H6</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>1235</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G7" s="23">
+        <v>805</v>
+      </c>
+      <c r="H7" s="23">
+        <v>25</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8" s="23">
+        <v>695</v>
+      </c>
+      <c r="H8" s="23">
+        <v>25</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>670</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>486</v>
+      </c>
+      <c r="F9" s="23">
+        <v>12</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0</v>
+      </c>
+      <c r="H9" s="23">
+        <v>30</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+      <c r="R9" s="24">
+        <f>H9</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" s="23">
+        <v>3600</v>
+      </c>
+      <c r="H10" s="23">
+        <v>35</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>3565</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M10" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+      <c r="R10" s="24">
+        <f>H10</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>1245</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G11" s="23">
+        <v>25</v>
+      </c>
+      <c r="H11" s="23">
+        <v>25</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="G12" s="23">
+        <v>660</v>
+      </c>
+      <c r="H12" s="23">
+        <v>20</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>1251</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G13" s="23">
+        <v>985</v>
+      </c>
+      <c r="H13" s="23">
+        <v>25</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>1254</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="23">
+        <v>1695</v>
+      </c>
+      <c r="H14" s="23">
+        <v>25</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>1670</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>1257</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="23">
+        <v>990</v>
+      </c>
+      <c r="H15" s="23">
+        <v>20</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
+        <v>970</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="23">
+        <v>540</v>
+      </c>
+      <c r="H16" s="23">
+        <v>30</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>510</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>1262</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>1263</v>
+      </c>
+      <c r="F17" s="23">
+        <v>12</v>
+      </c>
+      <c r="G17" s="23">
+        <v>1530</v>
+      </c>
+      <c r="H17" s="23">
+        <v>30</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G18" s="23">
+        <v>765</v>
+      </c>
+      <c r="H18" s="23">
+        <v>25</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22" t="s">
+        <v>1268</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G19" s="23">
+        <v>30</v>
+      </c>
+      <c r="H19" s="23">
+        <v>30</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F20" s="23">
+        <v>3</v>
+      </c>
+      <c r="G20" s="23">
+        <v>865</v>
+      </c>
+      <c r="H20" s="23">
+        <v>25</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F21" s="23">
+        <v>8</v>
+      </c>
+      <c r="G21" s="23">
+        <v>1890</v>
+      </c>
+      <c r="H21" s="23">
+        <v>30</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>1860</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22" s="23">
+        <v>815</v>
+      </c>
+      <c r="H22" s="23">
+        <v>25</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F23" s="23">
+        <v>4</v>
+      </c>
+      <c r="G23" s="23">
+        <v>895</v>
+      </c>
+      <c r="H23" s="23">
+        <v>25</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>1284</v>
+      </c>
+      <c r="F24" s="23">
+        <v>8</v>
+      </c>
+      <c r="G24" s="23">
+        <v>0</v>
+      </c>
+      <c r="H24" s="23">
+        <v>30</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22">
+        <v>1</v>
+      </c>
+      <c r="R24" s="24">
+        <f>H24</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G25" s="23">
+        <v>1765</v>
+      </c>
+      <c r="H25" s="23">
+        <v>25</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="0"/>
+        <v>1740</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>1288</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="G26" s="23">
+        <v>815</v>
+      </c>
+      <c r="H26" s="23">
+        <v>35</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>277</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="F27" s="23">
+        <v>6</v>
+      </c>
+      <c r="G27" s="23">
+        <v>805</v>
+      </c>
+      <c r="H27" s="23">
+        <v>25</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>1292</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G28" s="23">
+        <v>690</v>
+      </c>
+      <c r="H28" s="23">
+        <v>30</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>1295</v>
+      </c>
+      <c r="F29" s="23">
+        <v>7</v>
+      </c>
+      <c r="G29" s="23">
+        <v>1420</v>
+      </c>
+      <c r="H29" s="23">
+        <v>30</v>
+      </c>
+      <c r="I29" s="23">
+        <f t="shared" si="0"/>
+        <v>1390</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>1298</v>
+      </c>
+      <c r="F30" s="23">
+        <v>6</v>
+      </c>
+      <c r="G30" s="23">
+        <v>0</v>
+      </c>
+      <c r="H30" s="23">
+        <v>25</v>
+      </c>
+      <c r="I30" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22">
+        <v>1</v>
+      </c>
+      <c r="R30" s="24">
+        <f t="shared" ref="R30:R31" si="1">H30</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>1301</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G31" s="23">
+        <v>0</v>
+      </c>
+      <c r="H31" s="23">
+        <v>30</v>
+      </c>
+      <c r="I31" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J31" s="22" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K31" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22">
+        <v>1</v>
+      </c>
+      <c r="R31" s="24">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>1303</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F32" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G32" s="23">
+        <v>1390</v>
+      </c>
+      <c r="H32" s="23">
+        <v>30</v>
+      </c>
+      <c r="I32" s="23">
+        <f t="shared" si="0"/>
+        <v>1360</v>
+      </c>
+      <c r="J32" s="22" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K32" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L32" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>1307</v>
+      </c>
+      <c r="F33" s="23">
+        <v>7</v>
+      </c>
+      <c r="G33" s="23">
+        <v>1630</v>
+      </c>
+      <c r="H33" s="23">
+        <v>30</v>
+      </c>
+      <c r="I33" s="23">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+      <c r="J33" s="22" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K33" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M33" s="22"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>1310</v>
+      </c>
+      <c r="F34" s="23">
+        <v>10</v>
+      </c>
+      <c r="G34" s="23">
+        <v>815</v>
+      </c>
+      <c r="H34" s="23">
+        <v>25</v>
+      </c>
+      <c r="I34" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J34" s="22" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K34" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G36" s="1">
+        <f t="shared" ref="G36:R36" si="2">SUBTOTAL(9,G3:G35)</f>
+        <v>26995</v>
+      </c>
+      <c r="H36" s="1">
+        <f t="shared" si="2"/>
+        <v>885</v>
+      </c>
+      <c r="I36" s="1">
+        <f t="shared" si="2"/>
+        <v>26110</v>
+      </c>
+      <c r="J36" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M36" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N36" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O36" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P36" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="1">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="R36" s="1">
+        <f t="shared" si="2"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H40" s="4" t="s">
+        <v>1119</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H41" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="8">
+        <f>SUM(I35:I39)</f>
+        <v>26110</v>
+      </c>
+      <c r="J41" s="8">
+        <f>Q36</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H42" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="10">
+        <f>R36</f>
+        <v>210</v>
+      </c>
+      <c r="J42" s="11"/>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H43" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" s="10">
+        <f>S35</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="11"/>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H44" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" s="10">
+        <f>T35</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="11"/>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H45" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I45" s="10">
+        <f>U35</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="11"/>
+    </row>
+    <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H46" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
+    </row>
+    <row r="47" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H47" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
+    </row>
+    <row r="48" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H48" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I48" s="16">
+        <f>SUM(I41:I47)</f>
+        <v>26320</v>
+      </c>
+      <c r="J48" s="16">
+        <f>SUM(J41:J45)</f>
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P34" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P34">
+      <sortCondition ref="J2:J34"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{942E8E49-7BF0-44F1-B145-908507FDEC5B}">
+  <dimension ref="A1:R59"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="9.140625" style="1"/>
+    <col min="10" max="10" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>1315</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="23">
+        <v>0</v>
+      </c>
+      <c r="H3" s="23">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I39" si="0">G3-H3</f>
+        <v>-30</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>1316</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M3" s="28" t="s">
+        <v>1318</v>
+      </c>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+      <c r="R3" s="24">
+        <f>H3</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>1321</v>
+      </c>
+      <c r="F4" s="23">
+        <v>8</v>
+      </c>
+      <c r="G4" s="23">
+        <v>0</v>
+      </c>
+      <c r="H4" s="23">
+        <v>25</v>
+      </c>
+      <c r="I4" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>1316</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+      <c r="R4" s="24">
+        <f>H4</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>1324</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>1325</v>
+      </c>
+      <c r="G5" s="23">
+        <v>865</v>
+      </c>
+      <c r="H5" s="23">
+        <v>35</v>
+      </c>
+      <c r="I5" s="23">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>1316</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>1327</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>1328</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G6" s="23">
+        <v>1135</v>
+      </c>
+      <c r="H6" s="23">
+        <v>35</v>
+      </c>
+      <c r="I6" s="23">
+        <f t="shared" si="0"/>
+        <v>1100</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>1316</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M6" s="28" t="s">
+        <v>1049</v>
+      </c>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+      <c r="R6" s="24">
+        <f>H6</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>1328</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G7" s="23">
+        <v>0</v>
+      </c>
+      <c r="H7" s="23">
+        <v>0</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>1316</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M7" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+      <c r="R7" s="24">
+        <f>H7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>1333</v>
+      </c>
+      <c r="F8" s="23">
+        <v>11</v>
+      </c>
+      <c r="G8" s="23">
+        <v>1135</v>
+      </c>
+      <c r="H8" s="23">
+        <v>25</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>1110</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>1316</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F9" s="23">
+        <v>7</v>
+      </c>
+      <c r="G9" s="23">
+        <v>470</v>
+      </c>
+      <c r="H9" s="23">
+        <v>30</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>1316</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="23">
+        <v>985</v>
+      </c>
+      <c r="H10" s="23">
+        <v>25</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>1316</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M10" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>1341</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="23">
+        <v>850</v>
+      </c>
+      <c r="H11" s="23">
+        <v>0</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>1316</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M11" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>1343</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>1344</v>
+      </c>
+      <c r="F12" s="23">
+        <v>8</v>
+      </c>
+      <c r="G12" s="23">
+        <v>0</v>
+      </c>
+      <c r="H12" s="23">
+        <v>30</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>1316</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M12" s="28" t="s">
+        <v>1345</v>
+      </c>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+      <c r="R12" s="24">
+        <f>H12</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>1347</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F13" s="23">
+        <v>7</v>
+      </c>
+      <c r="G13" s="23">
+        <v>850</v>
+      </c>
+      <c r="H13" s="23">
+        <v>30</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>1316</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F14" s="23">
+        <v>7</v>
+      </c>
+      <c r="G14" s="23">
+        <v>820</v>
+      </c>
+      <c r="H14" s="23">
+        <v>30</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>1316</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>1352</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F15" s="23">
+        <v>11</v>
+      </c>
+      <c r="G15" s="23">
+        <v>1505</v>
+      </c>
+      <c r="H15" s="23">
+        <v>25</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
+        <v>1480</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>1316</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>730</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>1355</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>1356</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="23">
+        <v>725</v>
+      </c>
+      <c r="H16" s="23">
+        <v>25</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>1316</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="23">
+        <v>715</v>
+      </c>
+      <c r="H17" s="23">
+        <v>25</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>884</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>1360</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="23">
+        <v>0</v>
+      </c>
+      <c r="H18" s="23">
+        <v>25</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+      <c r="R18" s="24">
+        <f>H18</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>886</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="23">
+        <v>380</v>
+      </c>
+      <c r="H19" s="23">
+        <v>30</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" s="23">
+        <v>810</v>
+      </c>
+      <c r="H20" s="23">
+        <v>20</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" s="23">
+        <v>820</v>
+      </c>
+      <c r="H21" s="23">
+        <v>30</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F22" s="23">
+        <v>2</v>
+      </c>
+      <c r="G22" s="23">
+        <v>990</v>
+      </c>
+      <c r="H22" s="23">
+        <v>30</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G23" s="23">
+        <v>1770</v>
+      </c>
+      <c r="H23" s="23">
+        <v>20</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="0"/>
+        <v>1750</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="F24" s="23">
+        <v>12</v>
+      </c>
+      <c r="G24" s="23">
+        <v>0</v>
+      </c>
+      <c r="H24" s="23">
+        <v>30</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22">
+        <v>1</v>
+      </c>
+      <c r="R24" s="24">
+        <f>H24</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>1376</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G25" s="23">
+        <v>880</v>
+      </c>
+      <c r="H25" s="23">
+        <v>30</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F26" s="23">
+        <v>12</v>
+      </c>
+      <c r="G26" s="23">
+        <v>880</v>
+      </c>
+      <c r="H26" s="23">
+        <v>30</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>1382</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>1383</v>
+      </c>
+      <c r="F27" s="23">
+        <v>2</v>
+      </c>
+      <c r="G27" s="23">
+        <v>820</v>
+      </c>
+      <c r="H27" s="23">
+        <v>30</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22" t="s">
+        <v>1385</v>
+      </c>
+      <c r="F28" s="23">
+        <v>12</v>
+      </c>
+      <c r="G28" s="23">
+        <v>0</v>
+      </c>
+      <c r="H28" s="23">
+        <v>35</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22">
+        <v>1</v>
+      </c>
+      <c r="R28" s="24">
+        <f>H28</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G29" s="23">
+        <v>865</v>
+      </c>
+      <c r="H29" s="23">
+        <v>35</v>
+      </c>
+      <c r="I29" s="23">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>351</v>
+      </c>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G30" s="23">
+        <v>30</v>
+      </c>
+      <c r="H30" s="23">
+        <v>30</v>
+      </c>
+      <c r="I30" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G31" s="23">
+        <v>860</v>
+      </c>
+      <c r="H31" s="23">
+        <v>30</v>
+      </c>
+      <c r="I31" s="23">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J31" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K31" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>1388</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>1389</v>
+      </c>
+      <c r="F32" s="23">
+        <v>1</v>
+      </c>
+      <c r="G32" s="23">
+        <v>0</v>
+      </c>
+      <c r="H32" s="23">
+        <v>25</v>
+      </c>
+      <c r="I32" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J32" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K32" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L32" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M32" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22">
+        <v>1</v>
+      </c>
+      <c r="R32" s="24">
+        <f t="shared" ref="R32:R33" si="1">H32</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>1390</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F33" s="23">
+        <v>1</v>
+      </c>
+      <c r="G33" s="23">
+        <v>0</v>
+      </c>
+      <c r="H33" s="23">
+        <v>0</v>
+      </c>
+      <c r="I33" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K33" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M33" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22">
+        <v>1</v>
+      </c>
+      <c r="R33" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>1393</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>1394</v>
+      </c>
+      <c r="F34" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="G34" s="23">
+        <v>780</v>
+      </c>
+      <c r="H34" s="23">
+        <v>20</v>
+      </c>
+      <c r="I34" s="23">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J34" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K34" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>1397</v>
+      </c>
+      <c r="F35" s="23">
+        <v>1</v>
+      </c>
+      <c r="G35" s="23">
+        <v>755</v>
+      </c>
+      <c r="H35" s="23">
+        <v>25</v>
+      </c>
+      <c r="I35" s="23">
+        <f t="shared" si="0"/>
+        <v>730</v>
+      </c>
+      <c r="J35" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K35" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M35" s="22"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>1400</v>
+      </c>
+      <c r="F36" s="23">
+        <v>4</v>
+      </c>
+      <c r="G36" s="23">
+        <v>985</v>
+      </c>
+      <c r="H36" s="23">
+        <v>25</v>
+      </c>
+      <c r="I36" s="23">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J36" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K36" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="22"/>
+      <c r="B37" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>1402</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>1403</v>
+      </c>
+      <c r="F37" s="23">
+        <v>1</v>
+      </c>
+      <c r="G37" s="23">
+        <v>925</v>
+      </c>
+      <c r="H37" s="23">
+        <v>25</v>
+      </c>
+      <c r="I37" s="23">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="J37" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K37" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L37" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="22"/>
+      <c r="Q37" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>494</v>
+      </c>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22" t="s">
+        <v>495</v>
+      </c>
+      <c r="F38" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="G38" s="23">
+        <v>25</v>
+      </c>
+      <c r="H38" s="23">
+        <v>25</v>
+      </c>
+      <c r="I38" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K38" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M38" s="22"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="22"/>
+      <c r="P38" s="22"/>
+      <c r="Q38" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="22" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F39" s="23">
+        <v>5</v>
+      </c>
+      <c r="G39" s="23">
+        <v>0</v>
+      </c>
+      <c r="H39" s="23">
+        <v>30</v>
+      </c>
+      <c r="I39" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J39" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K39" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L39" s="22" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M39" s="22"/>
+      <c r="N39" s="22"/>
+      <c r="O39" s="22"/>
+      <c r="P39" s="22"/>
+      <c r="Q39" s="22">
+        <v>1</v>
+      </c>
+      <c r="R39" s="24">
+        <f>H39</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G41" s="1">
+        <f>SUBTOTAL(9,G3:G40)</f>
+        <v>22630</v>
+      </c>
+      <c r="H41" s="1">
+        <f>SUBTOTAL(9,H3:H40)</f>
+        <v>950</v>
+      </c>
+      <c r="I41" s="1">
+        <f>SUBTOTAL(9,I3:I40)</f>
+        <v>21680</v>
+      </c>
+      <c r="J41" s="1">
+        <f>SUBTOTAL(9,J3:J40)</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="1">
+        <f>SUBTOTAL(9,K3:K40)</f>
+        <v>0</v>
+      </c>
+      <c r="L41" s="1">
+        <f>SUBTOTAL(9,L3:L40)</f>
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <f>SUBTOTAL(9,M3:M40)</f>
+        <v>0</v>
+      </c>
+      <c r="N41" s="1">
+        <f>SUBTOTAL(9,N3:N40)</f>
+        <v>0</v>
+      </c>
+      <c r="O41" s="1">
+        <f>SUBTOTAL(9,O3:O40)</f>
+        <v>0</v>
+      </c>
+      <c r="P41" s="1">
+        <f>SUBTOTAL(9,P3:P40)</f>
+        <v>0</v>
+      </c>
+      <c r="Q41" s="1">
+        <f>SUBTOTAL(9,Q3:Q40)</f>
+        <v>37</v>
+      </c>
+      <c r="R41" s="1">
+        <f>SUBTOTAL(9,R3:R40)</f>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I42" s="1">
+        <v>-870</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I43" s="1">
+        <v>-2010</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H45" s="4" t="s">
+        <v>1219</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H46" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="8">
+        <f>SUM(I40:I44)</f>
+        <v>18800</v>
+      </c>
+      <c r="J46" s="8">
+        <f>Q41</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H47" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I47" s="10">
+        <f>R41</f>
+        <v>265</v>
+      </c>
+      <c r="J47" s="11"/>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H48" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I48" s="10">
+        <f>S40</f>
+        <v>0</v>
+      </c>
+      <c r="J48" s="11"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H49" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" s="10">
+        <f>T40</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="11"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H50" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I50" s="10">
+        <f>U40</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="11"/>
+    </row>
+    <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H51" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+    </row>
+    <row r="52" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H52" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
+    </row>
+    <row r="53" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H53" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I53" s="16">
+        <f>SUM(I46:I52)</f>
+        <v>19065</v>
+      </c>
+      <c r="J53" s="16">
+        <f>SUM(J46:J50)</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B56" s="36" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C56" s="36" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D56" s="36" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E56" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F56" s="37">
+        <v>4210</v>
+      </c>
+      <c r="G56" s="37">
+        <v>0</v>
+      </c>
+      <c r="H56" s="37">
+        <f>F56-G56</f>
+        <v>4210</v>
+      </c>
+      <c r="I56" s="36" t="s">
+        <v>1316</v>
+      </c>
+      <c r="J56" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="K56" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="L56" s="28" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B57" s="36" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C57" s="36" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D57" s="36" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E57" s="37">
+        <v>8</v>
+      </c>
+      <c r="F57" s="37">
+        <v>1820</v>
+      </c>
+      <c r="G57" s="37">
+        <v>0</v>
+      </c>
+      <c r="H57" s="37">
+        <f>F57-G57</f>
+        <v>1820</v>
+      </c>
+      <c r="I57" s="36" t="s">
+        <v>1316</v>
+      </c>
+      <c r="J57" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="K57" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="L57" s="28" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B59" s="36" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C59" s="36" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D59" s="36" t="s">
+        <v>1407</v>
+      </c>
+      <c r="E59" s="37">
+        <v>7</v>
+      </c>
+      <c r="F59" s="37">
+        <v>870</v>
+      </c>
+      <c r="G59" s="37">
+        <v>0</v>
+      </c>
+      <c r="H59" s="37">
+        <f>F59-G59</f>
+        <v>870</v>
+      </c>
+      <c r="I59" s="36" t="s">
+        <v>623</v>
+      </c>
+      <c r="J59" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="K59" s="36" t="s">
+        <v>1408</v>
+      </c>
+      <c r="L59" s="28" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P39" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P39">
+      <sortCondition ref="J2:J39"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47545709-E28D-4489-882A-82DB7E97D411}">
   <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6422,10 +14939,10 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>270</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>961</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -7528,57 +16045,57 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G58" s="1">
-        <f t="shared" ref="G58:R58" si="0">SUBTOTAL(9,G3:G57)</f>
+        <f>SUBTOTAL(9,G3:G57)</f>
         <v>0</v>
       </c>
       <c r="H58" s="1">
-        <f t="shared" si="0"/>
+        <f>SUBTOTAL(9,H3:H57)</f>
         <v>0</v>
       </c>
       <c r="I58" s="1">
-        <f t="shared" si="0"/>
+        <f>SUBTOTAL(9,I3:I57)</f>
         <v>0</v>
       </c>
       <c r="J58" s="1">
-        <f t="shared" si="0"/>
+        <f>SUBTOTAL(9,J3:J57)</f>
         <v>0</v>
       </c>
       <c r="K58" s="1">
-        <f t="shared" si="0"/>
+        <f>SUBTOTAL(9,K3:K57)</f>
         <v>0</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="0"/>
+        <f>SUBTOTAL(9,L3:L57)</f>
         <v>0</v>
       </c>
       <c r="M58" s="1">
-        <f t="shared" si="0"/>
+        <f>SUBTOTAL(9,M3:M57)</f>
         <v>0</v>
       </c>
       <c r="N58" s="1">
-        <f t="shared" si="0"/>
+        <f>SUBTOTAL(9,N3:N57)</f>
         <v>0</v>
       </c>
       <c r="O58" s="1">
-        <f t="shared" si="0"/>
+        <f>SUBTOTAL(9,O3:O57)</f>
         <v>0</v>
       </c>
       <c r="P58" s="1">
-        <f t="shared" si="0"/>
+        <f>SUBTOTAL(9,P3:P57)</f>
         <v>0</v>
       </c>
       <c r="Q58" s="1">
-        <f t="shared" si="0"/>
+        <f>SUBTOTAL(9,Q3:Q57)</f>
         <v>0</v>
       </c>
       <c r="R58" s="1">
-        <f t="shared" si="0"/>
+        <f>SUBTOTAL(9,R3:R57)</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H62" s="4" t="s">
-        <v>960</v>
+        <v>1312</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>15</v>

--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68516E69-2F31-4390-BB95-10FF87B91BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F64A88D-FAF3-4C13-83DC-903BC14214C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-5" sheetId="3" r:id="rId1"/>
@@ -27,6 +27,8 @@
     <sheet name="15-5" sheetId="14" r:id="rId12"/>
     <sheet name="16-5" sheetId="15" r:id="rId13"/>
     <sheet name="18-5" sheetId="16" r:id="rId14"/>
+    <sheet name="19-5" sheetId="17" r:id="rId15"/>
+    <sheet name="20-5" sheetId="18" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'11-5'!$A$2:$P$58</definedName>
@@ -36,7 +38,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-5'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'15-5'!$A$2:$P$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'16-5'!$A$2:$P$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'18-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'18-5'!$A$2:$P$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'19-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'20-5'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'4-5'!$A$2:$P$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'5-5'!$A$2:$P$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'6-5'!$A$2:$P$34</definedName>
@@ -65,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4090" uniqueCount="1411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4444" uniqueCount="1507">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -4298,6 +4302,294 @@
   </si>
   <si>
     <t>đơn trả 18.5</t>
+  </si>
+  <si>
+    <t>NGAY 19-5</t>
+  </si>
+  <si>
+    <t>T3.19.5.2026</t>
+  </si>
+  <si>
+    <t>Quỳnh Nga</t>
+  </si>
+  <si>
+    <t>HD021747</t>
+  </si>
+  <si>
+    <t>56/7 đường Tân Hoà 2 phường Hiệp Phú</t>
+  </si>
+  <si>
+    <t>18-05-2026</t>
+  </si>
+  <si>
+    <t>Hợp Vũ</t>
+  </si>
+  <si>
+    <t>HD021640</t>
+  </si>
+  <si>
+    <t>2A Phan Chu Trinh, P Hiệp Phú</t>
+  </si>
+  <si>
+    <t>AT 18-05</t>
+  </si>
+  <si>
+    <t>HD021621</t>
+  </si>
+  <si>
+    <t>Heng Roza (EV38382)</t>
+  </si>
+  <si>
+    <t>HD020691</t>
+  </si>
+  <si>
+    <t>HD021855</t>
+  </si>
+  <si>
+    <t>Ngọc Hồng Thương</t>
+  </si>
+  <si>
+    <t>HD021553</t>
+  </si>
+  <si>
+    <t>51 đường 81 tân quy</t>
+  </si>
+  <si>
+    <t>PIMVIPA 3883</t>
+  </si>
+  <si>
+    <t>HD021837</t>
+  </si>
+  <si>
+    <t>Gia Tuệ</t>
+  </si>
+  <si>
+    <t>HD021808</t>
+  </si>
+  <si>
+    <t>42/32 trần đại nghĩa, tân tạo a</t>
+  </si>
+  <si>
+    <t>HSM RIDA CHUON</t>
+  </si>
+  <si>
+    <t>HD021615</t>
+  </si>
+  <si>
+    <t>177c đường số 1 bình hưng hòa b</t>
+  </si>
+  <si>
+    <t>Nga Còi</t>
+  </si>
+  <si>
+    <t>Sửa xe Anh Sơn, liên ấp 2,3,4 Vĩnh Lộc A</t>
+  </si>
+  <si>
+    <t>HD021418</t>
+  </si>
+  <si>
+    <t>Central premium lock A</t>
+  </si>
+  <si>
+    <t>Ái Nương</t>
+  </si>
+  <si>
+    <t>HD021666</t>
+  </si>
+  <si>
+    <t>154/33 au dương lân phường 3</t>
+  </si>
+  <si>
+    <t>chị Bích Huyền</t>
+  </si>
+  <si>
+    <t>HD021868</t>
+  </si>
+  <si>
+    <t>Số 4 đường số 22 kdc bình hưng</t>
+  </si>
+  <si>
+    <t>Chị Bích Huyền</t>
+  </si>
+  <si>
+    <t>HD021775</t>
+  </si>
+  <si>
+    <t>số 4 đường số 22 kdc bình hưng</t>
+  </si>
+  <si>
+    <t>Phuong Nguyen</t>
+  </si>
+  <si>
+    <t>HD021530</t>
+  </si>
+  <si>
+    <t>Eco green toà I, HR30710, 39 Nguyễn Văn linh</t>
+  </si>
+  <si>
+    <t>Ngann Lee</t>
+  </si>
+  <si>
+    <t>HD021534</t>
+  </si>
+  <si>
+    <t>360 lạc long quân phường 5 (phường hòa bình)</t>
+  </si>
+  <si>
+    <t>NIKI</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Mỹ Phúc</t>
+  </si>
+  <si>
+    <t>HD021574</t>
+  </si>
+  <si>
+    <t>nha The Sun Avenue (tòa S5) 28 Mai Chí Thọ, An Phú</t>
+  </si>
+  <si>
+    <t>HD021424</t>
+  </si>
+  <si>
+    <t>Hoàng Trâm Anh</t>
+  </si>
+  <si>
+    <t>HD021810</t>
+  </si>
+  <si>
+    <t>11 Nguyễn Bá Huân phường thảo điền</t>
+  </si>
+  <si>
+    <t>Trúc Nguyễn</t>
+  </si>
+  <si>
+    <t>HD021871</t>
+  </si>
+  <si>
+    <t>38 Đường 6 Linh Chiếu</t>
+  </si>
+  <si>
+    <t>như fb Đặng Tố Trinh</t>
+  </si>
+  <si>
+    <t>HD021866</t>
+  </si>
+  <si>
+    <t>Đối diện 110/42 đường số 5 phường 17</t>
+  </si>
+  <si>
+    <t>Nguyễn Thảo Uyên</t>
+  </si>
+  <si>
+    <t>HD021746</t>
+  </si>
+  <si>
+    <t>15/32/56 võ duy ninh p22</t>
+  </si>
+  <si>
+    <t>HD021539</t>
+  </si>
+  <si>
+    <t>129/34 Nguyễn Văn Công, P. 3</t>
+  </si>
+  <si>
+    <t>MC Phương Nhi</t>
+  </si>
+  <si>
+    <t>HD021829</t>
+  </si>
+  <si>
+    <t>99 Trần Bá Giao An Nhơn</t>
+  </si>
+  <si>
+    <t>Ngân Ngân</t>
+  </si>
+  <si>
+    <t>HD021620</t>
+  </si>
+  <si>
+    <t>74B/148 thống nhất p15</t>
+  </si>
+  <si>
+    <t>Vân Thuỳ</t>
+  </si>
+  <si>
+    <t>HD021612</t>
+  </si>
+  <si>
+    <t>497/73/5 phan văn trị Phường 5</t>
+  </si>
+  <si>
+    <t>SU ANH</t>
+  </si>
+  <si>
+    <t>Hong Nho + NGUYỄN THỊ DIỄM CHI</t>
+  </si>
+  <si>
+    <t>29/7 Yên Thế, Phường 2</t>
+  </si>
+  <si>
+    <t>Gia Huy nhận của ELIS NGUYỄN ( singapore)</t>
+  </si>
+  <si>
+    <t>HD021334</t>
+  </si>
+  <si>
+    <t>2/11 Đường Thiên Phước, Phường 9</t>
+  </si>
+  <si>
+    <t>Ngọc - fb Naila Unner</t>
+  </si>
+  <si>
+    <t>HD021827</t>
+  </si>
+  <si>
+    <t>Rivergate</t>
+  </si>
+  <si>
+    <t>HD021876</t>
+  </si>
+  <si>
+    <t>Ngọc</t>
+  </si>
+  <si>
+    <t>HD021842</t>
+  </si>
+  <si>
+    <t>222 pasteur, phường xuân hòa</t>
+  </si>
+  <si>
+    <t>Thinh HB</t>
+  </si>
+  <si>
+    <t>HD021608</t>
+  </si>
+  <si>
+    <t>17 cô giang, phường cầu ông lãnh</t>
+  </si>
+  <si>
+    <t>Trân Nguyễn</t>
+  </si>
+  <si>
+    <t>HD021600</t>
+  </si>
+  <si>
+    <t>177 Nguyễn Đình Chiểu, p. Xuân Hòa</t>
+  </si>
+  <si>
+    <t>Tô Tô</t>
+  </si>
+  <si>
+    <t>HD021603</t>
+  </si>
+  <si>
+    <t>46 Lê Thị Riêng, phường Bến Thành</t>
+  </si>
+  <si>
+    <t>T4.20.5.2026</t>
+  </si>
+  <si>
+    <t>NGAY 20-5</t>
   </si>
 </sst>
 </file>
@@ -14628,51 +14920,51 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G41" s="1">
-        <f>SUBTOTAL(9,G3:G40)</f>
+        <f t="shared" ref="G41:R41" si="2">SUBTOTAL(9,G3:G40)</f>
         <v>22630</v>
       </c>
       <c r="H41" s="1">
-        <f>SUBTOTAL(9,H3:H40)</f>
+        <f t="shared" si="2"/>
         <v>950</v>
       </c>
       <c r="I41" s="1">
-        <f>SUBTOTAL(9,I3:I40)</f>
+        <f t="shared" si="2"/>
         <v>21680</v>
       </c>
       <c r="J41" s="1">
-        <f>SUBTOTAL(9,J3:J40)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K41" s="1">
-        <f>SUBTOTAL(9,K3:K40)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L41" s="1">
-        <f>SUBTOTAL(9,L3:L40)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M41" s="1">
-        <f>SUBTOTAL(9,M3:M40)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N41" s="1">
-        <f>SUBTOTAL(9,N3:N40)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O41" s="1">
-        <f>SUBTOTAL(9,O3:O40)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P41" s="1">
-        <f>SUBTOTAL(9,P3:P40)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q41" s="1">
-        <f>SUBTOTAL(9,Q3:Q40)</f>
+        <f t="shared" si="2"/>
         <v>37</v>
       </c>
       <c r="R41" s="1">
-        <f>SUBTOTAL(9,R3:R40)</f>
+        <f t="shared" si="2"/>
         <v>265</v>
       </c>
     </row>
@@ -14923,6 +15215,2011 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47545709-E28D-4489-882A-82DB7E97D411}">
+  <dimension ref="A1:R55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="43.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>1414</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F3" s="23">
+        <v>9</v>
+      </c>
+      <c r="G3" s="23">
+        <v>850</v>
+      </c>
+      <c r="H3" s="23">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I41" si="0">G3-H3</f>
+        <v>820</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>1418</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>1419</v>
+      </c>
+      <c r="F4" s="23">
+        <v>9</v>
+      </c>
+      <c r="G4" s="23">
+        <v>600</v>
+      </c>
+      <c r="H4" s="23">
+        <v>30</v>
+      </c>
+      <c r="I4" s="23">
+        <f t="shared" si="0"/>
+        <v>570</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>864</v>
+      </c>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22" t="s">
+        <v>626</v>
+      </c>
+      <c r="F5" s="23">
+        <v>6</v>
+      </c>
+      <c r="G5" s="23">
+        <v>0</v>
+      </c>
+      <c r="H5" s="23">
+        <v>30</v>
+      </c>
+      <c r="I5" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>1420</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+      <c r="R5" s="24">
+        <f>H5</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="25"/>
+      <c r="B6" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>1344</v>
+      </c>
+      <c r="F6" s="26">
+        <v>8</v>
+      </c>
+      <c r="G6" s="26">
+        <v>380</v>
+      </c>
+      <c r="H6" s="26">
+        <v>30</v>
+      </c>
+      <c r="I6" s="26">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>1420</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="25" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M6" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>736</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="23">
+        <v>0</v>
+      </c>
+      <c r="H7" s="23">
+        <v>30</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>1420</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+      <c r="R7" s="24">
+        <f t="shared" ref="R7:R12" si="1">H7</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>1424</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="23">
+        <v>0</v>
+      </c>
+      <c r="H8" s="23">
+        <v>30</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>1420</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+      <c r="R8" s="24">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>1427</v>
+      </c>
+      <c r="F9" s="23">
+        <v>7</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0</v>
+      </c>
+      <c r="H9" s="23">
+        <v>30</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>1420</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+      <c r="R9" s="24">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>626</v>
+      </c>
+      <c r="F10" s="23">
+        <v>6</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0</v>
+      </c>
+      <c r="H10" s="23">
+        <v>25</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>1420</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+      <c r="R10" s="24">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>1432</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="23">
+        <v>0</v>
+      </c>
+      <c r="H11" s="23">
+        <v>30</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>1420</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+      <c r="R11" s="24">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>1434</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>1435</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="23">
+        <v>0</v>
+      </c>
+      <c r="H12" s="23">
+        <v>30</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>1420</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+      <c r="R12" s="24">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="25"/>
+      <c r="B13" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>1436</v>
+      </c>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="G13" s="26">
+        <v>0</v>
+      </c>
+      <c r="H13" s="26">
+        <v>35</v>
+      </c>
+      <c r="I13" s="26">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>1420</v>
+      </c>
+      <c r="K13" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="25" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M13" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="25">
+        <v>1</v>
+      </c>
+      <c r="R13" s="31">
+        <f>H13</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>1439</v>
+      </c>
+      <c r="F14" s="23">
+        <v>8</v>
+      </c>
+      <c r="G14" s="23">
+        <v>980</v>
+      </c>
+      <c r="H14" s="23">
+        <v>30</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>1420</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>1441</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>1442</v>
+      </c>
+      <c r="F15" s="23">
+        <v>8</v>
+      </c>
+      <c r="G15" s="23">
+        <v>380</v>
+      </c>
+      <c r="H15" s="23">
+        <v>30</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>1420</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>1444</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>1445</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G16" s="23">
+        <v>695</v>
+      </c>
+      <c r="H16" s="23">
+        <v>35</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>1420</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M16" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>1447</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G17" s="23">
+        <v>820</v>
+      </c>
+      <c r="H17" s="23">
+        <v>0</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>1420</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M17" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>1451</v>
+      </c>
+      <c r="F18" s="23">
+        <v>7</v>
+      </c>
+      <c r="G18" s="23">
+        <v>980</v>
+      </c>
+      <c r="H18" s="23">
+        <v>30</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>1420</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F19" s="23">
+        <v>11</v>
+      </c>
+      <c r="G19" s="23">
+        <v>985</v>
+      </c>
+      <c r="H19" s="23">
+        <v>25</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>1420</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="F20" s="23">
+        <v>12</v>
+      </c>
+      <c r="G20" s="23">
+        <v>0</v>
+      </c>
+      <c r="H20" s="23">
+        <v>60</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>-60</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+      <c r="R20" s="24">
+        <f>H20</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>351</v>
+      </c>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="23">
+        <v>30</v>
+      </c>
+      <c r="H21" s="23">
+        <v>30</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22" t="s">
+        <v>1385</v>
+      </c>
+      <c r="F22" s="23">
+        <v>12</v>
+      </c>
+      <c r="G22" s="23">
+        <v>595</v>
+      </c>
+      <c r="H22" s="23">
+        <v>35</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="0"/>
+        <v>560</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>1458</v>
+      </c>
+      <c r="F23" s="23">
+        <v>2</v>
+      </c>
+      <c r="G23" s="23">
+        <v>890</v>
+      </c>
+      <c r="H23" s="23">
+        <v>30</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>993</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>1459</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>995</v>
+      </c>
+      <c r="F24" s="23">
+        <v>2</v>
+      </c>
+      <c r="G24" s="23">
+        <v>380</v>
+      </c>
+      <c r="H24" s="23">
+        <v>30</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>1462</v>
+      </c>
+      <c r="F25" s="23">
+        <v>2</v>
+      </c>
+      <c r="G25" s="23">
+        <v>1020</v>
+      </c>
+      <c r="H25" s="23">
+        <v>30</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>1464</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G26" s="23">
+        <v>0</v>
+      </c>
+      <c r="H26" s="23">
+        <v>30</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+      <c r="R26" s="24">
+        <f>H26</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="25"/>
+      <c r="B27" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>1466</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>1467</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" s="26">
+        <v>295</v>
+      </c>
+      <c r="H27" s="26">
+        <v>25</v>
+      </c>
+      <c r="I27" s="26">
+        <f t="shared" si="0"/>
+        <v>270</v>
+      </c>
+      <c r="J27" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="K27" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="25" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M27" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N27" s="25"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G28" s="23">
+        <v>1190</v>
+      </c>
+      <c r="H28" s="23">
+        <v>20</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="0"/>
+        <v>1170</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>469</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>1472</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G29" s="23">
+        <v>0</v>
+      </c>
+      <c r="H29" s="23">
+        <v>25</v>
+      </c>
+      <c r="I29" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22">
+        <v>1</v>
+      </c>
+      <c r="R29" s="24">
+        <f>H29</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G30" s="23">
+        <v>885</v>
+      </c>
+      <c r="H30" s="23">
+        <v>25</v>
+      </c>
+      <c r="I30" s="23">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G31" s="23">
+        <v>915</v>
+      </c>
+      <c r="H31" s="23">
+        <v>25</v>
+      </c>
+      <c r="I31" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J31" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K31" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F32" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G32" s="23">
+        <v>815</v>
+      </c>
+      <c r="H32" s="23">
+        <v>25</v>
+      </c>
+      <c r="I32" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J32" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K32" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L32" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="F33" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G33" s="23">
+        <v>0</v>
+      </c>
+      <c r="H33" s="23">
+        <v>30</v>
+      </c>
+      <c r="I33" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J33" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K33" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M33" s="22"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22">
+        <v>1</v>
+      </c>
+      <c r="R33" s="24">
+        <f>H33</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F34" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G34" s="23">
+        <v>30</v>
+      </c>
+      <c r="H34" s="23">
+        <v>30</v>
+      </c>
+      <c r="I34" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K34" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>1486</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>1487</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F35" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G35" s="23">
+        <v>0</v>
+      </c>
+      <c r="H35" s="23">
+        <v>25</v>
+      </c>
+      <c r="I35" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J35" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K35" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M35" s="22"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22">
+        <v>1</v>
+      </c>
+      <c r="R35" s="24">
+        <f>H35</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F36" s="23">
+        <v>4</v>
+      </c>
+      <c r="G36" s="23">
+        <v>1075</v>
+      </c>
+      <c r="H36" s="23">
+        <v>25</v>
+      </c>
+      <c r="I36" s="23">
+        <f t="shared" si="0"/>
+        <v>1050</v>
+      </c>
+      <c r="J36" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K36" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="22"/>
+      <c r="B37" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>595</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>597</v>
+      </c>
+      <c r="F37" s="23">
+        <v>5</v>
+      </c>
+      <c r="G37" s="23">
+        <v>1065</v>
+      </c>
+      <c r="H37" s="23">
+        <v>25</v>
+      </c>
+      <c r="I37" s="23">
+        <f t="shared" si="0"/>
+        <v>1040</v>
+      </c>
+      <c r="J37" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K37" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L37" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="22"/>
+      <c r="Q37" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25"/>
+      <c r="B38" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E38" s="25" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F38" s="26">
+        <v>3</v>
+      </c>
+      <c r="G38" s="26">
+        <v>25</v>
+      </c>
+      <c r="H38" s="26">
+        <v>25</v>
+      </c>
+      <c r="I38" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="K38" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38" s="25" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M38" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N38" s="25"/>
+      <c r="O38" s="25"/>
+      <c r="P38" s="25"/>
+      <c r="Q38" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="22"/>
+      <c r="B39" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="22" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D39" s="22" t="s">
+        <v>1497</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>1498</v>
+      </c>
+      <c r="F39" s="23">
+        <v>1</v>
+      </c>
+      <c r="G39" s="23">
+        <v>915</v>
+      </c>
+      <c r="H39" s="23">
+        <v>25</v>
+      </c>
+      <c r="I39" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J39" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K39" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L39" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M39" s="22"/>
+      <c r="N39" s="22"/>
+      <c r="O39" s="22"/>
+      <c r="P39" s="22"/>
+      <c r="Q39" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="22"/>
+      <c r="B40" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D40" s="22" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E40" s="22" t="s">
+        <v>1501</v>
+      </c>
+      <c r="F40" s="23">
+        <v>3</v>
+      </c>
+      <c r="G40" s="23">
+        <v>765</v>
+      </c>
+      <c r="H40" s="23">
+        <v>25</v>
+      </c>
+      <c r="I40" s="23">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J40" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K40" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L40" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M40" s="22"/>
+      <c r="N40" s="22"/>
+      <c r="O40" s="22"/>
+      <c r="P40" s="22"/>
+      <c r="Q40" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="22"/>
+      <c r="B41" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" s="22" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D41" s="22" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E41" s="22" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F41" s="23">
+        <v>1</v>
+      </c>
+      <c r="G41" s="23">
+        <v>855</v>
+      </c>
+      <c r="H41" s="23">
+        <v>25</v>
+      </c>
+      <c r="I41" s="23">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J41" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K41" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L41" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M41" s="22"/>
+      <c r="N41" s="22"/>
+      <c r="O41" s="22"/>
+      <c r="P41" s="22"/>
+      <c r="Q41" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G43" s="1">
+        <f t="shared" ref="G43:R43" si="2">SUBTOTAL(9,G3:G42)</f>
+        <v>18415</v>
+      </c>
+      <c r="H43" s="1">
+        <f t="shared" si="2"/>
+        <v>1105</v>
+      </c>
+      <c r="I43" s="1">
+        <f t="shared" si="2"/>
+        <v>17310</v>
+      </c>
+      <c r="J43" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L43" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N43" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O43" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P43" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q43" s="1">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="R43" s="1">
+        <f t="shared" si="2"/>
+        <v>410</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H47" s="4" t="s">
+        <v>1312</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H48" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" s="8">
+        <f>SUM(I42:I46)</f>
+        <v>17310</v>
+      </c>
+      <c r="J48" s="8">
+        <f>Q43</f>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="49" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H49" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I49" s="10">
+        <f>R43</f>
+        <v>410</v>
+      </c>
+      <c r="J49" s="11"/>
+    </row>
+    <row r="50" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H50" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I50" s="10">
+        <f>S42</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="11"/>
+    </row>
+    <row r="51" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H51" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" s="10">
+        <f>T42</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="11"/>
+    </row>
+    <row r="52" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H52" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I52" s="10">
+        <f>U42</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="11"/>
+    </row>
+    <row r="53" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H53" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" s="13"/>
+      <c r="J53" s="13"/>
+    </row>
+    <row r="54" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H54" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+    </row>
+    <row r="55" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H55" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I55" s="16">
+        <f>SUM(I48:I54)</f>
+        <v>17720</v>
+      </c>
+      <c r="J55" s="16">
+        <f>SUM(J48:J52)</f>
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P41" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P41">
+      <sortCondition ref="J2:J41"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56A752C0-C941-442A-A413-82BE1FD6C446}">
   <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -14939,10 +17236,10 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>205</v>
+        <v>266</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1311</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -16045,57 +18342,1331 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G58" s="1">
-        <f>SUBTOTAL(9,G3:G57)</f>
+        <f t="shared" ref="G58:R58" si="0">SUBTOTAL(9,G3:G57)</f>
         <v>0</v>
       </c>
       <c r="H58" s="1">
-        <f>SUBTOTAL(9,H3:H57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I58" s="1">
-        <f>SUBTOTAL(9,I3:I57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J58" s="1">
-        <f>SUBTOTAL(9,J3:J57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K58" s="1">
-        <f>SUBTOTAL(9,K3:K57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L58" s="1">
-        <f>SUBTOTAL(9,L3:L57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M58" s="1">
-        <f>SUBTOTAL(9,M3:M57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N58" s="1">
-        <f>SUBTOTAL(9,N3:N57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O58" s="1">
-        <f>SUBTOTAL(9,O3:O57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P58" s="1">
-        <f>SUBTOTAL(9,P3:P57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q58" s="1">
-        <f>SUBTOTAL(9,Q3:Q57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R58" s="1">
-        <f>SUBTOTAL(9,R3:R57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H62" s="4" t="s">
-        <v>1312</v>
+        <v>1412</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I63" s="8">
+        <f>SUM(I57:I61)</f>
+        <v>0</v>
+      </c>
+      <c r="J63" s="8">
+        <f>Q58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H64" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I64" s="10">
+        <f>R58</f>
+        <v>0</v>
+      </c>
+      <c r="J64" s="11"/>
+    </row>
+    <row r="65" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H65" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I65" s="10">
+        <f>S57</f>
+        <v>0</v>
+      </c>
+      <c r="J65" s="11"/>
+    </row>
+    <row r="66" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H66" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" s="10">
+        <f>T57</f>
+        <v>0</v>
+      </c>
+      <c r="J66" s="11"/>
+    </row>
+    <row r="67" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H67" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I67" s="10">
+        <f>U57</f>
+        <v>0</v>
+      </c>
+      <c r="J67" s="11"/>
+    </row>
+    <row r="68" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H68" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+    </row>
+    <row r="69" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H69" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
+    </row>
+    <row r="70" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H70" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I70" s="16">
+        <f>SUM(I63:I69)</f>
+        <v>0</v>
+      </c>
+      <c r="J70" s="16">
+        <f>SUM(J63:J67)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P56" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P56">
+      <sortCondition ref="J2:J56"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D597EC-9F26-4C4B-8BF1-26CBB7F3ED40}">
+  <dimension ref="A1:R70"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+    </row>
+    <row r="4" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+    </row>
+    <row r="5" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="20"/>
+    </row>
+    <row r="6" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+    </row>
+    <row r="7" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="20"/>
+    </row>
+    <row r="8" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+    </row>
+    <row r="9" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+    </row>
+    <row r="10" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="20"/>
+    </row>
+    <row r="11" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="20"/>
+    </row>
+    <row r="12" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+    </row>
+    <row r="13" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+    </row>
+    <row r="14" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+    </row>
+    <row r="15" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="20"/>
+    </row>
+    <row r="16" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="20"/>
+    </row>
+    <row r="17" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="20"/>
+    </row>
+    <row r="18" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+    </row>
+    <row r="19" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="20"/>
+    </row>
+    <row r="20" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+    </row>
+    <row r="21" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+    </row>
+    <row r="22" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+    </row>
+    <row r="23" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="20"/>
+    </row>
+    <row r="24" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+    </row>
+    <row r="25" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="20"/>
+    </row>
+    <row r="26" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+    </row>
+    <row r="27" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+    </row>
+    <row r="28" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="20"/>
+    </row>
+    <row r="29" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="20"/>
+    </row>
+    <row r="30" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+    </row>
+    <row r="31" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17"/>
+    </row>
+    <row r="32" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+    </row>
+    <row r="33" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="20"/>
+    </row>
+    <row r="34" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+    </row>
+    <row r="35" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+    </row>
+    <row r="36" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="20"/>
+    </row>
+    <row r="37" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+    </row>
+    <row r="38" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+    </row>
+    <row r="39" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="17"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="20"/>
+    </row>
+    <row r="40" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+    </row>
+    <row r="41" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+    </row>
+    <row r="42" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="17"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+    </row>
+    <row r="43" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17"/>
+      <c r="P43" s="17"/>
+      <c r="Q43" s="17"/>
+      <c r="R43" s="20"/>
+    </row>
+    <row r="44" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="17"/>
+    </row>
+    <row r="45" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="20"/>
+    </row>
+    <row r="46" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="17"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17"/>
+      <c r="P46" s="17"/>
+      <c r="Q46" s="17"/>
+      <c r="R46" s="20"/>
+    </row>
+    <row r="47" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="17"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="17"/>
+      <c r="M47" s="17"/>
+      <c r="N47" s="17"/>
+      <c r="O47" s="17"/>
+      <c r="P47" s="17"/>
+      <c r="Q47" s="17"/>
+    </row>
+    <row r="48" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="17"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
+      <c r="Q48" s="17"/>
+    </row>
+    <row r="49" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="17"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
+      <c r="L49" s="17"/>
+      <c r="M49" s="17"/>
+      <c r="N49" s="17"/>
+      <c r="O49" s="17"/>
+      <c r="P49" s="17"/>
+      <c r="Q49" s="17"/>
+      <c r="R49" s="20"/>
+    </row>
+    <row r="50" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="17"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="17"/>
+      <c r="M50" s="17"/>
+      <c r="N50" s="17"/>
+      <c r="O50" s="17"/>
+      <c r="P50" s="17"/>
+      <c r="Q50" s="17"/>
+    </row>
+    <row r="51" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="17"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="18"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="17"/>
+      <c r="M51" s="17"/>
+      <c r="N51" s="17"/>
+      <c r="O51" s="17"/>
+      <c r="P51" s="17"/>
+      <c r="Q51" s="17"/>
+    </row>
+    <row r="52" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="17"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
+      <c r="N52" s="17"/>
+      <c r="O52" s="17"/>
+      <c r="P52" s="17"/>
+      <c r="Q52" s="17"/>
+      <c r="R52" s="20"/>
+    </row>
+    <row r="53" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="17"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="17"/>
+      <c r="L53" s="17"/>
+      <c r="M53" s="17"/>
+      <c r="N53" s="17"/>
+      <c r="O53" s="17"/>
+      <c r="P53" s="17"/>
+      <c r="Q53" s="17"/>
+    </row>
+    <row r="54" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="17"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
+      <c r="O54" s="17"/>
+      <c r="P54" s="17"/>
+      <c r="Q54" s="17"/>
+    </row>
+    <row r="55" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="17"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="17"/>
+      <c r="K55" s="17"/>
+      <c r="L55" s="17"/>
+      <c r="M55" s="17"/>
+      <c r="N55" s="17"/>
+      <c r="O55" s="17"/>
+      <c r="P55" s="17"/>
+      <c r="Q55" s="17"/>
+    </row>
+    <row r="56" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="17"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="17"/>
+      <c r="M56" s="17"/>
+      <c r="N56" s="17"/>
+      <c r="O56" s="17"/>
+      <c r="P56" s="17"/>
+      <c r="Q56" s="17"/>
+      <c r="R56" s="20"/>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G58" s="1">
+        <f t="shared" ref="G58:R58" si="0">SUBTOTAL(9,G3:G57)</f>
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H62" s="4" t="s">
+        <v>1505</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>15</v>

--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F64A88D-FAF3-4C13-83DC-903BC14214C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF33C78-906D-47AB-AE34-D5BF6B58B769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-5" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'15-5'!$A$2:$P$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'16-5'!$A$2:$P$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'18-5'!$A$2:$P$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'19-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'19-5'!$A$2:$P$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'20-5'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'4-5'!$A$2:$P$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'5-5'!$A$2:$P$55</definedName>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4444" uniqueCount="1507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4647" uniqueCount="1575">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -4590,6 +4590,210 @@
   </si>
   <si>
     <t>NGAY 20-5</t>
+  </si>
+  <si>
+    <t>YẾN</t>
+  </si>
+  <si>
+    <t>HD022130</t>
+  </si>
+  <si>
+    <t>Số 21 đường 10, khu Khang Điền, P.Phước Long B</t>
+  </si>
+  <si>
+    <t>19-05-2026</t>
+  </si>
+  <si>
+    <t>HD021999</t>
+  </si>
+  <si>
+    <t>AT 19-05</t>
+  </si>
+  <si>
+    <t>HD021937</t>
+  </si>
+  <si>
+    <t>Trường Ruby Hồng Ngọc, số 4 Lê Quát, Phường Tân Thới Hoà</t>
+  </si>
+  <si>
+    <t>HD021909</t>
+  </si>
+  <si>
+    <t>Chung cư Tecco, block C, đường Nguyễn Cửu Phú, phường Tân Tạo</t>
+  </si>
+  <si>
+    <t>Thiều Phương Nhi</t>
+  </si>
+  <si>
+    <t>HD022153</t>
+  </si>
+  <si>
+    <t>115 Phan Huy Thực, P.Tân Hưng</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Hà Vy</t>
+  </si>
+  <si>
+    <t>HD021917</t>
+  </si>
+  <si>
+    <t>30/8 trịnh đình thảo p. Hòa Thạnh</t>
+  </si>
+  <si>
+    <t>Nguyễn Võ Thụy Hương (Hoàng Ngân)</t>
+  </si>
+  <si>
+    <t>HD022099</t>
+  </si>
+  <si>
+    <t>Châu Nguyễn</t>
+  </si>
+  <si>
+    <t>HD021967</t>
+  </si>
+  <si>
+    <t>chung cu eco green block H</t>
+  </si>
+  <si>
+    <t>Eny Nguyen</t>
+  </si>
+  <si>
+    <t>HD022152</t>
+  </si>
+  <si>
+    <t>362/26 lê văn lương, tân hưng</t>
+  </si>
+  <si>
+    <t>Ivy Tran</t>
+  </si>
+  <si>
+    <t>HD021976</t>
+  </si>
+  <si>
+    <t>128/3 Nguyễn Sơn, Phú Thọ Hoà</t>
+  </si>
+  <si>
+    <t>Ivy Nguyen</t>
+  </si>
+  <si>
+    <t>HD022104</t>
+  </si>
+  <si>
+    <t>296 gia phú p1</t>
+  </si>
+  <si>
+    <t>BELLA TRẦN</t>
+  </si>
+  <si>
+    <t>66đường 17 p10</t>
+  </si>
+  <si>
+    <t>Nguyễn Trương Phương Oanh</t>
+  </si>
+  <si>
+    <t>HD021780</t>
+  </si>
+  <si>
+    <t>125/42/2 Bùi Đình Tuý, phường 14</t>
+  </si>
+  <si>
+    <t>Bảo Ngân</t>
+  </si>
+  <si>
+    <t>HD021981</t>
+  </si>
+  <si>
+    <t>62 đường 36, Khu đô thị Vạn Phúc</t>
+  </si>
+  <si>
+    <t>Trang Gpe / Wang Yu Hua</t>
+  </si>
+  <si>
+    <t>HD021970</t>
+  </si>
+  <si>
+    <t>Số 192 Trần Bá Giao, Phường 5</t>
+  </si>
+  <si>
+    <t>Khả Hân</t>
+  </si>
+  <si>
+    <t>HD021776</t>
+  </si>
+  <si>
+    <t>10 Tạ Hiện Cát Lái</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thương Hoài</t>
+  </si>
+  <si>
+    <t>HD022106</t>
+  </si>
+  <si>
+    <t>32/4/17 khu phố 3, đường 21, phường Cát Lái</t>
+  </si>
+  <si>
+    <t>Phạm Ngọc Thương</t>
+  </si>
+  <si>
+    <t>HD022114</t>
+  </si>
+  <si>
+    <t>23/53 Nơ Trang Long, p7</t>
+  </si>
+  <si>
+    <t>Ngọc Trang</t>
+  </si>
+  <si>
+    <t>HD022158</t>
+  </si>
+  <si>
+    <t>Foxshop 28 Lê Văn Duyệt, P1</t>
+  </si>
+  <si>
+    <t>HD021846</t>
+  </si>
+  <si>
+    <t>NT Hải Yến</t>
+  </si>
+  <si>
+    <t>123 khu dân cư Tân Tiến, Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>LEMONA</t>
+  </si>
+  <si>
+    <t>HD022145</t>
+  </si>
+  <si>
+    <t>chung cư botanica premier block C2 Hồng Hà</t>
+  </si>
+  <si>
+    <t>Hiền Hiền</t>
+  </si>
+  <si>
+    <t>HD022103</t>
+  </si>
+  <si>
+    <t>163/25/42 Tô Hiến Thành p13</t>
+  </si>
+  <si>
+    <t>HD022101</t>
+  </si>
+  <si>
+    <t>khun leang 092559972</t>
+  </si>
+  <si>
+    <t>HD021974</t>
+  </si>
+  <si>
+    <t>nhà xe khải nam</t>
+  </si>
+  <si>
+    <t>GENY</t>
+  </si>
+  <si>
+    <t>B12 Đ. Bạch Đằng, Phường 2</t>
   </si>
 </sst>
 </file>
@@ -17220,7 +17424,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56A752C0-C941-442A-A413-82BE1FD6C446}">
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
@@ -17293,1198 +17497,1385 @@
       </c>
       <c r="Q2" s="3"/>
     </row>
-    <row r="3" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-    </row>
-    <row r="4" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-    </row>
-    <row r="5" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="20"/>
-    </row>
-    <row r="6" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-    </row>
-    <row r="7" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="20"/>
-    </row>
-    <row r="8" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-    </row>
-    <row r="9" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-    </row>
-    <row r="10" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="20"/>
-    </row>
-    <row r="11" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="20"/>
-    </row>
-    <row r="12" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-    </row>
-    <row r="13" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-    </row>
-    <row r="14" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-    </row>
-    <row r="15" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="20"/>
-    </row>
-    <row r="16" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="20"/>
-    </row>
-    <row r="17" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="20"/>
-    </row>
-    <row r="18" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-    </row>
-    <row r="19" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="20"/>
-    </row>
-    <row r="20" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
-    </row>
-    <row r="21" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-    </row>
-    <row r="22" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-    </row>
-    <row r="23" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="20"/>
-    </row>
-    <row r="24" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
-    </row>
-    <row r="25" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="20"/>
-    </row>
-    <row r="26" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
-    </row>
-    <row r="27" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
-    </row>
-    <row r="28" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="20"/>
-    </row>
-    <row r="29" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="20"/>
-    </row>
-    <row r="30" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
-      <c r="P30" s="17"/>
-      <c r="Q30" s="17"/>
-    </row>
-    <row r="31" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17"/>
-      <c r="O31" s="17"/>
-      <c r="P31" s="17"/>
-      <c r="Q31" s="17"/>
-    </row>
-    <row r="32" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="17"/>
-      <c r="P32" s="17"/>
-      <c r="Q32" s="17"/>
-    </row>
-    <row r="33" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
-      <c r="P33" s="17"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="20"/>
-    </row>
-    <row r="34" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="17"/>
-    </row>
-    <row r="35" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
-    </row>
-    <row r="36" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="17"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17"/>
-      <c r="P36" s="17"/>
-      <c r="Q36" s="17"/>
-      <c r="R36" s="20"/>
-    </row>
-    <row r="37" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="17"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
-    </row>
-    <row r="38" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="17"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
-      <c r="N38" s="17"/>
-      <c r="O38" s="17"/>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17"/>
-    </row>
-    <row r="39" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="17"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
-      <c r="N39" s="17"/>
-      <c r="O39" s="17"/>
-      <c r="P39" s="17"/>
-      <c r="Q39" s="17"/>
-      <c r="R39" s="20"/>
-    </row>
-    <row r="40" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
-      <c r="N40" s="17"/>
-      <c r="O40" s="17"/>
-      <c r="P40" s="17"/>
-      <c r="Q40" s="17"/>
-    </row>
-    <row r="41" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
-      <c r="N41" s="17"/>
-      <c r="O41" s="17"/>
-      <c r="P41" s="17"/>
-      <c r="Q41" s="17"/>
-    </row>
-    <row r="42" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
-      <c r="M42" s="17"/>
-      <c r="N42" s="17"/>
-      <c r="O42" s="17"/>
-      <c r="P42" s="17"/>
-      <c r="Q42" s="17"/>
-    </row>
-    <row r="43" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
-      <c r="M43" s="17"/>
-      <c r="N43" s="17"/>
-      <c r="O43" s="17"/>
-      <c r="P43" s="17"/>
-      <c r="Q43" s="17"/>
-      <c r="R43" s="20"/>
-    </row>
-    <row r="44" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-      <c r="N44" s="17"/>
-      <c r="O44" s="17"/>
-      <c r="P44" s="17"/>
-      <c r="Q44" s="17"/>
-    </row>
-    <row r="45" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17"/>
-      <c r="O45" s="17"/>
-      <c r="P45" s="17"/>
-      <c r="Q45" s="17"/>
-      <c r="R45" s="20"/>
-    </row>
-    <row r="46" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="17"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="18"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="17"/>
-      <c r="M46" s="17"/>
-      <c r="N46" s="17"/>
-      <c r="O46" s="17"/>
-      <c r="P46" s="17"/>
-      <c r="Q46" s="17"/>
-      <c r="R46" s="20"/>
-    </row>
-    <row r="47" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="17"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="18"/>
-      <c r="I47" s="18"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
-      <c r="L47" s="17"/>
-      <c r="M47" s="17"/>
-      <c r="N47" s="17"/>
-      <c r="O47" s="17"/>
-      <c r="P47" s="17"/>
-      <c r="Q47" s="17"/>
-    </row>
-    <row r="48" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="17"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="18"/>
-      <c r="I48" s="18"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="17"/>
-      <c r="M48" s="17"/>
-      <c r="N48" s="17"/>
-      <c r="O48" s="17"/>
-      <c r="P48" s="17"/>
-      <c r="Q48" s="17"/>
-    </row>
-    <row r="49" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="17"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="18"/>
-      <c r="I49" s="18"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
-      <c r="N49" s="17"/>
-      <c r="O49" s="17"/>
-      <c r="P49" s="17"/>
-      <c r="Q49" s="17"/>
-      <c r="R49" s="20"/>
-    </row>
-    <row r="50" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="17"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
-      <c r="H50" s="18"/>
-      <c r="I50" s="18"/>
-      <c r="J50" s="17"/>
-      <c r="K50" s="17"/>
-      <c r="L50" s="17"/>
-      <c r="M50" s="17"/>
-      <c r="N50" s="17"/>
-      <c r="O50" s="17"/>
-      <c r="P50" s="17"/>
-      <c r="Q50" s="17"/>
-    </row>
-    <row r="51" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="17"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="18"/>
-      <c r="I51" s="18"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="17"/>
-      <c r="M51" s="17"/>
-      <c r="N51" s="17"/>
-      <c r="O51" s="17"/>
-      <c r="P51" s="17"/>
-      <c r="Q51" s="17"/>
-    </row>
-    <row r="52" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="17"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="18"/>
-      <c r="H52" s="18"/>
-      <c r="I52" s="18"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
-      <c r="M52" s="17"/>
-      <c r="N52" s="17"/>
-      <c r="O52" s="17"/>
-      <c r="P52" s="17"/>
-      <c r="Q52" s="17"/>
-      <c r="R52" s="20"/>
-    </row>
-    <row r="53" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="17"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="18"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
-      <c r="M53" s="17"/>
-      <c r="N53" s="17"/>
-      <c r="O53" s="17"/>
-      <c r="P53" s="17"/>
-      <c r="Q53" s="17"/>
-    </row>
-    <row r="54" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="17"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
-      <c r="H54" s="18"/>
-      <c r="I54" s="18"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="17"/>
-      <c r="O54" s="17"/>
-      <c r="P54" s="17"/>
-      <c r="Q54" s="17"/>
-    </row>
-    <row r="55" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="17"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-      <c r="H55" s="18"/>
-      <c r="I55" s="18"/>
-      <c r="J55" s="17"/>
-      <c r="K55" s="17"/>
-      <c r="L55" s="17"/>
-      <c r="M55" s="17"/>
-      <c r="N55" s="17"/>
-      <c r="O55" s="17"/>
-      <c r="P55" s="17"/>
-      <c r="Q55" s="17"/>
-    </row>
-    <row r="56" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="17"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="18"/>
-      <c r="I56" s="18"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="17"/>
-      <c r="O56" s="17"/>
-      <c r="P56" s="17"/>
-      <c r="Q56" s="17"/>
-      <c r="R56" s="20"/>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="G58" s="1">
-        <f t="shared" ref="G58:R58" si="0">SUBTOTAL(9,G3:G57)</f>
-        <v>0</v>
-      </c>
-      <c r="H58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H62" s="4" t="s">
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F3" s="23">
+        <v>9</v>
+      </c>
+      <c r="G3" s="23">
+        <v>830</v>
+      </c>
+      <c r="H3" s="23">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I29" si="0">G3-H3</f>
+        <v>800</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>316</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G4" s="23">
+        <v>735</v>
+      </c>
+      <c r="H4" s="23">
+        <v>35</v>
+      </c>
+      <c r="I4" s="23">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>1512</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>831</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="23">
+        <v>985</v>
+      </c>
+      <c r="H5" s="23">
+        <v>25</v>
+      </c>
+      <c r="I5" s="23">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>1512</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>737</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>1515</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>1516</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G6" s="23">
+        <v>860</v>
+      </c>
+      <c r="H6" s="23">
+        <v>30</v>
+      </c>
+      <c r="I6" s="23">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>1512</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>1518</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>1519</v>
+      </c>
+      <c r="F7" s="23">
+        <v>7</v>
+      </c>
+      <c r="G7" s="23">
+        <v>850</v>
+      </c>
+      <c r="H7" s="23">
+        <v>30</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>1512</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>1521</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>1522</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="23">
+        <v>1115</v>
+      </c>
+      <c r="H8" s="23">
+        <v>25</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>1090</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>1512</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>1524</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="F9" s="23">
+        <v>6</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0</v>
+      </c>
+      <c r="H9" s="23">
+        <v>25</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>1512</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+      <c r="R9" s="24">
+        <f>H9</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>1525</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>1526</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>1527</v>
+      </c>
+      <c r="F10" s="23">
+        <v>7</v>
+      </c>
+      <c r="G10" s="23">
+        <v>850</v>
+      </c>
+      <c r="H10" s="23">
+        <v>30</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>1512</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>1529</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>1530</v>
+      </c>
+      <c r="F11" s="23">
+        <v>7</v>
+      </c>
+      <c r="G11" s="23">
+        <v>380</v>
+      </c>
+      <c r="H11" s="23">
+        <v>30</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>1512</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>1532</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>1533</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="23">
+        <v>0</v>
+      </c>
+      <c r="H12" s="23">
+        <v>25</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>1512</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+      <c r="R12" s="24">
+        <f>H12</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>1535</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>1536</v>
+      </c>
+      <c r="F13" s="23">
+        <v>6</v>
+      </c>
+      <c r="G13" s="23">
+        <v>765</v>
+      </c>
+      <c r="H13" s="23">
+        <v>25</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>1512</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22" t="s">
+        <v>1538</v>
+      </c>
+      <c r="F14" s="23">
+        <v>6</v>
+      </c>
+      <c r="G14" s="23">
+        <v>40</v>
+      </c>
+      <c r="H14" s="23">
+        <v>40</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>1512</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>1539</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>1541</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="23">
+        <v>0</v>
+      </c>
+      <c r="H15" s="23">
+        <v>20</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22">
+        <v>1</v>
+      </c>
+      <c r="R15" s="24">
+        <f>H15</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>1543</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>1544</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="23">
+        <v>1020</v>
+      </c>
+      <c r="H16" s="23">
+        <v>30</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>1545</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>1546</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>1547</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="23">
+        <v>0</v>
+      </c>
+      <c r="H17" s="23">
+        <v>25</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+      <c r="R17" s="24">
+        <f>H17</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>1549</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>1550</v>
+      </c>
+      <c r="F18" s="23">
+        <v>2</v>
+      </c>
+      <c r="G18" s="23">
+        <v>1020</v>
+      </c>
+      <c r="H18" s="23">
+        <v>30</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>1552</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>1553</v>
+      </c>
+      <c r="F19" s="23">
+        <v>2</v>
+      </c>
+      <c r="G19" s="23">
+        <v>0</v>
+      </c>
+      <c r="H19" s="23">
+        <v>30</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+      <c r="R19" s="24">
+        <f t="shared" ref="R19:R21" si="1">H19</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" s="23">
+        <v>0</v>
+      </c>
+      <c r="H20" s="23">
+        <v>20</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+      <c r="R20" s="24">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>1558</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" s="23">
+        <v>0</v>
+      </c>
+      <c r="H21" s="23">
+        <v>20</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+      <c r="R21" s="24">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>762</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>1560</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>764</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" s="23">
+        <v>1420</v>
+      </c>
+      <c r="H22" s="23">
+        <v>20</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22" t="s">
+        <v>1562</v>
+      </c>
+      <c r="F23" s="23">
+        <v>12</v>
+      </c>
+      <c r="G23" s="23">
+        <v>0</v>
+      </c>
+      <c r="H23" s="23">
+        <v>60</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="0"/>
+        <v>-60</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+      <c r="R23" s="24">
+        <f t="shared" ref="R23:R24" si="2">H23</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="F24" s="23">
+        <v>12</v>
+      </c>
+      <c r="G24" s="23">
+        <v>0</v>
+      </c>
+      <c r="H24" s="23">
+        <v>60</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
+        <v>-60</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22">
+        <v>1</v>
+      </c>
+      <c r="R24" s="24">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>496</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>1565</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G25" s="23">
+        <v>1015</v>
+      </c>
+      <c r="H25" s="23">
+        <v>25</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>1567</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>1568</v>
+      </c>
+      <c r="F26" s="23">
+        <v>10</v>
+      </c>
+      <c r="G26" s="23">
+        <v>1665</v>
+      </c>
+      <c r="H26" s="23">
+        <v>25</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="0"/>
+        <v>1640</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="25"/>
+      <c r="B27" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>617</v>
+      </c>
+      <c r="F27" s="26">
+        <v>1</v>
+      </c>
+      <c r="G27" s="26">
+        <v>25</v>
+      </c>
+      <c r="H27" s="26">
+        <v>25</v>
+      </c>
+      <c r="I27" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="K27" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="25" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M27" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N27" s="25"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>1571</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>1572</v>
+      </c>
+      <c r="F28" s="23">
+        <v>5</v>
+      </c>
+      <c r="G28" s="23">
+        <v>0</v>
+      </c>
+      <c r="H28" s="23">
+        <v>25</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22">
+        <v>1</v>
+      </c>
+      <c r="R28" s="24">
+        <f t="shared" ref="R28:R29" si="3">H28</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>1573</v>
+      </c>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22" t="s">
+        <v>1574</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G29" s="23">
+        <v>0</v>
+      </c>
+      <c r="H29" s="23">
+        <v>50</v>
+      </c>
+      <c r="I29" s="23">
+        <f t="shared" si="0"/>
+        <v>-50</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>1510</v>
+      </c>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22">
+        <v>1</v>
+      </c>
+      <c r="R29" s="24">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G31" s="1">
+        <f>SUBTOTAL(9,G3:G30)</f>
+        <v>13575</v>
+      </c>
+      <c r="H31" s="1">
+        <f>SUBTOTAL(9,H3:H30)</f>
+        <v>815</v>
+      </c>
+      <c r="I31" s="1">
+        <f>SUBTOTAL(9,I3:I30)</f>
+        <v>12760</v>
+      </c>
+      <c r="J31" s="1">
+        <f>SUBTOTAL(9,J3:J30)</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
+        <f>SUBTOTAL(9,K3:K30)</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="1">
+        <f>SUBTOTAL(9,L3:L30)</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <f>SUBTOTAL(9,M3:M30)</f>
+        <v>0</v>
+      </c>
+      <c r="N31" s="1">
+        <f>SUBTOTAL(9,N3:N30)</f>
+        <v>0</v>
+      </c>
+      <c r="O31" s="1">
+        <f>SUBTOTAL(9,O3:O30)</f>
+        <v>0</v>
+      </c>
+      <c r="P31" s="1">
+        <f>SUBTOTAL(9,P3:P30)</f>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="1">
+        <f>SUBTOTAL(9,Q3:Q30)</f>
+        <v>27</v>
+      </c>
+      <c r="R31" s="1">
+        <f>SUBTOTAL(9,R3:R30)</f>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="35" spans="8:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H35" s="4" t="s">
         <v>1412</v>
       </c>
-      <c r="I62" s="5" t="s">
+      <c r="I35" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J62" s="6" t="s">
+      <c r="J35" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H63" s="7" t="s">
+    <row r="36" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H36" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I63" s="8">
-        <f>SUM(I57:I61)</f>
-        <v>0</v>
-      </c>
-      <c r="J63" s="8">
-        <f>Q58</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="H64" s="9" t="s">
+      <c r="I36" s="8">
+        <f>SUM(I30:I34)</f>
+        <v>12760</v>
+      </c>
+      <c r="J36" s="8">
+        <f>Q31</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H37" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I64" s="10">
-        <f>R58</f>
-        <v>0</v>
-      </c>
-      <c r="J64" s="11"/>
-    </row>
-    <row r="65" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H65" s="9" t="s">
+      <c r="I37" s="10">
+        <f>R31</f>
+        <v>360</v>
+      </c>
+      <c r="J37" s="11"/>
+    </row>
+    <row r="38" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H38" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I65" s="10">
-        <f>S57</f>
-        <v>0</v>
-      </c>
-      <c r="J65" s="11"/>
-    </row>
-    <row r="66" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H66" s="9" t="s">
+      <c r="I38" s="10">
+        <f>S30</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="11"/>
+    </row>
+    <row r="39" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H39" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I66" s="10">
-        <f>T57</f>
-        <v>0</v>
-      </c>
-      <c r="J66" s="11"/>
-    </row>
-    <row r="67" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H67" s="9" t="s">
+      <c r="I39" s="10">
+        <f>T30</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="11"/>
+    </row>
+    <row r="40" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H40" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I67" s="10">
-        <f>U57</f>
-        <v>0</v>
-      </c>
-      <c r="J67" s="11"/>
-    </row>
-    <row r="68" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H68" s="12" t="s">
+      <c r="I40" s="10">
+        <f>U30</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="11"/>
+    </row>
+    <row r="41" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H41" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
-    </row>
-    <row r="69" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H69" s="14" t="s">
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+    </row>
+    <row r="42" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H42" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13"/>
-    </row>
-    <row r="70" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="H70" s="15" t="s">
+      <c r="I42" s="13"/>
+      <c r="J42" s="13"/>
+    </row>
+    <row r="43" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H43" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I70" s="16">
-        <f>SUM(I63:I69)</f>
-        <v>0</v>
-      </c>
-      <c r="J70" s="16">
-        <f>SUM(J63:J67)</f>
-        <v>0</v>
+      <c r="I43" s="16">
+        <f>SUM(I36:I42)</f>
+        <v>13120</v>
+      </c>
+      <c r="J43" s="16">
+        <f>SUM(J36:J40)</f>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P56" xr:uid="{00000000-0009-0000-0000-000006000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P56">
-      <sortCondition ref="J2:J56"/>
+  <autoFilter ref="A2:P29" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P29">
+      <sortCondition ref="J2:J29"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF33C78-906D-47AB-AE34-D5BF6B58B769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B921B2-B7B1-4B45-9D48-45CE135CD8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-5" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,8 @@
     <sheet name="16-5" sheetId="15" r:id="rId13"/>
     <sheet name="18-5" sheetId="16" r:id="rId14"/>
     <sheet name="19-5" sheetId="17" r:id="rId15"/>
-    <sheet name="20-5" sheetId="18" r:id="rId16"/>
+    <sheet name="20-5" sheetId="19" r:id="rId16"/>
+    <sheet name="21-5" sheetId="18" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'11-5'!$A$2:$P$58</definedName>
@@ -40,7 +41,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'16-5'!$A$2:$P$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'18-5'!$A$2:$P$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'19-5'!$A$2:$P$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'20-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'20-5'!$A$2:$P$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'21-5'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'4-5'!$A$2:$P$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'5-5'!$A$2:$P$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'6-5'!$A$2:$P$34</definedName>
@@ -69,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4647" uniqueCount="1575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4915" uniqueCount="1653">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -3461,9 +3463,6 @@
     <t>Lê Ngọc Nhân</t>
   </si>
   <si>
-    <t>HD20811</t>
-  </si>
-  <si>
     <t>192 Phạm đức Sơn, P. Phú Định</t>
   </si>
   <si>
@@ -4794,6 +4793,243 @@
   </si>
   <si>
     <t>B12 Đ. Bạch Đằng, Phường 2</t>
+  </si>
+  <si>
+    <t>NGAY 21-5</t>
+  </si>
+  <si>
+    <t>T5.21.5.2026</t>
+  </si>
+  <si>
+    <t>HD022402</t>
+  </si>
+  <si>
+    <t>20-05-2026</t>
+  </si>
+  <si>
+    <t>Jess-9244</t>
+  </si>
+  <si>
+    <t>275/14B1 Dạng Nguyên Cẩn, Phường Phú Lâm</t>
+  </si>
+  <si>
+    <t>AT 20-05</t>
+  </si>
+  <si>
+    <t>Bé Hiền - fb Yudy Phạm</t>
+  </si>
+  <si>
+    <t>HD022410</t>
+  </si>
+  <si>
+    <t>336/20 nguyễn văn luông p12</t>
+  </si>
+  <si>
+    <t>Trần Lê Trâm Anh</t>
+  </si>
+  <si>
+    <t>HD022426</t>
+  </si>
+  <si>
+    <t>179/13A hoà bình Phường Hiệp Tân</t>
+  </si>
+  <si>
+    <t>HD022286</t>
+  </si>
+  <si>
+    <t>Mr Quốc - VTS-64591HCR</t>
+  </si>
+  <si>
+    <t>HD022211</t>
+  </si>
+  <si>
+    <t>Thanh Yến</t>
+  </si>
+  <si>
+    <t>HD022266</t>
+  </si>
+  <si>
+    <t>188/4 đường thới an 16 phường thới an</t>
+  </si>
+  <si>
+    <t>HƯƠNG</t>
+  </si>
+  <si>
+    <t>HD022382</t>
+  </si>
+  <si>
+    <t>7g đường số 8 tân hưng</t>
+  </si>
+  <si>
+    <t>Vận</t>
+  </si>
+  <si>
+    <t>HD022293</t>
+  </si>
+  <si>
+    <t>Tháp RS6, chung cư Richstar 2, số 239 Hoà Bình, phường Phú Thạnh</t>
+  </si>
+  <si>
+    <t>nguyen lý</t>
+  </si>
+  <si>
+    <t>HD022279</t>
+  </si>
+  <si>
+    <t>62/7h ấp 3 xã xuaabn thơi thượng</t>
+  </si>
+  <si>
+    <t>Alice Nguyễn</t>
+  </si>
+  <si>
+    <t>HD022396</t>
+  </si>
+  <si>
+    <t>Lyly My</t>
+  </si>
+  <si>
+    <t>HD022377</t>
+  </si>
+  <si>
+    <t>50/26 thanh xuân 24 thới an</t>
+  </si>
+  <si>
+    <t>Mỹ Phượng</t>
+  </si>
+  <si>
+    <t>HD022263</t>
+  </si>
+  <si>
+    <t>1414 huỳnh tấn phát p phú mỹ</t>
+  </si>
+  <si>
+    <t>Any</t>
+  </si>
+  <si>
+    <t>HD022412</t>
+  </si>
+  <si>
+    <t>101 đông hưng thuận42 phường tân hưng thuận</t>
+  </si>
+  <si>
+    <t>HD022267</t>
+  </si>
+  <si>
+    <t>Thương</t>
+  </si>
+  <si>
+    <t>HD022196</t>
+  </si>
+  <si>
+    <t>181 đường số 79 phường tân quy</t>
+  </si>
+  <si>
+    <t>Moon Nguyễn</t>
+  </si>
+  <si>
+    <t>HD022375</t>
+  </si>
+  <si>
+    <t>16 kim ngân, khu dân cư phong phu 4, xã phong phú</t>
+  </si>
+  <si>
+    <t>Ngoc_Ann tiktok gingeri 16:39</t>
+  </si>
+  <si>
+    <t>HD022381</t>
+  </si>
+  <si>
+    <t>1/7 nguyễn văn yên tân thới hoà</t>
+  </si>
+  <si>
+    <t>VICKY TRẦN</t>
+  </si>
+  <si>
+    <t>Đắc Hội Express 127/17 bình lợi p13</t>
+  </si>
+  <si>
+    <t>ms Linh</t>
+  </si>
+  <si>
+    <t>HD022275</t>
+  </si>
+  <si>
+    <t>141A đường số 1 phường Thông Tây Hội</t>
+  </si>
+  <si>
+    <t>hsu_myat to</t>
+  </si>
+  <si>
+    <t>HD022406</t>
+  </si>
+  <si>
+    <t>2A/14, Nguyễn Thị Minh Khai, P. Đakao</t>
+  </si>
+  <si>
+    <t>HD022200</t>
+  </si>
+  <si>
+    <t>Vincom đồng khởi, 45 lý tự trọng, căn hộ 2604</t>
+  </si>
+  <si>
+    <t>HD022255</t>
+  </si>
+  <si>
+    <t>Tòa nhà C22 Building Số G5, Đường C22, Phường 12</t>
+  </si>
+  <si>
+    <t>Ý nhi</t>
+  </si>
+  <si>
+    <t>HD022414</t>
+  </si>
+  <si>
+    <t>53 phạm ngọc thạch p6</t>
+  </si>
+  <si>
+    <t>CUS19950/pelpanhaketya</t>
+  </si>
+  <si>
+    <t>HD022206</t>
+  </si>
+  <si>
+    <t>270B Lý thường kiệt, khu phố 1, Phường 6</t>
+  </si>
+  <si>
+    <t>Amsumalin Abu</t>
+  </si>
+  <si>
+    <t>HD022399</t>
+  </si>
+  <si>
+    <t>03 trương quốc dung p8</t>
+  </si>
+  <si>
+    <t>HD022240</t>
+  </si>
+  <si>
+    <t>Huyentran Nguyen</t>
+  </si>
+  <si>
+    <t>HD022374</t>
+  </si>
+  <si>
+    <t>86-88 pasteur</t>
+  </si>
+  <si>
+    <t>linh</t>
+  </si>
+  <si>
+    <t>HD022244</t>
+  </si>
+  <si>
+    <t>358/2/2 cmt8</t>
+  </si>
+  <si>
+    <t>đơn trả 21.5</t>
+  </si>
+  <si>
+    <t>HD020811</t>
   </si>
 </sst>
 </file>
@@ -9865,7 +10101,7 @@
         <v>30</v>
       </c>
       <c r="I3" s="23">
-        <f t="shared" ref="I3:I39" si="0">G3-H3</f>
+        <f>G3-H3</f>
         <v>950</v>
       </c>
       <c r="J3" s="22" t="s">
@@ -9908,7 +10144,7 @@
         <v>30</v>
       </c>
       <c r="I4" s="23">
-        <f t="shared" si="0"/>
+        <f>G4-H4</f>
         <v>-30</v>
       </c>
       <c r="J4" s="22" t="s">
@@ -9940,10 +10176,10 @@
         <v>1129</v>
       </c>
       <c r="D5" s="22" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E5" s="22" t="s">
         <v>1130</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>1131</v>
       </c>
       <c r="F5" s="23">
         <v>7</v>
@@ -9955,7 +10191,7 @@
         <v>30</v>
       </c>
       <c r="I5" s="23">
-        <f t="shared" si="0"/>
+        <f>G5-H5</f>
         <v>780</v>
       </c>
       <c r="J5" s="22" t="s">
@@ -9980,13 +10216,13 @@
         <v>30</v>
       </c>
       <c r="C6" s="22" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D6" s="22" t="s">
         <v>1132</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="E6" s="22" t="s">
         <v>1133</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>1134</v>
       </c>
       <c r="F6" s="23">
         <v>8</v>
@@ -9998,7 +10234,7 @@
         <v>30</v>
       </c>
       <c r="I6" s="23">
-        <f t="shared" si="0"/>
+        <f>G6-H6</f>
         <v>1520</v>
       </c>
       <c r="J6" s="22" t="s">
@@ -10023,13 +10259,13 @@
         <v>30</v>
       </c>
       <c r="C7" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>1135</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="E7" s="22" t="s">
         <v>1136</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>1137</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>59</v>
@@ -10041,7 +10277,7 @@
         <v>25</v>
       </c>
       <c r="I7" s="23">
-        <f t="shared" si="0"/>
+        <f>G7-H7</f>
         <v>810</v>
       </c>
       <c r="J7" s="22" t="s">
@@ -10066,13 +10302,13 @@
         <v>30</v>
       </c>
       <c r="C8" s="22" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>1138</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="E8" s="22" t="s">
         <v>1139</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>1140</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>39</v>
@@ -10084,7 +10320,7 @@
         <v>30</v>
       </c>
       <c r="I8" s="23">
-        <f t="shared" si="0"/>
+        <f>G8-H8</f>
         <v>-30</v>
       </c>
       <c r="J8" s="22" t="s">
@@ -10113,13 +10349,13 @@
         <v>30</v>
       </c>
       <c r="C9" s="22" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>1141</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="E9" s="22" t="s">
         <v>1142</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>1143</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>59</v>
@@ -10131,7 +10367,7 @@
         <v>25</v>
       </c>
       <c r="I9" s="23">
-        <f t="shared" si="0"/>
+        <f>G9-H9</f>
         <v>780</v>
       </c>
       <c r="J9" s="22" t="s">
@@ -10156,13 +10392,13 @@
         <v>30</v>
       </c>
       <c r="C10" s="22" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>1144</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="E10" s="22" t="s">
         <v>1145</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>1146</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>39</v>
@@ -10174,7 +10410,7 @@
         <v>30</v>
       </c>
       <c r="I10" s="23">
-        <f t="shared" si="0"/>
+        <f>G10-H10</f>
         <v>-30</v>
       </c>
       <c r="J10" s="22" t="s">
@@ -10203,13 +10439,13 @@
         <v>30</v>
       </c>
       <c r="C11" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>1147</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="E11" s="22" t="s">
         <v>1148</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>1149</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>39</v>
@@ -10221,7 +10457,7 @@
         <v>30</v>
       </c>
       <c r="I11" s="23">
-        <f t="shared" si="0"/>
+        <f>G11-H11</f>
         <v>780</v>
       </c>
       <c r="J11" s="22" t="s">
@@ -10246,13 +10482,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="22" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D12" s="22" t="s">
         <v>1150</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="E12" s="22" t="s">
         <v>1151</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>1152</v>
       </c>
       <c r="F12" s="23">
         <v>7</v>
@@ -10264,7 +10500,7 @@
         <v>30</v>
       </c>
       <c r="I12" s="23">
-        <f t="shared" si="0"/>
+        <f>G12-H12</f>
         <v>690</v>
       </c>
       <c r="J12" s="22" t="s">
@@ -10289,13 +10525,13 @@
         <v>30</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D13" s="22" t="s">
         <v>1153</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="E13" s="22" t="s">
         <v>1154</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>1155</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>59</v>
@@ -10307,7 +10543,7 @@
         <v>25</v>
       </c>
       <c r="I13" s="23">
-        <f t="shared" si="0"/>
+        <f>G13-H13</f>
         <v>-25</v>
       </c>
       <c r="J13" s="22" t="s">
@@ -10336,13 +10572,13 @@
         <v>30</v>
       </c>
       <c r="C14" s="22" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>1156</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="E14" s="22" t="s">
         <v>1157</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>1158</v>
       </c>
       <c r="F14" s="23">
         <v>8</v>
@@ -10354,7 +10590,7 @@
         <v>30</v>
       </c>
       <c r="I14" s="23">
-        <f t="shared" si="0"/>
+        <f>G14-H14</f>
         <v>780</v>
       </c>
       <c r="J14" s="22" t="s">
@@ -10379,13 +10615,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>1159</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="E15" s="22" t="s">
         <v>1160</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>1161</v>
       </c>
       <c r="F15" s="22" t="s">
         <v>39</v>
@@ -10397,7 +10633,7 @@
         <v>30</v>
       </c>
       <c r="I15" s="23">
-        <f t="shared" si="0"/>
+        <f>G15-H15</f>
         <v>720</v>
       </c>
       <c r="J15" s="22" t="s">
@@ -10424,11 +10660,11 @@
         <v>30</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="D16" s="22"/>
       <c r="E16" s="22" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="F16" s="22" t="s">
         <v>108</v>
@@ -10440,7 +10676,7 @@
         <v>40</v>
       </c>
       <c r="I16" s="23">
-        <f t="shared" si="0"/>
+        <f>G16-H16</f>
         <v>-40</v>
       </c>
       <c r="J16" s="22" t="s">
@@ -10475,7 +10711,7 @@
       </c>
       <c r="D17" s="22"/>
       <c r="E17" s="22" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="F17" s="22" t="s">
         <v>90</v>
@@ -10487,7 +10723,7 @@
         <v>30</v>
       </c>
       <c r="I17" s="23">
-        <f t="shared" si="0"/>
+        <f>G17-H17</f>
         <v>0</v>
       </c>
       <c r="J17" s="22" t="s">
@@ -10512,13 +10748,13 @@
         <v>30</v>
       </c>
       <c r="C18" s="22" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>1165</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="E18" s="22" t="s">
         <v>1166</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>1167</v>
       </c>
       <c r="F18" s="22" t="s">
         <v>90</v>
@@ -10530,7 +10766,7 @@
         <v>25</v>
       </c>
       <c r="I18" s="23">
-        <f t="shared" si="0"/>
+        <f>G18-H18</f>
         <v>0</v>
       </c>
       <c r="J18" s="22" t="s">
@@ -10558,7 +10794,7 @@
         <v>803</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E19" s="22" t="s">
         <v>805</v>
@@ -10573,7 +10809,7 @@
         <v>30</v>
       </c>
       <c r="I19" s="23">
-        <f t="shared" si="0"/>
+        <f>G19-H19</f>
         <v>-30</v>
       </c>
       <c r="J19" s="22" t="s">
@@ -10602,13 +10838,13 @@
         <v>30</v>
       </c>
       <c r="C20" s="22" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D20" s="22" t="s">
         <v>1169</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="E20" s="22" t="s">
         <v>1170</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>1171</v>
       </c>
       <c r="F20" s="22" t="s">
         <v>108</v>
@@ -10620,7 +10856,7 @@
         <v>25</v>
       </c>
       <c r="I20" s="23">
-        <f t="shared" si="0"/>
+        <f>G20-H20</f>
         <v>1120</v>
       </c>
       <c r="J20" s="22" t="s">
@@ -10645,13 +10881,13 @@
         <v>30</v>
       </c>
       <c r="C21" s="22" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D21" s="22" t="s">
         <v>1172</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="E21" s="22" t="s">
         <v>1173</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>1174</v>
       </c>
       <c r="F21" s="22" t="s">
         <v>94</v>
@@ -10663,7 +10899,7 @@
         <v>30</v>
       </c>
       <c r="I21" s="23">
-        <f t="shared" si="0"/>
+        <f>G21-H21</f>
         <v>-30</v>
       </c>
       <c r="J21" s="22" t="s">
@@ -10692,13 +10928,13 @@
         <v>30</v>
       </c>
       <c r="C22" s="22" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D22" s="22" t="s">
         <v>1175</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="E22" s="22" t="s">
         <v>1176</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>1177</v>
       </c>
       <c r="F22" s="22" t="s">
         <v>98</v>
@@ -10710,7 +10946,7 @@
         <v>20</v>
       </c>
       <c r="I22" s="23">
-        <f t="shared" si="0"/>
+        <f>G22-H22</f>
         <v>640</v>
       </c>
       <c r="J22" s="22" t="s">
@@ -10738,10 +10974,10 @@
         <v>133</v>
       </c>
       <c r="D23" s="22" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E23" s="22" t="s">
         <v>1178</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>1179</v>
       </c>
       <c r="F23" s="22" t="s">
         <v>98</v>
@@ -10753,7 +10989,7 @@
         <v>20</v>
       </c>
       <c r="I23" s="23">
-        <f t="shared" si="0"/>
+        <f>G23-H23</f>
         <v>780</v>
       </c>
       <c r="J23" s="22" t="s">
@@ -10778,13 +11014,13 @@
         <v>30</v>
       </c>
       <c r="C24" s="22" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D24" s="22" t="s">
         <v>1180</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="E24" s="22" t="s">
         <v>1181</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>1182</v>
       </c>
       <c r="F24" s="22" t="s">
         <v>90</v>
@@ -10796,7 +11032,7 @@
         <v>25</v>
       </c>
       <c r="I24" s="23">
-        <f t="shared" si="0"/>
+        <f>G24-H24</f>
         <v>800</v>
       </c>
       <c r="J24" s="22" t="s">
@@ -10823,11 +11059,11 @@
         <v>30</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="D25" s="22"/>
       <c r="E25" s="22" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="F25" s="22" t="s">
         <v>108</v>
@@ -10839,7 +11075,7 @@
         <v>40</v>
       </c>
       <c r="I25" s="23">
-        <f t="shared" si="0"/>
+        <f>G25-H25</f>
         <v>-40</v>
       </c>
       <c r="J25" s="22" t="s">
@@ -10858,7 +11094,7 @@
         <v>1</v>
       </c>
       <c r="R25" s="24">
-        <f t="shared" ref="R25:R27" si="1">H25</f>
+        <f>H25</f>
         <v>40</v>
       </c>
     </row>
@@ -10870,11 +11106,11 @@
         <v>30</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="22" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="F26" s="23">
         <v>5</v>
@@ -10886,7 +11122,7 @@
         <v>30</v>
       </c>
       <c r="I26" s="23">
-        <f t="shared" si="0"/>
+        <f>G26-H26</f>
         <v>-30</v>
       </c>
       <c r="J26" s="22" t="s">
@@ -10905,7 +11141,7 @@
         <v>1</v>
       </c>
       <c r="R26" s="24">
-        <f t="shared" si="1"/>
+        <f>H26</f>
         <v>30</v>
       </c>
     </row>
@@ -10933,7 +11169,7 @@
         <v>30</v>
       </c>
       <c r="I27" s="23">
-        <f t="shared" si="0"/>
+        <f>G27-H27</f>
         <v>-30</v>
       </c>
       <c r="J27" s="22" t="s">
@@ -10952,7 +11188,7 @@
         <v>1</v>
       </c>
       <c r="R27" s="24">
-        <f t="shared" si="1"/>
+        <f>H27</f>
         <v>30</v>
       </c>
     </row>
@@ -10962,13 +11198,13 @@
         <v>30</v>
       </c>
       <c r="C28" s="22" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D28" s="22" t="s">
         <v>1187</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="E28" s="22" t="s">
         <v>1188</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>1189</v>
       </c>
       <c r="F28" s="23">
         <v>10</v>
@@ -10980,7 +11216,7 @@
         <v>25</v>
       </c>
       <c r="I28" s="23">
-        <f t="shared" si="0"/>
+        <f>G28-H28</f>
         <v>780</v>
       </c>
       <c r="J28" s="22" t="s">
@@ -11005,13 +11241,13 @@
         <v>30</v>
       </c>
       <c r="C29" s="22" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D29" s="22" t="s">
         <v>1190</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="E29" s="22" t="s">
         <v>1191</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>1192</v>
       </c>
       <c r="F29" s="23">
         <v>4</v>
@@ -11023,7 +11259,7 @@
         <v>25</v>
       </c>
       <c r="I29" s="23">
-        <f t="shared" si="0"/>
+        <f>G29-H29</f>
         <v>-25</v>
       </c>
       <c r="J29" s="22" t="s">
@@ -11052,13 +11288,13 @@
         <v>30</v>
       </c>
       <c r="C30" s="22" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D30" s="22" t="s">
         <v>1193</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="E30" s="22" t="s">
         <v>1194</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>1195</v>
       </c>
       <c r="F30" s="22" t="s">
         <v>108</v>
@@ -11070,7 +11306,7 @@
         <v>25</v>
       </c>
       <c r="I30" s="23">
-        <f t="shared" si="0"/>
+        <f>G30-H30</f>
         <v>1630</v>
       </c>
       <c r="J30" s="22" t="s">
@@ -11095,13 +11331,13 @@
         <v>30</v>
       </c>
       <c r="C31" s="22" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D31" s="22" t="s">
         <v>1196</v>
       </c>
-      <c r="D31" s="22" t="s">
+      <c r="E31" s="22" t="s">
         <v>1197</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>1198</v>
       </c>
       <c r="F31" s="23">
         <v>10</v>
@@ -11113,7 +11349,7 @@
         <v>25</v>
       </c>
       <c r="I31" s="23">
-        <f t="shared" si="0"/>
+        <f>G31-H31</f>
         <v>350</v>
       </c>
       <c r="J31" s="22" t="s">
@@ -11138,13 +11374,13 @@
         <v>30</v>
       </c>
       <c r="C32" s="22" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D32" s="22" t="s">
         <v>1199</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="E32" s="22" t="s">
         <v>1200</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>1201</v>
       </c>
       <c r="F32" s="23">
         <v>4</v>
@@ -11156,7 +11392,7 @@
         <v>25</v>
       </c>
       <c r="I32" s="23">
-        <f t="shared" si="0"/>
+        <f>G32-H32</f>
         <v>1430</v>
       </c>
       <c r="J32" s="22" t="s">
@@ -11181,13 +11417,13 @@
         <v>30</v>
       </c>
       <c r="C33" s="22" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D33" s="22" t="s">
         <v>1202</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="E33" s="22" t="s">
         <v>1203</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>1204</v>
       </c>
       <c r="F33" s="23">
         <v>5</v>
@@ -11199,7 +11435,7 @@
         <v>25</v>
       </c>
       <c r="I33" s="23">
-        <f t="shared" si="0"/>
+        <f>G33-H33</f>
         <v>-25</v>
       </c>
       <c r="J33" s="22" t="s">
@@ -11231,7 +11467,7 @@
         <v>1107</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="E34" s="22" t="s">
         <v>1109</v>
@@ -11246,7 +11482,7 @@
         <v>25</v>
       </c>
       <c r="I34" s="23">
-        <f t="shared" si="0"/>
+        <f>G34-H34</f>
         <v>690</v>
       </c>
       <c r="J34" s="22" t="s">
@@ -11274,10 +11510,10 @@
         <v>127</v>
       </c>
       <c r="D35" s="22" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E35" s="22" t="s">
         <v>1206</v>
-      </c>
-      <c r="E35" s="22" t="s">
-        <v>1207</v>
       </c>
       <c r="F35" s="23">
         <v>10</v>
@@ -11289,7 +11525,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="23">
-        <f t="shared" si="0"/>
+        <f>G35-H35</f>
         <v>870</v>
       </c>
       <c r="J35" s="22" t="s">
@@ -11317,7 +11553,7 @@
         <v>193</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="E36" s="22" t="s">
         <v>195</v>
@@ -11332,7 +11568,7 @@
         <v>25</v>
       </c>
       <c r="I36" s="23">
-        <f t="shared" si="0"/>
+        <f>G36-H36</f>
         <v>-25</v>
       </c>
       <c r="J36" s="22" t="s">
@@ -11361,13 +11597,13 @@
         <v>30</v>
       </c>
       <c r="C37" s="22" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D37" s="22" t="s">
         <v>1209</v>
       </c>
-      <c r="D37" s="22" t="s">
+      <c r="E37" s="22" t="s">
         <v>1210</v>
-      </c>
-      <c r="E37" s="22" t="s">
-        <v>1211</v>
       </c>
       <c r="F37" s="23">
         <v>4</v>
@@ -11379,7 +11615,7 @@
         <v>25</v>
       </c>
       <c r="I37" s="23">
-        <f t="shared" si="0"/>
+        <f>G37-H37</f>
         <v>790</v>
       </c>
       <c r="J37" s="22" t="s">
@@ -11404,13 +11640,13 @@
         <v>30</v>
       </c>
       <c r="C38" s="22" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D38" s="22" t="s">
         <v>1212</v>
       </c>
-      <c r="D38" s="22" t="s">
+      <c r="E38" s="22" t="s">
         <v>1213</v>
-      </c>
-      <c r="E38" s="22" t="s">
-        <v>1214</v>
       </c>
       <c r="F38" s="23">
         <v>4</v>
@@ -11422,7 +11658,7 @@
         <v>35</v>
       </c>
       <c r="I38" s="23">
-        <f t="shared" si="0"/>
+        <f>G38-H38</f>
         <v>3065</v>
       </c>
       <c r="J38" s="22" t="s">
@@ -11453,13 +11689,13 @@
         <v>30</v>
       </c>
       <c r="C39" s="22" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D39" s="22" t="s">
         <v>1215</v>
       </c>
-      <c r="D39" s="22" t="s">
+      <c r="E39" s="22" t="s">
         <v>1216</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>1217</v>
       </c>
       <c r="F39" s="23">
         <v>5</v>
@@ -11471,7 +11707,7 @@
         <v>25</v>
       </c>
       <c r="I39" s="23">
-        <f t="shared" si="0"/>
+        <f>G39-H39</f>
         <v>-25</v>
       </c>
       <c r="J39" s="22" t="s">
@@ -11484,7 +11720,7 @@
         <v>1124</v>
       </c>
       <c r="M39" s="28" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="N39" s="22"/>
       <c r="O39" s="22"/>
@@ -11498,51 +11734,51 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G41" s="1">
-        <f t="shared" ref="G41:R41" si="2">SUBTOTAL(9,G3:G40)</f>
+        <f>SUBTOTAL(9,G3:G40)</f>
         <v>21370</v>
       </c>
       <c r="H41" s="1">
-        <f t="shared" si="2"/>
+        <f>SUBTOTAL(9,H3:H40)</f>
         <v>1030</v>
       </c>
       <c r="I41" s="1">
-        <f t="shared" si="2"/>
+        <f>SUBTOTAL(9,I3:I40)</f>
         <v>20340</v>
       </c>
       <c r="J41" s="1">
-        <f t="shared" si="2"/>
+        <f>SUBTOTAL(9,J3:J40)</f>
         <v>0</v>
       </c>
       <c r="K41" s="1">
-        <f t="shared" si="2"/>
+        <f>SUBTOTAL(9,K3:K40)</f>
         <v>0</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="2"/>
+        <f>SUBTOTAL(9,L3:L40)</f>
         <v>0</v>
       </c>
       <c r="M41" s="1">
-        <f t="shared" si="2"/>
+        <f>SUBTOTAL(9,M3:M40)</f>
         <v>0</v>
       </c>
       <c r="N41" s="1">
-        <f t="shared" si="2"/>
+        <f>SUBTOTAL(9,N3:N40)</f>
         <v>0</v>
       </c>
       <c r="O41" s="1">
-        <f t="shared" si="2"/>
+        <f>SUBTOTAL(9,O3:O40)</f>
         <v>0</v>
       </c>
       <c r="P41" s="1">
-        <f t="shared" si="2"/>
+        <f>SUBTOTAL(9,P3:P40)</f>
         <v>0</v>
       </c>
       <c r="Q41" s="1">
-        <f t="shared" si="2"/>
+        <f>SUBTOTAL(9,Q3:Q40)</f>
         <v>37</v>
       </c>
       <c r="R41" s="1">
-        <f t="shared" si="2"/>
+        <f>SUBTOTAL(9,R3:R40)</f>
         <v>450</v>
       </c>
     </row>
@@ -11647,13 +11883,13 @@
         <v>30</v>
       </c>
       <c r="B56" s="36" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C56" s="36" t="s">
         <v>1215</v>
       </c>
-      <c r="C56" s="36" t="s">
+      <c r="D56" s="36" t="s">
         <v>1216</v>
-      </c>
-      <c r="D56" s="36" t="s">
-        <v>1217</v>
       </c>
       <c r="E56" s="37">
         <v>5</v>
@@ -11665,7 +11901,7 @@
         <v>0</v>
       </c>
       <c r="H56" s="37">
-        <f t="shared" ref="H56" si="3">F56-G56</f>
+        <f t="shared" ref="H56" si="0">F56-G56</f>
         <v>775</v>
       </c>
       <c r="I56" s="36" t="s">
@@ -11678,7 +11914,7 @@
         <v>1124</v>
       </c>
       <c r="L56" s="28" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
   </sheetData>
@@ -11775,11 +12011,11 @@
         <v>30</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="D3" s="22"/>
       <c r="E3" s="22" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F3" s="23">
         <v>9</v>
@@ -11801,7 +12037,7 @@
         <v>34</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="22"/>
@@ -11817,13 +12053,13 @@
         <v>30</v>
       </c>
       <c r="C4" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D4" s="22" t="s">
         <v>1224</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="E4" s="22" t="s">
         <v>1225</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>1226</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>389</v>
@@ -11845,7 +12081,7 @@
         <v>34</v>
       </c>
       <c r="L4" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
@@ -11865,13 +12101,13 @@
         <v>30</v>
       </c>
       <c r="C5" s="22" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D5" s="22" t="s">
         <v>1227</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="E5" s="22" t="s">
         <v>1228</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>1229</v>
       </c>
       <c r="F5" s="23">
         <v>1</v>
@@ -11893,7 +12129,7 @@
         <v>34</v>
       </c>
       <c r="L5" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M5" s="22"/>
       <c r="N5" s="22"/>
@@ -11909,13 +12145,13 @@
         <v>30</v>
       </c>
       <c r="C6" s="22" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D6" s="22" t="s">
         <v>1230</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="E6" s="22" t="s">
         <v>1231</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>1232</v>
       </c>
       <c r="F6" s="23">
         <v>12</v>
@@ -11937,7 +12173,7 @@
         <v>34</v>
       </c>
       <c r="L6" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="22"/>
@@ -11957,13 +12193,13 @@
         <v>30</v>
       </c>
       <c r="C7" s="22" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>1233</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="E7" s="22" t="s">
         <v>1234</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>1235</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>108</v>
@@ -11985,7 +12221,7 @@
         <v>34</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M7" s="22"/>
       <c r="N7" s="22"/>
@@ -12001,13 +12237,13 @@
         <v>30</v>
       </c>
       <c r="C8" s="22" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>1236</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="E8" s="22" t="s">
         <v>1237</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>1238</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>90</v>
@@ -12029,7 +12265,7 @@
         <v>34</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M8" s="22"/>
       <c r="N8" s="22"/>
@@ -12045,10 +12281,10 @@
         <v>30</v>
       </c>
       <c r="C9" s="22" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>1239</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>1240</v>
       </c>
       <c r="E9" s="22" t="s">
         <v>486</v>
@@ -12073,7 +12309,7 @@
         <v>34</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -12093,13 +12329,13 @@
         <v>30</v>
       </c>
       <c r="C10" s="22" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>1241</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="E10" s="22" t="s">
         <v>1242</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>1243</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>90</v>
@@ -12121,7 +12357,7 @@
         <v>34</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M10" s="28" t="s">
         <v>180</v>
@@ -12146,10 +12382,10 @@
         <v>1101</v>
       </c>
       <c r="D11" s="22" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E11" s="22" t="s">
         <v>1244</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>1245</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>108</v>
@@ -12171,7 +12407,7 @@
         <v>34</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
@@ -12187,13 +12423,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="22" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D12" s="22" t="s">
         <v>1246</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="E12" s="22" t="s">
         <v>1247</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>1248</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>389</v>
@@ -12215,7 +12451,7 @@
         <v>34</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
@@ -12231,13 +12467,13 @@
         <v>30</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D13" s="22" t="s">
         <v>1249</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="E13" s="22" t="s">
         <v>1250</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>1251</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>108</v>
@@ -12259,7 +12495,7 @@
         <v>34</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M13" s="22"/>
       <c r="N13" s="22"/>
@@ -12275,13 +12511,13 @@
         <v>30</v>
       </c>
       <c r="C14" s="22" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>1252</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="E14" s="22" t="s">
         <v>1253</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>1254</v>
       </c>
       <c r="F14" s="22" t="s">
         <v>90</v>
@@ -12303,7 +12539,7 @@
         <v>34</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M14" s="22"/>
       <c r="N14" s="22"/>
@@ -12319,13 +12555,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>1255</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="E15" s="22" t="s">
         <v>1256</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>1257</v>
       </c>
       <c r="F15" s="22" t="s">
         <v>98</v>
@@ -12347,7 +12583,7 @@
         <v>34</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M15" s="22"/>
       <c r="N15" s="22"/>
@@ -12363,13 +12599,13 @@
         <v>30</v>
       </c>
       <c r="C16" s="22" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D16" s="22" t="s">
         <v>1258</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="E16" s="22" t="s">
         <v>1259</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>1260</v>
       </c>
       <c r="F16" s="22" t="s">
         <v>94</v>
@@ -12391,7 +12627,7 @@
         <v>34</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M16" s="22"/>
       <c r="N16" s="22"/>
@@ -12407,13 +12643,13 @@
         <v>30</v>
       </c>
       <c r="C17" s="22" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D17" s="22" t="s">
         <v>1261</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="E17" s="22" t="s">
         <v>1262</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>1263</v>
       </c>
       <c r="F17" s="23">
         <v>12</v>
@@ -12435,7 +12671,7 @@
         <v>34</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M17" s="22"/>
       <c r="N17" s="22"/>
@@ -12451,13 +12687,13 @@
         <v>30</v>
       </c>
       <c r="C18" s="22" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>1264</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="E18" s="22" t="s">
         <v>1265</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>1266</v>
       </c>
       <c r="F18" s="22" t="s">
         <v>108</v>
@@ -12479,7 +12715,7 @@
         <v>34</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M18" s="22"/>
       <c r="N18" s="22"/>
@@ -12497,11 +12733,11 @@
         <v>30</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="D19" s="22"/>
       <c r="E19" s="22" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="F19" s="22" t="s">
         <v>108</v>
@@ -12523,7 +12759,7 @@
         <v>34</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M19" s="22"/>
       <c r="N19" s="22"/>
@@ -12539,13 +12775,13 @@
         <v>30</v>
       </c>
       <c r="C20" s="22" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D20" s="22" t="s">
         <v>1269</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="E20" s="22" t="s">
         <v>1270</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>1271</v>
       </c>
       <c r="F20" s="23">
         <v>3</v>
@@ -12561,13 +12797,13 @@
         <v>840</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="K20" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
@@ -12583,13 +12819,13 @@
         <v>30</v>
       </c>
       <c r="C21" s="22" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D21" s="22" t="s">
         <v>1273</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="E21" s="22" t="s">
         <v>1274</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>1275</v>
       </c>
       <c r="F21" s="23">
         <v>8</v>
@@ -12605,13 +12841,13 @@
         <v>1860</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="K21" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M21" s="22"/>
       <c r="N21" s="22"/>
@@ -12627,13 +12863,13 @@
         <v>30</v>
       </c>
       <c r="C22" s="22" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D22" s="22" t="s">
         <v>1276</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="E22" s="22" t="s">
         <v>1277</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>1278</v>
       </c>
       <c r="F22" s="22" t="s">
         <v>59</v>
@@ -12649,13 +12885,13 @@
         <v>790</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="K22" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M22" s="22"/>
       <c r="N22" s="22"/>
@@ -12671,13 +12907,13 @@
         <v>30</v>
       </c>
       <c r="C23" s="22" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D23" s="22" t="s">
         <v>1279</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="E23" s="22" t="s">
         <v>1280</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>1281</v>
       </c>
       <c r="F23" s="23">
         <v>4</v>
@@ -12693,13 +12929,13 @@
         <v>870</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="K23" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M23" s="22"/>
       <c r="N23" s="22"/>
@@ -12715,13 +12951,13 @@
         <v>30</v>
       </c>
       <c r="C24" s="22" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D24" s="22" t="s">
         <v>1282</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="E24" s="22" t="s">
         <v>1283</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>1284</v>
       </c>
       <c r="F24" s="23">
         <v>8</v>
@@ -12737,13 +12973,13 @@
         <v>-30</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="K24" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M24" s="22"/>
       <c r="N24" s="22"/>
@@ -12766,7 +13002,7 @@
         <v>227</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="E25" s="22" t="s">
         <v>229</v>
@@ -12785,13 +13021,13 @@
         <v>1740</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="K25" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M25" s="22"/>
       <c r="N25" s="22"/>
@@ -12807,13 +13043,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="22" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D26" s="22" t="s">
         <v>1286</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="E26" s="22" t="s">
         <v>1287</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>1288</v>
       </c>
       <c r="F26" s="22" t="s">
         <v>147</v>
@@ -12829,13 +13065,13 @@
         <v>780</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="K26" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L26" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M26" s="22"/>
       <c r="N26" s="22"/>
@@ -12854,7 +13090,7 @@
         <v>277</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="E27" s="22" t="s">
         <v>279</v>
@@ -12873,13 +13109,13 @@
         <v>780</v>
       </c>
       <c r="J27" s="22" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="K27" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M27" s="22"/>
       <c r="N27" s="22"/>
@@ -12895,13 +13131,13 @@
         <v>30</v>
       </c>
       <c r="C28" s="22" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D28" s="22" t="s">
         <v>1290</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="E28" s="22" t="s">
         <v>1291</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>1292</v>
       </c>
       <c r="F28" s="22" t="s">
         <v>39</v>
@@ -12917,13 +13153,13 @@
         <v>660</v>
       </c>
       <c r="J28" s="22" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="K28" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L28" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
@@ -12939,13 +13175,13 @@
         <v>30</v>
       </c>
       <c r="C29" s="22" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D29" s="22" t="s">
         <v>1293</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="E29" s="22" t="s">
         <v>1294</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>1295</v>
       </c>
       <c r="F29" s="23">
         <v>7</v>
@@ -12961,13 +13197,13 @@
         <v>1390</v>
       </c>
       <c r="J29" s="22" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="K29" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L29" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M29" s="22"/>
       <c r="N29" s="22"/>
@@ -12983,13 +13219,13 @@
         <v>30</v>
       </c>
       <c r="C30" s="22" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D30" s="22" t="s">
         <v>1296</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="E30" s="22" t="s">
         <v>1297</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>1298</v>
       </c>
       <c r="F30" s="23">
         <v>6</v>
@@ -13005,13 +13241,13 @@
         <v>-25</v>
       </c>
       <c r="J30" s="22" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="K30" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L30" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M30" s="22"/>
       <c r="N30" s="22"/>
@@ -13031,13 +13267,13 @@
         <v>30</v>
       </c>
       <c r="C31" s="22" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D31" s="22" t="s">
         <v>1299</v>
       </c>
-      <c r="D31" s="22" t="s">
+      <c r="E31" s="22" t="s">
         <v>1300</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>1301</v>
       </c>
       <c r="F31" s="22" t="s">
         <v>39</v>
@@ -13053,13 +13289,13 @@
         <v>-30</v>
       </c>
       <c r="J31" s="22" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="K31" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L31" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M31" s="22"/>
       <c r="N31" s="22"/>
@@ -13079,13 +13315,13 @@
         <v>30</v>
       </c>
       <c r="C32" s="22" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D32" s="22" t="s">
         <v>1302</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="E32" s="22" t="s">
         <v>1303</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>1304</v>
       </c>
       <c r="F32" s="22" t="s">
         <v>39</v>
@@ -13101,13 +13337,13 @@
         <v>1360</v>
       </c>
       <c r="J32" s="22" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="K32" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L32" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M32" s="22"/>
       <c r="N32" s="22"/>
@@ -13123,13 +13359,13 @@
         <v>30</v>
       </c>
       <c r="C33" s="22" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D33" s="22" t="s">
         <v>1305</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="E33" s="22" t="s">
         <v>1306</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>1307</v>
       </c>
       <c r="F33" s="23">
         <v>7</v>
@@ -13145,13 +13381,13 @@
         <v>1600</v>
       </c>
       <c r="J33" s="22" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="K33" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L33" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M33" s="22"/>
       <c r="N33" s="22"/>
@@ -13167,13 +13403,13 @@
         <v>30</v>
       </c>
       <c r="C34" s="22" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D34" s="22" t="s">
         <v>1308</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="E34" s="22" t="s">
         <v>1309</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>1310</v>
       </c>
       <c r="F34" s="23">
         <v>10</v>
@@ -13189,13 +13425,13 @@
         <v>790</v>
       </c>
       <c r="J34" s="22" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="K34" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L34" s="22" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M34" s="22"/>
       <c r="N34" s="22"/>
@@ -13380,7 +13616,7 @@
         <v>717</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -13440,13 +13676,13 @@
         <v>30</v>
       </c>
       <c r="C3" s="22" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>1313</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="E3" s="22" t="s">
         <v>1314</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>1315</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>39</v>
@@ -13462,16 +13698,16 @@
         <v>-30</v>
       </c>
       <c r="J3" s="22" t="s">
+        <v>1315</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
         <v>1316</v>
       </c>
-      <c r="K3" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="22" t="s">
+      <c r="M3" s="28" t="s">
         <v>1317</v>
-      </c>
-      <c r="M3" s="28" t="s">
-        <v>1318</v>
       </c>
       <c r="N3" s="22"/>
       <c r="O3" s="22"/>
@@ -13490,13 +13726,13 @@
         <v>30</v>
       </c>
       <c r="C4" s="22" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D4" s="22" t="s">
         <v>1319</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="E4" s="22" t="s">
         <v>1320</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>1321</v>
       </c>
       <c r="F4" s="23">
         <v>8</v>
@@ -13512,13 +13748,13 @@
         <v>-25</v>
       </c>
       <c r="J4" s="22" t="s">
+        <v>1315</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
         <v>1316</v>
-      </c>
-      <c r="K4" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="22" t="s">
-        <v>1317</v>
       </c>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
@@ -13538,16 +13774,16 @@
         <v>30</v>
       </c>
       <c r="C5" s="22" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D5" s="22" t="s">
         <v>1322</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="E5" s="22" t="s">
         <v>1323</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="F5" s="22" t="s">
         <v>1324</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>1325</v>
       </c>
       <c r="G5" s="23">
         <v>865</v>
@@ -13560,13 +13796,13 @@
         <v>830</v>
       </c>
       <c r="J5" s="22" t="s">
+        <v>1315</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
         <v>1316</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>1317</v>
       </c>
       <c r="M5" s="22"/>
       <c r="N5" s="22"/>
@@ -13582,13 +13818,13 @@
         <v>30</v>
       </c>
       <c r="C6" s="22" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D6" s="22" t="s">
         <v>1326</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="E6" s="22" t="s">
         <v>1327</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>1328</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>152</v>
@@ -13604,13 +13840,13 @@
         <v>1100</v>
       </c>
       <c r="J6" s="22" t="s">
+        <v>1315</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
         <v>1316</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>1317</v>
       </c>
       <c r="M6" s="28" t="s">
         <v>1049</v>
@@ -13632,13 +13868,13 @@
         <v>30</v>
       </c>
       <c r="C7" s="22" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>1329</v>
       </c>
-      <c r="D7" s="22" t="s">
-        <v>1330</v>
-      </c>
       <c r="E7" s="22" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>152</v>
@@ -13654,13 +13890,13 @@
         <v>0</v>
       </c>
       <c r="J7" s="22" t="s">
+        <v>1315</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
         <v>1316</v>
-      </c>
-      <c r="K7" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="22" t="s">
-        <v>1317</v>
       </c>
       <c r="M7" s="28" t="s">
         <v>360</v>
@@ -13682,13 +13918,13 @@
         <v>30</v>
       </c>
       <c r="C8" s="22" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>1331</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="E8" s="22" t="s">
         <v>1332</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>1333</v>
       </c>
       <c r="F8" s="23">
         <v>11</v>
@@ -13704,13 +13940,13 @@
         <v>1110</v>
       </c>
       <c r="J8" s="22" t="s">
+        <v>1315</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
         <v>1316</v>
-      </c>
-      <c r="K8" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>1317</v>
       </c>
       <c r="M8" s="22"/>
       <c r="N8" s="22"/>
@@ -13726,13 +13962,13 @@
         <v>30</v>
       </c>
       <c r="C9" s="22" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>1334</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="E9" s="22" t="s">
         <v>1335</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>1336</v>
       </c>
       <c r="F9" s="23">
         <v>7</v>
@@ -13748,13 +13984,13 @@
         <v>440</v>
       </c>
       <c r="J9" s="22" t="s">
+        <v>1315</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
         <v>1316</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="22" t="s">
-        <v>1317</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -13770,13 +14006,13 @@
         <v>30</v>
       </c>
       <c r="C10" s="22" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>1337</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="E10" s="22" t="s">
         <v>1338</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>1339</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>59</v>
@@ -13792,13 +14028,13 @@
         <v>960</v>
       </c>
       <c r="J10" s="22" t="s">
+        <v>1315</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
         <v>1316</v>
-      </c>
-      <c r="K10" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10" s="22" t="s">
-        <v>1317</v>
       </c>
       <c r="M10" s="28" t="s">
         <v>360</v>
@@ -13816,13 +14052,13 @@
         <v>30</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D11" s="22" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E11" s="22" t="s">
         <v>1340</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>1341</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>59</v>
@@ -13838,13 +14074,13 @@
         <v>850</v>
       </c>
       <c r="J11" s="22" t="s">
+        <v>1315</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
         <v>1316</v>
-      </c>
-      <c r="K11" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L11" s="22" t="s">
-        <v>1317</v>
       </c>
       <c r="M11" s="28" t="s">
         <v>360</v>
@@ -13862,13 +14098,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="22" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D12" s="22" t="s">
         <v>1342</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="E12" s="22" t="s">
         <v>1343</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>1344</v>
       </c>
       <c r="F12" s="23">
         <v>8</v>
@@ -13884,16 +14120,16 @@
         <v>-30</v>
       </c>
       <c r="J12" s="22" t="s">
+        <v>1315</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
         <v>1316</v>
       </c>
-      <c r="K12" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L12" s="22" t="s">
-        <v>1317</v>
-      </c>
       <c r="M12" s="28" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="N12" s="22"/>
       <c r="O12" s="22"/>
@@ -13912,13 +14148,13 @@
         <v>30</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D13" s="22" t="s">
         <v>1346</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="E13" s="22" t="s">
         <v>1347</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>1348</v>
       </c>
       <c r="F13" s="23">
         <v>7</v>
@@ -13934,13 +14170,13 @@
         <v>820</v>
       </c>
       <c r="J13" s="22" t="s">
+        <v>1315</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
         <v>1316</v>
-      </c>
-      <c r="K13" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L13" s="22" t="s">
-        <v>1317</v>
       </c>
       <c r="M13" s="22"/>
       <c r="N13" s="22"/>
@@ -13956,13 +14192,13 @@
         <v>30</v>
       </c>
       <c r="C14" s="22" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>1349</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="E14" s="22" t="s">
         <v>1350</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>1351</v>
       </c>
       <c r="F14" s="23">
         <v>7</v>
@@ -13978,13 +14214,13 @@
         <v>790</v>
       </c>
       <c r="J14" s="22" t="s">
+        <v>1315</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
         <v>1316</v>
-      </c>
-      <c r="K14" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L14" s="22" t="s">
-        <v>1317</v>
       </c>
       <c r="M14" s="22"/>
       <c r="N14" s="22"/>
@@ -14000,13 +14236,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>1352</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="E15" s="22" t="s">
         <v>1353</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>1354</v>
       </c>
       <c r="F15" s="23">
         <v>11</v>
@@ -14022,13 +14258,13 @@
         <v>1480</v>
       </c>
       <c r="J15" s="22" t="s">
+        <v>1315</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
         <v>1316</v>
-      </c>
-      <c r="K15" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L15" s="22" t="s">
-        <v>1317</v>
       </c>
       <c r="M15" s="22"/>
       <c r="N15" s="22"/>
@@ -14047,10 +14283,10 @@
         <v>730</v>
       </c>
       <c r="D16" s="22" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E16" s="22" t="s">
         <v>1355</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>1356</v>
       </c>
       <c r="F16" s="22" t="s">
         <v>59</v>
@@ -14066,13 +14302,13 @@
         <v>700</v>
       </c>
       <c r="J16" s="22" t="s">
+        <v>1315</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
         <v>1316</v>
-      </c>
-      <c r="K16" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L16" s="22" t="s">
-        <v>1317</v>
       </c>
       <c r="M16" s="22"/>
       <c r="N16" s="22"/>
@@ -14088,13 +14324,13 @@
         <v>30</v>
       </c>
       <c r="C17" s="22" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D17" s="22" t="s">
         <v>1357</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="E17" s="22" t="s">
         <v>1358</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>1359</v>
       </c>
       <c r="F17" s="22" t="s">
         <v>90</v>
@@ -14116,7 +14352,7 @@
         <v>34</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M17" s="22"/>
       <c r="N17" s="22"/>
@@ -14135,7 +14371,7 @@
         <v>884</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E18" s="22" t="s">
         <v>244</v>
@@ -14160,7 +14396,7 @@
         <v>34</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M18" s="22"/>
       <c r="N18" s="22"/>
@@ -14183,10 +14419,10 @@
         <v>886</v>
       </c>
       <c r="D19" s="22" t="s">
+        <v>1360</v>
+      </c>
+      <c r="E19" s="22" t="s">
         <v>1361</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>1362</v>
       </c>
       <c r="F19" s="22" t="s">
         <v>94</v>
@@ -14208,7 +14444,7 @@
         <v>34</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M19" s="22"/>
       <c r="N19" s="22"/>
@@ -14224,13 +14460,13 @@
         <v>30</v>
       </c>
       <c r="C20" s="22" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D20" s="22" t="s">
         <v>1363</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="E20" s="22" t="s">
         <v>1364</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>1365</v>
       </c>
       <c r="F20" s="22" t="s">
         <v>98</v>
@@ -14252,7 +14488,7 @@
         <v>34</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
@@ -14268,13 +14504,13 @@
         <v>30</v>
       </c>
       <c r="C21" s="22" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D21" s="22" t="s">
         <v>1366</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="E21" s="22" t="s">
         <v>1367</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>1368</v>
       </c>
       <c r="F21" s="22" t="s">
         <v>94</v>
@@ -14296,7 +14532,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M21" s="22"/>
       <c r="N21" s="22"/>
@@ -14312,13 +14548,13 @@
         <v>30</v>
       </c>
       <c r="C22" s="22" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D22" s="22" t="s">
         <v>1369</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="E22" s="22" t="s">
         <v>1370</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>1371</v>
       </c>
       <c r="F22" s="23">
         <v>2</v>
@@ -14340,7 +14576,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M22" s="22"/>
       <c r="N22" s="22"/>
@@ -14359,7 +14595,7 @@
         <v>133</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="E23" s="22" t="s">
         <v>135</v>
@@ -14384,7 +14620,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M23" s="22"/>
       <c r="N23" s="22"/>
@@ -14400,10 +14636,10 @@
         <v>30</v>
       </c>
       <c r="C24" s="22" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D24" s="22" t="s">
         <v>1373</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>1374</v>
       </c>
       <c r="E24" s="22" t="s">
         <v>489</v>
@@ -14428,7 +14664,7 @@
         <v>34</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M24" s="22"/>
       <c r="N24" s="22"/>
@@ -14448,13 +14684,13 @@
         <v>30</v>
       </c>
       <c r="C25" s="22" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D25" s="22" t="s">
         <v>1375</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="E25" s="22" t="s">
         <v>1376</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>1377</v>
       </c>
       <c r="F25" s="22" t="s">
         <v>94</v>
@@ -14476,7 +14712,7 @@
         <v>34</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M25" s="22"/>
       <c r="N25" s="22"/>
@@ -14492,13 +14728,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="22" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D26" s="22" t="s">
         <v>1378</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="E26" s="22" t="s">
         <v>1379</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>1380</v>
       </c>
       <c r="F26" s="23">
         <v>12</v>
@@ -14520,7 +14756,7 @@
         <v>34</v>
       </c>
       <c r="L26" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M26" s="22"/>
       <c r="N26" s="22"/>
@@ -14536,13 +14772,13 @@
         <v>30</v>
       </c>
       <c r="C27" s="22" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D27" s="22" t="s">
         <v>1381</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="E27" s="22" t="s">
         <v>1382</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>1383</v>
       </c>
       <c r="F27" s="23">
         <v>2</v>
@@ -14564,7 +14800,7 @@
         <v>34</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M27" s="22"/>
       <c r="N27" s="22"/>
@@ -14582,11 +14818,11 @@
         <v>30</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="D28" s="22"/>
       <c r="E28" s="22" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F28" s="23">
         <v>12</v>
@@ -14608,7 +14844,7 @@
         <v>34</v>
       </c>
       <c r="L28" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
@@ -14656,7 +14892,7 @@
         <v>34</v>
       </c>
       <c r="L29" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M29" s="22"/>
       <c r="N29" s="22"/>
@@ -14678,7 +14914,7 @@
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="22" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F30" s="22" t="s">
         <v>90</v>
@@ -14700,7 +14936,7 @@
         <v>34</v>
       </c>
       <c r="L30" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M30" s="22"/>
       <c r="N30" s="22"/>
@@ -14744,7 +14980,7 @@
         <v>34</v>
       </c>
       <c r="L31" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M31" s="22"/>
       <c r="N31" s="22"/>
@@ -14760,13 +14996,13 @@
         <v>30</v>
       </c>
       <c r="C32" s="22" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D32" s="22" t="s">
         <v>1387</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="E32" s="22" t="s">
         <v>1388</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>1389</v>
       </c>
       <c r="F32" s="23">
         <v>1</v>
@@ -14788,7 +15024,7 @@
         <v>34</v>
       </c>
       <c r="L32" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M32" s="28" t="s">
         <v>360</v>
@@ -14810,13 +15046,13 @@
         <v>30</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="D33" s="22" t="s">
+        <v>1389</v>
+      </c>
+      <c r="E33" s="22" t="s">
         <v>1390</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>1391</v>
       </c>
       <c r="F33" s="23">
         <v>1</v>
@@ -14838,7 +15074,7 @@
         <v>34</v>
       </c>
       <c r="L33" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M33" s="28" t="s">
         <v>360</v>
@@ -14860,13 +15096,13 @@
         <v>30</v>
       </c>
       <c r="C34" s="22" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D34" s="22" t="s">
         <v>1392</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="E34" s="22" t="s">
         <v>1393</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>1394</v>
       </c>
       <c r="F34" s="22" t="s">
         <v>389</v>
@@ -14888,7 +15124,7 @@
         <v>34</v>
       </c>
       <c r="L34" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M34" s="22"/>
       <c r="N34" s="22"/>
@@ -14904,13 +15140,13 @@
         <v>30</v>
       </c>
       <c r="C35" s="22" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D35" s="22" t="s">
         <v>1395</v>
       </c>
-      <c r="D35" s="22" t="s">
+      <c r="E35" s="22" t="s">
         <v>1396</v>
-      </c>
-      <c r="E35" s="22" t="s">
-        <v>1397</v>
       </c>
       <c r="F35" s="23">
         <v>1</v>
@@ -14932,7 +15168,7 @@
         <v>34</v>
       </c>
       <c r="L35" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M35" s="22"/>
       <c r="N35" s="22"/>
@@ -14948,13 +15184,13 @@
         <v>30</v>
       </c>
       <c r="C36" s="22" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D36" s="22" t="s">
         <v>1398</v>
       </c>
-      <c r="D36" s="22" t="s">
+      <c r="E36" s="22" t="s">
         <v>1399</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>1400</v>
       </c>
       <c r="F36" s="23">
         <v>4</v>
@@ -14976,7 +15212,7 @@
         <v>34</v>
       </c>
       <c r="L36" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M36" s="22"/>
       <c r="N36" s="22"/>
@@ -14992,13 +15228,13 @@
         <v>30</v>
       </c>
       <c r="C37" s="22" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D37" s="22" t="s">
         <v>1401</v>
       </c>
-      <c r="D37" s="22" t="s">
+      <c r="E37" s="22" t="s">
         <v>1402</v>
-      </c>
-      <c r="E37" s="22" t="s">
-        <v>1403</v>
       </c>
       <c r="F37" s="23">
         <v>1</v>
@@ -15020,7 +15256,7 @@
         <v>34</v>
       </c>
       <c r="L37" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M37" s="22"/>
       <c r="N37" s="22"/>
@@ -15064,7 +15300,7 @@
         <v>34</v>
       </c>
       <c r="L38" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M38" s="22"/>
       <c r="N38" s="22"/>
@@ -15082,7 +15318,7 @@
         <v>30</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="D39" s="22"/>
       <c r="E39" s="22" t="s">
@@ -15108,7 +15344,7 @@
         <v>34</v>
       </c>
       <c r="L39" s="22" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M39" s="22"/>
       <c r="N39" s="22"/>
@@ -15185,12 +15421,12 @@
         <v>-2010</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="45" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H45" s="4" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="I45" s="5" t="s">
         <v>15</v>
@@ -15289,13 +15525,13 @@
         <v>30</v>
       </c>
       <c r="B56" s="36" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C56" s="36" t="s">
         <v>1313</v>
       </c>
-      <c r="C56" s="36" t="s">
+      <c r="D56" s="36" t="s">
         <v>1314</v>
-      </c>
-      <c r="D56" s="36" t="s">
-        <v>1315</v>
       </c>
       <c r="E56" s="37" t="s">
         <v>39</v>
@@ -15311,16 +15547,16 @@
         <v>4210</v>
       </c>
       <c r="I56" s="36" t="s">
+        <v>1315</v>
+      </c>
+      <c r="J56" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="K56" s="36" t="s">
         <v>1316</v>
       </c>
-      <c r="J56" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="K56" s="36" t="s">
+      <c r="L56" s="28" t="s">
         <v>1317</v>
-      </c>
-      <c r="L56" s="28" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -15328,13 +15564,13 @@
         <v>30</v>
       </c>
       <c r="B57" s="36" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C57" s="36" t="s">
         <v>1342</v>
       </c>
-      <c r="C57" s="36" t="s">
+      <c r="D57" s="36" t="s">
         <v>1343</v>
-      </c>
-      <c r="D57" s="36" t="s">
-        <v>1344</v>
       </c>
       <c r="E57" s="37">
         <v>8</v>
@@ -15350,16 +15586,16 @@
         <v>1820</v>
       </c>
       <c r="I57" s="36" t="s">
+        <v>1315</v>
+      </c>
+      <c r="J57" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="K57" s="36" t="s">
         <v>1316</v>
       </c>
-      <c r="J57" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="K57" s="36" t="s">
-        <v>1317</v>
-      </c>
       <c r="L57" s="28" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -15372,13 +15608,13 @@
         <v>30</v>
       </c>
       <c r="B59" s="36" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C59" s="36" t="s">
         <v>1405</v>
       </c>
-      <c r="C59" s="36" t="s">
+      <c r="D59" s="36" t="s">
         <v>1406</v>
-      </c>
-      <c r="D59" s="36" t="s">
-        <v>1407</v>
       </c>
       <c r="E59" s="37">
         <v>7</v>
@@ -15400,10 +15636,10 @@
         <v>34</v>
       </c>
       <c r="K59" s="36" t="s">
+        <v>1407</v>
+      </c>
+      <c r="L59" s="28" t="s">
         <v>1408</v>
-      </c>
-      <c r="L59" s="28" t="s">
-        <v>1409</v>
       </c>
     </row>
   </sheetData>
@@ -15438,7 +15674,7 @@
         <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -15498,13 +15734,13 @@
         <v>30</v>
       </c>
       <c r="C3" s="22" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>1413</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="E3" s="22" t="s">
         <v>1414</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>1415</v>
       </c>
       <c r="F3" s="23">
         <v>9</v>
@@ -15526,7 +15762,7 @@
         <v>34</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="22"/>
@@ -15542,13 +15778,13 @@
         <v>30</v>
       </c>
       <c r="C4" s="22" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D4" s="22" t="s">
         <v>1417</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="E4" s="22" t="s">
         <v>1418</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>1419</v>
       </c>
       <c r="F4" s="23">
         <v>9</v>
@@ -15570,7 +15806,7 @@
         <v>34</v>
       </c>
       <c r="L4" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
@@ -15608,13 +15844,13 @@
         <v>-30</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="K5" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L5" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M5" s="22"/>
       <c r="N5" s="22"/>
@@ -15634,13 +15870,13 @@
         <v>30</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="F6" s="26">
         <v>8</v>
@@ -15656,13 +15892,13 @@
         <v>350</v>
       </c>
       <c r="J6" s="25" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="K6" s="25" t="s">
         <v>34</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M6" s="25" t="s">
         <v>139</v>
@@ -15680,10 +15916,10 @@
         <v>30</v>
       </c>
       <c r="C7" s="22" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>1422</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>1423</v>
       </c>
       <c r="E7" s="22" t="s">
         <v>736</v>
@@ -15702,13 +15938,13 @@
         <v>-30</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="K7" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M7" s="22"/>
       <c r="N7" s="22"/>
@@ -15731,7 +15967,7 @@
         <v>1053</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="E8" s="22" t="s">
         <v>1055</v>
@@ -15750,13 +15986,13 @@
         <v>-30</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="K8" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M8" s="22"/>
       <c r="N8" s="22"/>
@@ -15776,13 +16012,13 @@
         <v>30</v>
       </c>
       <c r="C9" s="22" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>1425</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="E9" s="22" t="s">
         <v>1426</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>1427</v>
       </c>
       <c r="F9" s="23">
         <v>7</v>
@@ -15798,13 +16034,13 @@
         <v>-30</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="K9" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -15824,10 +16060,10 @@
         <v>30</v>
       </c>
       <c r="C10" s="22" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>1428</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>1429</v>
       </c>
       <c r="E10" s="22" t="s">
         <v>626</v>
@@ -15846,13 +16082,13 @@
         <v>-25</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="K10" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -15872,13 +16108,13 @@
         <v>30</v>
       </c>
       <c r="C11" s="22" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>1430</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="E11" s="22" t="s">
         <v>1431</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>1432</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>39</v>
@@ -15894,13 +16130,13 @@
         <v>-30</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="K11" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
@@ -15920,13 +16156,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="22" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D12" s="22" t="s">
         <v>1433</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="E12" s="22" t="s">
         <v>1434</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>1435</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>39</v>
@@ -15942,13 +16178,13 @@
         <v>-30</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="K12" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
@@ -15968,11 +16204,11 @@
         <v>30</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="D13" s="25"/>
       <c r="E13" s="25" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="F13" s="25" t="s">
         <v>152</v>
@@ -15988,13 +16224,13 @@
         <v>-35</v>
       </c>
       <c r="J13" s="25" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="K13" s="25" t="s">
         <v>34</v>
       </c>
       <c r="L13" s="25" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M13" s="25" t="s">
         <v>139</v>
@@ -16016,13 +16252,13 @@
         <v>30</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="D14" s="22" t="s">
+        <v>1437</v>
+      </c>
+      <c r="E14" s="22" t="s">
         <v>1438</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>1439</v>
       </c>
       <c r="F14" s="23">
         <v>8</v>
@@ -16038,13 +16274,13 @@
         <v>950</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="K14" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M14" s="22"/>
       <c r="N14" s="22"/>
@@ -16060,13 +16296,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>1440</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="E15" s="22" t="s">
         <v>1441</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>1442</v>
       </c>
       <c r="F15" s="23">
         <v>8</v>
@@ -16082,13 +16318,13 @@
         <v>350</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="K15" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M15" s="22"/>
       <c r="N15" s="22"/>
@@ -16104,13 +16340,13 @@
         <v>30</v>
       </c>
       <c r="C16" s="22" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D16" s="22" t="s">
         <v>1443</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="E16" s="22" t="s">
         <v>1444</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>1445</v>
       </c>
       <c r="F16" s="22" t="s">
         <v>152</v>
@@ -16126,13 +16362,13 @@
         <v>660</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M16" s="28" t="s">
         <v>360</v>
@@ -16150,13 +16386,13 @@
         <v>30</v>
       </c>
       <c r="C17" s="22" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D17" s="22" t="s">
         <v>1446</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="E17" s="22" t="s">
         <v>1447</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>1448</v>
       </c>
       <c r="F17" s="22" t="s">
         <v>152</v>
@@ -16172,13 +16408,13 @@
         <v>820</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="K17" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M17" s="28" t="s">
         <v>360</v>
@@ -16196,13 +16432,13 @@
         <v>30</v>
       </c>
       <c r="C18" s="22" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>1449</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="E18" s="22" t="s">
         <v>1450</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>1451</v>
       </c>
       <c r="F18" s="23">
         <v>7</v>
@@ -16218,13 +16454,13 @@
         <v>950</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="K18" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M18" s="22"/>
       <c r="N18" s="22"/>
@@ -16240,13 +16476,13 @@
         <v>30</v>
       </c>
       <c r="C19" s="22" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D19" s="22" t="s">
         <v>1452</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="E19" s="22" t="s">
         <v>1453</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>1454</v>
       </c>
       <c r="F19" s="23">
         <v>11</v>
@@ -16262,13 +16498,13 @@
         <v>960</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="K19" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M19" s="22"/>
       <c r="N19" s="22"/>
@@ -16286,7 +16522,7 @@
         <v>30</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="D20" s="22"/>
       <c r="E20" s="22" t="s">
@@ -16312,7 +16548,7 @@
         <v>34</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
@@ -16360,7 +16596,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M21" s="22"/>
       <c r="N21" s="22"/>
@@ -16378,11 +16614,11 @@
         <v>30</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="22" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F22" s="23">
         <v>12</v>
@@ -16404,7 +16640,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M22" s="22"/>
       <c r="N22" s="22"/>
@@ -16420,13 +16656,13 @@
         <v>30</v>
       </c>
       <c r="C23" s="22" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D23" s="22" t="s">
         <v>1456</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="E23" s="22" t="s">
         <v>1457</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>1458</v>
       </c>
       <c r="F23" s="23">
         <v>2</v>
@@ -16448,7 +16684,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M23" s="22"/>
       <c r="N23" s="22"/>
@@ -16467,7 +16703,7 @@
         <v>993</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="E24" s="22" t="s">
         <v>995</v>
@@ -16492,7 +16728,7 @@
         <v>34</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M24" s="22"/>
       <c r="N24" s="22"/>
@@ -16508,13 +16744,13 @@
         <v>30</v>
       </c>
       <c r="C25" s="22" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D25" s="22" t="s">
         <v>1460</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="E25" s="22" t="s">
         <v>1461</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>1462</v>
       </c>
       <c r="F25" s="23">
         <v>2</v>
@@ -16536,7 +16772,7 @@
         <v>34</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M25" s="22"/>
       <c r="N25" s="22"/>
@@ -16552,13 +16788,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="22" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D26" s="22" t="s">
         <v>1463</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="E26" s="22" t="s">
         <v>1464</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>1465</v>
       </c>
       <c r="F26" s="22" t="s">
         <v>94</v>
@@ -16580,7 +16816,7 @@
         <v>34</v>
       </c>
       <c r="L26" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M26" s="22"/>
       <c r="N26" s="22"/>
@@ -16600,13 +16836,13 @@
         <v>30</v>
       </c>
       <c r="C27" s="25" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D27" s="25" t="s">
         <v>1466</v>
       </c>
-      <c r="D27" s="25" t="s">
+      <c r="E27" s="25" t="s">
         <v>1467</v>
-      </c>
-      <c r="E27" s="25" t="s">
-        <v>1468</v>
       </c>
       <c r="F27" s="25" t="s">
         <v>90</v>
@@ -16628,7 +16864,7 @@
         <v>34</v>
       </c>
       <c r="L27" s="25" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M27" s="25" t="s">
         <v>139</v>
@@ -16646,13 +16882,13 @@
         <v>30</v>
       </c>
       <c r="C28" s="22" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D28" s="22" t="s">
         <v>1469</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="E28" s="22" t="s">
         <v>1470</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>1471</v>
       </c>
       <c r="F28" s="22" t="s">
         <v>98</v>
@@ -16674,7 +16910,7 @@
         <v>34</v>
       </c>
       <c r="L28" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
@@ -16693,10 +16929,10 @@
         <v>469</v>
       </c>
       <c r="D29" s="22" t="s">
+        <v>1471</v>
+      </c>
+      <c r="E29" s="22" t="s">
         <v>1472</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>1473</v>
       </c>
       <c r="F29" s="22" t="s">
         <v>90</v>
@@ -16718,7 +16954,7 @@
         <v>34</v>
       </c>
       <c r="L29" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M29" s="22"/>
       <c r="N29" s="22"/>
@@ -16738,13 +16974,13 @@
         <v>30</v>
       </c>
       <c r="C30" s="22" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D30" s="22" t="s">
         <v>1474</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="E30" s="22" t="s">
         <v>1475</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>1476</v>
       </c>
       <c r="F30" s="22" t="s">
         <v>90</v>
@@ -16766,7 +17002,7 @@
         <v>34</v>
       </c>
       <c r="L30" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M30" s="22"/>
       <c r="N30" s="22"/>
@@ -16782,13 +17018,13 @@
         <v>30</v>
       </c>
       <c r="C31" s="22" t="s">
+        <v>1476</v>
+      </c>
+      <c r="D31" s="22" t="s">
         <v>1477</v>
       </c>
-      <c r="D31" s="22" t="s">
+      <c r="E31" s="22" t="s">
         <v>1478</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>1479</v>
       </c>
       <c r="F31" s="22" t="s">
         <v>90</v>
@@ -16810,7 +17046,7 @@
         <v>34</v>
       </c>
       <c r="L31" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M31" s="22"/>
       <c r="N31" s="22"/>
@@ -16826,13 +17062,13 @@
         <v>30</v>
       </c>
       <c r="C32" s="22" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D32" s="22" t="s">
         <v>1480</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="E32" s="22" t="s">
         <v>1481</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>1482</v>
       </c>
       <c r="F32" s="22" t="s">
         <v>90</v>
@@ -16854,7 +17090,7 @@
         <v>34</v>
       </c>
       <c r="L32" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M32" s="22"/>
       <c r="N32" s="22"/>
@@ -16872,7 +17108,7 @@
         <v>30</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D33" s="22"/>
       <c r="E33" s="22" t="s">
@@ -16898,7 +17134,7 @@
         <v>34</v>
       </c>
       <c r="L33" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M33" s="22"/>
       <c r="N33" s="22"/>
@@ -16920,11 +17156,11 @@
         <v>30</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="D34" s="22"/>
       <c r="E34" s="22" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="F34" s="22" t="s">
         <v>108</v>
@@ -16946,7 +17182,7 @@
         <v>34</v>
       </c>
       <c r="L34" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M34" s="22"/>
       <c r="N34" s="22"/>
@@ -16962,13 +17198,13 @@
         <v>30</v>
       </c>
       <c r="C35" s="22" t="s">
+        <v>1485</v>
+      </c>
+      <c r="D35" s="22" t="s">
         <v>1486</v>
       </c>
-      <c r="D35" s="22" t="s">
+      <c r="E35" s="22" t="s">
         <v>1487</v>
-      </c>
-      <c r="E35" s="22" t="s">
-        <v>1488</v>
       </c>
       <c r="F35" s="22" t="s">
         <v>108</v>
@@ -16990,7 +17226,7 @@
         <v>34</v>
       </c>
       <c r="L35" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M35" s="22"/>
       <c r="N35" s="22"/>
@@ -17010,13 +17246,13 @@
         <v>30</v>
       </c>
       <c r="C36" s="22" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D36" s="22" t="s">
         <v>1489</v>
       </c>
-      <c r="D36" s="22" t="s">
+      <c r="E36" s="22" t="s">
         <v>1490</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>1491</v>
       </c>
       <c r="F36" s="23">
         <v>4</v>
@@ -17038,7 +17274,7 @@
         <v>34</v>
       </c>
       <c r="L36" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M36" s="22"/>
       <c r="N36" s="22"/>
@@ -17057,7 +17293,7 @@
         <v>595</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="E37" s="22" t="s">
         <v>597</v>
@@ -17082,7 +17318,7 @@
         <v>34</v>
       </c>
       <c r="L37" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M37" s="22"/>
       <c r="N37" s="22"/>
@@ -17098,13 +17334,13 @@
         <v>30</v>
       </c>
       <c r="C38" s="25" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D38" s="25" t="s">
         <v>1493</v>
       </c>
-      <c r="D38" s="25" t="s">
+      <c r="E38" s="25" t="s">
         <v>1494</v>
-      </c>
-      <c r="E38" s="25" t="s">
-        <v>1495</v>
       </c>
       <c r="F38" s="26">
         <v>3</v>
@@ -17126,7 +17362,7 @@
         <v>34</v>
       </c>
       <c r="L38" s="25" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M38" s="25" t="s">
         <v>139</v>
@@ -17144,13 +17380,13 @@
         <v>30</v>
       </c>
       <c r="C39" s="22" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D39" s="22" t="s">
         <v>1496</v>
       </c>
-      <c r="D39" s="22" t="s">
+      <c r="E39" s="22" t="s">
         <v>1497</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>1498</v>
       </c>
       <c r="F39" s="23">
         <v>1</v>
@@ -17172,7 +17408,7 @@
         <v>34</v>
       </c>
       <c r="L39" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M39" s="22"/>
       <c r="N39" s="22"/>
@@ -17188,13 +17424,13 @@
         <v>30</v>
       </c>
       <c r="C40" s="22" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D40" s="22" t="s">
         <v>1499</v>
       </c>
-      <c r="D40" s="22" t="s">
+      <c r="E40" s="22" t="s">
         <v>1500</v>
-      </c>
-      <c r="E40" s="22" t="s">
-        <v>1501</v>
       </c>
       <c r="F40" s="23">
         <v>3</v>
@@ -17216,7 +17452,7 @@
         <v>34</v>
       </c>
       <c r="L40" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M40" s="22"/>
       <c r="N40" s="22"/>
@@ -17232,13 +17468,13 @@
         <v>30</v>
       </c>
       <c r="C41" s="22" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D41" s="22" t="s">
         <v>1502</v>
       </c>
-      <c r="D41" s="22" t="s">
+      <c r="E41" s="22" t="s">
         <v>1503</v>
-      </c>
-      <c r="E41" s="22" t="s">
-        <v>1504</v>
       </c>
       <c r="F41" s="23">
         <v>1</v>
@@ -17260,7 +17496,7 @@
         <v>34</v>
       </c>
       <c r="L41" s="22" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M41" s="22"/>
       <c r="N41" s="22"/>
@@ -17322,7 +17558,7 @@
     </row>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H47" s="4" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="I47" s="5" t="s">
         <v>15</v>
@@ -17443,7 +17679,7 @@
         <v>266</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -17503,13 +17739,13 @@
         <v>30</v>
       </c>
       <c r="C3" s="22" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>1507</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="E3" s="22" t="s">
         <v>1508</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>1509</v>
       </c>
       <c r="F3" s="23">
         <v>9</v>
@@ -17531,7 +17767,7 @@
         <v>34</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="22"/>
@@ -17550,7 +17786,7 @@
         <v>314</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>316</v>
@@ -17569,13 +17805,13 @@
         <v>700</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="K4" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L4" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
@@ -17594,10 +17830,10 @@
         <v>831</v>
       </c>
       <c r="D5" s="22" t="s">
+        <v>1512</v>
+      </c>
+      <c r="E5" s="22" t="s">
         <v>1513</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>1514</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>59</v>
@@ -17613,13 +17849,13 @@
         <v>960</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="K5" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L5" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M5" s="22"/>
       <c r="N5" s="22"/>
@@ -17638,10 +17874,10 @@
         <v>737</v>
       </c>
       <c r="D6" s="22" t="s">
+        <v>1514</v>
+      </c>
+      <c r="E6" s="22" t="s">
         <v>1515</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>1516</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>108</v>
@@ -17657,13 +17893,13 @@
         <v>830</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="K6" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L6" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="22"/>
@@ -17679,13 +17915,13 @@
         <v>30</v>
       </c>
       <c r="C7" s="22" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>1517</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="E7" s="22" t="s">
         <v>1518</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>1519</v>
       </c>
       <c r="F7" s="23">
         <v>7</v>
@@ -17701,13 +17937,13 @@
         <v>820</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="K7" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M7" s="22"/>
       <c r="N7" s="22"/>
@@ -17723,13 +17959,13 @@
         <v>30</v>
       </c>
       <c r="C8" s="22" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>1520</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="E8" s="22" t="s">
         <v>1521</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>1522</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>59</v>
@@ -17745,13 +17981,13 @@
         <v>1090</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="K8" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M8" s="22"/>
       <c r="N8" s="22"/>
@@ -17767,10 +18003,10 @@
         <v>30</v>
       </c>
       <c r="C9" s="22" t="s">
+        <v>1522</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>1523</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>1524</v>
       </c>
       <c r="E9" s="22" t="s">
         <v>213</v>
@@ -17789,13 +18025,13 @@
         <v>-25</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="K9" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -17815,13 +18051,13 @@
         <v>30</v>
       </c>
       <c r="C10" s="22" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>1525</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="E10" s="22" t="s">
         <v>1526</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>1527</v>
       </c>
       <c r="F10" s="23">
         <v>7</v>
@@ -17837,13 +18073,13 @@
         <v>820</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="K10" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -17859,13 +18095,13 @@
         <v>30</v>
       </c>
       <c r="C11" s="22" t="s">
+        <v>1527</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>1528</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="E11" s="22" t="s">
         <v>1529</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>1530</v>
       </c>
       <c r="F11" s="23">
         <v>7</v>
@@ -17881,13 +18117,13 @@
         <v>350</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="K11" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
@@ -17903,13 +18139,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="22" t="s">
+        <v>1530</v>
+      </c>
+      <c r="D12" s="22" t="s">
         <v>1531</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="E12" s="22" t="s">
         <v>1532</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>1533</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>59</v>
@@ -17925,13 +18161,13 @@
         <v>-25</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="K12" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
@@ -17951,13 +18187,13 @@
         <v>30</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>1533</v>
+      </c>
+      <c r="D13" s="22" t="s">
         <v>1534</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="E13" s="22" t="s">
         <v>1535</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>1536</v>
       </c>
       <c r="F13" s="23">
         <v>6</v>
@@ -17973,13 +18209,13 @@
         <v>740</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="K13" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M13" s="22"/>
       <c r="N13" s="22"/>
@@ -17997,11 +18233,11 @@
         <v>30</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="22" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="F14" s="23">
         <v>6</v>
@@ -18017,13 +18253,13 @@
         <v>0</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="K14" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M14" s="22"/>
       <c r="N14" s="22"/>
@@ -18033,19 +18269,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="22"/>
       <c r="B15" s="22" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>1538</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>1539</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="E15" s="22" t="s">
         <v>1540</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>1541</v>
       </c>
       <c r="F15" s="22" t="s">
         <v>98</v>
@@ -18067,7 +18303,7 @@
         <v>34</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M15" s="22"/>
       <c r="N15" s="22"/>
@@ -18087,13 +18323,13 @@
         <v>30</v>
       </c>
       <c r="C16" s="22" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D16" s="22" t="s">
         <v>1542</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="E16" s="22" t="s">
         <v>1543</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>1544</v>
       </c>
       <c r="F16" s="22" t="s">
         <v>94</v>
@@ -18115,7 +18351,7 @@
         <v>34</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M16" s="22"/>
       <c r="N16" s="22"/>
@@ -18131,13 +18367,13 @@
         <v>30</v>
       </c>
       <c r="C17" s="22" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D17" s="22" t="s">
         <v>1545</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="E17" s="22" t="s">
         <v>1546</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>1547</v>
       </c>
       <c r="F17" s="22" t="s">
         <v>90</v>
@@ -18159,7 +18395,7 @@
         <v>34</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M17" s="22"/>
       <c r="N17" s="22"/>
@@ -18179,13 +18415,13 @@
         <v>30</v>
       </c>
       <c r="C18" s="22" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>1548</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="E18" s="22" t="s">
         <v>1549</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>1550</v>
       </c>
       <c r="F18" s="23">
         <v>2</v>
@@ -18207,7 +18443,7 @@
         <v>34</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M18" s="22"/>
       <c r="N18" s="22"/>
@@ -18223,13 +18459,13 @@
         <v>30</v>
       </c>
       <c r="C19" s="22" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D19" s="22" t="s">
         <v>1551</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="E19" s="22" t="s">
         <v>1552</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>1553</v>
       </c>
       <c r="F19" s="23">
         <v>2</v>
@@ -18251,7 +18487,7 @@
         <v>34</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M19" s="22"/>
       <c r="N19" s="22"/>
@@ -18271,13 +18507,13 @@
         <v>30</v>
       </c>
       <c r="C20" s="22" t="s">
+        <v>1553</v>
+      </c>
+      <c r="D20" s="22" t="s">
         <v>1554</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="E20" s="22" t="s">
         <v>1555</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>1556</v>
       </c>
       <c r="F20" s="22" t="s">
         <v>98</v>
@@ -18299,7 +18535,7 @@
         <v>34</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
@@ -18319,13 +18555,13 @@
         <v>30</v>
       </c>
       <c r="C21" s="22" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D21" s="22" t="s">
         <v>1557</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="E21" s="22" t="s">
         <v>1558</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>1559</v>
       </c>
       <c r="F21" s="22" t="s">
         <v>98</v>
@@ -18347,7 +18583,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M21" s="22"/>
       <c r="N21" s="22"/>
@@ -18370,7 +18606,7 @@
         <v>762</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="E22" s="22" t="s">
         <v>764</v>
@@ -18395,7 +18631,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M22" s="22"/>
       <c r="N22" s="22"/>
@@ -18413,11 +18649,11 @@
         <v>30</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D23" s="22"/>
       <c r="E23" s="22" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="F23" s="23">
         <v>12</v>
@@ -18439,7 +18675,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M23" s="22"/>
       <c r="N23" s="22"/>
@@ -18461,7 +18697,7 @@
         <v>30</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="D24" s="22"/>
       <c r="E24" s="22" t="s">
@@ -18487,7 +18723,7 @@
         <v>34</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M24" s="22"/>
       <c r="N24" s="22"/>
@@ -18510,10 +18746,10 @@
         <v>496</v>
       </c>
       <c r="D25" s="22" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E25" s="22" t="s">
         <v>1564</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>1565</v>
       </c>
       <c r="F25" s="22" t="s">
         <v>108</v>
@@ -18535,7 +18771,7 @@
         <v>34</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M25" s="22"/>
       <c r="N25" s="22"/>
@@ -18551,13 +18787,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="22" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D26" s="22" t="s">
         <v>1566</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="E26" s="22" t="s">
         <v>1567</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>1568</v>
       </c>
       <c r="F26" s="23">
         <v>10</v>
@@ -18579,7 +18815,7 @@
         <v>34</v>
       </c>
       <c r="L26" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M26" s="22"/>
       <c r="N26" s="22"/>
@@ -18598,7 +18834,7 @@
         <v>615</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="E27" s="25" t="s">
         <v>617</v>
@@ -18623,7 +18859,7 @@
         <v>34</v>
       </c>
       <c r="L27" s="25" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M27" s="25" t="s">
         <v>139</v>
@@ -18641,13 +18877,13 @@
         <v>30</v>
       </c>
       <c r="C28" s="22" t="s">
+        <v>1569</v>
+      </c>
+      <c r="D28" s="22" t="s">
         <v>1570</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="E28" s="22" t="s">
         <v>1571</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>1572</v>
       </c>
       <c r="F28" s="23">
         <v>5</v>
@@ -18669,7 +18905,7 @@
         <v>34</v>
       </c>
       <c r="L28" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
@@ -18691,11 +18927,11 @@
         <v>30</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="D29" s="22"/>
       <c r="E29" s="22" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="F29" s="22" t="s">
         <v>108</v>
@@ -18717,7 +18953,7 @@
         <v>34</v>
       </c>
       <c r="L29" s="22" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M29" s="22"/>
       <c r="N29" s="22"/>
@@ -18733,57 +18969,57 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G31" s="1">
-        <f>SUBTOTAL(9,G3:G30)</f>
+        <f t="shared" ref="G31:R31" si="4">SUBTOTAL(9,G3:G30)</f>
         <v>13575</v>
       </c>
       <c r="H31" s="1">
-        <f>SUBTOTAL(9,H3:H30)</f>
+        <f t="shared" si="4"/>
         <v>815</v>
       </c>
       <c r="I31" s="1">
-        <f>SUBTOTAL(9,I3:I30)</f>
+        <f t="shared" si="4"/>
         <v>12760</v>
       </c>
       <c r="J31" s="1">
-        <f>SUBTOTAL(9,J3:J30)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K31" s="1">
-        <f>SUBTOTAL(9,K3:K30)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L31" s="1">
-        <f>SUBTOTAL(9,L3:L30)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M31" s="1">
-        <f>SUBTOTAL(9,M3:M30)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N31" s="1">
-        <f>SUBTOTAL(9,N3:N30)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O31" s="1">
-        <f>SUBTOTAL(9,O3:O30)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P31" s="1">
-        <f>SUBTOTAL(9,P3:P30)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q31" s="1">
-        <f>SUBTOTAL(9,Q3:Q30)</f>
+        <f t="shared" si="4"/>
         <v>27</v>
       </c>
       <c r="R31" s="1">
-        <f>SUBTOTAL(9,R3:R30)</f>
+        <f t="shared" si="4"/>
         <v>360</v>
       </c>
     </row>
     <row r="35" spans="8:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H35" s="4" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>15</v>
@@ -18884,6 +19120,1665 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{990BEC2F-69A3-42F1-A9B2-FD77CE177594}">
+  <dimension ref="A1:R47"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F3" s="23">
+        <v>9</v>
+      </c>
+      <c r="G3" s="23">
+        <v>900</v>
+      </c>
+      <c r="H3" s="23">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I33" si="0">G3-H3</f>
+        <v>870</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>1578</v>
+      </c>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22" t="s">
+        <v>1579</v>
+      </c>
+      <c r="F4" s="23">
+        <v>6</v>
+      </c>
+      <c r="G4" s="23">
+        <v>0</v>
+      </c>
+      <c r="H4" s="23">
+        <v>30</v>
+      </c>
+      <c r="I4" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+      <c r="R4" s="24">
+        <f>H4</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>1581</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>1582</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F5" s="23">
+        <v>6</v>
+      </c>
+      <c r="G5" s="23">
+        <v>1875</v>
+      </c>
+      <c r="H5" s="23">
+        <v>25</v>
+      </c>
+      <c r="I5" s="23">
+        <f t="shared" si="0"/>
+        <v>1850</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>1584</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>1585</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>1586</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="23">
+        <v>895</v>
+      </c>
+      <c r="H6" s="23">
+        <v>25</v>
+      </c>
+      <c r="I6" s="23">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M6" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>1584</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>1587</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>1586</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="23">
+        <v>770</v>
+      </c>
+      <c r="H7" s="23">
+        <v>0</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M7" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>1589</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="23">
+        <v>810</v>
+      </c>
+      <c r="H8" s="23">
+        <v>30</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>1590</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>1591</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>1592</v>
+      </c>
+      <c r="F9" s="23">
+        <v>12</v>
+      </c>
+      <c r="G9" s="23">
+        <v>850</v>
+      </c>
+      <c r="H9" s="23">
+        <v>30</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>1593</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>1594</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>1595</v>
+      </c>
+      <c r="F10" s="23">
+        <v>7</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0</v>
+      </c>
+      <c r="H10" s="23">
+        <v>30</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+      <c r="R10" s="24">
+        <f>H10</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>1596</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>1597</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>1598</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="23">
+        <v>375</v>
+      </c>
+      <c r="H11" s="23">
+        <v>25</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>1601</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G12" s="23">
+        <v>825</v>
+      </c>
+      <c r="H12" s="23">
+        <v>35</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>1603</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="23">
+        <v>0</v>
+      </c>
+      <c r="H13" s="23">
+        <v>30</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+      <c r="R13" s="24">
+        <f>H13</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>1604</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>1605</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>1606</v>
+      </c>
+      <c r="F14" s="23">
+        <v>12</v>
+      </c>
+      <c r="G14" s="23">
+        <v>1530</v>
+      </c>
+      <c r="H14" s="23">
+        <v>30</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>1607</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>1609</v>
+      </c>
+      <c r="F15" s="23">
+        <v>7</v>
+      </c>
+      <c r="G15" s="23">
+        <v>1020</v>
+      </c>
+      <c r="H15" s="23">
+        <v>30</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>1611</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>1612</v>
+      </c>
+      <c r="F16" s="23">
+        <v>12</v>
+      </c>
+      <c r="G16" s="23">
+        <v>0</v>
+      </c>
+      <c r="H16" s="23">
+        <v>30</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+      <c r="R16" s="24">
+        <f>H16</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>1613</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G17" s="23">
+        <v>695</v>
+      </c>
+      <c r="H17" s="23">
+        <v>35</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>1614</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>1615</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>1616</v>
+      </c>
+      <c r="F18" s="23">
+        <v>7</v>
+      </c>
+      <c r="G18" s="23">
+        <v>2710</v>
+      </c>
+      <c r="H18" s="23">
+        <v>35</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>2675</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M18" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+      <c r="R18" s="24">
+        <f>H18</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>1617</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>1619</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G19" s="23">
+        <v>1685</v>
+      </c>
+      <c r="H19" s="23">
+        <v>35</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>1650</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>1621</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>1622</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20" s="23">
+        <v>855</v>
+      </c>
+      <c r="H20" s="23">
+        <v>25</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="23">
+        <v>30</v>
+      </c>
+      <c r="H21" s="23">
+        <v>30</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>351</v>
+      </c>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" s="23">
+        <v>0</v>
+      </c>
+      <c r="H22" s="23">
+        <v>30</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+      <c r="R22" s="24">
+        <f t="shared" ref="R22:R23" si="1">H22</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>1623</v>
+      </c>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22" t="s">
+        <v>1624</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G23" s="23">
+        <v>0</v>
+      </c>
+      <c r="H23" s="23">
+        <v>35</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+      <c r="R23" s="24">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>1625</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="23">
+        <v>595</v>
+      </c>
+      <c r="H24" s="23">
+        <v>25</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
+        <v>570</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M24" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22">
+        <v>1</v>
+      </c>
+      <c r="R24" s="24">
+        <f>H24</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>1630</v>
+      </c>
+      <c r="F25" s="23">
+        <v>1</v>
+      </c>
+      <c r="G25" s="23">
+        <v>0</v>
+      </c>
+      <c r="H25" s="23">
+        <v>25</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+      <c r="R25" s="24">
+        <f t="shared" ref="R25:R26" si="2">H25</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>788</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F26" s="23">
+        <v>1</v>
+      </c>
+      <c r="G26" s="23">
+        <v>0</v>
+      </c>
+      <c r="H26" s="23">
+        <v>25</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+      <c r="R26" s="24">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>1633</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>1634</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G27" s="23">
+        <v>25</v>
+      </c>
+      <c r="H27" s="23">
+        <v>25</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>1635</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>1636</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>1637</v>
+      </c>
+      <c r="F28" s="23">
+        <v>3</v>
+      </c>
+      <c r="G28" s="23">
+        <v>0</v>
+      </c>
+      <c r="H28" s="23">
+        <v>25</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22">
+        <v>1</v>
+      </c>
+      <c r="R28" s="24">
+        <f t="shared" ref="R28:R30" si="3">H28</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>1639</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>1640</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G29" s="23">
+        <v>0</v>
+      </c>
+      <c r="H29" s="23">
+        <v>25</v>
+      </c>
+      <c r="I29" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22">
+        <v>1</v>
+      </c>
+      <c r="R29" s="24">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>1642</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>1643</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="G30" s="23">
+        <v>0</v>
+      </c>
+      <c r="H30" s="23">
+        <v>20</v>
+      </c>
+      <c r="I30" s="23">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22">
+        <v>1</v>
+      </c>
+      <c r="R30" s="24">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>573</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>575</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="23">
+        <v>875</v>
+      </c>
+      <c r="H31" s="23">
+        <v>25</v>
+      </c>
+      <c r="I31" s="23">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J31" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K31" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>1646</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F32" s="23">
+        <v>1</v>
+      </c>
+      <c r="G32" s="23">
+        <v>1015</v>
+      </c>
+      <c r="H32" s="23">
+        <v>25</v>
+      </c>
+      <c r="I32" s="23">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J32" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K32" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L32" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>1649</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F33" s="23">
+        <v>3</v>
+      </c>
+      <c r="G33" s="23">
+        <v>915</v>
+      </c>
+      <c r="H33" s="23">
+        <v>25</v>
+      </c>
+      <c r="I33" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J33" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K33" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M33" s="22"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G35" s="1">
+        <f t="shared" ref="G35:R35" si="4">SUBTOTAL(9,G3:G34)</f>
+        <v>19250</v>
+      </c>
+      <c r="H35" s="1">
+        <f t="shared" si="4"/>
+        <v>850</v>
+      </c>
+      <c r="I35" s="1">
+        <f t="shared" si="4"/>
+        <v>18400</v>
+      </c>
+      <c r="J35" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M35" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N35" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O35" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P35" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="1">
+        <f t="shared" si="4"/>
+        <v>31</v>
+      </c>
+      <c r="R35" s="1">
+        <f t="shared" si="4"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I36" s="1">
+        <v>-2930</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H39" s="4" t="s">
+        <v>1504</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" s="8">
+        <f>SUM(I34:I38)</f>
+        <v>15470</v>
+      </c>
+      <c r="J40" s="8">
+        <f>Q35</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H41" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" s="10">
+        <f>R35</f>
+        <v>365</v>
+      </c>
+      <c r="J41" s="11"/>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H42" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" s="10">
+        <f>S34</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="11"/>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H43" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I43" s="10">
+        <f>T34</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="11"/>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H44" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I44" s="10">
+        <f>U34</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="11"/>
+    </row>
+    <row r="45" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H45" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I45" s="13"/>
+      <c r="J45" s="13"/>
+    </row>
+    <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H46" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
+    </row>
+    <row r="47" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H47" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" s="16">
+        <f>SUM(I40:I46)</f>
+        <v>15835</v>
+      </c>
+      <c r="J47" s="16">
+        <f>SUM(J40:J44)</f>
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P33" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P33">
+      <sortCondition ref="J2:J33"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D597EC-9F26-4C4B-8BF1-26CBB7F3ED40}">
   <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -18901,10 +20796,10 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>270</v>
+        <v>424</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1506</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -20057,7 +21952,7 @@
     </row>
     <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H62" s="4" t="s">
-        <v>1505</v>
+        <v>1575</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>15</v>

--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B921B2-B7B1-4B45-9D48-45CE135CD8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613B4BD7-E0FF-4B49-86B8-2F941BC6F0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-5" sheetId="3" r:id="rId1"/>
@@ -30,6 +30,9 @@
     <sheet name="19-5" sheetId="17" r:id="rId15"/>
     <sheet name="20-5" sheetId="19" r:id="rId16"/>
     <sheet name="21-5" sheetId="18" r:id="rId17"/>
+    <sheet name="22-5" sheetId="20" r:id="rId18"/>
+    <sheet name="23-5" sheetId="21" r:id="rId19"/>
+    <sheet name="25-5" sheetId="22" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'11-5'!$A$2:$P$58</definedName>
@@ -42,7 +45,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'18-5'!$A$2:$P$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'19-5'!$A$2:$P$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'20-5'!$A$2:$P$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'21-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'21-5'!$A$2:$P$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'22-5'!$A$2:$P$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'23-5'!$A$2:$P$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'25-5'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'4-5'!$A$2:$P$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'5-5'!$A$2:$P$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'6-5'!$A$2:$P$34</definedName>
@@ -71,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4915" uniqueCount="1653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5731" uniqueCount="1887">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -4861,9 +4867,6 @@
     <t>7g đường số 8 tân hưng</t>
   </si>
   <si>
-    <t>Vận</t>
-  </si>
-  <si>
     <t>HD022293</t>
   </si>
   <si>
@@ -5030,6 +5033,711 @@
   </si>
   <si>
     <t>HD020811</t>
+  </si>
+  <si>
+    <t>Lý Thanh Tâm</t>
+  </si>
+  <si>
+    <t>HD022564</t>
+  </si>
+  <si>
+    <t>71/6/16 lê tấn bê an lạc</t>
+  </si>
+  <si>
+    <t>AT 21-05</t>
+  </si>
+  <si>
+    <t>21-05-2026</t>
+  </si>
+  <si>
+    <t>Hana Le</t>
+  </si>
+  <si>
+    <t>HD022573</t>
+  </si>
+  <si>
+    <t>427/22 le van quoi binh tri dong A</t>
+  </si>
+  <si>
+    <t>Giap Anh Tuyet</t>
+  </si>
+  <si>
+    <t>HD022508</t>
+  </si>
+  <si>
+    <t>007 Lô B, Đường C6, Chung cư Tây Thạnh</t>
+  </si>
+  <si>
+    <t>Bùi Vĩ Thương</t>
+  </si>
+  <si>
+    <t>HD022636</t>
+  </si>
+  <si>
+    <t>3273 phạm thế hiển, p7</t>
+  </si>
+  <si>
+    <t>HD022628</t>
+  </si>
+  <si>
+    <t>Linh Ngô</t>
+  </si>
+  <si>
+    <t>HD022618</t>
+  </si>
+  <si>
+    <t>90 a lê lăng Phú thọ hoà</t>
+  </si>
+  <si>
+    <t>Lan Phạm</t>
+  </si>
+  <si>
+    <t>HD022621</t>
+  </si>
+  <si>
+    <t>685 âu cơ p tân thành - lô C</t>
+  </si>
+  <si>
+    <t>Phạm Thị Minh Tuyền</t>
+  </si>
+  <si>
+    <t>HD022341</t>
+  </si>
+  <si>
+    <t>352/4g lê văn quới, bình hưng hoà A</t>
+  </si>
+  <si>
+    <t>thuy vy</t>
+  </si>
+  <si>
+    <t>HD022620</t>
+  </si>
+  <si>
+    <t>chung cư Ruby - cổng 2, đường Tân Thắng, P. Tân Sơn Nhì</t>
+  </si>
+  <si>
+    <t>HD022604</t>
+  </si>
+  <si>
+    <t>HD022383</t>
+  </si>
+  <si>
+    <t>Nguyễn Yến Nhi</t>
+  </si>
+  <si>
+    <t>HD022491</t>
+  </si>
+  <si>
+    <t>Tháp v3 Chung cư sun rise city south 23 nguyễn hữu thọ tân hưng</t>
+  </si>
+  <si>
+    <t>Pé Thỏ</t>
+  </si>
+  <si>
+    <t>HD022455</t>
+  </si>
+  <si>
+    <t>1002 tạ quang bửu f6 Chung cư the pegasuite1 (zone1)</t>
+  </si>
+  <si>
+    <t>chủ mau - fb Hana Ngo</t>
+  </si>
+  <si>
+    <t>HD022615</t>
+  </si>
+  <si>
+    <t>67 Trang từ phường 14</t>
+  </si>
+  <si>
+    <t>Quỳnh Nhi</t>
+  </si>
+  <si>
+    <t>HD022493</t>
+  </si>
+  <si>
+    <t>180/1T QL1A Tân Phú</t>
+  </si>
+  <si>
+    <t>HD022342</t>
+  </si>
+  <si>
+    <t>320/14 nguyễn văn linh phường bình thuận</t>
+  </si>
+  <si>
+    <t>Nguyễn Thanh Ngân</t>
+  </si>
+  <si>
+    <t>HD022575</t>
+  </si>
+  <si>
+    <t>159c /18a dạ nam, chánh hưng</t>
+  </si>
+  <si>
+    <t>Huỳnh Mẫn</t>
+  </si>
+  <si>
+    <t>HD022522</t>
+  </si>
+  <si>
+    <t>1362 tỉnh lộ 10 tân tạo</t>
+  </si>
+  <si>
+    <t>Anh Trúc Huỳnh</t>
+  </si>
+  <si>
+    <t>HD022586</t>
+  </si>
+  <si>
+    <t>Số 64 dg 38 hiep binh chanh</t>
+  </si>
+  <si>
+    <t>BN182 miki chouchou Fb.</t>
+  </si>
+  <si>
+    <t>HD022533</t>
+  </si>
+  <si>
+    <t>163 Đường Trương Thị Hoa, phường Tân Thái Hiệp</t>
+  </si>
+  <si>
+    <t>HD022429</t>
+  </si>
+  <si>
+    <t>My Yến</t>
+  </si>
+  <si>
+    <t>HD022525</t>
+  </si>
+  <si>
+    <t>334/33/1C Chu văn an, phường 12</t>
+  </si>
+  <si>
+    <t>Hải Yến</t>
+  </si>
+  <si>
+    <t>HD003936</t>
+  </si>
+  <si>
+    <t>319/17 lê văn thọ p9</t>
+  </si>
+  <si>
+    <t>01우준</t>
+  </si>
+  <si>
+    <t>HD022601</t>
+  </si>
+  <si>
+    <t>Đảo kim cương phường bình trưng tây</t>
+  </si>
+  <si>
+    <t>HD022503</t>
+  </si>
+  <si>
+    <t>Toà Aster - Urban green (đối diện Vạn Phúc)</t>
+  </si>
+  <si>
+    <t>Khánh Thư Nguyen</t>
+  </si>
+  <si>
+    <t>HD022626</t>
+  </si>
+  <si>
+    <t>88 dien Hồng phường 1</t>
+  </si>
+  <si>
+    <t>Mỹ ý</t>
+  </si>
+  <si>
+    <t>HD022613</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Kim Hoàng</t>
+  </si>
+  <si>
+    <t>HD022430</t>
+  </si>
+  <si>
+    <t>265 Nơ Trang Long, phường Bình Lợi Trung</t>
+  </si>
+  <si>
+    <t>NHƯ- Khanh sale- airmy</t>
+  </si>
+  <si>
+    <t>HD022551</t>
+  </si>
+  <si>
+    <t>144C Trần Thị Trọng, Phường 15</t>
+  </si>
+  <si>
+    <t>PHƯƠNG DUNG</t>
+  </si>
+  <si>
+    <t>23/4A đường 48 khu phố 6 hiệp bình chánh</t>
+  </si>
+  <si>
+    <t>người nhận Hồng Sơn fb Duong Hyun</t>
+  </si>
+  <si>
+    <t>HD022495</t>
+  </si>
+  <si>
+    <t>135 Bạch Đằng, phường Tân Sơn Hòa (Phường 2) (CÔNG TY LÊ GIA EXPRESS)</t>
+  </si>
+  <si>
+    <t>Hoang Linh Le</t>
+  </si>
+  <si>
+    <t>HD022460</t>
+  </si>
+  <si>
+    <t>314 Điện Biên Phủ, Phường Vườn Lài</t>
+  </si>
+  <si>
+    <t>Chị Oanh</t>
+  </si>
+  <si>
+    <t>HD022599</t>
+  </si>
+  <si>
+    <t>291 hùng vương phương an đông</t>
+  </si>
+  <si>
+    <t>HD022442</t>
+  </si>
+  <si>
+    <t>Thuy Thuy</t>
+  </si>
+  <si>
+    <t>HD022451</t>
+  </si>
+  <si>
+    <t>58E cao thắng,p5 (Viện chăm sóc da aperio)</t>
+  </si>
+  <si>
+    <t>Sorinna items PhnomPenh ( Meng Kheang customer )</t>
+  </si>
+  <si>
+    <t>HD022445</t>
+  </si>
+  <si>
+    <t>301 phạm ngũ lão</t>
+  </si>
+  <si>
+    <t>Mỹ Vinh</t>
+  </si>
+  <si>
+    <t>HD022560</t>
+  </si>
+  <si>
+    <t>Aqua1 vinhome bason bến nghé</t>
+  </si>
+  <si>
+    <t>VVI EVA</t>
+  </si>
+  <si>
+    <t>141 Hùng Vương phường 4</t>
+  </si>
+  <si>
+    <t>NGAY 22-5</t>
+  </si>
+  <si>
+    <t>T6.22.5.2026</t>
+  </si>
+  <si>
+    <t>đơn trả 22.5</t>
+  </si>
+  <si>
+    <t>kh ck shop 375k</t>
+  </si>
+  <si>
+    <t>Vân</t>
+  </si>
+  <si>
+    <t>T7.23.5.2026</t>
+  </si>
+  <si>
+    <t>NGAY 23-5</t>
+  </si>
+  <si>
+    <t>HD022758</t>
+  </si>
+  <si>
+    <t>AT 22-05</t>
+  </si>
+  <si>
+    <t>22-05-2026</t>
+  </si>
+  <si>
+    <t>Trần Hương</t>
+  </si>
+  <si>
+    <t>HD022721</t>
+  </si>
+  <si>
+    <t>339 lê văn quới phường bình trị đông A</t>
+  </si>
+  <si>
+    <t>VTS-36588MNG</t>
+  </si>
+  <si>
+    <t>HD022692</t>
+  </si>
+  <si>
+    <t>kh ck shop 1710k</t>
+  </si>
+  <si>
+    <t>w3360</t>
+  </si>
+  <si>
+    <t>HD022791</t>
+  </si>
+  <si>
+    <t>624 Lê thị riêng,thới an</t>
+  </si>
+  <si>
+    <t>HD022655</t>
+  </si>
+  <si>
+    <t>Heng Roza</t>
+  </si>
+  <si>
+    <t>EV38382</t>
+  </si>
+  <si>
+    <t>315/18/6 Nguyễn Thị Tú, BHHB</t>
+  </si>
+  <si>
+    <t>Minh Hải zalo cẩm ngân</t>
+  </si>
+  <si>
+    <t>HD022896</t>
+  </si>
+  <si>
+    <t>Dung Dung</t>
+  </si>
+  <si>
+    <t>HD022794</t>
+  </si>
+  <si>
+    <t>125/191 nguyễn thị tần p2</t>
+  </si>
+  <si>
+    <t>Như Huỳnh</t>
+  </si>
+  <si>
+    <t>HD022787</t>
+  </si>
+  <si>
+    <t>16 đường 69 Tân Hưng</t>
+  </si>
+  <si>
+    <t>GUBY Fb Trương Ngọc</t>
+  </si>
+  <si>
+    <t>số 201/12 mã văn lò, P, bình trị đông a</t>
+  </si>
+  <si>
+    <t>HD022757</t>
+  </si>
+  <si>
+    <t>Nguyễn Chi</t>
+  </si>
+  <si>
+    <t>HD022759</t>
+  </si>
+  <si>
+    <t>51-53 duong số 57c f tân tạo</t>
+  </si>
+  <si>
+    <t>Ngọc Tiên</t>
+  </si>
+  <si>
+    <t>HD022897</t>
+  </si>
+  <si>
+    <t>59 trần hưng đạo p tân thành</t>
+  </si>
+  <si>
+    <t>HD022895</t>
+  </si>
+  <si>
+    <t>1123 quốc lộ la, tân tạo, chung cư an gia the star</t>
+  </si>
+  <si>
+    <t>Linh Chi Nguyễn</t>
+  </si>
+  <si>
+    <t>HD022915</t>
+  </si>
+  <si>
+    <t>54/24 đường 281 lý thường kiệt phường 15</t>
+  </si>
+  <si>
+    <t>HD022893</t>
+  </si>
+  <si>
+    <t>Diễm</t>
+  </si>
+  <si>
+    <t>HD022790</t>
+  </si>
+  <si>
+    <t>22/31/4 đường số 21, Phường 3</t>
+  </si>
+  <si>
+    <t>Nguyễn Loan</t>
+  </si>
+  <si>
+    <t>HD022726</t>
+  </si>
+  <si>
+    <t>91/33 nguyên hồng</t>
+  </si>
+  <si>
+    <t>HD022866</t>
+  </si>
+  <si>
+    <t>Hương Quỳnh (Nhượng)</t>
+  </si>
+  <si>
+    <t>HD022886</t>
+  </si>
+  <si>
+    <t>15/3 Lê Văn Huân, P13</t>
+  </si>
+  <si>
+    <t>Ivy Huyền</t>
+  </si>
+  <si>
+    <t>Số 5 Nhất Chi Mai phường 13</t>
+  </si>
+  <si>
+    <t>Đỗ Linh Chi</t>
+  </si>
+  <si>
+    <t>HD022673</t>
+  </si>
+  <si>
+    <t>86/36/3 Phố Quang, Phường Tân Sơn Hòa</t>
+  </si>
+  <si>
+    <t>Quỳnh Như</t>
+  </si>
+  <si>
+    <t>HD022888</t>
+  </si>
+  <si>
+    <t>66/68, Phổ Quang, Phường 2</t>
+  </si>
+  <si>
+    <t>Hạnh Hạnh</t>
+  </si>
+  <si>
+    <t>HD022865</t>
+  </si>
+  <si>
+    <t>334 tô hiến thành p14 Chung cư kingdom101 block a</t>
+  </si>
+  <si>
+    <t>Phạm Thùy Đan</t>
+  </si>
+  <si>
+    <t>HD022634</t>
+  </si>
+  <si>
+    <t>83/25b đường Hoà Hưng p12</t>
+  </si>
+  <si>
+    <t>Nguyễn Kim Ann</t>
+  </si>
+  <si>
+    <t>HD022824</t>
+  </si>
+  <si>
+    <t>NGAY 25-5</t>
+  </si>
+  <si>
+    <t>T2.25.5.2026</t>
+  </si>
+  <si>
+    <t>HD023055</t>
+  </si>
+  <si>
+    <t>AT 23-05</t>
+  </si>
+  <si>
+    <t>23-05-2026</t>
+  </si>
+  <si>
+    <t>HD023069</t>
+  </si>
+  <si>
+    <t>HD023108</t>
+  </si>
+  <si>
+    <t>41 Lê Quang Chiểu, Hiệp Tân</t>
+  </si>
+  <si>
+    <t>Lê Chi</t>
+  </si>
+  <si>
+    <t>HD023140</t>
+  </si>
+  <si>
+    <t>270 quốc lộ 50 p6</t>
+  </si>
+  <si>
+    <t>Cúc Phan</t>
+  </si>
+  <si>
+    <t>HD023112</t>
+  </si>
+  <si>
+    <t>A 12 liên ấp 1-2 vĩnh lộc b</t>
+  </si>
+  <si>
+    <t>HD023096</t>
+  </si>
+  <si>
+    <t>NGÂN HÀ</t>
+  </si>
+  <si>
+    <t>40 đường 53 p10</t>
+  </si>
+  <si>
+    <t>Bảo Như</t>
+  </si>
+  <si>
+    <t>HD023066</t>
+  </si>
+  <si>
+    <t>e208 nguyễn hữu cảnh p22 toà nhà landmark 3</t>
+  </si>
+  <si>
+    <t>HƯNG (hàng của Huyền Jendy)</t>
+  </si>
+  <si>
+    <t>HD023099</t>
+  </si>
+  <si>
+    <t>HD023121</t>
+  </si>
+  <si>
+    <t>624 Lê Thị Riêng, thới an</t>
+  </si>
+  <si>
+    <t>TONY ĐI ÚC</t>
+  </si>
+  <si>
+    <t>HD023116</t>
+  </si>
+  <si>
+    <t>965/16/11 QUANG TRUNG</t>
+  </si>
+  <si>
+    <t>HD022813</t>
+  </si>
+  <si>
+    <t>Ngọc Nhi</t>
+  </si>
+  <si>
+    <t>HD023141</t>
+  </si>
+  <si>
+    <t>92 nguyễn hữu cảnh p.22 (cc sg pearl toà sapphire 1)</t>
+  </si>
+  <si>
+    <t>HD023045</t>
+  </si>
+  <si>
+    <t>22/31/4 đường số 21, Phường 8 (phường Thông Tây Hội mới)</t>
+  </si>
+  <si>
+    <t>Trang Lê (note nhận đồ giúp chang)</t>
+  </si>
+  <si>
+    <t>HD023127</t>
+  </si>
+  <si>
+    <t>183/26 nguyễn hữu cảnh, f22</t>
+  </si>
+  <si>
+    <t>HÀ VY</t>
+  </si>
+  <si>
+    <t>482/10/26 nơ trang Long, p13</t>
+  </si>
+  <si>
+    <t>CAYLA</t>
+  </si>
+  <si>
+    <t>thanh (NHẬN HÀNG CHO TRÀ LY)</t>
+  </si>
+  <si>
+    <t>HD023142</t>
+  </si>
+  <si>
+    <t>404 VÕ VĂN TẦN</t>
+  </si>
+  <si>
+    <t>borameyyy</t>
+  </si>
+  <si>
+    <t>HD023106</t>
+  </si>
+  <si>
+    <t>Express M Village Nguyễn Du, Phòng 602</t>
+  </si>
+  <si>
+    <t>oanh fb Duong Tram</t>
+  </si>
+  <si>
+    <t>HD023118</t>
+  </si>
+  <si>
+    <t>346 bến vân đồn p1 Chung cư goldview a2</t>
+  </si>
+  <si>
+    <t>Trinh Trần</t>
+  </si>
+  <si>
+    <t>HD022990</t>
+  </si>
+  <si>
+    <t>22A truong dinh</t>
+  </si>
+  <si>
+    <t>HD023115</t>
+  </si>
+  <si>
+    <t>363 Hùng Vương, An Đông</t>
+  </si>
+  <si>
+    <t>Mai Chi</t>
+  </si>
+  <si>
+    <t>HD023061</t>
+  </si>
+  <si>
+    <t>215 nguyễn thị minh khai</t>
+  </si>
+  <si>
+    <t>Phương Trang</t>
+  </si>
+  <si>
+    <t>HD023132</t>
+  </si>
+  <si>
+    <t>189b/a29 công quỳnh phường nguyễn cư trinh</t>
+  </si>
+  <si>
+    <t>Như Ý Nguyễn</t>
+  </si>
+  <si>
+    <t>HD023113</t>
+  </si>
+  <si>
+    <t>24 Yên Thế, Phường 2</t>
   </si>
 </sst>
 </file>
@@ -5261,7 +5969,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -5341,6 +6049,8 @@
     <xf numFmtId="3" fontId="11" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="11" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10101,7 +10811,7 @@
         <v>30</v>
       </c>
       <c r="I3" s="23">
-        <f>G3-H3</f>
+        <f t="shared" ref="I3:I39" si="0">G3-H3</f>
         <v>950</v>
       </c>
       <c r="J3" s="22" t="s">
@@ -10144,7 +10854,7 @@
         <v>30</v>
       </c>
       <c r="I4" s="23">
-        <f>G4-H4</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J4" s="22" t="s">
@@ -10176,7 +10886,7 @@
         <v>1129</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="E5" s="22" t="s">
         <v>1130</v>
@@ -10191,7 +10901,7 @@
         <v>30</v>
       </c>
       <c r="I5" s="23">
-        <f>G5-H5</f>
+        <f t="shared" si="0"/>
         <v>780</v>
       </c>
       <c r="J5" s="22" t="s">
@@ -10234,7 +10944,7 @@
         <v>30</v>
       </c>
       <c r="I6" s="23">
-        <f>G6-H6</f>
+        <f t="shared" si="0"/>
         <v>1520</v>
       </c>
       <c r="J6" s="22" t="s">
@@ -10277,7 +10987,7 @@
         <v>25</v>
       </c>
       <c r="I7" s="23">
-        <f>G7-H7</f>
+        <f t="shared" si="0"/>
         <v>810</v>
       </c>
       <c r="J7" s="22" t="s">
@@ -10320,7 +11030,7 @@
         <v>30</v>
       </c>
       <c r="I8" s="23">
-        <f>G8-H8</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J8" s="22" t="s">
@@ -10367,7 +11077,7 @@
         <v>25</v>
       </c>
       <c r="I9" s="23">
-        <f>G9-H9</f>
+        <f t="shared" si="0"/>
         <v>780</v>
       </c>
       <c r="J9" s="22" t="s">
@@ -10410,7 +11120,7 @@
         <v>30</v>
       </c>
       <c r="I10" s="23">
-        <f>G10-H10</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J10" s="22" t="s">
@@ -10457,7 +11167,7 @@
         <v>30</v>
       </c>
       <c r="I11" s="23">
-        <f>G11-H11</f>
+        <f t="shared" si="0"/>
         <v>780</v>
       </c>
       <c r="J11" s="22" t="s">
@@ -10500,7 +11210,7 @@
         <v>30</v>
       </c>
       <c r="I12" s="23">
-        <f>G12-H12</f>
+        <f t="shared" si="0"/>
         <v>690</v>
       </c>
       <c r="J12" s="22" t="s">
@@ -10543,7 +11253,7 @@
         <v>25</v>
       </c>
       <c r="I13" s="23">
-        <f>G13-H13</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J13" s="22" t="s">
@@ -10590,7 +11300,7 @@
         <v>30</v>
       </c>
       <c r="I14" s="23">
-        <f>G14-H14</f>
+        <f t="shared" si="0"/>
         <v>780</v>
       </c>
       <c r="J14" s="22" t="s">
@@ -10633,7 +11343,7 @@
         <v>30</v>
       </c>
       <c r="I15" s="23">
-        <f>G15-H15</f>
+        <f t="shared" si="0"/>
         <v>720</v>
       </c>
       <c r="J15" s="22" t="s">
@@ -10676,7 +11386,7 @@
         <v>40</v>
       </c>
       <c r="I16" s="23">
-        <f>G16-H16</f>
+        <f t="shared" si="0"/>
         <v>-40</v>
       </c>
       <c r="J16" s="22" t="s">
@@ -10723,7 +11433,7 @@
         <v>30</v>
       </c>
       <c r="I17" s="23">
-        <f>G17-H17</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J17" s="22" t="s">
@@ -10766,7 +11476,7 @@
         <v>25</v>
       </c>
       <c r="I18" s="23">
-        <f>G18-H18</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J18" s="22" t="s">
@@ -10809,7 +11519,7 @@
         <v>30</v>
       </c>
       <c r="I19" s="23">
-        <f>G19-H19</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J19" s="22" t="s">
@@ -10856,7 +11566,7 @@
         <v>25</v>
       </c>
       <c r="I20" s="23">
-        <f>G20-H20</f>
+        <f t="shared" si="0"/>
         <v>1120</v>
       </c>
       <c r="J20" s="22" t="s">
@@ -10899,7 +11609,7 @@
         <v>30</v>
       </c>
       <c r="I21" s="23">
-        <f>G21-H21</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J21" s="22" t="s">
@@ -10946,7 +11656,7 @@
         <v>20</v>
       </c>
       <c r="I22" s="23">
-        <f>G22-H22</f>
+        <f t="shared" si="0"/>
         <v>640</v>
       </c>
       <c r="J22" s="22" t="s">
@@ -10989,7 +11699,7 @@
         <v>20</v>
       </c>
       <c r="I23" s="23">
-        <f>G23-H23</f>
+        <f t="shared" si="0"/>
         <v>780</v>
       </c>
       <c r="J23" s="22" t="s">
@@ -11032,7 +11742,7 @@
         <v>25</v>
       </c>
       <c r="I24" s="23">
-        <f>G24-H24</f>
+        <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="J24" s="22" t="s">
@@ -11075,7 +11785,7 @@
         <v>40</v>
       </c>
       <c r="I25" s="23">
-        <f>G25-H25</f>
+        <f t="shared" si="0"/>
         <v>-40</v>
       </c>
       <c r="J25" s="22" t="s">
@@ -11122,7 +11832,7 @@
         <v>30</v>
       </c>
       <c r="I26" s="23">
-        <f>G26-H26</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J26" s="22" t="s">
@@ -11169,7 +11879,7 @@
         <v>30</v>
       </c>
       <c r="I27" s="23">
-        <f>G27-H27</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J27" s="22" t="s">
@@ -11216,7 +11926,7 @@
         <v>25</v>
       </c>
       <c r="I28" s="23">
-        <f>G28-H28</f>
+        <f t="shared" si="0"/>
         <v>780</v>
       </c>
       <c r="J28" s="22" t="s">
@@ -11259,7 +11969,7 @@
         <v>25</v>
       </c>
       <c r="I29" s="23">
-        <f>G29-H29</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J29" s="22" t="s">
@@ -11306,7 +12016,7 @@
         <v>25</v>
       </c>
       <c r="I30" s="23">
-        <f>G30-H30</f>
+        <f t="shared" si="0"/>
         <v>1630</v>
       </c>
       <c r="J30" s="22" t="s">
@@ -11349,7 +12059,7 @@
         <v>25</v>
       </c>
       <c r="I31" s="23">
-        <f>G31-H31</f>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
       <c r="J31" s="22" t="s">
@@ -11392,7 +12102,7 @@
         <v>25</v>
       </c>
       <c r="I32" s="23">
-        <f>G32-H32</f>
+        <f t="shared" si="0"/>
         <v>1430</v>
       </c>
       <c r="J32" s="22" t="s">
@@ -11435,7 +12145,7 @@
         <v>25</v>
       </c>
       <c r="I33" s="23">
-        <f>G33-H33</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J33" s="22" t="s">
@@ -11482,7 +12192,7 @@
         <v>25</v>
       </c>
       <c r="I34" s="23">
-        <f>G34-H34</f>
+        <f t="shared" si="0"/>
         <v>690</v>
       </c>
       <c r="J34" s="22" t="s">
@@ -11525,7 +12235,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="23">
-        <f>G35-H35</f>
+        <f t="shared" si="0"/>
         <v>870</v>
       </c>
       <c r="J35" s="22" t="s">
@@ -11568,7 +12278,7 @@
         <v>25</v>
       </c>
       <c r="I36" s="23">
-        <f>G36-H36</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J36" s="22" t="s">
@@ -11615,7 +12325,7 @@
         <v>25</v>
       </c>
       <c r="I37" s="23">
-        <f>G37-H37</f>
+        <f t="shared" si="0"/>
         <v>790</v>
       </c>
       <c r="J37" s="22" t="s">
@@ -11658,7 +12368,7 @@
         <v>35</v>
       </c>
       <c r="I38" s="23">
-        <f>G38-H38</f>
+        <f t="shared" si="0"/>
         <v>3065</v>
       </c>
       <c r="J38" s="22" t="s">
@@ -11707,7 +12417,7 @@
         <v>25</v>
       </c>
       <c r="I39" s="23">
-        <f>G39-H39</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J39" s="22" t="s">
@@ -11734,51 +12444,51 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G41" s="1">
-        <f>SUBTOTAL(9,G3:G40)</f>
+        <f t="shared" ref="G41:R41" si="1">SUBTOTAL(9,G3:G40)</f>
         <v>21370</v>
       </c>
       <c r="H41" s="1">
-        <f>SUBTOTAL(9,H3:H40)</f>
+        <f t="shared" si="1"/>
         <v>1030</v>
       </c>
       <c r="I41" s="1">
-        <f>SUBTOTAL(9,I3:I40)</f>
+        <f t="shared" si="1"/>
         <v>20340</v>
       </c>
       <c r="J41" s="1">
-        <f>SUBTOTAL(9,J3:J40)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K41" s="1">
-        <f>SUBTOTAL(9,K3:K40)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L41" s="1">
-        <f>SUBTOTAL(9,L3:L40)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M41" s="1">
-        <f>SUBTOTAL(9,M3:M40)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N41" s="1">
-        <f>SUBTOTAL(9,N3:N40)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O41" s="1">
-        <f>SUBTOTAL(9,O3:O40)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P41" s="1">
-        <f>SUBTOTAL(9,P3:P40)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q41" s="1">
-        <f>SUBTOTAL(9,Q3:Q40)</f>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="R41" s="1">
-        <f>SUBTOTAL(9,R3:R40)</f>
+        <f t="shared" si="1"/>
         <v>450</v>
       </c>
     </row>
@@ -11901,7 +12611,7 @@
         <v>0</v>
       </c>
       <c r="H56" s="37">
-        <f t="shared" ref="H56" si="0">F56-G56</f>
+        <f t="shared" ref="H56" si="2">F56-G56</f>
         <v>775</v>
       </c>
       <c r="I56" s="36" t="s">
@@ -19564,13 +20274,13 @@
         <v>30</v>
       </c>
       <c r="C11" s="22" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>1596</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="E11" s="22" t="s">
         <v>1597</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>1598</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>59</v>
@@ -19608,13 +20318,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="22" t="s">
+        <v>1598</v>
+      </c>
+      <c r="D12" s="22" t="s">
         <v>1599</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="E12" s="22" t="s">
         <v>1600</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>1601</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>1324</v>
@@ -19652,10 +20362,10 @@
         <v>30</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>1601</v>
+      </c>
+      <c r="D13" s="22" t="s">
         <v>1602</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>1603</v>
       </c>
       <c r="E13" s="22" t="s">
         <v>1303</v>
@@ -19700,13 +20410,13 @@
         <v>30</v>
       </c>
       <c r="C14" s="22" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>1604</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="E14" s="22" t="s">
         <v>1605</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>1606</v>
       </c>
       <c r="F14" s="23">
         <v>12</v>
@@ -19744,13 +20454,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>1606</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>1607</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="E15" s="22" t="s">
         <v>1608</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>1609</v>
       </c>
       <c r="F15" s="23">
         <v>7</v>
@@ -19788,13 +20498,13 @@
         <v>30</v>
       </c>
       <c r="C16" s="22" t="s">
+        <v>1609</v>
+      </c>
+      <c r="D16" s="22" t="s">
         <v>1610</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="E16" s="22" t="s">
         <v>1611</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>1612</v>
       </c>
       <c r="F16" s="23">
         <v>12</v>
@@ -19839,7 +20549,7 @@
         <v>1442</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="E17" s="22" t="s">
         <v>1444</v>
@@ -19880,13 +20590,13 @@
         <v>30</v>
       </c>
       <c r="C18" s="22" t="s">
+        <v>1613</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>1614</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="E18" s="22" t="s">
         <v>1615</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>1616</v>
       </c>
       <c r="F18" s="23">
         <v>7</v>
@@ -19930,13 +20640,13 @@
         <v>30</v>
       </c>
       <c r="C19" s="22" t="s">
+        <v>1616</v>
+      </c>
+      <c r="D19" s="22" t="s">
         <v>1617</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="E19" s="22" t="s">
         <v>1618</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>1619</v>
       </c>
       <c r="F19" s="22" t="s">
         <v>152</v>
@@ -19974,13 +20684,13 @@
         <v>30</v>
       </c>
       <c r="C20" s="22" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D20" s="22" t="s">
         <v>1620</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="E20" s="22" t="s">
         <v>1621</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>1622</v>
       </c>
       <c r="F20" s="22" t="s">
         <v>59</v>
@@ -20112,11 +20822,11 @@
         <v>30</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="D23" s="22"/>
       <c r="E23" s="22" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="F23" s="22" t="s">
         <v>98</v>
@@ -20158,13 +20868,13 @@
         <v>30</v>
       </c>
       <c r="C24" s="22" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D24" s="22" t="s">
         <v>1625</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="E24" s="22" t="s">
         <v>1626</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>1627</v>
       </c>
       <c r="F24" s="22" t="s">
         <v>90</v>
@@ -20208,13 +20918,13 @@
         <v>30</v>
       </c>
       <c r="C25" s="22" t="s">
+        <v>1627</v>
+      </c>
+      <c r="D25" s="22" t="s">
         <v>1628</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="E25" s="22" t="s">
         <v>1629</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>1630</v>
       </c>
       <c r="F25" s="23">
         <v>1</v>
@@ -20259,10 +20969,10 @@
         <v>788</v>
       </c>
       <c r="D26" s="22" t="s">
+        <v>1630</v>
+      </c>
+      <c r="E26" s="22" t="s">
         <v>1631</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>1632</v>
       </c>
       <c r="F26" s="23">
         <v>1</v>
@@ -20307,10 +21017,10 @@
         <v>1101</v>
       </c>
       <c r="D27" s="22" t="s">
+        <v>1632</v>
+      </c>
+      <c r="E27" s="22" t="s">
         <v>1633</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>1634</v>
       </c>
       <c r="F27" s="22" t="s">
         <v>108</v>
@@ -20348,13 +21058,13 @@
         <v>30</v>
       </c>
       <c r="C28" s="22" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D28" s="22" t="s">
         <v>1635</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="E28" s="22" t="s">
         <v>1636</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>1637</v>
       </c>
       <c r="F28" s="23">
         <v>3</v>
@@ -20396,13 +21106,13 @@
         <v>30</v>
       </c>
       <c r="C29" s="22" t="s">
+        <v>1637</v>
+      </c>
+      <c r="D29" s="22" t="s">
         <v>1638</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="E29" s="22" t="s">
         <v>1639</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>1640</v>
       </c>
       <c r="F29" s="22" t="s">
         <v>108</v>
@@ -20444,13 +21154,13 @@
         <v>30</v>
       </c>
       <c r="C30" s="22" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D30" s="22" t="s">
         <v>1641</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="E30" s="22" t="s">
         <v>1642</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>1643</v>
       </c>
       <c r="F30" s="22" t="s">
         <v>389</v>
@@ -20495,7 +21205,7 @@
         <v>573</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="E31" s="22" t="s">
         <v>575</v>
@@ -20536,13 +21246,13 @@
         <v>30</v>
       </c>
       <c r="C32" s="22" t="s">
+        <v>1644</v>
+      </c>
+      <c r="D32" s="22" t="s">
         <v>1645</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="E32" s="22" t="s">
         <v>1646</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>1647</v>
       </c>
       <c r="F32" s="23">
         <v>1</v>
@@ -20580,13 +21290,13 @@
         <v>30</v>
       </c>
       <c r="C33" s="22" t="s">
+        <v>1647</v>
+      </c>
+      <c r="D33" s="22" t="s">
         <v>1648</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="E33" s="22" t="s">
         <v>1649</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>1650</v>
       </c>
       <c r="F33" s="23">
         <v>3</v>
@@ -20673,7 +21383,7 @@
         <v>-2930</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -20780,7 +21490,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D597EC-9F26-4C4B-8BF1-26CBB7F3ED40}">
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
@@ -20855,1196 +21565,4858 @@
     </row>
     <row r="3" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
+      <c r="B3" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="18">
+        <v>850</v>
+      </c>
+      <c r="H3" s="18">
+        <v>30</v>
+      </c>
+      <c r="I3" s="18">
+        <v>820</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M3" s="17"/>
       <c r="N3" s="17"/>
       <c r="O3" s="17"/>
       <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
+      <c r="Q3" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
+      <c r="B4" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="18">
+        <v>470</v>
+      </c>
+      <c r="H4" s="18">
+        <v>30</v>
+      </c>
+      <c r="I4" s="18">
+        <v>440</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M4" s="17"/>
       <c r="N4" s="17"/>
       <c r="O4" s="17"/>
       <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
+      <c r="Q4" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
+      <c r="B5" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>1662</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="18">
+        <v>0</v>
+      </c>
+      <c r="H5" s="18">
+        <v>25</v>
+      </c>
+      <c r="I5" s="18">
+        <v>-25</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M5" s="17"/>
       <c r="N5" s="17"/>
       <c r="O5" s="17"/>
       <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="20"/>
+      <c r="Q5" s="17">
+        <v>1</v>
+      </c>
+      <c r="R5" s="20">
+        <v>25</v>
+      </c>
     </row>
     <row r="6" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
+      <c r="B6" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>1663</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>1664</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F6" s="18">
+        <v>8</v>
+      </c>
+      <c r="G6" s="18">
+        <v>850</v>
+      </c>
+      <c r="H6" s="18">
+        <v>30</v>
+      </c>
+      <c r="I6" s="18">
+        <v>820</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M6" s="17"/>
       <c r="N6" s="17"/>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
+      <c r="Q6" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
+      <c r="B7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>831</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="18">
+        <v>915</v>
+      </c>
+      <c r="H7" s="18">
+        <v>25</v>
+      </c>
+      <c r="I7" s="18">
+        <v>890</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M7" s="17"/>
       <c r="N7" s="17"/>
       <c r="O7" s="17"/>
       <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
+      <c r="Q7" s="17">
+        <v>1</v>
+      </c>
       <c r="R7" s="20"/>
     </row>
     <row r="8" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
+      <c r="B8" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>1667</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="18">
+        <v>1855</v>
+      </c>
+      <c r="H8" s="18">
+        <v>25</v>
+      </c>
+      <c r="I8" s="18">
+        <v>1830</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M8" s="17"/>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
       <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
+      <c r="Q8" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
+      <c r="B9" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="18">
+        <v>795</v>
+      </c>
+      <c r="H9" s="18">
+        <v>25</v>
+      </c>
+      <c r="I9" s="18">
+        <v>770</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M9" s="17"/>
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
       <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
+      <c r="Q9" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
+      <c r="B10" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>1674</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>1675</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="18">
+        <v>1120</v>
+      </c>
+      <c r="H10" s="18">
+        <v>30</v>
+      </c>
+      <c r="I10" s="18">
+        <v>1090</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M10" s="21"/>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
       <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
+      <c r="Q10" s="17">
+        <v>1</v>
+      </c>
       <c r="R10" s="20"/>
     </row>
     <row r="11" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
+      <c r="B11" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>1677</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>1678</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="18">
+        <v>0</v>
+      </c>
+      <c r="H11" s="18">
+        <v>25</v>
+      </c>
+      <c r="I11" s="18">
+        <v>-25</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M11" s="17"/>
       <c r="N11" s="17"/>
       <c r="O11" s="17"/>
       <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="20"/>
+      <c r="Q11" s="17">
+        <v>1</v>
+      </c>
+      <c r="R11" s="20">
+        <v>25</v>
+      </c>
     </row>
     <row r="12" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
+      <c r="B12" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>1679</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>1323</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G12" s="18">
+        <v>775</v>
+      </c>
+      <c r="H12" s="18">
+        <v>35</v>
+      </c>
+      <c r="I12" s="18">
+        <v>740</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M12" s="17"/>
       <c r="N12" s="17"/>
       <c r="O12" s="17"/>
       <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
+      <c r="Q12" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
+      <c r="B13" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>1680</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>1291</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="18">
+        <v>710</v>
+      </c>
+      <c r="H13" s="18">
+        <v>30</v>
+      </c>
+      <c r="I13" s="18">
+        <v>680</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M13" s="17"/>
       <c r="N13" s="17"/>
       <c r="O13" s="17"/>
       <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
+      <c r="Q13" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
+      <c r="B14" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>1682</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>1683</v>
+      </c>
+      <c r="F14" s="17">
+        <v>7</v>
+      </c>
+      <c r="G14" s="18">
+        <v>520</v>
+      </c>
+      <c r="H14" s="18">
+        <v>30</v>
+      </c>
+      <c r="I14" s="18">
+        <v>490</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M14" s="17"/>
       <c r="N14" s="17"/>
       <c r="O14" s="17"/>
       <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
+      <c r="Q14" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
+      <c r="B15" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>1684</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F15" s="17">
+        <v>8</v>
+      </c>
+      <c r="G15" s="18">
+        <v>0</v>
+      </c>
+      <c r="H15" s="18">
+        <v>30</v>
+      </c>
+      <c r="I15" s="18">
+        <v>-30</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M15" s="17"/>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
       <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="20"/>
+      <c r="Q15" s="17">
+        <v>1</v>
+      </c>
+      <c r="R15" s="20">
+        <v>30</v>
+      </c>
     </row>
     <row r="16" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
+      <c r="B16" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>1687</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>1688</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>1689</v>
+      </c>
+      <c r="F16" s="17">
+        <v>5</v>
+      </c>
+      <c r="G16" s="18">
+        <v>0</v>
+      </c>
+      <c r="H16" s="18">
+        <v>25</v>
+      </c>
+      <c r="I16" s="18">
+        <v>-25</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M16" s="17"/>
       <c r="N16" s="17"/>
       <c r="O16" s="17"/>
       <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="20"/>
+      <c r="Q16" s="17">
+        <v>1</v>
+      </c>
+      <c r="R16" s="20">
+        <v>25</v>
+      </c>
     </row>
     <row r="17" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>1690</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>1691</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>1692</v>
+      </c>
+      <c r="F17" s="17">
+        <v>9</v>
+      </c>
+      <c r="G17" s="18">
+        <v>520</v>
+      </c>
+      <c r="H17" s="18">
+        <v>30</v>
+      </c>
+      <c r="I17" s="18">
+        <v>490</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M17" s="17"/>
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
       <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
+      <c r="Q17" s="17">
+        <v>1</v>
+      </c>
       <c r="R17" s="20"/>
     </row>
     <row r="18" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
+      <c r="B18" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>1693</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="F18" s="17">
+        <v>7</v>
+      </c>
+      <c r="G18" s="18">
+        <v>990</v>
+      </c>
+      <c r="H18" s="18">
+        <v>30</v>
+      </c>
+      <c r="I18" s="18">
+        <v>960</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M18" s="17"/>
       <c r="N18" s="17"/>
       <c r="O18" s="17"/>
       <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
+      <c r="Q18" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
+      <c r="B19" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>1695</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>1696</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>1697</v>
+      </c>
+      <c r="F19" s="17">
+        <v>8</v>
+      </c>
+      <c r="G19" s="18">
+        <v>1020</v>
+      </c>
+      <c r="H19" s="18">
+        <v>30</v>
+      </c>
+      <c r="I19" s="18">
+        <v>990</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M19" s="17"/>
       <c r="N19" s="17"/>
       <c r="O19" s="17"/>
       <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
+      <c r="Q19" s="17">
+        <v>1</v>
+      </c>
       <c r="R19" s="20"/>
     </row>
     <row r="20" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
+      <c r="B20" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>1698</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>1699</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="18">
+        <v>860</v>
+      </c>
+      <c r="H20" s="18">
+        <v>30</v>
+      </c>
+      <c r="I20" s="18">
+        <v>830</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M20" s="17"/>
       <c r="N20" s="17"/>
       <c r="O20" s="17"/>
       <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
+      <c r="Q20" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
+      <c r="A21" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>202</v>
+      </c>
       <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
+      <c r="E21" s="17" t="s">
+        <v>863</v>
+      </c>
+      <c r="F21" s="18">
+        <v>5</v>
+      </c>
+      <c r="G21" s="18">
+        <v>30</v>
+      </c>
+      <c r="H21" s="18">
+        <v>30</v>
+      </c>
+      <c r="I21" s="18">
+        <v>0</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M21" s="17"/>
       <c r="N21" s="17"/>
       <c r="O21" s="17"/>
       <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
+      <c r="Q21" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
+      <c r="B22" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>1702</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>1703</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22" s="18">
+        <v>1500</v>
+      </c>
+      <c r="H22" s="18">
+        <v>30</v>
+      </c>
+      <c r="I22" s="18">
+        <v>1470</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M22" s="17"/>
       <c r="N22" s="17"/>
       <c r="O22" s="17"/>
       <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
+      <c r="Q22" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
+      <c r="B23" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>1705</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>1706</v>
+      </c>
+      <c r="F23" s="18">
+        <v>12</v>
+      </c>
+      <c r="G23" s="18">
+        <v>0</v>
+      </c>
+      <c r="H23" s="18">
+        <v>30</v>
+      </c>
+      <c r="I23" s="18">
+        <v>-30</v>
+      </c>
+      <c r="J23" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M23" s="17"/>
       <c r="N23" s="17"/>
       <c r="O23" s="17"/>
       <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="20"/>
+      <c r="Q23" s="17">
+        <v>1</v>
+      </c>
+      <c r="R23" s="20">
+        <v>30</v>
+      </c>
     </row>
     <row r="24" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
+      <c r="B24" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>993</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>995</v>
+      </c>
+      <c r="F24" s="18">
+        <v>2</v>
+      </c>
+      <c r="G24" s="18">
+        <v>720</v>
+      </c>
+      <c r="H24" s="18">
+        <v>30</v>
+      </c>
+      <c r="I24" s="18">
+        <v>690</v>
+      </c>
+      <c r="J24" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M24" s="17"/>
       <c r="N24" s="17"/>
       <c r="O24" s="17"/>
       <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
+      <c r="Q24" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
+      <c r="B25" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>1708</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>1709</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>1710</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G25" s="18">
+        <v>510</v>
+      </c>
+      <c r="H25" s="18">
+        <v>20</v>
+      </c>
+      <c r="I25" s="18">
+        <v>490</v>
+      </c>
+      <c r="J25" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M25" s="17"/>
       <c r="N25" s="17"/>
       <c r="O25" s="17"/>
       <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
+      <c r="Q25" s="17">
+        <v>1</v>
+      </c>
       <c r="R25" s="20"/>
     </row>
     <row r="26" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
+      <c r="B26" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>1712</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>1713</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26" s="18">
+        <v>0</v>
+      </c>
+      <c r="H26" s="18">
+        <v>25</v>
+      </c>
+      <c r="I26" s="18">
+        <v>-25</v>
+      </c>
+      <c r="J26" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K26" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M26" s="17"/>
       <c r="N26" s="17"/>
       <c r="O26" s="17"/>
       <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
+      <c r="Q26" s="17">
+        <v>1</v>
+      </c>
+      <c r="R26" s="19">
+        <v>25</v>
+      </c>
     </row>
     <row r="27" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
+      <c r="B27" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>1715</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>1716</v>
+      </c>
+      <c r="F27" s="17">
+        <v>2</v>
+      </c>
+      <c r="G27" s="18">
+        <v>850</v>
+      </c>
+      <c r="H27" s="18">
+        <v>30</v>
+      </c>
+      <c r="I27" s="18">
+        <v>820</v>
+      </c>
+      <c r="J27" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M27" s="17"/>
       <c r="N27" s="17"/>
       <c r="O27" s="17"/>
       <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
+      <c r="Q27" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
+      <c r="B28" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>1717</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>1718</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="G28" s="18">
+        <v>520</v>
+      </c>
+      <c r="H28" s="18">
+        <v>30</v>
+      </c>
+      <c r="I28" s="18">
+        <v>490</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M28" s="21"/>
       <c r="N28" s="17"/>
       <c r="O28" s="17"/>
       <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
+      <c r="Q28" s="17">
+        <v>1</v>
+      </c>
       <c r="R28" s="20"/>
     </row>
     <row r="29" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
+      <c r="B29" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>1719</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>1720</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>1721</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="G29" s="18">
+        <v>800</v>
+      </c>
+      <c r="H29" s="18">
+        <v>20</v>
+      </c>
+      <c r="I29" s="18">
+        <v>780</v>
+      </c>
+      <c r="J29" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K29" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M29" s="17"/>
       <c r="N29" s="17"/>
       <c r="O29" s="17"/>
       <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
+      <c r="Q29" s="17">
+        <v>1</v>
+      </c>
       <c r="R29" s="20"/>
     </row>
     <row r="30" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
+      <c r="B30" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>1722</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>1723</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>678</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="G30" s="18">
+        <v>0</v>
+      </c>
+      <c r="H30" s="18">
+        <v>25</v>
+      </c>
+      <c r="I30" s="18">
+        <v>-25</v>
+      </c>
+      <c r="J30" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K30" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M30" s="17"/>
       <c r="N30" s="17"/>
       <c r="O30" s="17"/>
       <c r="P30" s="17"/>
-      <c r="Q30" s="17"/>
+      <c r="Q30" s="17">
+        <v>1</v>
+      </c>
+      <c r="R30" s="19">
+        <v>25</v>
+      </c>
     </row>
     <row r="31" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
+      <c r="B31" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>1724</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>1725</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>1726</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G31" s="18">
+        <v>850</v>
+      </c>
+      <c r="H31" s="18">
+        <v>20</v>
+      </c>
+      <c r="I31" s="18">
+        <v>830</v>
+      </c>
+      <c r="J31" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K31" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M31" s="17"/>
       <c r="N31" s="17"/>
       <c r="O31" s="17"/>
       <c r="P31" s="17"/>
-      <c r="Q31" s="17"/>
+      <c r="Q31" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
+      <c r="B32" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>1728</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>1729</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="G32" s="18">
+        <v>0</v>
+      </c>
+      <c r="H32" s="18">
+        <v>25</v>
+      </c>
+      <c r="I32" s="18">
+        <v>-25</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K32" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L32" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M32" s="17"/>
       <c r="N32" s="17"/>
       <c r="O32" s="17"/>
       <c r="P32" s="17"/>
-      <c r="Q32" s="17"/>
+      <c r="Q32" s="17">
+        <v>1</v>
+      </c>
+      <c r="R32" s="19">
+        <v>25</v>
+      </c>
     </row>
     <row r="33" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
+      <c r="A33" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>248</v>
+      </c>
       <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
+      <c r="E33" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="G33" s="18">
+        <v>0</v>
+      </c>
+      <c r="H33" s="18">
+        <v>40</v>
+      </c>
+      <c r="I33" s="18">
+        <v>-40</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K33" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M33" s="17"/>
       <c r="N33" s="17"/>
       <c r="O33" s="17"/>
       <c r="P33" s="17"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="20"/>
+      <c r="Q33" s="17">
+        <v>1</v>
+      </c>
+      <c r="R33" s="20">
+        <v>40</v>
+      </c>
     </row>
     <row r="34" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
+      <c r="A34" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>1730</v>
+      </c>
       <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
+      <c r="E34" s="17" t="s">
+        <v>1731</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G34" s="18">
+        <v>0</v>
+      </c>
+      <c r="H34" s="18">
+        <v>30</v>
+      </c>
+      <c r="I34" s="18">
+        <v>-30</v>
+      </c>
+      <c r="J34" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K34" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M34" s="17"/>
       <c r="N34" s="17"/>
       <c r="O34" s="17"/>
       <c r="P34" s="17"/>
-      <c r="Q34" s="17"/>
+      <c r="Q34" s="17">
+        <v>1</v>
+      </c>
+      <c r="R34" s="19">
+        <v>30</v>
+      </c>
     </row>
     <row r="35" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
+      <c r="B35" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>1733</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>1734</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="G35" s="18">
+        <v>4400</v>
+      </c>
+      <c r="H35" s="18">
+        <v>35</v>
+      </c>
+      <c r="I35" s="18">
+        <v>4365</v>
+      </c>
+      <c r="J35" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="K35" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" s="17" t="s">
+        <v>1656</v>
+      </c>
+      <c r="M35" s="17" t="s">
+        <v>180</v>
+      </c>
       <c r="N35" s="17"/>
       <c r="O35" s="17"/>
       <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
+      <c r="Q35" s="17">
+        <v>1</v>
+      </c>
+      <c r="R35" s="19">
+        <v>35</v>
+      </c>
     </row>
     <row r="36" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="17"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
+      <c r="B36" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>1735</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>1736</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>1737</v>
+      </c>
+      <c r="F36" s="18">
+        <v>10</v>
+      </c>
+      <c r="G36" s="18">
+        <v>515</v>
+      </c>
+      <c r="H36" s="18">
+        <v>25</v>
+      </c>
+      <c r="I36" s="18">
+        <v>490</v>
+      </c>
+      <c r="J36" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="K36" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M36" s="17"/>
       <c r="N36" s="17"/>
       <c r="O36" s="17"/>
       <c r="P36" s="17"/>
-      <c r="Q36" s="17"/>
+      <c r="Q36" s="17">
+        <v>1</v>
+      </c>
       <c r="R36" s="20"/>
     </row>
     <row r="37" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="17"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
+      <c r="B37" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>1738</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F37" s="18">
+        <v>5</v>
+      </c>
+      <c r="G37" s="18">
+        <v>895</v>
+      </c>
+      <c r="H37" s="18">
+        <v>25</v>
+      </c>
+      <c r="I37" s="18">
+        <v>870</v>
+      </c>
+      <c r="J37" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="K37" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L37" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M37" s="17"/>
       <c r="N37" s="17"/>
       <c r="O37" s="17"/>
       <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
+      <c r="Q37" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="17"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
+      <c r="B38" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>1741</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="G38" s="18">
+        <v>710</v>
+      </c>
+      <c r="H38" s="18">
+        <v>20</v>
+      </c>
+      <c r="I38" s="18">
+        <v>690</v>
+      </c>
+      <c r="J38" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="K38" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M38" s="17"/>
       <c r="N38" s="17"/>
       <c r="O38" s="17"/>
       <c r="P38" s="17"/>
-      <c r="Q38" s="17"/>
+      <c r="Q38" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="39" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="17"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
+      <c r="B39" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>1743</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>1744</v>
+      </c>
+      <c r="F39" s="17">
+        <v>3</v>
+      </c>
+      <c r="G39" s="18">
+        <v>515</v>
+      </c>
+      <c r="H39" s="18">
+        <v>25</v>
+      </c>
+      <c r="I39" s="18">
+        <v>490</v>
+      </c>
+      <c r="J39" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="K39" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L39" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M39" s="17"/>
       <c r="N39" s="17"/>
       <c r="O39" s="17"/>
       <c r="P39" s="17"/>
-      <c r="Q39" s="17"/>
+      <c r="Q39" s="17">
+        <v>1</v>
+      </c>
       <c r="R39" s="20"/>
     </row>
     <row r="40" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
+      <c r="B40" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>1747</v>
+      </c>
+      <c r="F40" s="17">
+        <v>1</v>
+      </c>
+      <c r="G40" s="18">
+        <v>0</v>
+      </c>
+      <c r="H40" s="18">
+        <v>25</v>
+      </c>
+      <c r="I40" s="18">
+        <v>-25</v>
+      </c>
+      <c r="J40" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="K40" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L40" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M40" s="17"/>
       <c r="N40" s="17"/>
       <c r="O40" s="17"/>
       <c r="P40" s="17"/>
-      <c r="Q40" s="17"/>
+      <c r="Q40" s="17">
+        <v>1</v>
+      </c>
+      <c r="R40" s="19">
+        <v>25</v>
+      </c>
     </row>
     <row r="41" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
+      <c r="B41" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>1749</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>1750</v>
+      </c>
+      <c r="F41" s="18">
+        <v>1</v>
+      </c>
+      <c r="G41" s="18">
+        <v>915</v>
+      </c>
+      <c r="H41" s="18">
+        <v>25</v>
+      </c>
+      <c r="I41" s="18">
+        <v>890</v>
+      </c>
+      <c r="J41" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="K41" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L41" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M41" s="17"/>
       <c r="N41" s="17"/>
       <c r="O41" s="17"/>
       <c r="P41" s="17"/>
-      <c r="Q41" s="17"/>
+      <c r="Q41" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="42" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
+      <c r="A42" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>1751</v>
+      </c>
       <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
+      <c r="E42" s="17" t="s">
+        <v>1752</v>
+      </c>
+      <c r="F42" s="18">
+        <v>5</v>
+      </c>
+      <c r="G42" s="18">
+        <v>30</v>
+      </c>
+      <c r="H42" s="18">
+        <v>30</v>
+      </c>
+      <c r="I42" s="18">
+        <v>0</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="K42" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L42" s="17" t="s">
+        <v>1656</v>
+      </c>
       <c r="M42" s="17"/>
       <c r="N42" s="17"/>
       <c r="O42" s="17"/>
       <c r="P42" s="17"/>
-      <c r="Q42" s="17"/>
-    </row>
-    <row r="43" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
-      <c r="M43" s="17"/>
-      <c r="N43" s="17"/>
-      <c r="O43" s="17"/>
-      <c r="P43" s="17"/>
-      <c r="Q43" s="17"/>
-      <c r="R43" s="20"/>
-    </row>
-    <row r="44" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-      <c r="N44" s="17"/>
-      <c r="O44" s="17"/>
-      <c r="P44" s="17"/>
-      <c r="Q44" s="17"/>
-    </row>
-    <row r="45" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17"/>
-      <c r="O45" s="17"/>
-      <c r="P45" s="17"/>
-      <c r="Q45" s="17"/>
-      <c r="R45" s="20"/>
-    </row>
-    <row r="46" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="17"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="18"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="17"/>
-      <c r="M46" s="17"/>
-      <c r="N46" s="17"/>
-      <c r="O46" s="17"/>
-      <c r="P46" s="17"/>
-      <c r="Q46" s="17"/>
-      <c r="R46" s="20"/>
-    </row>
-    <row r="47" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="17"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="18"/>
-      <c r="I47" s="18"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
-      <c r="L47" s="17"/>
-      <c r="M47" s="17"/>
-      <c r="N47" s="17"/>
-      <c r="O47" s="17"/>
-      <c r="P47" s="17"/>
-      <c r="Q47" s="17"/>
-    </row>
-    <row r="48" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="17"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="18"/>
-      <c r="I48" s="18"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="17"/>
-      <c r="M48" s="17"/>
-      <c r="N48" s="17"/>
-      <c r="O48" s="17"/>
-      <c r="P48" s="17"/>
-      <c r="Q48" s="17"/>
-    </row>
-    <row r="49" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="17"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="18"/>
-      <c r="I49" s="18"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
-      <c r="N49" s="17"/>
-      <c r="O49" s="17"/>
-      <c r="P49" s="17"/>
-      <c r="Q49" s="17"/>
-      <c r="R49" s="20"/>
-    </row>
-    <row r="50" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="17"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
-      <c r="H50" s="18"/>
-      <c r="I50" s="18"/>
-      <c r="J50" s="17"/>
-      <c r="K50" s="17"/>
-      <c r="L50" s="17"/>
-      <c r="M50" s="17"/>
-      <c r="N50" s="17"/>
-      <c r="O50" s="17"/>
-      <c r="P50" s="17"/>
-      <c r="Q50" s="17"/>
-    </row>
-    <row r="51" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="17"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="18"/>
-      <c r="I51" s="18"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="17"/>
-      <c r="M51" s="17"/>
-      <c r="N51" s="17"/>
-      <c r="O51" s="17"/>
-      <c r="P51" s="17"/>
-      <c r="Q51" s="17"/>
-    </row>
-    <row r="52" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="17"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="18"/>
-      <c r="H52" s="18"/>
-      <c r="I52" s="18"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
-      <c r="M52" s="17"/>
-      <c r="N52" s="17"/>
-      <c r="O52" s="17"/>
-      <c r="P52" s="17"/>
-      <c r="Q52" s="17"/>
-      <c r="R52" s="20"/>
-    </row>
-    <row r="53" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="17"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="18"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
-      <c r="M53" s="17"/>
-      <c r="N53" s="17"/>
-      <c r="O53" s="17"/>
-      <c r="P53" s="17"/>
-      <c r="Q53" s="17"/>
-    </row>
-    <row r="54" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="17"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
-      <c r="H54" s="18"/>
-      <c r="I54" s="18"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="17"/>
-      <c r="O54" s="17"/>
-      <c r="P54" s="17"/>
-      <c r="Q54" s="17"/>
-    </row>
-    <row r="55" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="17"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-      <c r="H55" s="18"/>
-      <c r="I55" s="18"/>
-      <c r="J55" s="17"/>
-      <c r="K55" s="17"/>
-      <c r="L55" s="17"/>
-      <c r="M55" s="17"/>
-      <c r="N55" s="17"/>
-      <c r="O55" s="17"/>
-      <c r="P55" s="17"/>
-      <c r="Q55" s="17"/>
-    </row>
-    <row r="56" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="17"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="18"/>
-      <c r="I56" s="18"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="17"/>
-      <c r="O56" s="17"/>
-      <c r="P56" s="17"/>
-      <c r="Q56" s="17"/>
-      <c r="R56" s="20"/>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="G58" s="1">
-        <f t="shared" ref="G58:R58" si="0">SUBTOTAL(9,G3:G57)</f>
-        <v>0</v>
-      </c>
-      <c r="H58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H62" s="4" t="s">
+      <c r="Q42" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G44" s="1">
+        <f t="shared" ref="G44:R44" si="0">SUBTOTAL(9,G3:G43)</f>
+        <v>26010</v>
+      </c>
+      <c r="H44" s="1">
+        <f t="shared" si="0"/>
+        <v>1110</v>
+      </c>
+      <c r="I44" s="1">
+        <f t="shared" si="0"/>
+        <v>24900</v>
+      </c>
+      <c r="J44" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L44" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N44" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O44" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P44" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q44" s="1">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="R44" s="1">
+        <f t="shared" si="0"/>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I45" s="1">
+        <v>-780</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I46" s="1">
+        <v>-375</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H48" s="4" t="s">
         <v>1575</v>
       </c>
-      <c r="I62" s="5" t="s">
+      <c r="I48" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J62" s="6" t="s">
+      <c r="J48" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H63" s="7" t="s">
+    <row r="49" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H49" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I63" s="8">
-        <f>SUM(I57:I61)</f>
-        <v>0</v>
-      </c>
-      <c r="J63" s="8">
-        <f>Q58</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="H64" s="9" t="s">
+      <c r="I49" s="8">
+        <f>SUM(I43:I47)</f>
+        <v>23745</v>
+      </c>
+      <c r="J49" s="8">
+        <f>Q44</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H50" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I64" s="10">
-        <f>R58</f>
-        <v>0</v>
-      </c>
-      <c r="J64" s="11"/>
-    </row>
-    <row r="65" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H65" s="9" t="s">
+      <c r="I50" s="10">
+        <f>R44</f>
+        <v>340</v>
+      </c>
+      <c r="J50" s="11"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H51" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I65" s="10">
-        <f>S57</f>
-        <v>0</v>
-      </c>
-      <c r="J65" s="11"/>
-    </row>
-    <row r="66" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H66" s="9" t="s">
+      <c r="I51" s="10">
+        <f>S43</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="11"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H52" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I66" s="10">
-        <f>T57</f>
-        <v>0</v>
-      </c>
-      <c r="J66" s="11"/>
-    </row>
-    <row r="67" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H67" s="9" t="s">
+      <c r="I52" s="10">
+        <f>T43</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="11"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H53" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I67" s="10">
-        <f>U57</f>
-        <v>0</v>
-      </c>
-      <c r="J67" s="11"/>
-    </row>
-    <row r="68" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H68" s="12" t="s">
+      <c r="I53" s="10">
+        <f>U43</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="11"/>
+    </row>
+    <row r="54" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H54" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
-    </row>
-    <row r="69" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H69" s="14" t="s">
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+    </row>
+    <row r="55" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H55" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13"/>
-    </row>
-    <row r="70" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="H70" s="15" t="s">
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+    </row>
+    <row r="56" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H56" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I70" s="16">
-        <f>SUM(I63:I69)</f>
-        <v>0</v>
-      </c>
-      <c r="J70" s="16">
-        <f>SUM(J63:J67)</f>
-        <v>0</v>
+      <c r="I56" s="16">
+        <f>SUM(I49:I55)</f>
+        <v>24085</v>
+      </c>
+      <c r="J56" s="16">
+        <f>SUM(J49:J53)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="B59" s="53" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C59" s="53" t="s">
+        <v>1596</v>
+      </c>
+      <c r="D59" s="53" t="s">
+        <v>1597</v>
+      </c>
+      <c r="E59" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="F59" s="54">
+        <v>375</v>
+      </c>
+      <c r="G59" s="54">
+        <v>0</v>
+      </c>
+      <c r="H59" s="54">
+        <f t="shared" ref="H59" si="1">F59-G59</f>
+        <v>375</v>
+      </c>
+      <c r="I59" s="53" t="s">
+        <v>623</v>
+      </c>
+      <c r="J59" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="K59" s="53" t="s">
+        <v>1577</v>
+      </c>
+      <c r="L59" s="28" t="s">
+        <v>1756</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P56" xr:uid="{00000000-0009-0000-0000-000006000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P56">
-      <sortCondition ref="J2:J56"/>
+  <autoFilter ref="A2:P42" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P42">
+      <sortCondition ref="J2:J42"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EE6B791-68C0-44F7-B9D9-C785498B1639}">
+  <dimension ref="A1:R45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>1760</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>1287</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="G3" s="23">
+        <v>855</v>
+      </c>
+      <c r="H3" s="23">
+        <v>35</v>
+      </c>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I28" si="0">G3-H3</f>
+        <v>820</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>1761</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>1764</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>1765</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="23">
+        <v>400</v>
+      </c>
+      <c r="H4" s="23">
+        <v>30</v>
+      </c>
+      <c r="I4" s="23">
+        <f t="shared" si="0"/>
+        <v>370</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>1761</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>1766</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>1767</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="23">
+        <v>0</v>
+      </c>
+      <c r="H5" s="23">
+        <v>30</v>
+      </c>
+      <c r="I5" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>1761</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M5" s="28" t="s">
+        <v>1768</v>
+      </c>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+      <c r="R5" s="24">
+        <f>H5</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>1770</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>1771</v>
+      </c>
+      <c r="F6" s="23">
+        <v>12</v>
+      </c>
+      <c r="G6" s="23">
+        <v>0</v>
+      </c>
+      <c r="H6" s="23">
+        <v>30</v>
+      </c>
+      <c r="I6" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>1761</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+      <c r="R6" s="24">
+        <f>H6</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>1772</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>1605</v>
+      </c>
+      <c r="F7" s="26">
+        <v>12</v>
+      </c>
+      <c r="G7" s="26">
+        <v>330</v>
+      </c>
+      <c r="H7" s="26">
+        <v>30</v>
+      </c>
+      <c r="I7" s="26">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>1761</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="25" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>1774</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>1775</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="23">
+        <v>0</v>
+      </c>
+      <c r="H8" s="23">
+        <v>30</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>1761</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+      <c r="R8" s="24">
+        <f>H8</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>1777</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>824</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="23">
+        <v>860</v>
+      </c>
+      <c r="H9" s="23">
+        <v>30</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>1761</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>1779</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>1780</v>
+      </c>
+      <c r="F10" s="23">
+        <v>8</v>
+      </c>
+      <c r="G10" s="23">
+        <v>690</v>
+      </c>
+      <c r="H10" s="23">
+        <v>30</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>1761</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>1782</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F11" s="23">
+        <v>7</v>
+      </c>
+      <c r="G11" s="23">
+        <v>920</v>
+      </c>
+      <c r="H11" s="23">
+        <v>30</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>1761</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>744</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>1785</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="23">
+        <v>820</v>
+      </c>
+      <c r="H12" s="23">
+        <v>30</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>1761</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M12" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>1786</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>1785</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="23">
+        <v>660</v>
+      </c>
+      <c r="H13" s="23">
+        <v>0</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>1761</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M13" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>1789</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="23">
+        <v>510</v>
+      </c>
+      <c r="H14" s="23">
+        <v>30</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>1761</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>1791</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>1792</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="23">
+        <v>915</v>
+      </c>
+      <c r="H15" s="23">
+        <v>25</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>1761</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>889</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>1793</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>1794</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="23">
+        <v>850</v>
+      </c>
+      <c r="H16" s="23">
+        <v>30</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>1761</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>1795</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>1796</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>1797</v>
+      </c>
+      <c r="F17" s="23">
+        <v>11</v>
+      </c>
+      <c r="G17" s="23">
+        <v>865</v>
+      </c>
+      <c r="H17" s="23">
+        <v>25</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>1761</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>579</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>1798</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>581</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" s="23">
+        <v>910</v>
+      </c>
+      <c r="H18" s="23">
+        <v>20</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>1799</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>1800</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>1801</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" s="23">
+        <v>1155</v>
+      </c>
+      <c r="H19" s="23">
+        <v>25</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>1130</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="23">
+        <v>915</v>
+      </c>
+      <c r="H20" s="23">
+        <v>25</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>667</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>1805</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>669</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G21" s="23">
+        <v>2520</v>
+      </c>
+      <c r="H21" s="23">
+        <v>30</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>2490</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>1807</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>1808</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G22" s="23">
+        <v>0</v>
+      </c>
+      <c r="H22" s="23">
+        <v>25</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+      <c r="R22" s="24">
+        <f>H22</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22" t="s">
+        <v>1810</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G23" s="23">
+        <v>40</v>
+      </c>
+      <c r="H23" s="23">
+        <v>40</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>1812</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="23">
+        <v>0</v>
+      </c>
+      <c r="H24" s="23">
+        <v>25</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22">
+        <v>1</v>
+      </c>
+      <c r="R24" s="24">
+        <f>H24</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>1815</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>1816</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G25" s="23">
+        <v>1595</v>
+      </c>
+      <c r="H25" s="23">
+        <v>25</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="0"/>
+        <v>1570</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>1818</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>1819</v>
+      </c>
+      <c r="F26" s="23">
+        <v>10</v>
+      </c>
+      <c r="G26" s="23">
+        <v>915</v>
+      </c>
+      <c r="H26" s="23">
+        <v>25</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>1821</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>1822</v>
+      </c>
+      <c r="F27" s="23">
+        <v>10</v>
+      </c>
+      <c r="G27" s="23">
+        <v>1225</v>
+      </c>
+      <c r="H27" s="23">
+        <v>25</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>1824</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>379</v>
+      </c>
+      <c r="F28" s="23">
+        <v>4</v>
+      </c>
+      <c r="G28" s="23">
+        <v>855</v>
+      </c>
+      <c r="H28" s="23">
+        <v>25</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G30" s="1">
+        <f t="shared" ref="G30:R30" si="1">SUBTOTAL(9,G3:G29)</f>
+        <v>18805</v>
+      </c>
+      <c r="H30" s="1">
+        <f t="shared" si="1"/>
+        <v>705</v>
+      </c>
+      <c r="I30" s="1">
+        <f t="shared" si="1"/>
+        <v>18100</v>
+      </c>
+      <c r="J30" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N30" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O30" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P30" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="1">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="R30" s="1">
+        <f t="shared" si="1"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I31" s="1">
+        <v>-1585</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H34" s="4" t="s">
+        <v>1754</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="8">
+        <f>SUM(I29:I33)</f>
+        <v>16515</v>
+      </c>
+      <c r="J35" s="8">
+        <f>Q30</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H36" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="10">
+        <f>R30</f>
+        <v>140</v>
+      </c>
+      <c r="J36" s="11"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H37" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" s="10">
+        <f>S29</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="11"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H38" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" s="10">
+        <f>T29</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="11"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H39" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I39" s="10">
+        <f>U29</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="11"/>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H40" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+    </row>
+    <row r="41" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H41" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+    </row>
+    <row r="42" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H42" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="16">
+        <f>SUM(I35:I41)</f>
+        <v>16655</v>
+      </c>
+      <c r="J42" s="16">
+        <f>SUM(J35:J39)</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" s="36" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C45" s="36" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D45" s="36" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E45" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="F45" s="37">
+        <v>1710</v>
+      </c>
+      <c r="G45" s="37">
+        <v>0</v>
+      </c>
+      <c r="H45" s="37">
+        <f t="shared" ref="H45" si="2">F45-G45</f>
+        <v>1710</v>
+      </c>
+      <c r="I45" s="36" t="s">
+        <v>1761</v>
+      </c>
+      <c r="J45" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="K45" s="36" t="s">
+        <v>1762</v>
+      </c>
+      <c r="L45" s="28" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P28" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P28">
+      <sortCondition ref="J2:J28"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{732BC793-A297-404B-A8DD-F38AD7348D10}">
+  <dimension ref="A1:R42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="25"/>
+      <c r="B3" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>1605</v>
+      </c>
+      <c r="F3" s="26">
+        <v>12</v>
+      </c>
+      <c r="G3" s="26">
+        <v>785</v>
+      </c>
+      <c r="H3" s="26">
+        <v>30</v>
+      </c>
+      <c r="I3" s="26">
+        <f t="shared" ref="I3:I28" si="0">G3-H3</f>
+        <v>755</v>
+      </c>
+      <c r="J3" s="25" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="25" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M3" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>1830</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="23">
+        <v>1550</v>
+      </c>
+      <c r="H4" s="23">
+        <v>30</v>
+      </c>
+      <c r="I4" s="23">
+        <f t="shared" si="0"/>
+        <v>1520</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>831</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>1832</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="23">
+        <v>0</v>
+      </c>
+      <c r="H5" s="23">
+        <v>25</v>
+      </c>
+      <c r="I5" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+      <c r="R5" s="24">
+        <f>H5</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>1834</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>1835</v>
+      </c>
+      <c r="F6" s="23">
+        <v>8</v>
+      </c>
+      <c r="G6" s="23">
+        <v>820</v>
+      </c>
+      <c r="H6" s="23">
+        <v>30</v>
+      </c>
+      <c r="I6" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>1836</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>1837</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>1838</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G7" s="23">
+        <v>1025</v>
+      </c>
+      <c r="H7" s="23">
+        <v>35</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>1839</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F8" s="23">
+        <v>7</v>
+      </c>
+      <c r="G8" s="23">
+        <v>820</v>
+      </c>
+      <c r="H8" s="23">
+        <v>30</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M8" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+      <c r="R8" s="24">
+        <f>H8</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22" t="s">
+        <v>1841</v>
+      </c>
+      <c r="F9" s="23">
+        <v>6</v>
+      </c>
+      <c r="G9" s="23">
+        <v>1400</v>
+      </c>
+      <c r="H9" s="23">
+        <v>30</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>1370</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>1842</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>1843</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>1844</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G10" s="23">
+        <v>810</v>
+      </c>
+      <c r="H10" s="23">
+        <v>20</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>1846</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>1729</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G11" s="23">
+        <v>845</v>
+      </c>
+      <c r="H11" s="23">
+        <v>25</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>1847</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>1848</v>
+      </c>
+      <c r="F12" s="23">
+        <v>12</v>
+      </c>
+      <c r="G12" s="23">
+        <v>0</v>
+      </c>
+      <c r="H12" s="23">
+        <v>30</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+      <c r="R12" s="24">
+        <f t="shared" ref="R12:R13" si="1">H12</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>1851</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="23">
+        <v>0</v>
+      </c>
+      <c r="H13" s="23">
+        <v>30</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+      <c r="R13" s="24">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>1852</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F14" s="23">
+        <v>2</v>
+      </c>
+      <c r="G14" s="23">
+        <v>920</v>
+      </c>
+      <c r="H14" s="23">
+        <v>30</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>1854</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>1855</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="23">
+        <v>500</v>
+      </c>
+      <c r="H15" s="23">
+        <v>20</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="25"/>
+      <c r="B16" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>1799</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>1857</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="26">
+        <v>25</v>
+      </c>
+      <c r="H16" s="26">
+        <v>25</v>
+      </c>
+      <c r="I16" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="25" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M16" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>1859</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>1860</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="23">
+        <v>0</v>
+      </c>
+      <c r="H17" s="23">
+        <v>20</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+      <c r="R17" s="24">
+        <f>H17</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="23">
+        <v>30</v>
+      </c>
+      <c r="H18" s="23">
+        <v>30</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22" t="s">
+        <v>1862</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="23">
+        <v>1575</v>
+      </c>
+      <c r="H19" s="23">
+        <v>25</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>1550</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="F20" s="23">
+        <v>12</v>
+      </c>
+      <c r="G20" s="23">
+        <v>0</v>
+      </c>
+      <c r="H20" s="23">
+        <v>40</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+      <c r="R20" s="24">
+        <f>H20</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>1865</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>1866</v>
+      </c>
+      <c r="F21" s="23">
+        <v>3</v>
+      </c>
+      <c r="G21" s="23">
+        <v>1830</v>
+      </c>
+      <c r="H21" s="23">
+        <v>25</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>1805</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M21" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+      <c r="R21" s="24">
+        <f>H21</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>1868</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>1869</v>
+      </c>
+      <c r="F22" s="23">
+        <v>1</v>
+      </c>
+      <c r="G22" s="23">
+        <v>0</v>
+      </c>
+      <c r="H22" s="23">
+        <v>25</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+      <c r="R22" s="24">
+        <f t="shared" ref="R22:R25" si="2">H22</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>1871</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>1872</v>
+      </c>
+      <c r="F23" s="23">
+        <v>4</v>
+      </c>
+      <c r="G23" s="23">
+        <v>0</v>
+      </c>
+      <c r="H23" s="23">
+        <v>25</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+      <c r="R23" s="24">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>1874</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>1875</v>
+      </c>
+      <c r="F24" s="23">
+        <v>3</v>
+      </c>
+      <c r="G24" s="23">
+        <v>0</v>
+      </c>
+      <c r="H24" s="23">
+        <v>25</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22">
+        <v>1</v>
+      </c>
+      <c r="R24" s="24">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>947</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>1876</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>1877</v>
+      </c>
+      <c r="F25" s="23">
+        <v>5</v>
+      </c>
+      <c r="G25" s="23">
+        <v>0</v>
+      </c>
+      <c r="H25" s="23">
+        <v>25</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+      <c r="R25" s="24">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>1878</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>1879</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>1880</v>
+      </c>
+      <c r="F26" s="23">
+        <v>3</v>
+      </c>
+      <c r="G26" s="23">
+        <v>845</v>
+      </c>
+      <c r="H26" s="23">
+        <v>25</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>1881</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>1882</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>1883</v>
+      </c>
+      <c r="F27" s="23">
+        <v>1</v>
+      </c>
+      <c r="G27" s="23">
+        <v>0</v>
+      </c>
+      <c r="H27" s="23">
+        <v>25</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22">
+        <v>1</v>
+      </c>
+      <c r="R27" s="24">
+        <f t="shared" ref="R27:R28" si="3">H27</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>1884</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>1885</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>1886</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G28" s="23">
+        <v>0</v>
+      </c>
+      <c r="H28" s="23">
+        <v>25</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>1829</v>
+      </c>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22">
+        <v>1</v>
+      </c>
+      <c r="R28" s="24">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G30" s="1">
+        <f>SUBTOTAL(9,G3:G29)</f>
+        <v>13780</v>
+      </c>
+      <c r="H30" s="1">
+        <f>SUBTOTAL(9,H3:H29)</f>
+        <v>705</v>
+      </c>
+      <c r="I30" s="1">
+        <f>SUBTOTAL(9,I3:I29)</f>
+        <v>13075</v>
+      </c>
+      <c r="J30" s="1">
+        <f>SUBTOTAL(9,J3:J29)</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
+        <f>SUBTOTAL(9,K3:K29)</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="1">
+        <f>SUBTOTAL(9,L3:L29)</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <f>SUBTOTAL(9,M3:M29)</f>
+        <v>0</v>
+      </c>
+      <c r="N30" s="1">
+        <f>SUBTOTAL(9,N3:N29)</f>
+        <v>0</v>
+      </c>
+      <c r="O30" s="1">
+        <f>SUBTOTAL(9,O3:O29)</f>
+        <v>0</v>
+      </c>
+      <c r="P30" s="1">
+        <f>SUBTOTAL(9,P3:P29)</f>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="1">
+        <f>SUBTOTAL(9,Q3:Q29)</f>
+        <v>26</v>
+      </c>
+      <c r="R30" s="1">
+        <f>SUBTOTAL(9,R3:R29)</f>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="34" spans="8:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H34" s="4" t="s">
+        <v>1758</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="8">
+        <f>SUM(I29:I33)</f>
+        <v>13075</v>
+      </c>
+      <c r="J35" s="8">
+        <f>Q30</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H36" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="10">
+        <f>R30</f>
+        <v>350</v>
+      </c>
+      <c r="J36" s="11"/>
+    </row>
+    <row r="37" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H37" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" s="10">
+        <f>S29</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="11"/>
+    </row>
+    <row r="38" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H38" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" s="10">
+        <f>T29</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="11"/>
+    </row>
+    <row r="39" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H39" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I39" s="10">
+        <f>U29</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="11"/>
+    </row>
+    <row r="40" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H40" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+    </row>
+    <row r="41" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H41" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+    </row>
+    <row r="42" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H42" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="16">
+        <f>SUM(I35:I41)</f>
+        <v>13425</v>
+      </c>
+      <c r="J42" s="16">
+        <f>SUM(J35:J39)</f>
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P28" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P28">
+      <sortCondition ref="J2:J28"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23168,6 +27540,1280 @@
   <autoFilter ref="A2:P22" xr:uid="{00000000-0009-0000-0000-000006000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P22">
       <sortCondition ref="J2:J22"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77CFE5FA-3A0A-4FBF-A036-7CE4C38D04EE}">
+  <dimension ref="A1:R70"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+    </row>
+    <row r="4" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+    </row>
+    <row r="5" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="20"/>
+    </row>
+    <row r="6" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+    </row>
+    <row r="7" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="20"/>
+    </row>
+    <row r="8" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+    </row>
+    <row r="9" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+    </row>
+    <row r="10" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="20"/>
+    </row>
+    <row r="11" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="20"/>
+    </row>
+    <row r="12" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+    </row>
+    <row r="13" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+    </row>
+    <row r="14" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+    </row>
+    <row r="15" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="20"/>
+    </row>
+    <row r="16" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="20"/>
+    </row>
+    <row r="17" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="20"/>
+    </row>
+    <row r="18" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+    </row>
+    <row r="19" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="20"/>
+    </row>
+    <row r="20" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+    </row>
+    <row r="21" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+    </row>
+    <row r="22" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+    </row>
+    <row r="23" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="20"/>
+    </row>
+    <row r="24" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+    </row>
+    <row r="25" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="20"/>
+    </row>
+    <row r="26" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+    </row>
+    <row r="27" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+    </row>
+    <row r="28" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="20"/>
+    </row>
+    <row r="29" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="20"/>
+    </row>
+    <row r="30" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+    </row>
+    <row r="31" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17"/>
+    </row>
+    <row r="32" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+    </row>
+    <row r="33" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="20"/>
+    </row>
+    <row r="34" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+    </row>
+    <row r="35" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+    </row>
+    <row r="36" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="20"/>
+    </row>
+    <row r="37" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+    </row>
+    <row r="38" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+    </row>
+    <row r="39" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="17"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="20"/>
+    </row>
+    <row r="40" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+    </row>
+    <row r="41" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+    </row>
+    <row r="42" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="17"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+    </row>
+    <row r="43" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17"/>
+      <c r="P43" s="17"/>
+      <c r="Q43" s="17"/>
+      <c r="R43" s="20"/>
+    </row>
+    <row r="44" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="17"/>
+    </row>
+    <row r="45" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="20"/>
+    </row>
+    <row r="46" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="17"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17"/>
+      <c r="P46" s="17"/>
+      <c r="Q46" s="17"/>
+      <c r="R46" s="20"/>
+    </row>
+    <row r="47" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="17"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="17"/>
+      <c r="M47" s="17"/>
+      <c r="N47" s="17"/>
+      <c r="O47" s="17"/>
+      <c r="P47" s="17"/>
+      <c r="Q47" s="17"/>
+    </row>
+    <row r="48" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="17"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
+      <c r="Q48" s="17"/>
+    </row>
+    <row r="49" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="17"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
+      <c r="L49" s="17"/>
+      <c r="M49" s="17"/>
+      <c r="N49" s="17"/>
+      <c r="O49" s="17"/>
+      <c r="P49" s="17"/>
+      <c r="Q49" s="17"/>
+      <c r="R49" s="20"/>
+    </row>
+    <row r="50" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="17"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="17"/>
+      <c r="M50" s="17"/>
+      <c r="N50" s="17"/>
+      <c r="O50" s="17"/>
+      <c r="P50" s="17"/>
+      <c r="Q50" s="17"/>
+    </row>
+    <row r="51" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="17"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="18"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="17"/>
+      <c r="M51" s="17"/>
+      <c r="N51" s="17"/>
+      <c r="O51" s="17"/>
+      <c r="P51" s="17"/>
+      <c r="Q51" s="17"/>
+    </row>
+    <row r="52" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="17"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
+      <c r="N52" s="17"/>
+      <c r="O52" s="17"/>
+      <c r="P52" s="17"/>
+      <c r="Q52" s="17"/>
+      <c r="R52" s="20"/>
+    </row>
+    <row r="53" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="17"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="17"/>
+      <c r="L53" s="17"/>
+      <c r="M53" s="17"/>
+      <c r="N53" s="17"/>
+      <c r="O53" s="17"/>
+      <c r="P53" s="17"/>
+      <c r="Q53" s="17"/>
+    </row>
+    <row r="54" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="17"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
+      <c r="O54" s="17"/>
+      <c r="P54" s="17"/>
+      <c r="Q54" s="17"/>
+    </row>
+    <row r="55" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="17"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="17"/>
+      <c r="K55" s="17"/>
+      <c r="L55" s="17"/>
+      <c r="M55" s="17"/>
+      <c r="N55" s="17"/>
+      <c r="O55" s="17"/>
+      <c r="P55" s="17"/>
+      <c r="Q55" s="17"/>
+    </row>
+    <row r="56" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="17"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="17"/>
+      <c r="M56" s="17"/>
+      <c r="N56" s="17"/>
+      <c r="O56" s="17"/>
+      <c r="P56" s="17"/>
+      <c r="Q56" s="17"/>
+      <c r="R56" s="20"/>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G58" s="1">
+        <f t="shared" ref="G58:R58" si="0">SUBTOTAL(9,G3:G57)</f>
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H62" s="4" t="s">
+        <v>1826</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I63" s="8">
+        <f>SUM(I57:I61)</f>
+        <v>0</v>
+      </c>
+      <c r="J63" s="8">
+        <f>Q58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H64" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I64" s="10">
+        <f>R58</f>
+        <v>0</v>
+      </c>
+      <c r="J64" s="11"/>
+    </row>
+    <row r="65" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H65" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I65" s="10">
+        <f>S57</f>
+        <v>0</v>
+      </c>
+      <c r="J65" s="11"/>
+    </row>
+    <row r="66" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H66" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" s="10">
+        <f>T57</f>
+        <v>0</v>
+      </c>
+      <c r="J66" s="11"/>
+    </row>
+    <row r="67" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H67" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I67" s="10">
+        <f>U57</f>
+        <v>0</v>
+      </c>
+      <c r="J67" s="11"/>
+    </row>
+    <row r="68" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H68" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+    </row>
+    <row r="69" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H69" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
+    </row>
+    <row r="70" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H70" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I70" s="16">
+        <f>SUM(I63:I69)</f>
+        <v>0</v>
+      </c>
+      <c r="J70" s="16">
+        <f>SUM(J63:J67)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P56" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P56">
+      <sortCondition ref="J2:J56"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613B4BD7-E0FF-4B49-86B8-2F941BC6F0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5AB279-F322-4AAF-9859-333043739DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-5" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,9 @@
     <sheet name="21-5" sheetId="18" r:id="rId17"/>
     <sheet name="22-5" sheetId="20" r:id="rId18"/>
     <sheet name="23-5" sheetId="21" r:id="rId19"/>
-    <sheet name="25-5" sheetId="22" r:id="rId20"/>
+    <sheet name="25-5" sheetId="23" r:id="rId20"/>
+    <sheet name="26-5" sheetId="22" r:id="rId21"/>
+    <sheet name="27-5" sheetId="24" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'11-5'!$A$2:$P$58</definedName>
@@ -48,7 +50,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'21-5'!$A$2:$P$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'22-5'!$A$2:$P$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'23-5'!$A$2:$P$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'25-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'25-5'!$A$2:$P$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'26-5'!$A$2:$P$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'27-5'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'4-5'!$A$2:$P$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'5-5'!$A$2:$P$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'6-5'!$A$2:$P$34</definedName>
@@ -77,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5731" uniqueCount="1887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6408" uniqueCount="2074">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -5738,6 +5742,567 @@
   </si>
   <si>
     <t>24 Yên Thế, Phường 2</t>
+  </si>
+  <si>
+    <t>T3.26.5.2026</t>
+  </si>
+  <si>
+    <t>NGAY 26-5</t>
+  </si>
+  <si>
+    <t>Trần Mai Phương</t>
+  </si>
+  <si>
+    <t>HD023562</t>
+  </si>
+  <si>
+    <t>442 Tô Ký- Tân Chánh Hiệp</t>
+  </si>
+  <si>
+    <t>AT 25-05</t>
+  </si>
+  <si>
+    <t>25-05-2026</t>
+  </si>
+  <si>
+    <t>HD023204</t>
+  </si>
+  <si>
+    <t>Phương Thảo TA</t>
+  </si>
+  <si>
+    <t>HD023551</t>
+  </si>
+  <si>
+    <t>HD022939</t>
+  </si>
+  <si>
+    <t>Chung cư aview KDC 13C ấp 5 xã phong phú</t>
+  </si>
+  <si>
+    <t>QP</t>
+  </si>
+  <si>
+    <t>HD021978</t>
+  </si>
+  <si>
+    <t>Số 28 KDC Nam Long, Thạnh Lộc</t>
+  </si>
+  <si>
+    <t>HD023578</t>
+  </si>
+  <si>
+    <t>Linh Phạm</t>
+  </si>
+  <si>
+    <t>HD023385</t>
+  </si>
+  <si>
+    <t>80/17 miếu gò xoài bình hưng hoà a</t>
+  </si>
+  <si>
+    <t>Thanh Hoài Hoàng</t>
+  </si>
+  <si>
+    <t>HD023530</t>
+  </si>
+  <si>
+    <t>7-9 Hải Thượng Lãn Ông, P chợ lớn</t>
+  </si>
+  <si>
+    <t>Minh Thoan</t>
+  </si>
+  <si>
+    <t>HD023208</t>
+  </si>
+  <si>
+    <t>195 tân hương p phú thọ hoà</t>
+  </si>
+  <si>
+    <t>Thanh Nhàn</t>
+  </si>
+  <si>
+    <t>HD023483</t>
+  </si>
+  <si>
+    <t>59 trần hưng đạo, p.tân thành</t>
+  </si>
+  <si>
+    <t>HD023291</t>
+  </si>
+  <si>
+    <t>Block d2, chung cư sài gòn riverside (số 4 đào trí, phú thuận)</t>
+  </si>
+  <si>
+    <t>Phương Anna</t>
+  </si>
+  <si>
+    <t>HD023553</t>
+  </si>
+  <si>
+    <t>258/77/2 dương bá trạc, P2</t>
+  </si>
+  <si>
+    <t>HD023457</t>
+  </si>
+  <si>
+    <t>Số 2 đường 75, khu phố 2, tân phong</t>
+  </si>
+  <si>
+    <t>HD022968</t>
+  </si>
+  <si>
+    <t>Gia Hue</t>
+  </si>
+  <si>
+    <t>HD023414</t>
+  </si>
+  <si>
+    <t>24 tân hoà đông p14</t>
+  </si>
+  <si>
+    <t>HD023330</t>
+  </si>
+  <si>
+    <t>Lê Nhật Tâm</t>
+  </si>
+  <si>
+    <t>HD023331</t>
+  </si>
+  <si>
+    <t>271 Mã Lò phường Bình Trị Đông</t>
+  </si>
+  <si>
+    <t>Phạm Tuyết</t>
+  </si>
+  <si>
+    <t>HD023561</t>
+  </si>
+  <si>
+    <t>Chung Cư Gia Phú (lô A),cuối Hẻm 219 đường Số 5, Khu Phố 7, Phường Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Julia Julia</t>
+  </si>
+  <si>
+    <t>HD023227</t>
+  </si>
+  <si>
+    <t>lô z01-02-03a KCN trong KCX tân thuận, phường tân thuận đông</t>
+  </si>
+  <si>
+    <t>HD023565</t>
+  </si>
+  <si>
+    <t>Số 242, Tân Kỳ Tân Quý, Phường Tân Sơn Nhì</t>
+  </si>
+  <si>
+    <t>HD023334</t>
+  </si>
+  <si>
+    <t>0967000176</t>
+  </si>
+  <si>
+    <t>HD023380</t>
+  </si>
+  <si>
+    <t>8/5b đỗ văn dậy</t>
+  </si>
+  <si>
+    <t>NGỌC DIỆP - fb Jenny Uyên</t>
+  </si>
+  <si>
+    <t>HD023210</t>
+  </si>
+  <si>
+    <t>30 trịnh đình thảo chung cư trung đông plaza</t>
+  </si>
+  <si>
+    <t>Anna Nguyen</t>
+  </si>
+  <si>
+    <t>HD023476</t>
+  </si>
+  <si>
+    <t>12a Nguyễn hữu thọ Phước kiểng Cc the park resident tòa b5</t>
+  </si>
+  <si>
+    <t>HD023571</t>
+  </si>
+  <si>
+    <t>Scenic Valley 1, Cổng Số 2, Kdc Phú Mỹ Hưng, Phường Tân Phú</t>
+  </si>
+  <si>
+    <t>Nguyễn thị ánh ngọc</t>
+  </si>
+  <si>
+    <t>HD023541</t>
+  </si>
+  <si>
+    <t>B1805-B1806 block B ecogreen 39B nguyễn văn linh - tân thuận tây</t>
+  </si>
+  <si>
+    <t>(Tuấn) Nhận Dùm Xiaomei</t>
+  </si>
+  <si>
+    <t>HD023332</t>
+  </si>
+  <si>
+    <t>77/8/2 đường số 1, khu phố ông nhiêu, phường long trường</t>
+  </si>
+  <si>
+    <t>HD023484</t>
+  </si>
+  <si>
+    <t>Thơm Thơm</t>
+  </si>
+  <si>
+    <t>HD023336</t>
+  </si>
+  <si>
+    <t>119 nguyễn văn công p. Hạnh thông</t>
+  </si>
+  <si>
+    <t>Nguyễn Phùng Thảo Như - fb Karen Van</t>
+  </si>
+  <si>
+    <t>HD023580</t>
+  </si>
+  <si>
+    <t>799/2 Nguyễn kiệm p3</t>
+  </si>
+  <si>
+    <t>Khánh Ly</t>
+  </si>
+  <si>
+    <t>HD023225</t>
+  </si>
+  <si>
+    <t>67 Đg số 6, Kp4, phường Bình Trưng Tây</t>
+  </si>
+  <si>
+    <t>HD023568</t>
+  </si>
+  <si>
+    <t>Vũ Thị Hà</t>
+  </si>
+  <si>
+    <t>HD023340</t>
+  </si>
+  <si>
+    <t>20 Vũ Tông Phan, phường bình trưng</t>
+  </si>
+  <si>
+    <t>HD023455</t>
+  </si>
+  <si>
+    <t>433/11/2 Lê Đức Thọ, Phường Gò Vấp (phường 17 cũ)</t>
+  </si>
+  <si>
+    <t>HD023569</t>
+  </si>
+  <si>
+    <t>HD023507</t>
+  </si>
+  <si>
+    <t>Hồ Thanh Phương</t>
+  </si>
+  <si>
+    <t>HD023466</t>
+  </si>
+  <si>
+    <t>158/56/21 Phạm Văn Chiêu, phường 8</t>
+  </si>
+  <si>
+    <t>Hang</t>
+  </si>
+  <si>
+    <t>HD023317</t>
+  </si>
+  <si>
+    <t>75/2A nguyễn sỹ sách,p.15 cũ(tân sơn mới)</t>
+  </si>
+  <si>
+    <t>Hồng Vân</t>
+  </si>
+  <si>
+    <t>HD023071</t>
+  </si>
+  <si>
+    <t>233 đồng khởi phường sài gòn</t>
+  </si>
+  <si>
+    <t>HD023217</t>
+  </si>
+  <si>
+    <t>Em hồng thuỷ, hàng của chị AMyp</t>
+  </si>
+  <si>
+    <t>HD023235</t>
+  </si>
+  <si>
+    <t>38 Giải Phóng, phường 4</t>
+  </si>
+  <si>
+    <t>Zy Ka</t>
+  </si>
+  <si>
+    <t>HD023410</t>
+  </si>
+  <si>
+    <t>9 nguyễn trường tộ, p12</t>
+  </si>
+  <si>
+    <t>Chế Vân</t>
+  </si>
+  <si>
+    <t>HD023327</t>
+  </si>
+  <si>
+    <t>140b nguyễn văn trỗi p8</t>
+  </si>
+  <si>
+    <t>Tiger Nhỏ _ Gia Huy</t>
+  </si>
+  <si>
+    <t>HD023468</t>
+  </si>
+  <si>
+    <t>2/11 đường Thiên Phước, phường 9</t>
+  </si>
+  <si>
+    <t>HD023354</t>
+  </si>
+  <si>
+    <t>kh ck shop 2230k</t>
+  </si>
+  <si>
+    <t>Khuê</t>
+  </si>
+  <si>
+    <t>HD021688</t>
+  </si>
+  <si>
+    <t>38/9 thích quảng đức p15</t>
+  </si>
+  <si>
+    <t>HD023415</t>
+  </si>
+  <si>
+    <t>672 đường 3/2 P14</t>
+  </si>
+  <si>
+    <t>HD022967</t>
+  </si>
+  <si>
+    <t>Trần Thị Anh Đào</t>
+  </si>
+  <si>
+    <t>HD023440</t>
+  </si>
+  <si>
+    <t>333/35 Lý Thái Tổ, Phường 9</t>
+  </si>
+  <si>
+    <t>NGAY 27-5</t>
+  </si>
+  <si>
+    <t>T4.27.5.2026</t>
+  </si>
+  <si>
+    <t>NGÂN KIM</t>
+  </si>
+  <si>
+    <t>T8-20 mahattan vinhomes grand park, phường long bình</t>
+  </si>
+  <si>
+    <t>26-05-2026</t>
+  </si>
+  <si>
+    <t>Kỳ Kỳ</t>
+  </si>
+  <si>
+    <t>HD023748</t>
+  </si>
+  <si>
+    <t>Trường Tiểu học Vinschool Grand Park, Vinhome Grand Park</t>
+  </si>
+  <si>
+    <t>AT 26-05</t>
+  </si>
+  <si>
+    <t>66 đường 17 p10</t>
+  </si>
+  <si>
+    <t>Minh Thư</t>
+  </si>
+  <si>
+    <t>HD023706</t>
+  </si>
+  <si>
+    <t>6/24 tân chánh hiệp 36, p trung mỹ tây</t>
+  </si>
+  <si>
+    <t>Trang Angels</t>
+  </si>
+  <si>
+    <t>HD023627</t>
+  </si>
+  <si>
+    <t>nhà 20 đường 2B phường Tân mỹ</t>
+  </si>
+  <si>
+    <t>Nhi Le</t>
+  </si>
+  <si>
+    <t>HD023579</t>
+  </si>
+  <si>
+    <t>743/11/10 hong bang p6</t>
+  </si>
+  <si>
+    <t>HDO1779701391142_472517</t>
+  </si>
+  <si>
+    <t>169/15 đường số 11 phường bình hưng hoà</t>
+  </si>
+  <si>
+    <t>HD023631</t>
+  </si>
+  <si>
+    <t>Huyền Trang Trần</t>
+  </si>
+  <si>
+    <t>HD023630</t>
+  </si>
+  <si>
+    <t>39/34 dạ nam</t>
+  </si>
+  <si>
+    <t>Annie Annie</t>
+  </si>
+  <si>
+    <t>HD023732</t>
+  </si>
+  <si>
+    <t>110 đường 14 Him Lam tân hưng</t>
+  </si>
+  <si>
+    <t>Linh Mỹ</t>
+  </si>
+  <si>
+    <t>HD023715</t>
+  </si>
+  <si>
+    <t>50/2/8 đường số 2, phường 3</t>
+  </si>
+  <si>
+    <t>이 우준</t>
+  </si>
+  <si>
+    <t>HD023636</t>
+  </si>
+  <si>
+    <t>Linh P Pham</t>
+  </si>
+  <si>
+    <t>HD023620</t>
+  </si>
+  <si>
+    <t>129/34 Nguyễn Văn Công, phường 3, Phường Gò Vấp</t>
+  </si>
+  <si>
+    <t>Thanh Thanh</t>
+  </si>
+  <si>
+    <t>HD023734</t>
+  </si>
+  <si>
+    <t>Cozrum Homes Premier Residences 135/4 Nguyễn Cửu Vân, P.Gia Định</t>
+  </si>
+  <si>
+    <t>Truc Le</t>
+  </si>
+  <si>
+    <t>HD023726</t>
+  </si>
+  <si>
+    <t>69 đường số 2 khu phố 1 p tam bình</t>
+  </si>
+  <si>
+    <t>Nguyen Minh Thu</t>
+  </si>
+  <si>
+    <t>HD023677</t>
+  </si>
+  <si>
+    <t>Số 2 đường số 51 p bình trưng đông</t>
+  </si>
+  <si>
+    <t>BN1356</t>
+  </si>
+  <si>
+    <t>HD023491</t>
+  </si>
+  <si>
+    <t>HD023733</t>
+  </si>
+  <si>
+    <t>32/11 Bùi Đình Tuý f12</t>
+  </si>
+  <si>
+    <t>NGUYÊN NGUYÊN</t>
+  </si>
+  <si>
+    <t>12 TÔN ĐẢN P13</t>
+  </si>
+  <si>
+    <t>Nga Nga</t>
+  </si>
+  <si>
+    <t>HD023717</t>
+  </si>
+  <si>
+    <t>29b Nguyễn đình chiểu dakao</t>
+  </si>
+  <si>
+    <t>Ngọc Thư</t>
+  </si>
+  <si>
+    <t>HD023656</t>
+  </si>
+  <si>
+    <t>400cd lê hồng phong p1</t>
+  </si>
+  <si>
+    <t>Kim ngân</t>
+  </si>
+  <si>
+    <t>HD023657</t>
+  </si>
+  <si>
+    <t>50 An Dương Vương,P.9</t>
+  </si>
+  <si>
+    <t>Thảo Ngân</t>
+  </si>
+  <si>
+    <t>HD023768</t>
+  </si>
+  <si>
+    <t>44/139 trần bình trọng</t>
+  </si>
+  <si>
+    <t>FB HOÀNG THỦY</t>
+  </si>
+  <si>
+    <t>HD023619</t>
+  </si>
+  <si>
+    <t>86/36/3 PHỔ QUANG TÂN SƠN HÒA</t>
+  </si>
+  <si>
+    <t>đơn trả 27.5</t>
   </si>
 </sst>
 </file>
@@ -5969,7 +6534,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -6051,6 +6616,7 @@
     <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -26274,51 +26840,51 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G30" s="1">
-        <f>SUBTOTAL(9,G3:G29)</f>
+        <f t="shared" ref="G30:R30" si="4">SUBTOTAL(9,G3:G29)</f>
         <v>13780</v>
       </c>
       <c r="H30" s="1">
-        <f>SUBTOTAL(9,H3:H29)</f>
+        <f t="shared" si="4"/>
         <v>705</v>
       </c>
       <c r="I30" s="1">
-        <f>SUBTOTAL(9,I3:I29)</f>
+        <f t="shared" si="4"/>
         <v>13075</v>
       </c>
       <c r="J30" s="1">
-        <f>SUBTOTAL(9,J3:J29)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K30" s="1">
-        <f>SUBTOTAL(9,K3:K29)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L30" s="1">
-        <f>SUBTOTAL(9,L3:L29)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M30" s="1">
-        <f>SUBTOTAL(9,M3:M29)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N30" s="1">
-        <f>SUBTOTAL(9,N3:N29)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O30" s="1">
-        <f>SUBTOTAL(9,O3:O29)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P30" s="1">
-        <f>SUBTOTAL(9,P3:P29)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q30" s="1">
-        <f>SUBTOTAL(9,Q3:Q29)</f>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="R30" s="1">
-        <f>SUBTOTAL(9,R3:R29)</f>
+        <f t="shared" si="4"/>
         <v>350</v>
       </c>
     </row>
@@ -27548,7 +28114,4143 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3840F276-2063-46DB-90A8-8062375B1F9A}">
+  <dimension ref="A1:R72"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>1890</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="F3" s="23">
+        <v>12</v>
+      </c>
+      <c r="G3" s="23">
+        <v>820</v>
+      </c>
+      <c r="H3" s="23">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I55" si="0">G3-H3</f>
+        <v>790</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>1894</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="F4" s="23">
+        <v>7</v>
+      </c>
+      <c r="G4" s="23">
+        <v>470</v>
+      </c>
+      <c r="H4" s="23">
+        <v>30</v>
+      </c>
+      <c r="I4" s="23">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>1896</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="23">
+        <v>6</v>
+      </c>
+      <c r="G5" s="23">
+        <v>505</v>
+      </c>
+      <c r="H5" s="23">
+        <v>25</v>
+      </c>
+      <c r="I5" s="23">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>1897</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>1898</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G6" s="23">
+        <v>5640</v>
+      </c>
+      <c r="H6" s="23">
+        <v>55</v>
+      </c>
+      <c r="I6" s="23">
+        <f t="shared" si="0"/>
+        <v>5585</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M6" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+      <c r="R6" s="24">
+        <f>H6</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>1899</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>1900</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F7" s="23">
+        <v>12</v>
+      </c>
+      <c r="G7" s="23">
+        <v>0</v>
+      </c>
+      <c r="H7" s="23">
+        <v>30</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+      <c r="R7" s="24">
+        <f>H7</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>1902</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F8" s="23">
+        <v>8</v>
+      </c>
+      <c r="G8" s="23">
+        <v>850</v>
+      </c>
+      <c r="H8" s="23">
+        <v>30</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>1904</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>1905</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="23">
+        <v>690</v>
+      </c>
+      <c r="H9" s="23">
+        <v>30</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>1906</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>1907</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F10" s="23">
+        <v>5</v>
+      </c>
+      <c r="G10" s="23">
+        <v>845</v>
+      </c>
+      <c r="H10" s="23">
+        <v>25</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>1910</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>1911</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="23">
+        <v>465</v>
+      </c>
+      <c r="H11" s="23">
+        <v>25</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>1913</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>1914</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="23">
+        <v>845</v>
+      </c>
+      <c r="H12" s="23">
+        <v>25</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>1915</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F13" s="23">
+        <v>7</v>
+      </c>
+      <c r="G13" s="23">
+        <v>990</v>
+      </c>
+      <c r="H13" s="23">
+        <v>30</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>1917</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>1918</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>1919</v>
+      </c>
+      <c r="F14" s="23">
+        <v>8</v>
+      </c>
+      <c r="G14" s="23">
+        <v>1640</v>
+      </c>
+      <c r="H14" s="23">
+        <v>30</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>1610</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>737</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>1920</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>1921</v>
+      </c>
+      <c r="F15" s="23">
+        <v>7</v>
+      </c>
+      <c r="G15" s="23">
+        <v>1260</v>
+      </c>
+      <c r="H15" s="23">
+        <v>30</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
+        <v>1230</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>1581</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>1922</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F16" s="23">
+        <v>6</v>
+      </c>
+      <c r="G16" s="23">
+        <v>1735</v>
+      </c>
+      <c r="H16" s="23">
+        <v>25</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>1710</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>1924</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>1925</v>
+      </c>
+      <c r="F17" s="23">
+        <v>6</v>
+      </c>
+      <c r="G17" s="23">
+        <v>995</v>
+      </c>
+      <c r="H17" s="23">
+        <v>25</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
+        <v>970</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>987</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>1926</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>989</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" s="23">
+        <v>470</v>
+      </c>
+      <c r="H18" s="23">
+        <v>30</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>1928</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>1929</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="23">
+        <v>520</v>
+      </c>
+      <c r="H19" s="23">
+        <v>30</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>1930</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>1931</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="23">
+        <v>0</v>
+      </c>
+      <c r="H20" s="23">
+        <v>30</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+      <c r="R20" s="24">
+        <f>H20</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>1934</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>1935</v>
+      </c>
+      <c r="F21" s="23">
+        <v>7</v>
+      </c>
+      <c r="G21" s="23">
+        <v>810</v>
+      </c>
+      <c r="H21" s="23">
+        <v>30</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>1936</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22" s="23">
+        <v>795</v>
+      </c>
+      <c r="H22" s="23">
+        <v>25</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>650</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>1938</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>652</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23" s="23">
+        <v>995</v>
+      </c>
+      <c r="H23" s="23">
+        <v>25</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="0"/>
+        <v>970</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="55" t="s">
+        <v>1939</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>1940</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>1941</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G24" s="23">
+        <v>865</v>
+      </c>
+      <c r="H24" s="23">
+        <v>35</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>1942</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>1943</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>1944</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G25" s="23">
+        <v>0</v>
+      </c>
+      <c r="H25" s="23">
+        <v>25</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+      <c r="R25" s="24">
+        <f>H25</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>1946</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>1947</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="G26" s="23">
+        <v>2760</v>
+      </c>
+      <c r="H26" s="23">
+        <v>35</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="0"/>
+        <v>2725</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M26" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+      <c r="R26" s="24">
+        <f>H26</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>598</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>1948</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>1949</v>
+      </c>
+      <c r="F27" s="23">
+        <v>7</v>
+      </c>
+      <c r="G27" s="23">
+        <v>820</v>
+      </c>
+      <c r="H27" s="23">
+        <v>30</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>1950</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>1951</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>1952</v>
+      </c>
+      <c r="F28" s="23">
+        <v>7</v>
+      </c>
+      <c r="G28" s="23">
+        <v>810</v>
+      </c>
+      <c r="H28" s="23">
+        <v>30</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>1953</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>1954</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>1955</v>
+      </c>
+      <c r="F29" s="23">
+        <v>9</v>
+      </c>
+      <c r="G29" s="23">
+        <v>0</v>
+      </c>
+      <c r="H29" s="23">
+        <v>30</v>
+      </c>
+      <c r="I29" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22">
+        <v>1</v>
+      </c>
+      <c r="R29" s="24">
+        <f t="shared" ref="R29:R31" si="1">H29</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>864</v>
+      </c>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22" t="s">
+        <v>626</v>
+      </c>
+      <c r="F30" s="23">
+        <v>6</v>
+      </c>
+      <c r="G30" s="23">
+        <v>0</v>
+      </c>
+      <c r="H30" s="23">
+        <v>30</v>
+      </c>
+      <c r="I30" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22">
+        <v>1</v>
+      </c>
+      <c r="R30" s="24">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>1538</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>1956</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G31" s="23">
+        <v>0</v>
+      </c>
+      <c r="H31" s="23">
+        <v>20</v>
+      </c>
+      <c r="I31" s="23">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J31" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K31" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22">
+        <v>1</v>
+      </c>
+      <c r="R31" s="24">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>1958</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>1959</v>
+      </c>
+      <c r="F32" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G32" s="23">
+        <v>1855</v>
+      </c>
+      <c r="H32" s="23">
+        <v>25</v>
+      </c>
+      <c r="I32" s="23">
+        <f t="shared" si="0"/>
+        <v>1830</v>
+      </c>
+      <c r="J32" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K32" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L32" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>1961</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>1962</v>
+      </c>
+      <c r="F33" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G33" s="23">
+        <v>785</v>
+      </c>
+      <c r="H33" s="23">
+        <v>25</v>
+      </c>
+      <c r="I33" s="23">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J33" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K33" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M33" s="22"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>1964</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>1965</v>
+      </c>
+      <c r="F34" s="23">
+        <v>2</v>
+      </c>
+      <c r="G34" s="23">
+        <v>1110</v>
+      </c>
+      <c r="H34" s="23">
+        <v>30</v>
+      </c>
+      <c r="I34" s="23">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J34" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K34" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>1966</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>1860</v>
+      </c>
+      <c r="F35" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G35" s="23">
+        <v>60</v>
+      </c>
+      <c r="H35" s="23">
+        <v>20</v>
+      </c>
+      <c r="I35" s="23">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="J35" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K35" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M35" s="22"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>1967</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>1968</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F36" s="23">
+        <v>2</v>
+      </c>
+      <c r="G36" s="23">
+        <v>880</v>
+      </c>
+      <c r="H36" s="23">
+        <v>30</v>
+      </c>
+      <c r="I36" s="23">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J36" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K36" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="22"/>
+      <c r="B37" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>1970</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>1971</v>
+      </c>
+      <c r="F37" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G37" s="23">
+        <v>995</v>
+      </c>
+      <c r="H37" s="23">
+        <v>25</v>
+      </c>
+      <c r="I37" s="23">
+        <f t="shared" si="0"/>
+        <v>970</v>
+      </c>
+      <c r="J37" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K37" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L37" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="22"/>
+      <c r="Q37" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="22"/>
+      <c r="B38" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>865</v>
+      </c>
+      <c r="D38" s="22" t="s">
+        <v>1972</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>867</v>
+      </c>
+      <c r="F38" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G38" s="23">
+        <v>725</v>
+      </c>
+      <c r="H38" s="23">
+        <v>25</v>
+      </c>
+      <c r="I38" s="23">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="J38" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K38" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M38" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N38" s="22"/>
+      <c r="O38" s="22"/>
+      <c r="P38" s="22"/>
+      <c r="Q38" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="22"/>
+      <c r="B39" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="22" t="s">
+        <v>865</v>
+      </c>
+      <c r="D39" s="22" t="s">
+        <v>1973</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>867</v>
+      </c>
+      <c r="F39" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G39" s="23">
+        <v>850</v>
+      </c>
+      <c r="H39" s="23">
+        <v>0</v>
+      </c>
+      <c r="I39" s="23">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J39" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K39" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L39" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M39" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N39" s="22"/>
+      <c r="O39" s="22"/>
+      <c r="P39" s="22"/>
+      <c r="Q39" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="22"/>
+      <c r="B40" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>1974</v>
+      </c>
+      <c r="D40" s="22" t="s">
+        <v>1975</v>
+      </c>
+      <c r="E40" s="22" t="s">
+        <v>1976</v>
+      </c>
+      <c r="F40" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G40" s="23">
+        <v>845</v>
+      </c>
+      <c r="H40" s="23">
+        <v>25</v>
+      </c>
+      <c r="I40" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J40" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K40" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L40" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M40" s="22"/>
+      <c r="N40" s="22"/>
+      <c r="O40" s="22"/>
+      <c r="P40" s="22"/>
+      <c r="Q40" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="22"/>
+      <c r="B41" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" s="22" t="s">
+        <v>1977</v>
+      </c>
+      <c r="D41" s="22" t="s">
+        <v>1978</v>
+      </c>
+      <c r="E41" s="22" t="s">
+        <v>1979</v>
+      </c>
+      <c r="F41" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G41" s="23">
+        <v>715</v>
+      </c>
+      <c r="H41" s="23">
+        <v>25</v>
+      </c>
+      <c r="I41" s="23">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J41" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K41" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L41" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M41" s="22"/>
+      <c r="N41" s="22"/>
+      <c r="O41" s="22"/>
+      <c r="P41" s="22"/>
+      <c r="Q41" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="F42" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G42" s="23">
+        <v>2450</v>
+      </c>
+      <c r="H42" s="23">
+        <v>30</v>
+      </c>
+      <c r="I42" s="23">
+        <f t="shared" si="0"/>
+        <v>2420</v>
+      </c>
+      <c r="J42" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K42" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L42" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M42" s="22"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="22"/>
+      <c r="P42" s="22"/>
+      <c r="Q42" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" s="22" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F43" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G43" s="23">
+        <v>0</v>
+      </c>
+      <c r="H43" s="23">
+        <v>30</v>
+      </c>
+      <c r="I43" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J43" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K43" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L43" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M43" s="22"/>
+      <c r="N43" s="22"/>
+      <c r="O43" s="22"/>
+      <c r="P43" s="22"/>
+      <c r="Q43" s="22">
+        <v>1</v>
+      </c>
+      <c r="R43" s="24">
+        <f>H43</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B44" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="F44" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G44" s="23">
+        <v>370</v>
+      </c>
+      <c r="H44" s="23">
+        <v>30</v>
+      </c>
+      <c r="I44" s="23">
+        <f t="shared" si="0"/>
+        <v>340</v>
+      </c>
+      <c r="J44" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K44" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L44" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M44" s="22"/>
+      <c r="N44" s="22"/>
+      <c r="O44" s="22"/>
+      <c r="P44" s="22"/>
+      <c r="Q44" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="22"/>
+      <c r="B45" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>1980</v>
+      </c>
+      <c r="D45" s="22" t="s">
+        <v>1981</v>
+      </c>
+      <c r="E45" s="22" t="s">
+        <v>1982</v>
+      </c>
+      <c r="F45" s="23">
+        <v>1</v>
+      </c>
+      <c r="G45" s="23">
+        <v>0</v>
+      </c>
+      <c r="H45" s="23">
+        <v>25</v>
+      </c>
+      <c r="I45" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J45" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K45" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L45" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M45" s="22"/>
+      <c r="N45" s="22"/>
+      <c r="O45" s="22"/>
+      <c r="P45" s="22"/>
+      <c r="Q45" s="22">
+        <v>1</v>
+      </c>
+      <c r="R45" s="24">
+        <f>H45</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="22"/>
+      <c r="B46" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" s="22" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D46" s="22" t="s">
+        <v>1983</v>
+      </c>
+      <c r="E46" s="22" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F46" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="G46" s="23">
+        <v>1100</v>
+      </c>
+      <c r="H46" s="23">
+        <v>20</v>
+      </c>
+      <c r="I46" s="23">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J46" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K46" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L46" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M46" s="22"/>
+      <c r="N46" s="22"/>
+      <c r="O46" s="22"/>
+      <c r="P46" s="22"/>
+      <c r="Q46" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="22"/>
+      <c r="B47" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47" s="22" t="s">
+        <v>1984</v>
+      </c>
+      <c r="D47" s="22" t="s">
+        <v>1985</v>
+      </c>
+      <c r="E47" s="22" t="s">
+        <v>1986</v>
+      </c>
+      <c r="F47" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G47" s="23">
+        <v>995</v>
+      </c>
+      <c r="H47" s="23">
+        <v>25</v>
+      </c>
+      <c r="I47" s="23">
+        <f t="shared" si="0"/>
+        <v>970</v>
+      </c>
+      <c r="J47" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K47" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L47" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M47" s="22"/>
+      <c r="N47" s="22"/>
+      <c r="O47" s="22"/>
+      <c r="P47" s="22"/>
+      <c r="Q47" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="22"/>
+      <c r="B48" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>1987</v>
+      </c>
+      <c r="D48" s="22" t="s">
+        <v>1988</v>
+      </c>
+      <c r="E48" s="22" t="s">
+        <v>1989</v>
+      </c>
+      <c r="F48" s="23">
+        <v>4</v>
+      </c>
+      <c r="G48" s="23">
+        <v>845</v>
+      </c>
+      <c r="H48" s="23">
+        <v>25</v>
+      </c>
+      <c r="I48" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J48" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K48" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L48" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M48" s="22"/>
+      <c r="N48" s="22"/>
+      <c r="O48" s="22"/>
+      <c r="P48" s="22"/>
+      <c r="Q48" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="22"/>
+      <c r="B49" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D49" s="22" t="s">
+        <v>1991</v>
+      </c>
+      <c r="E49" s="22" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F49" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="G49" s="23">
+        <v>1010</v>
+      </c>
+      <c r="H49" s="23">
+        <v>20</v>
+      </c>
+      <c r="I49" s="23">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J49" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K49" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L49" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M49" s="22"/>
+      <c r="N49" s="22"/>
+      <c r="O49" s="22"/>
+      <c r="P49" s="22"/>
+      <c r="Q49" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="22"/>
+      <c r="B50" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D50" s="22" t="s">
+        <v>1994</v>
+      </c>
+      <c r="E50" s="22" t="s">
+        <v>1995</v>
+      </c>
+      <c r="F50" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G50" s="23">
+        <v>0</v>
+      </c>
+      <c r="H50" s="23">
+        <v>25</v>
+      </c>
+      <c r="I50" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J50" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K50" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L50" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M50" s="22"/>
+      <c r="N50" s="22"/>
+      <c r="O50" s="22"/>
+      <c r="P50" s="22"/>
+      <c r="Q50" s="22">
+        <v>1</v>
+      </c>
+      <c r="R50" s="24">
+        <f t="shared" ref="R50:R51" si="2">H50</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="22"/>
+      <c r="B51" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D51" s="22" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E51" s="22" t="s">
+        <v>1875</v>
+      </c>
+      <c r="F51" s="23">
+        <v>3</v>
+      </c>
+      <c r="G51" s="23">
+        <v>0</v>
+      </c>
+      <c r="H51" s="23">
+        <v>25</v>
+      </c>
+      <c r="I51" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J51" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K51" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L51" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M51" s="28" t="s">
+        <v>1997</v>
+      </c>
+      <c r="N51" s="22"/>
+      <c r="O51" s="22"/>
+      <c r="P51" s="22"/>
+      <c r="Q51" s="22">
+        <v>1</v>
+      </c>
+      <c r="R51" s="24">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="22"/>
+      <c r="B52" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="22" t="s">
+        <v>1998</v>
+      </c>
+      <c r="D52" s="22" t="s">
+        <v>1999</v>
+      </c>
+      <c r="E52" s="22" t="s">
+        <v>2000</v>
+      </c>
+      <c r="F52" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="G52" s="23">
+        <v>390</v>
+      </c>
+      <c r="H52" s="23">
+        <v>20</v>
+      </c>
+      <c r="I52" s="23">
+        <f t="shared" si="0"/>
+        <v>370</v>
+      </c>
+      <c r="J52" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K52" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L52" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M52" s="22"/>
+      <c r="N52" s="22"/>
+      <c r="O52" s="22"/>
+      <c r="P52" s="22"/>
+      <c r="Q52" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="22"/>
+      <c r="B53" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="22" t="s">
+        <v>714</v>
+      </c>
+      <c r="D53" s="22" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E53" s="22" t="s">
+        <v>2002</v>
+      </c>
+      <c r="F53" s="23">
+        <v>10</v>
+      </c>
+      <c r="G53" s="23">
+        <v>845</v>
+      </c>
+      <c r="H53" s="23">
+        <v>25</v>
+      </c>
+      <c r="I53" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J53" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K53" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L53" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M53" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N53" s="22"/>
+      <c r="O53" s="22"/>
+      <c r="P53" s="22"/>
+      <c r="Q53" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="22"/>
+      <c r="B54" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" s="22" t="s">
+        <v>714</v>
+      </c>
+      <c r="D54" s="22" t="s">
+        <v>2003</v>
+      </c>
+      <c r="E54" s="22" t="s">
+        <v>2002</v>
+      </c>
+      <c r="F54" s="23">
+        <v>10</v>
+      </c>
+      <c r="G54" s="23">
+        <v>770</v>
+      </c>
+      <c r="H54" s="23">
+        <v>0</v>
+      </c>
+      <c r="I54" s="23">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J54" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K54" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L54" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M54" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N54" s="22"/>
+      <c r="O54" s="22"/>
+      <c r="P54" s="22"/>
+      <c r="Q54" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="22"/>
+      <c r="B55" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" s="22" t="s">
+        <v>2004</v>
+      </c>
+      <c r="D55" s="22" t="s">
+        <v>2005</v>
+      </c>
+      <c r="E55" s="22" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F55" s="23">
+        <v>10</v>
+      </c>
+      <c r="G55" s="23">
+        <v>465</v>
+      </c>
+      <c r="H55" s="23">
+        <v>25</v>
+      </c>
+      <c r="I55" s="23">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J55" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K55" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L55" s="22" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M55" s="22"/>
+      <c r="N55" s="22"/>
+      <c r="O55" s="22"/>
+      <c r="P55" s="22"/>
+      <c r="Q55" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G57" s="1">
+        <f t="shared" ref="G57:R57" si="3">SUBTOTAL(9,G3:G56)</f>
+        <v>44655</v>
+      </c>
+      <c r="H57" s="1">
+        <f t="shared" si="3"/>
+        <v>1405</v>
+      </c>
+      <c r="I57" s="1">
+        <f t="shared" si="3"/>
+        <v>43250</v>
+      </c>
+      <c r="J57" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L57" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M57" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N57" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O57" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P57" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q57" s="1">
+        <f t="shared" si="3"/>
+        <v>53</v>
+      </c>
+      <c r="R57" s="1">
+        <f t="shared" si="3"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H61" s="4" t="s">
+        <v>1826</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H62" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I62" s="8">
+        <f>SUM(I56:I60)</f>
+        <v>43250</v>
+      </c>
+      <c r="J62" s="8">
+        <f>Q57</f>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H63" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I63" s="10">
+        <f>R57</f>
+        <v>360</v>
+      </c>
+      <c r="J63" s="11"/>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H64" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I64" s="10">
+        <f>S56</f>
+        <v>0</v>
+      </c>
+      <c r="J64" s="11"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H65" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I65" s="10">
+        <f>T56</f>
+        <v>0</v>
+      </c>
+      <c r="J65" s="11"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H66" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I66" s="10">
+        <f>U56</f>
+        <v>0</v>
+      </c>
+      <c r="J66" s="11"/>
+    </row>
+    <row r="67" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H67" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I67" s="13"/>
+      <c r="J67" s="13"/>
+    </row>
+    <row r="68" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H68" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+    </row>
+    <row r="69" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H69" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I69" s="16">
+        <f>SUM(I62:I68)</f>
+        <v>43610</v>
+      </c>
+      <c r="J69" s="16">
+        <f>SUM(J62:J66)</f>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B72" s="36" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C72" s="36" t="s">
+        <v>1996</v>
+      </c>
+      <c r="D72" s="36" t="s">
+        <v>1875</v>
+      </c>
+      <c r="E72" s="37">
+        <v>3</v>
+      </c>
+      <c r="F72" s="37">
+        <v>2230</v>
+      </c>
+      <c r="G72" s="37">
+        <v>0</v>
+      </c>
+      <c r="H72" s="37">
+        <f t="shared" ref="H72" si="4">F72-G72</f>
+        <v>2230</v>
+      </c>
+      <c r="I72" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="J72" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="K72" s="36" t="s">
+        <v>1893</v>
+      </c>
+      <c r="L72" s="28" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P55" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P55">
+      <sortCondition ref="J2:J55"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77CFE5FA-3A0A-4FBF-A036-7CE4C38D04EE}">
+  <dimension ref="A1:R43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>2009</v>
+      </c>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22" t="s">
+        <v>2010</v>
+      </c>
+      <c r="F3" s="23">
+        <v>9</v>
+      </c>
+      <c r="G3" s="23">
+        <v>1545</v>
+      </c>
+      <c r="H3" s="23">
+        <v>35</v>
+      </c>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I29" si="0">G3-H3</f>
+        <v>1510</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>2013</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>2014</v>
+      </c>
+      <c r="F4" s="23">
+        <v>9</v>
+      </c>
+      <c r="G4" s="23">
+        <v>880</v>
+      </c>
+      <c r="H4" s="23">
+        <v>30</v>
+      </c>
+      <c r="I4" s="23">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22" t="s">
+        <v>863</v>
+      </c>
+      <c r="F5" s="23">
+        <v>5</v>
+      </c>
+      <c r="G5" s="23">
+        <v>30</v>
+      </c>
+      <c r="H5" s="23">
+        <v>30</v>
+      </c>
+      <c r="I5" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22" t="s">
+        <v>2016</v>
+      </c>
+      <c r="F6" s="23">
+        <v>6</v>
+      </c>
+      <c r="G6" s="23">
+        <v>0</v>
+      </c>
+      <c r="H6" s="23">
+        <v>30</v>
+      </c>
+      <c r="I6" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+      <c r="R6" s="24">
+        <f>H6</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>2018</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>2019</v>
+      </c>
+      <c r="F7" s="23">
+        <v>12</v>
+      </c>
+      <c r="G7" s="23">
+        <v>2270</v>
+      </c>
+      <c r="H7" s="23">
+        <v>30</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
+        <v>2240</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M7" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+      <c r="R7" s="24">
+        <f>H7</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>2020</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>2021</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>2022</v>
+      </c>
+      <c r="F8" s="23">
+        <v>7</v>
+      </c>
+      <c r="G8" s="23">
+        <v>2110</v>
+      </c>
+      <c r="H8" s="23">
+        <v>30</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>2080</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M8" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+      <c r="R8" s="24">
+        <f>H8</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>2023</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>2025</v>
+      </c>
+      <c r="F9" s="23">
+        <v>6</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0</v>
+      </c>
+      <c r="H9" s="23">
+        <v>25</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+      <c r="R9" s="24">
+        <f>H9</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>2026</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>2027</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="23">
+        <v>380</v>
+      </c>
+      <c r="H10" s="23">
+        <v>30</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>2028</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="F11" s="23">
+        <v>7</v>
+      </c>
+      <c r="G11" s="23">
+        <v>510</v>
+      </c>
+      <c r="H11" s="23">
+        <v>30</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="25"/>
+      <c r="B12" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>2029</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>2030</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>2031</v>
+      </c>
+      <c r="F12" s="26">
+        <v>8</v>
+      </c>
+      <c r="G12" s="26">
+        <v>0</v>
+      </c>
+      <c r="H12" s="26">
+        <v>30</v>
+      </c>
+      <c r="I12" s="26">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J12" s="25" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K12" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="25" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M12" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="25">
+        <v>1</v>
+      </c>
+      <c r="R12" s="31">
+        <f>H12</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>2033</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>2034</v>
+      </c>
+      <c r="F13" s="23">
+        <v>7</v>
+      </c>
+      <c r="G13" s="23">
+        <v>920</v>
+      </c>
+      <c r="H13" s="23">
+        <v>30</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>2035</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>2036</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>2037</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="23">
+        <v>0</v>
+      </c>
+      <c r="H14" s="23">
+        <v>25</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+      <c r="R14" s="24">
+        <f>H14</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>2039</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>1716</v>
+      </c>
+      <c r="F15" s="23">
+        <v>2</v>
+      </c>
+      <c r="G15" s="23">
+        <v>510</v>
+      </c>
+      <c r="H15" s="23">
+        <v>30</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>2040</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>2030</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="23">
+        <v>870</v>
+      </c>
+      <c r="H16" s="23">
+        <v>20</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>469</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>2041</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>2042</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="23">
+        <v>685</v>
+      </c>
+      <c r="H17" s="23">
+        <v>25</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>2043</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>2044</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" s="23">
+        <v>740</v>
+      </c>
+      <c r="H18" s="23">
+        <v>20</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>2048</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="23">
+        <v>920</v>
+      </c>
+      <c r="H19" s="23">
+        <v>30</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>2051</v>
+      </c>
+      <c r="F20" s="23">
+        <v>2</v>
+      </c>
+      <c r="G20" s="23">
+        <v>2410</v>
+      </c>
+      <c r="H20" s="23">
+        <v>35</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>2375</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M20" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+      <c r="R20" s="24">
+        <f>H20</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>2052</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>2053</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="F21" s="23">
+        <v>12</v>
+      </c>
+      <c r="G21" s="23">
+        <v>0</v>
+      </c>
+      <c r="H21" s="23">
+        <v>30</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+      <c r="R21" s="24">
+        <f>H21</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>2054</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>2055</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" s="23">
+        <v>890</v>
+      </c>
+      <c r="H22" s="23">
+        <v>20</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>2056</v>
+      </c>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F23" s="23">
+        <v>4</v>
+      </c>
+      <c r="G23" s="23">
+        <v>30</v>
+      </c>
+      <c r="H23" s="23">
+        <v>30</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="23">
+        <v>0</v>
+      </c>
+      <c r="H24" s="23">
+        <v>30</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22">
+        <v>1</v>
+      </c>
+      <c r="R24" s="24">
+        <f>H24</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>2060</v>
+      </c>
+      <c r="F25" s="23">
+        <v>1</v>
+      </c>
+      <c r="G25" s="23">
+        <v>855</v>
+      </c>
+      <c r="H25" s="23">
+        <v>25</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>2062</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>2063</v>
+      </c>
+      <c r="F26" s="23">
+        <v>10</v>
+      </c>
+      <c r="G26" s="23">
+        <v>1145</v>
+      </c>
+      <c r="H26" s="23">
+        <v>25</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>2064</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>2065</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>2066</v>
+      </c>
+      <c r="F27" s="23">
+        <v>5</v>
+      </c>
+      <c r="G27" s="23">
+        <v>1015</v>
+      </c>
+      <c r="H27" s="23">
+        <v>25</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>2067</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>2068</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>2069</v>
+      </c>
+      <c r="F28" s="23">
+        <v>5</v>
+      </c>
+      <c r="G28" s="23">
+        <v>1115</v>
+      </c>
+      <c r="H28" s="23">
+        <v>25</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="0"/>
+        <v>1090</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>2070</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>2071</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>2072</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G29" s="23">
+        <v>0</v>
+      </c>
+      <c r="H29" s="23">
+        <v>25</v>
+      </c>
+      <c r="I29" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22">
+        <v>1</v>
+      </c>
+      <c r="R29" s="24">
+        <f>H29</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G31" s="1">
+        <f>SUBTOTAL(9,G3:G30)</f>
+        <v>19830</v>
+      </c>
+      <c r="H31" s="1">
+        <f>SUBTOTAL(9,H3:H30)</f>
+        <v>750</v>
+      </c>
+      <c r="I31" s="1">
+        <f>SUBTOTAL(9,I3:I30)</f>
+        <v>19080</v>
+      </c>
+      <c r="J31" s="1">
+        <f>SUBTOTAL(9,J3:J30)</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
+        <f>SUBTOTAL(9,K3:K30)</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="1">
+        <f>SUBTOTAL(9,L3:L30)</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <f>SUBTOTAL(9,M3:M30)</f>
+        <v>0</v>
+      </c>
+      <c r="N31" s="1">
+        <f>SUBTOTAL(9,N3:N30)</f>
+        <v>0</v>
+      </c>
+      <c r="O31" s="1">
+        <f>SUBTOTAL(9,O3:O30)</f>
+        <v>0</v>
+      </c>
+      <c r="P31" s="1">
+        <f>SUBTOTAL(9,P3:P30)</f>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="1">
+        <f>SUBTOTAL(9,Q3:Q30)</f>
+        <v>27</v>
+      </c>
+      <c r="R31" s="1">
+        <f>SUBTOTAL(9,R3:R30)</f>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I32" s="1">
+        <v>-4330</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="35" spans="8:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H35" s="4" t="s">
+        <v>1887</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H36" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36" s="8">
+        <f>SUM(I30:I34)</f>
+        <v>14750</v>
+      </c>
+      <c r="J36" s="8">
+        <f>Q31</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="10">
+        <f>R31</f>
+        <v>290</v>
+      </c>
+      <c r="J37" s="11"/>
+    </row>
+    <row r="38" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H38" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" s="10">
+        <f>S30</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="11"/>
+    </row>
+    <row r="39" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H39" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I39" s="10">
+        <f>T30</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="11"/>
+    </row>
+    <row r="40" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H40" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I40" s="10">
+        <f>U30</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="11"/>
+    </row>
+    <row r="41" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H41" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+    </row>
+    <row r="42" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H42" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I42" s="13"/>
+      <c r="J42" s="13"/>
+    </row>
+    <row r="43" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H43" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43" s="16">
+        <f>SUM(I36:I42)</f>
+        <v>15040</v>
+      </c>
+      <c r="J43" s="16">
+        <f>SUM(J36:J40)</f>
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P29" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P29">
+      <sortCondition ref="J2:J29"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16D431B5-6A22-4DF7-8507-2FFA70595544}">
   <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -27565,10 +32267,10 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>205</v>
+        <v>270</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1825</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -28721,7 +33423,7 @@
     </row>
     <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H62" s="4" t="s">
-        <v>1826</v>
+        <v>2008</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>15</v>

--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5AB279-F322-4AAF-9859-333043739DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E9D181-64A2-48B3-9894-EDEC19ED85E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-5" sheetId="3" r:id="rId1"/>
@@ -35,6 +35,8 @@
     <sheet name="25-5" sheetId="23" r:id="rId20"/>
     <sheet name="26-5" sheetId="22" r:id="rId21"/>
     <sheet name="27-5" sheetId="24" r:id="rId22"/>
+    <sheet name="28-5" sheetId="25" r:id="rId23"/>
+    <sheet name="29-5" sheetId="26" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'11-5'!$A$2:$P$58</definedName>
@@ -52,7 +54,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'23-5'!$A$2:$P$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'25-5'!$A$2:$P$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'26-5'!$A$2:$P$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'27-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'27-5'!$A$2:$P$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'28-5'!$A$2:$P$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'29-5'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'4-5'!$A$2:$P$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'5-5'!$A$2:$P$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'6-5'!$A$2:$P$34</definedName>
@@ -81,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6408" uniqueCount="2074">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6875" uniqueCount="2209">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -6303,6 +6307,411 @@
   </si>
   <si>
     <t>đơn trả 27.5</t>
+  </si>
+  <si>
+    <t>T5.28.5.2026</t>
+  </si>
+  <si>
+    <t>NGAY 28-5</t>
+  </si>
+  <si>
+    <t>HD023837</t>
+  </si>
+  <si>
+    <t>Can 32.07 - the Pegasuite 1- số 1002 tạ quang bửu, phường 5</t>
+  </si>
+  <si>
+    <t>AT 27-05</t>
+  </si>
+  <si>
+    <t>27-05-2026</t>
+  </si>
+  <si>
+    <t>HD023572</t>
+  </si>
+  <si>
+    <t>HD023905</t>
+  </si>
+  <si>
+    <t>HD023917</t>
+  </si>
+  <si>
+    <t>195 tân hương P phú thọ hoà</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Ngọc Hân</t>
+  </si>
+  <si>
+    <t>HD023783</t>
+  </si>
+  <si>
+    <t>512 phạm thế hiển p4</t>
+  </si>
+  <si>
+    <t>Thiên An</t>
+  </si>
+  <si>
+    <t>HD023884</t>
+  </si>
+  <si>
+    <t>D aqua 301 bình động, phú định</t>
+  </si>
+  <si>
+    <t>S$3164-Mrskill)</t>
+  </si>
+  <si>
+    <t>HD022602</t>
+  </si>
+  <si>
+    <t>674 đường số 2, Phường 13</t>
+  </si>
+  <si>
+    <t>Khánh Như</t>
+  </si>
+  <si>
+    <t>HD023944</t>
+  </si>
+  <si>
+    <t>688/23/1c Hương Lộ 2, phường Bình Trị Đông A</t>
+  </si>
+  <si>
+    <t>Hoàng Trang</t>
+  </si>
+  <si>
+    <t>HD023850</t>
+  </si>
+  <si>
+    <t>1041/80/3/5 trần xuân soạn phường tân hưng</t>
+  </si>
+  <si>
+    <t>cô Loan fb Trịnh Trâm</t>
+  </si>
+  <si>
+    <t>HD023930</t>
+  </si>
+  <si>
+    <t>124/18/12 võ văn hát p long trường</t>
+  </si>
+  <si>
+    <t>NHƯ THẢO</t>
+  </si>
+  <si>
+    <t>259 đường 9a kdc Trung Sơn, Bình Hưng</t>
+  </si>
+  <si>
+    <t>Nhận hộ fb Nguyễn Hà</t>
+  </si>
+  <si>
+    <t>HD023711</t>
+  </si>
+  <si>
+    <t>Thúy Nguyễn</t>
+  </si>
+  <si>
+    <t>HD023794</t>
+  </si>
+  <si>
+    <t>598/10 điện biên phủ, p.22</t>
+  </si>
+  <si>
+    <t>ng nhận QP</t>
+  </si>
+  <si>
+    <t>HD023827</t>
+  </si>
+  <si>
+    <t>số 28 khu kdc nam long thạnh lộc</t>
+  </si>
+  <si>
+    <t>Giang Phạm</t>
+  </si>
+  <si>
+    <t>HD023787</t>
+  </si>
+  <si>
+    <t>136 hoàng hoa thám, p7</t>
+  </si>
+  <si>
+    <t>W24130 Miki (Chou)</t>
+  </si>
+  <si>
+    <t>HD023903</t>
+  </si>
+  <si>
+    <t>624 Lê thị riêng, thới an</t>
+  </si>
+  <si>
+    <t>SỈ HƯƠNG TRẦN</t>
+  </si>
+  <si>
+    <t>HUYỀN NGUYỄN</t>
+  </si>
+  <si>
+    <t>HD023936</t>
+  </si>
+  <si>
+    <t>Số 8 Ba Vì, P4</t>
+  </si>
+  <si>
+    <t>HD023906</t>
+  </si>
+  <si>
+    <t>77-89 nam kỳ khởi nghĩa bến thành</t>
+  </si>
+  <si>
+    <t>KimVy Phương Anh</t>
+  </si>
+  <si>
+    <t>HD023841</t>
+  </si>
+  <si>
+    <t>214/B14A nguyễn trãi, cầu ông lãnh</t>
+  </si>
+  <si>
+    <t>Thao Thanh Nguyen</t>
+  </si>
+  <si>
+    <t>HD023781</t>
+  </si>
+  <si>
+    <t>53 trần đình xu p cầu kho</t>
+  </si>
+  <si>
+    <t>GIA HUY nhận hộ ELIS NGUYỄN (singapore)</t>
+  </si>
+  <si>
+    <t>HD023838</t>
+  </si>
+  <si>
+    <t>Ellie Quach</t>
+  </si>
+  <si>
+    <t>8A Sông thương, Phường 2</t>
+  </si>
+  <si>
+    <t>NGAY 29-5</t>
+  </si>
+  <si>
+    <t>T6.29.5.2026</t>
+  </si>
+  <si>
+    <t>Uyên Trần</t>
+  </si>
+  <si>
+    <t>HD024168</t>
+  </si>
+  <si>
+    <t>137/84D âu dương lân - p2</t>
+  </si>
+  <si>
+    <t>AT 28-05</t>
+  </si>
+  <si>
+    <t>28-05-2026</t>
+  </si>
+  <si>
+    <t>Thanh Vy</t>
+  </si>
+  <si>
+    <t>HD024163</t>
+  </si>
+  <si>
+    <t>20B Trần Văn Quang, Phường Bảy Hiền</t>
+  </si>
+  <si>
+    <t>Thủy Heri</t>
+  </si>
+  <si>
+    <t>HD024145</t>
+  </si>
+  <si>
+    <t>184/17/35 bãi sậy phường bình tiên</t>
+  </si>
+  <si>
+    <t>Ngân</t>
+  </si>
+  <si>
+    <t>HD023968</t>
+  </si>
+  <si>
+    <t>Toà A2 Alnata diamond đường N1 Tân Sơn Nhì</t>
+  </si>
+  <si>
+    <t>HD023918</t>
+  </si>
+  <si>
+    <t>Diễm Phúc</t>
+  </si>
+  <si>
+    <t>HD024175</t>
+  </si>
+  <si>
+    <t>314/138 đường âu dương lân, p3</t>
+  </si>
+  <si>
+    <t>khả trinh</t>
+  </si>
+  <si>
+    <t>HD024033</t>
+  </si>
+  <si>
+    <t>82/17/20đinh tiên hoàng p1</t>
+  </si>
+  <si>
+    <t>Linh fb Phan Thị Tuyết Nhung</t>
+  </si>
+  <si>
+    <t>HD023982</t>
+  </si>
+  <si>
+    <t>201 Đường Hoàng Hoa Thám, Phường 13</t>
+  </si>
+  <si>
+    <t>Nguyễn Châu Tuệ Lâm</t>
+  </si>
+  <si>
+    <t>HD024027</t>
+  </si>
+  <si>
+    <t>74/1h ds9 linh trung</t>
+  </si>
+  <si>
+    <t>HD024142</t>
+  </si>
+  <si>
+    <t>Nguyễn Trinh</t>
+  </si>
+  <si>
+    <t>HD024157</t>
+  </si>
+  <si>
+    <t>29/10c trần thái tông</t>
+  </si>
+  <si>
+    <t>Minh Thư nhận hộ ( water) fb Thuỷ Vũ</t>
+  </si>
+  <si>
+    <t>HD024179</t>
+  </si>
+  <si>
+    <t>22, TÂN THỚI NHẤT 1B, Phường Tân Thới Nhất</t>
+  </si>
+  <si>
+    <t>HD023972</t>
+  </si>
+  <si>
+    <t>433/11, Lê Đức Thọ, Phường 17</t>
+  </si>
+  <si>
+    <t>chị hương fb Kim Tien Pham</t>
+  </si>
+  <si>
+    <t>HD024001</t>
+  </si>
+  <si>
+    <t>Trần Lan</t>
+  </si>
+  <si>
+    <t>HD024017</t>
+  </si>
+  <si>
+    <t>190 võ văn ngân</t>
+  </si>
+  <si>
+    <t>phạm minh phi_F3: Theer To Lao</t>
+  </si>
+  <si>
+    <t>HD024093</t>
+  </si>
+  <si>
+    <t>33 đường số 6 p26</t>
+  </si>
+  <si>
+    <t>Đậu Đậu</t>
+  </si>
+  <si>
+    <t>HD024181</t>
+  </si>
+  <si>
+    <t>106/4 phan van tri phường 12</t>
+  </si>
+  <si>
+    <t>kh ck shop 2020k</t>
+  </si>
+  <si>
+    <t>HD024164</t>
+  </si>
+  <si>
+    <t>Toà Aster - Urbun Green (đối diện Vạn Phúc)</t>
+  </si>
+  <si>
+    <t>Linh Nga Anna</t>
+  </si>
+  <si>
+    <t>Thảo My</t>
+  </si>
+  <si>
+    <t>HD024170</t>
+  </si>
+  <si>
+    <t>91/12 nguyễn thanh tuyền p1</t>
+  </si>
+  <si>
+    <t>Kelly Phan</t>
+  </si>
+  <si>
+    <t>HD024129</t>
+  </si>
+  <si>
+    <t>240/6A lê thánh tôn phường bến thành</t>
+  </si>
+  <si>
+    <t>Tuệ Nhi</t>
+  </si>
+  <si>
+    <t>HD024045</t>
+  </si>
+  <si>
+    <t>92-94 nam kỳ khởi nghĩa- bến nghé</t>
+  </si>
+  <si>
+    <t>kh ck shop 845k</t>
+  </si>
+  <si>
+    <t>HD024006</t>
+  </si>
+  <si>
+    <t>24 Lê Thánh Tôn (BIDV), P.Bến Nghé</t>
+  </si>
+  <si>
+    <t>kh ck shop 465k</t>
+  </si>
+  <si>
+    <t>Tất Phú</t>
+  </si>
+  <si>
+    <t>HD023941</t>
+  </si>
+  <si>
+    <t>Bệnh viện Nhi đồng 1: 532 Lý Thái Tổ, P10</t>
+  </si>
+  <si>
+    <t>Cô Kiều Hương fb Vân Trần</t>
+  </si>
+  <si>
+    <t>HD023954</t>
+  </si>
+  <si>
+    <t>168A Trần Huy Liệu Phường 15</t>
+  </si>
+  <si>
+    <t>HD023966</t>
+  </si>
+  <si>
+    <t>12 nguyễn công trứ, thái bình</t>
+  </si>
+  <si>
+    <t>đơn trả 29.5</t>
   </si>
 </sst>
 </file>
@@ -32091,51 +32500,51 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G31" s="1">
-        <f>SUBTOTAL(9,G3:G30)</f>
+        <f t="shared" ref="G31:R31" si="1">SUBTOTAL(9,G3:G30)</f>
         <v>19830</v>
       </c>
       <c r="H31" s="1">
-        <f>SUBTOTAL(9,H3:H30)</f>
+        <f t="shared" si="1"/>
         <v>750</v>
       </c>
       <c r="I31" s="1">
-        <f>SUBTOTAL(9,I3:I30)</f>
+        <f t="shared" si="1"/>
         <v>19080</v>
       </c>
       <c r="J31" s="1">
-        <f>SUBTOTAL(9,J3:J30)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K31" s="1">
-        <f>SUBTOTAL(9,K3:K30)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L31" s="1">
-        <f>SUBTOTAL(9,L3:L30)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M31" s="1">
-        <f>SUBTOTAL(9,M3:M30)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N31" s="1">
-        <f>SUBTOTAL(9,N3:N30)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O31" s="1">
-        <f>SUBTOTAL(9,O3:O30)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P31" s="1">
-        <f>SUBTOTAL(9,P3:P30)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q31" s="1">
-        <f>SUBTOTAL(9,Q3:Q30)</f>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="R31" s="1">
-        <f>SUBTOTAL(9,R3:R30)</f>
+        <f t="shared" si="1"/>
         <v>290</v>
       </c>
     </row>
@@ -32251,6 +32660,2880 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16D431B5-6A22-4DF7-8507-2FFA70595544}">
+  <dimension ref="A1:R40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>1799</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>2076</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>2077</v>
+      </c>
+      <c r="F3" s="23">
+        <v>8</v>
+      </c>
+      <c r="G3" s="23">
+        <v>810</v>
+      </c>
+      <c r="H3" s="23">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I26" si="0">G3-H3</f>
+        <v>780</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>2078</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>2080</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>736</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="23">
+        <v>0</v>
+      </c>
+      <c r="H4" s="23">
+        <v>30</v>
+      </c>
+      <c r="I4" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>2078</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+      <c r="R4" s="24">
+        <f>H4</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>2081</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>1434</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="23">
+        <v>0</v>
+      </c>
+      <c r="H5" s="23">
+        <v>30</v>
+      </c>
+      <c r="I5" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>2078</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+      <c r="R5" s="24">
+        <f t="shared" ref="R5:R6" si="1">H5</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>2082</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>2083</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="23">
+        <v>0</v>
+      </c>
+      <c r="H6" s="23">
+        <v>25</v>
+      </c>
+      <c r="I6" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>2078</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+      <c r="R6" s="24">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>2084</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F7" s="23">
+        <v>8</v>
+      </c>
+      <c r="G7" s="23">
+        <v>470</v>
+      </c>
+      <c r="H7" s="23">
+        <v>30</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>2078</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>2087</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>2088</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>2089</v>
+      </c>
+      <c r="F8" s="26">
+        <v>8</v>
+      </c>
+      <c r="G8" s="26">
+        <v>740</v>
+      </c>
+      <c r="H8" s="26">
+        <v>30</v>
+      </c>
+      <c r="I8" s="26">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>2078</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="25" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M8" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>2092</v>
+      </c>
+      <c r="F9" s="23">
+        <v>6</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0</v>
+      </c>
+      <c r="H9" s="23">
+        <v>25</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>2078</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+      <c r="R9" s="24">
+        <f>H9</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>2093</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>2094</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="23">
+        <v>850</v>
+      </c>
+      <c r="H10" s="23">
+        <v>30</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>2078</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>2097</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>2098</v>
+      </c>
+      <c r="F11" s="23">
+        <v>7</v>
+      </c>
+      <c r="G11" s="23">
+        <v>820</v>
+      </c>
+      <c r="H11" s="23">
+        <v>30</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>2078</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>2099</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>2100</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>2101</v>
+      </c>
+      <c r="F12" s="23">
+        <v>9</v>
+      </c>
+      <c r="G12" s="23">
+        <v>920</v>
+      </c>
+      <c r="H12" s="23">
+        <v>30</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>2078</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>2102</v>
+      </c>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22" t="s">
+        <v>2103</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G13" s="23">
+        <v>700</v>
+      </c>
+      <c r="H13" s="23">
+        <v>40</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>2078</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>2104</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>1358</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="23">
+        <v>1765</v>
+      </c>
+      <c r="H14" s="23">
+        <v>25</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>1740</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>2106</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>2107</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>2108</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="23">
+        <v>940</v>
+      </c>
+      <c r="H15" s="23">
+        <v>20</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>2109</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>2110</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>2111</v>
+      </c>
+      <c r="F16" s="23">
+        <v>12</v>
+      </c>
+      <c r="G16" s="23">
+        <v>0</v>
+      </c>
+      <c r="H16" s="23">
+        <v>30</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+      <c r="R16" s="24">
+        <f>H16</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>2112</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>2114</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="23">
+        <v>680</v>
+      </c>
+      <c r="H17" s="23">
+        <v>20</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>2115</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>2116</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>2117</v>
+      </c>
+      <c r="F18" s="23">
+        <v>12</v>
+      </c>
+      <c r="G18" s="23">
+        <v>0</v>
+      </c>
+      <c r="H18" s="23">
+        <v>30</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+      <c r="R18" s="24">
+        <f>H18</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>2118</v>
+      </c>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22" t="s">
+        <v>904</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="23">
+        <v>735</v>
+      </c>
+      <c r="H19" s="23">
+        <v>25</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>2120</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>2121</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G20" s="23">
+        <v>310</v>
+      </c>
+      <c r="H20" s="23">
+        <v>25</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>285</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>558</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>2122</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>2123</v>
+      </c>
+      <c r="F21" s="23">
+        <v>1</v>
+      </c>
+      <c r="G21" s="23">
+        <v>805</v>
+      </c>
+      <c r="H21" s="23">
+        <v>25</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>2124</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>2125</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>2126</v>
+      </c>
+      <c r="F22" s="23">
+        <v>1</v>
+      </c>
+      <c r="G22" s="23">
+        <v>845</v>
+      </c>
+      <c r="H22" s="23">
+        <v>25</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>2127</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>2128</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>2129</v>
+      </c>
+      <c r="F23" s="23">
+        <v>1</v>
+      </c>
+      <c r="G23" s="23">
+        <v>845</v>
+      </c>
+      <c r="H23" s="23">
+        <v>25</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>2130</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>2131</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="23">
+        <v>0</v>
+      </c>
+      <c r="H24" s="23">
+        <v>25</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22">
+        <v>1</v>
+      </c>
+      <c r="R24" s="24">
+        <f t="shared" ref="R24:R26" si="2">H24</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G25" s="23">
+        <v>0</v>
+      </c>
+      <c r="H25" s="23">
+        <v>30</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+      <c r="R25" s="24">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>2132</v>
+      </c>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G26" s="23">
+        <v>0</v>
+      </c>
+      <c r="H26" s="23">
+        <v>30</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+      <c r="R26" s="24">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G28" s="1">
+        <f t="shared" ref="G28:R28" si="3">SUBTOTAL(9,G3:G27)</f>
+        <v>12235</v>
+      </c>
+      <c r="H28" s="1">
+        <f t="shared" si="3"/>
+        <v>665</v>
+      </c>
+      <c r="I28" s="1">
+        <f t="shared" si="3"/>
+        <v>11570</v>
+      </c>
+      <c r="J28" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O28" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P28" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="1">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="R28" s="1">
+        <f t="shared" si="3"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H32" s="4" t="s">
+        <v>2008</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H33" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" s="8">
+        <f>SUM(I27:I31)</f>
+        <v>11570</v>
+      </c>
+      <c r="J33" s="8">
+        <f>Q28</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H34" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="10">
+        <f>R28</f>
+        <v>255</v>
+      </c>
+      <c r="J34" s="11"/>
+    </row>
+    <row r="35" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H35" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I35" s="10">
+        <f>S27</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="11"/>
+    </row>
+    <row r="36" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H36" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36" s="10">
+        <f>T27</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="11"/>
+    </row>
+    <row r="37" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H37" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I37" s="10">
+        <f>U27</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="11"/>
+    </row>
+    <row r="38" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H38" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+    </row>
+    <row r="39" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H39" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+    </row>
+    <row r="40" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H40" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40" s="16">
+        <f>SUM(I33:I39)</f>
+        <v>11825</v>
+      </c>
+      <c r="J40" s="16">
+        <f>SUM(J33:J37)</f>
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P26" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P26">
+      <sortCondition ref="J2:J26"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9DBB8CB-3951-4544-9094-C71217C4B322}">
+  <dimension ref="A1:R47"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>2136</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>2137</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>2138</v>
+      </c>
+      <c r="F3" s="23">
+        <v>8</v>
+      </c>
+      <c r="G3" s="23">
+        <v>720</v>
+      </c>
+      <c r="H3" s="23">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I28" si="0">G3-H3</f>
+        <v>690</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>2139</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>2141</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>2143</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4" s="23">
+        <v>1165</v>
+      </c>
+      <c r="H4" s="23">
+        <v>25</v>
+      </c>
+      <c r="I4" s="23">
+        <f t="shared" si="0"/>
+        <v>1140</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>2139</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>2144</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>2145</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>2146</v>
+      </c>
+      <c r="F5" s="23">
+        <v>6</v>
+      </c>
+      <c r="G5" s="23">
+        <v>0</v>
+      </c>
+      <c r="H5" s="23">
+        <v>25</v>
+      </c>
+      <c r="I5" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>2139</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+      <c r="R5" s="24">
+        <f>H5</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>2147</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>2148</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>2149</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="23">
+        <v>845</v>
+      </c>
+      <c r="H6" s="23">
+        <v>25</v>
+      </c>
+      <c r="I6" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>2139</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>1917</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>2150</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>1919</v>
+      </c>
+      <c r="F7" s="23">
+        <v>8</v>
+      </c>
+      <c r="G7" s="23">
+        <v>850</v>
+      </c>
+      <c r="H7" s="23">
+        <v>30</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>2139</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>2151</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>2152</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>2153</v>
+      </c>
+      <c r="F8" s="23">
+        <v>8</v>
+      </c>
+      <c r="G8" s="23">
+        <v>850</v>
+      </c>
+      <c r="H8" s="23">
+        <v>30</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>2139</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>2154</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>2155</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>2156</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9" s="23">
+        <v>900</v>
+      </c>
+      <c r="H9" s="23">
+        <v>20</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>2157</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>2158</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>2159</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0</v>
+      </c>
+      <c r="H10" s="23">
+        <v>25</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+      <c r="R10" s="24">
+        <f>H10</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>2160</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>2161</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G11" s="23">
+        <v>3650</v>
+      </c>
+      <c r="H11" s="23">
+        <v>40</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>3610</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M11" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+      <c r="R11" s="24">
+        <f>H11</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>2115</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>2117</v>
+      </c>
+      <c r="F12" s="23">
+        <v>12</v>
+      </c>
+      <c r="G12" s="23">
+        <v>0</v>
+      </c>
+      <c r="H12" s="23">
+        <v>30</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+      <c r="R12" s="24">
+        <f>H12</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>2164</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>2166</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G13" s="23">
+        <v>775</v>
+      </c>
+      <c r="H13" s="23">
+        <v>25</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>2167</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>2169</v>
+      </c>
+      <c r="F14" s="23">
+        <v>12</v>
+      </c>
+      <c r="G14" s="23">
+        <v>0</v>
+      </c>
+      <c r="H14" s="23">
+        <v>30</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+      <c r="R14" s="24">
+        <f>H14</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>730</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>2170</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>2171</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="23">
+        <v>1775</v>
+      </c>
+      <c r="H15" s="23">
+        <v>25</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
+        <v>1750</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>2172</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>2173</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="23">
+        <v>0</v>
+      </c>
+      <c r="H16" s="23">
+        <v>25</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+      <c r="R16" s="24">
+        <f>H16</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>2175</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>2176</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="23">
+        <v>1120</v>
+      </c>
+      <c r="H17" s="23">
+        <v>30</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
+        <v>1090</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>2177</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>2178</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>2179</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" s="23">
+        <v>1720</v>
+      </c>
+      <c r="H18" s="23">
+        <v>20</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>1700</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>2180</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>2181</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>2182</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="23">
+        <v>0</v>
+      </c>
+      <c r="H19" s="23">
+        <v>20</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M19" s="28" t="s">
+        <v>2183</v>
+      </c>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+      <c r="R19" s="24">
+        <f>H19</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>2184</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" s="23">
+        <v>860</v>
+      </c>
+      <c r="H20" s="23">
+        <v>30</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>2186</v>
+      </c>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22" t="s">
+        <v>2117</v>
+      </c>
+      <c r="F21" s="23">
+        <v>12</v>
+      </c>
+      <c r="G21" s="23">
+        <v>0</v>
+      </c>
+      <c r="H21" s="23">
+        <v>60</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>-60</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+      <c r="R21" s="24">
+        <f>H21</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>2187</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>2189</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G22" s="23">
+        <v>915</v>
+      </c>
+      <c r="H22" s="23">
+        <v>25</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>2190</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>2192</v>
+      </c>
+      <c r="F23" s="23">
+        <v>1</v>
+      </c>
+      <c r="G23" s="23">
+        <v>0</v>
+      </c>
+      <c r="H23" s="23">
+        <v>25</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+      <c r="R23" s="24">
+        <f t="shared" ref="R23:R25" si="1">H23</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>2193</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>2194</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>2195</v>
+      </c>
+      <c r="F24" s="23">
+        <v>1</v>
+      </c>
+      <c r="G24" s="23">
+        <v>0</v>
+      </c>
+      <c r="H24" s="23">
+        <v>25</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M24" s="28" t="s">
+        <v>2196</v>
+      </c>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22">
+        <v>1</v>
+      </c>
+      <c r="R24" s="24">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>1613</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>2197</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>2198</v>
+      </c>
+      <c r="F25" s="23">
+        <v>1</v>
+      </c>
+      <c r="G25" s="23">
+        <v>0</v>
+      </c>
+      <c r="H25" s="23">
+        <v>25</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M25" s="28" t="s">
+        <v>2199</v>
+      </c>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+      <c r="R25" s="24">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>2200</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>2201</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F26" s="23">
+        <v>10</v>
+      </c>
+      <c r="G26" s="23">
+        <v>595</v>
+      </c>
+      <c r="H26" s="23">
+        <v>25</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="0"/>
+        <v>570</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>2204</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>2205</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="G27" s="23">
+        <v>970</v>
+      </c>
+      <c r="H27" s="23">
+        <v>20</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>2206</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>2207</v>
+      </c>
+      <c r="F28" s="23">
+        <v>1</v>
+      </c>
+      <c r="G28" s="23">
+        <v>845</v>
+      </c>
+      <c r="H28" s="23">
+        <v>25</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G30" s="1">
+        <f t="shared" ref="G30:R30" si="2">SUBTOTAL(9,G3:G29)</f>
+        <v>18555</v>
+      </c>
+      <c r="H30" s="1">
+        <f t="shared" si="2"/>
+        <v>715</v>
+      </c>
+      <c r="I30" s="1">
+        <f t="shared" si="2"/>
+        <v>17840</v>
+      </c>
+      <c r="J30" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N30" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O30" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P30" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="1">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="R30" s="1">
+        <f t="shared" si="2"/>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I31" s="1">
+        <v>-820</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H34" s="4" t="s">
+        <v>2074</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="8">
+        <f>SUM(I29:I33)</f>
+        <v>17020</v>
+      </c>
+      <c r="J35" s="8">
+        <f>Q30</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H36" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="10">
+        <f>R30</f>
+        <v>330</v>
+      </c>
+      <c r="J36" s="11"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H37" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" s="10">
+        <f>S29</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="11"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H38" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" s="10">
+        <f>T29</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="11"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H39" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I39" s="10">
+        <f>U29</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="11"/>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H40" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+    </row>
+    <row r="41" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H41" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+    </row>
+    <row r="42" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H42" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="16">
+        <f>SUM(I35:I41)</f>
+        <v>17350</v>
+      </c>
+      <c r="J42" s="16">
+        <f>SUM(J35:J39)</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" s="36" t="s">
+        <v>2180</v>
+      </c>
+      <c r="C45" s="36" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D45" s="36" t="s">
+        <v>2182</v>
+      </c>
+      <c r="E45" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="F45" s="37">
+        <v>2020</v>
+      </c>
+      <c r="G45" s="37">
+        <v>0</v>
+      </c>
+      <c r="H45" s="37">
+        <f>F45-G45</f>
+        <v>2020</v>
+      </c>
+      <c r="I45" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="J45" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="K45" s="36" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L45" s="28" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B46" s="36" t="s">
+        <v>2193</v>
+      </c>
+      <c r="C46" s="36" t="s">
+        <v>2194</v>
+      </c>
+      <c r="D46" s="36" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E46" s="37">
+        <v>1</v>
+      </c>
+      <c r="F46" s="37">
+        <v>845</v>
+      </c>
+      <c r="G46" s="37">
+        <v>0</v>
+      </c>
+      <c r="H46" s="37">
+        <f t="shared" ref="H46:H47" si="3">F46-G46</f>
+        <v>845</v>
+      </c>
+      <c r="I46" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="J46" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="K46" s="36" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L46" s="28" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" s="36" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C47" s="36" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D47" s="36" t="s">
+        <v>2198</v>
+      </c>
+      <c r="E47" s="37">
+        <v>1</v>
+      </c>
+      <c r="F47" s="37">
+        <v>465</v>
+      </c>
+      <c r="G47" s="37">
+        <v>0</v>
+      </c>
+      <c r="H47" s="37">
+        <f t="shared" si="3"/>
+        <v>465</v>
+      </c>
+      <c r="I47" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="J47" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="K47" s="36" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L47" s="28" t="s">
+        <v>2199</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P28" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P28">
+      <sortCondition ref="J2:J28"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F958DF-2500-4E0A-8EAB-C494DB22964E}">
   <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -32267,10 +35550,10 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>270</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2007</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -33423,7 +36706,7 @@
     </row>
     <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H62" s="4" t="s">
-        <v>2008</v>
+        <v>2135</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>15</v>

--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E9D181-64A2-48B3-9894-EDEC19ED85E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093385B8-827E-4316-8CAA-8EF8763253FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-5" sheetId="3" r:id="rId1"/>
@@ -37,6 +37,7 @@
     <sheet name="27-5" sheetId="24" r:id="rId22"/>
     <sheet name="28-5" sheetId="25" r:id="rId23"/>
     <sheet name="29-5" sheetId="26" r:id="rId24"/>
+    <sheet name="30-5" sheetId="27" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'11-5'!$A$2:$P$58</definedName>
@@ -56,7 +57,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'26-5'!$A$2:$P$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'27-5'!$A$2:$P$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'28-5'!$A$2:$P$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'29-5'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'29-5'!$A$2:$P$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'30-5'!$A$2:$P$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'4-5'!$A$2:$P$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'5-5'!$A$2:$P$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'6-5'!$A$2:$P$34</definedName>
@@ -85,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6875" uniqueCount="2209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7290" uniqueCount="2348">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -6712,6 +6714,423 @@
   </si>
   <si>
     <t>đơn trả 29.5</t>
+  </si>
+  <si>
+    <t>T7.30.5.2026</t>
+  </si>
+  <si>
+    <t>NGAY 30-5</t>
+  </si>
+  <si>
+    <t>Cẩm Tiên</t>
+  </si>
+  <si>
+    <t>HD024200</t>
+  </si>
+  <si>
+    <t>Chung cư topaz dragon 2A 457-459 tạ quang bửu - phường 4</t>
+  </si>
+  <si>
+    <t>AT 29-05</t>
+  </si>
+  <si>
+    <t>29-05-2026</t>
+  </si>
+  <si>
+    <t>HD024203</t>
+  </si>
+  <si>
+    <t>Phương Đoan</t>
+  </si>
+  <si>
+    <t>HD024459</t>
+  </si>
+  <si>
+    <t>số 17 đường số 13 bình hưng hòa</t>
+  </si>
+  <si>
+    <t>Út Nhỏ (thu trần ) (Malaysia)</t>
+  </si>
+  <si>
+    <t>HD024433</t>
+  </si>
+  <si>
+    <t>24/5F, Ấp Đông Lân, Xã Bà Điểm</t>
+  </si>
+  <si>
+    <t>HD024304</t>
+  </si>
+  <si>
+    <t>Block d2, chung cư sài gòn riverside (số 4 đào trí phú thuận)</t>
+  </si>
+  <si>
+    <t>Kim Anh Phạm</t>
+  </si>
+  <si>
+    <t>HD024302</t>
+  </si>
+  <si>
+    <t>16 cư xá bình minh, dương Bá Trạc, phường 1</t>
+  </si>
+  <si>
+    <t>Thúy Duy</t>
+  </si>
+  <si>
+    <t>HD024294</t>
+  </si>
+  <si>
+    <t>539,22 hương lộ 3 phường bình hưng hòa</t>
+  </si>
+  <si>
+    <t>Kim Tuyền</t>
+  </si>
+  <si>
+    <t>HD024441</t>
+  </si>
+  <si>
+    <t>451/40 phạm thế hiển phường 3</t>
+  </si>
+  <si>
+    <t>Chan (inst char importshop) -BN2441</t>
+  </si>
+  <si>
+    <t>HD024246</t>
+  </si>
+  <si>
+    <t>163 Trương Thị Hoa phường Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>Uyên</t>
+  </si>
+  <si>
+    <t>HD024442</t>
+  </si>
+  <si>
+    <t>98 Vườn Lài, phường An Phú Đông</t>
+  </si>
+  <si>
+    <t>Nguyễn Huỳnh Cẩm Tú</t>
+  </si>
+  <si>
+    <t>HD024247</t>
+  </si>
+  <si>
+    <t>78/63 đường số 11, phường thông tây hội</t>
+  </si>
+  <si>
+    <t>Thùy</t>
+  </si>
+  <si>
+    <t>HD024086</t>
+  </si>
+  <si>
+    <t>175 quốc lộ 1k, linh xuân</t>
+  </si>
+  <si>
+    <t>Tuyen Nguyen</t>
+  </si>
+  <si>
+    <t>HD024412</t>
+  </si>
+  <si>
+    <t>39/44/6 hoàng bật đạt p15</t>
+  </si>
+  <si>
+    <t>Đào thị thanh tâm</t>
+  </si>
+  <si>
+    <t>HD024429</t>
+  </si>
+  <si>
+    <t>320/16 đường ĐHT 02 Phường đông hưng thuận</t>
+  </si>
+  <si>
+    <t>HD024270</t>
+  </si>
+  <si>
+    <t>Tạ Ngọc Mai</t>
+  </si>
+  <si>
+    <t>HD024430</t>
+  </si>
+  <si>
+    <t>Sarimi B1, khu chung cư Sala, P. An Lợi Đông</t>
+  </si>
+  <si>
+    <t>BN1B2 mini chouchou Fb.</t>
+  </si>
+  <si>
+    <t>HD024453</t>
+  </si>
+  <si>
+    <t>401 Quang Trung f10</t>
+  </si>
+  <si>
+    <t>Minh Hồng Nguyễn</t>
+  </si>
+  <si>
+    <t>HD024438</t>
+  </si>
+  <si>
+    <t>Jasmine 1 Hà đô - 118 Đường 3/2, phường 12</t>
+  </si>
+  <si>
+    <t>Daisy Le</t>
+  </si>
+  <si>
+    <t>HD024416</t>
+  </si>
+  <si>
+    <t>418 Trường Sa, p2</t>
+  </si>
+  <si>
+    <t>Ngọc Quyên</t>
+  </si>
+  <si>
+    <t>HD024258</t>
+  </si>
+  <si>
+    <t>148a hòa hưng p13</t>
+  </si>
+  <si>
+    <t>HD024290</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thùy Tiên</t>
+  </si>
+  <si>
+    <t>HD024686</t>
+  </si>
+  <si>
+    <t>1/10/2 nguyễn văn yến phường phú thạnh</t>
+  </si>
+  <si>
+    <t>AT 30-05</t>
+  </si>
+  <si>
+    <t>30-05-2026</t>
+  </si>
+  <si>
+    <t>Chị Bảo Châu</t>
+  </si>
+  <si>
+    <t>HD024669</t>
+  </si>
+  <si>
+    <t>Ngọc Diệu</t>
+  </si>
+  <si>
+    <t>HD024379</t>
+  </si>
+  <si>
+    <t>132 Le van quoi p bình hưng hòa a</t>
+  </si>
+  <si>
+    <t>Nhân (fb Cam Phu)</t>
+  </si>
+  <si>
+    <t>HD024666</t>
+  </si>
+  <si>
+    <t>11 đường 18 phường 4</t>
+  </si>
+  <si>
+    <t>HD024704</t>
+  </si>
+  <si>
+    <t>Anh Hải nhận hàng (Thảo Trần)</t>
+  </si>
+  <si>
+    <t>HD024613</t>
+  </si>
+  <si>
+    <t>số 17 đường số 13 phường bình hưng hòa</t>
+  </si>
+  <si>
+    <t>ĐỨC - FB MT MI Ngo</t>
+  </si>
+  <si>
+    <t>HD024678</t>
+  </si>
+  <si>
+    <t>39 an nhơn phường 17</t>
+  </si>
+  <si>
+    <t>Ngọc Vũ</t>
+  </si>
+  <si>
+    <t>HD024689</t>
+  </si>
+  <si>
+    <t>42 đương so 6 binh trưng đông</t>
+  </si>
+  <si>
+    <t>Ái Linh</t>
+  </si>
+  <si>
+    <t>HD024455</t>
+  </si>
+  <si>
+    <t>17/2 đường số 10 p bình trưng tây</t>
+  </si>
+  <si>
+    <t>Kiều Nhi</t>
+  </si>
+  <si>
+    <t>HD024623</t>
+  </si>
+  <si>
+    <t>4/2b đường số 26 phương an khánh</t>
+  </si>
+  <si>
+    <t>Ngô Hoàng Ánh</t>
+  </si>
+  <si>
+    <t>HD024510</t>
+  </si>
+  <si>
+    <t>235 QL13 Cũ, HBP</t>
+  </si>
+  <si>
+    <t>Trần Thị Mỹ Duyên</t>
+  </si>
+  <si>
+    <t>HD024528</t>
+  </si>
+  <si>
+    <t>84 song hành phường an phú</t>
+  </si>
+  <si>
+    <t>W3370</t>
+  </si>
+  <si>
+    <t>HD024406</t>
+  </si>
+  <si>
+    <t>HD024538</t>
+  </si>
+  <si>
+    <t>320/16 đường ĐHT 02 phường đông hưng thuận</t>
+  </si>
+  <si>
+    <t>BN6352</t>
+  </si>
+  <si>
+    <t>HD024138</t>
+  </si>
+  <si>
+    <t>HD024670</t>
+  </si>
+  <si>
+    <t>Phạm Duyên</t>
+  </si>
+  <si>
+    <t>HD024075</t>
+  </si>
+  <si>
+    <t>Số 107, Đường Dương Quảng Hàm phường 7 (tiệm rửa xe)</t>
+  </si>
+  <si>
+    <t>An Nguyen - fb Nguyễn Hoàng Thúy An</t>
+  </si>
+  <si>
+    <t>HD024454</t>
+  </si>
+  <si>
+    <t>105/48 Nguyễn tư giản f12</t>
+  </si>
+  <si>
+    <t>Phạm Thị Thanh Hồng</t>
+  </si>
+  <si>
+    <t>HD024697</t>
+  </si>
+  <si>
+    <t>Hẻm 95, nhà 95/5D, đường 15, phường tân hưng</t>
+  </si>
+  <si>
+    <t>Nguyễn Cẩm Tú</t>
+  </si>
+  <si>
+    <t>HD024680</t>
+  </si>
+  <si>
+    <t>Sky garden 2, cổng đông 3, phường tân phong</t>
+  </si>
+  <si>
+    <t>Irire Intara (phòng 505)</t>
+  </si>
+  <si>
+    <t>HD024607</t>
+  </si>
+  <si>
+    <t>A25 Hotel - 51-53-55 Cách Mạng Tháng 8, Phường Bến Thành</t>
+  </si>
+  <si>
+    <t>Nguyễn Thu Phương</t>
+  </si>
+  <si>
+    <t>HD024563</t>
+  </si>
+  <si>
+    <t>Sunrise riverside tháp H Đường Nguyễn hữu thọ</t>
+  </si>
+  <si>
+    <t>Hoàng Thu Thủy</t>
+  </si>
+  <si>
+    <t>HD024597</t>
+  </si>
+  <si>
+    <t>583 Nguyễn Thị Thập, phường Bình Thuận</t>
+  </si>
+  <si>
+    <t>Panhaketya (zalo_thiemuyen)</t>
+  </si>
+  <si>
+    <t>HD024702</t>
+  </si>
+  <si>
+    <t>Pham Ngu Lao A67 Nguyen Trai</t>
+  </si>
+  <si>
+    <t>HD024599</t>
+  </si>
+  <si>
+    <t>HD024659</t>
+  </si>
+  <si>
+    <t>Đặng Trung</t>
+  </si>
+  <si>
+    <t>HD023933</t>
+  </si>
+  <si>
+    <t>206 khu phố Mỹ Hào, Hà Huy tập, P. Tân Phong</t>
+  </si>
+  <si>
+    <t>đơn trả 1.6</t>
+  </si>
+  <si>
+    <t>Võ Hằng</t>
+  </si>
+  <si>
+    <t>HD024527</t>
+  </si>
+  <si>
+    <t>Cty leading star, lô C đường số 3, KCN Đồng An, Bình Hoà</t>
+  </si>
+  <si>
+    <t>tinh</t>
+  </si>
+  <si>
+    <t>hàng tỉnh</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>xx</t>
   </si>
 </sst>
 </file>
@@ -6943,7 +7362,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -7026,6 +7445,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -32550,7 +32970,7 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="I32" s="1">
-        <v>-4330</v>
+        <v>-4365</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>2073</v>
@@ -32573,7 +32993,7 @@
       </c>
       <c r="I36" s="8">
         <f>SUM(I30:I34)</f>
-        <v>14750</v>
+        <v>14715</v>
       </c>
       <c r="J36" s="8">
         <f>Q31</f>
@@ -32640,7 +33060,7 @@
       </c>
       <c r="I43" s="16">
         <f>SUM(I36:I42)</f>
-        <v>15040</v>
+        <v>15005</v>
       </c>
       <c r="J43" s="16">
         <f>SUM(J36:J40)</f>
@@ -35534,7 +35954,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F958DF-2500-4E0A-8EAB-C494DB22964E}">
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
@@ -35607,1198 +36027,2714 @@
       </c>
       <c r="Q2" s="3"/>
     </row>
-    <row r="3" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-    </row>
-    <row r="4" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-    </row>
-    <row r="5" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="20"/>
-    </row>
-    <row r="6" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-    </row>
-    <row r="7" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="20"/>
-    </row>
-    <row r="8" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-    </row>
-    <row r="9" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-    </row>
-    <row r="10" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="20"/>
-    </row>
-    <row r="11" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="20"/>
-    </row>
-    <row r="12" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-    </row>
-    <row r="13" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-    </row>
-    <row r="14" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-    </row>
-    <row r="15" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="20"/>
-    </row>
-    <row r="16" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="20"/>
-    </row>
-    <row r="17" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="20"/>
-    </row>
-    <row r="18" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-    </row>
-    <row r="19" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="20"/>
-    </row>
-    <row r="20" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
-    </row>
-    <row r="21" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-    </row>
-    <row r="22" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-    </row>
-    <row r="23" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="20"/>
-    </row>
-    <row r="24" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
-    </row>
-    <row r="25" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="20"/>
-    </row>
-    <row r="26" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
-    </row>
-    <row r="27" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
-    </row>
-    <row r="28" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="20"/>
-    </row>
-    <row r="29" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="20"/>
-    </row>
-    <row r="30" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
-      <c r="P30" s="17"/>
-      <c r="Q30" s="17"/>
-    </row>
-    <row r="31" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17"/>
-      <c r="O31" s="17"/>
-      <c r="P31" s="17"/>
-      <c r="Q31" s="17"/>
-    </row>
-    <row r="32" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="17"/>
-      <c r="P32" s="17"/>
-      <c r="Q32" s="17"/>
-    </row>
-    <row r="33" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
-      <c r="P33" s="17"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="20"/>
-    </row>
-    <row r="34" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="17"/>
-    </row>
-    <row r="35" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
-    </row>
-    <row r="36" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="17"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17"/>
-      <c r="P36" s="17"/>
-      <c r="Q36" s="17"/>
-      <c r="R36" s="20"/>
-    </row>
-    <row r="37" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="17"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
-    </row>
-    <row r="38" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="17"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
-      <c r="N38" s="17"/>
-      <c r="O38" s="17"/>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17"/>
-    </row>
-    <row r="39" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="17"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
-      <c r="N39" s="17"/>
-      <c r="O39" s="17"/>
-      <c r="P39" s="17"/>
-      <c r="Q39" s="17"/>
-      <c r="R39" s="20"/>
-    </row>
-    <row r="40" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
-      <c r="N40" s="17"/>
-      <c r="O40" s="17"/>
-      <c r="P40" s="17"/>
-      <c r="Q40" s="17"/>
-    </row>
-    <row r="41" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
-      <c r="N41" s="17"/>
-      <c r="O41" s="17"/>
-      <c r="P41" s="17"/>
-      <c r="Q41" s="17"/>
-    </row>
-    <row r="42" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
-      <c r="M42" s="17"/>
-      <c r="N42" s="17"/>
-      <c r="O42" s="17"/>
-      <c r="P42" s="17"/>
-      <c r="Q42" s="17"/>
-    </row>
-    <row r="43" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
-      <c r="M43" s="17"/>
-      <c r="N43" s="17"/>
-      <c r="O43" s="17"/>
-      <c r="P43" s="17"/>
-      <c r="Q43" s="17"/>
-      <c r="R43" s="20"/>
-    </row>
-    <row r="44" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-      <c r="N44" s="17"/>
-      <c r="O44" s="17"/>
-      <c r="P44" s="17"/>
-      <c r="Q44" s="17"/>
-    </row>
-    <row r="45" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17"/>
-      <c r="O45" s="17"/>
-      <c r="P45" s="17"/>
-      <c r="Q45" s="17"/>
-      <c r="R45" s="20"/>
-    </row>
-    <row r="46" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="17"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="18"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="17"/>
-      <c r="M46" s="17"/>
-      <c r="N46" s="17"/>
-      <c r="O46" s="17"/>
-      <c r="P46" s="17"/>
-      <c r="Q46" s="17"/>
-      <c r="R46" s="20"/>
-    </row>
-    <row r="47" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="17"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="18"/>
-      <c r="I47" s="18"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
-      <c r="L47" s="17"/>
-      <c r="M47" s="17"/>
-      <c r="N47" s="17"/>
-      <c r="O47" s="17"/>
-      <c r="P47" s="17"/>
-      <c r="Q47" s="17"/>
-    </row>
-    <row r="48" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="17"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="18"/>
-      <c r="I48" s="18"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="17"/>
-      <c r="M48" s="17"/>
-      <c r="N48" s="17"/>
-      <c r="O48" s="17"/>
-      <c r="P48" s="17"/>
-      <c r="Q48" s="17"/>
-    </row>
-    <row r="49" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="17"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="18"/>
-      <c r="I49" s="18"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
-      <c r="N49" s="17"/>
-      <c r="O49" s="17"/>
-      <c r="P49" s="17"/>
-      <c r="Q49" s="17"/>
-      <c r="R49" s="20"/>
-    </row>
-    <row r="50" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="17"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
-      <c r="H50" s="18"/>
-      <c r="I50" s="18"/>
-      <c r="J50" s="17"/>
-      <c r="K50" s="17"/>
-      <c r="L50" s="17"/>
-      <c r="M50" s="17"/>
-      <c r="N50" s="17"/>
-      <c r="O50" s="17"/>
-      <c r="P50" s="17"/>
-      <c r="Q50" s="17"/>
-    </row>
-    <row r="51" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="17"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="18"/>
-      <c r="I51" s="18"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="17"/>
-      <c r="M51" s="17"/>
-      <c r="N51" s="17"/>
-      <c r="O51" s="17"/>
-      <c r="P51" s="17"/>
-      <c r="Q51" s="17"/>
-    </row>
-    <row r="52" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="17"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="18"/>
-      <c r="H52" s="18"/>
-      <c r="I52" s="18"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
-      <c r="M52" s="17"/>
-      <c r="N52" s="17"/>
-      <c r="O52" s="17"/>
-      <c r="P52" s="17"/>
-      <c r="Q52" s="17"/>
-      <c r="R52" s="20"/>
-    </row>
-    <row r="53" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="17"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="18"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
-      <c r="M53" s="17"/>
-      <c r="N53" s="17"/>
-      <c r="O53" s="17"/>
-      <c r="P53" s="17"/>
-      <c r="Q53" s="17"/>
-    </row>
-    <row r="54" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="17"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
-      <c r="H54" s="18"/>
-      <c r="I54" s="18"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="17"/>
-      <c r="O54" s="17"/>
-      <c r="P54" s="17"/>
-      <c r="Q54" s="17"/>
-    </row>
-    <row r="55" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="17"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-      <c r="H55" s="18"/>
-      <c r="I55" s="18"/>
-      <c r="J55" s="17"/>
-      <c r="K55" s="17"/>
-      <c r="L55" s="17"/>
-      <c r="M55" s="17"/>
-      <c r="N55" s="17"/>
-      <c r="O55" s="17"/>
-      <c r="P55" s="17"/>
-      <c r="Q55" s="17"/>
-    </row>
-    <row r="56" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="17"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="18"/>
-      <c r="I56" s="18"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="17"/>
-      <c r="O56" s="17"/>
-      <c r="P56" s="17"/>
-      <c r="Q56" s="17"/>
-      <c r="R56" s="20"/>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="G58" s="1">
-        <f t="shared" ref="G58:R58" si="0">SUBTOTAL(9,G3:G57)</f>
-        <v>0</v>
-      </c>
-      <c r="H58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R58" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H62" s="4" t="s">
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>2211</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>2212</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>2213</v>
+      </c>
+      <c r="F3" s="23">
+        <v>8</v>
+      </c>
+      <c r="G3" s="23">
+        <v>920</v>
+      </c>
+      <c r="H3" s="23">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I24" si="0">G3-H3</f>
+        <v>890</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>2214</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>2216</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G4" s="23">
+        <v>1875</v>
+      </c>
+      <c r="H4" s="23">
+        <v>35</v>
+      </c>
+      <c r="I4" s="23">
+        <f t="shared" si="0"/>
+        <v>1840</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>2214</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>2217</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>2218</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>2219</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="23">
+        <v>1770</v>
+      </c>
+      <c r="H5" s="23">
+        <v>30</v>
+      </c>
+      <c r="I5" s="23">
+        <f t="shared" si="0"/>
+        <v>1740</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>2214</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>2220</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>2221</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>2222</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G6" s="23">
+        <v>825</v>
+      </c>
+      <c r="H6" s="23">
+        <v>35</v>
+      </c>
+      <c r="I6" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>2214</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>2224</v>
+      </c>
+      <c r="F7" s="23">
+        <v>7</v>
+      </c>
+      <c r="G7" s="23">
+        <v>1690</v>
+      </c>
+      <c r="H7" s="23">
+        <v>30</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
+        <v>1660</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>2214</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>2225</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>2226</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>2227</v>
+      </c>
+      <c r="F8" s="23">
+        <v>8</v>
+      </c>
+      <c r="G8" s="23">
+        <v>620</v>
+      </c>
+      <c r="H8" s="23">
+        <v>30</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>590</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>2214</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>2229</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>2230</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="23">
+        <v>8559</v>
+      </c>
+      <c r="H9" s="23">
+        <v>65</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>8494</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>2214</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M9" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+      <c r="R9" s="24">
+        <f>H9</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>2231</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>2232</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>2233</v>
+      </c>
+      <c r="F10" s="23">
+        <v>8</v>
+      </c>
+      <c r="G10" s="23">
+        <v>2620</v>
+      </c>
+      <c r="H10" s="23">
+        <v>35</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>2585</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>2214</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M10" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+      <c r="R10" s="24">
+        <f>H10</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>2236</v>
+      </c>
+      <c r="F11" s="23">
+        <v>12</v>
+      </c>
+      <c r="G11" s="23">
+        <v>0</v>
+      </c>
+      <c r="H11" s="23">
+        <v>40</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+      <c r="R11" s="24">
+        <f>H11</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>2237</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>2238</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>2239</v>
+      </c>
+      <c r="F12" s="23">
+        <v>12</v>
+      </c>
+      <c r="G12" s="23">
+        <v>910</v>
+      </c>
+      <c r="H12" s="23">
+        <v>30</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>2240</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>2241</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>2242</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="23">
+        <v>615</v>
+      </c>
+      <c r="H13" s="23">
+        <v>25</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>590</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>2244</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>2245</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" s="23">
+        <v>1120</v>
+      </c>
+      <c r="H14" s="23">
+        <v>30</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>1090</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>2246</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>2247</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>2248</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G15" s="23">
+        <v>1145</v>
+      </c>
+      <c r="H15" s="23">
+        <v>25</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>2249</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>2250</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>2251</v>
+      </c>
+      <c r="F16" s="23">
+        <v>12</v>
+      </c>
+      <c r="G16" s="23">
+        <v>30</v>
+      </c>
+      <c r="H16" s="23">
+        <v>30</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>2252</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>1379</v>
+      </c>
+      <c r="F17" s="23">
+        <v>12</v>
+      </c>
+      <c r="G17" s="23">
+        <v>1290</v>
+      </c>
+      <c r="H17" s="23">
+        <v>30</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
+        <v>1260</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>2253</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>2254</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>2255</v>
+      </c>
+      <c r="F18" s="23">
+        <v>2</v>
+      </c>
+      <c r="G18" s="23">
+        <v>1020</v>
+      </c>
+      <c r="H18" s="23">
+        <v>30</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>2256</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>2257</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="F19" s="23">
+        <v>12</v>
+      </c>
+      <c r="G19" s="23">
+        <v>0</v>
+      </c>
+      <c r="H19" s="23">
+        <v>30</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+      <c r="R19" s="24">
+        <f>H19</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22" t="s">
+        <v>2258</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="23">
+        <v>4440</v>
+      </c>
+      <c r="H20" s="23">
+        <v>40</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>4400</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>2259</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>2261</v>
+      </c>
+      <c r="F21" s="23">
+        <v>10</v>
+      </c>
+      <c r="G21" s="23">
+        <v>795</v>
+      </c>
+      <c r="H21" s="23">
+        <v>25</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>2262</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>2263</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>2264</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="G22" s="23">
+        <v>850</v>
+      </c>
+      <c r="H22" s="23">
+        <v>20</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>2265</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>2266</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>2267</v>
+      </c>
+      <c r="F23" s="23">
+        <v>10</v>
+      </c>
+      <c r="G23" s="23">
+        <v>0</v>
+      </c>
+      <c r="H23" s="23">
+        <v>25</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+      <c r="R23" s="24">
+        <f>H23</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>2268</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F24" s="23">
+        <v>10</v>
+      </c>
+      <c r="G24" s="23">
+        <v>915</v>
+      </c>
+      <c r="H24" s="23">
+        <v>25</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G26" s="1">
+        <f t="shared" ref="G26:R26" si="1">SUBTOTAL(9,G3:G25)</f>
+        <v>32009</v>
+      </c>
+      <c r="H26" s="1">
+        <f t="shared" si="1"/>
+        <v>695</v>
+      </c>
+      <c r="I26" s="1">
+        <f t="shared" si="1"/>
+        <v>31314</v>
+      </c>
+      <c r="J26" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O26" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P26" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="1">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="R26" s="1">
+        <f t="shared" si="1"/>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H30" s="4" t="s">
         <v>2135</v>
       </c>
-      <c r="I62" s="5" t="s">
+      <c r="I30" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J62" s="6" t="s">
+      <c r="J30" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H63" s="7" t="s">
+    <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H31" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I63" s="8">
-        <f>SUM(I57:I61)</f>
-        <v>0</v>
-      </c>
-      <c r="J63" s="8">
-        <f>Q58</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="H64" s="9" t="s">
+      <c r="I31" s="8">
+        <f>SUM(I25:I29)</f>
+        <v>31314</v>
+      </c>
+      <c r="J31" s="8">
+        <f>Q26</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H32" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I64" s="10">
-        <f>R58</f>
-        <v>0</v>
-      </c>
-      <c r="J64" s="11"/>
-    </row>
-    <row r="65" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H65" s="9" t="s">
+      <c r="I32" s="10">
+        <f>R26</f>
+        <v>195</v>
+      </c>
+      <c r="J32" s="11"/>
+    </row>
+    <row r="33" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H33" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I65" s="10">
-        <f>S57</f>
-        <v>0</v>
-      </c>
-      <c r="J65" s="11"/>
-    </row>
-    <row r="66" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H66" s="9" t="s">
+      <c r="I33" s="10">
+        <f>S25</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="11"/>
+    </row>
+    <row r="34" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H34" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I66" s="10">
-        <f>T57</f>
-        <v>0</v>
-      </c>
-      <c r="J66" s="11"/>
-    </row>
-    <row r="67" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H67" s="9" t="s">
+      <c r="I34" s="10">
+        <f>T25</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="11"/>
+    </row>
+    <row r="35" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H35" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I67" s="10">
-        <f>U57</f>
-        <v>0</v>
-      </c>
-      <c r="J67" s="11"/>
-    </row>
-    <row r="68" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H68" s="12" t="s">
+      <c r="I35" s="10">
+        <f>U25</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="11"/>
+    </row>
+    <row r="36" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H36" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
-    </row>
-    <row r="69" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H69" s="14" t="s">
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+    </row>
+    <row r="37" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H37" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13"/>
-    </row>
-    <row r="70" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="H70" s="15" t="s">
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+    </row>
+    <row r="38" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H38" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I70" s="16">
-        <f>SUM(I63:I69)</f>
-        <v>0</v>
-      </c>
-      <c r="J70" s="16">
-        <f>SUM(J63:J67)</f>
-        <v>0</v>
+      <c r="I38" s="16">
+        <f>SUM(I31:I37)</f>
+        <v>31509</v>
+      </c>
+      <c r="J38" s="16">
+        <f>SUM(J31:J35)</f>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P56" xr:uid="{00000000-0009-0000-0000-000006000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P56">
-      <sortCondition ref="J2:J56"/>
+  <autoFilter ref="A2:P24" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P24">
+      <sortCondition ref="J2:J24"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3F10B9-CCF0-4544-AE8A-AEB938F5CF2C}">
+  <dimension ref="A1:R45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>2269</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>2270</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>2271</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="23">
+        <v>845</v>
+      </c>
+      <c r="H3" s="23">
+        <v>25</v>
+      </c>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I31" si="0">G3-H3</f>
+        <v>820</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>2272</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>2274</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4" s="23">
+        <v>915</v>
+      </c>
+      <c r="H4" s="23">
+        <v>25</v>
+      </c>
+      <c r="I4" s="23">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>2272</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>2276</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>2277</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>2278</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="23">
+        <v>1640</v>
+      </c>
+      <c r="H5" s="23">
+        <v>30</v>
+      </c>
+      <c r="I5" s="23">
+        <f t="shared" si="0"/>
+        <v>1610</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>2272</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>2279</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>2280</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>2281</v>
+      </c>
+      <c r="F6" s="23">
+        <v>8</v>
+      </c>
+      <c r="G6" s="23">
+        <v>0</v>
+      </c>
+      <c r="H6" s="23">
+        <v>30</v>
+      </c>
+      <c r="I6" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>2272</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+      <c r="R6" s="24">
+        <f>H6</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>2282</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>1434</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="23">
+        <v>0</v>
+      </c>
+      <c r="H7" s="23">
+        <v>30</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>2272</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+      <c r="R7" s="24">
+        <f t="shared" ref="R7:R9" si="1">H7</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>2283</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>2284</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>2285</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="23">
+        <v>0</v>
+      </c>
+      <c r="H8" s="23">
+        <v>30</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>2272</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+      <c r="R8" s="24">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>1578</v>
+      </c>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22" t="s">
+        <v>626</v>
+      </c>
+      <c r="F9" s="23">
+        <v>6</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0</v>
+      </c>
+      <c r="H9" s="23">
+        <v>30</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>2272</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22">
+        <v>1</v>
+      </c>
+      <c r="R9" s="24">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>2286</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>2287</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>2288</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" s="23">
+        <v>1825</v>
+      </c>
+      <c r="H10" s="23">
+        <v>25</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>1800</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>2290</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>2291</v>
+      </c>
+      <c r="F11" s="23">
+        <v>2</v>
+      </c>
+      <c r="G11" s="23">
+        <v>850</v>
+      </c>
+      <c r="H11" s="23">
+        <v>30</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>2292</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>2293</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>2294</v>
+      </c>
+      <c r="F12" s="23">
+        <v>2</v>
+      </c>
+      <c r="G12" s="23">
+        <v>1110</v>
+      </c>
+      <c r="H12" s="23">
+        <v>30</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>2295</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>2296</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>2297</v>
+      </c>
+      <c r="F13" s="23">
+        <v>2</v>
+      </c>
+      <c r="G13" s="23">
+        <v>1740</v>
+      </c>
+      <c r="H13" s="23">
+        <v>30</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>1710</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>2298</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>2299</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>2300</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" s="23">
+        <v>520</v>
+      </c>
+      <c r="H14" s="23">
+        <v>30</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>2301</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>2302</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>2303</v>
+      </c>
+      <c r="F15" s="23">
+        <v>2</v>
+      </c>
+      <c r="G15" s="23">
+        <v>550</v>
+      </c>
+      <c r="H15" s="23">
+        <v>30</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
+        <v>520</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>2304</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>2305</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>2117</v>
+      </c>
+      <c r="F16" s="23">
+        <v>12</v>
+      </c>
+      <c r="G16" s="23">
+        <v>0</v>
+      </c>
+      <c r="H16" s="23">
+        <v>30</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+      <c r="R16" s="24">
+        <f>H16</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="25"/>
+      <c r="B17" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>2249</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>2306</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>2307</v>
+      </c>
+      <c r="F17" s="26">
+        <v>12</v>
+      </c>
+      <c r="G17" s="26">
+        <v>130</v>
+      </c>
+      <c r="H17" s="26">
+        <v>30</v>
+      </c>
+      <c r="I17" s="26">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J17" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="25" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M17" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="N17" s="25"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>2308</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>2309</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="F18" s="23">
+        <v>12</v>
+      </c>
+      <c r="G18" s="23">
+        <v>0</v>
+      </c>
+      <c r="H18" s="23">
+        <v>0</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M18" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22">
+        <v>1</v>
+      </c>
+      <c r="R18" s="24">
+        <f t="shared" ref="R18:R19" si="2">H18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>2308</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>2310</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="F19" s="23">
+        <v>12</v>
+      </c>
+      <c r="G19" s="23">
+        <v>0</v>
+      </c>
+      <c r="H19" s="23">
+        <v>40</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M19" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+      <c r="R19" s="24">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>2311</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>2312</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>2313</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="23">
+        <v>775</v>
+      </c>
+      <c r="H20" s="23">
+        <v>25</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>2314</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>2315</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>2316</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="23">
+        <v>0</v>
+      </c>
+      <c r="H21" s="23">
+        <v>25</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="23">
+        <v>1</v>
+      </c>
+      <c r="R21" s="24">
+        <f t="shared" ref="R21:R22" si="3">H21</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>2317</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>2318</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>2319</v>
+      </c>
+      <c r="F22" s="23">
+        <v>7</v>
+      </c>
+      <c r="G22" s="23">
+        <v>0</v>
+      </c>
+      <c r="H22" s="23">
+        <v>30</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22">
+        <v>1</v>
+      </c>
+      <c r="R22" s="24">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>2320</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>2321</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>2322</v>
+      </c>
+      <c r="F23" s="23">
+        <v>7</v>
+      </c>
+      <c r="G23" s="23">
+        <v>1730</v>
+      </c>
+      <c r="H23" s="23">
+        <v>30</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="0"/>
+        <v>1700</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>2323</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>2324</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>2325</v>
+      </c>
+      <c r="F24" s="23">
+        <v>1</v>
+      </c>
+      <c r="G24" s="23">
+        <v>0</v>
+      </c>
+      <c r="H24" s="23">
+        <v>25</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22">
+        <v>1</v>
+      </c>
+      <c r="R24" s="24">
+        <f>H24</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>2326</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>2327</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>2328</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="G25" s="23">
+        <v>525</v>
+      </c>
+      <c r="H25" s="23">
+        <v>35</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>2329</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>2330</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>2331</v>
+      </c>
+      <c r="F26" s="23">
+        <v>7</v>
+      </c>
+      <c r="G26" s="23">
+        <v>1110</v>
+      </c>
+      <c r="H26" s="23">
+        <v>30</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>2332</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>2333</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>2334</v>
+      </c>
+      <c r="F27" s="23">
+        <v>1</v>
+      </c>
+      <c r="G27" s="23">
+        <v>0</v>
+      </c>
+      <c r="H27" s="23">
+        <v>25</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22">
+        <v>1</v>
+      </c>
+      <c r="R27" s="24">
+        <f t="shared" ref="R27:R28" si="4">H27</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>2335</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="F28" s="23">
+        <v>3</v>
+      </c>
+      <c r="G28" s="23">
+        <v>0</v>
+      </c>
+      <c r="H28" s="23">
+        <v>25</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22">
+        <v>1</v>
+      </c>
+      <c r="R28" s="24">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>2336</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F29" s="23">
+        <v>4</v>
+      </c>
+      <c r="G29" s="23">
+        <v>1185</v>
+      </c>
+      <c r="H29" s="23">
+        <v>25</v>
+      </c>
+      <c r="I29" s="23">
+        <f t="shared" si="0"/>
+        <v>1160</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>2337</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>2338</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>2339</v>
+      </c>
+      <c r="F30" s="23">
+        <v>7</v>
+      </c>
+      <c r="G30" s="23">
+        <v>1600</v>
+      </c>
+      <c r="H30" s="23">
+        <v>30</v>
+      </c>
+      <c r="I30" s="23">
+        <f t="shared" ref="I30:I31" si="5">G30-H30</f>
+        <v>1570</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" s="56" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="53"/>
+      <c r="B31" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>2341</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>2342</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>2343</v>
+      </c>
+      <c r="F31" s="53" t="s">
+        <v>2344</v>
+      </c>
+      <c r="G31" s="54">
+        <v>570</v>
+      </c>
+      <c r="H31" s="54">
+        <v>0</v>
+      </c>
+      <c r="I31" s="54">
+        <f t="shared" si="5"/>
+        <v>570</v>
+      </c>
+      <c r="J31" s="53" t="s">
+        <v>623</v>
+      </c>
+      <c r="K31" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" s="53" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M31" s="53" t="s">
+        <v>2345</v>
+      </c>
+      <c r="N31" s="53" t="s">
+        <v>2346</v>
+      </c>
+      <c r="O31" s="53"/>
+      <c r="P31" s="53" t="s">
+        <v>2347</v>
+      </c>
+      <c r="Q31" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G33" s="1">
+        <f>SUBTOTAL(9,G3:G32)</f>
+        <v>17620</v>
+      </c>
+      <c r="H33" s="1">
+        <f>SUBTOTAL(9,H3:H32)</f>
+        <v>780</v>
+      </c>
+      <c r="I33" s="1">
+        <f>SUBTOTAL(9,I3:I32)</f>
+        <v>16840</v>
+      </c>
+      <c r="J33" s="1">
+        <f>SUBTOTAL(9,J3:J32)</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="1">
+        <f>SUBTOTAL(9,K3:K32)</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
+        <f>SUBTOTAL(9,L3:L32)</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
+        <f>SUBTOTAL(9,M3:M32)</f>
+        <v>0</v>
+      </c>
+      <c r="N33" s="1">
+        <f>SUBTOTAL(9,N3:N32)</f>
+        <v>0</v>
+      </c>
+      <c r="O33" s="1">
+        <f>SUBTOTAL(9,O3:O32)</f>
+        <v>0</v>
+      </c>
+      <c r="P33" s="1">
+        <f>SUBTOTAL(9,P3:P32)</f>
+        <v>0</v>
+      </c>
+      <c r="Q33" s="1">
+        <f>SUBTOTAL(9,Q3:Q32)</f>
+        <v>29</v>
+      </c>
+      <c r="R33" s="1">
+        <f>SUBTOTAL(9,R3:R32)</f>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="34" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="I34" s="1">
+        <v>-570</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="37" spans="7:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H37" s="4" t="s">
+        <v>2209</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="7:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H38" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" s="8">
+        <f>SUM(I32:I36)</f>
+        <v>16270</v>
+      </c>
+      <c r="J38" s="8">
+        <f>Q33</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="H39" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="10">
+        <f>R33</f>
+        <v>320</v>
+      </c>
+      <c r="J39" s="11"/>
+    </row>
+    <row r="40" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="H40" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" s="10">
+        <f>S32</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="11"/>
+    </row>
+    <row r="41" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="H41" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" s="10">
+        <f>T32</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="11"/>
+    </row>
+    <row r="42" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="H42" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" s="10">
+        <f>U32</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="11"/>
+    </row>
+    <row r="43" spans="7:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H43" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I43" s="13"/>
+      <c r="J43" s="13"/>
+    </row>
+    <row r="44" spans="7:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H44" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
+    </row>
+    <row r="45" spans="7:18" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H45" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45" s="16">
+        <f>SUM(I38:I44)</f>
+        <v>16590</v>
+      </c>
+      <c r="J45" s="16">
+        <f>SUM(J38:J42)</f>
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P31" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P31">
+      <sortCondition ref="J2:J31"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093385B8-827E-4316-8CAA-8EF8763253FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C078BE-6596-45D9-9C33-D590EC1BC61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37270,7 +37270,7 @@
         <v>25</v>
       </c>
       <c r="I3" s="23">
-        <f t="shared" ref="I3:I31" si="0">G3-H3</f>
+        <f t="shared" ref="I3:I29" si="0">G3-H3</f>
         <v>820</v>
       </c>
       <c r="J3" s="22" t="s">
@@ -38584,51 +38584,51 @@
     </row>
     <row r="33" spans="7:18" x14ac:dyDescent="0.25">
       <c r="G33" s="1">
-        <f>SUBTOTAL(9,G3:G32)</f>
+        <f>SUBTOTAL(9,G3:G31)</f>
         <v>17620</v>
       </c>
       <c r="H33" s="1">
-        <f>SUBTOTAL(9,H3:H32)</f>
+        <f t="shared" ref="H33:R33" si="6">SUBTOTAL(9,H3:H31)</f>
         <v>780</v>
       </c>
       <c r="I33" s="1">
-        <f>SUBTOTAL(9,I3:I32)</f>
+        <f t="shared" si="6"/>
         <v>16840</v>
       </c>
       <c r="J33" s="1">
-        <f>SUBTOTAL(9,J3:J32)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K33" s="1">
-        <f>SUBTOTAL(9,K3:K32)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L33" s="1">
-        <f>SUBTOTAL(9,L3:L32)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M33" s="1">
-        <f>SUBTOTAL(9,M3:M32)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N33" s="1">
-        <f>SUBTOTAL(9,N3:N32)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O33" s="1">
-        <f>SUBTOTAL(9,O3:O32)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P33" s="1">
-        <f>SUBTOTAL(9,P3:P32)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q33" s="1">
-        <f>SUBTOTAL(9,Q3:Q32)</f>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
       <c r="R33" s="1">
-        <f>SUBTOTAL(9,R3:R32)</f>
+        <f t="shared" si="6"/>
         <v>320</v>
       </c>
     </row>

--- a/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/May/THÁNG 5.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C078BE-6596-45D9-9C33-D590EC1BC61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF5E9FE-961D-4CBF-84E3-CE0694A3EBF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-5" sheetId="3" r:id="rId1"/>
@@ -4862,9 +4862,6 @@
     <t>Thanh Yến</t>
   </si>
   <si>
-    <t>HD022266</t>
-  </si>
-  <si>
     <t>188/4 đường thới an 16 phường thới an</t>
   </si>
   <si>
@@ -7131,6 +7128,9 @@
   </si>
   <si>
     <t>xx</t>
+  </si>
+  <si>
+    <t>HD022256</t>
   </si>
 </sst>
 </file>
@@ -12281,7 +12281,7 @@
         <v>1129</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="E5" s="22" t="s">
         <v>1130</v>
@@ -21580,10 +21580,10 @@
         <v>1590</v>
       </c>
       <c r="D9" s="22" t="s">
+        <v>2347</v>
+      </c>
+      <c r="E9" s="22" t="s">
         <v>1591</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>1592</v>
       </c>
       <c r="F9" s="23">
         <v>12</v>
@@ -21621,13 +21621,13 @@
         <v>30</v>
       </c>
       <c r="C10" s="22" t="s">
+        <v>1592</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>1593</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="E10" s="22" t="s">
         <v>1594</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>1595</v>
       </c>
       <c r="F10" s="23">
         <v>7</v>
@@ -21669,13 +21669,13 @@
         <v>30</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="D11" s="22" t="s">
+        <v>1595</v>
+      </c>
+      <c r="E11" s="22" t="s">
         <v>1596</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>1597</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>59</v>
@@ -21713,13 +21713,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="22" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D12" s="22" t="s">
         <v>1598</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="E12" s="22" t="s">
         <v>1599</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>1600</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>1324</v>
@@ -21757,10 +21757,10 @@
         <v>30</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D13" s="22" t="s">
         <v>1601</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>1602</v>
       </c>
       <c r="E13" s="22" t="s">
         <v>1303</v>
@@ -21805,13 +21805,13 @@
         <v>30</v>
       </c>
       <c r="C14" s="22" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>1603</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="E14" s="22" t="s">
         <v>1604</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>1605</v>
       </c>
       <c r="F14" s="23">
         <v>12</v>
@@ -21849,13 +21849,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>1606</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="E15" s="22" t="s">
         <v>1607</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>1608</v>
       </c>
       <c r="F15" s="23">
         <v>7</v>
@@ -21893,13 +21893,13 @@
         <v>30</v>
       </c>
       <c r="C16" s="22" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D16" s="22" t="s">
         <v>1609</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="E16" s="22" t="s">
         <v>1610</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>1611</v>
       </c>
       <c r="F16" s="23">
         <v>12</v>
@@ -21944,7 +21944,7 @@
         <v>1442</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="E17" s="22" t="s">
         <v>1444</v>
@@ -21985,13 +21985,13 @@
         <v>30</v>
       </c>
       <c r="C18" s="22" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>1613</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="E18" s="22" t="s">
         <v>1614</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>1615</v>
       </c>
       <c r="F18" s="23">
         <v>7</v>
@@ -22035,13 +22035,13 @@
         <v>30</v>
       </c>
       <c r="C19" s="22" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D19" s="22" t="s">
         <v>1616</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="E19" s="22" t="s">
         <v>1617</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>1618</v>
       </c>
       <c r="F19" s="22" t="s">
         <v>152</v>
@@ -22079,13 +22079,13 @@
         <v>30</v>
       </c>
       <c r="C20" s="22" t="s">
+        <v>1618</v>
+      </c>
+      <c r="D20" s="22" t="s">
         <v>1619</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="E20" s="22" t="s">
         <v>1620</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>1621</v>
       </c>
       <c r="F20" s="22" t="s">
         <v>59</v>
@@ -22217,11 +22217,11 @@
         <v>30</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="D23" s="22"/>
       <c r="E23" s="22" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="F23" s="22" t="s">
         <v>98</v>
@@ -22263,13 +22263,13 @@
         <v>30</v>
       </c>
       <c r="C24" s="22" t="s">
+        <v>1623</v>
+      </c>
+      <c r="D24" s="22" t="s">
         <v>1624</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="E24" s="22" t="s">
         <v>1625</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>1626</v>
       </c>
       <c r="F24" s="22" t="s">
         <v>90</v>
@@ -22313,13 +22313,13 @@
         <v>30</v>
       </c>
       <c r="C25" s="22" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D25" s="22" t="s">
         <v>1627</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="E25" s="22" t="s">
         <v>1628</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>1629</v>
       </c>
       <c r="F25" s="23">
         <v>1</v>
@@ -22364,10 +22364,10 @@
         <v>788</v>
       </c>
       <c r="D26" s="22" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E26" s="22" t="s">
         <v>1630</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>1631</v>
       </c>
       <c r="F26" s="23">
         <v>1</v>
@@ -22412,10 +22412,10 @@
         <v>1101</v>
       </c>
       <c r="D27" s="22" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E27" s="22" t="s">
         <v>1632</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>1633</v>
       </c>
       <c r="F27" s="22" t="s">
         <v>108</v>
@@ -22453,13 +22453,13 @@
         <v>30</v>
       </c>
       <c r="C28" s="22" t="s">
+        <v>1633</v>
+      </c>
+      <c r="D28" s="22" t="s">
         <v>1634</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="E28" s="22" t="s">
         <v>1635</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>1636</v>
       </c>
       <c r="F28" s="23">
         <v>3</v>
@@ -22501,13 +22501,13 @@
         <v>30</v>
       </c>
       <c r="C29" s="22" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D29" s="22" t="s">
         <v>1637</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="E29" s="22" t="s">
         <v>1638</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>1639</v>
       </c>
       <c r="F29" s="22" t="s">
         <v>108</v>
@@ -22549,13 +22549,13 @@
         <v>30</v>
       </c>
       <c r="C30" s="22" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D30" s="22" t="s">
         <v>1640</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="E30" s="22" t="s">
         <v>1641</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>1642</v>
       </c>
       <c r="F30" s="22" t="s">
         <v>389</v>
@@ -22600,7 +22600,7 @@
         <v>573</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="E31" s="22" t="s">
         <v>575</v>
@@ -22641,13 +22641,13 @@
         <v>30</v>
       </c>
       <c r="C32" s="22" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D32" s="22" t="s">
         <v>1644</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="E32" s="22" t="s">
         <v>1645</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>1646</v>
       </c>
       <c r="F32" s="23">
         <v>1</v>
@@ -22685,13 +22685,13 @@
         <v>30</v>
       </c>
       <c r="C33" s="22" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D33" s="22" t="s">
         <v>1647</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="E33" s="22" t="s">
         <v>1648</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>1649</v>
       </c>
       <c r="F33" s="23">
         <v>3</v>
@@ -22778,7 +22778,7 @@
         <v>-2930</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -22964,13 +22964,13 @@
         <v>30</v>
       </c>
       <c r="C3" s="17" t="s">
+        <v>1651</v>
+      </c>
+      <c r="D3" s="17" t="s">
         <v>1652</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="E3" s="17" t="s">
         <v>1653</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>1654</v>
       </c>
       <c r="F3" s="17" t="s">
         <v>39</v>
@@ -22985,13 +22985,13 @@
         <v>820</v>
       </c>
       <c r="J3" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="17" t="s">
         <v>1655</v>
-      </c>
-      <c r="K3" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="17" t="s">
-        <v>1656</v>
       </c>
       <c r="M3" s="17"/>
       <c r="N3" s="17"/>
@@ -23007,13 +23007,13 @@
         <v>30</v>
       </c>
       <c r="C4" s="17" t="s">
+        <v>1656</v>
+      </c>
+      <c r="D4" s="17" t="s">
         <v>1657</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="E4" s="17" t="s">
         <v>1658</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>1659</v>
       </c>
       <c r="F4" s="17" t="s">
         <v>39</v>
@@ -23028,13 +23028,13 @@
         <v>440</v>
       </c>
       <c r="J4" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="17" t="s">
         <v>1655</v>
-      </c>
-      <c r="K4" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="17" t="s">
-        <v>1656</v>
       </c>
       <c r="M4" s="17"/>
       <c r="N4" s="17"/>
@@ -23050,13 +23050,13 @@
         <v>30</v>
       </c>
       <c r="C5" s="17" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D5" s="17" t="s">
         <v>1660</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="E5" s="17" t="s">
         <v>1661</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>1662</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>59</v>
@@ -23071,13 +23071,13 @@
         <v>-25</v>
       </c>
       <c r="J5" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="17" t="s">
         <v>1655</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>1656</v>
       </c>
       <c r="M5" s="17"/>
       <c r="N5" s="17"/>
@@ -23096,13 +23096,13 @@
         <v>30</v>
       </c>
       <c r="C6" s="17" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D6" s="17" t="s">
         <v>1663</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="E6" s="17" t="s">
         <v>1664</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>1665</v>
       </c>
       <c r="F6" s="18">
         <v>8</v>
@@ -23117,13 +23117,13 @@
         <v>820</v>
       </c>
       <c r="J6" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="17" t="s">
         <v>1655</v>
-      </c>
-      <c r="K6" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>1656</v>
       </c>
       <c r="M6" s="17"/>
       <c r="N6" s="17"/>
@@ -23142,7 +23142,7 @@
         <v>831</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>1513</v>
@@ -23160,13 +23160,13 @@
         <v>890</v>
       </c>
       <c r="J7" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="17" t="s">
         <v>1655</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>1656</v>
       </c>
       <c r="M7" s="17"/>
       <c r="N7" s="17"/>
@@ -23183,13 +23183,13 @@
         <v>30</v>
       </c>
       <c r="C8" s="17" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D8" s="17" t="s">
         <v>1667</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="E8" s="17" t="s">
         <v>1668</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>1669</v>
       </c>
       <c r="F8" s="18" t="s">
         <v>59</v>
@@ -23204,13 +23204,13 @@
         <v>1830</v>
       </c>
       <c r="J8" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="17" t="s">
         <v>1655</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="17" t="s">
-        <v>1656</v>
       </c>
       <c r="M8" s="17"/>
       <c r="N8" s="17"/>
@@ -23226,13 +23226,13 @@
         <v>30</v>
       </c>
       <c r="C9" s="17" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D9" s="17" t="s">
         <v>1670</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="E9" s="17" t="s">
         <v>1671</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>1672</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>59</v>
@@ -23247,13 +23247,13 @@
         <v>770</v>
       </c>
       <c r="J9" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="17" t="s">
         <v>1655</v>
-      </c>
-      <c r="K9" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="17" t="s">
-        <v>1656</v>
       </c>
       <c r="M9" s="17"/>
       <c r="N9" s="17"/>
@@ -23269,13 +23269,13 @@
         <v>30</v>
       </c>
       <c r="C10" s="17" t="s">
+        <v>1672</v>
+      </c>
+      <c r="D10" s="17" t="s">
         <v>1673</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="E10" s="17" t="s">
         <v>1674</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>1675</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>39</v>
@@ -23290,13 +23290,13 @@
         <v>1090</v>
       </c>
       <c r="J10" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="17" t="s">
         <v>1655</v>
-      </c>
-      <c r="K10" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10" s="17" t="s">
-        <v>1656</v>
       </c>
       <c r="M10" s="21"/>
       <c r="N10" s="17"/>
@@ -23313,13 +23313,13 @@
         <v>30</v>
       </c>
       <c r="C11" s="17" t="s">
+        <v>1675</v>
+      </c>
+      <c r="D11" s="17" t="s">
         <v>1676</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="E11" s="17" t="s">
         <v>1677</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>1678</v>
       </c>
       <c r="F11" s="18" t="s">
         <v>59</v>
@@ -23334,13 +23334,13 @@
         <v>-25</v>
       </c>
       <c r="J11" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="17" t="s">
         <v>1655</v>
-      </c>
-      <c r="K11" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L11" s="17" t="s">
-        <v>1656</v>
       </c>
       <c r="M11" s="17"/>
       <c r="N11" s="17"/>
@@ -23362,7 +23362,7 @@
         <v>1321</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>1323</v>
@@ -23380,13 +23380,13 @@
         <v>740</v>
       </c>
       <c r="J12" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="17" t="s">
         <v>1655</v>
-      </c>
-      <c r="K12" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L12" s="17" t="s">
-        <v>1656</v>
       </c>
       <c r="M12" s="17"/>
       <c r="N12" s="17"/>
@@ -23405,7 +23405,7 @@
         <v>1289</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>1291</v>
@@ -23423,13 +23423,13 @@
         <v>680</v>
       </c>
       <c r="J13" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="17" t="s">
         <v>1655</v>
-      </c>
-      <c r="K13" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L13" s="17" t="s">
-        <v>1656</v>
       </c>
       <c r="M13" s="17"/>
       <c r="N13" s="17"/>
@@ -23445,13 +23445,13 @@
         <v>30</v>
       </c>
       <c r="C14" s="17" t="s">
+        <v>1680</v>
+      </c>
+      <c r="D14" s="17" t="s">
         <v>1681</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="E14" s="17" t="s">
         <v>1682</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>1683</v>
       </c>
       <c r="F14" s="17">
         <v>7</v>
@@ -23466,13 +23466,13 @@
         <v>490</v>
       </c>
       <c r="J14" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="17" t="s">
         <v>1655</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L14" s="17" t="s">
-        <v>1656</v>
       </c>
       <c r="M14" s="17"/>
       <c r="N14" s="17"/>
@@ -23488,13 +23488,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="17" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D15" s="17" t="s">
         <v>1684</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="E15" s="17" t="s">
         <v>1685</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>1686</v>
       </c>
       <c r="F15" s="17">
         <v>8</v>
@@ -23509,13 +23509,13 @@
         <v>-30</v>
       </c>
       <c r="J15" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="17" t="s">
         <v>1655</v>
-      </c>
-      <c r="K15" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L15" s="17" t="s">
-        <v>1656</v>
       </c>
       <c r="M15" s="17"/>
       <c r="N15" s="17"/>
@@ -23534,13 +23534,13 @@
         <v>30</v>
       </c>
       <c r="C16" s="17" t="s">
+        <v>1686</v>
+      </c>
+      <c r="D16" s="17" t="s">
         <v>1687</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="E16" s="17" t="s">
         <v>1688</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>1689</v>
       </c>
       <c r="F16" s="17">
         <v>5</v>
@@ -23555,13 +23555,13 @@
         <v>-25</v>
       </c>
       <c r="J16" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="17" t="s">
         <v>1655</v>
-      </c>
-      <c r="K16" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L16" s="17" t="s">
-        <v>1656</v>
       </c>
       <c r="M16" s="17"/>
       <c r="N16" s="17"/>
@@ -23580,13 +23580,13 @@
         <v>30</v>
       </c>
       <c r="C17" s="17" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D17" s="17" t="s">
         <v>1690</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="E17" s="17" t="s">
         <v>1691</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>1692</v>
       </c>
       <c r="F17" s="17">
         <v>9</v>
@@ -23601,13 +23601,13 @@
         <v>490</v>
       </c>
       <c r="J17" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="17" t="s">
         <v>1655</v>
-      </c>
-      <c r="K17" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L17" s="17" t="s">
-        <v>1656</v>
       </c>
       <c r="M17" s="17"/>
       <c r="N17" s="17"/>
@@ -23627,10 +23627,10 @@
         <v>1289</v>
       </c>
       <c r="D18" s="17" t="s">
+        <v>1692</v>
+      </c>
+      <c r="E18" s="17" t="s">
         <v>1693</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>1694</v>
       </c>
       <c r="F18" s="17">
         <v>7</v>
@@ -23645,13 +23645,13 @@
         <v>960</v>
       </c>
       <c r="J18" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="17" t="s">
         <v>1655</v>
-      </c>
-      <c r="K18" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L18" s="17" t="s">
-        <v>1656</v>
       </c>
       <c r="M18" s="17"/>
       <c r="N18" s="17"/>
@@ -23667,13 +23667,13 @@
         <v>30</v>
       </c>
       <c r="C19" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D19" s="17" t="s">
         <v>1695</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="E19" s="17" t="s">
         <v>1696</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>1697</v>
       </c>
       <c r="F19" s="17">
         <v>8</v>
@@ -23688,13 +23688,13 @@
         <v>990</v>
       </c>
       <c r="J19" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="17" t="s">
         <v>1655</v>
-      </c>
-      <c r="K19" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L19" s="17" t="s">
-        <v>1656</v>
       </c>
       <c r="M19" s="17"/>
       <c r="N19" s="17"/>
@@ -23711,13 +23711,13 @@
         <v>30</v>
       </c>
       <c r="C20" s="17" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D20" s="17" t="s">
         <v>1698</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="E20" s="17" t="s">
         <v>1699</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>1700</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>39</v>
@@ -23732,13 +23732,13 @@
         <v>830</v>
       </c>
       <c r="J20" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="17" t="s">
         <v>1655</v>
-      </c>
-      <c r="K20" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L20" s="17" t="s">
-        <v>1656</v>
       </c>
       <c r="M20" s="17"/>
       <c r="N20" s="17"/>
@@ -23775,13 +23775,13 @@
         <v>0</v>
       </c>
       <c r="J21" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="17" t="s">
         <v>1655</v>
-      </c>
-      <c r="K21" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L21" s="17" t="s">
-        <v>1656</v>
       </c>
       <c r="M21" s="17"/>
       <c r="N21" s="17"/>
@@ -23797,13 +23797,13 @@
         <v>30</v>
       </c>
       <c r="C22" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D22" s="17" t="s">
         <v>1701</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="E22" s="17" t="s">
         <v>1702</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>1703</v>
       </c>
       <c r="F22" s="18" t="s">
         <v>94</v>
@@ -23824,7 +23824,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M22" s="17"/>
       <c r="N22" s="17"/>
@@ -23840,13 +23840,13 @@
         <v>30</v>
       </c>
       <c r="C23" s="17" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D23" s="17" t="s">
         <v>1704</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="E23" s="17" t="s">
         <v>1705</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>1706</v>
       </c>
       <c r="F23" s="18">
         <v>12</v>
@@ -23867,7 +23867,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M23" s="17"/>
       <c r="N23" s="17"/>
@@ -23889,7 +23889,7 @@
         <v>993</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>995</v>
@@ -23913,7 +23913,7 @@
         <v>34</v>
       </c>
       <c r="L24" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M24" s="17"/>
       <c r="N24" s="17"/>
@@ -23929,13 +23929,13 @@
         <v>30</v>
       </c>
       <c r="C25" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D25" s="17" t="s">
         <v>1708</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="E25" s="17" t="s">
         <v>1709</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>1710</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>98</v>
@@ -23956,7 +23956,7 @@
         <v>34</v>
       </c>
       <c r="L25" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M25" s="17"/>
       <c r="N25" s="17"/>
@@ -23973,13 +23973,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="17" t="s">
+        <v>1710</v>
+      </c>
+      <c r="D26" s="17" t="s">
         <v>1711</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="E26" s="17" t="s">
         <v>1712</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>1713</v>
       </c>
       <c r="F26" s="18" t="s">
         <v>90</v>
@@ -24000,7 +24000,7 @@
         <v>34</v>
       </c>
       <c r="L26" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M26" s="17"/>
       <c r="N26" s="17"/>
@@ -24019,13 +24019,13 @@
         <v>30</v>
       </c>
       <c r="C27" s="17" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D27" s="17" t="s">
         <v>1714</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="E27" s="17" t="s">
         <v>1715</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>1716</v>
       </c>
       <c r="F27" s="17">
         <v>2</v>
@@ -24046,7 +24046,7 @@
         <v>34</v>
       </c>
       <c r="L27" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M27" s="17"/>
       <c r="N27" s="17"/>
@@ -24065,10 +24065,10 @@
         <v>124</v>
       </c>
       <c r="D28" s="17" t="s">
+        <v>1716</v>
+      </c>
+      <c r="E28" s="17" t="s">
         <v>1717</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>1718</v>
       </c>
       <c r="F28" s="17" t="s">
         <v>94</v>
@@ -24089,7 +24089,7 @@
         <v>34</v>
       </c>
       <c r="L28" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M28" s="21"/>
       <c r="N28" s="17"/>
@@ -24106,13 +24106,13 @@
         <v>30</v>
       </c>
       <c r="C29" s="17" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D29" s="17" t="s">
         <v>1719</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="E29" s="17" t="s">
         <v>1720</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>1721</v>
       </c>
       <c r="F29" s="18" t="s">
         <v>98</v>
@@ -24133,7 +24133,7 @@
         <v>34</v>
       </c>
       <c r="L29" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M29" s="17"/>
       <c r="N29" s="17"/>
@@ -24150,10 +24150,10 @@
         <v>30</v>
       </c>
       <c r="C30" s="17" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D30" s="17" t="s">
         <v>1722</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>1723</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>678</v>
@@ -24177,7 +24177,7 @@
         <v>34</v>
       </c>
       <c r="L30" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M30" s="17"/>
       <c r="N30" s="17"/>
@@ -24196,13 +24196,13 @@
         <v>30</v>
       </c>
       <c r="C31" s="17" t="s">
+        <v>1723</v>
+      </c>
+      <c r="D31" s="17" t="s">
         <v>1724</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="E31" s="17" t="s">
         <v>1725</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>1726</v>
       </c>
       <c r="F31" s="17" t="s">
         <v>98</v>
@@ -24223,7 +24223,7 @@
         <v>34</v>
       </c>
       <c r="L31" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M31" s="17"/>
       <c r="N31" s="17"/>
@@ -24239,13 +24239,13 @@
         <v>30</v>
       </c>
       <c r="C32" s="17" t="s">
+        <v>1726</v>
+      </c>
+      <c r="D32" s="17" t="s">
         <v>1727</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="E32" s="17" t="s">
         <v>1728</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>1729</v>
       </c>
       <c r="F32" s="17" t="s">
         <v>108</v>
@@ -24266,7 +24266,7 @@
         <v>34</v>
       </c>
       <c r="L32" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M32" s="17"/>
       <c r="N32" s="17"/>
@@ -24312,7 +24312,7 @@
         <v>34</v>
       </c>
       <c r="L33" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M33" s="17"/>
       <c r="N33" s="17"/>
@@ -24333,11 +24333,11 @@
         <v>30</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="D34" s="17"/>
       <c r="E34" s="17" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="F34" s="18" t="s">
         <v>94</v>
@@ -24358,7 +24358,7 @@
         <v>34</v>
       </c>
       <c r="L34" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M34" s="17"/>
       <c r="N34" s="17"/>
@@ -24377,13 +24377,13 @@
         <v>30</v>
       </c>
       <c r="C35" s="17" t="s">
+        <v>1731</v>
+      </c>
+      <c r="D35" s="17" t="s">
         <v>1732</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="E35" s="17" t="s">
         <v>1733</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>1734</v>
       </c>
       <c r="F35" s="18" t="s">
         <v>108</v>
@@ -24404,7 +24404,7 @@
         <v>34</v>
       </c>
       <c r="L35" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M35" s="17" t="s">
         <v>180</v>
@@ -24425,13 +24425,13 @@
         <v>30</v>
       </c>
       <c r="C36" s="17" t="s">
+        <v>1734</v>
+      </c>
+      <c r="D36" s="17" t="s">
         <v>1735</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="E36" s="17" t="s">
         <v>1736</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>1737</v>
       </c>
       <c r="F36" s="18">
         <v>10</v>
@@ -24452,7 +24452,7 @@
         <v>34</v>
       </c>
       <c r="L36" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M36" s="17"/>
       <c r="N36" s="17"/>
@@ -24469,13 +24469,13 @@
         <v>30</v>
       </c>
       <c r="C37" s="17" t="s">
+        <v>1737</v>
+      </c>
+      <c r="D37" s="17" t="s">
         <v>1738</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="E37" s="17" t="s">
         <v>1739</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>1740</v>
       </c>
       <c r="F37" s="18">
         <v>5</v>
@@ -24496,7 +24496,7 @@
         <v>34</v>
       </c>
       <c r="L37" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M37" s="17"/>
       <c r="N37" s="17"/>
@@ -24515,7 +24515,7 @@
         <v>1223</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="E38" s="17" t="s">
         <v>1225</v>
@@ -24539,7 +24539,7 @@
         <v>34</v>
       </c>
       <c r="L38" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M38" s="17"/>
       <c r="N38" s="17"/>
@@ -24555,13 +24555,13 @@
         <v>30</v>
       </c>
       <c r="C39" s="17" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D39" s="17" t="s">
         <v>1742</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="E39" s="17" t="s">
         <v>1743</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>1744</v>
       </c>
       <c r="F39" s="17">
         <v>3</v>
@@ -24582,7 +24582,7 @@
         <v>34</v>
       </c>
       <c r="L39" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M39" s="17"/>
       <c r="N39" s="17"/>
@@ -24599,13 +24599,13 @@
         <v>30</v>
       </c>
       <c r="C40" s="17" t="s">
+        <v>1744</v>
+      </c>
+      <c r="D40" s="17" t="s">
         <v>1745</v>
       </c>
-      <c r="D40" s="17" t="s">
+      <c r="E40" s="17" t="s">
         <v>1746</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>1747</v>
       </c>
       <c r="F40" s="17">
         <v>1</v>
@@ -24626,7 +24626,7 @@
         <v>34</v>
       </c>
       <c r="L40" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M40" s="17"/>
       <c r="N40" s="17"/>
@@ -24645,13 +24645,13 @@
         <v>30</v>
       </c>
       <c r="C41" s="17" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D41" s="17" t="s">
         <v>1748</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="E41" s="17" t="s">
         <v>1749</v>
-      </c>
-      <c r="E41" s="17" t="s">
-        <v>1750</v>
       </c>
       <c r="F41" s="18">
         <v>1</v>
@@ -24672,7 +24672,7 @@
         <v>34</v>
       </c>
       <c r="L41" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M41" s="17"/>
       <c r="N41" s="17"/>
@@ -24690,11 +24690,11 @@
         <v>30</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="D42" s="17"/>
       <c r="E42" s="17" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="F42" s="18">
         <v>5</v>
@@ -24715,7 +24715,7 @@
         <v>34</v>
       </c>
       <c r="L42" s="17" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M42" s="17"/>
       <c r="N42" s="17"/>
@@ -24780,7 +24780,7 @@
         <v>-780</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
@@ -24892,13 +24892,13 @@
         <v>30</v>
       </c>
       <c r="B59" s="53" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="C59" s="53" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D59" s="53" t="s">
         <v>1596</v>
-      </c>
-      <c r="D59" s="53" t="s">
-        <v>1597</v>
       </c>
       <c r="E59" s="54" t="s">
         <v>59</v>
@@ -24923,7 +24923,7 @@
         <v>1577</v>
       </c>
       <c r="L59" s="28" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
     </row>
   </sheetData>
@@ -24958,7 +24958,7 @@
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -25021,7 +25021,7 @@
         <v>1285</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="E3" s="22" t="s">
         <v>1287</v>
@@ -25040,13 +25040,13 @@
         <v>820</v>
       </c>
       <c r="J3" s="22" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
         <v>1761</v>
-      </c>
-      <c r="K3" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="22" t="s">
-        <v>1762</v>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="22"/>
@@ -25062,13 +25062,13 @@
         <v>30</v>
       </c>
       <c r="C4" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D4" s="22" t="s">
         <v>1763</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="E4" s="22" t="s">
         <v>1764</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>1765</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>39</v>
@@ -25084,13 +25084,13 @@
         <v>370</v>
       </c>
       <c r="J4" s="22" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
         <v>1761</v>
-      </c>
-      <c r="K4" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="22" t="s">
-        <v>1762</v>
       </c>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
@@ -25106,10 +25106,10 @@
         <v>30</v>
       </c>
       <c r="C5" s="22" t="s">
+        <v>1765</v>
+      </c>
+      <c r="D5" s="22" t="s">
         <v>1766</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>1767</v>
       </c>
       <c r="E5" s="22" t="s">
         <v>1300</v>
@@ -25128,16 +25128,16 @@
         <v>-30</v>
       </c>
       <c r="J5" s="22" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
         <v>1761</v>
       </c>
-      <c r="K5" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>1762</v>
-      </c>
       <c r="M5" s="28" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="N5" s="22"/>
       <c r="O5" s="22"/>
@@ -25156,13 +25156,13 @@
         <v>30</v>
       </c>
       <c r="C6" s="22" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D6" s="22" t="s">
         <v>1769</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="E6" s="22" t="s">
         <v>1770</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>1771</v>
       </c>
       <c r="F6" s="23">
         <v>12</v>
@@ -25178,13 +25178,13 @@
         <v>-30</v>
       </c>
       <c r="J6" s="22" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
         <v>1761</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>1762</v>
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="22"/>
@@ -25204,13 +25204,13 @@
         <v>30</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="F7" s="26">
         <v>12</v>
@@ -25226,13 +25226,13 @@
         <v>300</v>
       </c>
       <c r="J7" s="25" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="25" t="s">
         <v>1761</v>
-      </c>
-      <c r="K7" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="25" t="s">
-        <v>1762</v>
       </c>
       <c r="M7" s="25" t="s">
         <v>139</v>
@@ -25250,13 +25250,13 @@
         <v>30</v>
       </c>
       <c r="C8" s="22" t="s">
+        <v>1772</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>1773</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="E8" s="22" t="s">
         <v>1774</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>1775</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>39</v>
@@ -25272,13 +25272,13 @@
         <v>-30</v>
       </c>
       <c r="J8" s="22" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
         <v>1761</v>
-      </c>
-      <c r="K8" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>1762</v>
       </c>
       <c r="M8" s="22"/>
       <c r="N8" s="22"/>
@@ -25298,10 +25298,10 @@
         <v>30</v>
       </c>
       <c r="C9" s="22" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>1776</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>1777</v>
       </c>
       <c r="E9" s="22" t="s">
         <v>824</v>
@@ -25320,13 +25320,13 @@
         <v>830</v>
       </c>
       <c r="J9" s="22" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
         <v>1761</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="22" t="s">
-        <v>1762</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -25342,13 +25342,13 @@
         <v>30</v>
       </c>
       <c r="C10" s="22" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>1778</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="E10" s="22" t="s">
         <v>1779</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>1780</v>
       </c>
       <c r="F10" s="23">
         <v>8</v>
@@ -25364,13 +25364,13 @@
         <v>660</v>
       </c>
       <c r="J10" s="22" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
         <v>1761</v>
-      </c>
-      <c r="K10" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10" s="22" t="s">
-        <v>1762</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -25386,13 +25386,13 @@
         <v>30</v>
       </c>
       <c r="C11" s="22" t="s">
+        <v>1780</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>1781</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="E11" s="22" t="s">
         <v>1782</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>1783</v>
       </c>
       <c r="F11" s="23">
         <v>7</v>
@@ -25408,13 +25408,13 @@
         <v>890</v>
       </c>
       <c r="J11" s="22" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
         <v>1761</v>
-      </c>
-      <c r="K11" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L11" s="22" t="s">
-        <v>1762</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
@@ -25430,13 +25430,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="D12" s="22" t="s">
         <v>744</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>39</v>
@@ -25452,13 +25452,13 @@
         <v>790</v>
       </c>
       <c r="J12" s="22" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
         <v>1761</v>
-      </c>
-      <c r="K12" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L12" s="22" t="s">
-        <v>1762</v>
       </c>
       <c r="M12" s="28" t="s">
         <v>360</v>
@@ -25476,13 +25476,13 @@
         <v>30</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>1785</v>
+      </c>
+      <c r="E13" s="22" t="s">
         <v>1784</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>1786</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>1785</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>39</v>
@@ -25498,13 +25498,13 @@
         <v>660</v>
       </c>
       <c r="J13" s="22" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
         <v>1761</v>
-      </c>
-      <c r="K13" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L13" s="22" t="s">
-        <v>1762</v>
       </c>
       <c r="M13" s="28" t="s">
         <v>360</v>
@@ -25522,13 +25522,13 @@
         <v>30</v>
       </c>
       <c r="C14" s="22" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>1787</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="E14" s="22" t="s">
         <v>1788</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>1789</v>
       </c>
       <c r="F14" s="22" t="s">
         <v>39</v>
@@ -25544,13 +25544,13 @@
         <v>480</v>
       </c>
       <c r="J14" s="22" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
         <v>1761</v>
-      </c>
-      <c r="K14" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L14" s="22" t="s">
-        <v>1762</v>
       </c>
       <c r="M14" s="22"/>
       <c r="N14" s="22"/>
@@ -25566,13 +25566,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>1789</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>1790</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="E15" s="22" t="s">
         <v>1791</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>1792</v>
       </c>
       <c r="F15" s="22" t="s">
         <v>59</v>
@@ -25588,13 +25588,13 @@
         <v>890</v>
       </c>
       <c r="J15" s="22" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
         <v>1761</v>
-      </c>
-      <c r="K15" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L15" s="22" t="s">
-        <v>1762</v>
       </c>
       <c r="M15" s="22"/>
       <c r="N15" s="22"/>
@@ -25613,10 +25613,10 @@
         <v>889</v>
       </c>
       <c r="D16" s="22" t="s">
+        <v>1792</v>
+      </c>
+      <c r="E16" s="22" t="s">
         <v>1793</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>1794</v>
       </c>
       <c r="F16" s="22" t="s">
         <v>39</v>
@@ -25632,13 +25632,13 @@
         <v>820</v>
       </c>
       <c r="J16" s="22" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
         <v>1761</v>
-      </c>
-      <c r="K16" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L16" s="22" t="s">
-        <v>1762</v>
       </c>
       <c r="M16" s="22"/>
       <c r="N16" s="22"/>
@@ -25654,13 +25654,13 @@
         <v>30</v>
       </c>
       <c r="C17" s="22" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D17" s="22" t="s">
         <v>1795</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="E17" s="22" t="s">
         <v>1796</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>1797</v>
       </c>
       <c r="F17" s="23">
         <v>11</v>
@@ -25676,13 +25676,13 @@
         <v>840</v>
       </c>
       <c r="J17" s="22" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
         <v>1761</v>
-      </c>
-      <c r="K17" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L17" s="22" t="s">
-        <v>1762</v>
       </c>
       <c r="M17" s="22"/>
       <c r="N17" s="22"/>
@@ -25701,7 +25701,7 @@
         <v>579</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="E18" s="22" t="s">
         <v>581</v>
@@ -25726,7 +25726,7 @@
         <v>34</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="M18" s="22"/>
       <c r="N18" s="22"/>
@@ -25742,13 +25742,13 @@
         <v>30</v>
       </c>
       <c r="C19" s="22" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D19" s="22" t="s">
         <v>1799</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="E19" s="22" t="s">
         <v>1800</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>1801</v>
       </c>
       <c r="F19" s="22" t="s">
         <v>90</v>
@@ -25770,7 +25770,7 @@
         <v>34</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="M19" s="22"/>
       <c r="N19" s="22"/>
@@ -25786,13 +25786,13 @@
         <v>30</v>
       </c>
       <c r="C20" s="22" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D20" s="22" t="s">
         <v>1802</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="E20" s="22" t="s">
         <v>1803</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>1804</v>
       </c>
       <c r="F20" s="22" t="s">
         <v>90</v>
@@ -25814,7 +25814,7 @@
         <v>34</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
@@ -25833,7 +25833,7 @@
         <v>667</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="E21" s="22" t="s">
         <v>669</v>
@@ -25858,7 +25858,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="M21" s="22"/>
       <c r="N21" s="22"/>
@@ -25874,13 +25874,13 @@
         <v>30</v>
       </c>
       <c r="C22" s="22" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D22" s="22" t="s">
         <v>1806</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="E22" s="22" t="s">
         <v>1807</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>1808</v>
       </c>
       <c r="F22" s="22" t="s">
         <v>108</v>
@@ -25902,7 +25902,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="M22" s="22"/>
       <c r="N22" s="22"/>
@@ -25924,11 +25924,11 @@
         <v>30</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="D23" s="22"/>
       <c r="E23" s="22" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="F23" s="22" t="s">
         <v>108</v>
@@ -25950,7 +25950,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="M23" s="22"/>
       <c r="N23" s="22"/>
@@ -25966,13 +25966,13 @@
         <v>30</v>
       </c>
       <c r="C24" s="22" t="s">
+        <v>1810</v>
+      </c>
+      <c r="D24" s="22" t="s">
         <v>1811</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="E24" s="22" t="s">
         <v>1812</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>1813</v>
       </c>
       <c r="F24" s="22" t="s">
         <v>108</v>
@@ -25994,7 +25994,7 @@
         <v>34</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="M24" s="22"/>
       <c r="N24" s="22"/>
@@ -26014,13 +26014,13 @@
         <v>30</v>
       </c>
       <c r="C25" s="22" t="s">
+        <v>1813</v>
+      </c>
+      <c r="D25" s="22" t="s">
         <v>1814</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="E25" s="22" t="s">
         <v>1815</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>1816</v>
       </c>
       <c r="F25" s="22" t="s">
         <v>108</v>
@@ -26042,7 +26042,7 @@
         <v>34</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="M25" s="22"/>
       <c r="N25" s="22"/>
@@ -26058,13 +26058,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="22" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D26" s="22" t="s">
         <v>1817</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="E26" s="22" t="s">
         <v>1818</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>1819</v>
       </c>
       <c r="F26" s="23">
         <v>10</v>
@@ -26086,7 +26086,7 @@
         <v>34</v>
       </c>
       <c r="L26" s="22" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="M26" s="22"/>
       <c r="N26" s="22"/>
@@ -26102,13 +26102,13 @@
         <v>30</v>
       </c>
       <c r="C27" s="22" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D27" s="22" t="s">
         <v>1820</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="E27" s="22" t="s">
         <v>1821</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>1822</v>
       </c>
       <c r="F27" s="23">
         <v>10</v>
@@ -26130,7 +26130,7 @@
         <v>34</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="M27" s="22"/>
       <c r="N27" s="22"/>
@@ -26146,10 +26146,10 @@
         <v>30</v>
       </c>
       <c r="C28" s="22" t="s">
+        <v>1822</v>
+      </c>
+      <c r="D28" s="22" t="s">
         <v>1823</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>1824</v>
       </c>
       <c r="E28" s="22" t="s">
         <v>379</v>
@@ -26174,7 +26174,7 @@
         <v>34</v>
       </c>
       <c r="L28" s="22" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
@@ -26244,7 +26244,7 @@
     </row>
     <row r="34" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H34" s="4" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>15</v>
@@ -26343,10 +26343,10 @@
         <v>30</v>
       </c>
       <c r="B45" s="36" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C45" s="36" t="s">
         <v>1766</v>
-      </c>
-      <c r="C45" s="36" t="s">
-        <v>1767</v>
       </c>
       <c r="D45" s="36" t="s">
         <v>1300</v>
@@ -26365,16 +26365,16 @@
         <v>1710</v>
       </c>
       <c r="I45" s="36" t="s">
+        <v>1760</v>
+      </c>
+      <c r="J45" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="K45" s="36" t="s">
         <v>1761</v>
       </c>
-      <c r="J45" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="K45" s="36" t="s">
-        <v>1762</v>
-      </c>
       <c r="L45" s="28" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
   </sheetData>
@@ -26409,7 +26409,7 @@
         <v>717</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -26469,13 +26469,13 @@
         <v>30</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="F3" s="26">
         <v>12</v>
@@ -26491,13 +26491,13 @@
         <v>755</v>
       </c>
       <c r="J3" s="25" t="s">
+        <v>1827</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="25" t="s">
         <v>1828</v>
-      </c>
-      <c r="K3" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="25" t="s">
-        <v>1829</v>
       </c>
       <c r="M3" s="25" t="s">
         <v>139</v>
@@ -26518,7 +26518,7 @@
         <v>66</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>68</v>
@@ -26537,13 +26537,13 @@
         <v>1520</v>
       </c>
       <c r="J4" s="22" t="s">
+        <v>1827</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
         <v>1828</v>
-      </c>
-      <c r="K4" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="22" t="s">
-        <v>1829</v>
       </c>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
@@ -26562,10 +26562,10 @@
         <v>831</v>
       </c>
       <c r="D5" s="22" t="s">
+        <v>1830</v>
+      </c>
+      <c r="E5" s="22" t="s">
         <v>1831</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>1832</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>59</v>
@@ -26581,13 +26581,13 @@
         <v>-25</v>
       </c>
       <c r="J5" s="22" t="s">
+        <v>1827</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
         <v>1828</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>1829</v>
       </c>
       <c r="M5" s="22"/>
       <c r="N5" s="22"/>
@@ -26607,13 +26607,13 @@
         <v>30</v>
       </c>
       <c r="C6" s="22" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D6" s="22" t="s">
         <v>1833</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="E6" s="22" t="s">
         <v>1834</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>1835</v>
       </c>
       <c r="F6" s="23">
         <v>8</v>
@@ -26629,13 +26629,13 @@
         <v>790</v>
       </c>
       <c r="J6" s="22" t="s">
+        <v>1827</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
         <v>1828</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>1829</v>
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="22"/>
@@ -26651,13 +26651,13 @@
         <v>30</v>
       </c>
       <c r="C7" s="22" t="s">
+        <v>1835</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>1836</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="E7" s="22" t="s">
         <v>1837</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>1838</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>152</v>
@@ -26673,13 +26673,13 @@
         <v>990</v>
       </c>
       <c r="J7" s="22" t="s">
+        <v>1827</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
         <v>1828</v>
-      </c>
-      <c r="K7" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="22" t="s">
-        <v>1829</v>
       </c>
       <c r="M7" s="22"/>
       <c r="N7" s="22"/>
@@ -26695,13 +26695,13 @@
         <v>30</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="F8" s="23">
         <v>7</v>
@@ -26717,13 +26717,13 @@
         <v>790</v>
       </c>
       <c r="J8" s="22" t="s">
+        <v>1827</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
         <v>1828</v>
-      </c>
-      <c r="K8" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>1829</v>
       </c>
       <c r="M8" s="28" t="s">
         <v>180</v>
@@ -26747,11 +26747,11 @@
         <v>30</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="D9" s="22"/>
       <c r="E9" s="22" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="F9" s="23">
         <v>6</v>
@@ -26767,13 +26767,13 @@
         <v>1370</v>
       </c>
       <c r="J9" s="22" t="s">
+        <v>1827</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
         <v>1828</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="22" t="s">
-        <v>1829</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -26789,13 +26789,13 @@
         <v>30</v>
       </c>
       <c r="C10" s="22" t="s">
+        <v>1841</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>1842</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="E10" s="22" t="s">
         <v>1843</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>1844</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>98</v>
@@ -26817,7 +26817,7 @@
         <v>34</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -26833,13 +26833,13 @@
         <v>30</v>
       </c>
       <c r="C11" s="22" t="s">
+        <v>1844</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>1845</v>
       </c>
-      <c r="D11" s="22" t="s">
-        <v>1846</v>
-      </c>
       <c r="E11" s="22" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>108</v>
@@ -26861,7 +26861,7 @@
         <v>34</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
@@ -26880,10 +26880,10 @@
         <v>53</v>
       </c>
       <c r="D12" s="22" t="s">
+        <v>1846</v>
+      </c>
+      <c r="E12" s="22" t="s">
         <v>1847</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>1848</v>
       </c>
       <c r="F12" s="23">
         <v>12</v>
@@ -26905,7 +26905,7 @@
         <v>34</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
@@ -26925,13 +26925,13 @@
         <v>30</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D13" s="22" t="s">
         <v>1849</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="E13" s="22" t="s">
         <v>1850</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>1851</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>90</v>
@@ -26953,7 +26953,7 @@
         <v>34</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M13" s="22"/>
       <c r="N13" s="22"/>
@@ -26976,7 +26976,7 @@
         <v>1380</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="E14" s="22" t="s">
         <v>1382</v>
@@ -27001,7 +27001,7 @@
         <v>34</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M14" s="22"/>
       <c r="N14" s="22"/>
@@ -27017,13 +27017,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>1853</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="E15" s="22" t="s">
         <v>1854</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>1855</v>
       </c>
       <c r="F15" s="22" t="s">
         <v>98</v>
@@ -27045,7 +27045,7 @@
         <v>34</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M15" s="22"/>
       <c r="N15" s="22"/>
@@ -27061,13 +27061,13 @@
         <v>30</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="D16" s="25" t="s">
+        <v>1855</v>
+      </c>
+      <c r="E16" s="25" t="s">
         <v>1856</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>1857</v>
       </c>
       <c r="F16" s="25" t="s">
         <v>90</v>
@@ -27089,7 +27089,7 @@
         <v>34</v>
       </c>
       <c r="L16" s="25" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M16" s="25" t="s">
         <v>139</v>
@@ -27107,13 +27107,13 @@
         <v>30</v>
       </c>
       <c r="C17" s="22" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D17" s="22" t="s">
         <v>1858</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="E17" s="22" t="s">
         <v>1859</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>1860</v>
       </c>
       <c r="F17" s="22" t="s">
         <v>98</v>
@@ -27135,7 +27135,7 @@
         <v>34</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M17" s="22"/>
       <c r="N17" s="22"/>
@@ -27183,7 +27183,7 @@
         <v>34</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M18" s="22"/>
       <c r="N18" s="22"/>
@@ -27201,11 +27201,11 @@
         <v>30</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="D19" s="22"/>
       <c r="E19" s="22" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="F19" s="22" t="s">
         <v>98</v>
@@ -27227,7 +27227,7 @@
         <v>34</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M19" s="22"/>
       <c r="N19" s="22"/>
@@ -27245,7 +27245,7 @@
         <v>30</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="D20" s="22"/>
       <c r="E20" s="22" t="s">
@@ -27271,7 +27271,7 @@
         <v>34</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
@@ -27291,13 +27291,13 @@
         <v>30</v>
       </c>
       <c r="C21" s="22" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D21" s="22" t="s">
         <v>1864</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="E21" s="22" t="s">
         <v>1865</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>1866</v>
       </c>
       <c r="F21" s="23">
         <v>3</v>
@@ -27319,7 +27319,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M21" s="28" t="s">
         <v>180</v>
@@ -27341,13 +27341,13 @@
         <v>30</v>
       </c>
       <c r="C22" s="22" t="s">
+        <v>1866</v>
+      </c>
+      <c r="D22" s="22" t="s">
         <v>1867</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="E22" s="22" t="s">
         <v>1868</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>1869</v>
       </c>
       <c r="F22" s="23">
         <v>1</v>
@@ -27369,7 +27369,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M22" s="22"/>
       <c r="N22" s="22"/>
@@ -27389,13 +27389,13 @@
         <v>30</v>
       </c>
       <c r="C23" s="22" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D23" s="22" t="s">
         <v>1870</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="E23" s="22" t="s">
         <v>1871</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>1872</v>
       </c>
       <c r="F23" s="23">
         <v>4</v>
@@ -27417,7 +27417,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M23" s="22"/>
       <c r="N23" s="22"/>
@@ -27437,13 +27437,13 @@
         <v>30</v>
       </c>
       <c r="C24" s="22" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D24" s="22" t="s">
         <v>1873</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="E24" s="22" t="s">
         <v>1874</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>1875</v>
       </c>
       <c r="F24" s="23">
         <v>3</v>
@@ -27465,7 +27465,7 @@
         <v>34</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M24" s="22"/>
       <c r="N24" s="22"/>
@@ -27488,10 +27488,10 @@
         <v>947</v>
       </c>
       <c r="D25" s="22" t="s">
+        <v>1875</v>
+      </c>
+      <c r="E25" s="22" t="s">
         <v>1876</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>1877</v>
       </c>
       <c r="F25" s="23">
         <v>5</v>
@@ -27513,7 +27513,7 @@
         <v>34</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M25" s="22"/>
       <c r="N25" s="22"/>
@@ -27533,13 +27533,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="22" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D26" s="22" t="s">
         <v>1878</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="E26" s="22" t="s">
         <v>1879</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>1880</v>
       </c>
       <c r="F26" s="23">
         <v>3</v>
@@ -27561,7 +27561,7 @@
         <v>34</v>
       </c>
       <c r="L26" s="22" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M26" s="22"/>
       <c r="N26" s="22"/>
@@ -27577,13 +27577,13 @@
         <v>30</v>
       </c>
       <c r="C27" s="22" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D27" s="22" t="s">
         <v>1881</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="E27" s="22" t="s">
         <v>1882</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>1883</v>
       </c>
       <c r="F27" s="23">
         <v>1</v>
@@ -27605,7 +27605,7 @@
         <v>34</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M27" s="22"/>
       <c r="N27" s="22"/>
@@ -27625,13 +27625,13 @@
         <v>30</v>
       </c>
       <c r="C28" s="22" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D28" s="22" t="s">
         <v>1884</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="E28" s="22" t="s">
         <v>1885</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>1886</v>
       </c>
       <c r="F28" s="22" t="s">
         <v>108</v>
@@ -27653,7 +27653,7 @@
         <v>34</v>
       </c>
       <c r="L28" s="22" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
@@ -27719,7 +27719,7 @@
     </row>
     <row r="34" spans="8:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H34" s="4" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>15</v>
@@ -28963,7 +28963,7 @@
         <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -29023,13 +29023,13 @@
         <v>30</v>
       </c>
       <c r="C3" s="22" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>1889</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="E3" s="22" t="s">
         <v>1890</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>1891</v>
       </c>
       <c r="F3" s="23">
         <v>12</v>
@@ -29045,13 +29045,13 @@
         <v>790</v>
       </c>
       <c r="J3" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K3" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="22"/>
@@ -29070,7 +29070,7 @@
         <v>280</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>282</v>
@@ -29089,13 +29089,13 @@
         <v>440</v>
       </c>
       <c r="J4" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K4" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
@@ -29111,10 +29111,10 @@
         <v>30</v>
       </c>
       <c r="C5" s="22" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D5" s="22" t="s">
         <v>1895</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>1896</v>
       </c>
       <c r="E5" s="22" t="s">
         <v>71</v>
@@ -29133,13 +29133,13 @@
         <v>480</v>
       </c>
       <c r="J5" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M5" s="22"/>
       <c r="N5" s="22"/>
@@ -29155,13 +29155,13 @@
         <v>30</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="D6" s="22" t="s">
+        <v>1896</v>
+      </c>
+      <c r="E6" s="22" t="s">
         <v>1897</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>1898</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>152</v>
@@ -29177,13 +29177,13 @@
         <v>5585</v>
       </c>
       <c r="J6" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M6" s="28" t="s">
         <v>180</v>
@@ -29205,13 +29205,13 @@
         <v>30</v>
       </c>
       <c r="C7" s="22" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>1899</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="E7" s="22" t="s">
         <v>1900</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>1901</v>
       </c>
       <c r="F7" s="23">
         <v>12</v>
@@ -29227,13 +29227,13 @@
         <v>-30</v>
       </c>
       <c r="J7" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K7" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M7" s="22"/>
       <c r="N7" s="22"/>
@@ -29256,7 +29256,7 @@
         <v>1155</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="E8" s="22" t="s">
         <v>1157</v>
@@ -29275,13 +29275,13 @@
         <v>820</v>
       </c>
       <c r="J8" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K8" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M8" s="22"/>
       <c r="N8" s="22"/>
@@ -29297,13 +29297,13 @@
         <v>30</v>
       </c>
       <c r="C9" s="22" t="s">
+        <v>1902</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>1903</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="E9" s="22" t="s">
         <v>1904</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>1905</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>39</v>
@@ -29319,13 +29319,13 @@
         <v>660</v>
       </c>
       <c r="J9" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -29341,13 +29341,13 @@
         <v>30</v>
       </c>
       <c r="C10" s="22" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>1906</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="E10" s="22" t="s">
         <v>1907</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>1908</v>
       </c>
       <c r="F10" s="23">
         <v>5</v>
@@ -29363,13 +29363,13 @@
         <v>820</v>
       </c>
       <c r="J10" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K10" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -29385,13 +29385,13 @@
         <v>30</v>
       </c>
       <c r="C11" s="22" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>1909</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="E11" s="22" t="s">
         <v>1910</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>1911</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>59</v>
@@ -29407,13 +29407,13 @@
         <v>440</v>
       </c>
       <c r="J11" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K11" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L11" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
@@ -29429,13 +29429,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="22" t="s">
+        <v>1911</v>
+      </c>
+      <c r="D12" s="22" t="s">
         <v>1912</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="E12" s="22" t="s">
         <v>1913</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>1914</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>59</v>
@@ -29451,13 +29451,13 @@
         <v>820</v>
       </c>
       <c r="J12" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K12" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L12" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
@@ -29476,10 +29476,10 @@
         <v>298</v>
       </c>
       <c r="D13" s="22" t="s">
+        <v>1914</v>
+      </c>
+      <c r="E13" s="22" t="s">
         <v>1915</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>1916</v>
       </c>
       <c r="F13" s="23">
         <v>7</v>
@@ -29495,13 +29495,13 @@
         <v>960</v>
       </c>
       <c r="J13" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K13" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L13" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M13" s="22"/>
       <c r="N13" s="22"/>
@@ -29517,13 +29517,13 @@
         <v>30</v>
       </c>
       <c r="C14" s="22" t="s">
+        <v>1916</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>1917</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="E14" s="22" t="s">
         <v>1918</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>1919</v>
       </c>
       <c r="F14" s="23">
         <v>8</v>
@@ -29539,13 +29539,13 @@
         <v>1610</v>
       </c>
       <c r="J14" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K14" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L14" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M14" s="22"/>
       <c r="N14" s="22"/>
@@ -29564,10 +29564,10 @@
         <v>737</v>
       </c>
       <c r="D15" s="22" t="s">
+        <v>1919</v>
+      </c>
+      <c r="E15" s="22" t="s">
         <v>1920</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>1921</v>
       </c>
       <c r="F15" s="23">
         <v>7</v>
@@ -29583,13 +29583,13 @@
         <v>1230</v>
       </c>
       <c r="J15" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K15" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L15" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M15" s="22"/>
       <c r="N15" s="22"/>
@@ -29608,7 +29608,7 @@
         <v>1581</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="E16" s="22" t="s">
         <v>1583</v>
@@ -29627,13 +29627,13 @@
         <v>1710</v>
       </c>
       <c r="J16" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K16" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L16" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M16" s="22"/>
       <c r="N16" s="22"/>
@@ -29649,13 +29649,13 @@
         <v>30</v>
       </c>
       <c r="C17" s="22" t="s">
+        <v>1922</v>
+      </c>
+      <c r="D17" s="22" t="s">
         <v>1923</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="E17" s="22" t="s">
         <v>1924</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>1925</v>
       </c>
       <c r="F17" s="23">
         <v>6</v>
@@ -29671,13 +29671,13 @@
         <v>970</v>
       </c>
       <c r="J17" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K17" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L17" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M17" s="22"/>
       <c r="N17" s="22"/>
@@ -29696,7 +29696,7 @@
         <v>987</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="E18" s="22" t="s">
         <v>989</v>
@@ -29715,13 +29715,13 @@
         <v>440</v>
       </c>
       <c r="J18" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K18" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L18" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M18" s="22"/>
       <c r="N18" s="22"/>
@@ -29737,13 +29737,13 @@
         <v>30</v>
       </c>
       <c r="C19" s="22" t="s">
+        <v>1926</v>
+      </c>
+      <c r="D19" s="22" t="s">
         <v>1927</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="E19" s="22" t="s">
         <v>1928</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>1929</v>
       </c>
       <c r="F19" s="22" t="s">
         <v>39</v>
@@ -29759,13 +29759,13 @@
         <v>490</v>
       </c>
       <c r="J19" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K19" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L19" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M19" s="22"/>
       <c r="N19" s="22"/>
@@ -29781,13 +29781,13 @@
         <v>30</v>
       </c>
       <c r="C20" s="22" t="s">
+        <v>1929</v>
+      </c>
+      <c r="D20" s="22" t="s">
         <v>1930</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="E20" s="22" t="s">
         <v>1931</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>1932</v>
       </c>
       <c r="F20" s="22" t="s">
         <v>39</v>
@@ -29803,13 +29803,13 @@
         <v>-30</v>
       </c>
       <c r="J20" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K20" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L20" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
@@ -29829,13 +29829,13 @@
         <v>30</v>
       </c>
       <c r="C21" s="22" t="s">
+        <v>1932</v>
+      </c>
+      <c r="D21" s="22" t="s">
         <v>1933</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="E21" s="22" t="s">
         <v>1934</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>1935</v>
       </c>
       <c r="F21" s="23">
         <v>7</v>
@@ -29851,13 +29851,13 @@
         <v>780</v>
       </c>
       <c r="J21" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K21" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L21" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M21" s="22"/>
       <c r="N21" s="22"/>
@@ -29876,10 +29876,10 @@
         <v>162</v>
       </c>
       <c r="D22" s="22" t="s">
+        <v>1935</v>
+      </c>
+      <c r="E22" s="22" t="s">
         <v>1936</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>1937</v>
       </c>
       <c r="F22" s="22" t="s">
         <v>59</v>
@@ -29895,13 +29895,13 @@
         <v>770</v>
       </c>
       <c r="J22" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K22" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L22" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M22" s="22"/>
       <c r="N22" s="22"/>
@@ -29920,7 +29920,7 @@
         <v>650</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="E23" s="22" t="s">
         <v>652</v>
@@ -29939,13 +29939,13 @@
         <v>970</v>
       </c>
       <c r="J23" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K23" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L23" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M23" s="22"/>
       <c r="N23" s="22"/>
@@ -29961,13 +29961,13 @@
         <v>30</v>
       </c>
       <c r="C24" s="55" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D24" s="22" t="s">
         <v>1939</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="E24" s="22" t="s">
         <v>1940</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>1941</v>
       </c>
       <c r="F24" s="22" t="s">
         <v>1324</v>
@@ -29983,13 +29983,13 @@
         <v>830</v>
       </c>
       <c r="J24" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K24" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L24" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M24" s="22"/>
       <c r="N24" s="22"/>
@@ -30005,13 +30005,13 @@
         <v>30</v>
       </c>
       <c r="C25" s="22" t="s">
+        <v>1941</v>
+      </c>
+      <c r="D25" s="22" t="s">
         <v>1942</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="E25" s="22" t="s">
         <v>1943</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>1944</v>
       </c>
       <c r="F25" s="22" t="s">
         <v>59</v>
@@ -30027,13 +30027,13 @@
         <v>-25</v>
       </c>
       <c r="J25" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K25" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L25" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M25" s="22"/>
       <c r="N25" s="22"/>
@@ -30053,13 +30053,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="22" t="s">
+        <v>1944</v>
+      </c>
+      <c r="D26" s="22" t="s">
         <v>1945</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="E26" s="22" t="s">
         <v>1946</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>1947</v>
       </c>
       <c r="F26" s="22" t="s">
         <v>147</v>
@@ -30075,13 +30075,13 @@
         <v>2725</v>
       </c>
       <c r="J26" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K26" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L26" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M26" s="28" t="s">
         <v>180</v>
@@ -30106,10 +30106,10 @@
         <v>598</v>
       </c>
       <c r="D27" s="22" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E27" s="22" t="s">
         <v>1948</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>1949</v>
       </c>
       <c r="F27" s="23">
         <v>7</v>
@@ -30125,13 +30125,13 @@
         <v>790</v>
       </c>
       <c r="J27" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K27" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L27" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M27" s="22"/>
       <c r="N27" s="22"/>
@@ -30147,13 +30147,13 @@
         <v>30</v>
       </c>
       <c r="C28" s="22" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D28" s="22" t="s">
         <v>1950</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="E28" s="22" t="s">
         <v>1951</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>1952</v>
       </c>
       <c r="F28" s="23">
         <v>7</v>
@@ -30169,13 +30169,13 @@
         <v>780</v>
       </c>
       <c r="J28" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K28" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L28" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
@@ -30191,13 +30191,13 @@
         <v>30</v>
       </c>
       <c r="C29" s="22" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D29" s="22" t="s">
         <v>1953</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="E29" s="22" t="s">
         <v>1954</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>1955</v>
       </c>
       <c r="F29" s="23">
         <v>9</v>
@@ -30213,13 +30213,13 @@
         <v>-30</v>
       </c>
       <c r="J29" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K29" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L29" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M29" s="22"/>
       <c r="N29" s="22"/>
@@ -30261,13 +30261,13 @@
         <v>-30</v>
       </c>
       <c r="J30" s="22" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="22" t="s">
         <v>1892</v>
-      </c>
-      <c r="K30" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L30" s="22" t="s">
-        <v>1893</v>
       </c>
       <c r="M30" s="22"/>
       <c r="N30" s="22"/>
@@ -30290,7 +30290,7 @@
         <v>1538</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="E31" s="22" t="s">
         <v>1540</v>
@@ -30315,7 +30315,7 @@
         <v>34</v>
       </c>
       <c r="L31" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M31" s="22"/>
       <c r="N31" s="22"/>
@@ -30335,13 +30335,13 @@
         <v>30</v>
       </c>
       <c r="C32" s="22" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D32" s="22" t="s">
         <v>1957</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="E32" s="22" t="s">
         <v>1958</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>1959</v>
       </c>
       <c r="F32" s="22" t="s">
         <v>90</v>
@@ -30363,7 +30363,7 @@
         <v>34</v>
       </c>
       <c r="L32" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M32" s="22"/>
       <c r="N32" s="22"/>
@@ -30379,13 +30379,13 @@
         <v>30</v>
       </c>
       <c r="C33" s="22" t="s">
+        <v>1959</v>
+      </c>
+      <c r="D33" s="22" t="s">
         <v>1960</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="E33" s="22" t="s">
         <v>1961</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>1962</v>
       </c>
       <c r="F33" s="22" t="s">
         <v>90</v>
@@ -30407,7 +30407,7 @@
         <v>34</v>
       </c>
       <c r="L33" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M33" s="22"/>
       <c r="N33" s="22"/>
@@ -30423,13 +30423,13 @@
         <v>30</v>
       </c>
       <c r="C34" s="22" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D34" s="22" t="s">
         <v>1963</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="E34" s="22" t="s">
         <v>1964</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>1965</v>
       </c>
       <c r="F34" s="23">
         <v>2</v>
@@ -30451,7 +30451,7 @@
         <v>34</v>
       </c>
       <c r="L34" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M34" s="22"/>
       <c r="N34" s="22"/>
@@ -30467,13 +30467,13 @@
         <v>30</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="F35" s="22" t="s">
         <v>98</v>
@@ -30495,7 +30495,7 @@
         <v>34</v>
       </c>
       <c r="L35" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M35" s="22"/>
       <c r="N35" s="22"/>
@@ -30511,13 +30511,13 @@
         <v>30</v>
       </c>
       <c r="C36" s="22" t="s">
+        <v>1966</v>
+      </c>
+      <c r="D36" s="22" t="s">
         <v>1967</v>
       </c>
-      <c r="D36" s="22" t="s">
+      <c r="E36" s="22" t="s">
         <v>1968</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>1969</v>
       </c>
       <c r="F36" s="23">
         <v>2</v>
@@ -30539,7 +30539,7 @@
         <v>34</v>
       </c>
       <c r="L36" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M36" s="22"/>
       <c r="N36" s="22"/>
@@ -30558,10 +30558,10 @@
         <v>1085</v>
       </c>
       <c r="D37" s="22" t="s">
+        <v>1969</v>
+      </c>
+      <c r="E37" s="22" t="s">
         <v>1970</v>
-      </c>
-      <c r="E37" s="22" t="s">
-        <v>1971</v>
       </c>
       <c r="F37" s="22" t="s">
         <v>90</v>
@@ -30583,7 +30583,7 @@
         <v>34</v>
       </c>
       <c r="L37" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M37" s="22"/>
       <c r="N37" s="22"/>
@@ -30602,7 +30602,7 @@
         <v>865</v>
       </c>
       <c r="D38" s="22" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="E38" s="22" t="s">
         <v>867</v>
@@ -30627,7 +30627,7 @@
         <v>34</v>
       </c>
       <c r="L38" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M38" s="28" t="s">
         <v>360</v>
@@ -30648,7 +30648,7 @@
         <v>865</v>
       </c>
       <c r="D39" s="22" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="E39" s="22" t="s">
         <v>867</v>
@@ -30673,7 +30673,7 @@
         <v>34</v>
       </c>
       <c r="L39" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M39" s="28" t="s">
         <v>360</v>
@@ -30691,13 +30691,13 @@
         <v>30</v>
       </c>
       <c r="C40" s="22" t="s">
+        <v>1973</v>
+      </c>
+      <c r="D40" s="22" t="s">
         <v>1974</v>
       </c>
-      <c r="D40" s="22" t="s">
+      <c r="E40" s="22" t="s">
         <v>1975</v>
-      </c>
-      <c r="E40" s="22" t="s">
-        <v>1976</v>
       </c>
       <c r="F40" s="22" t="s">
         <v>90</v>
@@ -30719,7 +30719,7 @@
         <v>34</v>
       </c>
       <c r="L40" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M40" s="22"/>
       <c r="N40" s="22"/>
@@ -30735,13 +30735,13 @@
         <v>30</v>
       </c>
       <c r="C41" s="22" t="s">
+        <v>1976</v>
+      </c>
+      <c r="D41" s="22" t="s">
         <v>1977</v>
       </c>
-      <c r="D41" s="22" t="s">
+      <c r="E41" s="22" t="s">
         <v>1978</v>
-      </c>
-      <c r="E41" s="22" t="s">
-        <v>1979</v>
       </c>
       <c r="F41" s="22" t="s">
         <v>108</v>
@@ -30763,7 +30763,7 @@
         <v>34</v>
       </c>
       <c r="L41" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M41" s="22"/>
       <c r="N41" s="22"/>
@@ -30807,7 +30807,7 @@
         <v>34</v>
       </c>
       <c r="L42" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M42" s="22"/>
       <c r="N42" s="22"/>
@@ -30851,7 +30851,7 @@
         <v>34</v>
       </c>
       <c r="L43" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M43" s="22"/>
       <c r="N43" s="22"/>
@@ -30899,7 +30899,7 @@
         <v>34</v>
       </c>
       <c r="L44" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M44" s="22"/>
       <c r="N44" s="22"/>
@@ -30915,13 +30915,13 @@
         <v>30</v>
       </c>
       <c r="C45" s="22" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D45" s="22" t="s">
         <v>1980</v>
       </c>
-      <c r="D45" s="22" t="s">
+      <c r="E45" s="22" t="s">
         <v>1981</v>
-      </c>
-      <c r="E45" s="22" t="s">
-        <v>1982</v>
       </c>
       <c r="F45" s="23">
         <v>1</v>
@@ -30943,7 +30943,7 @@
         <v>34</v>
       </c>
       <c r="L45" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M45" s="22"/>
       <c r="N45" s="22"/>
@@ -30966,7 +30966,7 @@
         <v>1223</v>
       </c>
       <c r="D46" s="22" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E46" s="22" t="s">
         <v>1225</v>
@@ -30991,7 +30991,7 @@
         <v>34</v>
       </c>
       <c r="L46" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M46" s="22"/>
       <c r="N46" s="22"/>
@@ -31007,13 +31007,13 @@
         <v>30</v>
       </c>
       <c r="C47" s="22" t="s">
+        <v>1983</v>
+      </c>
+      <c r="D47" s="22" t="s">
         <v>1984</v>
       </c>
-      <c r="D47" s="22" t="s">
+      <c r="E47" s="22" t="s">
         <v>1985</v>
-      </c>
-      <c r="E47" s="22" t="s">
-        <v>1986</v>
       </c>
       <c r="F47" s="22" t="s">
         <v>108</v>
@@ -31035,7 +31035,7 @@
         <v>34</v>
       </c>
       <c r="L47" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M47" s="22"/>
       <c r="N47" s="22"/>
@@ -31051,13 +31051,13 @@
         <v>30</v>
       </c>
       <c r="C48" s="22" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D48" s="22" t="s">
         <v>1987</v>
       </c>
-      <c r="D48" s="22" t="s">
+      <c r="E48" s="22" t="s">
         <v>1988</v>
-      </c>
-      <c r="E48" s="22" t="s">
-        <v>1989</v>
       </c>
       <c r="F48" s="23">
         <v>4</v>
@@ -31079,7 +31079,7 @@
         <v>34</v>
       </c>
       <c r="L48" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M48" s="22"/>
       <c r="N48" s="22"/>
@@ -31095,13 +31095,13 @@
         <v>30</v>
       </c>
       <c r="C49" s="22" t="s">
+        <v>1989</v>
+      </c>
+      <c r="D49" s="22" t="s">
         <v>1990</v>
       </c>
-      <c r="D49" s="22" t="s">
+      <c r="E49" s="22" t="s">
         <v>1991</v>
-      </c>
-      <c r="E49" s="22" t="s">
-        <v>1992</v>
       </c>
       <c r="F49" s="22" t="s">
         <v>389</v>
@@ -31123,7 +31123,7 @@
         <v>34</v>
       </c>
       <c r="L49" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M49" s="22"/>
       <c r="N49" s="22"/>
@@ -31139,13 +31139,13 @@
         <v>30</v>
       </c>
       <c r="C50" s="22" t="s">
+        <v>1992</v>
+      </c>
+      <c r="D50" s="22" t="s">
         <v>1993</v>
       </c>
-      <c r="D50" s="22" t="s">
+      <c r="E50" s="22" t="s">
         <v>1994</v>
-      </c>
-      <c r="E50" s="22" t="s">
-        <v>1995</v>
       </c>
       <c r="F50" s="22" t="s">
         <v>108</v>
@@ -31167,7 +31167,7 @@
         <v>34</v>
       </c>
       <c r="L50" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M50" s="22"/>
       <c r="N50" s="22"/>
@@ -31187,13 +31187,13 @@
         <v>30</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="D51" s="22" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="F51" s="23">
         <v>3</v>
@@ -31215,10 +31215,10 @@
         <v>34</v>
       </c>
       <c r="L51" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M51" s="28" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="N51" s="22"/>
       <c r="O51" s="22"/>
@@ -31237,13 +31237,13 @@
         <v>30</v>
       </c>
       <c r="C52" s="22" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D52" s="22" t="s">
         <v>1998</v>
       </c>
-      <c r="D52" s="22" t="s">
+      <c r="E52" s="22" t="s">
         <v>1999</v>
-      </c>
-      <c r="E52" s="22" t="s">
-        <v>2000</v>
       </c>
       <c r="F52" s="22" t="s">
         <v>389</v>
@@ -31265,7 +31265,7 @@
         <v>34</v>
       </c>
       <c r="L52" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M52" s="22"/>
       <c r="N52" s="22"/>
@@ -31284,10 +31284,10 @@
         <v>714</v>
       </c>
       <c r="D53" s="22" t="s">
+        <v>2000</v>
+      </c>
+      <c r="E53" s="22" t="s">
         <v>2001</v>
-      </c>
-      <c r="E53" s="22" t="s">
-        <v>2002</v>
       </c>
       <c r="F53" s="23">
         <v>10</v>
@@ -31309,7 +31309,7 @@
         <v>34</v>
       </c>
       <c r="L53" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M53" s="28" t="s">
         <v>360</v>
@@ -31330,10 +31330,10 @@
         <v>714</v>
       </c>
       <c r="D54" s="22" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="F54" s="23">
         <v>10</v>
@@ -31355,7 +31355,7 @@
         <v>34</v>
       </c>
       <c r="L54" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M54" s="28" t="s">
         <v>360</v>
@@ -31373,13 +31373,13 @@
         <v>30</v>
       </c>
       <c r="C55" s="22" t="s">
+        <v>2003</v>
+      </c>
+      <c r="D55" s="22" t="s">
         <v>2004</v>
       </c>
-      <c r="D55" s="22" t="s">
+      <c r="E55" s="22" t="s">
         <v>2005</v>
-      </c>
-      <c r="E55" s="22" t="s">
-        <v>2006</v>
       </c>
       <c r="F55" s="23">
         <v>10</v>
@@ -31401,7 +31401,7 @@
         <v>34</v>
       </c>
       <c r="L55" s="22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="M55" s="22"/>
       <c r="N55" s="22"/>
@@ -31463,7 +31463,7 @@
     </row>
     <row r="61" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H61" s="4" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="I61" s="5" t="s">
         <v>15</v>
@@ -31562,13 +31562,13 @@
         <v>30</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="C72" s="36" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="D72" s="36" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="E72" s="37">
         <v>3</v>
@@ -31590,10 +31590,10 @@
         <v>34</v>
       </c>
       <c r="K72" s="36" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="L72" s="28" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
     </row>
   </sheetData>
@@ -31628,7 +31628,7 @@
         <v>266</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -31690,11 +31690,11 @@
         <v>30</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D3" s="22"/>
       <c r="E3" s="22" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="F3" s="23">
         <v>9</v>
@@ -31716,7 +31716,7 @@
         <v>34</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="22"/>
@@ -31732,13 +31732,13 @@
         <v>30</v>
       </c>
       <c r="C4" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D4" s="22" t="s">
         <v>2012</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="E4" s="22" t="s">
         <v>2013</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>2014</v>
       </c>
       <c r="F4" s="23">
         <v>9</v>
@@ -31760,7 +31760,7 @@
         <v>34</v>
       </c>
       <c r="L4" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
@@ -31798,13 +31798,13 @@
         <v>0</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="K5" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L5" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M5" s="22"/>
       <c r="N5" s="22"/>
@@ -31826,7 +31826,7 @@
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="22" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="F6" s="23">
         <v>6</v>
@@ -31842,13 +31842,13 @@
         <v>-30</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="K6" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L6" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="22"/>
@@ -31868,13 +31868,13 @@
         <v>30</v>
       </c>
       <c r="C7" s="22" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>2017</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="E7" s="22" t="s">
         <v>2018</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>2019</v>
       </c>
       <c r="F7" s="23">
         <v>12</v>
@@ -31890,13 +31890,13 @@
         <v>2240</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="K7" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M7" s="28" t="s">
         <v>180</v>
@@ -31918,13 +31918,13 @@
         <v>30</v>
       </c>
       <c r="C8" s="22" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>2020</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="E8" s="22" t="s">
         <v>2021</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>2022</v>
       </c>
       <c r="F8" s="23">
         <v>7</v>
@@ -31940,13 +31940,13 @@
         <v>2080</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="K8" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M8" s="28" t="s">
         <v>180</v>
@@ -31968,13 +31968,13 @@
         <v>30</v>
       </c>
       <c r="C9" s="22" t="s">
+        <v>2022</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>2023</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="E9" s="22" t="s">
         <v>2024</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>2025</v>
       </c>
       <c r="F9" s="23">
         <v>6</v>
@@ -31990,13 +31990,13 @@
         <v>-25</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="K9" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -32019,10 +32019,10 @@
         <v>295</v>
       </c>
       <c r="D10" s="22" t="s">
+        <v>2025</v>
+      </c>
+      <c r="E10" s="22" t="s">
         <v>2026</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>2027</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>39</v>
@@ -32038,13 +32038,13 @@
         <v>350</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="K10" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -32063,7 +32063,7 @@
         <v>168</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E11" s="22" t="s">
         <v>170</v>
@@ -32082,13 +32082,13 @@
         <v>480</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="K11" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
@@ -32104,13 +32104,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="25" t="s">
+        <v>2028</v>
+      </c>
+      <c r="D12" s="25" t="s">
         <v>2029</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="E12" s="25" t="s">
         <v>2030</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>2031</v>
       </c>
       <c r="F12" s="26">
         <v>8</v>
@@ -32126,13 +32126,13 @@
         <v>-30</v>
       </c>
       <c r="J12" s="25" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="K12" s="25" t="s">
         <v>34</v>
       </c>
       <c r="L12" s="25" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M12" s="25" t="s">
         <v>139</v>
@@ -32154,13 +32154,13 @@
         <v>30</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>2031</v>
+      </c>
+      <c r="D13" s="22" t="s">
         <v>2032</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="E13" s="22" t="s">
         <v>2033</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>2034</v>
       </c>
       <c r="F13" s="23">
         <v>7</v>
@@ -32176,13 +32176,13 @@
         <v>890</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="K13" s="22" t="s">
         <v>34</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M13" s="22"/>
       <c r="N13" s="22"/>
@@ -32198,13 +32198,13 @@
         <v>30</v>
       </c>
       <c r="C14" s="22" t="s">
+        <v>2034</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>2035</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="E14" s="22" t="s">
         <v>2036</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>2037</v>
       </c>
       <c r="F14" s="22" t="s">
         <v>90</v>
@@ -32226,7 +32226,7 @@
         <v>34</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M14" s="22"/>
       <c r="N14" s="22"/>
@@ -32246,13 +32246,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>2037</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>2038</v>
       </c>
-      <c r="D15" s="22" t="s">
-        <v>2039</v>
-      </c>
       <c r="E15" s="22" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="F15" s="23">
         <v>2</v>
@@ -32274,7 +32274,7 @@
         <v>34</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M15" s="22"/>
       <c r="N15" s="22"/>
@@ -32290,10 +32290,10 @@
         <v>30</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="E16" s="22" t="s">
         <v>1093</v>
@@ -32318,7 +32318,7 @@
         <v>34</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M16" s="22"/>
       <c r="N16" s="22"/>
@@ -32337,10 +32337,10 @@
         <v>469</v>
       </c>
       <c r="D17" s="22" t="s">
+        <v>2040</v>
+      </c>
+      <c r="E17" s="22" t="s">
         <v>2041</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>2042</v>
       </c>
       <c r="F17" s="22" t="s">
         <v>90</v>
@@ -32362,7 +32362,7 @@
         <v>34</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M17" s="22"/>
       <c r="N17" s="22"/>
@@ -32378,13 +32378,13 @@
         <v>30</v>
       </c>
       <c r="C18" s="22" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>2043</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="E18" s="22" t="s">
         <v>2044</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>2045</v>
       </c>
       <c r="F18" s="22" t="s">
         <v>98</v>
@@ -32406,7 +32406,7 @@
         <v>34</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M18" s="22"/>
       <c r="N18" s="22"/>
@@ -32422,13 +32422,13 @@
         <v>30</v>
       </c>
       <c r="C19" s="22" t="s">
+        <v>2045</v>
+      </c>
+      <c r="D19" s="22" t="s">
         <v>2046</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="E19" s="22" t="s">
         <v>2047</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>2048</v>
       </c>
       <c r="F19" s="22" t="s">
         <v>94</v>
@@ -32450,7 +32450,7 @@
         <v>34</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M19" s="22"/>
       <c r="N19" s="22"/>
@@ -32466,13 +32466,13 @@
         <v>30</v>
       </c>
       <c r="C20" s="22" t="s">
+        <v>2048</v>
+      </c>
+      <c r="D20" s="22" t="s">
         <v>2049</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="E20" s="22" t="s">
         <v>2050</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>2051</v>
       </c>
       <c r="F20" s="23">
         <v>2</v>
@@ -32494,7 +32494,7 @@
         <v>34</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M20" s="28" t="s">
         <v>180</v>
@@ -32516,10 +32516,10 @@
         <v>30</v>
       </c>
       <c r="C21" s="22" t="s">
+        <v>2051</v>
+      </c>
+      <c r="D21" s="22" t="s">
         <v>2052</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>2053</v>
       </c>
       <c r="E21" s="22" t="s">
         <v>489</v>
@@ -32544,7 +32544,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M21" s="22"/>
       <c r="N21" s="22"/>
@@ -32567,10 +32567,10 @@
         <v>245</v>
       </c>
       <c r="D22" s="22" t="s">
+        <v>2053</v>
+      </c>
+      <c r="E22" s="22" t="s">
         <v>2054</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>2055</v>
       </c>
       <c r="F22" s="22" t="s">
         <v>98</v>
@@ -32592,7 +32592,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M22" s="22"/>
       <c r="N22" s="22"/>
@@ -32610,11 +32610,11 @@
         <v>30</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="D23" s="22"/>
       <c r="E23" s="22" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F23" s="23">
         <v>4</v>
@@ -32636,7 +32636,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M23" s="22"/>
       <c r="N23" s="22"/>
@@ -32680,7 +32680,7 @@
         <v>34</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M24" s="22"/>
       <c r="N24" s="22"/>
@@ -32700,13 +32700,13 @@
         <v>30</v>
       </c>
       <c r="C25" s="22" t="s">
+        <v>2057</v>
+      </c>
+      <c r="D25" s="22" t="s">
         <v>2058</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="E25" s="22" t="s">
         <v>2059</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>2060</v>
       </c>
       <c r="F25" s="23">
         <v>1</v>
@@ -32728,7 +32728,7 @@
         <v>34</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M25" s="22"/>
       <c r="N25" s="22"/>
@@ -32744,13 +32744,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="22" t="s">
+        <v>2060</v>
+      </c>
+      <c r="D26" s="22" t="s">
         <v>2061</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="E26" s="22" t="s">
         <v>2062</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>2063</v>
       </c>
       <c r="F26" s="23">
         <v>10</v>
@@ -32772,7 +32772,7 @@
         <v>34</v>
       </c>
       <c r="L26" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M26" s="22"/>
       <c r="N26" s="22"/>
@@ -32788,13 +32788,13 @@
         <v>30</v>
       </c>
       <c r="C27" s="22" t="s">
+        <v>2063</v>
+      </c>
+      <c r="D27" s="22" t="s">
         <v>2064</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="E27" s="22" t="s">
         <v>2065</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>2066</v>
       </c>
       <c r="F27" s="23">
         <v>5</v>
@@ -32816,7 +32816,7 @@
         <v>34</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M27" s="22"/>
       <c r="N27" s="22"/>
@@ -32832,13 +32832,13 @@
         <v>30</v>
       </c>
       <c r="C28" s="22" t="s">
+        <v>2066</v>
+      </c>
+      <c r="D28" s="22" t="s">
         <v>2067</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="E28" s="22" t="s">
         <v>2068</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>2069</v>
       </c>
       <c r="F28" s="23">
         <v>5</v>
@@ -32860,7 +32860,7 @@
         <v>34</v>
       </c>
       <c r="L28" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
@@ -32876,13 +32876,13 @@
         <v>30</v>
       </c>
       <c r="C29" s="22" t="s">
+        <v>2069</v>
+      </c>
+      <c r="D29" s="22" t="s">
         <v>2070</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="E29" s="22" t="s">
         <v>2071</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>2072</v>
       </c>
       <c r="F29" s="22" t="s">
         <v>108</v>
@@ -32904,7 +32904,7 @@
         <v>34</v>
       </c>
       <c r="L29" s="22" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M29" s="22"/>
       <c r="N29" s="22"/>
@@ -32973,12 +32973,12 @@
         <v>-4365</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="35" spans="8:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H35" s="4" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>15</v>
@@ -33099,7 +33099,7 @@
         <v>270</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -33159,13 +33159,13 @@
         <v>30</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="D3" s="22" t="s">
+        <v>2075</v>
+      </c>
+      <c r="E3" s="22" t="s">
         <v>2076</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>2077</v>
       </c>
       <c r="F3" s="23">
         <v>8</v>
@@ -33181,13 +33181,13 @@
         <v>780</v>
       </c>
       <c r="J3" s="22" t="s">
+        <v>2077</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
         <v>2078</v>
-      </c>
-      <c r="K3" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="22" t="s">
-        <v>2079</v>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="22"/>
@@ -33206,7 +33206,7 @@
         <v>1421</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>736</v>
@@ -33225,13 +33225,13 @@
         <v>-30</v>
       </c>
       <c r="J4" s="22" t="s">
+        <v>2077</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
         <v>2078</v>
-      </c>
-      <c r="K4" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="22" t="s">
-        <v>2079</v>
       </c>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
@@ -33254,7 +33254,7 @@
         <v>1432</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="E5" s="22" t="s">
         <v>1434</v>
@@ -33273,13 +33273,13 @@
         <v>-30</v>
       </c>
       <c r="J5" s="22" t="s">
+        <v>2077</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
         <v>2078</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>2079</v>
       </c>
       <c r="M5" s="22"/>
       <c r="N5" s="22"/>
@@ -33299,13 +33299,13 @@
         <v>30</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="D6" s="22" t="s">
+        <v>2081</v>
+      </c>
+      <c r="E6" s="22" t="s">
         <v>2082</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>2083</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>59</v>
@@ -33321,13 +33321,13 @@
         <v>-25</v>
       </c>
       <c r="J6" s="22" t="s">
+        <v>2077</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
         <v>2078</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>2079</v>
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="22"/>
@@ -33347,13 +33347,13 @@
         <v>30</v>
       </c>
       <c r="C7" s="22" t="s">
+        <v>2083</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>2084</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="E7" s="22" t="s">
         <v>2085</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>2086</v>
       </c>
       <c r="F7" s="23">
         <v>8</v>
@@ -33369,13 +33369,13 @@
         <v>440</v>
       </c>
       <c r="J7" s="22" t="s">
+        <v>2077</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
         <v>2078</v>
-      </c>
-      <c r="K7" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="22" t="s">
-        <v>2079</v>
       </c>
       <c r="M7" s="22"/>
       <c r="N7" s="22"/>
@@ -33391,13 +33391,13 @@
         <v>30</v>
       </c>
       <c r="C8" s="25" t="s">
+        <v>2086</v>
+      </c>
+      <c r="D8" s="25" t="s">
         <v>2087</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="E8" s="25" t="s">
         <v>2088</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>2089</v>
       </c>
       <c r="F8" s="26">
         <v>8</v>
@@ -33413,13 +33413,13 @@
         <v>710</v>
       </c>
       <c r="J8" s="25" t="s">
+        <v>2077</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="25" t="s">
         <v>2078</v>
-      </c>
-      <c r="K8" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="25" t="s">
-        <v>2079</v>
       </c>
       <c r="M8" s="25" t="s">
         <v>139</v>
@@ -33437,13 +33437,13 @@
         <v>30</v>
       </c>
       <c r="C9" s="22" t="s">
+        <v>2089</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>2090</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="E9" s="22" t="s">
         <v>2091</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>2092</v>
       </c>
       <c r="F9" s="23">
         <v>6</v>
@@ -33459,13 +33459,13 @@
         <v>-25</v>
       </c>
       <c r="J9" s="22" t="s">
+        <v>2077</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
         <v>2078</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="22" t="s">
-        <v>2079</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -33485,13 +33485,13 @@
         <v>30</v>
       </c>
       <c r="C10" s="22" t="s">
+        <v>2092</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>2093</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="E10" s="22" t="s">
         <v>2094</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>2095</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>39</v>
@@ -33507,13 +33507,13 @@
         <v>820</v>
       </c>
       <c r="J10" s="22" t="s">
+        <v>2077</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
         <v>2078</v>
-      </c>
-      <c r="K10" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10" s="22" t="s">
-        <v>2079</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -33529,13 +33529,13 @@
         <v>30</v>
       </c>
       <c r="C11" s="22" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>2096</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="E11" s="22" t="s">
         <v>2097</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>2098</v>
       </c>
       <c r="F11" s="23">
         <v>7</v>
@@ -33551,13 +33551,13 @@
         <v>790</v>
       </c>
       <c r="J11" s="22" t="s">
+        <v>2077</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="22" t="s">
         <v>2078</v>
-      </c>
-      <c r="K11" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L11" s="22" t="s">
-        <v>2079</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
@@ -33573,13 +33573,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="22" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D12" s="22" t="s">
         <v>2099</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="E12" s="22" t="s">
         <v>2100</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>2101</v>
       </c>
       <c r="F12" s="23">
         <v>9</v>
@@ -33595,13 +33595,13 @@
         <v>890</v>
       </c>
       <c r="J12" s="22" t="s">
+        <v>2077</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
         <v>2078</v>
-      </c>
-      <c r="K12" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L12" s="22" t="s">
-        <v>2079</v>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
@@ -33619,11 +33619,11 @@
         <v>30</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="D13" s="22"/>
       <c r="E13" s="22" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>152</v>
@@ -33639,13 +33639,13 @@
         <v>660</v>
       </c>
       <c r="J13" s="22" t="s">
+        <v>2077</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="22" t="s">
         <v>2078</v>
-      </c>
-      <c r="K13" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L13" s="22" t="s">
-        <v>2079</v>
       </c>
       <c r="M13" s="22"/>
       <c r="N13" s="22"/>
@@ -33661,10 +33661,10 @@
         <v>30</v>
       </c>
       <c r="C14" s="22" t="s">
+        <v>2103</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>2104</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>2105</v>
       </c>
       <c r="E14" s="22" t="s">
         <v>1358</v>
@@ -33689,7 +33689,7 @@
         <v>34</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="M14" s="22"/>
       <c r="N14" s="22"/>
@@ -33705,13 +33705,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>2106</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="E15" s="22" t="s">
         <v>2107</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>2108</v>
       </c>
       <c r="F15" s="22" t="s">
         <v>98</v>
@@ -33733,7 +33733,7 @@
         <v>34</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="M15" s="22"/>
       <c r="N15" s="22"/>
@@ -33749,13 +33749,13 @@
         <v>30</v>
       </c>
       <c r="C16" s="22" t="s">
+        <v>2108</v>
+      </c>
+      <c r="D16" s="22" t="s">
         <v>2109</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="E16" s="22" t="s">
         <v>2110</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>2111</v>
       </c>
       <c r="F16" s="23">
         <v>12</v>
@@ -33777,7 +33777,7 @@
         <v>34</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="M16" s="22"/>
       <c r="N16" s="22"/>
@@ -33797,13 +33797,13 @@
         <v>30</v>
       </c>
       <c r="C17" s="22" t="s">
+        <v>2111</v>
+      </c>
+      <c r="D17" s="22" t="s">
         <v>2112</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="E17" s="22" t="s">
         <v>2113</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>2114</v>
       </c>
       <c r="F17" s="22" t="s">
         <v>98</v>
@@ -33825,7 +33825,7 @@
         <v>34</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="M17" s="22"/>
       <c r="N17" s="22"/>
@@ -33841,13 +33841,13 @@
         <v>30</v>
       </c>
       <c r="C18" s="22" t="s">
+        <v>2114</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>2115</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="E18" s="22" t="s">
         <v>2116</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>2117</v>
       </c>
       <c r="F18" s="23">
         <v>12</v>
@@ -33869,7 +33869,7 @@
         <v>34</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="M18" s="22"/>
       <c r="N18" s="22"/>
@@ -33891,7 +33891,7 @@
         <v>30</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="D19" s="22"/>
       <c r="E19" s="22" t="s">
@@ -33917,7 +33917,7 @@
         <v>34</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="M19" s="22"/>
       <c r="N19" s="22"/>
@@ -33933,13 +33933,13 @@
         <v>30</v>
       </c>
       <c r="C20" s="22" t="s">
+        <v>2118</v>
+      </c>
+      <c r="D20" s="22" t="s">
         <v>2119</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="E20" s="22" t="s">
         <v>2120</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>2121</v>
       </c>
       <c r="F20" s="22" t="s">
         <v>108</v>
@@ -33961,7 +33961,7 @@
         <v>34</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
@@ -33980,10 +33980,10 @@
         <v>558</v>
       </c>
       <c r="D21" s="22" t="s">
+        <v>2121</v>
+      </c>
+      <c r="E21" s="22" t="s">
         <v>2122</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>2123</v>
       </c>
       <c r="F21" s="23">
         <v>1</v>
@@ -34005,7 +34005,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="M21" s="22"/>
       <c r="N21" s="22"/>
@@ -34021,13 +34021,13 @@
         <v>30</v>
       </c>
       <c r="C22" s="22" t="s">
+        <v>2123</v>
+      </c>
+      <c r="D22" s="22" t="s">
         <v>2124</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="E22" s="22" t="s">
         <v>2125</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>2126</v>
       </c>
       <c r="F22" s="23">
         <v>1</v>
@@ -34049,7 +34049,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="M22" s="22"/>
       <c r="N22" s="22"/>
@@ -34065,13 +34065,13 @@
         <v>30</v>
       </c>
       <c r="C23" s="22" t="s">
+        <v>2126</v>
+      </c>
+      <c r="D23" s="22" t="s">
         <v>2127</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="E23" s="22" t="s">
         <v>2128</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>2129</v>
       </c>
       <c r="F23" s="23">
         <v>1</v>
@@ -34093,7 +34093,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="M23" s="22"/>
       <c r="N23" s="22"/>
@@ -34109,10 +34109,10 @@
         <v>30</v>
       </c>
       <c r="C24" s="22" t="s">
+        <v>2129</v>
+      </c>
+      <c r="D24" s="22" t="s">
         <v>2130</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>2131</v>
       </c>
       <c r="E24" s="22" t="s">
         <v>1487</v>
@@ -34137,7 +34137,7 @@
         <v>34</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="M24" s="22"/>
       <c r="N24" s="22"/>
@@ -34185,7 +34185,7 @@
         <v>34</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="M25" s="22"/>
       <c r="N25" s="22"/>
@@ -34207,11 +34207,11 @@
         <v>30</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="22" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="F26" s="22" t="s">
         <v>108</v>
@@ -34233,7 +34233,7 @@
         <v>34</v>
       </c>
       <c r="L26" s="22" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="M26" s="22"/>
       <c r="N26" s="22"/>
@@ -34299,7 +34299,7 @@
     </row>
     <row r="32" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H32" s="4" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>15</v>
@@ -34420,7 +34420,7 @@
         <v>424</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -34480,13 +34480,13 @@
         <v>30</v>
       </c>
       <c r="C3" s="22" t="s">
+        <v>2135</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>2136</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="E3" s="22" t="s">
         <v>2137</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>2138</v>
       </c>
       <c r="F3" s="23">
         <v>8</v>
@@ -34502,13 +34502,13 @@
         <v>690</v>
       </c>
       <c r="J3" s="22" t="s">
+        <v>2138</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
         <v>2139</v>
-      </c>
-      <c r="K3" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="22" t="s">
-        <v>2140</v>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="22"/>
@@ -34524,13 +34524,13 @@
         <v>30</v>
       </c>
       <c r="C4" s="22" t="s">
+        <v>2140</v>
+      </c>
+      <c r="D4" s="22" t="s">
         <v>2141</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="E4" s="22" t="s">
         <v>2142</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>2143</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>108</v>
@@ -34546,13 +34546,13 @@
         <v>1140</v>
       </c>
       <c r="J4" s="22" t="s">
+        <v>2138</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
         <v>2139</v>
-      </c>
-      <c r="K4" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="22" t="s">
-        <v>2140</v>
       </c>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
@@ -34568,13 +34568,13 @@
         <v>30</v>
       </c>
       <c r="C5" s="22" t="s">
+        <v>2143</v>
+      </c>
+      <c r="D5" s="22" t="s">
         <v>2144</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="E5" s="22" t="s">
         <v>2145</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>2146</v>
       </c>
       <c r="F5" s="23">
         <v>6</v>
@@ -34590,13 +34590,13 @@
         <v>-25</v>
       </c>
       <c r="J5" s="22" t="s">
+        <v>2138</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
         <v>2139</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>2140</v>
       </c>
       <c r="M5" s="22"/>
       <c r="N5" s="22"/>
@@ -34616,13 +34616,13 @@
         <v>30</v>
       </c>
       <c r="C6" s="22" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D6" s="22" t="s">
         <v>2147</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="E6" s="22" t="s">
         <v>2148</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>2149</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>59</v>
@@ -34638,13 +34638,13 @@
         <v>820</v>
       </c>
       <c r="J6" s="22" t="s">
+        <v>2138</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
         <v>2139</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>2140</v>
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="22"/>
@@ -34660,13 +34660,13 @@
         <v>30</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="F7" s="23">
         <v>8</v>
@@ -34682,13 +34682,13 @@
         <v>820</v>
       </c>
       <c r="J7" s="22" t="s">
+        <v>2138</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
         <v>2139</v>
-      </c>
-      <c r="K7" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="22" t="s">
-        <v>2140</v>
       </c>
       <c r="M7" s="22"/>
       <c r="N7" s="22"/>
@@ -34704,13 +34704,13 @@
         <v>30</v>
       </c>
       <c r="C8" s="22" t="s">
+        <v>2150</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>2151</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="E8" s="22" t="s">
         <v>2152</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>2153</v>
       </c>
       <c r="F8" s="23">
         <v>8</v>
@@ -34726,13 +34726,13 @@
         <v>820</v>
       </c>
       <c r="J8" s="22" t="s">
+        <v>2138</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
         <v>2139</v>
-      </c>
-      <c r="K8" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>2140</v>
       </c>
       <c r="M8" s="22"/>
       <c r="N8" s="22"/>
@@ -34748,13 +34748,13 @@
         <v>30</v>
       </c>
       <c r="C9" s="22" t="s">
+        <v>2153</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>2154</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="E9" s="22" t="s">
         <v>2155</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>2156</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>98</v>
@@ -34776,7 +34776,7 @@
         <v>34</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -34792,13 +34792,13 @@
         <v>30</v>
       </c>
       <c r="C10" s="22" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>2157</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="E10" s="22" t="s">
         <v>2158</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>2159</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>108</v>
@@ -34820,7 +34820,7 @@
         <v>34</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -34840,13 +34840,13 @@
         <v>30</v>
       </c>
       <c r="C11" s="22" t="s">
+        <v>2159</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>2160</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="E11" s="22" t="s">
         <v>2161</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>2162</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>94</v>
@@ -34868,7 +34868,7 @@
         <v>34</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M11" s="28" t="s">
         <v>180</v>
@@ -34890,13 +34890,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="F12" s="23">
         <v>12</v>
@@ -34918,7 +34918,7 @@
         <v>34</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
@@ -34938,13 +34938,13 @@
         <v>30</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>2163</v>
+      </c>
+      <c r="D13" s="22" t="s">
         <v>2164</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="E13" s="22" t="s">
         <v>2165</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>2166</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>108</v>
@@ -34966,7 +34966,7 @@
         <v>34</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M13" s="22"/>
       <c r="N13" s="22"/>
@@ -34982,13 +34982,13 @@
         <v>30</v>
       </c>
       <c r="C14" s="22" t="s">
+        <v>2166</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>2167</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="E14" s="22" t="s">
         <v>2168</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>2169</v>
       </c>
       <c r="F14" s="23">
         <v>12</v>
@@ -35010,7 +35010,7 @@
         <v>34</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M14" s="22"/>
       <c r="N14" s="22"/>
@@ -35033,10 +35033,10 @@
         <v>730</v>
       </c>
       <c r="D15" s="22" t="s">
+        <v>2169</v>
+      </c>
+      <c r="E15" s="22" t="s">
         <v>2170</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>2171</v>
       </c>
       <c r="F15" s="22" t="s">
         <v>90</v>
@@ -35058,7 +35058,7 @@
         <v>34</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M15" s="22"/>
       <c r="N15" s="22"/>
@@ -35074,10 +35074,10 @@
         <v>30</v>
       </c>
       <c r="C16" s="22" t="s">
+        <v>2171</v>
+      </c>
+      <c r="D16" s="22" t="s">
         <v>2172</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>2173</v>
       </c>
       <c r="E16" s="22" t="s">
         <v>244</v>
@@ -35102,7 +35102,7 @@
         <v>34</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M16" s="22"/>
       <c r="N16" s="22"/>
@@ -35122,13 +35122,13 @@
         <v>30</v>
       </c>
       <c r="C17" s="22" t="s">
+        <v>2173</v>
+      </c>
+      <c r="D17" s="22" t="s">
         <v>2174</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="E17" s="22" t="s">
         <v>2175</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>2176</v>
       </c>
       <c r="F17" s="22" t="s">
         <v>94</v>
@@ -35150,7 +35150,7 @@
         <v>34</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M17" s="22"/>
       <c r="N17" s="22"/>
@@ -35166,13 +35166,13 @@
         <v>30</v>
       </c>
       <c r="C18" s="22" t="s">
+        <v>2176</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>2177</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="E18" s="22" t="s">
         <v>2178</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>2179</v>
       </c>
       <c r="F18" s="22" t="s">
         <v>98</v>
@@ -35194,7 +35194,7 @@
         <v>34</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M18" s="22"/>
       <c r="N18" s="22"/>
@@ -35210,13 +35210,13 @@
         <v>30</v>
       </c>
       <c r="C19" s="22" t="s">
+        <v>2179</v>
+      </c>
+      <c r="D19" s="22" t="s">
         <v>2180</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="E19" s="22" t="s">
         <v>2181</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>2182</v>
       </c>
       <c r="F19" s="22" t="s">
         <v>98</v>
@@ -35238,10 +35238,10 @@
         <v>34</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M19" s="28" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="N19" s="22"/>
       <c r="O19" s="22"/>
@@ -35263,10 +35263,10 @@
         <v>124</v>
       </c>
       <c r="D20" s="22" t="s">
+        <v>2183</v>
+      </c>
+      <c r="E20" s="22" t="s">
         <v>2184</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>2185</v>
       </c>
       <c r="F20" s="22" t="s">
         <v>94</v>
@@ -35288,7 +35288,7 @@
         <v>34</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
@@ -35306,11 +35306,11 @@
         <v>30</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="D21" s="22"/>
       <c r="E21" s="22" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="F21" s="23">
         <v>12</v>
@@ -35332,7 +35332,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M21" s="22"/>
       <c r="N21" s="22"/>
@@ -35352,13 +35352,13 @@
         <v>30</v>
       </c>
       <c r="C22" s="22" t="s">
+        <v>2186</v>
+      </c>
+      <c r="D22" s="22" t="s">
         <v>2187</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="E22" s="22" t="s">
         <v>2188</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>2189</v>
       </c>
       <c r="F22" s="22" t="s">
         <v>108</v>
@@ -35380,7 +35380,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M22" s="22"/>
       <c r="N22" s="22"/>
@@ -35396,13 +35396,13 @@
         <v>30</v>
       </c>
       <c r="C23" s="22" t="s">
+        <v>2189</v>
+      </c>
+      <c r="D23" s="22" t="s">
         <v>2190</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="E23" s="22" t="s">
         <v>2191</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>2192</v>
       </c>
       <c r="F23" s="23">
         <v>1</v>
@@ -35424,7 +35424,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M23" s="22"/>
       <c r="N23" s="22"/>
@@ -35444,13 +35444,13 @@
         <v>30</v>
       </c>
       <c r="C24" s="22" t="s">
+        <v>2192</v>
+      </c>
+      <c r="D24" s="22" t="s">
         <v>2193</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="E24" s="22" t="s">
         <v>2194</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>2195</v>
       </c>
       <c r="F24" s="23">
         <v>1</v>
@@ -35472,10 +35472,10 @@
         <v>34</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M24" s="28" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="N24" s="22"/>
       <c r="O24" s="22"/>
@@ -35494,13 +35494,13 @@
         <v>30</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="D25" s="22" t="s">
+        <v>2196</v>
+      </c>
+      <c r="E25" s="22" t="s">
         <v>2197</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>2198</v>
       </c>
       <c r="F25" s="23">
         <v>1</v>
@@ -35522,10 +35522,10 @@
         <v>34</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M25" s="28" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="N25" s="22"/>
       <c r="O25" s="22"/>
@@ -35544,13 +35544,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="22" t="s">
+        <v>2199</v>
+      </c>
+      <c r="D26" s="22" t="s">
         <v>2200</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="E26" s="22" t="s">
         <v>2201</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>2202</v>
       </c>
       <c r="F26" s="23">
         <v>10</v>
@@ -35572,7 +35572,7 @@
         <v>34</v>
       </c>
       <c r="L26" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M26" s="22"/>
       <c r="N26" s="22"/>
@@ -35588,13 +35588,13 @@
         <v>30</v>
       </c>
       <c r="C27" s="22" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D27" s="22" t="s">
         <v>2203</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="E27" s="22" t="s">
         <v>2204</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>2205</v>
       </c>
       <c r="F27" s="22" t="s">
         <v>389</v>
@@ -35616,7 +35616,7 @@
         <v>34</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M27" s="22"/>
       <c r="N27" s="22"/>
@@ -35635,10 +35635,10 @@
         <v>1174</v>
       </c>
       <c r="D28" s="22" t="s">
+        <v>2205</v>
+      </c>
+      <c r="E28" s="22" t="s">
         <v>2206</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>2207</v>
       </c>
       <c r="F28" s="23">
         <v>1</v>
@@ -35660,7 +35660,7 @@
         <v>34</v>
       </c>
       <c r="L28" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
@@ -35725,12 +35725,12 @@
         <v>-820</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H34" s="4" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>15</v>
@@ -35829,13 +35829,13 @@
         <v>30</v>
       </c>
       <c r="B45" s="36" t="s">
+        <v>2179</v>
+      </c>
+      <c r="C45" s="36" t="s">
         <v>2180</v>
       </c>
-      <c r="C45" s="36" t="s">
+      <c r="D45" s="36" t="s">
         <v>2181</v>
-      </c>
-      <c r="D45" s="36" t="s">
-        <v>2182</v>
       </c>
       <c r="E45" s="36" t="s">
         <v>98</v>
@@ -35857,10 +35857,10 @@
         <v>34</v>
       </c>
       <c r="K45" s="36" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="L45" s="28" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -35868,13 +35868,13 @@
         <v>30</v>
       </c>
       <c r="B46" s="36" t="s">
+        <v>2192</v>
+      </c>
+      <c r="C46" s="36" t="s">
         <v>2193</v>
       </c>
-      <c r="C46" s="36" t="s">
+      <c r="D46" s="36" t="s">
         <v>2194</v>
-      </c>
-      <c r="D46" s="36" t="s">
-        <v>2195</v>
       </c>
       <c r="E46" s="37">
         <v>1</v>
@@ -35896,10 +35896,10 @@
         <v>34</v>
       </c>
       <c r="K46" s="36" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="L46" s="28" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -35907,13 +35907,13 @@
         <v>30</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="C47" s="36" t="s">
+        <v>2196</v>
+      </c>
+      <c r="D47" s="36" t="s">
         <v>2197</v>
-      </c>
-      <c r="D47" s="36" t="s">
-        <v>2198</v>
       </c>
       <c r="E47" s="37">
         <v>1</v>
@@ -35935,10 +35935,10 @@
         <v>34</v>
       </c>
       <c r="K47" s="36" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="L47" s="28" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
     </row>
   </sheetData>
@@ -35973,7 +35973,7 @@
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -36033,13 +36033,13 @@
         <v>30</v>
       </c>
       <c r="C3" s="22" t="s">
+        <v>2210</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>2211</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="E3" s="22" t="s">
         <v>2212</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>2213</v>
       </c>
       <c r="F3" s="23">
         <v>8</v>
@@ -36055,13 +36055,13 @@
         <v>890</v>
       </c>
       <c r="J3" s="22" t="s">
+        <v>2213</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
         <v>2214</v>
-      </c>
-      <c r="K3" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="22" t="s">
-        <v>2215</v>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="22"/>
@@ -36080,7 +36080,7 @@
         <v>149</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>151</v>
@@ -36099,13 +36099,13 @@
         <v>1840</v>
       </c>
       <c r="J4" s="22" t="s">
+        <v>2213</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
         <v>2214</v>
-      </c>
-      <c r="K4" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="22" t="s">
-        <v>2215</v>
       </c>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
@@ -36121,13 +36121,13 @@
         <v>30</v>
       </c>
       <c r="C5" s="22" t="s">
+        <v>2216</v>
+      </c>
+      <c r="D5" s="22" t="s">
         <v>2217</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="E5" s="22" t="s">
         <v>2218</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>2219</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>39</v>
@@ -36143,13 +36143,13 @@
         <v>1740</v>
       </c>
       <c r="J5" s="22" t="s">
+        <v>2213</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
         <v>2214</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>2215</v>
       </c>
       <c r="M5" s="22"/>
       <c r="N5" s="22"/>
@@ -36165,13 +36165,13 @@
         <v>30</v>
       </c>
       <c r="C6" s="22" t="s">
+        <v>2219</v>
+      </c>
+      <c r="D6" s="22" t="s">
         <v>2220</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="E6" s="22" t="s">
         <v>2221</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>2222</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>1324</v>
@@ -36187,13 +36187,13 @@
         <v>790</v>
       </c>
       <c r="J6" s="22" t="s">
+        <v>2213</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
         <v>2214</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>2215</v>
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="22"/>
@@ -36212,10 +36212,10 @@
         <v>298</v>
       </c>
       <c r="D7" s="22" t="s">
+        <v>2222</v>
+      </c>
+      <c r="E7" s="22" t="s">
         <v>2223</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>2224</v>
       </c>
       <c r="F7" s="23">
         <v>7</v>
@@ -36231,13 +36231,13 @@
         <v>1660</v>
       </c>
       <c r="J7" s="22" t="s">
+        <v>2213</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
         <v>2214</v>
-      </c>
-      <c r="K7" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="22" t="s">
-        <v>2215</v>
       </c>
       <c r="M7" s="22"/>
       <c r="N7" s="22"/>
@@ -36253,13 +36253,13 @@
         <v>30</v>
       </c>
       <c r="C8" s="22" t="s">
+        <v>2224</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>2225</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="E8" s="22" t="s">
         <v>2226</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>2227</v>
       </c>
       <c r="F8" s="23">
         <v>8</v>
@@ -36275,13 +36275,13 @@
         <v>590</v>
       </c>
       <c r="J8" s="22" t="s">
+        <v>2213</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
         <v>2214</v>
-      </c>
-      <c r="K8" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>2215</v>
       </c>
       <c r="M8" s="22"/>
       <c r="N8" s="22"/>
@@ -36297,13 +36297,13 @@
         <v>30</v>
       </c>
       <c r="C9" s="22" t="s">
+        <v>2227</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>2228</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="E9" s="22" t="s">
         <v>2229</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>2230</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>39</v>
@@ -36319,13 +36319,13 @@
         <v>8494</v>
       </c>
       <c r="J9" s="22" t="s">
+        <v>2213</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
         <v>2214</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="22" t="s">
-        <v>2215</v>
       </c>
       <c r="M9" s="28" t="s">
         <v>180</v>
@@ -36347,13 +36347,13 @@
         <v>30</v>
       </c>
       <c r="C10" s="22" t="s">
+        <v>2230</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>2231</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="E10" s="22" t="s">
         <v>2232</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>2233</v>
       </c>
       <c r="F10" s="23">
         <v>8</v>
@@ -36369,13 +36369,13 @@
         <v>2585</v>
       </c>
       <c r="J10" s="22" t="s">
+        <v>2213</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="22" t="s">
         <v>2214</v>
-      </c>
-      <c r="K10" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10" s="22" t="s">
-        <v>2215</v>
       </c>
       <c r="M10" s="28" t="s">
         <v>180</v>
@@ -36397,13 +36397,13 @@
         <v>30</v>
       </c>
       <c r="C11" s="22" t="s">
+        <v>2233</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>2234</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="E11" s="22" t="s">
         <v>2235</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>2236</v>
       </c>
       <c r="F11" s="23">
         <v>12</v>
@@ -36425,7 +36425,7 @@
         <v>34</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
@@ -36445,13 +36445,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="22" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D12" s="22" t="s">
         <v>2237</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="E12" s="22" t="s">
         <v>2238</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>2239</v>
       </c>
       <c r="F12" s="23">
         <v>12</v>
@@ -36473,7 +36473,7 @@
         <v>34</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
@@ -36489,13 +36489,13 @@
         <v>30</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>2239</v>
+      </c>
+      <c r="D13" s="22" t="s">
         <v>2240</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="E13" s="22" t="s">
         <v>2241</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>2242</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>90</v>
@@ -36517,7 +36517,7 @@
         <v>34</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="M13" s="22"/>
       <c r="N13" s="22"/>
@@ -36533,13 +36533,13 @@
         <v>30</v>
       </c>
       <c r="C14" s="22" t="s">
+        <v>2242</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>2243</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="E14" s="22" t="s">
         <v>2244</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>2245</v>
       </c>
       <c r="F14" s="22" t="s">
         <v>94</v>
@@ -36561,7 +36561,7 @@
         <v>34</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="M14" s="22"/>
       <c r="N14" s="22"/>
@@ -36577,13 +36577,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>2245</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>2246</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="E15" s="22" t="s">
         <v>2247</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>2248</v>
       </c>
       <c r="F15" s="22" t="s">
         <v>108</v>
@@ -36605,7 +36605,7 @@
         <v>34</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="M15" s="22"/>
       <c r="N15" s="22"/>
@@ -36621,13 +36621,13 @@
         <v>30</v>
       </c>
       <c r="C16" s="22" t="s">
+        <v>2248</v>
+      </c>
+      <c r="D16" s="22" t="s">
         <v>2249</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="E16" s="22" t="s">
         <v>2250</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>2251</v>
       </c>
       <c r="F16" s="23">
         <v>12</v>
@@ -36649,7 +36649,7 @@
         <v>34</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="M16" s="22"/>
       <c r="N16" s="22"/>
@@ -36668,7 +36668,7 @@
         <v>1377</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="E17" s="22" t="s">
         <v>1379</v>
@@ -36693,7 +36693,7 @@
         <v>34</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="M17" s="22"/>
       <c r="N17" s="22"/>
@@ -36709,13 +36709,13 @@
         <v>30</v>
       </c>
       <c r="C18" s="22" t="s">
+        <v>2252</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>2253</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="E18" s="22" t="s">
         <v>2254</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>2255</v>
       </c>
       <c r="F18" s="23">
         <v>2</v>
@@ -36737,7 +36737,7 @@
         <v>34</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="M18" s="22"/>
       <c r="N18" s="22"/>
@@ -36753,10 +36753,10 @@
         <v>30</v>
       </c>
       <c r="C19" s="22" t="s">
+        <v>2255</v>
+      </c>
+      <c r="D19" s="22" t="s">
         <v>2256</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>2257</v>
       </c>
       <c r="E19" s="22" t="s">
         <v>489</v>
@@ -36781,7 +36781,7 @@
         <v>34</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="M19" s="22"/>
       <c r="N19" s="22"/>
@@ -36807,7 +36807,7 @@
       </c>
       <c r="D20" s="22"/>
       <c r="E20" s="22" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="F20" s="22" t="s">
         <v>90</v>
@@ -36829,7 +36829,7 @@
         <v>34</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
@@ -36845,13 +36845,13 @@
         <v>30</v>
       </c>
       <c r="C21" s="22" t="s">
+        <v>2258</v>
+      </c>
+      <c r="D21" s="22" t="s">
         <v>2259</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="E21" s="22" t="s">
         <v>2260</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>2261</v>
       </c>
       <c r="F21" s="23">
         <v>10</v>
@@ -36873,7 +36873,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="M21" s="22"/>
       <c r="N21" s="22"/>
@@ -36889,13 +36889,13 @@
         <v>30</v>
       </c>
       <c r="C22" s="22" t="s">
+        <v>2261</v>
+      </c>
+      <c r="D22" s="22" t="s">
         <v>2262</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="E22" s="22" t="s">
         <v>2263</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>2264</v>
       </c>
       <c r="F22" s="22" t="s">
         <v>389</v>
@@ -36917,7 +36917,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="M22" s="22"/>
       <c r="N22" s="22"/>
@@ -36933,13 +36933,13 @@
         <v>30</v>
       </c>
       <c r="C23" s="22" t="s">
+        <v>2264</v>
+      </c>
+      <c r="D23" s="22" t="s">
         <v>2265</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="E23" s="22" t="s">
         <v>2266</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>2267</v>
       </c>
       <c r="F23" s="23">
         <v>10</v>
@@ -36961,7 +36961,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="M23" s="22"/>
       <c r="N23" s="22"/>
@@ -36984,7 +36984,7 @@
         <v>127</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="E24" s="22" t="s">
         <v>1206</v>
@@ -37009,7 +37009,7 @@
         <v>34</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="M24" s="22"/>
       <c r="N24" s="22"/>
@@ -37071,7 +37071,7 @@
     </row>
     <row r="30" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H30" s="4" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>15</v>
@@ -37192,7 +37192,7 @@
         <v>717</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -37252,13 +37252,13 @@
         <v>30</v>
       </c>
       <c r="C3" s="22" t="s">
+        <v>2268</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>2269</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="E3" s="22" t="s">
         <v>2270</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>2271</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>59</v>
@@ -37274,13 +37274,13 @@
         <v>820</v>
       </c>
       <c r="J3" s="22" t="s">
+        <v>2271</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="22" t="s">
         <v>2272</v>
-      </c>
-      <c r="K3" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="22" t="s">
-        <v>2273</v>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="22"/>
@@ -37296,10 +37296,10 @@
         <v>30</v>
       </c>
       <c r="C4" s="22" t="s">
+        <v>2273</v>
+      </c>
+      <c r="D4" s="22" t="s">
         <v>2274</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>2275</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>1039</v>
@@ -37318,13 +37318,13 @@
         <v>890</v>
       </c>
       <c r="J4" s="22" t="s">
+        <v>2271</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
         <v>2272</v>
-      </c>
-      <c r="K4" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="22" t="s">
-        <v>2273</v>
       </c>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
@@ -37340,13 +37340,13 @@
         <v>30</v>
       </c>
       <c r="C5" s="22" t="s">
+        <v>2275</v>
+      </c>
+      <c r="D5" s="22" t="s">
         <v>2276</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="E5" s="22" t="s">
         <v>2277</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>2278</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>39</v>
@@ -37362,13 +37362,13 @@
         <v>1610</v>
       </c>
       <c r="J5" s="22" t="s">
+        <v>2271</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="22" t="s">
         <v>2272</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>2273</v>
       </c>
       <c r="M5" s="22"/>
       <c r="N5" s="22"/>
@@ -37384,13 +37384,13 @@
         <v>30</v>
       </c>
       <c r="C6" s="22" t="s">
+        <v>2278</v>
+      </c>
+      <c r="D6" s="22" t="s">
         <v>2279</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="E6" s="22" t="s">
         <v>2280</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>2281</v>
       </c>
       <c r="F6" s="23">
         <v>8</v>
@@ -37406,13 +37406,13 @@
         <v>-30</v>
       </c>
       <c r="J6" s="22" t="s">
+        <v>2271</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="22" t="s">
         <v>2272</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>2273</v>
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="22"/>
@@ -37435,7 +37435,7 @@
         <v>1432</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E7" s="22" t="s">
         <v>1434</v>
@@ -37454,13 +37454,13 @@
         <v>-30</v>
       </c>
       <c r="J7" s="22" t="s">
+        <v>2271</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="22" t="s">
         <v>2272</v>
-      </c>
-      <c r="K7" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="22" t="s">
-        <v>2273</v>
       </c>
       <c r="M7" s="22"/>
       <c r="N7" s="22"/>
@@ -37480,13 +37480,13 @@
         <v>30</v>
       </c>
       <c r="C8" s="22" t="s">
+        <v>2282</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>2283</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="E8" s="22" t="s">
         <v>2284</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>2285</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>39</v>
@@ -37502,13 +37502,13 @@
         <v>-30</v>
       </c>
       <c r="J8" s="22" t="s">
+        <v>2271</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
         <v>2272</v>
-      </c>
-      <c r="K8" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>2273</v>
       </c>
       <c r="M8" s="22"/>
       <c r="N8" s="22"/>
@@ -37550,13 +37550,13 @@
         <v>-30</v>
       </c>
       <c r="J9" s="22" t="s">
+        <v>2271</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="22" t="s">
         <v>2272</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="22" t="s">
-        <v>2273</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -37576,13 +37576,13 @@
         <v>30</v>
       </c>
       <c r="C10" s="22" t="s">
+        <v>2285</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>2286</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="E10" s="22" t="s">
         <v>2287</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>2288</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>90</v>
@@ -37604,7 +37604,7 @@
         <v>34</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -37620,13 +37620,13 @@
         <v>30</v>
       </c>
       <c r="C11" s="22" t="s">
+        <v>2288</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>2289</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="E11" s="22" t="s">
         <v>2290</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>2291</v>
       </c>
       <c r="F11" s="23">
         <v>2</v>
@@ -37648,7 +37648,7 @@
         <v>34</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
@@ -37664,13 +37664,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="22" t="s">
+        <v>2291</v>
+      </c>
+      <c r="D12" s="22" t="s">
         <v>2292</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="E12" s="22" t="s">
         <v>2293</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>2294</v>
       </c>
       <c r="F12" s="23">
         <v>2</v>
@@ -37692,7 +37692,7 @@
         <v>34</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
@@ -37708,13 +37708,13 @@
         <v>30</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>2294</v>
+      </c>
+      <c r="D13" s="22" t="s">
         <v>2295</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="E13" s="22" t="s">
         <v>2296</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>2297</v>
       </c>
       <c r="F13" s="23">
         <v>2</v>
@@ -37736,7 +37736,7 @@
         <v>34</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M13" s="22"/>
       <c r="N13" s="22"/>
@@ -37752,13 +37752,13 @@
         <v>30</v>
       </c>
       <c r="C14" s="22" t="s">
+        <v>2297</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>2298</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="E14" s="22" t="s">
         <v>2299</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>2300</v>
       </c>
       <c r="F14" s="22" t="s">
         <v>94</v>
@@ -37780,7 +37780,7 @@
         <v>34</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M14" s="22"/>
       <c r="N14" s="22"/>
@@ -37796,13 +37796,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>2300</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>2301</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="E15" s="22" t="s">
         <v>2302</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>2303</v>
       </c>
       <c r="F15" s="23">
         <v>2</v>
@@ -37824,7 +37824,7 @@
         <v>34</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M15" s="22"/>
       <c r="N15" s="22"/>
@@ -37840,13 +37840,13 @@
         <v>30</v>
       </c>
       <c r="C16" s="22" t="s">
+        <v>2303</v>
+      </c>
+      <c r="D16" s="22" t="s">
         <v>2304</v>
       </c>
-      <c r="D16" s="22" t="s">
-        <v>2305</v>
-      </c>
       <c r="E16" s="22" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="F16" s="23">
         <v>12</v>
@@ -37868,7 +37868,7 @@
         <v>34</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M16" s="22"/>
       <c r="N16" s="22"/>
@@ -37888,13 +37888,13 @@
         <v>30</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="D17" s="25" t="s">
+        <v>2305</v>
+      </c>
+      <c r="E17" s="25" t="s">
         <v>2306</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>2307</v>
       </c>
       <c r="F17" s="26">
         <v>12</v>
@@ -37916,7 +37916,7 @@
         <v>34</v>
       </c>
       <c r="L17" s="25" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M17" s="25" t="s">
         <v>139</v>
@@ -37934,10 +37934,10 @@
         <v>30</v>
       </c>
       <c r="C18" s="22" t="s">
+        <v>2307</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>2308</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>2309</v>
       </c>
       <c r="E18" s="22" t="s">
         <v>489</v>
@@ -37962,7 +37962,7 @@
         <v>34</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M18" s="28" t="s">
         <v>360</v>
@@ -37984,10 +37984,10 @@
         <v>30</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="E19" s="22" t="s">
         <v>489</v>
@@ -38012,7 +38012,7 @@
         <v>34</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M19" s="28" t="s">
         <v>360</v>
@@ -38034,13 +38034,13 @@
         <v>30</v>
       </c>
       <c r="C20" s="22" t="s">
+        <v>2310</v>
+      </c>
+      <c r="D20" s="22" t="s">
         <v>2311</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="E20" s="22" t="s">
         <v>2312</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>2313</v>
       </c>
       <c r="F20" s="22" t="s">
         <v>90</v>
@@ -38062,7 +38062,7 @@
         <v>34</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
@@ -38078,13 +38078,13 @@
         <v>30</v>
       </c>
       <c r="C21" s="22" t="s">
+        <v>2313</v>
+      </c>
+      <c r="D21" s="22" t="s">
         <v>2314</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="E21" s="22" t="s">
         <v>2315</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>2316</v>
       </c>
       <c r="F21" s="22" t="s">
         <v>90</v>
@@ -38106,7 +38106,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M21" s="22"/>
       <c r="N21" s="22"/>
@@ -38126,13 +38126,13 @@
         <v>30</v>
       </c>
       <c r="C22" s="22" t="s">
+        <v>2316</v>
+      </c>
+      <c r="D22" s="22" t="s">
         <v>2317</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="E22" s="22" t="s">
         <v>2318</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>2319</v>
       </c>
       <c r="F22" s="23">
         <v>7</v>
@@ -38154,7 +38154,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M22" s="22"/>
       <c r="N22" s="22"/>
@@ -38174,13 +38174,13 @@
         <v>30</v>
       </c>
       <c r="C23" s="22" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D23" s="22" t="s">
         <v>2320</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="E23" s="22" t="s">
         <v>2321</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>2322</v>
       </c>
       <c r="F23" s="23">
         <v>7</v>
@@ -38202,7 +38202,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M23" s="22"/>
       <c r="N23" s="22"/>
@@ -38218,13 +38218,13 @@
         <v>30</v>
       </c>
       <c r="C24" s="22" t="s">
+        <v>2322</v>
+      </c>
+      <c r="D24" s="22" t="s">
         <v>2323</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="E24" s="22" t="s">
         <v>2324</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>2325</v>
       </c>
       <c r="F24" s="23">
         <v>1</v>
@@ -38246,7 +38246,7 @@
         <v>34</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M24" s="22"/>
       <c r="N24" s="22"/>
@@ -38266,13 +38266,13 @@
         <v>30</v>
       </c>
       <c r="C25" s="22" t="s">
+        <v>2325</v>
+      </c>
+      <c r="D25" s="22" t="s">
         <v>2326</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="E25" s="22" t="s">
         <v>2327</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>2328</v>
       </c>
       <c r="F25" s="22" t="s">
         <v>147</v>
@@ -38294,7 +38294,7 @@
         <v>34</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M25" s="22"/>
       <c r="N25" s="22"/>
@@ -38310,13 +38310,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="22" t="s">
+        <v>2328</v>
+      </c>
+      <c r="D26" s="22" t="s">
         <v>2329</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="E26" s="22" t="s">
         <v>2330</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>2331</v>
       </c>
       <c r="F26" s="23">
         <v>7</v>
@@ -38338,7 +38338,7 @@
         <v>34</v>
       </c>
       <c r="L26" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M26" s="22"/>
       <c r="N26" s="22"/>
@@ -38354,13 +38354,13 @@
         <v>30</v>
       </c>
       <c r="C27" s="22" t="s">
+        <v>2331</v>
+      </c>
+      <c r="D27" s="22" t="s">
         <v>2332</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="E27" s="22" t="s">
         <v>2333</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>2334</v>
       </c>
       <c r="F27" s="23">
         <v>1</v>
@@ -38382,7 +38382,7 @@
         <v>34</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M27" s="22"/>
       <c r="N27" s="22"/>
@@ -38405,7 +38405,7 @@
         <v>193</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="E28" s="22" t="s">
         <v>195</v>
@@ -38430,7 +38430,7 @@
         <v>34</v>
       </c>
       <c r="L28" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
@@ -38453,7 +38453,7 @@
         <v>1198</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="E29" s="22" t="s">
         <v>1200</v>
@@ -38478,7 +38478,7 @@
         <v>34</v>
       </c>
       <c r="L29" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M29" s="22"/>
       <c r="N29" s="22"/>
@@ -38494,13 +38494,13 @@
         <v>30</v>
       </c>
       <c r="C30" s="22" t="s">
+        <v>2336</v>
+      </c>
+      <c r="D30" s="22" t="s">
         <v>2337</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="E30" s="22" t="s">
         <v>2338</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>2339</v>
       </c>
       <c r="F30" s="23">
         <v>7</v>
@@ -38522,7 +38522,7 @@
         <v>34</v>
       </c>
       <c r="L30" s="22" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M30" s="22"/>
       <c r="N30" s="22"/>
@@ -38538,16 +38538,16 @@
         <v>30</v>
       </c>
       <c r="C31" s="53" t="s">
+        <v>2340</v>
+      </c>
+      <c r="D31" s="53" t="s">
         <v>2341</v>
       </c>
-      <c r="D31" s="53" t="s">
+      <c r="E31" s="53" t="s">
         <v>2342</v>
       </c>
-      <c r="E31" s="53" t="s">
+      <c r="F31" s="53" t="s">
         <v>2343</v>
-      </c>
-      <c r="F31" s="53" t="s">
-        <v>2344</v>
       </c>
       <c r="G31" s="54">
         <v>570</v>
@@ -38566,17 +38566,17 @@
         <v>34</v>
       </c>
       <c r="L31" s="53" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="M31" s="53" t="s">
+        <v>2344</v>
+      </c>
+      <c r="N31" s="53" t="s">
         <v>2345</v>
-      </c>
-      <c r="N31" s="53" t="s">
-        <v>2346</v>
       </c>
       <c r="O31" s="53"/>
       <c r="P31" s="53" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="Q31" s="53">
         <v>1</v>
@@ -38637,12 +38637,12 @@
         <v>-570</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="37" spans="7:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H37" s="4" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="I37" s="5" t="s">
         <v>15</v>
